--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$825</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$842</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O825"/>
+  <dimension ref="A1:O842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（23都道府県／821校）</t>
+          <t>私立高等学校 架電リスト（24都道府県／838校）</t>
         </is>
       </c>
     </row>
@@ -42233,22 +42233,22 @@
       </c>
       <c r="B710" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C710" s="5" t="inlineStr">
         <is>
-          <t>磐田市</t>
+          <t>岐阜市</t>
         </is>
       </c>
       <c r="D710" s="5" t="inlineStr">
         <is>
-          <t>磐田東高等学校</t>
+          <t>鶯谷高等学校</t>
         </is>
       </c>
       <c r="E710" s="6" t="inlineStr">
         <is>
-          <t>0538-32-6118</t>
+          <t>058-265-7571</t>
         </is>
       </c>
       <c r="F710" s="7" t="inlineStr">
@@ -42258,7 +42258,7 @@
       </c>
       <c r="G710" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H710" s="8" t="n"/>
@@ -42272,12 +42272,12 @@
       <c r="L710" s="9" t="n"/>
       <c r="M710" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>代表として掲載。中高共通</t>
         </is>
       </c>
       <c r="N710" s="11" t="inlineStr">
         <is>
-          <t>https://www.iwatahigashi-h.ed.jp/ ; https://www.mapion.co.jp/phonebook/M11004/22211/ILSP0000041612_ipclm/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/21201/ILSP0000041163_ipclm/ ; https://www.inter-edu.com/schools/school/1452</t>
         </is>
       </c>
       <c r="O710" s="12" t="inlineStr">
@@ -42292,22 +42292,22 @@
       </c>
       <c r="B711" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C711" s="5" t="inlineStr">
         <is>
-          <t>浜松市中央区</t>
+          <t>大垣市</t>
         </is>
       </c>
       <c r="D711" s="5" t="inlineStr">
         <is>
-          <t>オイスカ浜松国際高等学校</t>
+          <t>大垣日本大学高等学校</t>
         </is>
       </c>
       <c r="E711" s="6" t="inlineStr">
         <is>
-          <t>053-486-3011</t>
+          <t>0584-81-7323</t>
         </is>
       </c>
       <c r="F711" s="7" t="inlineStr">
@@ -42331,12 +42331,12 @@
       <c r="L711" s="9" t="n"/>
       <c r="M711" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。所在地は浜松市中央区</t>
+          <t>公式サイトと岐阜県の資料で一致</t>
         </is>
       </c>
       <c r="N711" s="11" t="inlineStr">
         <is>
-          <t>https://www.oisca.ed.jp/school/access/ ; https://www.minkou.jp/hischool/school/646/</t>
+          <t>https://www.ogaki.ac.jp/ ; https://www.gifu-net.ed.jp/ssd/sien/guide/gakkou/309.pdf</t>
         </is>
       </c>
       <c r="O711" s="12" t="inlineStr">
@@ -42351,22 +42351,22 @@
       </c>
       <c r="B712" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C712" s="5" t="inlineStr">
         <is>
-          <t>沼津市</t>
+          <t>岐阜市</t>
         </is>
       </c>
       <c r="D712" s="5" t="inlineStr">
         <is>
-          <t>加藤学園暁秀高等学校</t>
+          <t>ぎふ国際高等学校</t>
         </is>
       </c>
       <c r="E712" s="6" t="inlineStr">
         <is>
-          <t>055-924-1900</t>
+          <t>058-251-8181</t>
         </is>
       </c>
       <c r="F712" s="7" t="inlineStr">
@@ -42390,12 +42390,12 @@
       <c r="L712" s="9" t="n"/>
       <c r="M712" s="10" t="inlineStr">
         <is>
-          <t>中高共通。加藤学園高校とは別の学校</t>
+          <t>通信制。公式サイトと岐阜県の資料で一致</t>
         </is>
       </c>
       <c r="N712" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/22203/ILSP0000041290_ipclm/ ; https://school.js88.com/scl_h/22009120</t>
+          <t>https://gifu-kokusai.denpa.jp/ ; https://www.gifu-net.ed.jp/ssd/sien/guide/gakkou/318.pdf</t>
         </is>
       </c>
       <c r="O712" s="12" t="inlineStr">
@@ -42410,22 +42410,22 @@
       </c>
       <c r="B713" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C713" s="5" t="inlineStr">
         <is>
-          <t>沼津市</t>
+          <t>岐阜市</t>
         </is>
       </c>
       <c r="D713" s="5" t="inlineStr">
         <is>
-          <t>加藤学園高等学校</t>
+          <t>岐阜聖徳学園高等学校</t>
         </is>
       </c>
       <c r="E713" s="6" t="inlineStr">
         <is>
-          <t>055-921-0347</t>
+          <t>058-271-5451</t>
         </is>
       </c>
       <c r="F713" s="7" t="inlineStr">
@@ -42435,7 +42435,7 @@
       </c>
       <c r="G713" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H713" s="8" t="n"/>
@@ -42449,12 +42449,12 @@
       <c r="L713" s="9" t="n"/>
       <c r="M713" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載。加藤学園暁秀とは別の学校</t>
+          <t>公式サイトで確認。法人本部（058-279-3300）とは別</t>
         </is>
       </c>
       <c r="N713" s="11" t="inlineStr">
         <is>
-          <t>https://www.katogaku.jp/KatohHS/</t>
+          <t>https://www.shotoku.jp/access/index.html</t>
         </is>
       </c>
       <c r="O713" s="12" t="inlineStr">
@@ -42469,22 +42469,22 @@
       </c>
       <c r="B714" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C714" s="5" t="inlineStr">
         <is>
-          <t>吉田町</t>
+          <t>岐南町</t>
         </is>
       </c>
       <c r="D714" s="5" t="inlineStr">
         <is>
-          <t>キラリ高等学校</t>
+          <t>岐阜女子高等学校</t>
         </is>
       </c>
       <c r="E714" s="6" t="inlineStr">
         <is>
-          <t>0548-33-4976</t>
+          <t>058-245-2670</t>
         </is>
       </c>
       <c r="F714" s="7" t="inlineStr">
@@ -42494,7 +42494,7 @@
       </c>
       <c r="G714" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H714" s="8" t="n"/>
@@ -42508,12 +42508,12 @@
       <c r="L714" s="9" t="n"/>
       <c r="M714" s="10" t="inlineStr">
         <is>
-          <t>通信制。吉田本校の番号（公式サイト）</t>
+          <t>公式サイトに「代表」と記載</t>
         </is>
       </c>
       <c r="N714" s="11" t="inlineStr">
         <is>
-          <t>https://www.kirari-highschool.jp/introduction/access/</t>
+          <t>https://www.gifujoshi.ed.jp/info/</t>
         </is>
       </c>
       <c r="O714" s="12" t="inlineStr">
@@ -42528,22 +42528,22 @@
       </c>
       <c r="B715" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C715" s="5" t="inlineStr">
         <is>
-          <t>御殿場市</t>
+          <t>本巣市</t>
         </is>
       </c>
       <c r="D715" s="5" t="inlineStr">
         <is>
-          <t>御殿場西高等学校</t>
+          <t>岐阜第一高等学校</t>
         </is>
       </c>
       <c r="E715" s="6" t="inlineStr">
         <is>
-          <t>0550-89-2466</t>
+          <t>058-324-2161</t>
         </is>
       </c>
       <c r="F715" s="7" t="inlineStr">
@@ -42553,7 +42553,7 @@
       </c>
       <c r="G715" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H715" s="8" t="n"/>
@@ -42567,12 +42567,12 @@
       <c r="L715" s="9" t="n"/>
       <c r="M715" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>2つのサイトで一致、公式未確認</t>
         </is>
       </c>
       <c r="N715" s="11" t="inlineStr">
         <is>
-          <t>https://gotembanishi-h.ed.jp/access/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/21218/ILSP0000041106_ipclm/ ; https://www.iezo.net/tiikinavi/gifu/motosu/</t>
         </is>
       </c>
       <c r="O715" s="12" t="inlineStr">
@@ -42587,22 +42587,22 @@
       </c>
       <c r="B716" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C716" s="5" t="inlineStr">
         <is>
-          <t>静岡市葵区</t>
+          <t>岐阜市</t>
         </is>
       </c>
       <c r="D716" s="5" t="inlineStr">
         <is>
-          <t>静岡英和女学院高等学校</t>
+          <t>岐阜東高等学校</t>
         </is>
       </c>
       <c r="E716" s="6" t="inlineStr">
         <is>
-          <t>054-254-7401</t>
+          <t>058-246-2956</t>
         </is>
       </c>
       <c r="F716" s="7" t="inlineStr">
@@ -42626,12 +42626,12 @@
       <c r="L716" s="9" t="n"/>
       <c r="M716" s="10" t="inlineStr">
         <is>
-          <t>中高共通。2つのサイトで一致</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N716" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000040742_ipclm/ ; https://shizu-hsmap.com/3460/</t>
+          <t>https://www.gito.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O716" s="12" t="inlineStr">
@@ -42646,22 +42646,22 @@
       </c>
       <c r="B717" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C717" s="5" t="inlineStr">
         <is>
-          <t>静岡市葵区</t>
+          <t>岐阜市</t>
         </is>
       </c>
       <c r="D717" s="5" t="inlineStr">
         <is>
-          <t>静岡学園高等学校</t>
+          <t>城南高等学校</t>
         </is>
       </c>
       <c r="E717" s="6" t="inlineStr">
         <is>
-          <t>054-200-0191</t>
+          <t>058-240-3335</t>
         </is>
       </c>
       <c r="F717" s="7" t="inlineStr">
@@ -42685,12 +42685,12 @@
       <c r="L717" s="9" t="n"/>
       <c r="M717" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>通信制。公式サイトで確認（城南高等専修学校と共通）</t>
         </is>
       </c>
       <c r="N717" s="11" t="inlineStr">
         <is>
-          <t>https://www.shizugaku.ed.jp/</t>
+          <t>https://hope.sc/access/</t>
         </is>
       </c>
       <c r="O717" s="12" t="inlineStr">
@@ -42705,22 +42705,22 @@
       </c>
       <c r="B718" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C718" s="5" t="inlineStr">
         <is>
-          <t>静岡市葵区</t>
+          <t>岐阜市</t>
         </is>
       </c>
       <c r="D718" s="5" t="inlineStr">
         <is>
-          <t>静岡北高等学校</t>
+          <t>済美高等学校（岐阜県）</t>
         </is>
       </c>
       <c r="E718" s="6" t="inlineStr">
         <is>
-          <t>054-261-5801</t>
+          <t>058-271-0345</t>
         </is>
       </c>
       <c r="F718" s="7" t="inlineStr">
@@ -42744,12 +42744,12 @@
       <c r="L718" s="9" t="n"/>
       <c r="M718" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載。中学校は054-267-6151</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N718" s="11" t="inlineStr">
         <is>
-          <t>https://shizukita.jp/contact/</t>
+          <t>https://www.gifu-seibi.ed.jp/access/</t>
         </is>
       </c>
       <c r="O718" s="12" t="inlineStr">
@@ -42764,22 +42764,22 @@
       </c>
       <c r="B719" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C719" s="5" t="inlineStr">
         <is>
-          <t>浜松市中央区</t>
+          <t>岐阜市</t>
         </is>
       </c>
       <c r="D719" s="5" t="inlineStr">
         <is>
-          <t>静岡県西遠女子学園高等学校</t>
+          <t>聖マリア女学院高等学校</t>
         </is>
       </c>
       <c r="E719" s="6" t="inlineStr">
         <is>
-          <t>053-461-0374</t>
+          <t>058-229-1102</t>
         </is>
       </c>
       <c r="F719" s="7" t="inlineStr">
@@ -42803,12 +42803,12 @@
       <c r="L719" s="9" t="n"/>
       <c r="M719" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通。所在地は浜松市中央区</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N719" s="11" t="inlineStr">
         <is>
-          <t>https://www.seien.ed.jp/</t>
+          <t>https://maria.ed.jp/access/</t>
         </is>
       </c>
       <c r="O719" s="12" t="inlineStr">
@@ -42823,22 +42823,22 @@
       </c>
       <c r="B720" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C720" s="5" t="inlineStr">
         <is>
-          <t>富士市</t>
+          <t>高山市</t>
         </is>
       </c>
       <c r="D720" s="5" t="inlineStr">
         <is>
-          <t>静岡県富士見高等学校</t>
+          <t>高山西高等学校</t>
         </is>
       </c>
       <c r="E720" s="6" t="inlineStr">
         <is>
-          <t>0545-61-0250</t>
+          <t>0577-32-2590</t>
         </is>
       </c>
       <c r="F720" s="7" t="inlineStr">
@@ -42862,12 +42862,12 @@
       <c r="L720" s="9" t="n"/>
       <c r="M720" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N720" s="11" t="inlineStr">
         <is>
-          <t>https://fujimi.ed.jp/</t>
+          <t>https://takanishi.ed.jp/</t>
         </is>
       </c>
       <c r="O720" s="12" t="inlineStr">
@@ -42882,22 +42882,22 @@
       </c>
       <c r="B721" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C721" s="5" t="inlineStr">
         <is>
-          <t>静岡市清水区</t>
+          <t>多治見市</t>
         </is>
       </c>
       <c r="D721" s="5" t="inlineStr">
         <is>
-          <t>静岡サレジオ高等学校</t>
+          <t>多治見西高等学校</t>
         </is>
       </c>
       <c r="E721" s="6" t="inlineStr">
         <is>
-          <t>054-345-2296</t>
+          <t>0572-27-2547</t>
         </is>
       </c>
       <c r="F721" s="7" t="inlineStr">
@@ -42907,7 +42907,7 @@
       </c>
       <c r="G721" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H721" s="8" t="n"/>
@@ -42926,7 +42926,7 @@
       </c>
       <c r="N721" s="11" t="inlineStr">
         <is>
-          <t>https://ssalesio.ac.jp/high/contact/</t>
+          <t>https://www.tajiminishi.ed.jp/high/attending-school/</t>
         </is>
       </c>
       <c r="O721" s="12" t="inlineStr">
@@ -42941,22 +42941,22 @@
       </c>
       <c r="B722" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C722" s="5" t="inlineStr">
         <is>
-          <t>静岡市駿河区</t>
+          <t>瑞浪市</t>
         </is>
       </c>
       <c r="D722" s="5" t="inlineStr">
         <is>
-          <t>静岡女子高等学校</t>
+          <t>中京高等学校</t>
         </is>
       </c>
       <c r="E722" s="6" t="inlineStr">
         <is>
-          <t>054-285-2274</t>
+          <t>0572-68-4501</t>
         </is>
       </c>
       <c r="F722" s="7" t="inlineStr">
@@ -42966,7 +42966,7 @@
       </c>
       <c r="G722" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H722" s="8" t="n"/>
@@ -42980,12 +42980,12 @@
       <c r="L722" s="9" t="n"/>
       <c r="M722" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>全日制の番号（瑞浪市のサイトほかで一致）。通信制課程は0572-66-1255。愛知の中京大学附属中京とは別の学校</t>
         </is>
       </c>
       <c r="N722" s="11" t="inlineStr">
         <is>
-          <t>https://shizuoka-joshi.ac.jp/</t>
+          <t>https://www.city.mizunami.lg.jp/kosodate/gakkoukyouiku/1002127.html ; https://www.mapion.co.jp/phonebook/M11004/21208/ILSP0000040904_ipclm/</t>
         </is>
       </c>
       <c r="O722" s="12" t="inlineStr">
@@ -43000,22 +43000,22 @@
       </c>
       <c r="B723" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C723" s="5" t="inlineStr">
         <is>
-          <t>静岡市駿河区</t>
+          <t>可児市</t>
         </is>
       </c>
       <c r="D723" s="5" t="inlineStr">
         <is>
-          <t>静岡聖光学院高等学校</t>
+          <t>帝京大学可児高等学校</t>
         </is>
       </c>
       <c r="E723" s="6" t="inlineStr">
         <is>
-          <t>054-285-9136</t>
+          <t>0574-64-3211</t>
         </is>
       </c>
       <c r="F723" s="7" t="inlineStr">
@@ -43039,12 +43039,12 @@
       <c r="L723" s="9" t="n"/>
       <c r="M723" s="10" t="inlineStr">
         <is>
-          <t>中高共通。高校募集なし（完全中高一貫）。公式未確認</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N723" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/22102/ILSP0000041139_ipclm/ ; https://itp.ne.jp/info/229451737200000899/</t>
+          <t>https://www.teikyo-kani.ed.jp/high/access/</t>
         </is>
       </c>
       <c r="O723" s="12" t="inlineStr">
@@ -43059,22 +43059,22 @@
       </c>
       <c r="B724" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C724" s="5" t="inlineStr">
         <is>
-          <t>静岡市葵区</t>
+          <t>岐阜市</t>
         </is>
       </c>
       <c r="D724" s="5" t="inlineStr">
         <is>
-          <t>静岡大成高等学校</t>
+          <t>富田高等学校</t>
         </is>
       </c>
       <c r="E724" s="6" t="inlineStr">
         <is>
-          <t>054-254-7334</t>
+          <t>058-245-3621</t>
         </is>
       </c>
       <c r="F724" s="7" t="inlineStr">
@@ -43084,7 +43084,7 @@
       </c>
       <c r="G724" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H724" s="8" t="n"/>
@@ -43098,12 +43098,12 @@
       <c r="L724" s="9" t="n"/>
       <c r="M724" s="10" t="inlineStr">
         <is>
-          <t>複数サイトで一致、公式未確認</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N724" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000040794_ipclm/</t>
+          <t>https://www.tomita.ac.jp/</t>
         </is>
       </c>
       <c r="O724" s="12" t="inlineStr">
@@ -43118,22 +43118,22 @@
       </c>
       <c r="B725" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C725" s="5" t="inlineStr">
         <is>
-          <t>静岡市葵区</t>
+          <t>美濃加茂市</t>
         </is>
       </c>
       <c r="D725" s="5" t="inlineStr">
         <is>
-          <t>静岡雙葉高等学校</t>
+          <t>美濃加茂高等学校</t>
         </is>
       </c>
       <c r="E725" s="6" t="inlineStr">
         <is>
-          <t>054-255-0305</t>
+          <t>0574-26-7181</t>
         </is>
       </c>
       <c r="F725" s="7" t="inlineStr">
@@ -43157,12 +43157,12 @@
       <c r="L725" s="9" t="n"/>
       <c r="M725" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>公式サイトで確認（私立）。0574-26-7182を載せるサイトもあり。公式サイトに電話設備の故障のお知らせあり</t>
         </is>
       </c>
       <c r="N725" s="11" t="inlineStr">
         <is>
-          <t>https://shizuoka-futaba.ac.jp/graduate/certificate/ ; https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000041364_ipclm/</t>
+          <t>https://minokamo.ed.jp/</t>
         </is>
       </c>
       <c r="O725" s="12" t="inlineStr">
@@ -43177,22 +43177,22 @@
       </c>
       <c r="B726" s="5" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="C726" s="5" t="inlineStr">
         <is>
-          <t>島田市</t>
+          <t>瑞浪市</t>
         </is>
       </c>
       <c r="D726" s="5" t="inlineStr">
         <is>
-          <t>島田樟誠高等学校</t>
+          <t>麗澤瑞浪高等学校</t>
         </is>
       </c>
       <c r="E726" s="6" t="inlineStr">
         <is>
-          <t>0547-37-3116</t>
+          <t>0572-66-3111</t>
         </is>
       </c>
       <c r="F726" s="7" t="inlineStr">
@@ -43216,12 +43216,12 @@
       <c r="L726" s="9" t="n"/>
       <c r="M726" s="10" t="inlineStr">
         <is>
-          <t>複数サイトで一致、公式未確認</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N726" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/22209/ILSP0000041690_ipclm/ ; https://www.minkou.jp/hischool/school/2271/</t>
+          <t>https://www.mz.reitaku.jp/school-guide/overview_history/</t>
         </is>
       </c>
       <c r="O726" s="12" t="inlineStr">
@@ -43241,17 +43241,17 @@
       </c>
       <c r="C727" s="5" t="inlineStr">
         <is>
-          <t>静岡市清水区</t>
+          <t>磐田市</t>
         </is>
       </c>
       <c r="D727" s="5" t="inlineStr">
         <is>
-          <t>清水国際高等学校</t>
+          <t>磐田東高等学校</t>
         </is>
       </c>
       <c r="E727" s="6" t="inlineStr">
         <is>
-          <t>054-366-4155</t>
+          <t>0538-32-6118</t>
         </is>
       </c>
       <c r="F727" s="7" t="inlineStr">
@@ -43275,12 +43275,12 @@
       <c r="L727" s="9" t="n"/>
       <c r="M727" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N727" s="11" t="inlineStr">
         <is>
-          <t>https://www.shimizu-kokusai.ac.jp/</t>
+          <t>https://www.iwatahigashi-h.ed.jp/ ; https://www.mapion.co.jp/phonebook/M11004/22211/ILSP0000041612_ipclm/</t>
         </is>
       </c>
       <c r="O727" s="12" t="inlineStr">
@@ -43300,17 +43300,17 @@
       </c>
       <c r="C728" s="5" t="inlineStr">
         <is>
-          <t>静岡市駿河区</t>
+          <t>浜松市中央区</t>
         </is>
       </c>
       <c r="D728" s="5" t="inlineStr">
         <is>
-          <t>城南静岡高等学校</t>
+          <t>オイスカ浜松国際高等学校</t>
         </is>
       </c>
       <c r="E728" s="6" t="inlineStr">
         <is>
-          <t>054-285-6156</t>
+          <t>053-486-3011</t>
         </is>
       </c>
       <c r="F728" s="7" t="inlineStr">
@@ -43320,7 +43320,7 @@
       </c>
       <c r="G728" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H728" s="8" t="n"/>
@@ -43334,12 +43334,12 @@
       <c r="L728" s="9" t="n"/>
       <c r="M728" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>公式サイトで確認。所在地は浜松市中央区</t>
         </is>
       </c>
       <c r="N728" s="11" t="inlineStr">
         <is>
-          <t>https://www.johnan.ac.jp/</t>
+          <t>https://www.oisca.ed.jp/school/access/ ; https://www.minkou.jp/hischool/school/646/</t>
         </is>
       </c>
       <c r="O728" s="12" t="inlineStr">
@@ -43364,12 +43364,12 @@
       </c>
       <c r="D729" s="5" t="inlineStr">
         <is>
-          <t>誠恵高等学校</t>
+          <t>加藤学園暁秀高等学校</t>
         </is>
       </c>
       <c r="E729" s="6" t="inlineStr">
         <is>
-          <t>055-921-5088</t>
+          <t>055-924-1900</t>
         </is>
       </c>
       <c r="F729" s="7" t="inlineStr">
@@ -43393,12 +43393,12 @@
       <c r="L729" s="9" t="n"/>
       <c r="M729" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載</t>
+          <t>中高共通。加藤学園高校とは別の学校</t>
         </is>
       </c>
       <c r="N729" s="11" t="inlineStr">
         <is>
-          <t>http://www.seikei-on.ac.jp/contact/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22203/ILSP0000041290_ipclm/ ; https://school.js88.com/scl_h/22009120</t>
         </is>
       </c>
       <c r="O729" s="12" t="inlineStr">
@@ -43418,17 +43418,17 @@
       </c>
       <c r="C730" s="5" t="inlineStr">
         <is>
-          <t>藤枝市</t>
+          <t>沼津市</t>
         </is>
       </c>
       <c r="D730" s="5" t="inlineStr">
         <is>
-          <t>静清高等学校</t>
+          <t>加藤学園高等学校</t>
         </is>
       </c>
       <c r="E730" s="6" t="inlineStr">
         <is>
-          <t>054-641-6693</t>
+          <t>055-921-0347</t>
         </is>
       </c>
       <c r="F730" s="7" t="inlineStr">
@@ -43438,7 +43438,7 @@
       </c>
       <c r="G730" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H730" s="8" t="n"/>
@@ -43452,12 +43452,12 @@
       <c r="L730" s="9" t="n"/>
       <c r="M730" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。通信制課程も同じ番号</t>
+          <t>公式サイトに「代表」と記載。加藤学園暁秀とは別の学校</t>
         </is>
       </c>
       <c r="N730" s="11" t="inlineStr">
         <is>
-          <t>https://seisei.ed.jp/access/</t>
+          <t>https://www.katogaku.jp/KatohHS/</t>
         </is>
       </c>
       <c r="O730" s="12" t="inlineStr">
@@ -43477,17 +43477,17 @@
       </c>
       <c r="C731" s="5" t="inlineStr">
         <is>
-          <t>富士宮市</t>
+          <t>吉田町</t>
         </is>
       </c>
       <c r="D731" s="5" t="inlineStr">
         <is>
-          <t>星陵高等学校</t>
+          <t>キラリ高等学校</t>
         </is>
       </c>
       <c r="E731" s="6" t="inlineStr">
         <is>
-          <t>0544-24-4811</t>
+          <t>0548-33-4976</t>
         </is>
       </c>
       <c r="F731" s="7" t="inlineStr">
@@ -43497,7 +43497,7 @@
       </c>
       <c r="G731" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H731" s="8" t="n"/>
@@ -43511,12 +43511,12 @@
       <c r="L731" s="9" t="n"/>
       <c r="M731" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認（静岡理工科大学星陵中学校・高等学校）</t>
+          <t>通信制。吉田本校の番号（公式サイト）</t>
         </is>
       </c>
       <c r="N731" s="11" t="inlineStr">
         <is>
-          <t>https://starhill.ed.jp/hs/</t>
+          <t>https://www.kirari-highschool.jp/introduction/access/</t>
         </is>
       </c>
       <c r="O731" s="12" t="inlineStr">
@@ -43536,17 +43536,17 @@
       </c>
       <c r="C732" s="5" t="inlineStr">
         <is>
-          <t>浜松市中央区</t>
+          <t>御殿場市</t>
         </is>
       </c>
       <c r="D732" s="5" t="inlineStr">
         <is>
-          <t>聖隷クリストファー高等学校</t>
+          <t>御殿場西高等学校</t>
         </is>
       </c>
       <c r="E732" s="6" t="inlineStr">
         <is>
-          <t>053-436-5313</t>
+          <t>0550-89-2466</t>
         </is>
       </c>
       <c r="F732" s="7" t="inlineStr">
@@ -43556,7 +43556,7 @@
       </c>
       <c r="G732" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H732" s="8" t="n"/>
@@ -43570,12 +43570,12 @@
       <c r="L732" s="9" t="n"/>
       <c r="M732" s="10" t="inlineStr">
         <is>
-          <t>複数サイトで一致、公式未確認。所在地は浜松市中央区</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N732" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/22138/ILSP0000041195_ipclm/ ; https://school.js88.com/scl_h/22009420</t>
+          <t>https://gotembanishi-h.ed.jp/access/</t>
         </is>
       </c>
       <c r="O732" s="12" t="inlineStr">
@@ -43595,17 +43595,17 @@
       </c>
       <c r="C733" s="5" t="inlineStr">
         <is>
-          <t>長泉町</t>
+          <t>静岡市葵区</t>
         </is>
       </c>
       <c r="D733" s="5" t="inlineStr">
         <is>
-          <t>知徳高等学校</t>
+          <t>静岡英和女学院高等学校</t>
         </is>
       </c>
       <c r="E733" s="6" t="inlineStr">
         <is>
-          <t>055-975-0080</t>
+          <t>054-254-7401</t>
         </is>
       </c>
       <c r="F733" s="7" t="inlineStr">
@@ -43615,7 +43615,7 @@
       </c>
       <c r="G733" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H733" s="8" t="n"/>
@@ -43629,12 +43629,12 @@
       <c r="L733" s="9" t="n"/>
       <c r="M733" s="10" t="inlineStr">
         <is>
-          <t>複数サイトで一致。055-976-0735はFAXなので注意</t>
+          <t>中高共通。2つのサイトで一致</t>
         </is>
       </c>
       <c r="N733" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/22342/ILSP0000041799_ipclm/ ; https://itp.ne.jp/info/225247068200000899/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000040742_ipclm/ ; https://shizu-hsmap.com/3460/</t>
         </is>
       </c>
       <c r="O733" s="12" t="inlineStr">
@@ -43654,17 +43654,17 @@
       </c>
       <c r="C734" s="5" t="inlineStr">
         <is>
-          <t>静岡市清水区</t>
+          <t>静岡市葵区</t>
         </is>
       </c>
       <c r="D734" s="5" t="inlineStr">
         <is>
-          <t>東海大学付属静岡翔洋高等学校</t>
+          <t>静岡学園高等学校</t>
         </is>
       </c>
       <c r="E734" s="6" t="inlineStr">
         <is>
-          <t>054-334-0726</t>
+          <t>054-200-0191</t>
         </is>
       </c>
       <c r="F734" s="7" t="inlineStr">
@@ -43674,7 +43674,7 @@
       </c>
       <c r="G734" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H734" s="8" t="n"/>
@@ -43688,12 +43688,12 @@
       <c r="L734" s="9" t="n"/>
       <c r="M734" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中等部は054-334-1851</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N734" s="11" t="inlineStr">
         <is>
-          <t>https://www.shoyo.tokai.ed.jp/contact/</t>
+          <t>https://www.shizugaku.ed.jp/</t>
         </is>
       </c>
       <c r="O734" s="12" t="inlineStr">
@@ -43713,17 +43713,17 @@
       </c>
       <c r="C735" s="5" t="inlineStr">
         <is>
-          <t>沼津市</t>
+          <t>静岡市葵区</t>
         </is>
       </c>
       <c r="D735" s="5" t="inlineStr">
         <is>
-          <t>桐陽高等学校</t>
+          <t>静岡北高等学校</t>
         </is>
       </c>
       <c r="E735" s="6" t="inlineStr">
         <is>
-          <t>055-921-0350</t>
+          <t>054-261-5801</t>
         </is>
       </c>
       <c r="F735" s="7" t="inlineStr">
@@ -43733,7 +43733,7 @@
       </c>
       <c r="G735" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H735" s="8" t="n"/>
@@ -43747,12 +43747,12 @@
       <c r="L735" s="9" t="n"/>
       <c r="M735" s="10" t="inlineStr">
         <is>
-          <t>公式サイトでは募集広報部の番号。055-921-0096を載せるサイトもあり（旧番号の可能性）</t>
+          <t>公式サイトに「代表」と記載。中学校は054-267-6151</t>
         </is>
       </c>
       <c r="N735" s="11" t="inlineStr">
         <is>
-          <t>https://toyo-numazu.ac.jp/contact/ ; https://www.mapion.co.jp/phonebook/M11004/22203/ILSP0000041817_ipclm/</t>
+          <t>https://shizukita.jp/contact/</t>
         </is>
       </c>
       <c r="O735" s="12" t="inlineStr">
@@ -43772,17 +43772,17 @@
       </c>
       <c r="C736" s="5" t="inlineStr">
         <is>
-          <t>菊川市</t>
+          <t>浜松市中央区</t>
         </is>
       </c>
       <c r="D736" s="5" t="inlineStr">
         <is>
-          <t>常葉大学附属菊川高等学校</t>
+          <t>静岡県西遠女子学園高等学校</t>
         </is>
       </c>
       <c r="E736" s="6" t="inlineStr">
         <is>
-          <t>0537-35-3171</t>
+          <t>053-461-0374</t>
         </is>
       </c>
       <c r="F736" s="7" t="inlineStr">
@@ -43792,7 +43792,7 @@
       </c>
       <c r="G736" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H736" s="8" t="n"/>
@@ -43806,12 +43806,12 @@
       <c r="L736" s="9" t="n"/>
       <c r="M736" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>公式サイトで確認。中高共通。所在地は浜松市中央区</t>
         </is>
       </c>
       <c r="N736" s="11" t="inlineStr">
         <is>
-          <t>https://tokoha.net/kikugawa/guide/access/</t>
+          <t>https://www.seien.ed.jp/</t>
         </is>
       </c>
       <c r="O736" s="12" t="inlineStr">
@@ -43831,17 +43831,17 @@
       </c>
       <c r="C737" s="5" t="inlineStr">
         <is>
-          <t>静岡市葵区</t>
+          <t>富士市</t>
         </is>
       </c>
       <c r="D737" s="5" t="inlineStr">
         <is>
-          <t>常葉大学附属橘高等学校</t>
+          <t>静岡県富士見高等学校</t>
         </is>
       </c>
       <c r="E737" s="6" t="inlineStr">
         <is>
-          <t>054-261-2256</t>
+          <t>0545-61-0250</t>
         </is>
       </c>
       <c r="F737" s="7" t="inlineStr">
@@ -43851,7 +43851,7 @@
       </c>
       <c r="G737" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H737" s="8" t="n"/>
@@ -43870,7 +43870,7 @@
       </c>
       <c r="N737" s="11" t="inlineStr">
         <is>
-          <t>https://www.tokoha.ac.jp/tachibana-jh/</t>
+          <t>https://fujimi.ed.jp/</t>
         </is>
       </c>
       <c r="O737" s="12" t="inlineStr">
@@ -43890,17 +43890,17 @@
       </c>
       <c r="C738" s="5" t="inlineStr">
         <is>
-          <t>静岡市葵区</t>
+          <t>静岡市清水区</t>
         </is>
       </c>
       <c r="D738" s="5" t="inlineStr">
         <is>
-          <t>常葉大学附属常葉高等学校</t>
+          <t>静岡サレジオ高等学校</t>
         </is>
       </c>
       <c r="E738" s="6" t="inlineStr">
         <is>
-          <t>054-245-5401</t>
+          <t>054-345-2296</t>
         </is>
       </c>
       <c r="F738" s="7" t="inlineStr">
@@ -43924,12 +43924,12 @@
       <c r="L738" s="9" t="n"/>
       <c r="M738" s="10" t="inlineStr">
         <is>
-          <t>中高共通の代表</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N738" s="11" t="inlineStr">
         <is>
-          <t>https://www.tokoha-u.ac.jp/university/links/ ; https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000041765_ipclm/</t>
+          <t>https://ssalesio.ac.jp/high/contact/</t>
         </is>
       </c>
       <c r="O738" s="12" t="inlineStr">
@@ -43949,17 +43949,17 @@
       </c>
       <c r="C739" s="5" t="inlineStr">
         <is>
-          <t>三島市</t>
+          <t>静岡市駿河区</t>
         </is>
       </c>
       <c r="D739" s="5" t="inlineStr">
         <is>
-          <t>日本大学三島高等学校</t>
+          <t>静岡女子高等学校</t>
         </is>
       </c>
       <c r="E739" s="6" t="inlineStr">
         <is>
-          <t>055-988-3500</t>
+          <t>054-285-2274</t>
         </is>
       </c>
       <c r="F739" s="7" t="inlineStr">
@@ -43969,7 +43969,7 @@
       </c>
       <c r="G739" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H739" s="8" t="n"/>
@@ -43983,12 +43983,12 @@
       <c r="L739" s="9" t="n"/>
       <c r="M739" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N739" s="11" t="inlineStr">
         <is>
-          <t>https://www.mishima.hs.nihon-u.ac.jp/</t>
+          <t>https://shizuoka-joshi.ac.jp/</t>
         </is>
       </c>
       <c r="O739" s="12" t="inlineStr">
@@ -44008,17 +44008,17 @@
       </c>
       <c r="C740" s="5" t="inlineStr">
         <is>
-          <t>沼津市</t>
+          <t>静岡市駿河区</t>
         </is>
       </c>
       <c r="D740" s="5" t="inlineStr">
         <is>
-          <t>沼津中央高等学校</t>
+          <t>静岡聖光学院高等学校</t>
         </is>
       </c>
       <c r="E740" s="6" t="inlineStr">
         <is>
-          <t>055-921-0346</t>
+          <t>054-285-9136</t>
         </is>
       </c>
       <c r="F740" s="7" t="inlineStr">
@@ -44042,12 +44042,12 @@
       <c r="L740" s="9" t="n"/>
       <c r="M740" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>中高共通。高校募集なし（完全中高一貫）。公式未確認</t>
         </is>
       </c>
       <c r="N740" s="11" t="inlineStr">
         <is>
-          <t>https://www.n-chuo.ac.jp/contact ; https://www.mapion.co.jp/phonebook/M11004/22203/ILSP0000041058_ipclm/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22102/ILSP0000041139_ipclm/ ; https://itp.ne.jp/info/229451737200000899/</t>
         </is>
       </c>
       <c r="O740" s="12" t="inlineStr">
@@ -44067,17 +44067,17 @@
       </c>
       <c r="C741" s="5" t="inlineStr">
         <is>
-          <t>浜松市中央区</t>
+          <t>静岡市葵区</t>
         </is>
       </c>
       <c r="D741" s="5" t="inlineStr">
         <is>
-          <t>浜松開誠館高等学校</t>
+          <t>静岡大成高等学校</t>
         </is>
       </c>
       <c r="E741" s="6" t="inlineStr">
         <is>
-          <t>053-456-7111</t>
+          <t>054-254-7334</t>
         </is>
       </c>
       <c r="F741" s="7" t="inlineStr">
@@ -44101,12 +44101,12 @@
       <c r="L741" s="9" t="n"/>
       <c r="M741" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>複数サイトで一致、公式未確認</t>
         </is>
       </c>
       <c r="N741" s="11" t="inlineStr">
         <is>
-          <t>https://www.kaiseikan.ed.jp/top-page/school-overview/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000040794_ipclm/</t>
         </is>
       </c>
       <c r="O741" s="12" t="inlineStr">
@@ -44126,17 +44126,17 @@
       </c>
       <c r="C742" s="5" t="inlineStr">
         <is>
-          <t>浜松市中央区</t>
+          <t>静岡市葵区</t>
         </is>
       </c>
       <c r="D742" s="5" t="inlineStr">
         <is>
-          <t>浜松学院高等学校</t>
+          <t>静岡雙葉高等学校</t>
         </is>
       </c>
       <c r="E742" s="6" t="inlineStr">
         <is>
-          <t>053-471-4136</t>
+          <t>054-255-0305</t>
         </is>
       </c>
       <c r="F742" s="7" t="inlineStr">
@@ -44160,12 +44160,12 @@
       <c r="L742" s="9" t="n"/>
       <c r="M742" s="10" t="inlineStr">
         <is>
-          <t>【校名変更】2025年4月に「浜松学院興誠高等学校」へ改称。法人本部と同じ番号</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N742" s="11" t="inlineStr">
         <is>
-          <t>https://www.hamagaku.ac.jp/gakuin/schoolprospectus/history/ ; https://school.js88.com/scl_h/22009350</t>
+          <t>https://shizuoka-futaba.ac.jp/graduate/certificate/ ; https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000041364_ipclm/</t>
         </is>
       </c>
       <c r="O742" s="12" t="inlineStr">
@@ -44185,17 +44185,17 @@
       </c>
       <c r="C743" s="5" t="inlineStr">
         <is>
-          <t>浜松市中央区</t>
+          <t>島田市</t>
         </is>
       </c>
       <c r="D743" s="5" t="inlineStr">
         <is>
-          <t>浜松学芸高等学校</t>
+          <t>島田樟誠高等学校</t>
         </is>
       </c>
       <c r="E743" s="6" t="inlineStr">
         <is>
-          <t>053-471-5336</t>
+          <t>0547-37-3116</t>
         </is>
       </c>
       <c r="F743" s="7" t="inlineStr">
@@ -44205,7 +44205,7 @@
       </c>
       <c r="G743" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H743" s="8" t="n"/>
@@ -44219,12 +44219,12 @@
       <c r="L743" s="9" t="n"/>
       <c r="M743" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>複数サイトで一致、公式未確認</t>
         </is>
       </c>
       <c r="N743" s="11" t="inlineStr">
         <is>
-          <t>https://www.gakugei.ed.jp/high/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22209/ILSP0000041690_ipclm/ ; https://www.minkou.jp/hischool/school/2271/</t>
         </is>
       </c>
       <c r="O743" s="12" t="inlineStr">
@@ -44244,17 +44244,17 @@
       </c>
       <c r="C744" s="5" t="inlineStr">
         <is>
-          <t>浜松市中央区</t>
+          <t>静岡市清水区</t>
         </is>
       </c>
       <c r="D744" s="5" t="inlineStr">
         <is>
-          <t>浜松啓陽高等学校</t>
+          <t>清水国際高等学校</t>
         </is>
       </c>
       <c r="E744" s="6" t="inlineStr">
         <is>
-          <t>053-420-0431</t>
+          <t>054-366-4155</t>
         </is>
       </c>
       <c r="F744" s="7" t="inlineStr">
@@ -44264,7 +44264,7 @@
       </c>
       <c r="G744" s="5" t="inlineStr">
         <is>
-          <t>専門学科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H744" s="8" t="n"/>
@@ -44278,12 +44278,12 @@
       <c r="L744" s="9" t="n"/>
       <c r="M744" s="10" t="inlineStr">
         <is>
-          <t>通信制。公式サイトで確認</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N744" s="11" t="inlineStr">
         <is>
-          <t>https://keiyo.ed.jp/ ; https://school.js88.com/scl_h/34029510?page=6</t>
+          <t>https://www.shimizu-kokusai.ac.jp/</t>
         </is>
       </c>
       <c r="O744" s="12" t="inlineStr">
@@ -44303,17 +44303,17 @@
       </c>
       <c r="C745" s="5" t="inlineStr">
         <is>
-          <t>浜松市中央区</t>
+          <t>静岡市駿河区</t>
         </is>
       </c>
       <c r="D745" s="5" t="inlineStr">
         <is>
-          <t>浜松修学舎高等学校</t>
+          <t>城南静岡高等学校</t>
         </is>
       </c>
       <c r="E745" s="6" t="inlineStr">
         <is>
-          <t>053-461-7356</t>
+          <t>054-285-6156</t>
         </is>
       </c>
       <c r="F745" s="7" t="inlineStr">
@@ -44337,12 +44337,12 @@
       <c r="L745" s="9" t="n"/>
       <c r="M745" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N745" s="11" t="inlineStr">
         <is>
-          <t>https://www.shugakusha.ed.jp/</t>
+          <t>https://www.johnan.ac.jp/</t>
         </is>
       </c>
       <c r="O745" s="12" t="inlineStr">
@@ -44362,17 +44362,17 @@
       </c>
       <c r="C746" s="5" t="inlineStr">
         <is>
-          <t>浜松市中央区</t>
+          <t>沼津市</t>
         </is>
       </c>
       <c r="D746" s="5" t="inlineStr">
         <is>
-          <t>浜松聖星高等学校</t>
+          <t>誠恵高等学校</t>
         </is>
       </c>
       <c r="E746" s="6" t="inlineStr">
         <is>
-          <t>053-454-5376</t>
+          <t>055-921-5088</t>
         </is>
       </c>
       <c r="F746" s="7" t="inlineStr">
@@ -44396,12 +44396,12 @@
       <c r="L746" s="9" t="n"/>
       <c r="M746" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトに「代表」と記載</t>
         </is>
       </c>
       <c r="N746" s="11" t="inlineStr">
         <is>
-          <t>https://hamamatsu-seisei.jp/about/school_outline.html</t>
+          <t>http://www.seikei-on.ac.jp/contact/</t>
         </is>
       </c>
       <c r="O746" s="12" t="inlineStr">
@@ -44421,17 +44421,17 @@
       </c>
       <c r="C747" s="5" t="inlineStr">
         <is>
-          <t>浜松市中央区</t>
+          <t>藤枝市</t>
         </is>
       </c>
       <c r="D747" s="5" t="inlineStr">
         <is>
-          <t>浜松日体高等学校</t>
+          <t>静清高等学校</t>
         </is>
       </c>
       <c r="E747" s="6" t="inlineStr">
         <is>
-          <t>053-434-0632</t>
+          <t>054-641-6693</t>
         </is>
       </c>
       <c r="F747" s="7" t="inlineStr">
@@ -44441,7 +44441,7 @@
       </c>
       <c r="G747" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H747" s="8" t="n"/>
@@ -44455,12 +44455,12 @@
       <c r="L747" s="9" t="n"/>
       <c r="M747" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトで確認。通信制課程も同じ番号</t>
         </is>
       </c>
       <c r="N747" s="11" t="inlineStr">
         <is>
-          <t>https://www.h-nittai.ed.jp/</t>
+          <t>https://seisei.ed.jp/access/</t>
         </is>
       </c>
       <c r="O747" s="12" t="inlineStr">
@@ -44480,17 +44480,17 @@
       </c>
       <c r="C748" s="5" t="inlineStr">
         <is>
-          <t>沼津市</t>
+          <t>富士宮市</t>
         </is>
       </c>
       <c r="D748" s="5" t="inlineStr">
         <is>
-          <t>飛龍高等学校</t>
+          <t>星陵高等学校</t>
         </is>
       </c>
       <c r="E748" s="6" t="inlineStr">
         <is>
-          <t>055-921-7942</t>
+          <t>0544-24-4811</t>
         </is>
       </c>
       <c r="F748" s="7" t="inlineStr">
@@ -44514,12 +44514,12 @@
       <c r="L748" s="9" t="n"/>
       <c r="M748" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。055-921-0348を載せるサイトは旧番号の可能性</t>
+          <t>公式サイトで確認（静岡理工科大学星陵中学校・高等学校）</t>
         </is>
       </c>
       <c r="N748" s="11" t="inlineStr">
         <is>
-          <t>https://hiryu.ed.jp/about-us/access/</t>
+          <t>https://starhill.ed.jp/hs/</t>
         </is>
       </c>
       <c r="O748" s="12" t="inlineStr">
@@ -44539,17 +44539,17 @@
       </c>
       <c r="C749" s="5" t="inlineStr">
         <is>
-          <t>藤枝市</t>
+          <t>浜松市中央区</t>
         </is>
       </c>
       <c r="D749" s="5" t="inlineStr">
         <is>
-          <t>藤枝順心高等学校</t>
+          <t>聖隷クリストファー高等学校</t>
         </is>
       </c>
       <c r="E749" s="6" t="inlineStr">
         <is>
-          <t>054-635-1311</t>
+          <t>053-436-5313</t>
         </is>
       </c>
       <c r="F749" s="7" t="inlineStr">
@@ -44573,12 +44573,12 @@
       <c r="L749" s="9" t="n"/>
       <c r="M749" s="10" t="inlineStr">
         <is>
-          <t>2つのサイトで一致、公式未確認</t>
+          <t>複数サイトで一致、公式未確認。所在地は浜松市中央区</t>
         </is>
       </c>
       <c r="N749" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/22214/ILSP0000041630_ipclm/ ; https://school.js88.com/scl_h/22009310?page=9</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22138/ILSP0000041195_ipclm/ ; https://school.js88.com/scl_h/22009420</t>
         </is>
       </c>
       <c r="O749" s="12" t="inlineStr">
@@ -44598,17 +44598,17 @@
       </c>
       <c r="C750" s="5" t="inlineStr">
         <is>
-          <t>藤枝市</t>
+          <t>長泉町</t>
         </is>
       </c>
       <c r="D750" s="5" t="inlineStr">
         <is>
-          <t>藤枝明誠高等学校</t>
+          <t>知徳高等学校</t>
         </is>
       </c>
       <c r="E750" s="6" t="inlineStr">
         <is>
-          <t>054-635-8155</t>
+          <t>055-975-0080</t>
         </is>
       </c>
       <c r="F750" s="7" t="inlineStr">
@@ -44632,12 +44632,12 @@
       <c r="L750" s="9" t="n"/>
       <c r="M750" s="10" t="inlineStr">
         <is>
-          <t>公式サイトの事務室の番号</t>
+          <t>複数サイトで一致。055-976-0735はFAXなので注意</t>
         </is>
       </c>
       <c r="N750" s="11" t="inlineStr">
         <is>
-          <t>https://www.fgmeisei.ed.jp/contact/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22342/ILSP0000041799_ipclm/ ; https://itp.ne.jp/info/225247068200000899/</t>
         </is>
       </c>
       <c r="O750" s="12" t="inlineStr">
@@ -44657,17 +44657,17 @@
       </c>
       <c r="C751" s="5" t="inlineStr">
         <is>
-          <t>裾野市</t>
+          <t>静岡市清水区</t>
         </is>
       </c>
       <c r="D751" s="5" t="inlineStr">
         <is>
-          <t>不二聖心女子学院高等学校</t>
+          <t>東海大学付属静岡翔洋高等学校</t>
         </is>
       </c>
       <c r="E751" s="6" t="inlineStr">
         <is>
-          <t>055-992-0213</t>
+          <t>054-334-0726</t>
         </is>
       </c>
       <c r="F751" s="7" t="inlineStr">
@@ -44691,12 +44691,12 @@
       <c r="L751" s="9" t="n"/>
       <c r="M751" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>公式サイトで確認。中等部は054-334-1851</t>
         </is>
       </c>
       <c r="N751" s="11" t="inlineStr">
         <is>
-          <t>https://www.fujiseishin-jh.ed.jp/access/</t>
+          <t>https://www.shoyo.tokai.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O751" s="12" t="inlineStr">
@@ -44716,17 +44716,17 @@
       </c>
       <c r="C752" s="5" t="inlineStr">
         <is>
-          <t>焼津市</t>
+          <t>沼津市</t>
         </is>
       </c>
       <c r="D752" s="5" t="inlineStr">
         <is>
-          <t>焼津高等学校</t>
+          <t>桐陽高等学校</t>
         </is>
       </c>
       <c r="E752" s="6" t="inlineStr">
         <is>
-          <t>054-628-7235</t>
+          <t>055-921-0350</t>
         </is>
       </c>
       <c r="F752" s="7" t="inlineStr">
@@ -44736,7 +44736,7 @@
       </c>
       <c r="G752" s="5" t="inlineStr">
         <is>
-          <t>総合学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H752" s="8" t="n"/>
@@ -44750,12 +44750,12 @@
       <c r="L752" s="9" t="n"/>
       <c r="M752" s="10" t="inlineStr">
         <is>
-          <t>私立（学校法人松薫学園）。公式サイトで確認</t>
+          <t>公式サイトでは募集広報部の番号。055-921-0096を載せるサイトもあり（旧番号の可能性）</t>
         </is>
       </c>
       <c r="N752" s="11" t="inlineStr">
         <is>
-          <t>https://yaizu-h.ed.jp/</t>
+          <t>https://toyo-numazu.ac.jp/contact/ ; https://www.mapion.co.jp/phonebook/M11004/22203/ILSP0000041817_ipclm/</t>
         </is>
       </c>
       <c r="O752" s="12" t="inlineStr">
@@ -44770,22 +44770,22 @@
       </c>
       <c r="B753" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C753" s="5" t="inlineStr">
         <is>
-          <t>稲沢市</t>
+          <t>菊川市</t>
         </is>
       </c>
       <c r="D753" s="5" t="inlineStr">
         <is>
-          <t>愛知啓成高等学校</t>
+          <t>常葉大学附属菊川高等学校</t>
         </is>
       </c>
       <c r="E753" s="6" t="inlineStr">
         <is>
-          <t>0587-32-5141</t>
+          <t>0537-35-3171</t>
         </is>
       </c>
       <c r="F753" s="7" t="inlineStr">
@@ -44795,7 +44795,7 @@
       </c>
       <c r="G753" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H753" s="8" t="n"/>
@@ -44809,12 +44809,12 @@
       <c r="L753" s="9" t="n"/>
       <c r="M753" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N753" s="11" t="inlineStr">
         <is>
-          <t>https://keisei.ed.jp/ ; https://www.city.inazawa.aichi.jp/0000002446.html</t>
+          <t>https://tokoha.net/kikugawa/guide/access/</t>
         </is>
       </c>
       <c r="O753" s="12" t="inlineStr">
@@ -44829,22 +44829,22 @@
       </c>
       <c r="B754" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C754" s="5" t="inlineStr">
         <is>
-          <t>名古屋市千種区</t>
+          <t>静岡市葵区</t>
         </is>
       </c>
       <c r="D754" s="5" t="inlineStr">
         <is>
-          <t>愛知工業大学名電高等学校</t>
+          <t>常葉大学附属橘高等学校</t>
         </is>
       </c>
       <c r="E754" s="6" t="inlineStr">
         <is>
-          <t>052-721-0311</t>
+          <t>054-261-2256</t>
         </is>
       </c>
       <c r="F754" s="7" t="inlineStr">
@@ -44868,12 +44868,12 @@
       <c r="L754" s="9" t="n"/>
       <c r="M754" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N754" s="11" t="inlineStr">
         <is>
-          <t>https://www.meiden.ed.jp/others/contact.html</t>
+          <t>https://www.tokoha.ac.jp/tachibana-jh/</t>
         </is>
       </c>
       <c r="O754" s="12" t="inlineStr">
@@ -44888,22 +44888,22 @@
       </c>
       <c r="B755" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C755" s="5" t="inlineStr">
         <is>
-          <t>名古屋市千種区</t>
+          <t>静岡市葵区</t>
         </is>
       </c>
       <c r="D755" s="5" t="inlineStr">
         <is>
-          <t>愛知高等学校</t>
+          <t>常葉大学附属常葉高等学校</t>
         </is>
       </c>
       <c r="E755" s="6" t="inlineStr">
         <is>
-          <t>052-721-1521</t>
+          <t>054-245-5401</t>
         </is>
       </c>
       <c r="F755" s="7" t="inlineStr">
@@ -44927,12 +44927,12 @@
       <c r="L755" s="9" t="n"/>
       <c r="M755" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載。中高共通</t>
+          <t>中高共通の代表</t>
         </is>
       </c>
       <c r="N755" s="11" t="inlineStr">
         <is>
-          <t>https://www.aichi-h.ed.jp/hs/access/</t>
+          <t>https://www.tokoha-u.ac.jp/university/links/ ; https://www.mapion.co.jp/phonebook/M11004/22101/ILSP0000041765_ipclm/</t>
         </is>
       </c>
       <c r="O755" s="12" t="inlineStr">
@@ -44947,22 +44947,22 @@
       </c>
       <c r="B756" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C756" s="5" t="inlineStr">
         <is>
-          <t>岡崎市</t>
+          <t>三島市</t>
         </is>
       </c>
       <c r="D756" s="5" t="inlineStr">
         <is>
-          <t>愛知産業大学三河高等学校</t>
+          <t>日本大学三島高等学校</t>
         </is>
       </c>
       <c r="E756" s="6" t="inlineStr">
         <is>
-          <t>0564-48-5211</t>
+          <t>055-988-3500</t>
         </is>
       </c>
       <c r="F756" s="7" t="inlineStr">
@@ -44972,7 +44972,7 @@
       </c>
       <c r="G756" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H756" s="8" t="n"/>
@@ -44986,12 +44986,12 @@
       <c r="L756" s="9" t="n"/>
       <c r="M756" s="10" t="inlineStr">
         <is>
-          <t>全日制の番号（公式サイト）。通信制課程は0564-48-5230</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N756" s="11" t="inlineStr">
         <is>
-          <t>https://www.mikawa.ed.jp/introduction/information/</t>
+          <t>https://www.mishima.hs.nihon-u.ac.jp/</t>
         </is>
       </c>
       <c r="O756" s="12" t="inlineStr">
@@ -45006,22 +45006,22 @@
       </c>
       <c r="B757" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C757" s="5" t="inlineStr">
         <is>
-          <t>名古屋市千種区</t>
+          <t>沼津市</t>
         </is>
       </c>
       <c r="D757" s="5" t="inlineStr">
         <is>
-          <t>愛知淑徳高等学校</t>
+          <t>沼津中央高等学校</t>
         </is>
       </c>
       <c r="E757" s="6" t="inlineStr">
         <is>
-          <t>052-781-1151</t>
+          <t>055-921-0346</t>
         </is>
       </c>
       <c r="F757" s="7" t="inlineStr">
@@ -45045,12 +45045,12 @@
       <c r="L757" s="9" t="n"/>
       <c r="M757" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで代表番号として確認。中高共通</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N757" s="11" t="inlineStr">
         <is>
-          <t>https://www.aichishukutoku-h.jp/contact/</t>
+          <t>https://www.n-chuo.ac.jp/contact ; https://www.mapion.co.jp/phonebook/M11004/22203/ILSP0000041058_ipclm/</t>
         </is>
       </c>
       <c r="O757" s="12" t="inlineStr">
@@ -45065,22 +45065,22 @@
       </c>
       <c r="B758" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C758" s="5" t="inlineStr">
         <is>
-          <t>名古屋市瑞穂区</t>
+          <t>浜松市中央区</t>
         </is>
       </c>
       <c r="D758" s="5" t="inlineStr">
         <is>
-          <t>愛知みずほ大学瑞穂高等学校</t>
+          <t>浜松開誠館高等学校</t>
         </is>
       </c>
       <c r="E758" s="6" t="inlineStr">
         <is>
-          <t>052-882-1811</t>
+          <t>053-456-7111</t>
         </is>
       </c>
       <c r="F758" s="7" t="inlineStr">
@@ -45090,7 +45090,7 @@
       </c>
       <c r="G758" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H758" s="8" t="n"/>
@@ -45104,12 +45104,12 @@
       <c r="L758" s="9" t="n"/>
       <c r="M758" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N758" s="11" t="inlineStr">
         <is>
-          <t>https://www.aichi-mizuho.ac.jp/mhs/</t>
+          <t>https://www.kaiseikan.ed.jp/top-page/school-overview/</t>
         </is>
       </c>
       <c r="O758" s="12" t="inlineStr">
@@ -45124,22 +45124,22 @@
       </c>
       <c r="B759" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C759" s="5" t="inlineStr">
         <is>
-          <t>弥富市</t>
+          <t>浜松市中央区</t>
         </is>
       </c>
       <c r="D759" s="5" t="inlineStr">
         <is>
-          <t>愛知黎明高等学校</t>
+          <t>浜松学院高等学校</t>
         </is>
       </c>
       <c r="E759" s="6" t="inlineStr">
         <is>
-          <t>0567-68-2233</t>
+          <t>053-471-4136</t>
         </is>
       </c>
       <c r="F759" s="7" t="inlineStr">
@@ -45149,7 +45149,7 @@
       </c>
       <c r="G759" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H759" s="8" t="n"/>
@@ -45163,12 +45163,12 @@
       <c r="L759" s="9" t="n"/>
       <c r="M759" s="10" t="inlineStr">
         <is>
-          <t>複数サイトで一致、公式未確認。定時制あり</t>
+          <t>【校名変更】2025年4月に「浜松学院興誠高等学校」へ改称。法人本部と同じ番号</t>
         </is>
       </c>
       <c r="N759" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/23235/ILSP0000040620_ipclm/ ; https://school.js88.com/scl_h/22011520</t>
+          <t>https://www.hamagaku.ac.jp/gakuin/schoolprospectus/history/ ; https://school.js88.com/scl_h/22009350</t>
         </is>
       </c>
       <c r="O759" s="12" t="inlineStr">
@@ -45183,22 +45183,22 @@
       </c>
       <c r="B760" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C760" s="5" t="inlineStr">
         <is>
-          <t>安城市</t>
+          <t>浜松市中央区</t>
         </is>
       </c>
       <c r="D760" s="5" t="inlineStr">
         <is>
-          <t>安城学園高等学校</t>
+          <t>浜松学芸高等学校</t>
         </is>
       </c>
       <c r="E760" s="6" t="inlineStr">
         <is>
-          <t>0566-76-5105</t>
+          <t>053-471-5336</t>
         </is>
       </c>
       <c r="F760" s="7" t="inlineStr">
@@ -45222,12 +45222,12 @@
       <c r="L760" s="9" t="n"/>
       <c r="M760" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。法人本部（0566-77-7788）とは別</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N760" s="11" t="inlineStr">
         <is>
-          <t>https://www.angaku.jp/contact</t>
+          <t>https://www.gakugei.ed.jp/high/</t>
         </is>
       </c>
       <c r="O760" s="12" t="inlineStr">
@@ -45242,22 +45242,22 @@
       </c>
       <c r="B761" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C761" s="5" t="inlineStr">
         <is>
-          <t>長久手市</t>
+          <t>浜松市中央区</t>
         </is>
       </c>
       <c r="D761" s="5" t="inlineStr">
         <is>
-          <t>栄徳高等学校</t>
+          <t>浜松啓陽高等学校</t>
         </is>
       </c>
       <c r="E761" s="6" t="inlineStr">
         <is>
-          <t>0561-62-5000</t>
+          <t>053-420-0431</t>
         </is>
       </c>
       <c r="F761" s="7" t="inlineStr">
@@ -45267,7 +45267,7 @@
       </c>
       <c r="G761" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>専門学科</t>
         </is>
       </c>
       <c r="H761" s="8" t="n"/>
@@ -45281,12 +45281,12 @@
       <c r="L761" s="9" t="n"/>
       <c r="M761" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載</t>
+          <t>通信制。公式サイトで確認</t>
         </is>
       </c>
       <c r="N761" s="11" t="inlineStr">
         <is>
-          <t>https://www.eitoku-h.ed.jp/</t>
+          <t>https://keiyo.ed.jp/ ; https://school.js88.com/scl_h/34029510?page=6</t>
         </is>
       </c>
       <c r="O761" s="12" t="inlineStr">
@@ -45301,22 +45301,22 @@
       </c>
       <c r="B762" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C762" s="5" t="inlineStr">
         <is>
-          <t>名古屋市昭和区</t>
+          <t>浜松市中央区</t>
         </is>
       </c>
       <c r="D762" s="5" t="inlineStr">
         <is>
-          <t>桜花学園高等学校</t>
+          <t>浜松修学舎高等学校</t>
         </is>
       </c>
       <c r="E762" s="6" t="inlineStr">
         <is>
-          <t>052-741-1221</t>
+          <t>053-461-7356</t>
         </is>
       </c>
       <c r="F762" s="7" t="inlineStr">
@@ -45326,7 +45326,7 @@
       </c>
       <c r="G762" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H762" s="8" t="n"/>
@@ -45345,7 +45345,7 @@
       </c>
       <c r="N762" s="11" t="inlineStr">
         <is>
-          <t>https://ohka-hs.com/profile/</t>
+          <t>https://www.shugakusha.ed.jp/</t>
         </is>
       </c>
       <c r="O762" s="12" t="inlineStr">
@@ -45360,22 +45360,22 @@
       </c>
       <c r="B763" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C763" s="5" t="inlineStr">
         <is>
-          <t>岡崎市</t>
+          <t>浜松市中央区</t>
         </is>
       </c>
       <c r="D763" s="5" t="inlineStr">
         <is>
-          <t>岡崎城西高等学校</t>
+          <t>浜松聖星高等学校</t>
         </is>
       </c>
       <c r="E763" s="6" t="inlineStr">
         <is>
-          <t>0564-31-4165</t>
+          <t>053-454-5376</t>
         </is>
       </c>
       <c r="F763" s="7" t="inlineStr">
@@ -45399,12 +45399,12 @@
       <c r="L763" s="9" t="n"/>
       <c r="M763" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認（安城学園岡崎城西）</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N763" s="11" t="inlineStr">
         <is>
-          <t>https://www.johsei.jp/contact/</t>
+          <t>https://hamamatsu-seisei.jp/about/school_outline.html</t>
         </is>
       </c>
       <c r="O763" s="12" t="inlineStr">
@@ -45419,22 +45419,22 @@
       </c>
       <c r="B764" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C764" s="5" t="inlineStr">
         <is>
-          <t>名古屋市守山区</t>
+          <t>浜松市中央区</t>
         </is>
       </c>
       <c r="D764" s="5" t="inlineStr">
         <is>
-          <t>菊華高等学校</t>
+          <t>浜松日体高等学校</t>
         </is>
       </c>
       <c r="E764" s="6" t="inlineStr">
         <is>
-          <t>052-791-8261</t>
+          <t>053-434-0632</t>
         </is>
       </c>
       <c r="F764" s="7" t="inlineStr">
@@ -45444,7 +45444,7 @@
       </c>
       <c r="G764" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H764" s="8" t="n"/>
@@ -45458,12 +45458,12 @@
       <c r="L764" s="9" t="n"/>
       <c r="M764" s="10" t="inlineStr">
         <is>
-          <t>全日制の本校の番号（公式サイト）</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N764" s="11" t="inlineStr">
         <is>
-          <t>https://kikuka.ed.jp/</t>
+          <t>https://www.h-nittai.ed.jp/</t>
         </is>
       </c>
       <c r="O764" s="12" t="inlineStr">
@@ -45478,22 +45478,22 @@
       </c>
       <c r="B765" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C765" s="5" t="inlineStr">
         <is>
-          <t>名古屋市瑞穂区</t>
+          <t>沼津市</t>
         </is>
       </c>
       <c r="D765" s="5" t="inlineStr">
         <is>
-          <t>享栄高等学校</t>
+          <t>飛龍高等学校</t>
         </is>
       </c>
       <c r="E765" s="6" t="inlineStr">
         <is>
-          <t>052-841-8151</t>
+          <t>055-921-7942</t>
         </is>
       </c>
       <c r="F765" s="7" t="inlineStr">
@@ -45517,12 +45517,12 @@
       <c r="L765" s="9" t="n"/>
       <c r="M765" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載</t>
+          <t>公式サイトで確認。055-921-0348を載せるサイトは旧番号の可能性</t>
         </is>
       </c>
       <c r="N765" s="11" t="inlineStr">
         <is>
-          <t>https://www.kyoei-h.ed.jp/contact/</t>
+          <t>https://hiryu.ed.jp/about-us/access/</t>
         </is>
       </c>
       <c r="O765" s="12" t="inlineStr">
@@ -45537,22 +45537,22 @@
       </c>
       <c r="B766" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C766" s="5" t="inlineStr">
         <is>
-          <t>名古屋市東区</t>
+          <t>藤枝市</t>
         </is>
       </c>
       <c r="D766" s="5" t="inlineStr">
         <is>
-          <t>金城学院高等学校</t>
+          <t>藤枝順心高等学校</t>
         </is>
       </c>
       <c r="E766" s="6" t="inlineStr">
         <is>
-          <t>052-931-6236</t>
+          <t>054-635-1311</t>
         </is>
       </c>
       <c r="F766" s="7" t="inlineStr">
@@ -45562,7 +45562,7 @@
       </c>
       <c r="G766" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H766" s="8" t="n"/>
@@ -45576,12 +45576,12 @@
       <c r="L766" s="9" t="n"/>
       <c r="M766" s="10" t="inlineStr">
         <is>
-          <t>高校の番号（公式サイト）。中学校は052-931-0821、大学は別番号</t>
+          <t>2つのサイトで一致、公式未確認</t>
         </is>
       </c>
       <c r="N766" s="11" t="inlineStr">
         <is>
-          <t>https://www.hs.kinjo-u.ac.jp/contact/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/22214/ILSP0000041630_ipclm/ ; https://school.js88.com/scl_h/22009310?page=9</t>
         </is>
       </c>
       <c r="O766" s="12" t="inlineStr">
@@ -45596,27 +45596,27 @@
       </c>
       <c r="B767" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C767" s="5" t="inlineStr">
         <is>
-          <t>名古屋市西区</t>
+          <t>藤枝市</t>
         </is>
       </c>
       <c r="D767" s="5" t="inlineStr">
         <is>
-          <t>啓明学館高等学校</t>
+          <t>藤枝明誠高等学校</t>
         </is>
       </c>
       <c r="E767" s="6" t="inlineStr">
         <is>
-          <t>052-571-2561</t>
-        </is>
-      </c>
-      <c r="F767" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>054-635-8155</t>
+        </is>
+      </c>
+      <c r="F767" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="G767" s="5" t="inlineStr">
@@ -45635,12 +45635,12 @@
       <c r="L767" s="9" t="n"/>
       <c r="M767" s="10" t="inlineStr">
         <is>
-          <t>公式サイトの事務所の番号（「代表」の表記なし）。職員室は052-571-7366</t>
+          <t>公式サイトの事務室の番号</t>
         </is>
       </c>
       <c r="N767" s="11" t="inlineStr">
         <is>
-          <t>https://keimeigakkan-h.ed.jp/</t>
+          <t>https://www.fgmeisei.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O767" s="12" t="inlineStr">
@@ -45655,27 +45655,27 @@
       </c>
       <c r="B768" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C768" s="5" t="inlineStr">
         <is>
-          <t>豊橋市</t>
+          <t>裾野市</t>
         </is>
       </c>
       <c r="D768" s="5" t="inlineStr">
         <is>
-          <t>桜丘高等学校（愛知県）</t>
+          <t>不二聖心女子学院高等学校</t>
         </is>
       </c>
       <c r="E768" s="6" t="inlineStr">
         <is>
-          <t>0570-039-396</t>
-        </is>
-      </c>
-      <c r="F768" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>055-992-0213</t>
+        </is>
+      </c>
+      <c r="F768" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="G768" s="5" t="inlineStr">
@@ -45694,12 +45694,12 @@
       <c r="L768" s="9" t="n"/>
       <c r="M768" s="10" t="inlineStr">
         <is>
-          <t>公式サイトのナビダイヤル（学園・高校共通、通話料がかかる番号）。旧番号0532-61-6421が一部サイトに残る</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N768" s="11" t="inlineStr">
         <is>
-          <t>https://www.sakuragaoka-gakuen.ed.jp/h/</t>
+          <t>https://www.fujiseishin-jh.ed.jp/access/</t>
         </is>
       </c>
       <c r="O768" s="12" t="inlineStr">
@@ -45714,22 +45714,22 @@
       </c>
       <c r="B769" s="5" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="C769" s="5" t="inlineStr">
         <is>
-          <t>名古屋市東区</t>
+          <t>焼津市</t>
         </is>
       </c>
       <c r="D769" s="5" t="inlineStr">
         <is>
-          <t>至学館高等学校</t>
+          <t>焼津高等学校</t>
         </is>
       </c>
       <c r="E769" s="6" t="inlineStr">
         <is>
-          <t>052-723-0851</t>
+          <t>054-628-7235</t>
         </is>
       </c>
       <c r="F769" s="7" t="inlineStr">
@@ -45739,7 +45739,7 @@
       </c>
       <c r="G769" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>総合学科</t>
         </is>
       </c>
       <c r="H769" s="8" t="n"/>
@@ -45753,12 +45753,12 @@
       <c r="L769" s="9" t="n"/>
       <c r="M769" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>私立（学校法人松薫学園）。公式サイトで確認</t>
         </is>
       </c>
       <c r="N769" s="11" t="inlineStr">
         <is>
-          <t>https://www.shigakukan-h.ed.jp/</t>
+          <t>https://yaizu-h.ed.jp/</t>
         </is>
       </c>
       <c r="O769" s="12" t="inlineStr">
@@ -45778,17 +45778,17 @@
       </c>
       <c r="C770" s="5" t="inlineStr">
         <is>
-          <t>一宮市</t>
+          <t>稲沢市</t>
         </is>
       </c>
       <c r="D770" s="5" t="inlineStr">
         <is>
-          <t>修文学院高等学校</t>
+          <t>愛知啓成高等学校</t>
         </is>
       </c>
       <c r="E770" s="6" t="inlineStr">
         <is>
-          <t>0586-45-2102</t>
+          <t>0587-32-5141</t>
         </is>
       </c>
       <c r="F770" s="7" t="inlineStr">
@@ -45798,7 +45798,7 @@
       </c>
       <c r="G770" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H770" s="8" t="n"/>
@@ -45812,12 +45812,12 @@
       <c r="L770" s="9" t="n"/>
       <c r="M770" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。【校名変更】2022年に修文女子高校から改称・共学化</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N770" s="11" t="inlineStr">
         <is>
-          <t>https://www.gakuin-hs.shubun.ac.jp/contact</t>
+          <t>https://keisei.ed.jp/ ; https://www.city.inazawa.aichi.jp/0000002446.html</t>
         </is>
       </c>
       <c r="O770" s="12" t="inlineStr">
@@ -45842,12 +45842,12 @@
       </c>
       <c r="D771" s="5" t="inlineStr">
         <is>
-          <t>椙山女学園高等学校</t>
+          <t>愛知工業大学名電高等学校</t>
         </is>
       </c>
       <c r="E771" s="6" t="inlineStr">
         <is>
-          <t>052-751-8131</t>
+          <t>052-721-0311</t>
         </is>
       </c>
       <c r="F771" s="7" t="inlineStr">
@@ -45857,7 +45857,7 @@
       </c>
       <c r="G771" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H771" s="8" t="n"/>
@@ -45876,7 +45876,7 @@
       </c>
       <c r="N771" s="11" t="inlineStr">
         <is>
-          <t>https://www.sugiyama-u.ac.jp/high/index.html</t>
+          <t>https://www.meiden.ed.jp/others/contact.html</t>
         </is>
       </c>
       <c r="O771" s="12" t="inlineStr">
@@ -45896,17 +45896,17 @@
       </c>
       <c r="C772" s="5" t="inlineStr">
         <is>
-          <t>瀬戸市</t>
+          <t>名古屋市千種区</t>
         </is>
       </c>
       <c r="D772" s="5" t="inlineStr">
         <is>
-          <t>聖カピタニオ女子高等学校</t>
+          <t>愛知高等学校</t>
         </is>
       </c>
       <c r="E772" s="6" t="inlineStr">
         <is>
-          <t>0561-82-7711</t>
+          <t>052-721-1521</t>
         </is>
       </c>
       <c r="F772" s="7" t="inlineStr">
@@ -45930,12 +45930,12 @@
       <c r="L772" s="9" t="n"/>
       <c r="M772" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトに「代表」と記載。中高共通</t>
         </is>
       </c>
       <c r="N772" s="11" t="inlineStr">
         <is>
-          <t>https://www.st-capitanio.ed.jp/access/access.html</t>
+          <t>https://www.aichi-h.ed.jp/hs/access/</t>
         </is>
       </c>
       <c r="O772" s="12" t="inlineStr">
@@ -45955,17 +45955,17 @@
       </c>
       <c r="C773" s="5" t="inlineStr">
         <is>
-          <t>扶桑町</t>
+          <t>岡崎市</t>
         </is>
       </c>
       <c r="D773" s="5" t="inlineStr">
         <is>
-          <t>誠信高等学校</t>
+          <t>愛知産業大学三河高等学校</t>
         </is>
       </c>
       <c r="E773" s="6" t="inlineStr">
         <is>
-          <t>0587-93-5380</t>
+          <t>0564-48-5211</t>
         </is>
       </c>
       <c r="F773" s="7" t="inlineStr">
@@ -45975,7 +45975,7 @@
       </c>
       <c r="G773" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H773" s="8" t="n"/>
@@ -45989,12 +45989,12 @@
       <c r="L773" s="9" t="n"/>
       <c r="M773" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載。0587-93-8172はFAXなので注意</t>
+          <t>全日制の番号（公式サイト）。通信制課程は0564-48-5230</t>
         </is>
       </c>
       <c r="N773" s="11" t="inlineStr">
         <is>
-          <t>https://www.a-seishin.ed.jp/contact/</t>
+          <t>https://www.mikawa.ed.jp/introduction/information/</t>
         </is>
       </c>
       <c r="O773" s="12" t="inlineStr">
@@ -46014,17 +46014,17 @@
       </c>
       <c r="C774" s="5" t="inlineStr">
         <is>
-          <t>豊明市</t>
+          <t>名古屋市千種区</t>
         </is>
       </c>
       <c r="D774" s="5" t="inlineStr">
         <is>
-          <t>星城高等学校</t>
+          <t>愛知淑徳高等学校</t>
         </is>
       </c>
       <c r="E774" s="6" t="inlineStr">
         <is>
-          <t>0562-97-3111</t>
+          <t>052-781-1151</t>
         </is>
       </c>
       <c r="F774" s="7" t="inlineStr">
@@ -46048,12 +46048,12 @@
       <c r="L774" s="9" t="n"/>
       <c r="M774" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載</t>
+          <t>公式サイトで代表番号として確認。中高共通</t>
         </is>
       </c>
       <c r="N774" s="11" t="inlineStr">
         <is>
-          <t>https://www.seijoh.ed.jp/</t>
+          <t>https://www.aichishukutoku-h.jp/contact/</t>
         </is>
       </c>
       <c r="O774" s="12" t="inlineStr">
@@ -46073,17 +46073,17 @@
       </c>
       <c r="C775" s="5" t="inlineStr">
         <is>
-          <t>愛西市</t>
+          <t>名古屋市瑞穂区</t>
         </is>
       </c>
       <c r="D775" s="5" t="inlineStr">
         <is>
-          <t>清林館高等学校</t>
+          <t>愛知みずほ大学瑞穂高等学校</t>
         </is>
       </c>
       <c r="E775" s="6" t="inlineStr">
         <is>
-          <t>0567-28-3010</t>
+          <t>052-882-1811</t>
         </is>
       </c>
       <c r="F775" s="7" t="inlineStr">
@@ -46093,7 +46093,7 @@
       </c>
       <c r="G775" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H775" s="8" t="n"/>
@@ -46112,7 +46112,7 @@
       </c>
       <c r="N775" s="11" t="inlineStr">
         <is>
-          <t>https://www.seirinkan.ed.jp/high/access</t>
+          <t>https://www.aichi-mizuho.ac.jp/mhs/</t>
         </is>
       </c>
       <c r="O775" s="12" t="inlineStr">
@@ -46132,17 +46132,17 @@
       </c>
       <c r="C776" s="5" t="inlineStr">
         <is>
-          <t>瀬戸市</t>
+          <t>弥富市</t>
         </is>
       </c>
       <c r="D776" s="5" t="inlineStr">
         <is>
-          <t>聖霊高等学校</t>
+          <t>愛知黎明高等学校</t>
         </is>
       </c>
       <c r="E776" s="6" t="inlineStr">
         <is>
-          <t>0561-21-3121</t>
+          <t>0567-68-2233</t>
         </is>
       </c>
       <c r="F776" s="7" t="inlineStr">
@@ -46152,7 +46152,7 @@
       </c>
       <c r="G776" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H776" s="8" t="n"/>
@@ -46166,12 +46166,12 @@
       <c r="L776" s="9" t="n"/>
       <c r="M776" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>複数サイトで一致、公式未確認。定時制あり</t>
         </is>
       </c>
       <c r="N776" s="11" t="inlineStr">
         <is>
-          <t>https://www.seto-seirei-js.ed.jp/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/23235/ILSP0000040620_ipclm/ ; https://school.js88.com/scl_h/22011520</t>
         </is>
       </c>
       <c r="O776" s="12" t="inlineStr">
@@ -46191,17 +46191,17 @@
       </c>
       <c r="C777" s="5" t="inlineStr">
         <is>
-          <t>一宮市</t>
+          <t>安城市</t>
         </is>
       </c>
       <c r="D777" s="5" t="inlineStr">
         <is>
-          <t>大成高等学校（愛知県）</t>
+          <t>安城学園高等学校</t>
         </is>
       </c>
       <c r="E777" s="6" t="inlineStr">
         <is>
-          <t>0586-77-9900</t>
+          <t>0566-76-5105</t>
         </is>
       </c>
       <c r="F777" s="7" t="inlineStr">
@@ -46211,7 +46211,7 @@
       </c>
       <c r="G777" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H777" s="8" t="n"/>
@@ -46225,12 +46225,12 @@
       <c r="L777" s="9" t="n"/>
       <c r="M777" s="10" t="inlineStr">
         <is>
-          <t>公式サイトと一宮市のサイトで一致</t>
+          <t>公式サイトで確認。法人本部（0566-77-7788）とは別</t>
         </is>
       </c>
       <c r="N777" s="11" t="inlineStr">
         <is>
-          <t>https://www.aichi-shinwa-taisei.ed.jp/high/ ; https://www.city.ichinomiya.aichi.jp/shisetsu/hoikugakko/1008935/1009298.html</t>
+          <t>https://www.angaku.jp/contact</t>
         </is>
       </c>
       <c r="O777" s="12" t="inlineStr">
@@ -46250,17 +46250,17 @@
       </c>
       <c r="C778" s="5" t="inlineStr">
         <is>
-          <t>江南市</t>
+          <t>長久手市</t>
         </is>
       </c>
       <c r="D778" s="5" t="inlineStr">
         <is>
-          <t>滝高等学校</t>
+          <t>栄徳高等学校</t>
         </is>
       </c>
       <c r="E778" s="6" t="inlineStr">
         <is>
-          <t>0587-56-2127</t>
+          <t>0561-62-5000</t>
         </is>
       </c>
       <c r="F778" s="7" t="inlineStr">
@@ -46284,12 +46284,12 @@
       <c r="L778" s="9" t="n"/>
       <c r="M778" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトに「代表」と記載</t>
         </is>
       </c>
       <c r="N778" s="11" t="inlineStr">
         <is>
-          <t>https://www.taki-hj.ac.jp/guide/access.html</t>
+          <t>https://www.eitoku-h.ed.jp/</t>
         </is>
       </c>
       <c r="O778" s="12" t="inlineStr">
@@ -46309,17 +46309,17 @@
       </c>
       <c r="C779" s="5" t="inlineStr">
         <is>
-          <t>名古屋市南区</t>
+          <t>名古屋市昭和区</t>
         </is>
       </c>
       <c r="D779" s="5" t="inlineStr">
         <is>
-          <t>大同大学大同高等学校</t>
+          <t>桜花学園高等学校</t>
         </is>
       </c>
       <c r="E779" s="6" t="inlineStr">
         <is>
-          <t>052-611-0511</t>
+          <t>052-741-1221</t>
         </is>
       </c>
       <c r="F779" s="7" t="inlineStr">
@@ -46329,7 +46329,7 @@
       </c>
       <c r="G779" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H779" s="8" t="n"/>
@@ -46343,12 +46343,12 @@
       <c r="L779" s="9" t="n"/>
       <c r="M779" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N779" s="11" t="inlineStr">
         <is>
-          <t>https://www.daido-h.ed.jp/access/</t>
+          <t>https://ohka-hs.com/profile/</t>
         </is>
       </c>
       <c r="O779" s="12" t="inlineStr">
@@ -46368,17 +46368,17 @@
       </c>
       <c r="C780" s="5" t="inlineStr">
         <is>
-          <t>名古屋市昭和区</t>
+          <t>岡崎市</t>
         </is>
       </c>
       <c r="D780" s="5" t="inlineStr">
         <is>
-          <t>中京大学附属中京高等学校</t>
+          <t>岡崎城西高等学校</t>
         </is>
       </c>
       <c r="E780" s="6" t="inlineStr">
         <is>
-          <t>052-761-5311</t>
+          <t>0564-31-4165</t>
         </is>
       </c>
       <c r="F780" s="7" t="inlineStr">
@@ -46402,12 +46402,12 @@
       <c r="L780" s="9" t="n"/>
       <c r="M780" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載。通信制課程も同じ番号</t>
+          <t>公式サイトで確認（安城学園岡崎城西）</t>
         </is>
       </c>
       <c r="N780" s="11" t="inlineStr">
         <is>
-          <t>https://www.chukyo.ed.jp/contact/</t>
+          <t>https://www.johsei.jp/contact/</t>
         </is>
       </c>
       <c r="O780" s="12" t="inlineStr">
@@ -46427,17 +46427,17 @@
       </c>
       <c r="C781" s="5" t="inlineStr">
         <is>
-          <t>日進市</t>
+          <t>名古屋市守山区</t>
         </is>
       </c>
       <c r="D781" s="5" t="inlineStr">
         <is>
-          <t>中部大学第一高等学校</t>
+          <t>菊華高等学校</t>
         </is>
       </c>
       <c r="E781" s="6" t="inlineStr">
         <is>
-          <t>0561-73-8111</t>
+          <t>052-791-8261</t>
         </is>
       </c>
       <c r="F781" s="7" t="inlineStr">
@@ -46461,12 +46461,12 @@
       <c r="L781" s="9" t="n"/>
       <c r="M781" s="10" t="inlineStr">
         <is>
-          <t>2つのサイトで一致、公式未確認</t>
+          <t>全日制の本校の番号（公式サイト）</t>
         </is>
       </c>
       <c r="N781" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/23230/ILSP0000041881_ipclm/ ; https://www.gakkou.net/kou/view/index_303623.html</t>
+          <t>https://kikuka.ed.jp/</t>
         </is>
       </c>
       <c r="O781" s="12" t="inlineStr">
@@ -46486,17 +46486,17 @@
       </c>
       <c r="C782" s="5" t="inlineStr">
         <is>
-          <t>春日井市</t>
+          <t>名古屋市瑞穂区</t>
         </is>
       </c>
       <c r="D782" s="5" t="inlineStr">
         <is>
-          <t>中部大学春日丘高等学校</t>
+          <t>享栄高等学校</t>
         </is>
       </c>
       <c r="E782" s="6" t="inlineStr">
         <is>
-          <t>0568-51-1131</t>
+          <t>052-841-8151</t>
         </is>
       </c>
       <c r="F782" s="7" t="inlineStr">
@@ -46506,7 +46506,7 @@
       </c>
       <c r="G782" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H782" s="8" t="n"/>
@@ -46520,12 +46520,12 @@
       <c r="L782" s="9" t="n"/>
       <c r="M782" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中学校は0568-51-1115</t>
+          <t>公式サイトに「代表」と記載</t>
         </is>
       </c>
       <c r="N782" s="11" t="inlineStr">
         <is>
-          <t>https://www.haruhigaoka.ed.jp/senior/ ; https://www.city.kasugai.lg.jp/shisei/shisetsu/kosodate/1010552/1010560.html</t>
+          <t>https://www.kyoei-h.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O782" s="12" t="inlineStr">
@@ -46545,17 +46545,17 @@
       </c>
       <c r="C783" s="5" t="inlineStr">
         <is>
-          <t>新城市</t>
+          <t>名古屋市東区</t>
         </is>
       </c>
       <c r="D783" s="5" t="inlineStr">
         <is>
-          <t>黄柳野高等学校</t>
+          <t>金城学院高等学校</t>
         </is>
       </c>
       <c r="E783" s="6" t="inlineStr">
         <is>
-          <t>0536-34-0330</t>
+          <t>052-931-6236</t>
         </is>
       </c>
       <c r="F783" s="7" t="inlineStr">
@@ -46579,12 +46579,12 @@
       <c r="L783" s="9" t="n"/>
       <c r="M783" s="10" t="inlineStr">
         <is>
-          <t>複数サイトで一致、公式未確認</t>
+          <t>高校の番号（公式サイト）。中学校は052-931-0821、大学は別番号</t>
         </is>
       </c>
       <c r="N783" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/23221/ILSP0000041060_ipclm/ ; https://www.navitime.co.jp/poi?spot=00004-23108700184</t>
+          <t>https://www.hs.kinjo-u.ac.jp/contact/</t>
         </is>
       </c>
       <c r="O783" s="12" t="inlineStr">
@@ -46604,27 +46604,27 @@
       </c>
       <c r="C784" s="5" t="inlineStr">
         <is>
-          <t>名古屋市天白区</t>
+          <t>名古屋市西区</t>
         </is>
       </c>
       <c r="D784" s="5" t="inlineStr">
         <is>
-          <t>東海学園高等学校</t>
+          <t>啓明学館高等学校</t>
         </is>
       </c>
       <c r="E784" s="6" t="inlineStr">
         <is>
-          <t>052-801-6222</t>
-        </is>
-      </c>
-      <c r="F784" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>052-571-2561</t>
+        </is>
+      </c>
+      <c r="F784" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="G784" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H784" s="8" t="n"/>
@@ -46638,12 +46638,12 @@
       <c r="L784" s="9" t="n"/>
       <c r="M784" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。東海高校（東区）とは別の学校</t>
+          <t>公式サイトの事務所の番号（「代表」の表記なし）。職員室は052-571-7366</t>
         </is>
       </c>
       <c r="N784" s="11" t="inlineStr">
         <is>
-          <t>https://tokaigakuen.ed.jp/</t>
+          <t>https://keimeigakkan-h.ed.jp/</t>
         </is>
       </c>
       <c r="O784" s="12" t="inlineStr">
@@ -46663,22 +46663,22 @@
       </c>
       <c r="C785" s="5" t="inlineStr">
         <is>
-          <t>名古屋市東区</t>
+          <t>豊橋市</t>
         </is>
       </c>
       <c r="D785" s="5" t="inlineStr">
         <is>
-          <t>東海高等学校</t>
+          <t>桜丘高等学校（愛知県）</t>
         </is>
       </c>
       <c r="E785" s="6" t="inlineStr">
         <is>
-          <t>052-936-5111</t>
-        </is>
-      </c>
-      <c r="F785" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>0570-039-396</t>
+        </is>
+      </c>
+      <c r="F785" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="G785" s="5" t="inlineStr">
@@ -46697,12 +46697,12 @@
       <c r="L785" s="9" t="n"/>
       <c r="M785" s="10" t="inlineStr">
         <is>
-          <t>中高共通の代表（事務所）。高校の直通は052-936-5112。東海学園（天白区）とは別の学校</t>
+          <t>公式サイトのナビダイヤル（学園・高校共通、通話料がかかる番号）。旧番号0532-61-6421が一部サイトに残る</t>
         </is>
       </c>
       <c r="N785" s="11" t="inlineStr">
         <is>
-          <t>https://www.tokai-jh.ed.jp/profile/06.html</t>
+          <t>https://www.sakuragaoka-gakuen.ed.jp/h/</t>
         </is>
       </c>
       <c r="O785" s="12" t="inlineStr">
@@ -46722,17 +46722,17 @@
       </c>
       <c r="C786" s="5" t="inlineStr">
         <is>
-          <t>名古屋市名東区</t>
+          <t>名古屋市東区</t>
         </is>
       </c>
       <c r="D786" s="5" t="inlineStr">
         <is>
-          <t>東邦高等学校</t>
+          <t>至学館高等学校</t>
         </is>
       </c>
       <c r="E786" s="6" t="inlineStr">
         <is>
-          <t>052-782-1171</t>
+          <t>052-723-0851</t>
         </is>
       </c>
       <c r="F786" s="7" t="inlineStr">
@@ -46756,12 +46756,12 @@
       <c r="L786" s="9" t="n"/>
       <c r="M786" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載。052-782-1241は愛知東邦大学の番号</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N786" s="11" t="inlineStr">
         <is>
-          <t>https://www.toho-h.ed.jp/</t>
+          <t>https://www.shigakukan-h.ed.jp/</t>
         </is>
       </c>
       <c r="O786" s="12" t="inlineStr">
@@ -46781,17 +46781,17 @@
       </c>
       <c r="C787" s="5" t="inlineStr">
         <is>
-          <t>豊田市</t>
+          <t>一宮市</t>
         </is>
       </c>
       <c r="D787" s="5" t="inlineStr">
         <is>
-          <t>杜若高等学校</t>
+          <t>修文学院高等学校</t>
         </is>
       </c>
       <c r="E787" s="6" t="inlineStr">
         <is>
-          <t>0565-45-5000</t>
+          <t>0586-45-2102</t>
         </is>
       </c>
       <c r="F787" s="7" t="inlineStr">
@@ -46801,7 +46801,7 @@
       </c>
       <c r="G787" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H787" s="8" t="n"/>
@@ -46815,12 +46815,12 @@
       <c r="L787" s="9" t="n"/>
       <c r="M787" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトで確認。【校名変更】2022年に修文女子高校から改称・共学化</t>
         </is>
       </c>
       <c r="N787" s="11" t="inlineStr">
         <is>
-          <t>https://www.tojaku-h.ed.jp/</t>
+          <t>https://www.gakuin-hs.shubun.ac.jp/contact</t>
         </is>
       </c>
       <c r="O787" s="12" t="inlineStr">
@@ -46840,17 +46840,17 @@
       </c>
       <c r="C788" s="5" t="inlineStr">
         <is>
-          <t>豊川市</t>
+          <t>名古屋市千種区</t>
         </is>
       </c>
       <c r="D788" s="5" t="inlineStr">
         <is>
-          <t>豊川高等学校</t>
+          <t>椙山女学園高等学校</t>
         </is>
       </c>
       <c r="E788" s="6" t="inlineStr">
         <is>
-          <t>0533-86-4121</t>
+          <t>052-751-8131</t>
         </is>
       </c>
       <c r="F788" s="7" t="inlineStr">
@@ -46874,12 +46874,12 @@
       <c r="L788" s="9" t="n"/>
       <c r="M788" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「学校代表」と記載</t>
+          <t>公式サイトに「代表」と記載</t>
         </is>
       </c>
       <c r="N788" s="11" t="inlineStr">
         <is>
-          <t>https://toyokawa.ed.jp/contact</t>
+          <t>https://www.sugiyama-u.ac.jp/high/index.html</t>
         </is>
       </c>
       <c r="O788" s="12" t="inlineStr">
@@ -46899,17 +46899,17 @@
       </c>
       <c r="C789" s="5" t="inlineStr">
         <is>
-          <t>豊田市</t>
+          <t>瀬戸市</t>
         </is>
       </c>
       <c r="D789" s="5" t="inlineStr">
         <is>
-          <t>豊田大谷高等学校</t>
+          <t>聖カピタニオ女子高等学校</t>
         </is>
       </c>
       <c r="E789" s="6" t="inlineStr">
         <is>
-          <t>0565-48-3511</t>
+          <t>0561-82-7711</t>
         </is>
       </c>
       <c r="F789" s="7" t="inlineStr">
@@ -46933,12 +46933,12 @@
       <c r="L789" s="9" t="n"/>
       <c r="M789" s="10" t="inlineStr">
         <is>
-          <t>2つのサイトで一致（代表として掲載）、公式未確認</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N789" s="11" t="inlineStr">
         <is>
-          <t>https://www.navita.co.jp/s/11101207/ ; https://www.mapion.co.jp/phonebook/M11004/23211/ILSP0000041953_ipclm/</t>
+          <t>https://www.st-capitanio.ed.jp/access/access.html</t>
         </is>
       </c>
       <c r="O789" s="12" t="inlineStr">
@@ -46958,17 +46958,17 @@
       </c>
       <c r="C790" s="5" t="inlineStr">
         <is>
-          <t>豊橋市</t>
+          <t>扶桑町</t>
         </is>
       </c>
       <c r="D790" s="5" t="inlineStr">
         <is>
-          <t>豊橋中央高等学校</t>
+          <t>誠信高等学校</t>
         </is>
       </c>
       <c r="E790" s="6" t="inlineStr">
         <is>
-          <t>0532-54-1301</t>
+          <t>0587-93-5380</t>
         </is>
       </c>
       <c r="F790" s="7" t="inlineStr">
@@ -46978,7 +46978,7 @@
       </c>
       <c r="G790" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H790" s="8" t="n"/>
@@ -46992,12 +46992,12 @@
       <c r="L790" s="9" t="n"/>
       <c r="M790" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトに「代表」と記載。0587-93-8172はFAXなので注意</t>
         </is>
       </c>
       <c r="N790" s="11" t="inlineStr">
         <is>
-          <t>https://toyohashi-chuo.ed.jp/?page_id=53</t>
+          <t>https://www.a-seishin.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O790" s="12" t="inlineStr">
@@ -47017,27 +47017,27 @@
       </c>
       <c r="C791" s="5" t="inlineStr">
         <is>
-          <t>名古屋市中村区</t>
+          <t>豊明市</t>
         </is>
       </c>
       <c r="D791" s="5" t="inlineStr">
         <is>
-          <t>同朋高等学校</t>
+          <t>星城高等学校</t>
         </is>
       </c>
       <c r="E791" s="6" t="inlineStr">
         <is>
-          <t>052-411-1159</t>
-        </is>
-      </c>
-      <c r="F791" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>0562-97-3111</t>
+        </is>
+      </c>
+      <c r="F791" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="G791" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H791" s="8" t="n"/>
@@ -47051,12 +47051,12 @@
       <c r="L791" s="9" t="n"/>
       <c r="M791" s="10" t="inlineStr">
         <is>
-          <t>公式サイトの職員室の番号。入試広報室は052-411-1216。ほかの番号を載せるサイトもあり</t>
+          <t>公式サイトに「代表」と記載</t>
         </is>
       </c>
       <c r="N791" s="11" t="inlineStr">
         <is>
-          <t>https://www.doho-h.ed.jp/</t>
+          <t>https://www.seijoh.ed.jp/</t>
         </is>
       </c>
       <c r="O791" s="12" t="inlineStr">
@@ -47076,17 +47076,17 @@
       </c>
       <c r="C792" s="5" t="inlineStr">
         <is>
-          <t>名古屋市瑞穂区</t>
+          <t>愛西市</t>
         </is>
       </c>
       <c r="D792" s="5" t="inlineStr">
         <is>
-          <t>名古屋葵大学高等学校</t>
+          <t>清林館高等学校</t>
         </is>
       </c>
       <c r="E792" s="6" t="inlineStr">
         <is>
-          <t>052-841-8181</t>
+          <t>0567-28-3010</t>
         </is>
       </c>
       <c r="F792" s="7" t="inlineStr">
@@ -47110,12 +47110,12 @@
       <c r="L792" s="9" t="n"/>
       <c r="M792" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通。【校名変更】2025年4月に名古屋女子大学高校から改称</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N792" s="11" t="inlineStr">
         <is>
-          <t>https://www.nagoya-aoi.ed.jp/contact/</t>
+          <t>https://www.seirinkan.ed.jp/high/access</t>
         </is>
       </c>
       <c r="O792" s="12" t="inlineStr">
@@ -47135,17 +47135,17 @@
       </c>
       <c r="C793" s="5" t="inlineStr">
         <is>
-          <t>名古屋市瑞穂区</t>
+          <t>瀬戸市</t>
         </is>
       </c>
       <c r="D793" s="5" t="inlineStr">
         <is>
-          <t>名古屋大谷高等学校</t>
+          <t>聖霊高等学校</t>
         </is>
       </c>
       <c r="E793" s="6" t="inlineStr">
         <is>
-          <t>052-852-1121</t>
+          <t>0561-21-3121</t>
         </is>
       </c>
       <c r="F793" s="7" t="inlineStr">
@@ -47155,7 +47155,7 @@
       </c>
       <c r="G793" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H793" s="8" t="n"/>
@@ -47169,12 +47169,12 @@
       <c r="L793" s="9" t="n"/>
       <c r="M793" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N793" s="11" t="inlineStr">
         <is>
-          <t>https://nagoyaotani.owari.ac.jp/access/</t>
+          <t>https://www.seto-seirei-js.ed.jp/</t>
         </is>
       </c>
       <c r="O793" s="12" t="inlineStr">
@@ -47194,17 +47194,17 @@
       </c>
       <c r="C794" s="5" t="inlineStr">
         <is>
-          <t>名古屋市千種区</t>
+          <t>一宮市</t>
         </is>
       </c>
       <c r="D794" s="5" t="inlineStr">
         <is>
-          <t>名古屋経済大学市邨高等学校</t>
+          <t>大成高等学校（愛知県）</t>
         </is>
       </c>
       <c r="E794" s="6" t="inlineStr">
         <is>
-          <t>052-721-0161</t>
+          <t>0586-77-9900</t>
         </is>
       </c>
       <c r="F794" s="7" t="inlineStr">
@@ -47228,12 +47228,12 @@
       <c r="L794" s="9" t="n"/>
       <c r="M794" s="10" t="inlineStr">
         <is>
-          <t>公式資料に「代表」と記載</t>
+          <t>公式サイトと一宮市のサイトで一致</t>
         </is>
       </c>
       <c r="N794" s="11" t="inlineStr">
         <is>
-          <t>https://ichimura.ed.jp/access/</t>
+          <t>https://www.aichi-shinwa-taisei.ed.jp/high/ ; https://www.city.ichinomiya.aichi.jp/shisetsu/hoikugakko/1008935/1009298.html</t>
         </is>
       </c>
       <c r="O794" s="12" t="inlineStr">
@@ -47253,17 +47253,17 @@
       </c>
       <c r="C795" s="5" t="inlineStr">
         <is>
-          <t>名古屋市瑞穂区</t>
+          <t>江南市</t>
         </is>
       </c>
       <c r="D795" s="5" t="inlineStr">
         <is>
-          <t>名古屋経済大学高蔵高等学校</t>
+          <t>滝高等学校</t>
         </is>
       </c>
       <c r="E795" s="6" t="inlineStr">
         <is>
-          <t>052-853-0050</t>
+          <t>0587-56-2127</t>
         </is>
       </c>
       <c r="F795" s="7" t="inlineStr">
@@ -47273,7 +47273,7 @@
       </c>
       <c r="G795" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H795" s="8" t="n"/>
@@ -47287,12 +47287,12 @@
       <c r="L795" s="9" t="n"/>
       <c r="M795" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N795" s="11" t="inlineStr">
         <is>
-          <t>https://www.takakura-hj.info/access</t>
+          <t>https://www.taki-hj.ac.jp/guide/access.html</t>
         </is>
       </c>
       <c r="O795" s="12" t="inlineStr">
@@ -47312,17 +47312,17 @@
       </c>
       <c r="C796" s="5" t="inlineStr">
         <is>
-          <t>名古屋市昭和区</t>
+          <t>名古屋市南区</t>
         </is>
       </c>
       <c r="D796" s="5" t="inlineStr">
         <is>
-          <t>名古屋工業高等学校</t>
+          <t>大同大学大同高等学校</t>
         </is>
       </c>
       <c r="E796" s="6" t="inlineStr">
         <is>
-          <t>052-871-2681</t>
+          <t>052-611-0511</t>
         </is>
       </c>
       <c r="F796" s="7" t="inlineStr">
@@ -47332,7 +47332,7 @@
       </c>
       <c r="G796" s="5" t="inlineStr">
         <is>
-          <t>専門学科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H796" s="8" t="n"/>
@@ -47346,12 +47346,12 @@
       <c r="L796" s="9" t="n"/>
       <c r="M796" s="10" t="inlineStr">
         <is>
-          <t>公式サイトと愛知県私学協会の資料で一致（私立）</t>
+          <t>公式サイトに「代表」と記載</t>
         </is>
       </c>
       <c r="N796" s="11" t="inlineStr">
         <is>
-          <t>https://nagoya-th.ed.jp/ ; https://www.aichi-shigaku.gr.jp/guidebook2025/pageindices/index68.html</t>
+          <t>https://www.daido-h.ed.jp/access/</t>
         </is>
       </c>
       <c r="O796" s="12" t="inlineStr">
@@ -47371,17 +47371,17 @@
       </c>
       <c r="C797" s="5" t="inlineStr">
         <is>
-          <t>名古屋市東区</t>
+          <t>名古屋市昭和区</t>
         </is>
       </c>
       <c r="D797" s="5" t="inlineStr">
         <is>
-          <t>名古屋高等学校</t>
+          <t>中京大学附属中京高等学校</t>
         </is>
       </c>
       <c r="E797" s="6" t="inlineStr">
         <is>
-          <t>052-721-5271</t>
+          <t>052-761-5311</t>
         </is>
       </c>
       <c r="F797" s="7" t="inlineStr">
@@ -47405,12 +47405,12 @@
       <c r="L797" s="9" t="n"/>
       <c r="M797" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。052-722-2835は同窓会の番号</t>
+          <t>公式サイトに「代表」と記載。通信制課程も同じ番号</t>
         </is>
       </c>
       <c r="N797" s="11" t="inlineStr">
         <is>
-          <t>https://www.meigaku.ac.jp/access/</t>
+          <t>https://www.chukyo.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O797" s="12" t="inlineStr">
@@ -47430,22 +47430,22 @@
       </c>
       <c r="C798" s="5" t="inlineStr">
         <is>
-          <t>名古屋市昭和区</t>
+          <t>日進市</t>
         </is>
       </c>
       <c r="D798" s="5" t="inlineStr">
         <is>
-          <t>名古屋国際高等学校</t>
+          <t>中部大学第一高等学校</t>
         </is>
       </c>
       <c r="E798" s="6" t="inlineStr">
         <is>
-          <t>052-858-2200</t>
-        </is>
-      </c>
-      <c r="F798" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>0561-73-8111</t>
+        </is>
+      </c>
+      <c r="F798" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="G798" s="5" t="inlineStr">
@@ -47464,12 +47464,12 @@
       <c r="L798" s="9" t="n"/>
       <c r="M798" s="10" t="inlineStr">
         <is>
-          <t>中高代表として掲載。高校の番号として052-853-5151を載せるサイトもあり食い違い</t>
+          <t>2つのサイトで一致、公式未確認</t>
         </is>
       </c>
       <c r="N798" s="11" t="inlineStr">
         <is>
-          <t>https://www.unesco-school.mext.go.jp/schools/list/nagoya-international-junior-senior-high-school/ ; https://www.aichi.sc/gakkou/kokusai/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/23230/ILSP0000041881_ipclm/ ; https://www.gakkou.net/kou/view/index_303623.html</t>
         </is>
       </c>
       <c r="O798" s="12" t="inlineStr">
@@ -47489,17 +47489,17 @@
       </c>
       <c r="C799" s="5" t="inlineStr">
         <is>
-          <t>名古屋市中区</t>
+          <t>春日井市</t>
         </is>
       </c>
       <c r="D799" s="5" t="inlineStr">
         <is>
-          <t>名古屋たちばな高等学校</t>
+          <t>中部大学春日丘高等学校</t>
         </is>
       </c>
       <c r="E799" s="6" t="inlineStr">
         <is>
-          <t>052-322-1911</t>
+          <t>0568-51-1131</t>
         </is>
       </c>
       <c r="F799" s="7" t="inlineStr">
@@ -47509,7 +47509,7 @@
       </c>
       <c r="G799" s="5" t="inlineStr">
         <is>
-          <t>専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H799" s="8" t="n"/>
@@ -47523,12 +47523,12 @@
       <c r="L799" s="9" t="n"/>
       <c r="M799" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトで確認。中学校は0568-51-1115</t>
         </is>
       </c>
       <c r="N799" s="11" t="inlineStr">
         <is>
-          <t>https://tachibana-hs.ed.jp/</t>
+          <t>https://www.haruhigaoka.ed.jp/senior/ ; https://www.city.kasugai.lg.jp/shisei/shisetsu/kosodate/1010552/1010560.html</t>
         </is>
       </c>
       <c r="O799" s="12" t="inlineStr">
@@ -47548,17 +47548,17 @@
       </c>
       <c r="C800" s="5" t="inlineStr">
         <is>
-          <t>名古屋市昭和区</t>
+          <t>新城市</t>
         </is>
       </c>
       <c r="D800" s="5" t="inlineStr">
         <is>
-          <t>南山高等学校 女子部</t>
+          <t>黄柳野高等学校</t>
         </is>
       </c>
       <c r="E800" s="6" t="inlineStr">
         <is>
-          <t>052-831-0704</t>
+          <t>0536-34-0330</t>
         </is>
       </c>
       <c r="F800" s="7" t="inlineStr">
@@ -47582,12 +47582,12 @@
       <c r="L800" s="9" t="n"/>
       <c r="M800" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通。男子部とは別番号</t>
+          <t>複数サイトで一致、公式未確認</t>
         </is>
       </c>
       <c r="N800" s="11" t="inlineStr">
         <is>
-          <t>https://www.nanzan-girls.ed.jp/access.html</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/23221/ILSP0000041060_ipclm/ ; https://www.navitime.co.jp/poi?spot=00004-23108700184</t>
         </is>
       </c>
       <c r="O800" s="12" t="inlineStr">
@@ -47607,17 +47607,17 @@
       </c>
       <c r="C801" s="5" t="inlineStr">
         <is>
-          <t>名古屋市昭和区</t>
+          <t>名古屋市天白区</t>
         </is>
       </c>
       <c r="D801" s="5" t="inlineStr">
         <is>
-          <t>南山高等学校 男子部</t>
+          <t>東海学園高等学校</t>
         </is>
       </c>
       <c r="E801" s="6" t="inlineStr">
         <is>
-          <t>052-831-6455</t>
+          <t>052-801-6222</t>
         </is>
       </c>
       <c r="F801" s="7" t="inlineStr">
@@ -47641,12 +47641,12 @@
       <c r="L801" s="9" t="n"/>
       <c r="M801" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。女子部とは別番号</t>
+          <t>公式サイトで確認。東海高校（東区）とは別の学校</t>
         </is>
       </c>
       <c r="N801" s="11" t="inlineStr">
         <is>
-          <t>https://www.nanzan-boys.ed.jp/</t>
+          <t>https://tokaigakuen.ed.jp/</t>
         </is>
       </c>
       <c r="O801" s="12" t="inlineStr">
@@ -47666,17 +47666,17 @@
       </c>
       <c r="C802" s="5" t="inlineStr">
         <is>
-          <t>美浜町</t>
+          <t>名古屋市東区</t>
         </is>
       </c>
       <c r="D802" s="5" t="inlineStr">
         <is>
-          <t>日本福祉大学付属高等学校</t>
+          <t>東海高等学校</t>
         </is>
       </c>
       <c r="E802" s="6" t="inlineStr">
         <is>
-          <t>0569-87-2311</t>
+          <t>052-936-5111</t>
         </is>
       </c>
       <c r="F802" s="7" t="inlineStr">
@@ -47700,12 +47700,12 @@
       <c r="L802" s="9" t="n"/>
       <c r="M802" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。大学の代表（0569-87-2211）とは別</t>
+          <t>中高共通の代表（事務所）。高校の直通は052-936-5112。東海学園（天白区）とは別の学校</t>
         </is>
       </c>
       <c r="N802" s="11" t="inlineStr">
         <is>
-          <t>https://www.n-fukushi.ac.jp/koukou/</t>
+          <t>https://www.tokai-jh.ed.jp/profile/06.html</t>
         </is>
       </c>
       <c r="O802" s="12" t="inlineStr">
@@ -47725,17 +47725,17 @@
       </c>
       <c r="C803" s="5" t="inlineStr">
         <is>
-          <t>岡崎市</t>
+          <t>名古屋市名東区</t>
         </is>
       </c>
       <c r="D803" s="5" t="inlineStr">
         <is>
-          <t>人間環境大学附属岡崎高等学校</t>
+          <t>東邦高等学校</t>
         </is>
       </c>
       <c r="E803" s="6" t="inlineStr">
         <is>
-          <t>0564-22-0274</t>
+          <t>052-782-1171</t>
         </is>
       </c>
       <c r="F803" s="7" t="inlineStr">
@@ -47745,7 +47745,7 @@
       </c>
       <c r="G803" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H803" s="8" t="n"/>
@@ -47759,12 +47759,12 @@
       <c r="L803" s="9" t="n"/>
       <c r="M803" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。2022年に旧校名から改称</t>
+          <t>公式サイトに「代表」と記載。052-782-1241は愛知東邦大学の番号</t>
         </is>
       </c>
       <c r="N803" s="11" t="inlineStr">
         <is>
-          <t>https://www.jinkan-okazaki.ed.jp/about/</t>
+          <t>https://www.toho-h.ed.jp/</t>
         </is>
       </c>
       <c r="O803" s="12" t="inlineStr">
@@ -47784,17 +47784,17 @@
       </c>
       <c r="C804" s="5" t="inlineStr">
         <is>
-          <t>岡崎市</t>
+          <t>豊田市</t>
         </is>
       </c>
       <c r="D804" s="5" t="inlineStr">
         <is>
-          <t>光ヶ丘女子高等学校</t>
+          <t>杜若高等学校</t>
         </is>
       </c>
       <c r="E804" s="6" t="inlineStr">
         <is>
-          <t>0564-51-5651</t>
+          <t>0565-45-5000</t>
         </is>
       </c>
       <c r="F804" s="7" t="inlineStr">
@@ -47804,7 +47804,7 @@
       </c>
       <c r="G804" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H804" s="8" t="n"/>
@@ -47823,7 +47823,7 @@
       </c>
       <c r="N804" s="11" t="inlineStr">
         <is>
-          <t>https://hikarigaoka-h.ed.jp/</t>
+          <t>https://www.tojaku-h.ed.jp/</t>
         </is>
       </c>
       <c r="O804" s="12" t="inlineStr">
@@ -47843,17 +47843,17 @@
       </c>
       <c r="C805" s="5" t="inlineStr">
         <is>
-          <t>豊橋市</t>
+          <t>豊川市</t>
         </is>
       </c>
       <c r="D805" s="5" t="inlineStr">
         <is>
-          <t>藤ノ花女子高等学校</t>
+          <t>豊川高等学校</t>
         </is>
       </c>
       <c r="E805" s="6" t="inlineStr">
         <is>
-          <t>0532-61-5468</t>
+          <t>0533-86-4121</t>
         </is>
       </c>
       <c r="F805" s="7" t="inlineStr">
@@ -47863,7 +47863,7 @@
       </c>
       <c r="G805" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H805" s="8" t="n"/>
@@ -47877,12 +47877,12 @@
       <c r="L805" s="9" t="n"/>
       <c r="M805" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトに「学校代表」と記載</t>
         </is>
       </c>
       <c r="N805" s="11" t="inlineStr">
         <is>
-          <t>https://www.fujinohana-h.ed.jp/</t>
+          <t>https://toyokawa.ed.jp/contact</t>
         </is>
       </c>
       <c r="O805" s="12" t="inlineStr">
@@ -47902,17 +47902,17 @@
       </c>
       <c r="C806" s="5" t="inlineStr">
         <is>
-          <t>小牧市</t>
+          <t>豊田市</t>
         </is>
       </c>
       <c r="D806" s="5" t="inlineStr">
         <is>
-          <t>誉高等学校</t>
+          <t>豊田大谷高等学校</t>
         </is>
       </c>
       <c r="E806" s="6" t="inlineStr">
         <is>
-          <t>0568-79-7700</t>
+          <t>0565-48-3511</t>
         </is>
       </c>
       <c r="F806" s="7" t="inlineStr">
@@ -47936,12 +47936,12 @@
       <c r="L806" s="9" t="n"/>
       <c r="M806" s="10" t="inlineStr">
         <is>
-          <t>小牧市のサイトほかで一致、公式未確認</t>
+          <t>2つのサイトで一致（代表として掲載）、公式未確認</t>
         </is>
       </c>
       <c r="N806" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/23219/ILSP0000041861_ipclm/ ; https://www.city.komaki.aichi.jp/admin/soshiki/fumei/highscool/4872.html</t>
+          <t>https://www.navita.co.jp/s/11101207/ ; https://www.mapion.co.jp/phonebook/M11004/23211/ILSP0000041953_ipclm/</t>
         </is>
       </c>
       <c r="O806" s="12" t="inlineStr">
@@ -47961,17 +47961,17 @@
       </c>
       <c r="C807" s="5" t="inlineStr">
         <is>
-          <t>名古屋市中村区</t>
+          <t>豊橋市</t>
         </is>
       </c>
       <c r="D807" s="5" t="inlineStr">
         <is>
-          <t>名城大学附属高等学校</t>
+          <t>豊橋中央高等学校</t>
         </is>
       </c>
       <c r="E807" s="6" t="inlineStr">
         <is>
-          <t>052-481-7436</t>
+          <t>0532-54-1301</t>
         </is>
       </c>
       <c r="F807" s="7" t="inlineStr">
@@ -47981,7 +47981,7 @@
       </c>
       <c r="G807" s="5" t="inlineStr">
         <is>
-          <t>普通科・総合学科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H807" s="8" t="n"/>
@@ -48000,7 +48000,7 @@
       </c>
       <c r="N807" s="11" t="inlineStr">
         <is>
-          <t>https://www.meijo-h.ed.jp/profile/</t>
+          <t>https://toyohashi-chuo.ed.jp/?page_id=53</t>
         </is>
       </c>
       <c r="O807" s="12" t="inlineStr">
@@ -48015,32 +48015,32 @@
       </c>
       <c r="B808" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C808" s="5" t="inlineStr">
         <is>
-          <t>伊賀市</t>
+          <t>名古屋市中村区</t>
         </is>
       </c>
       <c r="D808" s="5" t="inlineStr">
         <is>
-          <t>愛農学園農業高等学校</t>
+          <t>同朋高等学校</t>
         </is>
       </c>
       <c r="E808" s="6" t="inlineStr">
         <is>
-          <t>0595-52-0327</t>
-        </is>
-      </c>
-      <c r="F808" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>052-411-1159</t>
+        </is>
+      </c>
+      <c r="F808" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="G808" s="5" t="inlineStr">
         <is>
-          <t>専門学科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H808" s="8" t="n"/>
@@ -48054,12 +48054,12 @@
       <c r="L808" s="9" t="n"/>
       <c r="M808" s="10" t="inlineStr">
         <is>
-          <t>公式サイトほかで一致</t>
+          <t>公式サイトの職員室の番号。入試広報室は052-411-1216。ほかの番号を載せるサイトもあり</t>
         </is>
       </c>
       <c r="N808" s="11" t="inlineStr">
         <is>
-          <t>https://ainogakuen.ed.jp/ ; https://www.mapion.co.jp/phonebook/M11004/24216/ILSP0000041735_ipclm/</t>
+          <t>https://www.doho-h.ed.jp/</t>
         </is>
       </c>
       <c r="O808" s="12" t="inlineStr">
@@ -48074,22 +48074,22 @@
       </c>
       <c r="B809" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C809" s="5" t="inlineStr">
         <is>
-          <t>津市</t>
+          <t>名古屋市瑞穂区</t>
         </is>
       </c>
       <c r="D809" s="5" t="inlineStr">
         <is>
-          <t>青山高等学校（三重県）</t>
+          <t>名古屋葵大学高等学校</t>
         </is>
       </c>
       <c r="E809" s="6" t="inlineStr">
         <is>
-          <t>059-262-4321</t>
+          <t>052-841-8181</t>
         </is>
       </c>
       <c r="F809" s="7" t="inlineStr">
@@ -48113,12 +48113,12 @@
       <c r="L809" s="9" t="n"/>
       <c r="M809" s="10" t="inlineStr">
         <is>
-          <t>公式サイトに「代表」と記載</t>
+          <t>公式サイトで確認。中高共通。【校名変更】2025年4月に名古屋女子大学高校から改称</t>
         </is>
       </c>
       <c r="N809" s="11" t="inlineStr">
         <is>
-          <t>https://aoyama-h.ed.jp/</t>
+          <t>https://www.nagoya-aoi.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O809" s="12" t="inlineStr">
@@ -48133,32 +48133,32 @@
       </c>
       <c r="B810" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C810" s="5" t="inlineStr">
         <is>
-          <t>四日市市</t>
+          <t>名古屋市瑞穂区</t>
         </is>
       </c>
       <c r="D810" s="5" t="inlineStr">
         <is>
-          <t>暁高等学校</t>
+          <t>名古屋大谷高等学校</t>
         </is>
       </c>
       <c r="E810" s="6" t="inlineStr">
         <is>
-          <t>059-337-2347</t>
-        </is>
-      </c>
-      <c r="F810" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>052-852-1121</t>
+        </is>
+      </c>
+      <c r="F810" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="G810" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H810" s="8" t="n"/>
@@ -48172,12 +48172,12 @@
       <c r="L810" s="9" t="n"/>
       <c r="M810" s="10" t="inlineStr">
         <is>
-          <t>公式サイトの3年制課程の番号（「代表」の表記なし）。中高一貫（6年制）は059-337-1213。059-337-2345を載せるサイトもあり</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N810" s="11" t="inlineStr">
         <is>
-          <t>https://www.akatsuki.ed.jp/akatsuki-h/</t>
+          <t>https://nagoyaotani.owari.ac.jp/access/</t>
         </is>
       </c>
       <c r="O810" s="12" t="inlineStr">
@@ -48192,22 +48192,22 @@
       </c>
       <c r="B811" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C811" s="5" t="inlineStr">
         <is>
-          <t>伊勢市</t>
+          <t>名古屋市千種区</t>
         </is>
       </c>
       <c r="D811" s="5" t="inlineStr">
         <is>
-          <t>伊勢学園高等学校</t>
+          <t>名古屋経済大学市邨高等学校</t>
         </is>
       </c>
       <c r="E811" s="6" t="inlineStr">
         <is>
-          <t>0596-22-4155</t>
+          <t>052-721-0161</t>
         </is>
       </c>
       <c r="F811" s="7" t="inlineStr">
@@ -48231,12 +48231,12 @@
       <c r="L811" s="9" t="n"/>
       <c r="M811" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。0596-22-4836は法人事務局の番号</t>
+          <t>公式資料に「代表」と記載</t>
         </is>
       </c>
       <c r="N811" s="11" t="inlineStr">
         <is>
-          <t>https://www.isegakuen.ac.jp/contact.html</t>
+          <t>https://ichimura.ed.jp/access/</t>
         </is>
       </c>
       <c r="O811" s="12" t="inlineStr">
@@ -48251,22 +48251,22 @@
       </c>
       <c r="B812" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C812" s="5" t="inlineStr">
         <is>
-          <t>伊勢市</t>
+          <t>名古屋市瑞穂区</t>
         </is>
       </c>
       <c r="D812" s="5" t="inlineStr">
         <is>
-          <t>英心高等学校</t>
+          <t>名古屋経済大学高蔵高等学校</t>
         </is>
       </c>
       <c r="E812" s="6" t="inlineStr">
         <is>
-          <t>0596-28-2077</t>
+          <t>052-853-0050</t>
         </is>
       </c>
       <c r="F812" s="7" t="inlineStr">
@@ -48276,7 +48276,7 @@
       </c>
       <c r="G812" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H812" s="8" t="n"/>
@@ -48290,12 +48290,12 @@
       <c r="L812" s="9" t="n"/>
       <c r="M812" s="10" t="inlineStr">
         <is>
-          <t>通信制。伊勢本校の番号（公式サイト）。桔梗が丘校は0595-41-1267</t>
+          <t>公式サイトで確認。中高共通</t>
         </is>
       </c>
       <c r="N812" s="11" t="inlineStr">
         <is>
-          <t>https://www.ckip.jp/eishin/infomations/contact ; https://www.mapion.co.jp/phonebook/M11004/24203/ILSP0060149148_ipclm/</t>
+          <t>https://www.takakura-hj.info/access</t>
         </is>
       </c>
       <c r="O812" s="12" t="inlineStr">
@@ -48310,22 +48310,22 @@
       </c>
       <c r="B813" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C813" s="5" t="inlineStr">
         <is>
-          <t>四日市市</t>
+          <t>名古屋市昭和区</t>
         </is>
       </c>
       <c r="D813" s="5" t="inlineStr">
         <is>
-          <t>大橋学園高等学校</t>
+          <t>名古屋工業高等学校</t>
         </is>
       </c>
       <c r="E813" s="6" t="inlineStr">
         <is>
-          <t>059-348-4800</t>
+          <t>052-871-2681</t>
         </is>
       </c>
       <c r="F813" s="7" t="inlineStr">
@@ -48335,7 +48335,7 @@
       </c>
       <c r="G813" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>専門学科</t>
         </is>
       </c>
       <c r="H813" s="8" t="n"/>
@@ -48349,12 +48349,12 @@
       <c r="L813" s="9" t="n"/>
       <c r="M813" s="10" t="inlineStr">
         <is>
-          <t>通信制。公式サイトで確認。旧所在地の番号059-354-1357は使わない</t>
+          <t>公式サイトと愛知県私学協会の資料で一致（私立）</t>
         </is>
       </c>
       <c r="N813" s="11" t="inlineStr">
         <is>
-          <t>https://www.ohashigh.ed.jp/school_info/access/</t>
+          <t>https://nagoya-th.ed.jp/ ; https://www.aichi-shigaku.gr.jp/guidebook2025/pageindices/index68.html</t>
         </is>
       </c>
       <c r="O813" s="12" t="inlineStr">
@@ -48369,22 +48369,22 @@
       </c>
       <c r="B814" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C814" s="5" t="inlineStr">
         <is>
-          <t>四日市市</t>
+          <t>名古屋市東区</t>
         </is>
       </c>
       <c r="D814" s="5" t="inlineStr">
         <is>
-          <t>海星高等学校（三重県）</t>
+          <t>名古屋高等学校</t>
         </is>
       </c>
       <c r="E814" s="6" t="inlineStr">
         <is>
-          <t>059-345-0036</t>
+          <t>052-721-5271</t>
         </is>
       </c>
       <c r="F814" s="7" t="inlineStr">
@@ -48408,12 +48408,12 @@
       <c r="L814" s="9" t="n"/>
       <c r="M814" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>公式サイトで確認。052-722-2835は同窓会の番号</t>
         </is>
       </c>
       <c r="N814" s="11" t="inlineStr">
         <is>
-          <t>https://www.kaisei.ed.jp/access/</t>
+          <t>https://www.meigaku.ac.jp/access/</t>
         </is>
       </c>
       <c r="O814" s="12" t="inlineStr">
@@ -48428,32 +48428,32 @@
       </c>
       <c r="B815" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C815" s="5" t="inlineStr">
         <is>
-          <t>伊賀市</t>
+          <t>名古屋市昭和区</t>
         </is>
       </c>
       <c r="D815" s="5" t="inlineStr">
         <is>
-          <t>神村学園高等部 伊賀分校</t>
+          <t>名古屋国際高等学校</t>
         </is>
       </c>
       <c r="E815" s="6" t="inlineStr">
         <is>
-          <t>0595-41-1234</t>
-        </is>
-      </c>
-      <c r="F815" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>052-858-2200</t>
+        </is>
+      </c>
+      <c r="F815" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="G815" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H815" s="8" t="n"/>
@@ -48467,12 +48467,12 @@
       <c r="L815" s="9" t="n"/>
       <c r="M815" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認（伊賀分校）。0595-53-1190を載せるサイトは旧番号の可能性</t>
+          <t>中高代表として掲載。高校の番号として052-853-5151を載せるサイトもあり食い違い</t>
         </is>
       </c>
       <c r="N815" s="11" t="inlineStr">
         <is>
-          <t>https://angel.kamimura.ac.jp/koiki/iga/access/</t>
+          <t>https://www.unesco-school.mext.go.jp/schools/list/nagoya-international-junior-senior-high-school/ ; https://www.aichi.sc/gakkou/kokusai/</t>
         </is>
       </c>
       <c r="O815" s="12" t="inlineStr">
@@ -48487,22 +48487,22 @@
       </c>
       <c r="B816" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C816" s="5" t="inlineStr">
         <is>
-          <t>伊勢市</t>
+          <t>名古屋市中区</t>
         </is>
       </c>
       <c r="D816" s="5" t="inlineStr">
         <is>
-          <t>皇學館高等学校</t>
+          <t>名古屋たちばな高等学校</t>
         </is>
       </c>
       <c r="E816" s="6" t="inlineStr">
         <is>
-          <t>0596-22-0205</t>
+          <t>052-322-1911</t>
         </is>
       </c>
       <c r="F816" s="7" t="inlineStr">
@@ -48512,7 +48512,7 @@
       </c>
       <c r="G816" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>専門学科</t>
         </is>
       </c>
       <c r="H816" s="8" t="n"/>
@@ -48531,7 +48531,7 @@
       </c>
       <c r="N816" s="11" t="inlineStr">
         <is>
-          <t>https://www.kogakkan-h.jp/access/</t>
+          <t>https://tachibana-hs.ed.jp/</t>
         </is>
       </c>
       <c r="O816" s="12" t="inlineStr">
@@ -48546,22 +48546,22 @@
       </c>
       <c r="B817" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C817" s="5" t="inlineStr">
         <is>
-          <t>伊賀市</t>
+          <t>名古屋市昭和区</t>
         </is>
       </c>
       <c r="D817" s="5" t="inlineStr">
         <is>
-          <t>桜丘高等学校（三重県）</t>
+          <t>南山高等学校 女子部</t>
         </is>
       </c>
       <c r="E817" s="6" t="inlineStr">
         <is>
-          <t>0595-38-1201</t>
+          <t>052-831-0704</t>
         </is>
       </c>
       <c r="F817" s="7" t="inlineStr">
@@ -48585,12 +48585,12 @@
       <c r="L817" s="9" t="n"/>
       <c r="M817" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>公式サイトで確認。中高共通。男子部とは別番号</t>
         </is>
       </c>
       <c r="N817" s="11" t="inlineStr">
         <is>
-          <t>https://sakura-gaoka.ed.jp/ ; https://school.js88.com/scl_h/22012400</t>
+          <t>https://www.nanzan-girls.ed.jp/access.html</t>
         </is>
       </c>
       <c r="O817" s="12" t="inlineStr">
@@ -48605,22 +48605,22 @@
       </c>
       <c r="B818" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C818" s="5" t="inlineStr">
         <is>
-          <t>鈴鹿市</t>
+          <t>名古屋市昭和区</t>
         </is>
       </c>
       <c r="D818" s="5" t="inlineStr">
         <is>
-          <t>鈴鹿高等学校</t>
+          <t>南山高等学校 男子部</t>
         </is>
       </c>
       <c r="E818" s="6" t="inlineStr">
         <is>
-          <t>059-378-0307</t>
+          <t>052-831-6455</t>
         </is>
       </c>
       <c r="F818" s="7" t="inlineStr">
@@ -48644,12 +48644,12 @@
       <c r="L818" s="9" t="n"/>
       <c r="M818" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認</t>
+          <t>公式サイトで確認。女子部とは別番号</t>
         </is>
       </c>
       <c r="N818" s="11" t="inlineStr">
         <is>
-          <t>https://suzukakyoei.ed.jp/suzukah/page06_00/</t>
+          <t>https://www.nanzan-boys.ed.jp/</t>
         </is>
       </c>
       <c r="O818" s="12" t="inlineStr">
@@ -48664,22 +48664,22 @@
       </c>
       <c r="B819" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C819" s="5" t="inlineStr">
         <is>
-          <t>津市</t>
+          <t>美浜町</t>
         </is>
       </c>
       <c r="D819" s="5" t="inlineStr">
         <is>
-          <t>セントヨゼフ女子学園高等学校</t>
+          <t>日本福祉大学付属高等学校</t>
         </is>
       </c>
       <c r="E819" s="6" t="inlineStr">
         <is>
-          <t>059-227-6465</t>
+          <t>0569-87-2311</t>
         </is>
       </c>
       <c r="F819" s="7" t="inlineStr">
@@ -48703,12 +48703,12 @@
       <c r="L819" s="9" t="n"/>
       <c r="M819" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>公式サイトで確認。大学の代表（0569-87-2211）とは別</t>
         </is>
       </c>
       <c r="N819" s="11" t="inlineStr">
         <is>
-          <t>https://sjjg.ac.jp/</t>
+          <t>https://www.n-fukushi.ac.jp/koukou/</t>
         </is>
       </c>
       <c r="O819" s="12" t="inlineStr">
@@ -48723,22 +48723,22 @@
       </c>
       <c r="B820" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C820" s="5" t="inlineStr">
         <is>
-          <t>津市</t>
+          <t>岡崎市</t>
         </is>
       </c>
       <c r="D820" s="5" t="inlineStr">
         <is>
-          <t>高田高等学校</t>
+          <t>人間環境大学附属岡崎高等学校</t>
         </is>
       </c>
       <c r="E820" s="6" t="inlineStr">
         <is>
-          <t>059-232-2004</t>
+          <t>0564-22-0274</t>
         </is>
       </c>
       <c r="F820" s="7" t="inlineStr">
@@ -48762,12 +48762,12 @@
       <c r="L820" s="9" t="n"/>
       <c r="M820" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通。学苑本部（059-231-0367）とは別</t>
+          <t>公式サイトで確認。2022年に旧校名から改称</t>
         </is>
       </c>
       <c r="N820" s="11" t="inlineStr">
         <is>
-          <t>https://www.mie-takada-hj.ed.jp/hj4/</t>
+          <t>https://www.jinkan-okazaki.ed.jp/about/</t>
         </is>
       </c>
       <c r="O820" s="12" t="inlineStr">
@@ -48782,22 +48782,22 @@
       </c>
       <c r="B821" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C821" s="5" t="inlineStr">
         <is>
-          <t>桑名市</t>
+          <t>岡崎市</t>
         </is>
       </c>
       <c r="D821" s="5" t="inlineStr">
         <is>
-          <t>津田学園高等学校</t>
+          <t>光ヶ丘女子高等学校</t>
         </is>
       </c>
       <c r="E821" s="6" t="inlineStr">
         <is>
-          <t>0594-31-6311</t>
+          <t>0564-51-5651</t>
         </is>
       </c>
       <c r="F821" s="7" t="inlineStr">
@@ -48807,7 +48807,7 @@
       </c>
       <c r="G821" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H821" s="8" t="n"/>
@@ -48821,12 +48821,12 @@
       <c r="L821" s="9" t="n"/>
       <c r="M821" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認。中高共通</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N821" s="11" t="inlineStr">
         <is>
-          <t>https://tsudagakuen.ac.jp/access.html</t>
+          <t>https://hikarigaoka-h.ed.jp/</t>
         </is>
       </c>
       <c r="O821" s="12" t="inlineStr">
@@ -48841,22 +48841,22 @@
       </c>
       <c r="B822" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C822" s="5" t="inlineStr">
         <is>
-          <t>亀山市</t>
+          <t>豊橋市</t>
         </is>
       </c>
       <c r="D822" s="5" t="inlineStr">
         <is>
-          <t>徳風高等学校</t>
+          <t>藤ノ花女子高等学校</t>
         </is>
       </c>
       <c r="E822" s="6" t="inlineStr">
         <is>
-          <t>0595-82-3561</t>
+          <t>0532-61-5468</t>
         </is>
       </c>
       <c r="F822" s="7" t="inlineStr">
@@ -48866,7 +48866,7 @@
       </c>
       <c r="G822" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H822" s="8" t="n"/>
@@ -48880,12 +48880,12 @@
       <c r="L822" s="9" t="n"/>
       <c r="M822" s="10" t="inlineStr">
         <is>
-          <t>通信制。公式サイトで確認（徳風技能専門学校と共通）</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N822" s="11" t="inlineStr">
         <is>
-          <t>https://mietokufu.ed.jp/</t>
+          <t>https://www.fujinohana-h.ed.jp/</t>
         </is>
       </c>
       <c r="O822" s="12" t="inlineStr">
@@ -48900,22 +48900,22 @@
       </c>
       <c r="B823" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C823" s="5" t="inlineStr">
         <is>
-          <t>松阪市</t>
+          <t>小牧市</t>
         </is>
       </c>
       <c r="D823" s="5" t="inlineStr">
         <is>
-          <t>三重高等学校</t>
+          <t>誉高等学校</t>
         </is>
       </c>
       <c r="E823" s="6" t="inlineStr">
         <is>
-          <t>0598-29-2959</t>
+          <t>0568-79-7700</t>
         </is>
       </c>
       <c r="F823" s="7" t="inlineStr">
@@ -48939,12 +48939,12 @@
       <c r="L823" s="9" t="n"/>
       <c r="M823" s="10" t="inlineStr">
         <is>
-          <t>公式サイトと三重県のサイトで一致</t>
+          <t>小牧市のサイトほかで一致、公式未確認</t>
         </is>
       </c>
       <c r="N823" s="11" t="inlineStr">
         <is>
-          <t>https://www.mie-mie-h.ed.jp/high/ ; https://www.pref.mie.lg.jp/SIGAKU/HP/shigaku/20490021350.htm</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/23219/ILSP0000041861_ipclm/ ; https://www.city.komaki.aichi.jp/admin/soshiki/fumei/highscool/4872.html</t>
         </is>
       </c>
       <c r="O823" s="12" t="inlineStr">
@@ -48959,22 +48959,22 @@
       </c>
       <c r="B824" s="5" t="inlineStr">
         <is>
-          <t>三重県</t>
+          <t>愛知県</t>
         </is>
       </c>
       <c r="C824" s="5" t="inlineStr">
         <is>
-          <t>四日市市</t>
+          <t>名古屋市中村区</t>
         </is>
       </c>
       <c r="D824" s="5" t="inlineStr">
         <is>
-          <t>四日市メリノール学院高等学校</t>
+          <t>名城大学附属高等学校</t>
         </is>
       </c>
       <c r="E824" s="6" t="inlineStr">
         <is>
-          <t>059-326-0067</t>
+          <t>052-481-7436</t>
         </is>
       </c>
       <c r="F824" s="7" t="inlineStr">
@@ -48984,7 +48984,7 @@
       </c>
       <c r="G824" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・総合学科</t>
         </is>
       </c>
       <c r="H824" s="8" t="n"/>
@@ -48998,12 +48998,12 @@
       <c r="L824" s="9" t="n"/>
       <c r="M824" s="10" t="inlineStr">
         <is>
-          <t>公式サイトで確認（中高共通の事務室）</t>
+          <t>公式サイトで確認</t>
         </is>
       </c>
       <c r="N824" s="11" t="inlineStr">
         <is>
-          <t>https://maryknoll.ed.jp/contact</t>
+          <t>https://www.meijo-h.ed.jp/profile/</t>
         </is>
       </c>
       <c r="O824" s="12" t="inlineStr">
@@ -49023,27 +49023,27 @@
       </c>
       <c r="C825" s="5" t="inlineStr">
         <is>
-          <t>志摩市</t>
+          <t>伊賀市</t>
         </is>
       </c>
       <c r="D825" s="5" t="inlineStr">
         <is>
-          <t>代々木高等学校</t>
+          <t>愛農学園農業高等学校</t>
         </is>
       </c>
       <c r="E825" s="6" t="inlineStr">
         <is>
-          <t>0599-56-0772</t>
-        </is>
-      </c>
-      <c r="F825" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>0595-52-0327</t>
+        </is>
+      </c>
+      <c r="F825" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="G825" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>専門学科</t>
         </is>
       </c>
       <c r="H825" s="8" t="n"/>
@@ -49057,23 +49057,1026 @@
       <c r="L825" s="9" t="n"/>
       <c r="M825" s="10" t="inlineStr">
         <is>
+          <t>公式サイトほかで一致</t>
+        </is>
+      </c>
+      <c r="N825" s="11" t="inlineStr">
+        <is>
+          <t>https://ainogakuen.ed.jp/ ; https://www.mapion.co.jp/phonebook/M11004/24216/ILSP0000041735_ipclm/</t>
+        </is>
+      </c>
+      <c r="O825" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" s="4" t="n">
+        <v>822</v>
+      </c>
+      <c r="B826" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C826" s="5" t="inlineStr">
+        <is>
+          <t>津市</t>
+        </is>
+      </c>
+      <c r="D826" s="5" t="inlineStr">
+        <is>
+          <t>青山高等学校（三重県）</t>
+        </is>
+      </c>
+      <c r="E826" s="6" t="inlineStr">
+        <is>
+          <t>059-262-4321</t>
+        </is>
+      </c>
+      <c r="F826" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G826" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H826" s="8" t="n"/>
+      <c r="I826" s="9" t="n"/>
+      <c r="J826" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K826" s="8" t="n"/>
+      <c r="L826" s="9" t="n"/>
+      <c r="M826" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N826" s="11" t="inlineStr">
+        <is>
+          <t>https://aoyama-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O826" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" s="4" t="n">
+        <v>823</v>
+      </c>
+      <c r="B827" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C827" s="5" t="inlineStr">
+        <is>
+          <t>四日市市</t>
+        </is>
+      </c>
+      <c r="D827" s="5" t="inlineStr">
+        <is>
+          <t>暁高等学校</t>
+        </is>
+      </c>
+      <c r="E827" s="6" t="inlineStr">
+        <is>
+          <t>059-337-2347</t>
+        </is>
+      </c>
+      <c r="F827" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G827" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H827" s="8" t="n"/>
+      <c r="I827" s="9" t="n"/>
+      <c r="J827" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K827" s="8" t="n"/>
+      <c r="L827" s="9" t="n"/>
+      <c r="M827" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトの3年制課程の番号（「代表」の表記なし）。中高一貫（6年制）は059-337-1213。059-337-2345を載せるサイトもあり</t>
+        </is>
+      </c>
+      <c r="N827" s="11" t="inlineStr">
+        <is>
+          <t>https://www.akatsuki.ed.jp/akatsuki-h/</t>
+        </is>
+      </c>
+      <c r="O827" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" s="4" t="n">
+        <v>824</v>
+      </c>
+      <c r="B828" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C828" s="5" t="inlineStr">
+        <is>
+          <t>伊勢市</t>
+        </is>
+      </c>
+      <c r="D828" s="5" t="inlineStr">
+        <is>
+          <t>伊勢学園高等学校</t>
+        </is>
+      </c>
+      <c r="E828" s="6" t="inlineStr">
+        <is>
+          <t>0596-22-4155</t>
+        </is>
+      </c>
+      <c r="F828" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G828" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H828" s="8" t="n"/>
+      <c r="I828" s="9" t="n"/>
+      <c r="J828" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K828" s="8" t="n"/>
+      <c r="L828" s="9" t="n"/>
+      <c r="M828" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。0596-22-4836は法人事務局の番号</t>
+        </is>
+      </c>
+      <c r="N828" s="11" t="inlineStr">
+        <is>
+          <t>https://www.isegakuen.ac.jp/contact.html</t>
+        </is>
+      </c>
+      <c r="O828" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" s="4" t="n">
+        <v>825</v>
+      </c>
+      <c r="B829" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C829" s="5" t="inlineStr">
+        <is>
+          <t>伊勢市</t>
+        </is>
+      </c>
+      <c r="D829" s="5" t="inlineStr">
+        <is>
+          <t>英心高等学校</t>
+        </is>
+      </c>
+      <c r="E829" s="6" t="inlineStr">
+        <is>
+          <t>0596-28-2077</t>
+        </is>
+      </c>
+      <c r="F829" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G829" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H829" s="8" t="n"/>
+      <c r="I829" s="9" t="n"/>
+      <c r="J829" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K829" s="8" t="n"/>
+      <c r="L829" s="9" t="n"/>
+      <c r="M829" s="10" t="inlineStr">
+        <is>
+          <t>通信制。伊勢本校の番号（公式サイト）。桔梗が丘校は0595-41-1267</t>
+        </is>
+      </c>
+      <c r="N829" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ckip.jp/eishin/infomations/contact ; https://www.mapion.co.jp/phonebook/M11004/24203/ILSP0060149148_ipclm/</t>
+        </is>
+      </c>
+      <c r="O829" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" s="4" t="n">
+        <v>826</v>
+      </c>
+      <c r="B830" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C830" s="5" t="inlineStr">
+        <is>
+          <t>四日市市</t>
+        </is>
+      </c>
+      <c r="D830" s="5" t="inlineStr">
+        <is>
+          <t>大橋学園高等学校</t>
+        </is>
+      </c>
+      <c r="E830" s="6" t="inlineStr">
+        <is>
+          <t>059-348-4800</t>
+        </is>
+      </c>
+      <c r="F830" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G830" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H830" s="8" t="n"/>
+      <c r="I830" s="9" t="n"/>
+      <c r="J830" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K830" s="8" t="n"/>
+      <c r="L830" s="9" t="n"/>
+      <c r="M830" s="10" t="inlineStr">
+        <is>
+          <t>通信制。公式サイトで確認。旧所在地の番号059-354-1357は使わない</t>
+        </is>
+      </c>
+      <c r="N830" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ohashigh.ed.jp/school_info/access/</t>
+        </is>
+      </c>
+      <c r="O830" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" s="4" t="n">
+        <v>827</v>
+      </c>
+      <c r="B831" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C831" s="5" t="inlineStr">
+        <is>
+          <t>四日市市</t>
+        </is>
+      </c>
+      <c r="D831" s="5" t="inlineStr">
+        <is>
+          <t>海星高等学校（三重県）</t>
+        </is>
+      </c>
+      <c r="E831" s="6" t="inlineStr">
+        <is>
+          <t>059-345-0036</t>
+        </is>
+      </c>
+      <c r="F831" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G831" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H831" s="8" t="n"/>
+      <c r="I831" s="9" t="n"/>
+      <c r="J831" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K831" s="8" t="n"/>
+      <c r="L831" s="9" t="n"/>
+      <c r="M831" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N831" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kaisei.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O831" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" s="4" t="n">
+        <v>828</v>
+      </c>
+      <c r="B832" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C832" s="5" t="inlineStr">
+        <is>
+          <t>伊賀市</t>
+        </is>
+      </c>
+      <c r="D832" s="5" t="inlineStr">
+        <is>
+          <t>神村学園高等部 伊賀分校</t>
+        </is>
+      </c>
+      <c r="E832" s="6" t="inlineStr">
+        <is>
+          <t>0595-41-1234</t>
+        </is>
+      </c>
+      <c r="F832" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G832" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H832" s="8" t="n"/>
+      <c r="I832" s="9" t="n"/>
+      <c r="J832" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K832" s="8" t="n"/>
+      <c r="L832" s="9" t="n"/>
+      <c r="M832" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認（伊賀分校）。0595-53-1190を載せるサイトは旧番号の可能性</t>
+        </is>
+      </c>
+      <c r="N832" s="11" t="inlineStr">
+        <is>
+          <t>https://angel.kamimura.ac.jp/koiki/iga/access/</t>
+        </is>
+      </c>
+      <c r="O832" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" s="4" t="n">
+        <v>829</v>
+      </c>
+      <c r="B833" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C833" s="5" t="inlineStr">
+        <is>
+          <t>伊勢市</t>
+        </is>
+      </c>
+      <c r="D833" s="5" t="inlineStr">
+        <is>
+          <t>皇學館高等学校</t>
+        </is>
+      </c>
+      <c r="E833" s="6" t="inlineStr">
+        <is>
+          <t>0596-22-0205</t>
+        </is>
+      </c>
+      <c r="F833" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G833" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H833" s="8" t="n"/>
+      <c r="I833" s="9" t="n"/>
+      <c r="J833" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K833" s="8" t="n"/>
+      <c r="L833" s="9" t="n"/>
+      <c r="M833" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N833" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kogakkan-h.jp/access/</t>
+        </is>
+      </c>
+      <c r="O833" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" s="4" t="n">
+        <v>830</v>
+      </c>
+      <c r="B834" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C834" s="5" t="inlineStr">
+        <is>
+          <t>伊賀市</t>
+        </is>
+      </c>
+      <c r="D834" s="5" t="inlineStr">
+        <is>
+          <t>桜丘高等学校（三重県）</t>
+        </is>
+      </c>
+      <c r="E834" s="6" t="inlineStr">
+        <is>
+          <t>0595-38-1201</t>
+        </is>
+      </c>
+      <c r="F834" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G834" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H834" s="8" t="n"/>
+      <c r="I834" s="9" t="n"/>
+      <c r="J834" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K834" s="8" t="n"/>
+      <c r="L834" s="9" t="n"/>
+      <c r="M834" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N834" s="11" t="inlineStr">
+        <is>
+          <t>https://sakura-gaoka.ed.jp/ ; https://school.js88.com/scl_h/22012400</t>
+        </is>
+      </c>
+      <c r="O834" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="4" t="n">
+        <v>831</v>
+      </c>
+      <c r="B835" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C835" s="5" t="inlineStr">
+        <is>
+          <t>鈴鹿市</t>
+        </is>
+      </c>
+      <c r="D835" s="5" t="inlineStr">
+        <is>
+          <t>鈴鹿高等学校</t>
+        </is>
+      </c>
+      <c r="E835" s="6" t="inlineStr">
+        <is>
+          <t>059-378-0307</t>
+        </is>
+      </c>
+      <c r="F835" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G835" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H835" s="8" t="n"/>
+      <c r="I835" s="9" t="n"/>
+      <c r="J835" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K835" s="8" t="n"/>
+      <c r="L835" s="9" t="n"/>
+      <c r="M835" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N835" s="11" t="inlineStr">
+        <is>
+          <t>https://suzukakyoei.ed.jp/suzukah/page06_00/</t>
+        </is>
+      </c>
+      <c r="O835" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="4" t="n">
+        <v>832</v>
+      </c>
+      <c r="B836" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C836" s="5" t="inlineStr">
+        <is>
+          <t>津市</t>
+        </is>
+      </c>
+      <c r="D836" s="5" t="inlineStr">
+        <is>
+          <t>セントヨゼフ女子学園高等学校</t>
+        </is>
+      </c>
+      <c r="E836" s="6" t="inlineStr">
+        <is>
+          <t>059-227-6465</t>
+        </is>
+      </c>
+      <c r="F836" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G836" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H836" s="8" t="n"/>
+      <c r="I836" s="9" t="n"/>
+      <c r="J836" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K836" s="8" t="n"/>
+      <c r="L836" s="9" t="n"/>
+      <c r="M836" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N836" s="11" t="inlineStr">
+        <is>
+          <t>https://sjjg.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O836" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="4" t="n">
+        <v>833</v>
+      </c>
+      <c r="B837" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C837" s="5" t="inlineStr">
+        <is>
+          <t>津市</t>
+        </is>
+      </c>
+      <c r="D837" s="5" t="inlineStr">
+        <is>
+          <t>高田高等学校</t>
+        </is>
+      </c>
+      <c r="E837" s="6" t="inlineStr">
+        <is>
+          <t>059-232-2004</t>
+        </is>
+      </c>
+      <c r="F837" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G837" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H837" s="8" t="n"/>
+      <c r="I837" s="9" t="n"/>
+      <c r="J837" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K837" s="8" t="n"/>
+      <c r="L837" s="9" t="n"/>
+      <c r="M837" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通。学苑本部（059-231-0367）とは別</t>
+        </is>
+      </c>
+      <c r="N837" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mie-takada-hj.ed.jp/hj4/</t>
+        </is>
+      </c>
+      <c r="O837" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="4" t="n">
+        <v>834</v>
+      </c>
+      <c r="B838" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C838" s="5" t="inlineStr">
+        <is>
+          <t>桑名市</t>
+        </is>
+      </c>
+      <c r="D838" s="5" t="inlineStr">
+        <is>
+          <t>津田学園高等学校</t>
+        </is>
+      </c>
+      <c r="E838" s="6" t="inlineStr">
+        <is>
+          <t>0594-31-6311</t>
+        </is>
+      </c>
+      <c r="F838" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G838" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H838" s="8" t="n"/>
+      <c r="I838" s="9" t="n"/>
+      <c r="J838" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K838" s="8" t="n"/>
+      <c r="L838" s="9" t="n"/>
+      <c r="M838" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N838" s="11" t="inlineStr">
+        <is>
+          <t>https://tsudagakuen.ac.jp/access.html</t>
+        </is>
+      </c>
+      <c r="O838" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="4" t="n">
+        <v>835</v>
+      </c>
+      <c r="B839" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C839" s="5" t="inlineStr">
+        <is>
+          <t>亀山市</t>
+        </is>
+      </c>
+      <c r="D839" s="5" t="inlineStr">
+        <is>
+          <t>徳風高等学校</t>
+        </is>
+      </c>
+      <c r="E839" s="6" t="inlineStr">
+        <is>
+          <t>0595-82-3561</t>
+        </is>
+      </c>
+      <c r="F839" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G839" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H839" s="8" t="n"/>
+      <c r="I839" s="9" t="n"/>
+      <c r="J839" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K839" s="8" t="n"/>
+      <c r="L839" s="9" t="n"/>
+      <c r="M839" s="10" t="inlineStr">
+        <is>
+          <t>通信制。公式サイトで確認（徳風技能専門学校と共通）</t>
+        </is>
+      </c>
+      <c r="N839" s="11" t="inlineStr">
+        <is>
+          <t>https://mietokufu.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O839" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="4" t="n">
+        <v>836</v>
+      </c>
+      <c r="B840" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C840" s="5" t="inlineStr">
+        <is>
+          <t>松阪市</t>
+        </is>
+      </c>
+      <c r="D840" s="5" t="inlineStr">
+        <is>
+          <t>三重高等学校</t>
+        </is>
+      </c>
+      <c r="E840" s="6" t="inlineStr">
+        <is>
+          <t>0598-29-2959</t>
+        </is>
+      </c>
+      <c r="F840" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G840" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H840" s="8" t="n"/>
+      <c r="I840" s="9" t="n"/>
+      <c r="J840" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K840" s="8" t="n"/>
+      <c r="L840" s="9" t="n"/>
+      <c r="M840" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトと三重県のサイトで一致</t>
+        </is>
+      </c>
+      <c r="N840" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mie-mie-h.ed.jp/high/ ; https://www.pref.mie.lg.jp/SIGAKU/HP/shigaku/20490021350.htm</t>
+        </is>
+      </c>
+      <c r="O840" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="4" t="n">
+        <v>837</v>
+      </c>
+      <c r="B841" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C841" s="5" t="inlineStr">
+        <is>
+          <t>四日市市</t>
+        </is>
+      </c>
+      <c r="D841" s="5" t="inlineStr">
+        <is>
+          <t>四日市メリノール学院高等学校</t>
+        </is>
+      </c>
+      <c r="E841" s="6" t="inlineStr">
+        <is>
+          <t>059-326-0067</t>
+        </is>
+      </c>
+      <c r="F841" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G841" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H841" s="8" t="n"/>
+      <c r="I841" s="9" t="n"/>
+      <c r="J841" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K841" s="8" t="n"/>
+      <c r="L841" s="9" t="n"/>
+      <c r="M841" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認（中高共通の事務室）</t>
+        </is>
+      </c>
+      <c r="N841" s="11" t="inlineStr">
+        <is>
+          <t>https://maryknoll.ed.jp/contact</t>
+        </is>
+      </c>
+      <c r="O841" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="4" t="n">
+        <v>838</v>
+      </c>
+      <c r="B842" s="5" t="inlineStr">
+        <is>
+          <t>三重県</t>
+        </is>
+      </c>
+      <c r="C842" s="5" t="inlineStr">
+        <is>
+          <t>志摩市</t>
+        </is>
+      </c>
+      <c r="D842" s="5" t="inlineStr">
+        <is>
+          <t>代々木高等学校</t>
+        </is>
+      </c>
+      <c r="E842" s="6" t="inlineStr">
+        <is>
+          <t>0599-56-0772</t>
+        </is>
+      </c>
+      <c r="F842" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G842" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H842" s="8" t="n"/>
+      <c r="I842" s="9" t="n"/>
+      <c r="J842" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K842" s="8" t="n"/>
+      <c r="L842" s="9" t="n"/>
+      <c r="M842" s="10" t="inlineStr">
+        <is>
           <t>広域通信制。志摩の本校。公式の問い合わせページの番号。0599-56-0770を載せる公式ページもあり、どちらが代表か不明</t>
         </is>
       </c>
-      <c r="N825" s="11" t="inlineStr">
+      <c r="N842" s="11" t="inlineStr">
         <is>
           <t>https://yoyogi.ed.jp/otoiawasetel/</t>
         </is>
       </c>
-      <c r="O825" s="12" t="inlineStr">
+      <c r="O842" s="12" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O825"/>
-  <conditionalFormatting sqref="A5:O825">
+  <autoFilter ref="A4:O842"/>
+  <conditionalFormatting sqref="A5:O842">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -49082,10 +50085,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J825" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J842" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H825 K5:K825" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H842 K5:K842" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -49911,6 +50914,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O823" r:id="rId819"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O824" r:id="rId820"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O825" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O826" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O827" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O828" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O829" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O830" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O831" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O832" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O833" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O834" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O835" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O836" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O837" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O838" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O839" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O840" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O841" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O842" r:id="rId838"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -49923,7 +50943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -50010,43 +51030,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A4,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A4,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$825,A4,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A4,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$842,A4,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A4,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A4,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A4,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A4,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A4,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A4,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A4,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A4,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50057,43 +51077,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A5,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A5,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$825,A5,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A5,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$842,A5,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A5,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A5,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A5,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A5,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A5,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A5,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A5,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A5,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50104,43 +51124,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A6,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A6,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$825,A6,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A6,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$842,A6,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A6,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A6,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A6,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A6,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A6,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A6,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A6,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A6,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50151,43 +51171,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A7,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A7,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$825,A7,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A7,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$842,A7,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A7,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A7,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A7,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A7,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A7,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A7,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A7,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A7,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50198,43 +51218,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A8,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A8,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$825,A8,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A8,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$842,A8,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A8,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A8,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A8,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A8,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A8,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A8,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A8,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A8,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50245,43 +51265,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A9,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A9,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$825,A9,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A9,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$842,A9,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A9,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A9,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A9,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A9,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A9,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A9,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A9,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A9,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50292,43 +51312,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A10,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A10,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$825,A10,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A10,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$842,A10,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A10,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A10,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A10,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A10,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A10,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A10,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A10,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A10,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50339,43 +51359,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A11,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A11,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$825,A11,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A11,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$842,A11,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A11,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A11,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A11,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A11,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A11,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A11,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A11,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A11,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50386,43 +51406,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A12,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A12,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$825,A12,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A12,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$842,A12,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A12,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A12,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A12,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A12,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A12,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A12,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A12,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A12,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50433,43 +51453,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A13,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A13,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$825,A13,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A13,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$842,A13,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A13,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A13,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A13,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A13,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A13,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A13,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A13,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A13,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50480,43 +51500,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A14,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A14,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$825,A14,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A14,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$842,A14,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A14,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A14,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A14,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A14,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A14,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A14,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A14,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A14,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50527,43 +51547,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A15,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A15,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$825,A15,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A15,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$842,A15,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A15,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A15,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A15,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A15,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A15,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A15,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A15,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A15,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50574,43 +51594,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A16,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A16,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$825,A16,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A16,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$842,A16,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A16,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A16,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A16,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A16,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A16,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A16,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A16,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A16,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50621,43 +51641,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A17,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A17,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$825,A17,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A17,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$842,A17,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A17,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A17,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A17,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A17,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A17,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A17,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A17,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A17,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50668,43 +51688,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A18,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A18,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$825,A18,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A18,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$842,A18,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A18,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A18,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A18,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A18,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A18,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A18,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A18,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A18,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50715,43 +51735,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A19,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A19,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$825,A19,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A19,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$842,A19,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A19,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A19,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A19,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A19,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A19,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A19,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A19,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A19,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50762,43 +51782,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A20,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A20,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$825,A20,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A20,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$842,A20,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A20,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A20,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A20,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A20,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A20,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A20,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A20,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A20,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50809,43 +51829,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A21,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A21,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$825,A21,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A21,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$842,A21,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A21,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A21,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A21,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A21,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A21,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A21,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A21,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A21,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50856,43 +51876,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A22,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A22,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$825,A22,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A22,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$842,A22,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A22,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A22,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A22,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A22,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A22,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A22,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A22,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A22,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -50903,231 +51923,278 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A23,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A23,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$825,A23,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A23,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$842,A23,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A23,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A23,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A23,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A23,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A23,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A23,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A23,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A23,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>静岡県</t>
+          <t>岐阜県</t>
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A24,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A24,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$825,A24,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A24,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$842,A24,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A24,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A24,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A24,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A24,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A24,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A24,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A24,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A24,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>愛知県</t>
+          <t>静岡県</t>
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A25,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A25,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$825,A25,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A25,'架電リスト'!$J$5:$J$825,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$842,A25,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A25,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A25,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A25,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A25,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A25,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A25,'架電リスト'!$J$5:$J$825,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A25,'架電リスト'!$J$5:$J$825,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A25,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
+          <t>愛知県</t>
+        </is>
+      </c>
+      <c r="B26" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A26)</f>
+        <v/>
+      </c>
+      <c r="C26" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A26,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D26" s="16">
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$842,A26,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A26,'架電リスト'!$J$5:$J$842,"")</f>
+        <v/>
+      </c>
+      <c r="E26" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F26" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G26" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H26" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I26" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <v/>
+      </c>
+      <c r="K26" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
           <t>三重県</t>
         </is>
       </c>
-      <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$825,A26)</f>
+      <c r="B27" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$842,A27)</f>
         <v/>
       </c>
-      <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,A26,'架電リスト'!$E$5:$E$825,"&lt;&gt;")</f>
+      <c r="C27" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A27,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$825,A26,'架電リスト'!$J$5:$J$825,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$825,A26,'架電リスト'!$J$5:$J$825,"")</f>
+      <c r="D27" s="16">
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$842,A27,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A27,'架電リスト'!$J$5:$J$842,"")</f>
         <v/>
       </c>
-      <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A26,'架電リスト'!$J$5:$J$825,"不在・折返し待ち")</f>
+      <c r="E27" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A26,'架電リスト'!$J$5:$J$825,"担当者不在")</f>
+      <c r="F27" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A26,'架電リスト'!$J$5:$J$825,"資料送付")</f>
+      <c r="G27" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"資料送付")</f>
         <v/>
       </c>
-      <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A26,'架電リスト'!$J$5:$J$825,"アポ獲得")</f>
+      <c r="H27" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A26,'架電リスト'!$J$5:$J$825,"検討中")</f>
+      <c r="I27" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"検討中")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A26,'架電リスト'!$J$5:$J$825,"NG")</f>
+      <c r="J27" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"NG")</f>
         <v/>
       </c>
-      <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$825,$A26,'架電リスト'!$J$5:$J$825,"番号不明")</f>
+      <c r="K27" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"番号不明")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B27" s="17">
-        <f>SUM(B4:B26)</f>
+      <c r="B28" s="17">
+        <f>SUM(B4:B27)</f>
         <v/>
       </c>
-      <c r="C27" s="17">
-        <f>SUM(C4:C26)</f>
+      <c r="C28" s="17">
+        <f>SUM(C4:C27)</f>
         <v/>
       </c>
-      <c r="D27" s="17">
-        <f>SUM(D4:D26)</f>
+      <c r="D28" s="17">
+        <f>SUM(D4:D27)</f>
         <v/>
       </c>
-      <c r="E27" s="17">
-        <f>SUM(E4:E26)</f>
+      <c r="E28" s="17">
+        <f>SUM(E4:E27)</f>
         <v/>
       </c>
-      <c r="F27" s="17">
-        <f>SUM(F4:F26)</f>
+      <c r="F28" s="17">
+        <f>SUM(F4:F27)</f>
         <v/>
       </c>
-      <c r="G27" s="17">
-        <f>SUM(G4:G26)</f>
+      <c r="G28" s="17">
+        <f>SUM(G4:G27)</f>
         <v/>
       </c>
-      <c r="H27" s="17">
-        <f>SUM(H4:H26)</f>
+      <c r="H28" s="17">
+        <f>SUM(H4:H27)</f>
         <v/>
       </c>
-      <c r="I27" s="17">
-        <f>SUM(I4:I26)</f>
+      <c r="I28" s="17">
+        <f>SUM(I4:I27)</f>
         <v/>
       </c>
-      <c r="J27" s="17">
-        <f>SUM(J4:J26)</f>
+      <c r="J28" s="17">
+        <f>SUM(J4:J27)</f>
         <v/>
       </c>
-      <c r="K27" s="17">
-        <f>SUM(K4:K26)</f>
+      <c r="K28" s="17">
+        <f>SUM(K4:K27)</f>
         <v/>
       </c>
     </row>
@@ -51217,7 +52284,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・23都道府県、821校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・24都道府県、838校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$842</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$853</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O842"/>
+  <dimension ref="A1:O853"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（24都道府県／838校）</t>
+          <t>私立高等学校 架電リスト（25都道府県／849校）</t>
         </is>
       </c>
     </row>
@@ -50074,9 +50074,658 @@
         </is>
       </c>
     </row>
+    <row r="843">
+      <c r="A843" s="4" t="n">
+        <v>839</v>
+      </c>
+      <c r="B843" s="5" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="C843" s="5" t="inlineStr">
+        <is>
+          <t>草津市</t>
+        </is>
+      </c>
+      <c r="D843" s="5" t="inlineStr">
+        <is>
+          <t>綾羽高等学校</t>
+        </is>
+      </c>
+      <c r="E843" s="6" t="inlineStr">
+        <is>
+          <t>077-563-3435</t>
+        </is>
+      </c>
+      <c r="F843" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G843" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H843" s="8" t="n"/>
+      <c r="I843" s="9" t="n"/>
+      <c r="J843" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K843" s="8" t="n"/>
+      <c r="L843" s="9" t="n"/>
+      <c r="M843" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。入試広報室は077-565-5821。定時制あり</t>
+        </is>
+      </c>
+      <c r="N843" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ayaha.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O843" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="4" t="n">
+        <v>840</v>
+      </c>
+      <c r="B844" s="5" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="C844" s="5" t="inlineStr">
+        <is>
+          <t>高島市</t>
+        </is>
+      </c>
+      <c r="D844" s="5" t="inlineStr">
+        <is>
+          <t>ECC学園高等学校</t>
+        </is>
+      </c>
+      <c r="E844" s="6" t="inlineStr">
+        <is>
+          <t>0740-24-8101</t>
+        </is>
+      </c>
+      <c r="F844" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G844" s="5" t="inlineStr">
+        <is>
+          <t>総合学科</t>
+        </is>
+      </c>
+      <c r="H844" s="8" t="n"/>
+      <c r="I844" s="9" t="n"/>
+      <c r="J844" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K844" s="8" t="n"/>
+      <c r="L844" s="9" t="n"/>
+      <c r="M844" s="10" t="inlineStr">
+        <is>
+          <t>通信制。高島市の本校の番号（公式サイト）。フリーダイヤル0120-027-144は全国向けの相談窓口</t>
+        </is>
+      </c>
+      <c r="N844" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ecc.ed.jp/about/overview.html ; https://www.mapion.co.jp/phonebook/M11004/25212/22530407740/</t>
+        </is>
+      </c>
+      <c r="O844" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="4" t="n">
+        <v>841</v>
+      </c>
+      <c r="B845" s="5" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="C845" s="5" t="inlineStr">
+        <is>
+          <t>近江八幡市</t>
+        </is>
+      </c>
+      <c r="D845" s="5" t="inlineStr">
+        <is>
+          <t>近江兄弟社高等学校</t>
+        </is>
+      </c>
+      <c r="E845" s="6" t="inlineStr">
+        <is>
+          <t>0748-32-3444</t>
+        </is>
+      </c>
+      <c r="F845" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G845" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H845" s="8" t="n"/>
+      <c r="I845" s="9" t="n"/>
+      <c r="J845" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K845" s="8" t="n"/>
+      <c r="L845" s="9" t="n"/>
+      <c r="M845" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N845" s="11" t="inlineStr">
+        <is>
+          <t>https://www.vories.ac.jp/omibh-shs</t>
+        </is>
+      </c>
+      <c r="O845" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="4" t="n">
+        <v>842</v>
+      </c>
+      <c r="B846" s="5" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="C846" s="5" t="inlineStr">
+        <is>
+          <t>彦根市</t>
+        </is>
+      </c>
+      <c r="D846" s="5" t="inlineStr">
+        <is>
+          <t>近江高等学校</t>
+        </is>
+      </c>
+      <c r="E846" s="6" t="inlineStr">
+        <is>
+          <t>0749-22-2323</t>
+        </is>
+      </c>
+      <c r="F846" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G846" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H846" s="8" t="n"/>
+      <c r="I846" s="9" t="n"/>
+      <c r="J846" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K846" s="8" t="n"/>
+      <c r="L846" s="9" t="n"/>
+      <c r="M846" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N846" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ohmi-h.ed.jp/information/access.php</t>
+        </is>
+      </c>
+      <c r="O846" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="4" t="n">
+        <v>843</v>
+      </c>
+      <c r="B847" s="5" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="C847" s="5" t="inlineStr">
+        <is>
+          <t>草津市</t>
+        </is>
+      </c>
+      <c r="D847" s="5" t="inlineStr">
+        <is>
+          <t>光泉カトリック高等学校</t>
+        </is>
+      </c>
+      <c r="E847" s="6" t="inlineStr">
+        <is>
+          <t>077-564-5600</t>
+        </is>
+      </c>
+      <c r="F847" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G847" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H847" s="8" t="n"/>
+      <c r="I847" s="9" t="n"/>
+      <c r="J847" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K847" s="8" t="n"/>
+      <c r="L847" s="9" t="n"/>
+      <c r="M847" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。入試部は077-564-7771</t>
+        </is>
+      </c>
+      <c r="N847" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kousen.ed.jp/high/contact/</t>
+        </is>
+      </c>
+      <c r="O847" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="4" t="n">
+        <v>844</v>
+      </c>
+      <c r="B848" s="5" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="C848" s="5" t="inlineStr">
+        <is>
+          <t>東近江市</t>
+        </is>
+      </c>
+      <c r="D848" s="5" t="inlineStr">
+        <is>
+          <t>滋賀学園高等学校</t>
+        </is>
+      </c>
+      <c r="E848" s="6" t="inlineStr">
+        <is>
+          <t>0748-23-0858</t>
+        </is>
+      </c>
+      <c r="F848" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G848" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H848" s="8" t="n"/>
+      <c r="I848" s="9" t="n"/>
+      <c r="J848" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K848" s="8" t="n"/>
+      <c r="L848" s="9" t="n"/>
+      <c r="M848" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N848" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shigagakuen.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O848" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="4" t="n">
+        <v>845</v>
+      </c>
+      <c r="B849" s="5" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="C849" s="5" t="inlineStr">
+        <is>
+          <t>東近江市</t>
+        </is>
+      </c>
+      <c r="D849" s="5" t="inlineStr">
+        <is>
+          <t>司学館高等学校</t>
+        </is>
+      </c>
+      <c r="E849" s="6" t="inlineStr">
+        <is>
+          <t>0748-22-1176</t>
+        </is>
+      </c>
+      <c r="F849" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G849" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H849" s="8" t="n"/>
+      <c r="I849" s="9" t="n"/>
+      <c r="J849" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K849" s="8" t="n"/>
+      <c r="L849" s="9" t="n"/>
+      <c r="M849" s="10" t="inlineStr">
+        <is>
+          <t>通信制。複数サイトで一致、公式未確認</t>
+        </is>
+      </c>
+      <c r="N849" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/25213/ILSP0000040974_ipclm/ ; https://miraitizu.com/tsushin-school/7364</t>
+        </is>
+      </c>
+      <c r="O849" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="4" t="n">
+        <v>846</v>
+      </c>
+      <c r="B850" s="5" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="C850" s="5" t="inlineStr">
+        <is>
+          <t>大津市</t>
+        </is>
+      </c>
+      <c r="D850" s="5" t="inlineStr">
+        <is>
+          <t>滋賀短期大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E850" s="6" t="inlineStr">
+        <is>
+          <t>0570-052-230</t>
+        </is>
+      </c>
+      <c r="F850" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G850" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H850" s="8" t="n"/>
+      <c r="I850" s="9" t="n"/>
+      <c r="J850" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K850" s="8" t="n"/>
+      <c r="L850" s="9" t="n"/>
+      <c r="M850" s="10" t="inlineStr">
+        <is>
+          <t>公式の問い合わせページの代表はナビダイヤル（通話料がかかる番号）。従来の番号077-522-3465も公式アクセスページなどに掲載あり</t>
+        </is>
+      </c>
+      <c r="N850" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sumire.ac.jp/highschool/form/</t>
+        </is>
+      </c>
+      <c r="O850" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="4" t="n">
+        <v>847</v>
+      </c>
+      <c r="B851" s="5" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="C851" s="5" t="inlineStr">
+        <is>
+          <t>大津市</t>
+        </is>
+      </c>
+      <c r="D851" s="5" t="inlineStr">
+        <is>
+          <t>比叡山高等学校</t>
+        </is>
+      </c>
+      <c r="E851" s="6" t="inlineStr">
+        <is>
+          <t>077-578-0091</t>
+        </is>
+      </c>
+      <c r="F851" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G851" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H851" s="8" t="n"/>
+      <c r="I851" s="9" t="n"/>
+      <c r="J851" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K851" s="8" t="n"/>
+      <c r="L851" s="9" t="n"/>
+      <c r="M851" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで高校の番号として確認。077-578-0132は中学校の番号</t>
+        </is>
+      </c>
+      <c r="N851" s="11" t="inlineStr">
+        <is>
+          <t>https://hieizan.ed.jp/hieizan-jh-hs/about/access/</t>
+        </is>
+      </c>
+      <c r="O851" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="4" t="n">
+        <v>848</v>
+      </c>
+      <c r="B852" s="5" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="C852" s="5" t="inlineStr">
+        <is>
+          <t>彦根市</t>
+        </is>
+      </c>
+      <c r="D852" s="5" t="inlineStr">
+        <is>
+          <t>彦根総合高等学校</t>
+        </is>
+      </c>
+      <c r="E852" s="6" t="inlineStr">
+        <is>
+          <t>0749-26-0016</t>
+        </is>
+      </c>
+      <c r="F852" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G852" s="5" t="inlineStr">
+        <is>
+          <t>総合学科</t>
+        </is>
+      </c>
+      <c r="H852" s="8" t="n"/>
+      <c r="I852" s="9" t="n"/>
+      <c r="J852" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K852" s="8" t="n"/>
+      <c r="L852" s="9" t="n"/>
+      <c r="M852" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。入試広報部は0749-24-7855</t>
+        </is>
+      </c>
+      <c r="N852" s="11" t="inlineStr">
+        <is>
+          <t>https://hikosou.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O852" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="4" t="n">
+        <v>849</v>
+      </c>
+      <c r="B853" s="5" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="C853" s="5" t="inlineStr">
+        <is>
+          <t>守山市</t>
+        </is>
+      </c>
+      <c r="D853" s="5" t="inlineStr">
+        <is>
+          <t>立命館守山高等学校</t>
+        </is>
+      </c>
+      <c r="E853" s="6" t="inlineStr">
+        <is>
+          <t>077-582-8000</t>
+        </is>
+      </c>
+      <c r="F853" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G853" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H853" s="8" t="n"/>
+      <c r="I853" s="9" t="n"/>
+      <c r="J853" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K853" s="8" t="n"/>
+      <c r="L853" s="9" t="n"/>
+      <c r="M853" s="10" t="inlineStr">
+        <is>
+          <t>中高共通の代表。守山市のサイトほかで一致</t>
+        </is>
+      </c>
+      <c r="N853" s="11" t="inlineStr">
+        <is>
+          <t>https://www.city.moriyama.lg.jp/shisetsu/jidoushisetsu/1006181/1006184.html ; https://school.js88.com/scl_h/22012790</t>
+        </is>
+      </c>
+      <c r="O853" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O842"/>
-  <conditionalFormatting sqref="A5:O842">
+  <autoFilter ref="A4:O853"/>
+  <conditionalFormatting sqref="A5:O853">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -50085,10 +50734,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J842" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J853" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H842 K5:K842" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H853 K5:K853" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -50931,6 +51580,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O840" r:id="rId836"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O841" r:id="rId837"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O842" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O843" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O844" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O845" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O846" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O847" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O848" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O849" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O850" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O851" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O852" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O853" r:id="rId849"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -50943,7 +51603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -51030,43 +51690,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A4,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A4,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$842,A4,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A4,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$853,A4,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A4,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A4,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51077,43 +51737,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A5,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A5,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$842,A5,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A5,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$853,A5,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A5,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A5,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51124,43 +51784,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A6,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A6,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$842,A6,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A6,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$853,A6,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A6,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A6,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51171,43 +51831,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A7,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A7,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$842,A7,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A7,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$853,A7,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A7,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A7,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51218,43 +51878,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A8,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A8,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$842,A8,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A8,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$853,A8,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A8,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A8,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51265,43 +51925,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A9,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A9,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$842,A9,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A9,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$853,A9,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A9,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A9,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51312,43 +51972,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A10,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A10,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$842,A10,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A10,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$853,A10,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A10,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A10,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51359,43 +52019,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A11,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A11,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$842,A11,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A11,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$853,A11,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A11,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A11,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51406,43 +52066,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A12,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A12,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$842,A12,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A12,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$853,A12,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A12,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A12,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51453,43 +52113,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A13,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A13,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$842,A13,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A13,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$853,A13,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A13,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A13,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51500,43 +52160,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A14,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A14,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$842,A14,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A14,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$853,A14,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A14,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A14,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51547,43 +52207,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A15,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A15,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$842,A15,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A15,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$853,A15,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A15,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A15,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51594,43 +52254,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A16,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A16,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$842,A16,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A16,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$853,A16,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A16,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A16,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51641,43 +52301,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A17,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A17,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$842,A17,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A17,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$853,A17,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A17,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A17,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51688,43 +52348,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A18,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A18,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$842,A18,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A18,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$853,A18,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A18,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A18,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51735,43 +52395,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A19,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A19,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$842,A19,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A19,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$853,A19,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A19,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A19,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51782,43 +52442,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A20,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A20,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$842,A20,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A20,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$853,A20,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A20,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A20,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51829,43 +52489,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A21,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A21,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$842,A21,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A21,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$853,A21,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A21,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A21,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51876,43 +52536,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A22,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A22,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$842,A22,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A22,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$853,A22,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A22,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A22,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51923,43 +52583,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A23,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A23,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$842,A23,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A23,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$853,A23,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A23,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A23,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51970,43 +52630,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A24,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A24,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$842,A24,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A24,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$853,A24,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A24,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A24,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52017,43 +52677,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A25,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A25,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$842,A25,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A25,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$853,A25,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A25,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A25,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52064,43 +52724,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A26,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A26,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$842,A26,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A26,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$853,A26,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A26,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A26,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52111,90 +52771,137 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$842,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,A27,'架電リスト'!$E$5:$E$842,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A27,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$842,A27,'架電リスト'!$J$5:$J$842,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$842,A27,'架電リスト'!$J$5:$J$842,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$853,A27,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A27,'架電リスト'!$J$5:$J$853,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$842,$A27,'架電リスト'!$J$5:$J$842,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>滋賀県</t>
+        </is>
+      </c>
+      <c r="B28" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$853,A28)</f>
+        <v/>
+      </c>
+      <c r="C28" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A28,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D28" s="16">
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$853,A28,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A28,'架電リスト'!$J$5:$J$853,"")</f>
+        <v/>
+      </c>
+      <c r="E28" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F28" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G28" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H28" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I28" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <v/>
+      </c>
+      <c r="K28" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B28" s="17">
-        <f>SUM(B4:B27)</f>
+      <c r="B29" s="17">
+        <f>SUM(B4:B28)</f>
         <v/>
       </c>
-      <c r="C28" s="17">
-        <f>SUM(C4:C27)</f>
+      <c r="C29" s="17">
+        <f>SUM(C4:C28)</f>
         <v/>
       </c>
-      <c r="D28" s="17">
-        <f>SUM(D4:D27)</f>
+      <c r="D29" s="17">
+        <f>SUM(D4:D28)</f>
         <v/>
       </c>
-      <c r="E28" s="17">
-        <f>SUM(E4:E27)</f>
+      <c r="E29" s="17">
+        <f>SUM(E4:E28)</f>
         <v/>
       </c>
-      <c r="F28" s="17">
-        <f>SUM(F4:F27)</f>
+      <c r="F29" s="17">
+        <f>SUM(F4:F28)</f>
         <v/>
       </c>
-      <c r="G28" s="17">
-        <f>SUM(G4:G27)</f>
+      <c r="G29" s="17">
+        <f>SUM(G4:G28)</f>
         <v/>
       </c>
-      <c r="H28" s="17">
-        <f>SUM(H4:H27)</f>
+      <c r="H29" s="17">
+        <f>SUM(H4:H28)</f>
         <v/>
       </c>
-      <c r="I28" s="17">
-        <f>SUM(I4:I27)</f>
+      <c r="I29" s="17">
+        <f>SUM(I4:I28)</f>
         <v/>
       </c>
-      <c r="J28" s="17">
-        <f>SUM(J4:J27)</f>
+      <c r="J29" s="17">
+        <f>SUM(J4:J28)</f>
         <v/>
       </c>
-      <c r="K28" s="17">
-        <f>SUM(K4:K27)</f>
+      <c r="K29" s="17">
+        <f>SUM(K4:K28)</f>
         <v/>
       </c>
     </row>
@@ -52284,7 +52991,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・24都道府県、838校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・25都道府県、849校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$853</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$894</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O853"/>
+  <dimension ref="A1:O894"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（25都道府県／849校）</t>
+          <t>私立高等学校 架電リスト（26都道府県／890校）</t>
         </is>
       </c>
     </row>
@@ -50723,9 +50723,2428 @@
         </is>
       </c>
     </row>
+    <row r="854">
+      <c r="A854" s="4" t="n">
+        <v>850</v>
+      </c>
+      <c r="B854" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C854" s="5" t="inlineStr">
+        <is>
+          <t>京都市山科区</t>
+        </is>
+      </c>
+      <c r="D854" s="5" t="inlineStr">
+        <is>
+          <t>一燈園高等学校</t>
+        </is>
+      </c>
+      <c r="E854" s="6" t="inlineStr">
+        <is>
+          <t>075-595-3711</t>
+        </is>
+      </c>
+      <c r="F854" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G854" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H854" s="8" t="n"/>
+      <c r="I854" s="9" t="n"/>
+      <c r="J854" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K854" s="8" t="n"/>
+      <c r="L854" s="9" t="n"/>
+      <c r="M854" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。複数サイトで一致。定時制あり</t>
+        </is>
+      </c>
+      <c r="N854" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/26110/ILSP0000041313_ipclm/ ; https://ksf-site.com/school/ittoen/</t>
+        </is>
+      </c>
+      <c r="O854" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="4" t="n">
+        <v>851</v>
+      </c>
+      <c r="B855" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C855" s="5" t="inlineStr">
+        <is>
+          <t>京都市東山区</t>
+        </is>
+      </c>
+      <c r="D855" s="5" t="inlineStr">
+        <is>
+          <t>大谷高等学校（京都府）</t>
+        </is>
+      </c>
+      <c r="E855" s="6" t="inlineStr">
+        <is>
+          <t>075-541-1312</t>
+        </is>
+      </c>
+      <c r="F855" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G855" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H855" s="8" t="n"/>
+      <c r="I855" s="9" t="n"/>
+      <c r="J855" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K855" s="8" t="n"/>
+      <c r="L855" s="9" t="n"/>
+      <c r="M855" s="10" t="inlineStr">
+        <is>
+          <t>中高共通の代表</t>
+        </is>
+      </c>
+      <c r="N855" s="11" t="inlineStr">
+        <is>
+          <t>https://www.otani.ac.jp/sinsyu_gakuen/index.html ; https://school.js88.com/scl_h/22013530</t>
+        </is>
+      </c>
+      <c r="O855" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="4" t="n">
+        <v>852</v>
+      </c>
+      <c r="B856" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C856" s="5" t="inlineStr">
+        <is>
+          <t>京都市東山区</t>
+        </is>
+      </c>
+      <c r="D856" s="5" t="inlineStr">
+        <is>
+          <t>華頂女子高等学校</t>
+        </is>
+      </c>
+      <c r="E856" s="6" t="inlineStr">
+        <is>
+          <t>075-541-0391</t>
+        </is>
+      </c>
+      <c r="F856" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G856" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H856" s="8" t="n"/>
+      <c r="I856" s="9" t="n"/>
+      <c r="J856" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K856" s="8" t="n"/>
+      <c r="L856" s="9" t="n"/>
+      <c r="M856" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N856" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kacho.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O856" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="4" t="n">
+        <v>853</v>
+      </c>
+      <c r="B857" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C857" s="5" t="inlineStr">
+        <is>
+          <t>京都市右京区</t>
+        </is>
+      </c>
+      <c r="D857" s="5" t="inlineStr">
+        <is>
+          <t>京都外大西高等学校</t>
+        </is>
+      </c>
+      <c r="E857" s="6" t="inlineStr">
+        <is>
+          <t>075-321-0712</t>
+        </is>
+      </c>
+      <c r="F857" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G857" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H857" s="8" t="n"/>
+      <c r="I857" s="9" t="n"/>
+      <c r="J857" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K857" s="8" t="n"/>
+      <c r="L857" s="9" t="n"/>
+      <c r="M857" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N857" s="11" t="inlineStr">
+        <is>
+          <t>https://kgn.kufs.ac.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O857" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="4" t="n">
+        <v>854</v>
+      </c>
+      <c r="B858" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C858" s="5" t="inlineStr">
+        <is>
+          <t>福知山市</t>
+        </is>
+      </c>
+      <c r="D858" s="5" t="inlineStr">
+        <is>
+          <t>京都共栄学園高等学校</t>
+        </is>
+      </c>
+      <c r="E858" s="6" t="inlineStr">
+        <is>
+          <t>0773-22-6241</t>
+        </is>
+      </c>
+      <c r="F858" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G858" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H858" s="8" t="n"/>
+      <c r="I858" s="9" t="n"/>
+      <c r="J858" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K858" s="8" t="n"/>
+      <c r="L858" s="9" t="n"/>
+      <c r="M858" s="10" t="inlineStr">
+        <is>
+          <t>全日制の番号。通信制は0773-22-6210</t>
+        </is>
+      </c>
+      <c r="N858" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/26201/ILSP0000041239_ipclm/</t>
+        </is>
+      </c>
+      <c r="O858" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="4" t="n">
+        <v>855</v>
+      </c>
+      <c r="B859" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C859" s="5" t="inlineStr">
+        <is>
+          <t>宮津市</t>
+        </is>
+      </c>
+      <c r="D859" s="5" t="inlineStr">
+        <is>
+          <t>京都暁星高等学校</t>
+        </is>
+      </c>
+      <c r="E859" s="6" t="inlineStr">
+        <is>
+          <t>0772-22-2560</t>
+        </is>
+      </c>
+      <c r="F859" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G859" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H859" s="8" t="n"/>
+      <c r="I859" s="9" t="n"/>
+      <c r="J859" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K859" s="8" t="n"/>
+      <c r="L859" s="9" t="n"/>
+      <c r="M859" s="10" t="inlineStr">
+        <is>
+          <t>複数サイトで一致</t>
+        </is>
+      </c>
+      <c r="N859" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/26205/ILSP0000041228_ipclm/ ; https://ksf-site.com/school/kyotogyosei/</t>
+        </is>
+      </c>
+      <c r="O859" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="4" t="n">
+        <v>856</v>
+      </c>
+      <c r="B860" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C860" s="5" t="inlineStr">
+        <is>
+          <t>宇治市</t>
+        </is>
+      </c>
+      <c r="D860" s="5" t="inlineStr">
+        <is>
+          <t>京都芸術高等学校</t>
+        </is>
+      </c>
+      <c r="E860" s="6" t="inlineStr">
+        <is>
+          <t>0774-32-7012</t>
+        </is>
+      </c>
+      <c r="F860" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G860" s="5" t="inlineStr">
+        <is>
+          <t>専門学科</t>
+        </is>
+      </c>
+      <c r="H860" s="8" t="n"/>
+      <c r="I860" s="9" t="n"/>
+      <c r="J860" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K860" s="8" t="n"/>
+      <c r="L860" s="9" t="n"/>
+      <c r="M860" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。京都芸術大学附属とは別の学校</t>
+        </is>
+      </c>
+      <c r="N860" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kyoto-geikou.ed.jp/school/access.html</t>
+        </is>
+      </c>
+      <c r="O860" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="4" t="n">
+        <v>857</v>
+      </c>
+      <c r="B861" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C861" s="5" t="inlineStr">
+        <is>
+          <t>京都市左京区</t>
+        </is>
+      </c>
+      <c r="D861" s="5" t="inlineStr">
+        <is>
+          <t>京都芸術大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E861" s="6" t="inlineStr">
+        <is>
+          <t>075-791-9454</t>
+        </is>
+      </c>
+      <c r="F861" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G861" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H861" s="8" t="n"/>
+      <c r="I861" s="9" t="n"/>
+      <c r="J861" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K861" s="8" t="n"/>
+      <c r="L861" s="9" t="n"/>
+      <c r="M861" s="10" t="inlineStr">
+        <is>
+          <t>通信制。事務室の番号。公式サイトの問い合わせ窓口はフリーダイヤル0120-87-37-39（平日9:00〜17:30）</t>
+        </is>
+      </c>
+      <c r="N861" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kyoto-art.ac.jp/news/press/899</t>
+        </is>
+      </c>
+      <c r="O861" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="4" t="n">
+        <v>858</v>
+      </c>
+      <c r="B862" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C862" s="5" t="inlineStr">
+        <is>
+          <t>京都市右京区</t>
+        </is>
+      </c>
+      <c r="D862" s="5" t="inlineStr">
+        <is>
+          <t>京都光華高等学校</t>
+        </is>
+      </c>
+      <c r="E862" s="6" t="inlineStr">
+        <is>
+          <t>075-325-5255</t>
+        </is>
+      </c>
+      <c r="F862" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G862" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H862" s="8" t="n"/>
+      <c r="I862" s="9" t="n"/>
+      <c r="J862" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K862" s="8" t="n"/>
+      <c r="L862" s="9" t="n"/>
+      <c r="M862" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。代表とする情報と入学広報部の直通とする情報が混在。事務室は075-325-5223</t>
+        </is>
+      </c>
+      <c r="N862" s="11" t="inlineStr">
+        <is>
+          <t>https://www.schoolnetwork.jp/kansai/shs/school_list/school/koka/ ; https://ksf-site.com/school/kyotokoka/</t>
+        </is>
+      </c>
+      <c r="O862" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="4" t="n">
+        <v>859</v>
+      </c>
+      <c r="B863" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C863" s="5" t="inlineStr">
+        <is>
+          <t>精華町</t>
+        </is>
+      </c>
+      <c r="D863" s="5" t="inlineStr">
+        <is>
+          <t>京都廣学館高等学校</t>
+        </is>
+      </c>
+      <c r="E863" s="6" t="inlineStr">
+        <is>
+          <t>0774-93-0518</t>
+        </is>
+      </c>
+      <c r="F863" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G863" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H863" s="8" t="n"/>
+      <c r="I863" s="9" t="n"/>
+      <c r="J863" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K863" s="8" t="n"/>
+      <c r="L863" s="9" t="n"/>
+      <c r="M863" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N863" s="11" t="inlineStr">
+        <is>
+          <t>https://kyoto-kogakkan.mkg.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O863" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="4" t="n">
+        <v>860</v>
+      </c>
+      <c r="B864" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C864" s="5" t="inlineStr">
+        <is>
+          <t>京都市東山区</t>
+        </is>
+      </c>
+      <c r="D864" s="5" t="inlineStr">
+        <is>
+          <t>京都国際高等学校</t>
+        </is>
+      </c>
+      <c r="E864" s="6" t="inlineStr">
+        <is>
+          <t>075-525-3535</t>
+        </is>
+      </c>
+      <c r="F864" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G864" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H864" s="8" t="n"/>
+      <c r="I864" s="9" t="n"/>
+      <c r="J864" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K864" s="8" t="n"/>
+      <c r="L864" s="9" t="n"/>
+      <c r="M864" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N864" s="11" t="inlineStr">
+        <is>
+          <t>https://kyoto-kokusai.ed.jp/jp/entranceguide</t>
+        </is>
+      </c>
+      <c r="O864" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="4" t="n">
+        <v>861</v>
+      </c>
+      <c r="B865" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C865" s="5" t="inlineStr">
+        <is>
+          <t>京都市下京区</t>
+        </is>
+      </c>
+      <c r="D865" s="5" t="inlineStr">
+        <is>
+          <t>京都産業大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E865" s="6" t="inlineStr">
+        <is>
+          <t>075-279-0001</t>
+        </is>
+      </c>
+      <c r="F865" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G865" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H865" s="8" t="n"/>
+      <c r="I865" s="9" t="n"/>
+      <c r="J865" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K865" s="8" t="n"/>
+      <c r="L865" s="9" t="n"/>
+      <c r="M865" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトと京都府の資料で一致。中高共通</t>
+        </is>
+      </c>
+      <c r="N865" s="11" t="inlineStr">
+        <is>
+          <t>https://www.jsh.kyoto-su.ac.jp/about/index.html ; https://www.pref.kyoto.jp/bunkyo/documents/05_kyotosangyo.pdf</t>
+        </is>
+      </c>
+      <c r="O865" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="4" t="n">
+        <v>862</v>
+      </c>
+      <c r="B866" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C866" s="5" t="inlineStr">
+        <is>
+          <t>宇治市</t>
+        </is>
+      </c>
+      <c r="D866" s="5" t="inlineStr">
+        <is>
+          <t>京都翔英高等学校</t>
+        </is>
+      </c>
+      <c r="E866" s="6" t="inlineStr">
+        <is>
+          <t>0774-23-2238</t>
+        </is>
+      </c>
+      <c r="F866" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G866" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H866" s="8" t="n"/>
+      <c r="I866" s="9" t="n"/>
+      <c r="J866" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K866" s="8" t="n"/>
+      <c r="L866" s="9" t="n"/>
+      <c r="M866" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N866" s="11" t="inlineStr">
+        <is>
+          <t>http://www.kyoto-shoei.ac.jp/%E3%82%A2%E3%82%AF%E3%82%BB%E3%82%B9.html</t>
+        </is>
+      </c>
+      <c r="O866" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="4" t="n">
+        <v>863</v>
+      </c>
+      <c r="B867" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C867" s="5" t="inlineStr">
+        <is>
+          <t>京都市東山区</t>
+        </is>
+      </c>
+      <c r="D867" s="5" t="inlineStr">
+        <is>
+          <t>京都女子高等学校</t>
+        </is>
+      </c>
+      <c r="E867" s="6" t="inlineStr">
+        <is>
+          <t>075-531-7358</t>
+        </is>
+      </c>
+      <c r="F867" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G867" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H867" s="8" t="n"/>
+      <c r="I867" s="9" t="n"/>
+      <c r="J867" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K867" s="8" t="n"/>
+      <c r="L867" s="9" t="n"/>
+      <c r="M867" s="10" t="inlineStr">
+        <is>
+          <t>中高共通の事務室の番号（公式サイト）。入試広報部は075-531-7334</t>
+        </is>
+      </c>
+      <c r="N867" s="11" t="inlineStr">
+        <is>
+          <t>https://kgs.ed.jp/about_us/outline</t>
+        </is>
+      </c>
+      <c r="O867" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="4" t="n">
+        <v>864</v>
+      </c>
+      <c r="B868" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C868" s="5" t="inlineStr">
+        <is>
+          <t>京都市左京区</t>
+        </is>
+      </c>
+      <c r="D868" s="5" t="inlineStr">
+        <is>
+          <t>京都精華学園高等学校</t>
+        </is>
+      </c>
+      <c r="E868" s="6" t="inlineStr">
+        <is>
+          <t>075-771-4181</t>
+        </is>
+      </c>
+      <c r="F868" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G868" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H868" s="8" t="n"/>
+      <c r="I868" s="9" t="n"/>
+      <c r="J868" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K868" s="8" t="n"/>
+      <c r="L868" s="9" t="n"/>
+      <c r="M868" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。複数サイトで一致</t>
+        </is>
+      </c>
+      <c r="N868" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/26103/ILSP0000041269_ipclm/ ; https://school.js88.com/scl_h/22013670</t>
+        </is>
+      </c>
+      <c r="O868" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="4" t="n">
+        <v>865</v>
+      </c>
+      <c r="B869" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C869" s="5" t="inlineStr">
+        <is>
+          <t>南丹市</t>
+        </is>
+      </c>
+      <c r="D869" s="5" t="inlineStr">
+        <is>
+          <t>京都聖カタリナ高等学校</t>
+        </is>
+      </c>
+      <c r="E869" s="6" t="inlineStr">
+        <is>
+          <t>0771-62-0163</t>
+        </is>
+      </c>
+      <c r="F869" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G869" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H869" s="8" t="n"/>
+      <c r="I869" s="9" t="n"/>
+      <c r="J869" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K869" s="8" t="n"/>
+      <c r="L869" s="9" t="n"/>
+      <c r="M869" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N869" s="11" t="inlineStr">
+        <is>
+          <t>https://www.catalina-kyoto.ed.jp/about/access/</t>
+        </is>
+      </c>
+      <c r="O869" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="4" t="n">
+        <v>866</v>
+      </c>
+      <c r="B870" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C870" s="5" t="inlineStr">
+        <is>
+          <t>京都市西京区</t>
+        </is>
+      </c>
+      <c r="D870" s="5" t="inlineStr">
+        <is>
+          <t>京都成章高等学校</t>
+        </is>
+      </c>
+      <c r="E870" s="6" t="inlineStr">
+        <is>
+          <t>075-332-4830</t>
+        </is>
+      </c>
+      <c r="F870" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G870" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H870" s="8" t="n"/>
+      <c r="I870" s="9" t="n"/>
+      <c r="J870" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K870" s="8" t="n"/>
+      <c r="L870" s="9" t="n"/>
+      <c r="M870" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N870" s="11" t="inlineStr">
+        <is>
+          <t>https://kyoto-seisho.ed.jp/graduate/</t>
+        </is>
+      </c>
+      <c r="O870" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="4" t="n">
+        <v>867</v>
+      </c>
+      <c r="B871" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C871" s="5" t="inlineStr">
+        <is>
+          <t>京都市伏見区</t>
+        </is>
+      </c>
+      <c r="D871" s="5" t="inlineStr">
+        <is>
+          <t>京都聖母学院高等学校</t>
+        </is>
+      </c>
+      <c r="E871" s="6" t="inlineStr">
+        <is>
+          <t>075-645-8103</t>
+        </is>
+      </c>
+      <c r="F871" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G871" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H871" s="8" t="n"/>
+      <c r="I871" s="9" t="n"/>
+      <c r="J871" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K871" s="8" t="n"/>
+      <c r="L871" s="9" t="n"/>
+      <c r="M871" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。中高共通</t>
+        </is>
+      </c>
+      <c r="N871" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seibo.ed.jp/kyoto-hs/kyotoseibo-only</t>
+        </is>
+      </c>
+      <c r="O871" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="4" t="n">
+        <v>868</v>
+      </c>
+      <c r="B872" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C872" s="5" t="inlineStr">
+        <is>
+          <t>京都市右京区</t>
+        </is>
+      </c>
+      <c r="D872" s="5" t="inlineStr">
+        <is>
+          <t>京都先端科学大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E872" s="6" t="inlineStr">
+        <is>
+          <t>075-461-5105</t>
+        </is>
+      </c>
+      <c r="F872" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G872" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H872" s="8" t="n"/>
+      <c r="I872" s="9" t="n"/>
+      <c r="J872" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K872" s="8" t="n"/>
+      <c r="L872" s="9" t="n"/>
+      <c r="M872" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N872" s="11" t="inlineStr">
+        <is>
+          <t>https://www.js.kuas.ac.jp/contact</t>
+        </is>
+      </c>
+      <c r="O872" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="4" t="n">
+        <v>869</v>
+      </c>
+      <c r="B873" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C873" s="5" t="inlineStr">
+        <is>
+          <t>京都市伏見区</t>
+        </is>
+      </c>
+      <c r="D873" s="5" t="inlineStr">
+        <is>
+          <t>京都橘高等学校</t>
+        </is>
+      </c>
+      <c r="E873" s="6" t="inlineStr">
+        <is>
+          <t>075-623-0066</t>
+        </is>
+      </c>
+      <c r="F873" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G873" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H873" s="8" t="n"/>
+      <c r="I873" s="9" t="n"/>
+      <c r="J873" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K873" s="8" t="n"/>
+      <c r="L873" s="9" t="n"/>
+      <c r="M873" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N873" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tachibana-hs.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O873" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="4" t="n">
+        <v>870</v>
+      </c>
+      <c r="B874" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C874" s="5" t="inlineStr">
+        <is>
+          <t>向日市</t>
+        </is>
+      </c>
+      <c r="D874" s="5" t="inlineStr">
+        <is>
+          <t>京都西山高等学校</t>
+        </is>
+      </c>
+      <c r="E874" s="6" t="inlineStr">
+        <is>
+          <t>075-934-2480</t>
+        </is>
+      </c>
+      <c r="F874" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G874" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H874" s="8" t="n"/>
+      <c r="I874" s="9" t="n"/>
+      <c r="J874" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K874" s="8" t="n"/>
+      <c r="L874" s="9" t="n"/>
+      <c r="M874" s="10" t="inlineStr">
+        <is>
+          <t>全日制の番号。複数サイトで一致、公式未確認。通信制課程は別番号</t>
+        </is>
+      </c>
+      <c r="N874" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/26208/ILSP0000041262_ipclm/ ; https://school.js88.com/scl_h/22013730</t>
+        </is>
+      </c>
+      <c r="O874" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="4" t="n">
+        <v>871</v>
+      </c>
+      <c r="B875" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C875" s="5" t="inlineStr">
+        <is>
+          <t>京都市左京区</t>
+        </is>
+      </c>
+      <c r="D875" s="5" t="inlineStr">
+        <is>
+          <t>京都文教高等学校</t>
+        </is>
+      </c>
+      <c r="E875" s="6" t="inlineStr">
+        <is>
+          <t>075-771-6155</t>
+        </is>
+      </c>
+      <c r="F875" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G875" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H875" s="8" t="n"/>
+      <c r="I875" s="9" t="n"/>
+      <c r="J875" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K875" s="8" t="n"/>
+      <c r="L875" s="9" t="n"/>
+      <c r="M875" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。入試部直通は075-752-6818</t>
+        </is>
+      </c>
+      <c r="N875" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kbu.ac.jp/kbghs/inquiry/index.html</t>
+        </is>
+      </c>
+      <c r="O875" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="4" t="n">
+        <v>872</v>
+      </c>
+      <c r="B876" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C876" s="5" t="inlineStr">
+        <is>
+          <t>京都市上京区</t>
+        </is>
+      </c>
+      <c r="D876" s="5" t="inlineStr">
+        <is>
+          <t>京都美山高等学校</t>
+        </is>
+      </c>
+      <c r="E876" s="6" t="inlineStr">
+        <is>
+          <t>075-441-3401</t>
+        </is>
+      </c>
+      <c r="F876" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G876" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H876" s="8" t="n"/>
+      <c r="I876" s="9" t="n"/>
+      <c r="J876" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K876" s="8" t="n"/>
+      <c r="L876" s="9" t="n"/>
+      <c r="M876" s="10" t="inlineStr">
+        <is>
+          <t>通信制。公式サイトに「代表」と記載。フリーダイヤル0120-561-380もあり</t>
+        </is>
+      </c>
+      <c r="N876" s="11" t="inlineStr">
+        <is>
+          <t>https://www.miyama.ed.jp/cgi/kexplan_cl_1.php</t>
+        </is>
+      </c>
+      <c r="O876" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="4" t="n">
+        <v>873</v>
+      </c>
+      <c r="B877" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C877" s="5" t="inlineStr">
+        <is>
+          <t>京都市西京区</t>
+        </is>
+      </c>
+      <c r="D877" s="5" t="inlineStr">
+        <is>
+          <t>京都明徳高等学校</t>
+        </is>
+      </c>
+      <c r="E877" s="6" t="inlineStr">
+        <is>
+          <t>075-331-3361</t>
+        </is>
+      </c>
+      <c r="F877" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G877" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H877" s="8" t="n"/>
+      <c r="I877" s="9" t="n"/>
+      <c r="J877" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K877" s="8" t="n"/>
+      <c r="L877" s="9" t="n"/>
+      <c r="M877" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N877" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meitoku.ac.jp/inquiry</t>
+        </is>
+      </c>
+      <c r="O877" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="4" t="n">
+        <v>874</v>
+      </c>
+      <c r="B878" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C878" s="5" t="inlineStr">
+        <is>
+          <t>京都市中京区</t>
+        </is>
+      </c>
+      <c r="D878" s="5" t="inlineStr">
+        <is>
+          <t>京都両洋高等学校</t>
+        </is>
+      </c>
+      <c r="E878" s="6" t="inlineStr">
+        <is>
+          <t>075-841-2025</t>
+        </is>
+      </c>
+      <c r="F878" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G878" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H878" s="8" t="n"/>
+      <c r="I878" s="9" t="n"/>
+      <c r="J878" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K878" s="8" t="n"/>
+      <c r="L878" s="9" t="n"/>
+      <c r="M878" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N878" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kyoto-ryoyo.ed.jp/inquiry/</t>
+        </is>
+      </c>
+      <c r="O878" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="4" t="n">
+        <v>875</v>
+      </c>
+      <c r="B879" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C879" s="5" t="inlineStr">
+        <is>
+          <t>京都市上京区</t>
+        </is>
+      </c>
+      <c r="D879" s="5" t="inlineStr">
+        <is>
+          <t>同志社女子高等学校</t>
+        </is>
+      </c>
+      <c r="E879" s="6" t="inlineStr">
+        <is>
+          <t>075-251-4305</t>
+        </is>
+      </c>
+      <c r="F879" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G879" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H879" s="8" t="n"/>
+      <c r="I879" s="9" t="n"/>
+      <c r="J879" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K879" s="8" t="n"/>
+      <c r="L879" s="9" t="n"/>
+      <c r="M879" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。複数サイトで一致、公式未確認</t>
+        </is>
+      </c>
+      <c r="N879" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/26102/ILSP0000041353_ipclm/ ; https://www.studyh.jp/kansai/school/C27P001/</t>
+        </is>
+      </c>
+      <c r="O879" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="4" t="n">
+        <v>876</v>
+      </c>
+      <c r="B880" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C880" s="5" t="inlineStr">
+        <is>
+          <t>京都市左京区</t>
+        </is>
+      </c>
+      <c r="D880" s="5" t="inlineStr">
+        <is>
+          <t>同志社高等学校</t>
+        </is>
+      </c>
+      <c r="E880" s="6" t="inlineStr">
+        <is>
+          <t>075-781-7121</t>
+        </is>
+      </c>
+      <c r="F880" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G880" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H880" s="8" t="n"/>
+      <c r="I880" s="9" t="n"/>
+      <c r="J880" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K880" s="8" t="n"/>
+      <c r="L880" s="9" t="n"/>
+      <c r="M880" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N880" s="11" t="inlineStr">
+        <is>
+          <t>https://js.doshisha.ac.jp/high/access/</t>
+        </is>
+      </c>
+      <c r="O880" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="4" t="n">
+        <v>877</v>
+      </c>
+      <c r="B881" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C881" s="5" t="inlineStr">
+        <is>
+          <t>京田辺市</t>
+        </is>
+      </c>
+      <c r="D881" s="5" t="inlineStr">
+        <is>
+          <t>同志社国際高等学校</t>
+        </is>
+      </c>
+      <c r="E881" s="6" t="inlineStr">
+        <is>
+          <t>0774-65-8911</t>
+        </is>
+      </c>
+      <c r="F881" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G881" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H881" s="8" t="n"/>
+      <c r="I881" s="9" t="n"/>
+      <c r="J881" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K881" s="8" t="n"/>
+      <c r="L881" s="9" t="n"/>
+      <c r="M881" s="10" t="inlineStr">
+        <is>
+          <t>代表として掲載。中高共通</t>
+        </is>
+      </c>
+      <c r="N881" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/26211/ILSP0000041744_ipclm/ ; https://school.js88.com/scl_h/22013860</t>
+        </is>
+      </c>
+      <c r="O881" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="4" t="n">
+        <v>878</v>
+      </c>
+      <c r="B882" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C882" s="5" t="inlineStr">
+        <is>
+          <t>舞鶴市</t>
+        </is>
+      </c>
+      <c r="D882" s="5" t="inlineStr">
+        <is>
+          <t>日星高等学校</t>
+        </is>
+      </c>
+      <c r="E882" s="6" t="inlineStr">
+        <is>
+          <t>0773-75-0452</t>
+        </is>
+      </c>
+      <c r="F882" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G882" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H882" s="8" t="n"/>
+      <c r="I882" s="9" t="n"/>
+      <c r="J882" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K882" s="8" t="n"/>
+      <c r="L882" s="9" t="n"/>
+      <c r="M882" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。専攻科は0773-75-7610</t>
+        </is>
+      </c>
+      <c r="N882" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nisseihs.ed.jp/ ; https://www.mapion.co.jp/phonebook/M11004/26202/ILSP0000040685_ipclm/</t>
+        </is>
+      </c>
+      <c r="O882" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="4" t="n">
+        <v>879</v>
+      </c>
+      <c r="B883" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C883" s="5" t="inlineStr">
+        <is>
+          <t>京都市右京区</t>
+        </is>
+      </c>
+      <c r="D883" s="5" t="inlineStr">
+        <is>
+          <t>花園高等学校</t>
+        </is>
+      </c>
+      <c r="E883" s="6" t="inlineStr">
+        <is>
+          <t>075-463-5221</t>
+        </is>
+      </c>
+      <c r="F883" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G883" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H883" s="8" t="n"/>
+      <c r="I883" s="9" t="n"/>
+      <c r="J883" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K883" s="8" t="n"/>
+      <c r="L883" s="9" t="n"/>
+      <c r="M883" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N883" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kyoto-hanazono-h.ed.jp/hanazono_hs/</t>
+        </is>
+      </c>
+      <c r="O883" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="4" t="n">
+        <v>880</v>
+      </c>
+      <c r="B884" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C884" s="5" t="inlineStr">
+        <is>
+          <t>京都市左京区</t>
+        </is>
+      </c>
+      <c r="D884" s="5" t="inlineStr">
+        <is>
+          <t>東山高等学校</t>
+        </is>
+      </c>
+      <c r="E884" s="6" t="inlineStr">
+        <is>
+          <t>075-771-9121</t>
+        </is>
+      </c>
+      <c r="F884" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G884" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H884" s="8" t="n"/>
+      <c r="I884" s="9" t="n"/>
+      <c r="J884" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K884" s="8" t="n"/>
+      <c r="L884" s="9" t="n"/>
+      <c r="M884" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N884" s="11" t="inlineStr">
+        <is>
+          <t>https://www.higashiyama.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O884" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="4" t="n">
+        <v>881</v>
+      </c>
+      <c r="B885" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C885" s="5" t="inlineStr">
+        <is>
+          <t>福知山市</t>
+        </is>
+      </c>
+      <c r="D885" s="5" t="inlineStr">
+        <is>
+          <t>福知山淑徳高等学校</t>
+        </is>
+      </c>
+      <c r="E885" s="6" t="inlineStr">
+        <is>
+          <t>0773-22-3763</t>
+        </is>
+      </c>
+      <c r="F885" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G885" s="5" t="inlineStr">
+        <is>
+          <t>総合学科</t>
+        </is>
+      </c>
+      <c r="H885" s="8" t="n"/>
+      <c r="I885" s="9" t="n"/>
+      <c r="J885" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K885" s="8" t="n"/>
+      <c r="L885" s="9" t="n"/>
+      <c r="M885" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。福知山成美とは別の学校</t>
+        </is>
+      </c>
+      <c r="N885" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kan-on-sen-ku.ed.jp/art2017/art-design/contact.html</t>
+        </is>
+      </c>
+      <c r="O885" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="4" t="n">
+        <v>882</v>
+      </c>
+      <c r="B886" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C886" s="5" t="inlineStr">
+        <is>
+          <t>福知山市</t>
+        </is>
+      </c>
+      <c r="D886" s="5" t="inlineStr">
+        <is>
+          <t>福知山成美高等学校</t>
+        </is>
+      </c>
+      <c r="E886" s="6" t="inlineStr">
+        <is>
+          <t>0773-22-6224</t>
+        </is>
+      </c>
+      <c r="F886" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G886" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H886" s="8" t="n"/>
+      <c r="I886" s="9" t="n"/>
+      <c r="J886" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K886" s="8" t="n"/>
+      <c r="L886" s="9" t="n"/>
+      <c r="M886" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。福知山淑徳とは別の学校</t>
+        </is>
+      </c>
+      <c r="N886" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seibi-hs.jp/guide/access.html</t>
+        </is>
+      </c>
+      <c r="O886" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="4" t="n">
+        <v>883</v>
+      </c>
+      <c r="B887" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C887" s="5" t="inlineStr">
+        <is>
+          <t>京都市上京区</t>
+        </is>
+      </c>
+      <c r="D887" s="5" t="inlineStr">
+        <is>
+          <t>平安女学院高等学校</t>
+        </is>
+      </c>
+      <c r="E887" s="6" t="inlineStr">
+        <is>
+          <t>075-414-8111</t>
+        </is>
+      </c>
+      <c r="F887" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G887" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H887" s="8" t="n"/>
+      <c r="I887" s="9" t="n"/>
+      <c r="J887" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K887" s="8" t="n"/>
+      <c r="L887" s="9" t="n"/>
+      <c r="M887" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表番号（入試関連以外）」と記載。入試は入学センター075-414-8101</t>
+        </is>
+      </c>
+      <c r="N887" s="11" t="inlineStr">
+        <is>
+          <t>http://jh.heian.ac.jp/otoiawase</t>
+        </is>
+      </c>
+      <c r="O887" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="4" t="n">
+        <v>884</v>
+      </c>
+      <c r="B888" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C888" s="5" t="inlineStr">
+        <is>
+          <t>京都市北区</t>
+        </is>
+      </c>
+      <c r="D888" s="5" t="inlineStr">
+        <is>
+          <t>洛星高等学校</t>
+        </is>
+      </c>
+      <c r="E888" s="6" t="inlineStr">
+        <is>
+          <t>075-466-0001</t>
+        </is>
+      </c>
+      <c r="F888" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G888" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H888" s="8" t="n"/>
+      <c r="I888" s="9" t="n"/>
+      <c r="J888" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K888" s="8" t="n"/>
+      <c r="L888" s="9" t="n"/>
+      <c r="M888" s="10" t="inlineStr">
+        <is>
+          <t>中高共通の代表。洛星ノートルダム女学院とは別の学校</t>
+        </is>
+      </c>
+      <c r="N888" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/26101/ILSP0000041505_ipclm/ ; https://www.schoolnetwork.jp/kansai/jhs/school_list/school/rakusei/</t>
+        </is>
+      </c>
+      <c r="O888" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="4" t="n">
+        <v>885</v>
+      </c>
+      <c r="B889" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C889" s="5" t="inlineStr">
+        <is>
+          <t>京都市左京区</t>
+        </is>
+      </c>
+      <c r="D889" s="5" t="inlineStr">
+        <is>
+          <t>洛星ノートルダム女学院高等学校</t>
+        </is>
+      </c>
+      <c r="E889" s="6" t="inlineStr">
+        <is>
+          <t>075-771-0570</t>
+        </is>
+      </c>
+      <c r="F889" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G889" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H889" s="8" t="n"/>
+      <c r="I889" s="9" t="n"/>
+      <c r="J889" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K889" s="8" t="n"/>
+      <c r="L889" s="9" t="n"/>
+      <c r="M889" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトに「代表」と記載。【校名変更】2026年4月にノートルダム女学院から改称。洛星高校とは別の学校</t>
+        </is>
+      </c>
+      <c r="N889" s="11" t="inlineStr">
+        <is>
+          <t>https://www.notredame-jogakuin.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O889" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="4" t="n">
+        <v>886</v>
+      </c>
+      <c r="B890" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C890" s="5" t="inlineStr">
+        <is>
+          <t>京都市南区</t>
+        </is>
+      </c>
+      <c r="D890" s="5" t="inlineStr">
+        <is>
+          <t>洛南高等学校</t>
+        </is>
+      </c>
+      <c r="E890" s="6" t="inlineStr">
+        <is>
+          <t>075-681-6511</t>
+        </is>
+      </c>
+      <c r="F890" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G890" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H890" s="8" t="n"/>
+      <c r="I890" s="9" t="n"/>
+      <c r="J890" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K890" s="8" t="n"/>
+      <c r="L890" s="9" t="n"/>
+      <c r="M890" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。附属中学校は075-672-2661</t>
+        </is>
+      </c>
+      <c r="N890" s="11" t="inlineStr">
+        <is>
+          <t>https://www.rakunan-h.ed.jp/gakuen/access/</t>
+        </is>
+      </c>
+      <c r="O890" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="4" t="n">
+        <v>887</v>
+      </c>
+      <c r="B891" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C891" s="5" t="inlineStr">
+        <is>
+          <t>京都市中京区</t>
+        </is>
+      </c>
+      <c r="D891" s="5" t="inlineStr">
+        <is>
+          <t>洛陽総合高等学校</t>
+        </is>
+      </c>
+      <c r="E891" s="6" t="inlineStr">
+        <is>
+          <t>075-802-0394</t>
+        </is>
+      </c>
+      <c r="F891" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G891" s="5" t="inlineStr">
+        <is>
+          <t>総合学科</t>
+        </is>
+      </c>
+      <c r="H891" s="8" t="n"/>
+      <c r="I891" s="9" t="n"/>
+      <c r="J891" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K891" s="8" t="n"/>
+      <c r="L891" s="9" t="n"/>
+      <c r="M891" s="10" t="inlineStr">
+        <is>
+          <t>複数サイトで一致、公式未確認</t>
+        </is>
+      </c>
+      <c r="N891" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/26104/ILSP0000040710_ipclm/ ; https://koukounyushi.net/kinki/kyoto/highschool/01kyotocity_otokuni/425rakuyosogo/</t>
+        </is>
+      </c>
+      <c r="O891" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="4" t="n">
+        <v>888</v>
+      </c>
+      <c r="B892" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C892" s="5" t="inlineStr">
+        <is>
+          <t>宇治市</t>
+        </is>
+      </c>
+      <c r="D892" s="5" t="inlineStr">
+        <is>
+          <t>立命館宇治高等学校</t>
+        </is>
+      </c>
+      <c r="E892" s="6" t="inlineStr">
+        <is>
+          <t>0774-41-3000</t>
+        </is>
+      </c>
+      <c r="F892" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G892" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H892" s="8" t="n"/>
+      <c r="I892" s="9" t="n"/>
+      <c r="J892" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K892" s="8" t="n"/>
+      <c r="L892" s="9" t="n"/>
+      <c r="M892" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。中高共通</t>
+        </is>
+      </c>
+      <c r="N892" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ritsumei.ac.jp/uji/</t>
+        </is>
+      </c>
+      <c r="O892" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="4" t="n">
+        <v>889</v>
+      </c>
+      <c r="B893" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C893" s="5" t="inlineStr">
+        <is>
+          <t>長岡京市</t>
+        </is>
+      </c>
+      <c r="D893" s="5" t="inlineStr">
+        <is>
+          <t>立命館高等学校</t>
+        </is>
+      </c>
+      <c r="E893" s="6" t="inlineStr">
+        <is>
+          <t>075-323-7111</t>
+        </is>
+      </c>
+      <c r="F893" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G893" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H893" s="8" t="n"/>
+      <c r="I893" s="9" t="n"/>
+      <c r="J893" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K893" s="8" t="n"/>
+      <c r="L893" s="9" t="n"/>
+      <c r="M893" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認。【移転】学校ネットの一覧では伏見区だが、現在は長岡京市（旧番号075-645-1051は使わない）</t>
+        </is>
+      </c>
+      <c r="N893" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ritsumei.ac.jp/nkc/</t>
+        </is>
+      </c>
+      <c r="O893" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="4" t="n">
+        <v>890</v>
+      </c>
+      <c r="B894" s="5" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="C894" s="5" t="inlineStr">
+        <is>
+          <t>京都市下京区</t>
+        </is>
+      </c>
+      <c r="D894" s="5" t="inlineStr">
+        <is>
+          <t>龍谷大学付属平安高等学校</t>
+        </is>
+      </c>
+      <c r="E894" s="6" t="inlineStr">
+        <is>
+          <t>075-361-4231</t>
+        </is>
+      </c>
+      <c r="F894" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G894" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H894" s="8" t="n"/>
+      <c r="I894" s="9" t="n"/>
+      <c r="J894" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K894" s="8" t="n"/>
+      <c r="L894" s="9" t="n"/>
+      <c r="M894" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで確認</t>
+        </is>
+      </c>
+      <c r="N894" s="11" t="inlineStr">
+        <is>
+          <t>https://www.heian.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O894" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O853"/>
-  <conditionalFormatting sqref="A5:O853">
+  <autoFilter ref="A4:O894"/>
+  <conditionalFormatting sqref="A5:O894">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -50734,10 +53153,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J853" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J894" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H853 K5:K853" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H894 K5:K894" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -51591,6 +54010,47 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O851" r:id="rId847"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O852" r:id="rId848"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O853" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O854" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O855" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O856" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O857" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O858" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O859" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O860" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O861" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O862" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O863" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O864" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O865" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O866" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O867" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O868" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O869" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O870" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O871" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O872" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O873" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O874" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O875" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O876" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O877" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O878" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O879" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O880" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O881" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O882" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O883" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O884" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O885" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O886" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O887" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O888" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O889" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O890" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O891" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O892" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O893" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O894" r:id="rId890"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -51603,7 +54063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -51690,43 +54150,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A4,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A4,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$853,A4,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A4,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$894,A4,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A4,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A4,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51737,43 +54197,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A5,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A5,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$853,A5,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A5,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$894,A5,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A5,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A5,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51784,43 +54244,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A6,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A6,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$853,A6,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A6,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$894,A6,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A6,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A6,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51831,43 +54291,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A7,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A7,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$853,A7,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A7,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$894,A7,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A7,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A7,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51878,43 +54338,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A8,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A8,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$853,A8,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A8,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$894,A8,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A8,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A8,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51925,43 +54385,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A9,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A9,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$853,A9,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A9,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$894,A9,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A9,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A9,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -51972,43 +54432,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A10,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A10,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$853,A10,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A10,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$894,A10,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A10,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A10,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52019,43 +54479,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A11,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A11,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$853,A11,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A11,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$894,A11,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A11,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A11,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52066,43 +54526,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A12,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A12,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$853,A12,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A12,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$894,A12,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A12,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A12,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52113,43 +54573,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A13,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A13,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$853,A13,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A13,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$894,A13,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A13,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A13,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52160,43 +54620,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A14,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A14,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$853,A14,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A14,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$894,A14,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A14,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A14,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52207,43 +54667,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A15,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A15,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$853,A15,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A15,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$894,A15,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A15,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A15,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52254,43 +54714,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A16,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A16,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$853,A16,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A16,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$894,A16,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A16,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A16,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52301,43 +54761,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A17,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A17,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$853,A17,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A17,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$894,A17,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A17,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A17,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52348,43 +54808,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A18,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A18,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$853,A18,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A18,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$894,A18,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A18,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A18,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52395,43 +54855,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A19,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A19,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$853,A19,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A19,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$894,A19,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A19,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A19,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52442,43 +54902,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A20,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A20,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$853,A20,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A20,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$894,A20,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A20,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A20,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52489,43 +54949,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A21,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A21,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$853,A21,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A21,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$894,A21,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A21,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A21,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52536,43 +54996,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A22,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A22,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$853,A22,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A22,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$894,A22,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A22,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A22,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52583,43 +55043,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A23,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A23,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$853,A23,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A23,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$894,A23,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A23,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A23,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52630,43 +55090,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A24,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A24,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$853,A24,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A24,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$894,A24,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A24,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A24,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52677,43 +55137,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A25,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A25,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$853,A25,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A25,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$894,A25,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A25,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A25,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52724,43 +55184,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A26,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A26,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$853,A26,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A26,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$894,A26,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A26,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A26,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52771,43 +55231,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A27,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A27,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$853,A27,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A27,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$894,A27,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A27,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A27,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -52818,90 +55278,137 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$853,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,A28,'架電リスト'!$E$5:$E$853,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A28,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$853,A28,'架電リスト'!$J$5:$J$853,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$853,A28,'架電リスト'!$J$5:$J$853,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$894,A28,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A28,'架電リスト'!$J$5:$J$894,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$853,$A28,'架電リスト'!$J$5:$J$853,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>京都府</t>
+        </is>
+      </c>
+      <c r="B29" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$894,A29)</f>
+        <v/>
+      </c>
+      <c r="C29" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A29,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D29" s="16">
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$894,A29,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A29,'架電リスト'!$J$5:$J$894,"")</f>
+        <v/>
+      </c>
+      <c r="E29" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F29" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G29" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H29" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I29" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <v/>
+      </c>
+      <c r="K29" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B29" s="17">
-        <f>SUM(B4:B28)</f>
+      <c r="B30" s="17">
+        <f>SUM(B4:B29)</f>
         <v/>
       </c>
-      <c r="C29" s="17">
-        <f>SUM(C4:C28)</f>
+      <c r="C30" s="17">
+        <f>SUM(C4:C29)</f>
         <v/>
       </c>
-      <c r="D29" s="17">
-        <f>SUM(D4:D28)</f>
+      <c r="D30" s="17">
+        <f>SUM(D4:D29)</f>
         <v/>
       </c>
-      <c r="E29" s="17">
-        <f>SUM(E4:E28)</f>
+      <c r="E30" s="17">
+        <f>SUM(E4:E29)</f>
         <v/>
       </c>
-      <c r="F29" s="17">
-        <f>SUM(F4:F28)</f>
+      <c r="F30" s="17">
+        <f>SUM(F4:F29)</f>
         <v/>
       </c>
-      <c r="G29" s="17">
-        <f>SUM(G4:G28)</f>
+      <c r="G30" s="17">
+        <f>SUM(G4:G29)</f>
         <v/>
       </c>
-      <c r="H29" s="17">
-        <f>SUM(H4:H28)</f>
+      <c r="H30" s="17">
+        <f>SUM(H4:H29)</f>
         <v/>
       </c>
-      <c r="I29" s="17">
-        <f>SUM(I4:I28)</f>
+      <c r="I30" s="17">
+        <f>SUM(I4:I29)</f>
         <v/>
       </c>
-      <c r="J29" s="17">
-        <f>SUM(J4:J28)</f>
+      <c r="J30" s="17">
+        <f>SUM(J4:J29)</f>
         <v/>
       </c>
-      <c r="K29" s="17">
-        <f>SUM(K4:K28)</f>
+      <c r="K30" s="17">
+        <f>SUM(K4:K29)</f>
         <v/>
       </c>
     </row>
@@ -52991,7 +55498,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・25都道府県、849校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・26都道府県、890校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$894</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$994</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O894"/>
+  <dimension ref="A1:O994"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（26都道府県／890校）</t>
+          <t>私立高等学校 架電リスト（27都道府県／990校）</t>
         </is>
       </c>
     </row>
@@ -53142,9 +53142,5753 @@
         </is>
       </c>
     </row>
+    <row r="895">
+      <c r="A895" s="4" t="n">
+        <v>891</v>
+      </c>
+      <c r="B895" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C895" s="5" t="inlineStr">
+        <is>
+          <t>箕面市</t>
+        </is>
+      </c>
+      <c r="D895" s="5" t="inlineStr">
+        <is>
+          <t>アサンプション国際高等学校</t>
+        </is>
+      </c>
+      <c r="E895" s="6" t="inlineStr">
+        <is>
+          <t>072-721-3080</t>
+        </is>
+      </c>
+      <c r="F895" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G895" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H895" s="8" t="n"/>
+      <c r="I895" s="9" t="n"/>
+      <c r="J895" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K895" s="8" t="n"/>
+      <c r="L895" s="9" t="n"/>
+      <c r="M895" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号。1サイトのみ072-721-7680と記載（誤記とみられる）</t>
+        </is>
+      </c>
+      <c r="N895" s="11" t="inlineStr">
+        <is>
+          <t>https://www.assumption.ed.jp/jsh/</t>
+        </is>
+      </c>
+      <c r="O895" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="4" t="n">
+        <v>892</v>
+      </c>
+      <c r="B896" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C896" s="5" t="inlineStr">
+        <is>
+          <t>東大阪市</t>
+        </is>
+      </c>
+      <c r="D896" s="5" t="inlineStr">
+        <is>
+          <t>アナン学園高等学校</t>
+        </is>
+      </c>
+      <c r="E896" s="6" t="inlineStr">
+        <is>
+          <t>06-6723-5511</t>
+        </is>
+      </c>
+      <c r="F896" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G896" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H896" s="8" t="n"/>
+      <c r="I896" s="9" t="n"/>
+      <c r="J896" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K896" s="8" t="n"/>
+      <c r="L896" s="9" t="n"/>
+      <c r="M896" s="10" t="inlineStr">
+        <is>
+          <t>法人の事業報告書（公式）で確認。1サイトのみ06-6732-1209と記載</t>
+        </is>
+      </c>
+      <c r="N896" s="11" t="inlineStr">
+        <is>
+          <t>https://www.anangakuen.ed.jp/pdf/infodisclosure/2022/report/report01.pdf</t>
+        </is>
+      </c>
+      <c r="O896" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="4" t="n">
+        <v>893</v>
+      </c>
+      <c r="B897" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C897" s="5" t="inlineStr">
+        <is>
+          <t>大阪市阿倍野区</t>
+        </is>
+      </c>
+      <c r="D897" s="5" t="inlineStr">
+        <is>
+          <t>あべの翔学高等学校</t>
+        </is>
+      </c>
+      <c r="E897" s="6" t="inlineStr">
+        <is>
+          <t>06-6719-2801</t>
+        </is>
+      </c>
+      <c r="F897" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G897" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H897" s="8" t="n"/>
+      <c r="I897" s="9" t="n"/>
+      <c r="J897" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K897" s="8" t="n"/>
+      <c r="L897" s="9" t="n"/>
+      <c r="M897" s="10" t="n"/>
+      <c r="N897" s="11" t="inlineStr">
+        <is>
+          <t>https://abeno-shogaku.ed.jp/school/access</t>
+        </is>
+      </c>
+      <c r="O897" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="4" t="n">
+        <v>894</v>
+      </c>
+      <c r="B898" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C898" s="5" t="inlineStr">
+        <is>
+          <t>大阪市天王寺区</t>
+        </is>
+      </c>
+      <c r="D898" s="5" t="inlineStr">
+        <is>
+          <t>上宮高等学校</t>
+        </is>
+      </c>
+      <c r="E898" s="6" t="inlineStr">
+        <is>
+          <t>06-6771-5701</t>
+        </is>
+      </c>
+      <c r="F898" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G898" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H898" s="8" t="n"/>
+      <c r="I898" s="9" t="n"/>
+      <c r="J898" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K898" s="8" t="n"/>
+      <c r="L898" s="9" t="n"/>
+      <c r="M898" s="10" t="n"/>
+      <c r="N898" s="11" t="inlineStr">
+        <is>
+          <t>https://www.uenomiya.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O898" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="4" t="n">
+        <v>895</v>
+      </c>
+      <c r="B899" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C899" s="5" t="inlineStr">
+        <is>
+          <t>太子町</t>
+        </is>
+      </c>
+      <c r="D899" s="5" t="inlineStr">
+        <is>
+          <t>上宮太子高等学校</t>
+        </is>
+      </c>
+      <c r="E899" s="6" t="inlineStr">
+        <is>
+          <t>0721-98-3611</t>
+        </is>
+      </c>
+      <c r="F899" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G899" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H899" s="8" t="n"/>
+      <c r="I899" s="9" t="n"/>
+      <c r="J899" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K899" s="8" t="n"/>
+      <c r="L899" s="9" t="n"/>
+      <c r="M899" s="10" t="n"/>
+      <c r="N899" s="11" t="inlineStr">
+        <is>
+          <t>https://uenomiya-taishi.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O899" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="4" t="n">
+        <v>896</v>
+      </c>
+      <c r="B900" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C900" s="5" t="inlineStr">
+        <is>
+          <t>大阪市淀川区</t>
+        </is>
+      </c>
+      <c r="D900" s="5" t="inlineStr">
+        <is>
+          <t>英真学園高等学校</t>
+        </is>
+      </c>
+      <c r="E900" s="6" t="inlineStr">
+        <is>
+          <t>06-6303-2181</t>
+        </is>
+      </c>
+      <c r="F900" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G900" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H900" s="8" t="n"/>
+      <c r="I900" s="9" t="n"/>
+      <c r="J900" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K900" s="8" t="n"/>
+      <c r="L900" s="9" t="n"/>
+      <c r="M900" s="10" t="n"/>
+      <c r="N900" s="11" t="inlineStr">
+        <is>
+          <t>https://eishingakuen.ac.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O900" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="4" t="n">
+        <v>897</v>
+      </c>
+      <c r="B901" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C901" s="5" t="inlineStr">
+        <is>
+          <t>大阪市福島区</t>
+        </is>
+      </c>
+      <c r="D901" s="5" t="inlineStr">
+        <is>
+          <t>英風高等学校</t>
+        </is>
+      </c>
+      <c r="E901" s="6" t="inlineStr">
+        <is>
+          <t>06-6464-0668</t>
+        </is>
+      </c>
+      <c r="F901" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G901" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H901" s="8" t="n"/>
+      <c r="I901" s="9" t="n"/>
+      <c r="J901" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K901" s="8" t="n"/>
+      <c r="L901" s="9" t="n"/>
+      <c r="M901" s="10" t="inlineStr">
+        <is>
+          <t>通信制（女子）。フリーダイヤル0120-812-078も公式記載</t>
+        </is>
+      </c>
+      <c r="N901" s="11" t="inlineStr">
+        <is>
+          <t>https://www.eifu.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O901" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="4" t="n">
+        <v>898</v>
+      </c>
+      <c r="B902" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C902" s="5" t="inlineStr">
+        <is>
+          <t>大阪市中央区</t>
+        </is>
+      </c>
+      <c r="D902" s="5" t="inlineStr">
+        <is>
+          <t>追手門学院大手前高等学校</t>
+        </is>
+      </c>
+      <c r="E902" s="6" t="inlineStr">
+        <is>
+          <t>06-6942-2235</t>
+        </is>
+      </c>
+      <c r="F902" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G902" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H902" s="8" t="n"/>
+      <c r="I902" s="9" t="n"/>
+      <c r="J902" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K902" s="8" t="n"/>
+      <c r="L902" s="9" t="n"/>
+      <c r="M902" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N902" s="11" t="inlineStr">
+        <is>
+          <t>https://www.otemon-js.ed.jp/hs/</t>
+        </is>
+      </c>
+      <c r="O902" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="4" t="n">
+        <v>899</v>
+      </c>
+      <c r="B903" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C903" s="5" t="inlineStr">
+        <is>
+          <t>茨木市</t>
+        </is>
+      </c>
+      <c r="D903" s="5" t="inlineStr">
+        <is>
+          <t>追手門学院高等学校</t>
+        </is>
+      </c>
+      <c r="E903" s="6" t="inlineStr">
+        <is>
+          <t>072-697-8185</t>
+        </is>
+      </c>
+      <c r="F903" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G903" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H903" s="8" t="n"/>
+      <c r="I903" s="9" t="n"/>
+      <c r="J903" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K903" s="8" t="n"/>
+      <c r="L903" s="9" t="n"/>
+      <c r="M903" s="10" t="inlineStr">
+        <is>
+          <t>中高共通代表。ユネスコ関連ページに072-643-1333の記載あり（旧番号の可能性）</t>
+        </is>
+      </c>
+      <c r="N903" s="11" t="inlineStr">
+        <is>
+          <t>https://www.otemon-jh.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O903" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="4" t="n">
+        <v>900</v>
+      </c>
+      <c r="B904" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C904" s="5" t="inlineStr">
+        <is>
+          <t>大阪市生野区</t>
+        </is>
+      </c>
+      <c r="D904" s="5" t="inlineStr">
+        <is>
+          <t>大阪偕星学園高等学校</t>
+        </is>
+      </c>
+      <c r="E904" s="6" t="inlineStr">
+        <is>
+          <t>06-6716-0003</t>
+        </is>
+      </c>
+      <c r="F904" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G904" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H904" s="8" t="n"/>
+      <c r="I904" s="9" t="n"/>
+      <c r="J904" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K904" s="8" t="n"/>
+      <c r="L904" s="9" t="n"/>
+      <c r="M904" s="10" t="n"/>
+      <c r="N904" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osaka-kaisei.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O904" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="4" t="n">
+        <v>901</v>
+      </c>
+      <c r="B905" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C905" s="5" t="inlineStr">
+        <is>
+          <t>吹田市</t>
+        </is>
+      </c>
+      <c r="D905" s="5" t="inlineStr">
+        <is>
+          <t>大阪学院大学高等学校</t>
+        </is>
+      </c>
+      <c r="E905" s="6" t="inlineStr">
+        <is>
+          <t>06-6381-6661</t>
+        </is>
+      </c>
+      <c r="F905" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G905" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H905" s="8" t="n"/>
+      <c r="I905" s="9" t="n"/>
+      <c r="J905" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K905" s="8" t="n"/>
+      <c r="L905" s="9" t="n"/>
+      <c r="M905" s="10" t="n"/>
+      <c r="N905" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ogu-h.ed.jp/access.html</t>
+        </is>
+      </c>
+      <c r="O905" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="4" t="n">
+        <v>902</v>
+      </c>
+      <c r="B906" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C906" s="5" t="inlineStr">
+        <is>
+          <t>大阪市住吉区</t>
+        </is>
+      </c>
+      <c r="D906" s="5" t="inlineStr">
+        <is>
+          <t>大阪学芸高等学校</t>
+        </is>
+      </c>
+      <c r="E906" s="6" t="inlineStr">
+        <is>
+          <t>06-6693-6301</t>
+        </is>
+      </c>
+      <c r="F906" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G906" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H906" s="8" t="n"/>
+      <c r="I906" s="9" t="n"/>
+      <c r="J906" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K906" s="8" t="n"/>
+      <c r="L906" s="9" t="n"/>
+      <c r="M906" s="10" t="inlineStr">
+        <is>
+          <t>法人代表は06-6693-6303</t>
+        </is>
+      </c>
+      <c r="N906" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osakagakugei.ac.jp/senior/</t>
+        </is>
+      </c>
+      <c r="O906" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="4" t="n">
+        <v>903</v>
+      </c>
+      <c r="B907" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C907" s="5" t="inlineStr">
+        <is>
+          <t>河内長野市</t>
+        </is>
+      </c>
+      <c r="D907" s="5" t="inlineStr">
+        <is>
+          <t>大阪暁光高等学校</t>
+        </is>
+      </c>
+      <c r="E907" s="6" t="inlineStr">
+        <is>
+          <t>0721-53-5281</t>
+        </is>
+      </c>
+      <c r="F907" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G907" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H907" s="8" t="n"/>
+      <c r="I907" s="9" t="n"/>
+      <c r="J907" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K907" s="8" t="n"/>
+      <c r="L907" s="9" t="n"/>
+      <c r="M907" s="10" t="inlineStr">
+        <is>
+          <t>入試広報室は0721-26-7098</t>
+        </is>
+      </c>
+      <c r="N907" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osakagyoko.ed.jp/official/</t>
+        </is>
+      </c>
+      <c r="O907" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="4" t="n">
+        <v>904</v>
+      </c>
+      <c r="B908" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C908" s="5" t="inlineStr">
+        <is>
+          <t>摂津市</t>
+        </is>
+      </c>
+      <c r="D908" s="5" t="inlineStr">
+        <is>
+          <t>大阪薫英女学院高等学校</t>
+        </is>
+      </c>
+      <c r="E908" s="6" t="inlineStr">
+        <is>
+          <t>06-6381-5381</t>
+        </is>
+      </c>
+      <c r="F908" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G908" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H908" s="8" t="n"/>
+      <c r="I908" s="9" t="n"/>
+      <c r="J908" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K908" s="8" t="n"/>
+      <c r="L908" s="9" t="n"/>
+      <c r="M908" s="10" t="inlineStr">
+        <is>
+          <t>入試直通06-6381-0335。法人代表は06-6381-6548</t>
+        </is>
+      </c>
+      <c r="N908" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kun-ei.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O908" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="4" t="n">
+        <v>905</v>
+      </c>
+      <c r="B909" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C909" s="5" t="inlineStr">
+        <is>
+          <t>大阪市東淀川区</t>
+        </is>
+      </c>
+      <c r="D909" s="5" t="inlineStr">
+        <is>
+          <t>大阪高等学校</t>
+        </is>
+      </c>
+      <c r="E909" s="6" t="inlineStr">
+        <is>
+          <t>06-6340-3031</t>
+        </is>
+      </c>
+      <c r="F909" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G909" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H909" s="8" t="n"/>
+      <c r="I909" s="9" t="n"/>
+      <c r="J909" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K909" s="8" t="n"/>
+      <c r="L909" s="9" t="n"/>
+      <c r="M909" s="10" t="inlineStr">
+        <is>
+          <t>大阪市東淀川区ページでも一致</t>
+        </is>
+      </c>
+      <c r="N909" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osakashs.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O909" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="4" t="n">
+        <v>906</v>
+      </c>
+      <c r="B910" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C910" s="5" t="inlineStr">
+        <is>
+          <t>守口市</t>
+        </is>
+      </c>
+      <c r="D910" s="5" t="inlineStr">
+        <is>
+          <t>大阪国際高等学校</t>
+        </is>
+      </c>
+      <c r="E910" s="6" t="inlineStr">
+        <is>
+          <t>06-6992-5931</t>
+        </is>
+      </c>
+      <c r="F910" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G910" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H910" s="8" t="n"/>
+      <c r="I910" s="9" t="n"/>
+      <c r="J910" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K910" s="8" t="n"/>
+      <c r="L910" s="9" t="n"/>
+      <c r="M910" s="10" t="inlineStr">
+        <is>
+          <t>中高一体（大阪国際中学校高等学校）。所在地は守口市松下町。募集広報部直通06-6992-5941</t>
+        </is>
+      </c>
+      <c r="N910" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kokusai-h.oiu.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O910" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="4" t="n">
+        <v>907</v>
+      </c>
+      <c r="B911" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C911" s="5" t="inlineStr">
+        <is>
+          <t>大阪市住之江区</t>
+        </is>
+      </c>
+      <c r="D911" s="5" t="inlineStr">
+        <is>
+          <t>大阪金剛インターナショナル高等学校</t>
+        </is>
+      </c>
+      <c r="E911" s="6" t="inlineStr">
+        <is>
+          <t>06-4703-1780</t>
+        </is>
+      </c>
+      <c r="F911" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G911" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H911" s="8" t="n"/>
+      <c r="I911" s="9" t="n"/>
+      <c r="J911" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K911" s="8" t="n"/>
+      <c r="L911" s="9" t="n"/>
+      <c r="M911" s="10" t="inlineStr">
+        <is>
+          <t>一部サイトに06-4703-1781の記載あり</t>
+        </is>
+      </c>
+      <c r="N911" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kongogakuen.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O911" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="4" t="n">
+        <v>908</v>
+      </c>
+      <c r="B912" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C912" s="5" t="inlineStr">
+        <is>
+          <t>大阪市城東区</t>
+        </is>
+      </c>
+      <c r="D912" s="5" t="inlineStr">
+        <is>
+          <t>大阪産業大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E912" s="6" t="inlineStr">
+        <is>
+          <t>06-6939-1491</t>
+        </is>
+      </c>
+      <c r="F912" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G912" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H912" s="8" t="n"/>
+      <c r="I912" s="9" t="n"/>
+      <c r="J912" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K912" s="8" t="n"/>
+      <c r="L912" s="9" t="n"/>
+      <c r="M912" s="10" t="n"/>
+      <c r="N912" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osaka-sandai.ed.jp/guide/outline</t>
+        </is>
+      </c>
+      <c r="O912" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="4" t="n">
+        <v>909</v>
+      </c>
+      <c r="B913" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C913" s="5" t="inlineStr">
+        <is>
+          <t>東大阪市</t>
+        </is>
+      </c>
+      <c r="D913" s="5" t="inlineStr">
+        <is>
+          <t>大阪商業大学高等学校</t>
+        </is>
+      </c>
+      <c r="E913" s="6" t="inlineStr">
+        <is>
+          <t>06-6781-3050</t>
+        </is>
+      </c>
+      <c r="F913" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G913" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H913" s="8" t="n"/>
+      <c r="I913" s="9" t="n"/>
+      <c r="J913" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K913" s="8" t="n"/>
+      <c r="L913" s="9" t="n"/>
+      <c r="M913" s="10" t="inlineStr">
+        <is>
+          <t>一部電話帳サイトに06-6781-3060の記載あり（公式と不一致）</t>
+        </is>
+      </c>
+      <c r="N913" s="11" t="inlineStr">
+        <is>
+          <t>https://www.daishodai-h.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O913" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="4" t="n">
+        <v>910</v>
+      </c>
+      <c r="B914" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C914" s="5" t="inlineStr">
+        <is>
+          <t>堺市中区</t>
+        </is>
+      </c>
+      <c r="D914" s="5" t="inlineStr">
+        <is>
+          <t>大阪商業大学堺高等学校</t>
+        </is>
+      </c>
+      <c r="E914" s="6" t="inlineStr">
+        <is>
+          <t>072-278-2252</t>
+        </is>
+      </c>
+      <c r="F914" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G914" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H914" s="8" t="n"/>
+      <c r="I914" s="9" t="n"/>
+      <c r="J914" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K914" s="8" t="n"/>
+      <c r="L914" s="9" t="n"/>
+      <c r="M914" s="10" t="n"/>
+      <c r="N914" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shodaisakai.ac.jp/inquiry/</t>
+        </is>
+      </c>
+      <c r="O914" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="4" t="n">
+        <v>911</v>
+      </c>
+      <c r="B915" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C915" s="5" t="inlineStr">
+        <is>
+          <t>大阪市城東区</t>
+        </is>
+      </c>
+      <c r="D915" s="5" t="inlineStr">
+        <is>
+          <t>大阪信愛学院高等学校</t>
+        </is>
+      </c>
+      <c r="E915" s="6" t="inlineStr">
+        <is>
+          <t>06-6939-4391</t>
+        </is>
+      </c>
+      <c r="F915" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G915" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H915" s="8" t="n"/>
+      <c r="I915" s="9" t="n"/>
+      <c r="J915" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K915" s="8" t="n"/>
+      <c r="L915" s="9" t="n"/>
+      <c r="M915" s="10" t="inlineStr">
+        <is>
+          <t>公式に「代表」と明記。公式アクセス・問合せページには06-6167-8546の記載もあり</t>
+        </is>
+      </c>
+      <c r="N915" s="11" t="inlineStr">
+        <is>
+          <t>https://high.osaka-shinai.ed.jp/admissions/opencampus/</t>
+        </is>
+      </c>
+      <c r="O915" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="4" t="n">
+        <v>912</v>
+      </c>
+      <c r="B916" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C916" s="5" t="inlineStr">
+        <is>
+          <t>大阪市中央区</t>
+        </is>
+      </c>
+      <c r="D916" s="5" t="inlineStr">
+        <is>
+          <t>大阪女学院高等学校</t>
+        </is>
+      </c>
+      <c r="E916" s="6" t="inlineStr">
+        <is>
+          <t>06-6761-4113</t>
+        </is>
+      </c>
+      <c r="F916" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G916" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H916" s="8" t="n"/>
+      <c r="I916" s="9" t="n"/>
+      <c r="J916" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K916" s="8" t="n"/>
+      <c r="L916" s="9" t="n"/>
+      <c r="M916" s="10" t="inlineStr">
+        <is>
+          <t>法人事務局は06-6761-4013</t>
+        </is>
+      </c>
+      <c r="N916" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osaka-jogakuin.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O916" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="4" t="n">
+        <v>913</v>
+      </c>
+      <c r="B917" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C917" s="5" t="inlineStr">
+        <is>
+          <t>大阪市東淀川区</t>
+        </is>
+      </c>
+      <c r="D917" s="5" t="inlineStr">
+        <is>
+          <t>大阪成蹊女子高等学校</t>
+        </is>
+      </c>
+      <c r="E917" s="6" t="inlineStr">
+        <is>
+          <t>06-6829-2510</t>
+        </is>
+      </c>
+      <c r="F917" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G917" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H917" s="8" t="n"/>
+      <c r="I917" s="9" t="n"/>
+      <c r="J917" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K917" s="8" t="n"/>
+      <c r="L917" s="9" t="n"/>
+      <c r="M917" s="10" t="inlineStr">
+        <is>
+          <t>募集広報企画室は06-6829-2514</t>
+        </is>
+      </c>
+      <c r="N917" s="11" t="inlineStr">
+        <is>
+          <t>https://high.osaka-seikei.jp/access/</t>
+        </is>
+      </c>
+      <c r="O917" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="4" t="n">
+        <v>914</v>
+      </c>
+      <c r="B918" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C918" s="5" t="inlineStr">
+        <is>
+          <t>大阪市天王寺区</t>
+        </is>
+      </c>
+      <c r="D918" s="5" t="inlineStr">
+        <is>
+          <t>大阪星光学院高等学校</t>
+        </is>
+      </c>
+      <c r="E918" s="6" t="inlineStr">
+        <is>
+          <t>06-6771-0737</t>
+        </is>
+      </c>
+      <c r="F918" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G918" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H918" s="8" t="n"/>
+      <c r="I918" s="9" t="n"/>
+      <c r="J918" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K918" s="8" t="n"/>
+      <c r="L918" s="9" t="n"/>
+      <c r="M918" s="10" t="inlineStr">
+        <is>
+          <t>中高共通。高校からの募集は停止との第三者情報あり</t>
+        </is>
+      </c>
+      <c r="N918" s="11" t="inlineStr">
+        <is>
+          <t>http://www.osakaseiko.ac.jp/access/access.html</t>
+        </is>
+      </c>
+      <c r="O918" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="4" t="n">
+        <v>915</v>
+      </c>
+      <c r="B919" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C919" s="5" t="inlineStr">
+        <is>
+          <t>島本町</t>
+        </is>
+      </c>
+      <c r="D919" s="5" t="inlineStr">
+        <is>
+          <t>大阪青凌高等学校</t>
+        </is>
+      </c>
+      <c r="E919" s="6" t="inlineStr">
+        <is>
+          <t>075-754-7771</t>
+        </is>
+      </c>
+      <c r="F919" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G919" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H919" s="8" t="n"/>
+      <c r="I919" s="9" t="n"/>
+      <c r="J919" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K919" s="8" t="n"/>
+      <c r="L919" s="9" t="n"/>
+      <c r="M919" s="10" t="inlineStr">
+        <is>
+          <t>2020年に三島郡島本町へ移転（旧・高槻市の番号は072-669-4111）。入試広報室は075-754-7754</t>
+        </is>
+      </c>
+      <c r="N919" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osakaseiryo.jp/access/</t>
+        </is>
+      </c>
+      <c r="O919" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="4" t="n">
+        <v>916</v>
+      </c>
+      <c r="B920" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C920" s="5" t="inlineStr">
+        <is>
+          <t>熊取町</t>
+        </is>
+      </c>
+      <c r="D920" s="5" t="inlineStr">
+        <is>
+          <t>大阪体育大学浪商高等学校</t>
+        </is>
+      </c>
+      <c r="E920" s="6" t="inlineStr">
+        <is>
+          <t>072-453-7001</t>
+        </is>
+      </c>
+      <c r="F920" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G920" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H920" s="8" t="n"/>
+      <c r="I920" s="9" t="n"/>
+      <c r="J920" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K920" s="8" t="n"/>
+      <c r="L920" s="9" t="n"/>
+      <c r="M920" s="10" t="inlineStr">
+        <is>
+          <t>入試対策室は072-453-7972</t>
+        </is>
+      </c>
+      <c r="N920" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ouhs-school.jp/namisho/</t>
+        </is>
+      </c>
+      <c r="O920" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="4" t="n">
+        <v>917</v>
+      </c>
+      <c r="B921" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C921" s="5" t="inlineStr">
+        <is>
+          <t>守口市</t>
+        </is>
+      </c>
+      <c r="D921" s="5" t="inlineStr">
+        <is>
+          <t>大阪電気通信大学高等学校</t>
+        </is>
+      </c>
+      <c r="E921" s="6" t="inlineStr">
+        <is>
+          <t>06-6992-6261</t>
+        </is>
+      </c>
+      <c r="F921" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G921" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H921" s="8" t="n"/>
+      <c r="I921" s="9" t="n"/>
+      <c r="J921" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K921" s="8" t="n"/>
+      <c r="L921" s="9" t="n"/>
+      <c r="M921" s="10" t="inlineStr">
+        <is>
+          <t>大学法人の公式サイトに「代表」と記載</t>
+        </is>
+      </c>
+      <c r="N921" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osakac.ac.jp/corp/access/</t>
+        </is>
+      </c>
+      <c r="O921" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="4" t="n">
+        <v>918</v>
+      </c>
+      <c r="B922" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C922" s="5" t="inlineStr">
+        <is>
+          <t>大東市</t>
+        </is>
+      </c>
+      <c r="D922" s="5" t="inlineStr">
+        <is>
+          <t>大阪桐蔭高等学校</t>
+        </is>
+      </c>
+      <c r="E922" s="6" t="inlineStr">
+        <is>
+          <t>072-870-1001</t>
+        </is>
+      </c>
+      <c r="F922" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G922" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H922" s="8" t="n"/>
+      <c r="I922" s="9" t="n"/>
+      <c r="J922" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K922" s="8" t="n"/>
+      <c r="L922" s="9" t="n"/>
+      <c r="M922" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトのフッター・大東市HPで一致</t>
+        </is>
+      </c>
+      <c r="N922" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osakatoin.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O922" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="4" t="n">
+        <v>919</v>
+      </c>
+      <c r="B923" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C923" s="5" t="inlineStr">
+        <is>
+          <t>大阪市天王寺区</t>
+        </is>
+      </c>
+      <c r="D923" s="5" t="inlineStr">
+        <is>
+          <t>大阪夕陽丘学園高等学校</t>
+        </is>
+      </c>
+      <c r="E923" s="6" t="inlineStr">
+        <is>
+          <t>06-6771-9510</t>
+        </is>
+      </c>
+      <c r="F923" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G923" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H923" s="8" t="n"/>
+      <c r="I923" s="9" t="n"/>
+      <c r="J923" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K923" s="8" t="n"/>
+      <c r="L923" s="9" t="n"/>
+      <c r="M923" s="10" t="n"/>
+      <c r="N923" s="11" t="inlineStr">
+        <is>
+          <t>https://www.oyg.ed.jp/about/</t>
+        </is>
+      </c>
+      <c r="O923" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="4" t="n">
+        <v>920</v>
+      </c>
+      <c r="B924" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C924" s="5" t="inlineStr">
+        <is>
+          <t>藤井寺市</t>
+        </is>
+      </c>
+      <c r="D924" s="5" t="inlineStr">
+        <is>
+          <t>大阪緑涼高等学校</t>
+        </is>
+      </c>
+      <c r="E924" s="6" t="inlineStr">
+        <is>
+          <t>072-955-0718</t>
+        </is>
+      </c>
+      <c r="F924" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G924" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H924" s="8" t="n"/>
+      <c r="I924" s="9" t="n"/>
+      <c r="J924" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K924" s="8" t="n"/>
+      <c r="L924" s="9" t="n"/>
+      <c r="M924" s="10" t="n"/>
+      <c r="N924" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osakaryokuryo.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O924" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="4" t="n">
+        <v>921</v>
+      </c>
+      <c r="B925" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C925" s="5" t="inlineStr">
+        <is>
+          <t>大阪市阿倍野区</t>
+        </is>
+      </c>
+      <c r="D925" s="5" t="inlineStr">
+        <is>
+          <t>大谷高等学校（大阪府）</t>
+        </is>
+      </c>
+      <c r="E925" s="6" t="inlineStr">
+        <is>
+          <t>06-6661-8400</t>
+        </is>
+      </c>
+      <c r="F925" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G925" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H925" s="8" t="n"/>
+      <c r="I925" s="9" t="n"/>
+      <c r="J925" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K925" s="8" t="n"/>
+      <c r="L925" s="9" t="n"/>
+      <c r="M925" s="10" t="inlineStr">
+        <is>
+          <t>中学校は06-6661-0385</t>
+        </is>
+      </c>
+      <c r="N925" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osk-ohtani.ed.jp/policy/</t>
+        </is>
+      </c>
+      <c r="O925" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="4" t="n">
+        <v>922</v>
+      </c>
+      <c r="B926" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C926" s="5" t="inlineStr">
+        <is>
+          <t>大阪市城東区</t>
+        </is>
+      </c>
+      <c r="D926" s="5" t="inlineStr">
+        <is>
+          <t>開明高等学校</t>
+        </is>
+      </c>
+      <c r="E926" s="6" t="inlineStr">
+        <is>
+          <t>06-6932-4461</t>
+        </is>
+      </c>
+      <c r="F926" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G926" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H926" s="8" t="n"/>
+      <c r="I926" s="9" t="n"/>
+      <c r="J926" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K926" s="8" t="n"/>
+      <c r="L926" s="9" t="n"/>
+      <c r="M926" s="10" t="inlineStr">
+        <is>
+          <t>中高共通</t>
+        </is>
+      </c>
+      <c r="N926" s="11" t="inlineStr">
+        <is>
+          <t>https://kaimei.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O926" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="4" t="n">
+        <v>923</v>
+      </c>
+      <c r="B927" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C927" s="5" t="inlineStr">
+        <is>
+          <t>堺市堺区</t>
+        </is>
+      </c>
+      <c r="D927" s="5" t="inlineStr">
+        <is>
+          <t>香ヶ丘リベルテ高等学校</t>
+        </is>
+      </c>
+      <c r="E927" s="6" t="inlineStr">
+        <is>
+          <t>072-238-7881</t>
+        </is>
+      </c>
+      <c r="F927" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G927" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H927" s="8" t="n"/>
+      <c r="I927" s="9" t="n"/>
+      <c r="J927" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K927" s="8" t="n"/>
+      <c r="L927" s="9" t="n"/>
+      <c r="M927" s="10" t="n"/>
+      <c r="N927" s="11" t="inlineStr">
+        <is>
+          <t>https://liberte.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O927" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="4" t="n">
+        <v>924</v>
+      </c>
+      <c r="B928" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C928" s="5" t="inlineStr">
+        <is>
+          <t>茨木市</t>
+        </is>
+      </c>
+      <c r="D928" s="5" t="inlineStr">
+        <is>
+          <t>関西大倉高等学校</t>
+        </is>
+      </c>
+      <c r="E928" s="6" t="inlineStr">
+        <is>
+          <t>072-643-6321</t>
+        </is>
+      </c>
+      <c r="F928" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G928" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H928" s="8" t="n"/>
+      <c r="I928" s="9" t="n"/>
+      <c r="J928" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K928" s="8" t="n"/>
+      <c r="L928" s="9" t="n"/>
+      <c r="M928" s="10" t="n"/>
+      <c r="N928" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kankura.jp/</t>
+        </is>
+      </c>
+      <c r="O928" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="4" t="n">
+        <v>925</v>
+      </c>
+      <c r="B929" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C929" s="5" t="inlineStr">
+        <is>
+          <t>交野市</t>
+        </is>
+      </c>
+      <c r="D929" s="5" t="inlineStr">
+        <is>
+          <t>関西創価高等学校</t>
+        </is>
+      </c>
+      <c r="E929" s="6" t="inlineStr">
+        <is>
+          <t>072-891-0011</t>
+        </is>
+      </c>
+      <c r="F929" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G929" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H929" s="8" t="n"/>
+      <c r="I929" s="9" t="n"/>
+      <c r="J929" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K929" s="8" t="n"/>
+      <c r="L929" s="9" t="n"/>
+      <c r="M929" s="10" t="n"/>
+      <c r="N929" s="11" t="inlineStr">
+        <is>
+          <t>https://kansai-senior.soka.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O929" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="4" t="n">
+        <v>926</v>
+      </c>
+      <c r="B930" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C930" s="5" t="inlineStr">
+        <is>
+          <t>高槻市</t>
+        </is>
+      </c>
+      <c r="D930" s="5" t="inlineStr">
+        <is>
+          <t>関西大学高等部</t>
+        </is>
+      </c>
+      <c r="E930" s="6" t="inlineStr">
+        <is>
+          <t>072-684-4327</t>
+        </is>
+      </c>
+      <c r="F930" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G930" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H930" s="8" t="n"/>
+      <c r="I930" s="9" t="n"/>
+      <c r="J930" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K930" s="8" t="n"/>
+      <c r="L930" s="9" t="n"/>
+      <c r="M930" s="10" t="inlineStr">
+        <is>
+          <t>高槻ミューズキャンパス内。キャンパス代表は072-684-4000</t>
+        </is>
+      </c>
+      <c r="N930" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kansai-u.ac.jp/Fc_ss/access.php</t>
+        </is>
+      </c>
+      <c r="O930" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="4" t="n">
+        <v>927</v>
+      </c>
+      <c r="B931" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C931" s="5" t="inlineStr">
+        <is>
+          <t>吹田市</t>
+        </is>
+      </c>
+      <c r="D931" s="5" t="inlineStr">
+        <is>
+          <t>関西大学第一高等学校</t>
+        </is>
+      </c>
+      <c r="E931" s="6" t="inlineStr">
+        <is>
+          <t>06-6337-7750</t>
+        </is>
+      </c>
+      <c r="F931" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G931" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H931" s="8" t="n"/>
+      <c r="I931" s="9" t="n"/>
+      <c r="J931" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K931" s="8" t="n"/>
+      <c r="L931" s="9" t="n"/>
+      <c r="M931" s="10" t="n"/>
+      <c r="N931" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kansai-u.ac.jp/dai-ichi/high/</t>
+        </is>
+      </c>
+      <c r="O931" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="4" t="n">
+        <v>928</v>
+      </c>
+      <c r="B932" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C932" s="5" t="inlineStr">
+        <is>
+          <t>大阪市東淀川区</t>
+        </is>
+      </c>
+      <c r="D932" s="5" t="inlineStr">
+        <is>
+          <t>関西大学北陽高等学校</t>
+        </is>
+      </c>
+      <c r="E932" s="6" t="inlineStr">
+        <is>
+          <t>06-6328-5964</t>
+        </is>
+      </c>
+      <c r="F932" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G932" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H932" s="8" t="n"/>
+      <c r="I932" s="9" t="n"/>
+      <c r="J932" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K932" s="8" t="n"/>
+      <c r="L932" s="9" t="n"/>
+      <c r="M932" s="10" t="n"/>
+      <c r="N932" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kansai-u.ac.jp/hokuyo/header/access.html</t>
+        </is>
+      </c>
+      <c r="O932" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="4" t="n">
+        <v>929</v>
+      </c>
+      <c r="B933" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C933" s="5" t="inlineStr">
+        <is>
+          <t>柏原市</t>
+        </is>
+      </c>
+      <c r="D933" s="5" t="inlineStr">
+        <is>
+          <t>関西福祉科学大学高等学校</t>
+        </is>
+      </c>
+      <c r="E933" s="6" t="inlineStr">
+        <is>
+          <t>072-976-1112</t>
+        </is>
+      </c>
+      <c r="F933" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G933" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H933" s="8" t="n"/>
+      <c r="I933" s="9" t="n"/>
+      <c r="J933" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K933" s="8" t="n"/>
+      <c r="L933" s="9" t="n"/>
+      <c r="M933" s="10" t="inlineStr">
+        <is>
+          <t>公式表記は072-976-1112〜5</t>
+        </is>
+      </c>
+      <c r="N933" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hs.fuksi-kagk-u.ac.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O933" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="4" t="n">
+        <v>930</v>
+      </c>
+      <c r="B934" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C934" s="5" t="inlineStr">
+        <is>
+          <t>箕面市</t>
+        </is>
+      </c>
+      <c r="D934" s="5" t="inlineStr">
+        <is>
+          <t>関西学院千里国際高等部</t>
+        </is>
+      </c>
+      <c r="E934" s="6" t="inlineStr">
+        <is>
+          <t>072-727-5050</t>
+        </is>
+      </c>
+      <c r="F934" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G934" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H934" s="8" t="n"/>
+      <c r="I934" s="9" t="n"/>
+      <c r="J934" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K934" s="8" t="n"/>
+      <c r="L934" s="9" t="n"/>
+      <c r="M934" s="10" t="inlineStr">
+        <is>
+          <t>072-727-5070は中等部等の別番号とみられる</t>
+        </is>
+      </c>
+      <c r="N934" s="11" t="inlineStr">
+        <is>
+          <t>https://sis.kwansei.ac.jp/contact</t>
+        </is>
+      </c>
+      <c r="O934" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="4" t="n">
+        <v>931</v>
+      </c>
+      <c r="B935" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C935" s="5" t="inlineStr">
+        <is>
+          <t>岸和田市</t>
+        </is>
+      </c>
+      <c r="D935" s="5" t="inlineStr">
+        <is>
+          <t>近畿大学泉州高等学校</t>
+        </is>
+      </c>
+      <c r="E935" s="6" t="inlineStr">
+        <is>
+          <t>072-479-1231</t>
+        </is>
+      </c>
+      <c r="F935" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G935" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H935" s="8" t="n"/>
+      <c r="I935" s="9" t="n"/>
+      <c r="J935" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K935" s="8" t="n"/>
+      <c r="L935" s="9" t="n"/>
+      <c r="M935" s="10" t="n"/>
+      <c r="N935" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kindai-sensyu.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O935" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="4" t="n">
+        <v>932</v>
+      </c>
+      <c r="B936" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C936" s="5" t="inlineStr">
+        <is>
+          <t>東大阪市</t>
+        </is>
+      </c>
+      <c r="D936" s="5" t="inlineStr">
+        <is>
+          <t>近畿大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E936" s="6" t="inlineStr">
+        <is>
+          <t>06-6722-1261</t>
+        </is>
+      </c>
+      <c r="F936" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G936" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H936" s="8" t="n"/>
+      <c r="I936" s="9" t="n"/>
+      <c r="J936" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K936" s="8" t="n"/>
+      <c r="L936" s="9" t="n"/>
+      <c r="M936" s="10" t="inlineStr">
+        <is>
+          <t>公式に「代表電話番号」と記載</t>
+        </is>
+      </c>
+      <c r="N936" s="11" t="inlineStr">
+        <is>
+          <t>https://www.jsh.kindai.ac.jp/hs/access/</t>
+        </is>
+      </c>
+      <c r="O936" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="4" t="n">
+        <v>933</v>
+      </c>
+      <c r="B937" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C937" s="5" t="inlineStr">
+        <is>
+          <t>大阪市北区</t>
+        </is>
+      </c>
+      <c r="D937" s="5" t="inlineStr">
+        <is>
+          <t>金蘭会高等学校</t>
+        </is>
+      </c>
+      <c r="E937" s="6" t="inlineStr">
+        <is>
+          <t>06-6453-0281</t>
+        </is>
+      </c>
+      <c r="F937" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G937" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H937" s="8" t="n"/>
+      <c r="I937" s="9" t="n"/>
+      <c r="J937" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K937" s="8" t="n"/>
+      <c r="L937" s="9" t="n"/>
+      <c r="M937" s="10" t="n"/>
+      <c r="N937" s="11" t="inlineStr">
+        <is>
+          <t>https://kinran.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O937" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="4" t="n">
+        <v>934</v>
+      </c>
+      <c r="B938" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C938" s="5" t="inlineStr">
+        <is>
+          <t>吹田市</t>
+        </is>
+      </c>
+      <c r="D938" s="5" t="inlineStr">
+        <is>
+          <t>金蘭千里高等学校</t>
+        </is>
+      </c>
+      <c r="E938" s="6" t="inlineStr">
+        <is>
+          <t>06-6872-0263</t>
+        </is>
+      </c>
+      <c r="F938" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G938" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H938" s="8" t="n"/>
+      <c r="I938" s="9" t="n"/>
+      <c r="J938" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K938" s="8" t="n"/>
+      <c r="L938" s="9" t="n"/>
+      <c r="M938" s="10" t="inlineStr">
+        <is>
+          <t>完全中高一貫で高校募集なしとの記載あり</t>
+        </is>
+      </c>
+      <c r="N938" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kinransenri.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O938" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="4" t="n">
+        <v>935</v>
+      </c>
+      <c r="B939" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C939" s="5" t="inlineStr">
+        <is>
+          <t>大阪市住吉区</t>
+        </is>
+      </c>
+      <c r="D939" s="5" t="inlineStr">
+        <is>
+          <t>建国高等学校</t>
+        </is>
+      </c>
+      <c r="E939" s="6" t="inlineStr">
+        <is>
+          <t>06-6691-1231</t>
+        </is>
+      </c>
+      <c r="F939" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G939" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H939" s="8" t="n"/>
+      <c r="I939" s="9" t="n"/>
+      <c r="J939" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K939" s="8" t="n"/>
+      <c r="L939" s="9" t="n"/>
+      <c r="M939" s="10" t="n"/>
+      <c r="N939" s="11" t="inlineStr">
+        <is>
+          <t>https://keonguk.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O939" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="4" t="n">
+        <v>936</v>
+      </c>
+      <c r="B940" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C940" s="5" t="inlineStr">
+        <is>
+          <t>堺市堺区</t>
+        </is>
+      </c>
+      <c r="D940" s="5" t="inlineStr">
+        <is>
+          <t>賢明学院高等学校</t>
+        </is>
+      </c>
+      <c r="E940" s="6" t="inlineStr">
+        <is>
+          <t>072-241-1679</t>
+        </is>
+      </c>
+      <c r="F940" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G940" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H940" s="8" t="n"/>
+      <c r="I940" s="9" t="n"/>
+      <c r="J940" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K940" s="8" t="n"/>
+      <c r="L940" s="9" t="n"/>
+      <c r="M940" s="10" t="inlineStr">
+        <is>
+          <t>通信制課程は072-241-2111</t>
+        </is>
+      </c>
+      <c r="N940" s="11" t="inlineStr">
+        <is>
+          <t>https://kenmei.jp/contact/inquiry/</t>
+        </is>
+      </c>
+      <c r="O940" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="4" t="n">
+        <v>937</v>
+      </c>
+      <c r="B941" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C941" s="5" t="inlineStr">
+        <is>
+          <t>大阪市天王寺区</t>
+        </is>
+      </c>
+      <c r="D941" s="5" t="inlineStr">
+        <is>
+          <t>興國高等学校</t>
+        </is>
+      </c>
+      <c r="E941" s="6" t="inlineStr">
+        <is>
+          <t>06-6779-8151</t>
+        </is>
+      </c>
+      <c r="F941" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G941" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H941" s="8" t="n"/>
+      <c r="I941" s="9" t="n"/>
+      <c r="J941" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K941" s="8" t="n"/>
+      <c r="L941" s="9" t="n"/>
+      <c r="M941" s="10" t="n"/>
+      <c r="N941" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kokoku.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O941" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="4" t="n">
+        <v>938</v>
+      </c>
+      <c r="B942" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C942" s="5" t="inlineStr">
+        <is>
+          <t>大阪市西淀川区</t>
+        </is>
+      </c>
+      <c r="D942" s="5" t="inlineStr">
+        <is>
+          <t>好文学園女子高等学校</t>
+        </is>
+      </c>
+      <c r="E942" s="6" t="inlineStr">
+        <is>
+          <t>06-6472-2281</t>
+        </is>
+      </c>
+      <c r="F942" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G942" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H942" s="8" t="n"/>
+      <c r="I942" s="9" t="n"/>
+      <c r="J942" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K942" s="8" t="n"/>
+      <c r="L942" s="9" t="n"/>
+      <c r="M942" s="10" t="n"/>
+      <c r="N942" s="11" t="inlineStr">
+        <is>
+          <t>https://koubun.ed.jp/access.html</t>
+        </is>
+      </c>
+      <c r="O942" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="4" t="n">
+        <v>939</v>
+      </c>
+      <c r="B943" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C943" s="5" t="inlineStr">
+        <is>
+          <t>茨木市</t>
+        </is>
+      </c>
+      <c r="D943" s="5" t="inlineStr">
+        <is>
+          <t>向陽台高等学校</t>
+        </is>
+      </c>
+      <c r="E943" s="6" t="inlineStr">
+        <is>
+          <t>072-643-6681</t>
+        </is>
+      </c>
+      <c r="F943" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G943" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H943" s="8" t="n"/>
+      <c r="I943" s="9" t="n"/>
+      <c r="J943" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K943" s="8" t="n"/>
+      <c r="L943" s="9" t="n"/>
+      <c r="M943" s="10" t="n"/>
+      <c r="N943" s="11" t="inlineStr">
+        <is>
+          <t>https://www.koyodai.ed.jp/form.php</t>
+        </is>
+      </c>
+      <c r="O943" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="4" t="n">
+        <v>940</v>
+      </c>
+      <c r="B944" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C944" s="5" t="inlineStr">
+        <is>
+          <t>寝屋川市</t>
+        </is>
+      </c>
+      <c r="D944" s="5" t="inlineStr">
+        <is>
+          <t>香里ヌヴェール学院高等学校</t>
+        </is>
+      </c>
+      <c r="E944" s="6" t="inlineStr">
+        <is>
+          <t>072-831-8452</t>
+        </is>
+      </c>
+      <c r="F944" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G944" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H944" s="8" t="n"/>
+      <c r="I944" s="9" t="n"/>
+      <c r="J944" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K944" s="8" t="n"/>
+      <c r="L944" s="9" t="n"/>
+      <c r="M944" s="10" t="inlineStr">
+        <is>
+          <t>一部サイトに072-833-3344の記載あり（旧番号の可能性）</t>
+        </is>
+      </c>
+      <c r="N944" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seibo.ed.jp/nevers-hs/</t>
+        </is>
+      </c>
+      <c r="O944" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="4" t="n">
+        <v>941</v>
+      </c>
+      <c r="B945" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C945" s="5" t="inlineStr">
+        <is>
+          <t>高槻市</t>
+        </is>
+      </c>
+      <c r="D945" s="5" t="inlineStr">
+        <is>
+          <t>金光大阪高等学校</t>
+        </is>
+      </c>
+      <c r="E945" s="6" t="inlineStr">
+        <is>
+          <t>072-669-5211</t>
+        </is>
+      </c>
+      <c r="F945" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G945" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H945" s="8" t="n"/>
+      <c r="I945" s="9" t="n"/>
+      <c r="J945" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K945" s="8" t="n"/>
+      <c r="L945" s="9" t="n"/>
+      <c r="M945" s="10" t="n"/>
+      <c r="N945" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kohs.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O945" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="4" t="n">
+        <v>942</v>
+      </c>
+      <c r="B946" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C946" s="5" t="inlineStr">
+        <is>
+          <t>大阪市生野区</t>
+        </is>
+      </c>
+      <c r="D946" s="5" t="inlineStr">
+        <is>
+          <t>金光藤蔭高等学校</t>
+        </is>
+      </c>
+      <c r="E946" s="6" t="inlineStr">
+        <is>
+          <t>06-6751-2461</t>
+        </is>
+      </c>
+      <c r="F946" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G946" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H946" s="8" t="n"/>
+      <c r="I946" s="9" t="n"/>
+      <c r="J946" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K946" s="8" t="n"/>
+      <c r="L946" s="9" t="n"/>
+      <c r="M946" s="10" t="inlineStr">
+        <is>
+          <t>生野キャンパス代表。香芝キャンパスは0745-79-0333</t>
+        </is>
+      </c>
+      <c r="N946" s="11" t="inlineStr">
+        <is>
+          <t>https://www.konkoutouin.ed.jp/school/access.html</t>
+        </is>
+      </c>
+      <c r="O946" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="4" t="n">
+        <v>943</v>
+      </c>
+      <c r="B947" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C947" s="5" t="inlineStr">
+        <is>
+          <t>八尾市</t>
+        </is>
+      </c>
+      <c r="D947" s="5" t="inlineStr">
+        <is>
+          <t>金光八尾高等学校</t>
+        </is>
+      </c>
+      <c r="E947" s="6" t="inlineStr">
+        <is>
+          <t>072-922-9162</t>
+        </is>
+      </c>
+      <c r="F947" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G947" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H947" s="8" t="n"/>
+      <c r="I947" s="9" t="n"/>
+      <c r="J947" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K947" s="8" t="n"/>
+      <c r="L947" s="9" t="n"/>
+      <c r="M947" s="10" t="n"/>
+      <c r="N947" s="11" t="inlineStr">
+        <is>
+          <t>https://konkoyao.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O947" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="4" t="n">
+        <v>944</v>
+      </c>
+      <c r="B948" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C948" s="5" t="inlineStr">
+        <is>
+          <t>堺市堺区</t>
+        </is>
+      </c>
+      <c r="D948" s="5" t="inlineStr">
+        <is>
+          <t>堺リベラル高等学校</t>
+        </is>
+      </c>
+      <c r="E948" s="6" t="inlineStr">
+        <is>
+          <t>072-275-7688</t>
+        </is>
+      </c>
+      <c r="F948" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G948" s="5" t="inlineStr">
+        <is>
+          <t>専門学科</t>
+        </is>
+      </c>
+      <c r="H948" s="8" t="n"/>
+      <c r="I948" s="9" t="n"/>
+      <c r="J948" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K948" s="8" t="n"/>
+      <c r="L948" s="9" t="n"/>
+      <c r="M948" s="10" t="inlineStr">
+        <is>
+          <t>入試対策室は072-226-8814</t>
+        </is>
+      </c>
+      <c r="N948" s="11" t="inlineStr">
+        <is>
+          <t>https://www.liberal.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O948" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="4" t="n">
+        <v>945</v>
+      </c>
+      <c r="B949" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C949" s="5" t="inlineStr">
+        <is>
+          <t>大東市</t>
+        </is>
+      </c>
+      <c r="D949" s="5" t="inlineStr">
+        <is>
+          <t>四條畷学園高等学校</t>
+        </is>
+      </c>
+      <c r="E949" s="6" t="inlineStr">
+        <is>
+          <t>072-876-1327</t>
+        </is>
+      </c>
+      <c r="F949" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G949" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H949" s="8" t="n"/>
+      <c r="I949" s="9" t="n"/>
+      <c r="J949" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K949" s="8" t="n"/>
+      <c r="L949" s="9" t="n"/>
+      <c r="M949" s="10" t="inlineStr">
+        <is>
+          <t>高校直通。学園代表は072-876-1321</t>
+        </is>
+      </c>
+      <c r="N949" s="11" t="inlineStr">
+        <is>
+          <t>https://hs.shijonawate-gakuen.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O949" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="4" t="n">
+        <v>946</v>
+      </c>
+      <c r="B950" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C950" s="5" t="inlineStr">
+        <is>
+          <t>大阪市天王寺区</t>
+        </is>
+      </c>
+      <c r="D950" s="5" t="inlineStr">
+        <is>
+          <t>四天王寺高等学校</t>
+        </is>
+      </c>
+      <c r="E950" s="6" t="inlineStr">
+        <is>
+          <t>06-6772-6201</t>
+        </is>
+      </c>
+      <c r="F950" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G950" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H950" s="8" t="n"/>
+      <c r="I950" s="9" t="n"/>
+      <c r="J950" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K950" s="8" t="n"/>
+      <c r="L950" s="9" t="n"/>
+      <c r="M950" s="10" t="inlineStr">
+        <is>
+          <t>公式サイトで未確認、複数の第三者サイトで一致</t>
+        </is>
+      </c>
+      <c r="N950" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/27109/ILSP0000040799_ipclm/</t>
+        </is>
+      </c>
+      <c r="O950" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="4" t="n">
+        <v>947</v>
+      </c>
+      <c r="B951" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C951" s="5" t="inlineStr">
+        <is>
+          <t>貝塚市</t>
+        </is>
+      </c>
+      <c r="D951" s="5" t="inlineStr">
+        <is>
+          <t>秋桜高等学校</t>
+        </is>
+      </c>
+      <c r="E951" s="6" t="inlineStr">
+        <is>
+          <t>072-432-6007</t>
+        </is>
+      </c>
+      <c r="F951" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G951" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H951" s="8" t="n"/>
+      <c r="I951" s="9" t="n"/>
+      <c r="J951" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K951" s="8" t="n"/>
+      <c r="L951" s="9" t="n"/>
+      <c r="M951" s="10" t="n"/>
+      <c r="N951" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shuoh.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O951" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="4" t="n">
+        <v>948</v>
+      </c>
+      <c r="B952" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C952" s="5" t="inlineStr">
+        <is>
+          <t>東大阪市</t>
+        </is>
+      </c>
+      <c r="D952" s="5" t="inlineStr">
+        <is>
+          <t>樟蔭高等学校</t>
+        </is>
+      </c>
+      <c r="E952" s="6" t="inlineStr">
+        <is>
+          <t>06-6723-8185</t>
+        </is>
+      </c>
+      <c r="F952" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G952" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H952" s="8" t="n"/>
+      <c r="I952" s="9" t="n"/>
+      <c r="J952" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K952" s="8" t="n"/>
+      <c r="L952" s="9" t="n"/>
+      <c r="M952" s="10" t="n"/>
+      <c r="N952" s="11" t="inlineStr">
+        <is>
+          <t>https://shoin-chuko.sakuraweb.com/hs/contact/</t>
+        </is>
+      </c>
+      <c r="O952" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="4" t="n">
+        <v>949</v>
+      </c>
+      <c r="B953" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C953" s="5" t="inlineStr">
+        <is>
+          <t>大阪市東住吉区</t>
+        </is>
+      </c>
+      <c r="D953" s="5" t="inlineStr">
+        <is>
+          <t>城南学園高等学校</t>
+        </is>
+      </c>
+      <c r="E953" s="6" t="inlineStr">
+        <is>
+          <t>06-6702-9784</t>
+        </is>
+      </c>
+      <c r="F953" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G953" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H953" s="8" t="n"/>
+      <c r="I953" s="9" t="n"/>
+      <c r="J953" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K953" s="8" t="n"/>
+      <c r="L953" s="9" t="n"/>
+      <c r="M953" s="10" t="inlineStr">
+        <is>
+          <t>事務局番号。職員室は06-6702-9781（第三者サイトはこちらが多い）</t>
+        </is>
+      </c>
+      <c r="N953" s="11" t="inlineStr">
+        <is>
+          <t>https://www.jonan.ac.jp/senior/access/</t>
+        </is>
+      </c>
+      <c r="O953" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="4" t="n">
+        <v>950</v>
+      </c>
+      <c r="B954" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C954" s="5" t="inlineStr">
+        <is>
+          <t>大阪市此花区</t>
+        </is>
+      </c>
+      <c r="D954" s="5" t="inlineStr">
+        <is>
+          <t>昇陽高等学校</t>
+        </is>
+      </c>
+      <c r="E954" s="6" t="inlineStr">
+        <is>
+          <t>06-6461-0091</t>
+        </is>
+      </c>
+      <c r="F954" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G954" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H954" s="8" t="n"/>
+      <c r="I954" s="9" t="n"/>
+      <c r="J954" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K954" s="8" t="n"/>
+      <c r="L954" s="9" t="n"/>
+      <c r="M954" s="10" t="n"/>
+      <c r="N954" s="11" t="inlineStr">
+        <is>
+          <t>https://www.oskshoyo.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O954" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="4" t="n">
+        <v>951</v>
+      </c>
+      <c r="B955" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C955" s="5" t="inlineStr">
+        <is>
+          <t>大阪市旭区</t>
+        </is>
+      </c>
+      <c r="D955" s="5" t="inlineStr">
+        <is>
+          <t>常翔学園高等学校</t>
+        </is>
+      </c>
+      <c r="E955" s="6" t="inlineStr">
+        <is>
+          <t>06-6954-4435</t>
+        </is>
+      </c>
+      <c r="F955" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G955" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H955" s="8" t="n"/>
+      <c r="I955" s="9" t="n"/>
+      <c r="J955" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K955" s="8" t="n"/>
+      <c r="L955" s="9" t="n"/>
+      <c r="M955" s="10" t="inlineStr">
+        <is>
+          <t>事務室番号（入試部は06-6954-4436）</t>
+        </is>
+      </c>
+      <c r="N955" s="11" t="inlineStr">
+        <is>
+          <t>https://www.highs.josho.ac.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O955" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="4" t="n">
+        <v>952</v>
+      </c>
+      <c r="B956" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C956" s="5" t="inlineStr">
+        <is>
+          <t>枚方市</t>
+        </is>
+      </c>
+      <c r="D956" s="5" t="inlineStr">
+        <is>
+          <t>常翔啓光学園高等学校</t>
+        </is>
+      </c>
+      <c r="E956" s="6" t="inlineStr">
+        <is>
+          <t>072-848-0521</t>
+        </is>
+      </c>
+      <c r="F956" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G956" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H956" s="8" t="n"/>
+      <c r="I956" s="9" t="n"/>
+      <c r="J956" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K956" s="8" t="n"/>
+      <c r="L956" s="9" t="n"/>
+      <c r="M956" s="10" t="inlineStr">
+        <is>
+          <t>公式に代表と記載。一部サイトに072-807-6632の記載あり</t>
+        </is>
+      </c>
+      <c r="N956" s="11" t="inlineStr">
+        <is>
+          <t>https://www.keiko.josho.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O956" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="4" t="n">
+        <v>953</v>
+      </c>
+      <c r="B957" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C957" s="5" t="inlineStr">
+        <is>
+          <t>大阪市中央区</t>
+        </is>
+      </c>
+      <c r="D957" s="5" t="inlineStr">
+        <is>
+          <t>城星学園高等学校</t>
+        </is>
+      </c>
+      <c r="E957" s="6" t="inlineStr">
+        <is>
+          <t>06-6941-5977</t>
+        </is>
+      </c>
+      <c r="F957" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G957" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H957" s="8" t="n"/>
+      <c r="I957" s="9" t="n"/>
+      <c r="J957" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K957" s="8" t="n"/>
+      <c r="L957" s="9" t="n"/>
+      <c r="M957" s="10" t="inlineStr">
+        <is>
+          <t>2022年4月に「ヴェリタス城星学園高等学校」へ校名変更</t>
+        </is>
+      </c>
+      <c r="N957" s="11" t="inlineStr">
+        <is>
+          <t>https://www.josei.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O957" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="4" t="n">
+        <v>954</v>
+      </c>
+      <c r="B958" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C958" s="5" t="inlineStr">
+        <is>
+          <t>堺市中区</t>
+        </is>
+      </c>
+      <c r="D958" s="5" t="inlineStr">
+        <is>
+          <t>精華高等学校</t>
+        </is>
+      </c>
+      <c r="E958" s="6" t="inlineStr">
+        <is>
+          <t>072-234-3391</t>
+        </is>
+      </c>
+      <c r="F958" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G958" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H958" s="8" t="n"/>
+      <c r="I958" s="9" t="n"/>
+      <c r="J958" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K958" s="8" t="n"/>
+      <c r="L958" s="9" t="n"/>
+      <c r="M958" s="10" t="n"/>
+      <c r="N958" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seika-h.ed.jp/inquiry/</t>
+        </is>
+      </c>
+      <c r="O958" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="4" t="n">
+        <v>955</v>
+      </c>
+      <c r="B959" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C959" s="5" t="inlineStr">
+        <is>
+          <t>河内長野市</t>
+        </is>
+      </c>
+      <c r="D959" s="5" t="inlineStr">
+        <is>
+          <t>清教学園高等学校</t>
+        </is>
+      </c>
+      <c r="E959" s="6" t="inlineStr">
+        <is>
+          <t>0721-62-6828</t>
+        </is>
+      </c>
+      <c r="F959" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G959" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H959" s="8" t="n"/>
+      <c r="I959" s="9" t="n"/>
+      <c r="J959" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K959" s="8" t="n"/>
+      <c r="L959" s="9" t="n"/>
+      <c r="M959" s="10" t="inlineStr">
+        <is>
+          <t>代表番号（入試は0721-63-8568）</t>
+        </is>
+      </c>
+      <c r="N959" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seikyo.ed.jp/guide/</t>
+        </is>
+      </c>
+      <c r="O959" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="4" t="n">
+        <v>956</v>
+      </c>
+      <c r="B960" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C960" s="5" t="inlineStr">
+        <is>
+          <t>摂津市</t>
+        </is>
+      </c>
+      <c r="D960" s="5" t="inlineStr">
+        <is>
+          <t>星翔高等学校</t>
+        </is>
+      </c>
+      <c r="E960" s="6" t="inlineStr">
+        <is>
+          <t>06-6381-0220</t>
+        </is>
+      </c>
+      <c r="F960" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G960" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H960" s="8" t="n"/>
+      <c r="I960" s="9" t="n"/>
+      <c r="J960" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K960" s="8" t="n"/>
+      <c r="L960" s="9" t="n"/>
+      <c r="M960" s="10" t="n"/>
+      <c r="N960" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osaka-seisho.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O960" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="4" t="n">
+        <v>957</v>
+      </c>
+      <c r="B961" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C961" s="5" t="inlineStr">
+        <is>
+          <t>大阪市天王寺区</t>
+        </is>
+      </c>
+      <c r="D961" s="5" t="inlineStr">
+        <is>
+          <t>清風高等学校</t>
+        </is>
+      </c>
+      <c r="E961" s="6" t="inlineStr">
+        <is>
+          <t>06-6771-5757</t>
+        </is>
+      </c>
+      <c r="F961" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G961" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H961" s="8" t="n"/>
+      <c r="I961" s="9" t="n"/>
+      <c r="J961" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K961" s="8" t="n"/>
+      <c r="L961" s="9" t="n"/>
+      <c r="M961" s="10" t="n"/>
+      <c r="N961" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seifu.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O961" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="4" t="n">
+        <v>958</v>
+      </c>
+      <c r="B962" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C962" s="5" t="inlineStr">
+        <is>
+          <t>高石市</t>
+        </is>
+      </c>
+      <c r="D962" s="5" t="inlineStr">
+        <is>
+          <t>清風南海高等学校</t>
+        </is>
+      </c>
+      <c r="E962" s="6" t="inlineStr">
+        <is>
+          <t>072-261-7761</t>
+        </is>
+      </c>
+      <c r="F962" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G962" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H962" s="8" t="n"/>
+      <c r="I962" s="9" t="n"/>
+      <c r="J962" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K962" s="8" t="n"/>
+      <c r="L962" s="9" t="n"/>
+      <c r="M962" s="10" t="inlineStr">
+        <is>
+          <t>中高共通の代表番号</t>
+        </is>
+      </c>
+      <c r="N962" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seifunankai.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O962" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="4" t="n">
+        <v>959</v>
+      </c>
+      <c r="B963" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C963" s="5" t="inlineStr">
+        <is>
+          <t>大阪市住吉区</t>
+        </is>
+      </c>
+      <c r="D963" s="5" t="inlineStr">
+        <is>
+          <t>清明学院高等学校</t>
+        </is>
+      </c>
+      <c r="E963" s="6" t="inlineStr">
+        <is>
+          <t>06-6673-8181</t>
+        </is>
+      </c>
+      <c r="F963" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G963" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H963" s="8" t="n"/>
+      <c r="I963" s="9" t="n"/>
+      <c r="J963" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K963" s="8" t="n"/>
+      <c r="L963" s="9" t="n"/>
+      <c r="M963" s="10" t="n"/>
+      <c r="N963" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seimei.ed.jp/about/access.html</t>
+        </is>
+      </c>
+      <c r="O963" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="4" t="n">
+        <v>960</v>
+      </c>
+      <c r="B964" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C964" s="5" t="inlineStr">
+        <is>
+          <t>池田市</t>
+        </is>
+      </c>
+      <c r="D964" s="5" t="inlineStr">
+        <is>
+          <t>宣真高等学校</t>
+        </is>
+      </c>
+      <c r="E964" s="6" t="inlineStr">
+        <is>
+          <t>072-761-8801</t>
+        </is>
+      </c>
+      <c r="F964" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G964" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H964" s="8" t="n"/>
+      <c r="I964" s="9" t="n"/>
+      <c r="J964" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K964" s="8" t="n"/>
+      <c r="L964" s="9" t="n"/>
+      <c r="M964" s="10" t="inlineStr">
+        <is>
+          <t>代表番号（入試広報部直通は072-760-3020）</t>
+        </is>
+      </c>
+      <c r="N964" s="11" t="inlineStr">
+        <is>
+          <t>https://senshin-gakuen.jp/access/</t>
+        </is>
+      </c>
+      <c r="O964" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="4" t="n">
+        <v>961</v>
+      </c>
+      <c r="B965" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C965" s="5" t="inlineStr">
+        <is>
+          <t>大阪市中央区</t>
+        </is>
+      </c>
+      <c r="D965" s="5" t="inlineStr">
+        <is>
+          <t>相愛高等学校</t>
+        </is>
+      </c>
+      <c r="E965" s="6" t="inlineStr">
+        <is>
+          <t>06-6262-0621</t>
+        </is>
+      </c>
+      <c r="F965" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G965" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H965" s="8" t="n"/>
+      <c r="I965" s="9" t="n"/>
+      <c r="J965" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K965" s="8" t="n"/>
+      <c r="L965" s="9" t="n"/>
+      <c r="M965" s="10" t="n"/>
+      <c r="N965" s="11" t="inlineStr">
+        <is>
+          <t>https://www.soai.ed.jp/school/access.html</t>
+        </is>
+      </c>
+      <c r="O965" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="4" t="n">
+        <v>962</v>
+      </c>
+      <c r="B966" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C966" s="5" t="inlineStr">
+        <is>
+          <t>大東市</t>
+        </is>
+      </c>
+      <c r="D966" s="5" t="inlineStr">
+        <is>
+          <t>太成学院大学高等学校</t>
+        </is>
+      </c>
+      <c r="E966" s="6" t="inlineStr">
+        <is>
+          <t>072-871-1921</t>
+        </is>
+      </c>
+      <c r="F966" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G966" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H966" s="8" t="n"/>
+      <c r="I966" s="9" t="n"/>
+      <c r="J966" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K966" s="8" t="n"/>
+      <c r="L966" s="9" t="n"/>
+      <c r="M966" s="10" t="inlineStr">
+        <is>
+          <t>大東市公式サイトとも一致</t>
+        </is>
+      </c>
+      <c r="N966" s="11" t="inlineStr">
+        <is>
+          <t>https://www.taisei-hs.ac.jp/hs/</t>
+        </is>
+      </c>
+      <c r="O966" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="4" t="n">
+        <v>963</v>
+      </c>
+      <c r="B967" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C967" s="5" t="inlineStr">
+        <is>
+          <t>高槻市</t>
+        </is>
+      </c>
+      <c r="D967" s="5" t="inlineStr">
+        <is>
+          <t>高槻高等学校</t>
+        </is>
+      </c>
+      <c r="E967" s="6" t="inlineStr">
+        <is>
+          <t>072-671-0001</t>
+        </is>
+      </c>
+      <c r="F967" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G967" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H967" s="8" t="n"/>
+      <c r="I967" s="9" t="n"/>
+      <c r="J967" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K967" s="8" t="n"/>
+      <c r="L967" s="9" t="n"/>
+      <c r="M967" s="10" t="inlineStr">
+        <is>
+          <t>公式ページで番号未確認。マピオン・学校情報サイトで一致</t>
+        </is>
+      </c>
+      <c r="N967" s="11" t="inlineStr">
+        <is>
+          <t>https://www.takatsuki.ed.jp/access</t>
+        </is>
+      </c>
+      <c r="O967" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="4" t="n">
+        <v>964</v>
+      </c>
+      <c r="B968" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C968" s="5" t="inlineStr">
+        <is>
+          <t>豊中市</t>
+        </is>
+      </c>
+      <c r="D968" s="5" t="inlineStr">
+        <is>
+          <t>大商学園高等学校</t>
+        </is>
+      </c>
+      <c r="E968" s="6" t="inlineStr">
+        <is>
+          <t>06-6862-5223</t>
+        </is>
+      </c>
+      <c r="F968" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G968" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H968" s="8" t="n"/>
+      <c r="I968" s="9" t="n"/>
+      <c r="J968" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K968" s="8" t="n"/>
+      <c r="L968" s="9" t="n"/>
+      <c r="M968" s="10" t="n"/>
+      <c r="N968" s="11" t="inlineStr">
+        <is>
+          <t>https://www.daisho.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O968" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="4" t="n">
+        <v>965</v>
+      </c>
+      <c r="B969" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C969" s="5" t="inlineStr">
+        <is>
+          <t>堺市南区</t>
+        </is>
+      </c>
+      <c r="D969" s="5" t="inlineStr">
+        <is>
+          <t>帝塚山学院泉ヶ丘高等学校</t>
+        </is>
+      </c>
+      <c r="E969" s="6" t="inlineStr">
+        <is>
+          <t>072-293-1221</t>
+        </is>
+      </c>
+      <c r="F969" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G969" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H969" s="8" t="n"/>
+      <c r="I969" s="9" t="n"/>
+      <c r="J969" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K969" s="8" t="n"/>
+      <c r="L969" s="9" t="n"/>
+      <c r="M969" s="10" t="n"/>
+      <c r="N969" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tezuka-i-h.jp/</t>
+        </is>
+      </c>
+      <c r="O969" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="4" t="n">
+        <v>966</v>
+      </c>
+      <c r="B970" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C970" s="5" t="inlineStr">
+        <is>
+          <t>大阪市住吉区</t>
+        </is>
+      </c>
+      <c r="D970" s="5" t="inlineStr">
+        <is>
+          <t>帝塚山学院高等学校</t>
+        </is>
+      </c>
+      <c r="E970" s="6" t="inlineStr">
+        <is>
+          <t>06-6672-1151</t>
+        </is>
+      </c>
+      <c r="F970" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G970" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H970" s="8" t="n"/>
+      <c r="I970" s="9" t="n"/>
+      <c r="J970" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K970" s="8" t="n"/>
+      <c r="L970" s="9" t="n"/>
+      <c r="M970" s="10" t="inlineStr">
+        <is>
+          <t>学校法人の公式アクセスページに記載</t>
+        </is>
+      </c>
+      <c r="N970" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tezukayama.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O970" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="4" t="n">
+        <v>967</v>
+      </c>
+      <c r="B971" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C971" s="5" t="inlineStr">
+        <is>
+          <t>大阪市平野区</t>
+        </is>
+      </c>
+      <c r="D971" s="5" t="inlineStr">
+        <is>
+          <t>天王寺学館高等学校</t>
+        </is>
+      </c>
+      <c r="E971" s="6" t="inlineStr">
+        <is>
+          <t>06-6795-1860</t>
+        </is>
+      </c>
+      <c r="F971" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G971" s="5" t="inlineStr">
+        <is>
+          <t>総合学科</t>
+        </is>
+      </c>
+      <c r="H971" s="8" t="n"/>
+      <c r="I971" s="9" t="n"/>
+      <c r="J971" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K971" s="8" t="n"/>
+      <c r="L971" s="9" t="n"/>
+      <c r="M971" s="10" t="inlineStr">
+        <is>
+          <t>通信制。2010年に平野区へ移転済み（旧番号06-6621-1860は古い情報）</t>
+        </is>
+      </c>
+      <c r="N971" s="11" t="inlineStr">
+        <is>
+          <t>https://tg-group.ac.jp/tgkoko/i/ipc/contact/</t>
+        </is>
+      </c>
+      <c r="O971" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="4" t="n">
+        <v>968</v>
+      </c>
+      <c r="B972" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C972" s="5" t="inlineStr">
+        <is>
+          <t>枚方市</t>
+        </is>
+      </c>
+      <c r="D972" s="5" t="inlineStr">
+        <is>
+          <t>東海大学付属大阪仰星高等学校</t>
+        </is>
+      </c>
+      <c r="E972" s="6" t="inlineStr">
+        <is>
+          <t>072-849-7211</t>
+        </is>
+      </c>
+      <c r="F972" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G972" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H972" s="8" t="n"/>
+      <c r="I972" s="9" t="n"/>
+      <c r="J972" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K972" s="8" t="n"/>
+      <c r="L972" s="9" t="n"/>
+      <c r="M972" s="10" t="n"/>
+      <c r="N972" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tokai-gyosei.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O972" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="4" t="n">
+        <v>969</v>
+      </c>
+      <c r="B973" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C973" s="5" t="inlineStr">
+        <is>
+          <t>寝屋川市</t>
+        </is>
+      </c>
+      <c r="D973" s="5" t="inlineStr">
+        <is>
+          <t>同志社香里高等学校</t>
+        </is>
+      </c>
+      <c r="E973" s="6" t="inlineStr">
+        <is>
+          <t>072-831-0285</t>
+        </is>
+      </c>
+      <c r="F973" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G973" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H973" s="8" t="n"/>
+      <c r="I973" s="9" t="n"/>
+      <c r="J973" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K973" s="8" t="n"/>
+      <c r="L973" s="9" t="n"/>
+      <c r="M973" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号。寝屋川市サイトとも一致</t>
+        </is>
+      </c>
+      <c r="N973" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kori.doshisha.ac.jp/agreement/</t>
+        </is>
+      </c>
+      <c r="O973" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="4" t="n">
+        <v>970</v>
+      </c>
+      <c r="B974" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C974" s="5" t="inlineStr">
+        <is>
+          <t>枚方市</t>
+        </is>
+      </c>
+      <c r="D974" s="5" t="inlineStr">
+        <is>
+          <t>長尾谷高等学校</t>
+        </is>
+      </c>
+      <c r="E974" s="6" t="inlineStr">
+        <is>
+          <t>072-850-9111</t>
+        </is>
+      </c>
+      <c r="F974" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G974" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H974" s="8" t="n"/>
+      <c r="I974" s="9" t="n"/>
+      <c r="J974" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K974" s="8" t="n"/>
+      <c r="L974" s="9" t="n"/>
+      <c r="M974" s="10" t="inlineStr">
+        <is>
+          <t>通信制・枚方本校（フリーダイヤル0120-750-150）</t>
+        </is>
+      </c>
+      <c r="N974" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nagaodani.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O974" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="4" t="n">
+        <v>971</v>
+      </c>
+      <c r="B975" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C975" s="5" t="inlineStr">
+        <is>
+          <t>大阪市住吉区</t>
+        </is>
+      </c>
+      <c r="D975" s="5" t="inlineStr">
+        <is>
+          <t>浪速高等学校</t>
+        </is>
+      </c>
+      <c r="E975" s="6" t="inlineStr">
+        <is>
+          <t>06-6693-4031</t>
+        </is>
+      </c>
+      <c r="F975" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G975" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H975" s="8" t="n"/>
+      <c r="I975" s="9" t="n"/>
+      <c r="J975" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K975" s="8" t="n"/>
+      <c r="L975" s="9" t="n"/>
+      <c r="M975" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。入試広報部は06-6693-0965</t>
+        </is>
+      </c>
+      <c r="N975" s="11" t="inlineStr">
+        <is>
+          <t>https://www.naniwa.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O975" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="4" t="n">
+        <v>972</v>
+      </c>
+      <c r="B976" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C976" s="5" t="inlineStr">
+        <is>
+          <t>高石市</t>
+        </is>
+      </c>
+      <c r="D976" s="5" t="inlineStr">
+        <is>
+          <t>羽衣学園高等学校</t>
+        </is>
+      </c>
+      <c r="E976" s="6" t="inlineStr">
+        <is>
+          <t>072-265-7561</t>
+        </is>
+      </c>
+      <c r="F976" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G976" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H976" s="8" t="n"/>
+      <c r="I976" s="9" t="n"/>
+      <c r="J976" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K976" s="8" t="n"/>
+      <c r="L976" s="9" t="n"/>
+      <c r="M976" s="10" t="n"/>
+      <c r="N976" s="11" t="inlineStr">
+        <is>
+          <t>https://hagoromogakuen.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O976" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="4" t="n">
+        <v>973</v>
+      </c>
+      <c r="B977" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C977" s="5" t="inlineStr">
+        <is>
+          <t>富田林市</t>
+        </is>
+      </c>
+      <c r="D977" s="5" t="inlineStr">
+        <is>
+          <t>初芝富田林高等学校</t>
+        </is>
+      </c>
+      <c r="E977" s="6" t="inlineStr">
+        <is>
+          <t>0721-34-1010</t>
+        </is>
+      </c>
+      <c r="F977" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G977" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H977" s="8" t="n"/>
+      <c r="I977" s="9" t="n"/>
+      <c r="J977" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K977" s="8" t="n"/>
+      <c r="L977" s="9" t="n"/>
+      <c r="M977" s="10" t="inlineStr">
+        <is>
+          <t>2026年4月に「利晶学園高等学校」へ校名変更</t>
+        </is>
+      </c>
+      <c r="N977" s="11" t="inlineStr">
+        <is>
+          <t>https://www.rishogakuen.ed.jp/tondabayashi/info/inquiry.html</t>
+        </is>
+      </c>
+      <c r="O977" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="4" t="n">
+        <v>974</v>
+      </c>
+      <c r="B978" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C978" s="5" t="inlineStr">
+        <is>
+          <t>松原市</t>
+        </is>
+      </c>
+      <c r="D978" s="5" t="inlineStr">
+        <is>
+          <t>阪南大学高等学校</t>
+        </is>
+      </c>
+      <c r="E978" s="6" t="inlineStr">
+        <is>
+          <t>072-332-1221</t>
+        </is>
+      </c>
+      <c r="F978" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G978" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H978" s="8" t="n"/>
+      <c r="I978" s="9" t="n"/>
+      <c r="J978" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K978" s="8" t="n"/>
+      <c r="L978" s="9" t="n"/>
+      <c r="M978" s="10" t="n"/>
+      <c r="N978" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hdk.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O978" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="4" t="n">
+        <v>975</v>
+      </c>
+      <c r="B979" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C979" s="5" t="inlineStr">
+        <is>
+          <t>豊中市</t>
+        </is>
+      </c>
+      <c r="D979" s="5" t="inlineStr">
+        <is>
+          <t>梅花高等学校</t>
+        </is>
+      </c>
+      <c r="E979" s="6" t="inlineStr">
+        <is>
+          <t>06-6852-0001</t>
+        </is>
+      </c>
+      <c r="F979" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G979" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H979" s="8" t="n"/>
+      <c r="I979" s="9" t="n"/>
+      <c r="J979" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K979" s="8" t="n"/>
+      <c r="L979" s="9" t="n"/>
+      <c r="M979" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。入試広報部直通は06-6852-0002</t>
+        </is>
+      </c>
+      <c r="N979" s="11" t="inlineStr">
+        <is>
+          <t>https://www.baika-jh.ed.jp/guide/access/</t>
+        </is>
+      </c>
+      <c r="O979" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="4" t="n">
+        <v>976</v>
+      </c>
+      <c r="B980" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C980" s="5" t="inlineStr">
+        <is>
+          <t>柏原市</t>
+        </is>
+      </c>
+      <c r="D980" s="5" t="inlineStr">
+        <is>
+          <t>東大阪大学柏原高等学校</t>
+        </is>
+      </c>
+      <c r="E980" s="6" t="inlineStr">
+        <is>
+          <t>072-972-1565</t>
+        </is>
+      </c>
+      <c r="F980" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G980" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H980" s="8" t="n"/>
+      <c r="I980" s="9" t="n"/>
+      <c r="J980" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K980" s="8" t="n"/>
+      <c r="L980" s="9" t="n"/>
+      <c r="M980" s="10" t="inlineStr">
+        <is>
+          <t>マピオン等の複数サイトで一致。公式サイトでは未確認</t>
+        </is>
+      </c>
+      <c r="N980" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gakkou.net/kou/view/index_304261.html</t>
+        </is>
+      </c>
+      <c r="O980" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="4" t="n">
+        <v>977</v>
+      </c>
+      <c r="B981" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C981" s="5" t="inlineStr">
+        <is>
+          <t>東大阪市</t>
+        </is>
+      </c>
+      <c r="D981" s="5" t="inlineStr">
+        <is>
+          <t>東大阪大学敬愛高等学校</t>
+        </is>
+      </c>
+      <c r="E981" s="6" t="inlineStr">
+        <is>
+          <t>06-6782-2881</t>
+        </is>
+      </c>
+      <c r="F981" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G981" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H981" s="8" t="n"/>
+      <c r="I981" s="9" t="n"/>
+      <c r="J981" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K981" s="8" t="n"/>
+      <c r="L981" s="9" t="n"/>
+      <c r="M981" s="10" t="n"/>
+      <c r="N981" s="11" t="inlineStr">
+        <is>
+          <t>https://www.higashiosaka-hs.ac.jp/keiai/</t>
+        </is>
+      </c>
+      <c r="O981" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="4" t="n">
+        <v>978</v>
+      </c>
+      <c r="B982" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C982" s="5" t="inlineStr">
+        <is>
+          <t>堺市南区</t>
+        </is>
+      </c>
+      <c r="D982" s="5" t="inlineStr">
+        <is>
+          <t>東大谷高等学校</t>
+        </is>
+      </c>
+      <c r="E982" s="6" t="inlineStr">
+        <is>
+          <t>072-289-8069</t>
+        </is>
+      </c>
+      <c r="F982" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G982" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H982" s="8" t="n"/>
+      <c r="I982" s="9" t="n"/>
+      <c r="J982" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K982" s="8" t="n"/>
+      <c r="L982" s="9" t="n"/>
+      <c r="M982" s="10" t="inlineStr">
+        <is>
+          <t>2013年に堺市南区三原台へ移転済み。現所在地の番号</t>
+        </is>
+      </c>
+      <c r="N982" s="11" t="inlineStr">
+        <is>
+          <t>https://higashiohtani.ac.jp/contact</t>
+        </is>
+      </c>
+      <c r="O982" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="4" t="n">
+        <v>979</v>
+      </c>
+      <c r="B983" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C983" s="5" t="inlineStr">
+        <is>
+          <t>富田林市</t>
+        </is>
+      </c>
+      <c r="D983" s="5" t="inlineStr">
+        <is>
+          <t>PL学園高等学校</t>
+        </is>
+      </c>
+      <c r="E983" s="6" t="inlineStr">
+        <is>
+          <t>0721-24-5132</t>
+        </is>
+      </c>
+      <c r="F983" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G983" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H983" s="8" t="n"/>
+      <c r="I983" s="9" t="n"/>
+      <c r="J983" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K983" s="8" t="n"/>
+      <c r="L983" s="9" t="n"/>
+      <c r="M983" s="10" t="inlineStr">
+        <is>
+          <t>富田林市の公式サイトでも番号が一致</t>
+        </is>
+      </c>
+      <c r="N983" s="11" t="inlineStr">
+        <is>
+          <t>https://www.pl-gakuen.ac.jp/schoolguide/</t>
+        </is>
+      </c>
+      <c r="O983" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="4" t="n">
+        <v>980</v>
+      </c>
+      <c r="B984" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C984" s="5" t="inlineStr">
+        <is>
+          <t>大阪市生野区</t>
+        </is>
+      </c>
+      <c r="D984" s="5" t="inlineStr">
+        <is>
+          <t>プール学院高等学校</t>
+        </is>
+      </c>
+      <c r="E984" s="6" t="inlineStr">
+        <is>
+          <t>06-6741-7005</t>
+        </is>
+      </c>
+      <c r="F984" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G984" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H984" s="8" t="n"/>
+      <c r="I984" s="9" t="n"/>
+      <c r="J984" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K984" s="8" t="n"/>
+      <c r="L984" s="9" t="n"/>
+      <c r="M984" s="10" t="n"/>
+      <c r="N984" s="11" t="inlineStr">
+        <is>
+          <t>https://poole.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O984" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="4" t="n">
+        <v>981</v>
+      </c>
+      <c r="B985" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C985" s="5" t="inlineStr">
+        <is>
+          <t>箕面市</t>
+        </is>
+      </c>
+      <c r="D985" s="5" t="inlineStr">
+        <is>
+          <t>箕面学園高等学校</t>
+        </is>
+      </c>
+      <c r="E985" s="6" t="inlineStr">
+        <is>
+          <t>072-723-6551</t>
+        </is>
+      </c>
+      <c r="F985" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G985" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H985" s="8" t="n"/>
+      <c r="I985" s="9" t="n"/>
+      <c r="J985" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K985" s="8" t="n"/>
+      <c r="L985" s="9" t="n"/>
+      <c r="M985" s="10" t="inlineStr">
+        <is>
+          <t>代表番号</t>
+        </is>
+      </c>
+      <c r="N985" s="11" t="inlineStr">
+        <is>
+          <t>https://minohgakuen.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O985" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="4" t="n">
+        <v>982</v>
+      </c>
+      <c r="B986" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C986" s="5" t="inlineStr">
+        <is>
+          <t>豊中市</t>
+        </is>
+      </c>
+      <c r="D986" s="5" t="inlineStr">
+        <is>
+          <t>箕面自由学園高等学校</t>
+        </is>
+      </c>
+      <c r="E986" s="6" t="inlineStr">
+        <is>
+          <t>06-6852-8110</t>
+        </is>
+      </c>
+      <c r="F986" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G986" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H986" s="8" t="n"/>
+      <c r="I986" s="9" t="n"/>
+      <c r="J986" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K986" s="8" t="n"/>
+      <c r="L986" s="9" t="n"/>
+      <c r="M986" s="10" t="inlineStr">
+        <is>
+          <t>NAVITIMEには別番号（06-6852-7595）の記載あるが公式と不一致</t>
+        </is>
+      </c>
+      <c r="N986" s="11" t="inlineStr">
+        <is>
+          <t>https://mino-jiyu.ed.jp/hs/</t>
+        </is>
+      </c>
+      <c r="O986" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="4" t="n">
+        <v>983</v>
+      </c>
+      <c r="B987" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C987" s="5" t="inlineStr">
+        <is>
+          <t>大阪市阿倍野区</t>
+        </is>
+      </c>
+      <c r="D987" s="5" t="inlineStr">
+        <is>
+          <t>明浄学院高等学校</t>
+        </is>
+      </c>
+      <c r="E987" s="6" t="inlineStr">
+        <is>
+          <t>06-6623-0016</t>
+        </is>
+      </c>
+      <c r="F987" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G987" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H987" s="8" t="n"/>
+      <c r="I987" s="9" t="n"/>
+      <c r="J987" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K987" s="8" t="n"/>
+      <c r="L987" s="9" t="n"/>
+      <c r="M987" s="10" t="inlineStr">
+        <is>
+          <t>文科省ユネスコスクールのページ等の複数サイトで一致。2024年に藍野高校と統合し共学化</t>
+        </is>
+      </c>
+      <c r="N987" s="11" t="inlineStr">
+        <is>
+          <t>https://www.unesco-school.mext.go.jp/schools/list/meijo-gakuin-high-school/</t>
+        </is>
+      </c>
+      <c r="O987" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="4" t="n">
+        <v>984</v>
+      </c>
+      <c r="B988" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C988" s="5" t="inlineStr">
+        <is>
+          <t>大阪市天王寺区</t>
+        </is>
+      </c>
+      <c r="D988" s="5" t="inlineStr">
+        <is>
+          <t>明星高等学校（大阪府）</t>
+        </is>
+      </c>
+      <c r="E988" s="6" t="inlineStr">
+        <is>
+          <t>06-6761-5606</t>
+        </is>
+      </c>
+      <c r="F988" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G988" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H988" s="8" t="n"/>
+      <c r="I988" s="9" t="n"/>
+      <c r="J988" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K988" s="8" t="n"/>
+      <c r="L988" s="9" t="n"/>
+      <c r="M988" s="10" t="n"/>
+      <c r="N988" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meisei.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O988" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="4" t="n">
+        <v>985</v>
+      </c>
+      <c r="B989" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C989" s="5" t="inlineStr">
+        <is>
+          <t>大阪市阿倍野区</t>
+        </is>
+      </c>
+      <c r="D989" s="5" t="inlineStr">
+        <is>
+          <t>桃山学院高等学校</t>
+        </is>
+      </c>
+      <c r="E989" s="6" t="inlineStr">
+        <is>
+          <t>06-6621-1181</t>
+        </is>
+      </c>
+      <c r="F989" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G989" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H989" s="8" t="n"/>
+      <c r="I989" s="9" t="n"/>
+      <c r="J989" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K989" s="8" t="n"/>
+      <c r="L989" s="9" t="n"/>
+      <c r="M989" s="10" t="inlineStr">
+        <is>
+          <t>代表番号</t>
+        </is>
+      </c>
+      <c r="N989" s="11" t="inlineStr">
+        <is>
+          <t>https://www.momoyamagakuin-h.ed.jp/about/access/</t>
+        </is>
+      </c>
+      <c r="O989" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="4" t="n">
+        <v>986</v>
+      </c>
+      <c r="B990" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C990" s="5" t="inlineStr">
+        <is>
+          <t>堺市西区</t>
+        </is>
+      </c>
+      <c r="D990" s="5" t="inlineStr">
+        <is>
+          <t>八洲学園高等学校</t>
+        </is>
+      </c>
+      <c r="E990" s="6" t="inlineStr">
+        <is>
+          <t>072-262-8281</t>
+        </is>
+      </c>
+      <c r="F990" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G990" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H990" s="8" t="n"/>
+      <c r="I990" s="9" t="n"/>
+      <c r="J990" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K990" s="8" t="n"/>
+      <c r="L990" s="9" t="n"/>
+      <c r="M990" s="10" t="inlineStr">
+        <is>
+          <t>通信制・堺本校。堺本校二号館は072-262-5849</t>
+        </is>
+      </c>
+      <c r="N990" s="11" t="inlineStr">
+        <is>
+          <t>https://yashima.ac.jp/?page_id=167</t>
+        </is>
+      </c>
+      <c r="O990" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="4" t="n">
+        <v>987</v>
+      </c>
+      <c r="B991" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C991" s="5" t="inlineStr">
+        <is>
+          <t>堺市東区</t>
+        </is>
+      </c>
+      <c r="D991" s="5" t="inlineStr">
+        <is>
+          <t>利晶学園大阪立命館高等学校</t>
+        </is>
+      </c>
+      <c r="E991" s="6" t="inlineStr">
+        <is>
+          <t>072-235-3900</t>
+        </is>
+      </c>
+      <c r="F991" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G991" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H991" s="8" t="n"/>
+      <c r="I991" s="9" t="n"/>
+      <c r="J991" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K991" s="8" t="n"/>
+      <c r="L991" s="9" t="n"/>
+      <c r="M991" s="10" t="inlineStr">
+        <is>
+          <t>高校の番号。中学校は072-235-6400（旧校名は初芝立命館）</t>
+        </is>
+      </c>
+      <c r="N991" s="11" t="inlineStr">
+        <is>
+          <t>https://www.rishogakuen.ed.jp/ritsumeikan/info/information.html</t>
+        </is>
+      </c>
+      <c r="O991" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="4" t="n">
+        <v>988</v>
+      </c>
+      <c r="B992" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C992" s="5" t="inlineStr">
+        <is>
+          <t>豊中市</t>
+        </is>
+      </c>
+      <c r="D992" s="5" t="inlineStr">
+        <is>
+          <t>履正社高等学校</t>
+        </is>
+      </c>
+      <c r="E992" s="6" t="inlineStr">
+        <is>
+          <t>06-6864-0456</t>
+        </is>
+      </c>
+      <c r="F992" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G992" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H992" s="8" t="n"/>
+      <c r="I992" s="9" t="n"/>
+      <c r="J992" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K992" s="8" t="n"/>
+      <c r="L992" s="9" t="n"/>
+      <c r="M992" s="10" t="inlineStr">
+        <is>
+          <t>代表番号</t>
+        </is>
+      </c>
+      <c r="N992" s="11" t="inlineStr">
+        <is>
+          <t>https://riseisha.ed.jp/info/access/</t>
+        </is>
+      </c>
+      <c r="O992" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="4" t="n">
+        <v>989</v>
+      </c>
+      <c r="B993" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C993" s="5" t="inlineStr">
+        <is>
+          <t>大阪市天王寺区</t>
+        </is>
+      </c>
+      <c r="D993" s="5" t="inlineStr">
+        <is>
+          <t>YMCA学院高等学校</t>
+        </is>
+      </c>
+      <c r="E993" s="6" t="inlineStr">
+        <is>
+          <t>06-6779-5690</t>
+        </is>
+      </c>
+      <c r="F993" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G993" s="5" t="inlineStr">
+        <is>
+          <t>総合学科</t>
+        </is>
+      </c>
+      <c r="H993" s="8" t="n"/>
+      <c r="I993" s="9" t="n"/>
+      <c r="J993" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K993" s="8" t="n"/>
+      <c r="L993" s="9" t="n"/>
+      <c r="M993" s="10" t="inlineStr">
+        <is>
+          <t>通信制・単位制</t>
+        </is>
+      </c>
+      <c r="N993" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ymcagakuin.ac.jp/introduction/access.html</t>
+        </is>
+      </c>
+      <c r="O993" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="4" t="n">
+        <v>990</v>
+      </c>
+      <c r="B994" s="5" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="C994" s="5" t="inlineStr">
+        <is>
+          <t>茨木市</t>
+        </is>
+      </c>
+      <c r="D994" s="5" t="inlineStr">
+        <is>
+          <t>早稲田大阪高等学校</t>
+        </is>
+      </c>
+      <c r="E994" s="6" t="inlineStr">
+        <is>
+          <t>072-643-6363</t>
+        </is>
+      </c>
+      <c r="F994" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G994" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H994" s="8" t="n"/>
+      <c r="I994" s="9" t="n"/>
+      <c r="J994" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K994" s="8" t="n"/>
+      <c r="L994" s="9" t="n"/>
+      <c r="M994" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。入試広報部は072-640-5570、学校法人は072-643-6361</t>
+        </is>
+      </c>
+      <c r="N994" s="11" t="inlineStr">
+        <is>
+          <t>https://waseda-osaka.jp/</t>
+        </is>
+      </c>
+      <c r="O994" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O894"/>
-  <conditionalFormatting sqref="A5:O894">
+  <autoFilter ref="A4:O994"/>
+  <conditionalFormatting sqref="A5:O994">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -53153,10 +58897,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J894" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J994" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H894 K5:K894" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H994 K5:K994" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -54051,6 +59795,106 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O892" r:id="rId888"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O893" r:id="rId889"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O894" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O895" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O896" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O897" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O898" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O899" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O900" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O901" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O902" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O903" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O904" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O905" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O906" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O907" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O908" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O909" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O910" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O911" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O912" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O913" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O914" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O915" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O916" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O917" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O918" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O919" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O920" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O921" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O922" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O923" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O924" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O925" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O926" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O927" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O928" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O929" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O930" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O931" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O932" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O933" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O934" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O935" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O936" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O937" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O938" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O939" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O940" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O941" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O942" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O943" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O944" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O945" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O946" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O947" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O948" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O949" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O950" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O951" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O952" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O953" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O954" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O955" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O956" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O957" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O958" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O959" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O960" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O961" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O962" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O963" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O964" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O965" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O966" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O967" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O968" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O969" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O970" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O971" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O972" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O973" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O974" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O975" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O976" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O977" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O978" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O979" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O980" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O981" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O982" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O983" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O984" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O985" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O986" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O987" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O988" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O989" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O990" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O991" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O992" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O993" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O994" r:id="rId990"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -54063,7 +59907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -54150,43 +59994,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A4,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A4,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$894,A4,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A4,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$994,A4,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A4,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A4,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54197,43 +60041,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A5,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A5,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$894,A5,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A5,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$994,A5,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A5,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A5,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54244,43 +60088,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A6,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A6,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$894,A6,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A6,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$994,A6,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A6,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A6,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54291,43 +60135,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A7,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A7,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$894,A7,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A7,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$994,A7,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A7,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A7,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54338,43 +60182,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A8,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A8,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$894,A8,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A8,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$994,A8,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A8,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A8,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54385,43 +60229,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A9,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A9,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$894,A9,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A9,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$994,A9,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A9,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A9,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54432,43 +60276,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A10,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A10,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$894,A10,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A10,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$994,A10,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A10,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A10,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54479,43 +60323,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A11,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A11,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$894,A11,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A11,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$994,A11,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A11,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A11,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54526,43 +60370,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A12,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A12,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$894,A12,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A12,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$994,A12,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A12,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A12,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54573,43 +60417,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A13,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A13,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$894,A13,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A13,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$994,A13,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A13,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A13,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54620,43 +60464,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A14,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A14,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$894,A14,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A14,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$994,A14,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A14,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A14,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54667,43 +60511,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A15,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A15,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$894,A15,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A15,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$994,A15,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A15,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A15,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54714,43 +60558,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A16,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A16,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$894,A16,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A16,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$994,A16,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A16,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A16,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54761,43 +60605,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A17,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A17,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$894,A17,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A17,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$994,A17,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A17,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A17,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54808,43 +60652,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A18,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A18,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$894,A18,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A18,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$994,A18,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A18,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A18,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54855,43 +60699,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A19,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A19,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$894,A19,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A19,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$994,A19,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A19,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A19,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54902,43 +60746,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A20,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A20,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$894,A20,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A20,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$994,A20,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A20,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A20,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54949,43 +60793,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A21,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A21,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$894,A21,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A21,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$994,A21,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A21,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A21,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -54996,43 +60840,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A22,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A22,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$894,A22,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A22,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$994,A22,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A22,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A22,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -55043,43 +60887,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A23,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A23,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$894,A23,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A23,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$994,A23,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A23,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A23,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -55090,43 +60934,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A24,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A24,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$894,A24,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A24,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$994,A24,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A24,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A24,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -55137,43 +60981,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A25,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A25,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$894,A25,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A25,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$994,A25,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A25,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A25,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -55184,43 +61028,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A26,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A26,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$894,A26,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A26,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$994,A26,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A26,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A26,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -55231,43 +61075,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A27,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A27,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$894,A27,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A27,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$994,A27,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A27,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A27,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -55278,43 +61122,43 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A28,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A28,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$894,A28,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A28,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$994,A28,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A28,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A28,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -55325,90 +61169,137 @@
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$894,A29)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,A29,'架電リスト'!$E$5:$E$894,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A29,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$894,A29,'架電リスト'!$J$5:$J$894,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$894,A29,'架電リスト'!$J$5:$J$894,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$994,A29,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A29,'架電リスト'!$J$5:$J$994,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$894,$A29,'架電リスト'!$J$5:$J$894,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>大阪府</t>
+        </is>
+      </c>
+      <c r="B30" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$994,A30)</f>
+        <v/>
+      </c>
+      <c r="C30" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A30,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D30" s="16">
+        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$994,A30,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A30,'架電リスト'!$J$5:$J$994,"")</f>
+        <v/>
+      </c>
+      <c r="E30" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F30" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G30" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H30" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I30" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J30" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <v/>
+      </c>
+      <c r="K30" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B30" s="17">
-        <f>SUM(B4:B29)</f>
+      <c r="B31" s="17">
+        <f>SUM(B4:B30)</f>
         <v/>
       </c>
-      <c r="C30" s="17">
-        <f>SUM(C4:C29)</f>
+      <c r="C31" s="17">
+        <f>SUM(C4:C30)</f>
         <v/>
       </c>
-      <c r="D30" s="17">
-        <f>SUM(D4:D29)</f>
+      <c r="D31" s="17">
+        <f>SUM(D4:D30)</f>
         <v/>
       </c>
-      <c r="E30" s="17">
-        <f>SUM(E4:E29)</f>
+      <c r="E31" s="17">
+        <f>SUM(E4:E30)</f>
         <v/>
       </c>
-      <c r="F30" s="17">
-        <f>SUM(F4:F29)</f>
+      <c r="F31" s="17">
+        <f>SUM(F4:F30)</f>
         <v/>
       </c>
-      <c r="G30" s="17">
-        <f>SUM(G4:G29)</f>
+      <c r="G31" s="17">
+        <f>SUM(G4:G30)</f>
         <v/>
       </c>
-      <c r="H30" s="17">
-        <f>SUM(H4:H29)</f>
+      <c r="H31" s="17">
+        <f>SUM(H4:H30)</f>
         <v/>
       </c>
-      <c r="I30" s="17">
-        <f>SUM(I4:I29)</f>
+      <c r="I31" s="17">
+        <f>SUM(I4:I30)</f>
         <v/>
       </c>
-      <c r="J30" s="17">
-        <f>SUM(J4:J29)</f>
+      <c r="J31" s="17">
+        <f>SUM(J4:J30)</f>
         <v/>
       </c>
-      <c r="K30" s="17">
-        <f>SUM(K4:K29)</f>
+      <c r="K31" s="17">
+        <f>SUM(K4:K30)</f>
         <v/>
       </c>
     </row>
@@ -55498,7 +61389,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・26都道府県、890校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・27都道府県、990校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$994</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1019</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O994"/>
+  <dimension ref="A1:O1019"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（27都道府県／990校）</t>
+          <t>私立高等学校 架電リスト（29都道府県／1015校）</t>
         </is>
       </c>
     </row>
@@ -58886,9 +58886,1472 @@
         </is>
       </c>
     </row>
+    <row r="995">
+      <c r="A995" s="4" t="n">
+        <v>991</v>
+      </c>
+      <c r="B995" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C995" s="5" t="inlineStr">
+        <is>
+          <t>天理市</t>
+        </is>
+      </c>
+      <c r="D995" s="5" t="inlineStr">
+        <is>
+          <t>飛鳥未来高等学校</t>
+        </is>
+      </c>
+      <c r="E995" s="6" t="inlineStr">
+        <is>
+          <t>0743-61-0031</t>
+        </is>
+      </c>
+      <c r="F995" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G995" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H995" s="8" t="n"/>
+      <c r="I995" s="9" t="n"/>
+      <c r="J995" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K995" s="8" t="n"/>
+      <c r="L995" s="9" t="n"/>
+      <c r="M995" s="10" t="inlineStr">
+        <is>
+          <t>通信制・天理市の奈良本校の番号。他キャンパスは別番号</t>
+        </is>
+      </c>
+      <c r="N995" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sanko.ac.jp/asuka/group/outline/</t>
+        </is>
+      </c>
+      <c r="O995" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="4" t="n">
+        <v>992</v>
+      </c>
+      <c r="B996" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C996" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D996" s="5" t="inlineStr">
+        <is>
+          <t>育英西高等学校</t>
+        </is>
+      </c>
+      <c r="E996" s="6" t="inlineStr">
+        <is>
+          <t>0742-47-0688</t>
+        </is>
+      </c>
+      <c r="F996" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G996" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H996" s="8" t="n"/>
+      <c r="I996" s="9" t="n"/>
+      <c r="J996" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K996" s="8" t="n"/>
+      <c r="L996" s="9" t="n"/>
+      <c r="M996" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N996" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ikuei.ed.jp/ikunishi/about/access/</t>
+        </is>
+      </c>
+      <c r="O996" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="4" t="n">
+        <v>993</v>
+      </c>
+      <c r="B997" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C997" s="5" t="inlineStr">
+        <is>
+          <t>橿原市</t>
+        </is>
+      </c>
+      <c r="D997" s="5" t="inlineStr">
+        <is>
+          <t>橿原学院高等学校</t>
+        </is>
+      </c>
+      <c r="E997" s="6" t="inlineStr">
+        <is>
+          <t>0744-27-3242</t>
+        </is>
+      </c>
+      <c r="F997" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G997" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H997" s="8" t="n"/>
+      <c r="I997" s="9" t="n"/>
+      <c r="J997" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K997" s="8" t="n"/>
+      <c r="L997" s="9" t="n"/>
+      <c r="M997" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。一部サイトに0744-27-0742の記載あり（旧番号の可能性）</t>
+        </is>
+      </c>
+      <c r="N997" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kashigaku.ed.jp/introduction-access.html</t>
+        </is>
+      </c>
+      <c r="O997" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="4" t="n">
+        <v>994</v>
+      </c>
+      <c r="B998" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C998" s="5" t="inlineStr">
+        <is>
+          <t>五條市</t>
+        </is>
+      </c>
+      <c r="D998" s="5" t="inlineStr">
+        <is>
+          <t>智辯学園高等学校</t>
+        </is>
+      </c>
+      <c r="E998" s="6" t="inlineStr">
+        <is>
+          <t>0747-22-3191</t>
+        </is>
+      </c>
+      <c r="F998" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G998" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H998" s="8" t="n"/>
+      <c r="I998" s="9" t="n"/>
+      <c r="J998" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K998" s="8" t="n"/>
+      <c r="L998" s="9" t="n"/>
+      <c r="M998" s="10" t="inlineStr">
+        <is>
+          <t>募集要項に代表として記載</t>
+        </is>
+      </c>
+      <c r="N998" s="11" t="inlineStr">
+        <is>
+          <t>https://www.chiben.ac.jp/gojo/wp-content/uploads/sites/5/2025/07/13b1883b7cc9a504f8251f3cfd903829.pdf</t>
+        </is>
+      </c>
+      <c r="O998" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="4" t="n">
+        <v>995</v>
+      </c>
+      <c r="B999" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C999" s="5" t="inlineStr">
+        <is>
+          <t>香芝市</t>
+        </is>
+      </c>
+      <c r="D999" s="5" t="inlineStr">
+        <is>
+          <t>智辯学園奈良カレッジ高等部</t>
+        </is>
+      </c>
+      <c r="E999" s="6" t="inlineStr">
+        <is>
+          <t>0745-79-1111</t>
+        </is>
+      </c>
+      <c r="F999" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G999" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H999" s="8" t="n"/>
+      <c r="I999" s="9" t="n"/>
+      <c r="J999" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K999" s="8" t="n"/>
+      <c r="L999" s="9" t="n"/>
+      <c r="M999" s="10" t="inlineStr">
+        <is>
+          <t>香芝市HP（2021年）は0745-76-2001を掲載</t>
+        </is>
+      </c>
+      <c r="N999" s="11" t="inlineStr">
+        <is>
+          <t>https://www.chiben.ac.jp/naracollege/futures/</t>
+        </is>
+      </c>
+      <c r="O999" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="4" t="n">
+        <v>996</v>
+      </c>
+      <c r="B1000" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1000" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1000" s="5" t="inlineStr">
+        <is>
+          <t>帝塚山高等学校</t>
+        </is>
+      </c>
+      <c r="E1000" s="6" t="inlineStr">
+        <is>
+          <t>0742-41-4685</t>
+        </is>
+      </c>
+      <c r="F1000" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1000" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1000" s="8" t="n"/>
+      <c r="I1000" s="9" t="n"/>
+      <c r="J1000" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1000" s="8" t="n"/>
+      <c r="L1000" s="9" t="n"/>
+      <c r="M1000" s="10" t="inlineStr">
+        <is>
+          <t>中高事務室の番号。学園代表は0742-43-4433</t>
+        </is>
+      </c>
+      <c r="N1000" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tezukayama-h.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1000" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="4" t="n">
+        <v>997</v>
+      </c>
+      <c r="B1001" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1001" s="5" t="inlineStr">
+        <is>
+          <t>天理市</t>
+        </is>
+      </c>
+      <c r="D1001" s="5" t="inlineStr">
+        <is>
+          <t>天理教校学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1001" s="14" t="n"/>
+      <c r="F1001" s="15" t="inlineStr">
+        <is>
+          <t>要調査</t>
+        </is>
+      </c>
+      <c r="G1001" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1001" s="8" t="n"/>
+      <c r="I1001" s="9" t="n"/>
+      <c r="J1001" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1001" s="8" t="n"/>
+      <c r="L1001" s="9" t="n"/>
+      <c r="M1001" s="10" t="inlineStr">
+        <is>
+          <t>【閉校】2023年3月31日に閉校。閉校前の代表は0743-63-1511。架電対象外</t>
+        </is>
+      </c>
+      <c r="N1001" s="11" t="inlineStr">
+        <is>
+          <t>https://rirc.or.jp/database/?rircdb=16033</t>
+        </is>
+      </c>
+      <c r="O1001" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="4" t="n">
+        <v>998</v>
+      </c>
+      <c r="B1002" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1002" s="5" t="inlineStr">
+        <is>
+          <t>天理市</t>
+        </is>
+      </c>
+      <c r="D1002" s="5" t="inlineStr">
+        <is>
+          <t>天理高等学校</t>
+        </is>
+      </c>
+      <c r="E1002" s="6" t="inlineStr">
+        <is>
+          <t>0743-63-7691</t>
+        </is>
+      </c>
+      <c r="F1002" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1002" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1002" s="8" t="n"/>
+      <c r="I1002" s="9" t="n"/>
+      <c r="J1002" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1002" s="8" t="n"/>
+      <c r="L1002" s="9" t="n"/>
+      <c r="M1002" s="10" t="inlineStr">
+        <is>
+          <t>全日制（第一部）の番号。定時制（第二部）は0743-63-7682</t>
+        </is>
+      </c>
+      <c r="N1002" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tenri-h.ed.jp/1bu/</t>
+        </is>
+      </c>
+      <c r="O1002" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="4" t="n">
+        <v>999</v>
+      </c>
+      <c r="B1003" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1003" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1003" s="5" t="inlineStr">
+        <is>
+          <t>東大寺学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1003" s="6" t="inlineStr">
+        <is>
+          <t>0742-47-5511</t>
+        </is>
+      </c>
+      <c r="F1003" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1003" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1003" s="8" t="n"/>
+      <c r="I1003" s="9" t="n"/>
+      <c r="J1003" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1003" s="8" t="n"/>
+      <c r="L1003" s="9" t="n"/>
+      <c r="M1003" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1003" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tdj.ac.jp/access.html</t>
+        </is>
+      </c>
+      <c r="O1003" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B1004" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1004" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1004" s="5" t="inlineStr">
+        <is>
+          <t>奈良育英高等学校</t>
+        </is>
+      </c>
+      <c r="E1004" s="6" t="inlineStr">
+        <is>
+          <t>0742-26-2845</t>
+        </is>
+      </c>
+      <c r="F1004" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1004" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1004" s="8" t="n"/>
+      <c r="I1004" s="9" t="n"/>
+      <c r="J1004" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1004" s="8" t="n"/>
+      <c r="L1004" s="9" t="n"/>
+      <c r="M1004" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1004" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ikuei.ed.jp/ikuei-jh/</t>
+        </is>
+      </c>
+      <c r="O1004" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B1005" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1005" s="5" t="inlineStr">
+        <is>
+          <t>大和郡山市</t>
+        </is>
+      </c>
+      <c r="D1005" s="5" t="inlineStr">
+        <is>
+          <t>奈良学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1005" s="6" t="inlineStr">
+        <is>
+          <t>0743-54-0351</t>
+        </is>
+      </c>
+      <c r="F1005" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1005" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1005" s="8" t="n"/>
+      <c r="I1005" s="9" t="n"/>
+      <c r="J1005" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1005" s="8" t="n"/>
+      <c r="L1005" s="9" t="n"/>
+      <c r="M1005" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1005" s="11" t="inlineStr">
+        <is>
+          <t>https://www.naragakuen.ed.jp/info/edu_corp.html</t>
+        </is>
+      </c>
+      <c r="O1005" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="4" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B1006" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1006" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1006" s="5" t="inlineStr">
+        <is>
+          <t>奈良学園登美ヶ丘高等学校</t>
+        </is>
+      </c>
+      <c r="E1006" s="6" t="inlineStr">
+        <is>
+          <t>0742-93-5111</t>
+        </is>
+      </c>
+      <c r="F1006" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1006" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1006" s="8" t="n"/>
+      <c r="I1006" s="9" t="n"/>
+      <c r="J1006" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1006" s="8" t="n"/>
+      <c r="L1006" s="9" t="n"/>
+      <c r="M1006" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。地図サイトに0742-93-5500の記載あり</t>
+        </is>
+      </c>
+      <c r="N1006" s="11" t="inlineStr">
+        <is>
+          <t>https://www.naragakuen.jp/inquary/</t>
+        </is>
+      </c>
+      <c r="O1006" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="4" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B1007" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1007" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1007" s="5" t="inlineStr">
+        <is>
+          <t>奈良女子高等学校</t>
+        </is>
+      </c>
+      <c r="E1007" s="6" t="inlineStr">
+        <is>
+          <t>0742-33-3601</t>
+        </is>
+      </c>
+      <c r="F1007" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1007" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1007" s="8" t="n"/>
+      <c r="I1007" s="9" t="n"/>
+      <c r="J1007" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1007" s="8" t="n"/>
+      <c r="L1007" s="9" t="n"/>
+      <c r="M1007" s="10" t="inlineStr">
+        <is>
+          <t>白藤学園。通信制課程も同じ番号</t>
+        </is>
+      </c>
+      <c r="N1007" s="11" t="inlineStr">
+        <is>
+          <t>https://shirafuji.ac.jp/shirafuji_high/?page_id=43</t>
+        </is>
+      </c>
+      <c r="O1007" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="4" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B1008" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1008" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1008" s="5" t="inlineStr">
+        <is>
+          <t>奈良大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E1008" s="6" t="inlineStr">
+        <is>
+          <t>0742-41-8840</t>
+        </is>
+      </c>
+      <c r="F1008" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1008" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1008" s="8" t="n"/>
+      <c r="I1008" s="9" t="n"/>
+      <c r="J1008" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1008" s="8" t="n"/>
+      <c r="L1008" s="9" t="n"/>
+      <c r="M1008" s="10" t="n"/>
+      <c r="N1008" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nara-u-h.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1008" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="4" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B1009" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1009" s="5" t="inlineStr">
+        <is>
+          <t>大和高田市</t>
+        </is>
+      </c>
+      <c r="D1009" s="5" t="inlineStr">
+        <is>
+          <t>奈良文化高等学校</t>
+        </is>
+      </c>
+      <c r="E1009" s="6" t="inlineStr">
+        <is>
+          <t>0745-22-8315</t>
+        </is>
+      </c>
+      <c r="F1009" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1009" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1009" s="8" t="n"/>
+      <c r="I1009" s="9" t="n"/>
+      <c r="J1009" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1009" s="8" t="n"/>
+      <c r="L1009" s="9" t="n"/>
+      <c r="M1009" s="10" t="inlineStr">
+        <is>
+          <t>法人ページには0745-22-8268も掲載</t>
+        </is>
+      </c>
+      <c r="N1009" s="11" t="inlineStr">
+        <is>
+          <t>https://www.narabunka.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1009" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="4" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B1010" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1010" s="5" t="inlineStr">
+        <is>
+          <t>河合町</t>
+        </is>
+      </c>
+      <c r="D1010" s="5" t="inlineStr">
+        <is>
+          <t>西大和学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1010" s="6" t="inlineStr">
+        <is>
+          <t>0745-73-6565</t>
+        </is>
+      </c>
+      <c r="F1010" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1010" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1010" s="8" t="n"/>
+      <c r="I1010" s="9" t="n"/>
+      <c r="J1010" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1010" s="8" t="n"/>
+      <c r="L1010" s="9" t="n"/>
+      <c r="M1010" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1010" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nishiyamato.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1010" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="4" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B1011" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1011" s="5" t="inlineStr">
+        <is>
+          <t>和歌山市</t>
+        </is>
+      </c>
+      <c r="D1011" s="5" t="inlineStr">
+        <is>
+          <t>開智高等学校（和歌山県）</t>
+        </is>
+      </c>
+      <c r="E1011" s="6" t="inlineStr">
+        <is>
+          <t>073-461-8080</t>
+        </is>
+      </c>
+      <c r="F1011" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1011" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1011" s="8" t="n"/>
+      <c r="I1011" s="9" t="n"/>
+      <c r="J1011" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1011" s="8" t="n"/>
+      <c r="L1011" s="9" t="n"/>
+      <c r="M1011" s="10" t="inlineStr">
+        <is>
+          <t>中学校併設</t>
+        </is>
+      </c>
+      <c r="N1011" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kaichi.ed.jp/about/access.html</t>
+        </is>
+      </c>
+      <c r="O1011" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="4" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B1012" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1012" s="5" t="inlineStr">
+        <is>
+          <t>新宮市</t>
+        </is>
+      </c>
+      <c r="D1012" s="5" t="inlineStr">
+        <is>
+          <t>近畿大学附属新宮高等学校</t>
+        </is>
+      </c>
+      <c r="E1012" s="6" t="inlineStr">
+        <is>
+          <t>0735-22-2005</t>
+        </is>
+      </c>
+      <c r="F1012" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1012" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1012" s="8" t="n"/>
+      <c r="I1012" s="9" t="n"/>
+      <c r="J1012" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1012" s="8" t="n"/>
+      <c r="L1012" s="9" t="n"/>
+      <c r="M1012" s="10" t="inlineStr">
+        <is>
+          <t>中学校併設</t>
+        </is>
+      </c>
+      <c r="N1012" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shingu.kindai.ac.jp/current_students-graduates/</t>
+        </is>
+      </c>
+      <c r="O1012" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="4" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B1013" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1013" s="5" t="inlineStr">
+        <is>
+          <t>和歌山市</t>
+        </is>
+      </c>
+      <c r="D1013" s="5" t="inlineStr">
+        <is>
+          <t>近畿大学附属和歌山高等学校</t>
+        </is>
+      </c>
+      <c r="E1013" s="6" t="inlineStr">
+        <is>
+          <t>073-452-1161</t>
+        </is>
+      </c>
+      <c r="F1013" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1013" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1013" s="8" t="n"/>
+      <c r="I1013" s="9" t="n"/>
+      <c r="J1013" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1013" s="8" t="n"/>
+      <c r="L1013" s="9" t="n"/>
+      <c r="M1013" s="10" t="inlineStr">
+        <is>
+          <t>中学校併設</t>
+        </is>
+      </c>
+      <c r="N1013" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hwaka.kindai.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1013" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="4" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B1014" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1014" s="5" t="inlineStr">
+        <is>
+          <t>紀美野町</t>
+        </is>
+      </c>
+      <c r="D1014" s="5" t="inlineStr">
+        <is>
+          <t>慶風高等学校</t>
+        </is>
+      </c>
+      <c r="E1014" s="6" t="inlineStr">
+        <is>
+          <t>073-498-0100</t>
+        </is>
+      </c>
+      <c r="F1014" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1014" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1014" s="8" t="n"/>
+      <c r="I1014" s="9" t="n"/>
+      <c r="J1014" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1014" s="8" t="n"/>
+      <c r="L1014" s="9" t="n"/>
+      <c r="M1014" s="10" t="inlineStr">
+        <is>
+          <t>通信制・紀美野町の本校。法人本部（和歌山市）は073-474-2828</t>
+        </is>
+      </c>
+      <c r="N1014" s="11" t="inlineStr">
+        <is>
+          <t>https://keifu.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1014" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="4" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B1015" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1015" s="5" t="inlineStr">
+        <is>
+          <t>高野町</t>
+        </is>
+      </c>
+      <c r="D1015" s="5" t="inlineStr">
+        <is>
+          <t>高野山高等学校</t>
+        </is>
+      </c>
+      <c r="E1015" s="6" t="inlineStr">
+        <is>
+          <t>0736-56-2204</t>
+        </is>
+      </c>
+      <c r="F1015" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1015" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1015" s="8" t="n"/>
+      <c r="I1015" s="9" t="n"/>
+      <c r="J1015" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1015" s="8" t="n"/>
+      <c r="L1015" s="9" t="n"/>
+      <c r="M1015" s="10" t="n"/>
+      <c r="N1015" s="11" t="inlineStr">
+        <is>
+          <t>https://www.koyasan-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1015" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="4" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B1016" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1016" s="5" t="inlineStr">
+        <is>
+          <t>和歌山市</t>
+        </is>
+      </c>
+      <c r="D1016" s="5" t="inlineStr">
+        <is>
+          <t>智辯学園和歌山高等学校</t>
+        </is>
+      </c>
+      <c r="E1016" s="6" t="inlineStr">
+        <is>
+          <t>073-479-2811</t>
+        </is>
+      </c>
+      <c r="F1016" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1016" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1016" s="8" t="n"/>
+      <c r="I1016" s="9" t="n"/>
+      <c r="J1016" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1016" s="8" t="n"/>
+      <c r="L1016" s="9" t="n"/>
+      <c r="M1016" s="10" t="inlineStr">
+        <is>
+          <t>中学校併設</t>
+        </is>
+      </c>
+      <c r="N1016" s="11" t="inlineStr">
+        <is>
+          <t>https://www.chiben.ac.jp/wakayama/</t>
+        </is>
+      </c>
+      <c r="O1016" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="4" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B1017" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1017" s="5" t="inlineStr">
+        <is>
+          <t>橋本市</t>
+        </is>
+      </c>
+      <c r="D1017" s="5" t="inlineStr">
+        <is>
+          <t>初芝橋本高等学校</t>
+        </is>
+      </c>
+      <c r="E1017" s="6" t="inlineStr">
+        <is>
+          <t>0736-37-5600</t>
+        </is>
+      </c>
+      <c r="F1017" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1017" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1017" s="8" t="n"/>
+      <c r="I1017" s="9" t="n"/>
+      <c r="J1017" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1017" s="8" t="n"/>
+      <c r="L1017" s="9" t="n"/>
+      <c r="M1017" s="10" t="inlineStr">
+        <is>
+          <t>2025年4月に運営法人が利晶学園へ改称（校名は変更なし）</t>
+        </is>
+      </c>
+      <c r="N1017" s="11" t="inlineStr">
+        <is>
+          <t>https://www.rishogakuen.ed.jp/hatsuhashi/guide/enkaku.html</t>
+        </is>
+      </c>
+      <c r="O1017" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="4" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B1018" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1018" s="5" t="inlineStr">
+        <is>
+          <t>和歌山市</t>
+        </is>
+      </c>
+      <c r="D1018" s="5" t="inlineStr">
+        <is>
+          <t>和歌山信愛高等学校</t>
+        </is>
+      </c>
+      <c r="E1018" s="6" t="inlineStr">
+        <is>
+          <t>073-424-1141</t>
+        </is>
+      </c>
+      <c r="F1018" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1018" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1018" s="8" t="n"/>
+      <c r="I1018" s="9" t="n"/>
+      <c r="J1018" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1018" s="8" t="n"/>
+      <c r="L1018" s="9" t="n"/>
+      <c r="M1018" s="10" t="inlineStr">
+        <is>
+          <t>中学校併設</t>
+        </is>
+      </c>
+      <c r="N1018" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shin-ai.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1018" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="4" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B1019" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1019" s="5" t="inlineStr">
+        <is>
+          <t>日高川町</t>
+        </is>
+      </c>
+      <c r="D1019" s="5" t="inlineStr">
+        <is>
+          <t>和歌山南陵高等学校</t>
+        </is>
+      </c>
+      <c r="E1019" s="6" t="inlineStr">
+        <is>
+          <t>0738-53-0316</t>
+        </is>
+      </c>
+      <c r="F1019" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1019" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1019" s="8" t="n"/>
+      <c r="I1019" s="9" t="n"/>
+      <c r="J1019" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1019" s="8" t="n"/>
+      <c r="L1019" s="9" t="n"/>
+      <c r="M1019" s="10" t="inlineStr">
+        <is>
+          <t>経営難で一時募集停止命令→2024年11月解除、募集再開済み</t>
+        </is>
+      </c>
+      <c r="N1019" s="11" t="inlineStr">
+        <is>
+          <t>https://w-nanryo.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1019" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O994"/>
-  <conditionalFormatting sqref="A5:O994">
+  <autoFilter ref="A4:O1019"/>
+  <conditionalFormatting sqref="A5:O1019">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -58897,10 +60360,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J994" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J1019" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H994 K5:K994" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H1019 K5:K1019" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -59895,6 +61358,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O992" r:id="rId988"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O993" r:id="rId989"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O994" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O995" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O996" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O997" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O998" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O999" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1000" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1001" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1002" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1003" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1004" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1005" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1006" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1007" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1008" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1009" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1010" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1011" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1012" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1013" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1014" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1015" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1016" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1017" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1018" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1019" r:id="rId1015"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -59907,7 +61395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -59994,43 +61482,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A4,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A4,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$994,A4,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A4,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1019,A4,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A4,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A4,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60041,43 +61529,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A5,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A5,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$994,A5,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A5,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1019,A5,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A5,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A5,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60088,43 +61576,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A6,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A6,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$994,A6,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A6,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1019,A6,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A6,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A6,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60135,43 +61623,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A7,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A7,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$994,A7,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A7,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1019,A7,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A7,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A7,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60182,43 +61670,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A8,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A8,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$994,A8,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A8,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1019,A8,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A8,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A8,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60229,43 +61717,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A9,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A9,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$994,A9,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A9,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1019,A9,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A9,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A9,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60276,43 +61764,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A10,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A10,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$994,A10,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A10,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1019,A10,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A10,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A10,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60323,43 +61811,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A11,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A11,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$994,A11,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A11,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1019,A11,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A11,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A11,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60370,43 +61858,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A12,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A12,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$994,A12,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A12,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1019,A12,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A12,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A12,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60417,43 +61905,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A13,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A13,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$994,A13,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A13,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1019,A13,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A13,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A13,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60464,43 +61952,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A14,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A14,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$994,A14,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A14,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1019,A14,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A14,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A14,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60511,43 +61999,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A15,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A15,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$994,A15,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A15,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1019,A15,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A15,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A15,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60558,43 +62046,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A16,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A16,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$994,A16,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A16,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1019,A16,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A16,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A16,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60605,43 +62093,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A17,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A17,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$994,A17,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A17,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1019,A17,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A17,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A17,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60652,43 +62140,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A18,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A18,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$994,A18,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A18,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1019,A18,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A18,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A18,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60699,43 +62187,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A19,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A19,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$994,A19,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A19,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1019,A19,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A19,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A19,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60746,43 +62234,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A20,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A20,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$994,A20,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A20,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1019,A20,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A20,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A20,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60793,43 +62281,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A21,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A21,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$994,A21,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A21,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1019,A21,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A21,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A21,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60840,43 +62328,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A22,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A22,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$994,A22,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A22,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1019,A22,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A22,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A22,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60887,43 +62375,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A23,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A23,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$994,A23,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A23,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1019,A23,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A23,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A23,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60934,43 +62422,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A24,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A24,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$994,A24,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A24,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1019,A24,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A24,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A24,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -60981,43 +62469,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A25,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A25,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$994,A25,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A25,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1019,A25,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A25,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A25,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61028,43 +62516,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A26,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A26,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$994,A26,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A26,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1019,A26,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A26,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A26,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61075,43 +62563,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A27,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A27,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$994,A27,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A27,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1019,A27,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A27,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A27,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61122,43 +62610,43 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A28,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A28,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$994,A28,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A28,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1019,A28,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A28,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A28,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61169,43 +62657,43 @@
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A29)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A29,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A29,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$994,A29,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A29,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1019,A29,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A29,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A29,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61216,90 +62704,184 @@
         </is>
       </c>
       <c r="B30" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$994,A30)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A30)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,A30,'架電リスト'!$E$5:$E$994,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A30,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$994,A30,'架電リスト'!$J$5:$J$994,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$994,A30,'架電リスト'!$J$5:$J$994,"")</f>
+        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1019,A30,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A30,'架電リスト'!$J$5:$J$1019,"")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"検討中")</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"NG")</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$994,$A30,'架電リスト'!$J$5:$J$994,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="B31" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A31)</f>
+        <v/>
+      </c>
+      <c r="C31" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A31,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D31" s="16">
+        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1019,A31,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A31,'架電リスト'!$J$5:$J$1019,"")</f>
+        <v/>
+      </c>
+      <c r="E31" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F31" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G31" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H31" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I31" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J31" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <v/>
+      </c>
+      <c r="K31" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="B32" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A32)</f>
+        <v/>
+      </c>
+      <c r="C32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A32,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D32" s="16">
+        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1019,A32,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A32,'架電リスト'!$J$5:$J$1019,"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <v/>
+      </c>
+      <c r="K32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B31" s="17">
-        <f>SUM(B4:B30)</f>
+      <c r="B33" s="17">
+        <f>SUM(B4:B32)</f>
         <v/>
       </c>
-      <c r="C31" s="17">
-        <f>SUM(C4:C30)</f>
+      <c r="C33" s="17">
+        <f>SUM(C4:C32)</f>
         <v/>
       </c>
-      <c r="D31" s="17">
-        <f>SUM(D4:D30)</f>
+      <c r="D33" s="17">
+        <f>SUM(D4:D32)</f>
         <v/>
       </c>
-      <c r="E31" s="17">
-        <f>SUM(E4:E30)</f>
+      <c r="E33" s="17">
+        <f>SUM(E4:E32)</f>
         <v/>
       </c>
-      <c r="F31" s="17">
-        <f>SUM(F4:F30)</f>
+      <c r="F33" s="17">
+        <f>SUM(F4:F32)</f>
         <v/>
       </c>
-      <c r="G31" s="17">
-        <f>SUM(G4:G30)</f>
+      <c r="G33" s="17">
+        <f>SUM(G4:G32)</f>
         <v/>
       </c>
-      <c r="H31" s="17">
-        <f>SUM(H4:H30)</f>
+      <c r="H33" s="17">
+        <f>SUM(H4:H32)</f>
         <v/>
       </c>
-      <c r="I31" s="17">
-        <f>SUM(I4:I30)</f>
+      <c r="I33" s="17">
+        <f>SUM(I4:I32)</f>
         <v/>
       </c>
-      <c r="J31" s="17">
-        <f>SUM(J4:J30)</f>
+      <c r="J33" s="17">
+        <f>SUM(J4:J32)</f>
         <v/>
       </c>
-      <c r="K31" s="17">
-        <f>SUM(K4:K30)</f>
+      <c r="K33" s="17">
+        <f>SUM(K4:K32)</f>
         <v/>
       </c>
     </row>
@@ -61389,7 +62971,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・27都道府県、990校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・29都道府県、1015校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1019</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1073</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O1019"/>
+  <dimension ref="A1:O1073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（29都道府県／1015校）</t>
+          <t>私立高等学校 架電リスト（30都道府県／1069校）</t>
         </is>
       </c>
     </row>
@@ -58892,27 +58892,27 @@
       </c>
       <c r="B995" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C995" s="5" t="inlineStr">
         <is>
-          <t>天理市</t>
+          <t>相生市</t>
         </is>
       </c>
       <c r="D995" s="5" t="inlineStr">
         <is>
-          <t>飛鳥未来高等学校</t>
+          <t>相生学院高等学校</t>
         </is>
       </c>
       <c r="E995" s="6" t="inlineStr">
         <is>
-          <t>0743-61-0031</t>
-        </is>
-      </c>
-      <c r="F995" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>0791-24-0100</t>
+        </is>
+      </c>
+      <c r="F995" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="G995" s="5" t="inlineStr">
@@ -58931,12 +58931,12 @@
       <c r="L995" s="9" t="n"/>
       <c r="M995" s="10" t="inlineStr">
         <is>
-          <t>通信制・天理市の奈良本校の番号。他キャンパスは別番号</t>
+          <t>通信制・相生市の本校。公式未確認、複数サイトで一致。学習センターは別番号</t>
         </is>
       </c>
       <c r="N995" s="11" t="inlineStr">
         <is>
-          <t>https://www.sanko.ac.jp/asuka/group/outline/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/28208/ILSP0000041756_ipclm/</t>
         </is>
       </c>
       <c r="O995" s="12" t="inlineStr">
@@ -58951,22 +58951,22 @@
       </c>
       <c r="B996" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C996" s="5" t="inlineStr">
         <is>
-          <t>奈良市</t>
+          <t>神戸市垂水区</t>
         </is>
       </c>
       <c r="D996" s="5" t="inlineStr">
         <is>
-          <t>育英西高等学校</t>
+          <t>愛徳学園高等学校</t>
         </is>
       </c>
       <c r="E996" s="6" t="inlineStr">
         <is>
-          <t>0742-47-0688</t>
+          <t>078-708-5353</t>
         </is>
       </c>
       <c r="F996" s="7" t="inlineStr">
@@ -58995,7 +58995,7 @@
       </c>
       <c r="N996" s="11" t="inlineStr">
         <is>
-          <t>https://www.ikuei.ed.jp/ikunishi/about/access/</t>
+          <t>https://www.aitokugakuen.ed.jp/contact</t>
         </is>
       </c>
       <c r="O996" s="12" t="inlineStr">
@@ -59010,22 +59010,22 @@
       </c>
       <c r="B997" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C997" s="5" t="inlineStr">
         <is>
-          <t>橿原市</t>
+          <t>芦屋市</t>
         </is>
       </c>
       <c r="D997" s="5" t="inlineStr">
         <is>
-          <t>橿原学院高等学校</t>
+          <t>芦屋学園高等学校</t>
         </is>
       </c>
       <c r="E997" s="6" t="inlineStr">
         <is>
-          <t>0744-27-3242</t>
+          <t>0797-31-0666</t>
         </is>
       </c>
       <c r="F997" s="7" t="inlineStr">
@@ -59049,12 +59049,12 @@
       <c r="L997" s="9" t="n"/>
       <c r="M997" s="10" t="inlineStr">
         <is>
-          <t>代表番号。一部サイトに0744-27-0742の記載あり（旧番号の可能性）</t>
+          <t>代表番号。入試対策室フリーダイヤル0120-898-075</t>
         </is>
       </c>
       <c r="N997" s="11" t="inlineStr">
         <is>
-          <t>https://www.kashigaku.ed.jp/introduction-access.html</t>
+          <t>https://www.ashiya.ed.jp/</t>
         </is>
       </c>
       <c r="O997" s="12" t="inlineStr">
@@ -59069,22 +59069,22 @@
       </c>
       <c r="B998" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C998" s="5" t="inlineStr">
         <is>
-          <t>五條市</t>
+          <t>神戸市長田区</t>
         </is>
       </c>
       <c r="D998" s="5" t="inlineStr">
         <is>
-          <t>智辯学園高等学校</t>
+          <t>育英高等学校</t>
         </is>
       </c>
       <c r="E998" s="6" t="inlineStr">
         <is>
-          <t>0747-22-3191</t>
+          <t>078-611-6001</t>
         </is>
       </c>
       <c r="F998" s="7" t="inlineStr">
@@ -59106,14 +59106,10 @@
       </c>
       <c r="K998" s="8" t="n"/>
       <c r="L998" s="9" t="n"/>
-      <c r="M998" s="10" t="inlineStr">
-        <is>
-          <t>募集要項に代表として記載</t>
-        </is>
-      </c>
+      <c r="M998" s="10" t="n"/>
       <c r="N998" s="11" t="inlineStr">
         <is>
-          <t>https://www.chiben.ac.jp/gojo/wp-content/uploads/sites/5/2025/07/13b1883b7cc9a504f8251f3cfd903829.pdf</t>
+          <t>https://www.ikuei.ac.jp/access/</t>
         </is>
       </c>
       <c r="O998" s="12" t="inlineStr">
@@ -59128,22 +59124,22 @@
       </c>
       <c r="B999" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C999" s="5" t="inlineStr">
         <is>
-          <t>香芝市</t>
+          <t>朝来市</t>
         </is>
       </c>
       <c r="D999" s="5" t="inlineStr">
         <is>
-          <t>智辯学園奈良カレッジ高等部</t>
+          <t>生野学園高等学校</t>
         </is>
       </c>
       <c r="E999" s="6" t="inlineStr">
         <is>
-          <t>0745-79-1111</t>
+          <t>079-679-3451</t>
         </is>
       </c>
       <c r="F999" s="7" t="inlineStr">
@@ -59165,14 +59161,10 @@
       </c>
       <c r="K999" s="8" t="n"/>
       <c r="L999" s="9" t="n"/>
-      <c r="M999" s="10" t="inlineStr">
-        <is>
-          <t>香芝市HP（2021年）は0745-76-2001を掲載</t>
-        </is>
-      </c>
+      <c r="M999" s="10" t="n"/>
       <c r="N999" s="11" t="inlineStr">
         <is>
-          <t>https://www.chiben.ac.jp/naracollege/futures/</t>
+          <t>https://www.ikuno.ed.jp/highschool/</t>
         </is>
       </c>
       <c r="O999" s="12" t="inlineStr">
@@ -59187,22 +59179,22 @@
       </c>
       <c r="B1000" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1000" s="5" t="inlineStr">
         <is>
-          <t>奈良市</t>
+          <t>市川町</t>
         </is>
       </c>
       <c r="D1000" s="5" t="inlineStr">
         <is>
-          <t>帝塚山高等学校</t>
+          <t>市川高等学校（兵庫県）</t>
         </is>
       </c>
       <c r="E1000" s="6" t="inlineStr">
         <is>
-          <t>0742-41-4685</t>
+          <t>0790-26-0751</t>
         </is>
       </c>
       <c r="F1000" s="7" t="inlineStr">
@@ -59226,12 +59218,12 @@
       <c r="L1000" s="9" t="n"/>
       <c r="M1000" s="10" t="inlineStr">
         <is>
-          <t>中高事務室の番号。学園代表は0742-43-4433</t>
+          <t>代表番号</t>
         </is>
       </c>
       <c r="N1000" s="11" t="inlineStr">
         <is>
-          <t>https://www.tezukayama-h.ed.jp/access/</t>
+          <t>https://ichikawa.ed.jp/other/access/</t>
         </is>
       </c>
       <c r="O1000" s="12" t="inlineStr">
@@ -59246,23 +59238,27 @@
       </c>
       <c r="B1001" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1001" s="5" t="inlineStr">
         <is>
-          <t>天理市</t>
+          <t>西宮市</t>
         </is>
       </c>
       <c r="D1001" s="5" t="inlineStr">
         <is>
-          <t>天理教校学園高等学校</t>
-        </is>
-      </c>
-      <c r="E1001" s="14" t="n"/>
-      <c r="F1001" s="15" t="inlineStr">
-        <is>
-          <t>要調査</t>
+          <t>関西学院高等部</t>
+        </is>
+      </c>
+      <c r="E1001" s="6" t="inlineStr">
+        <is>
+          <t>0798-51-0975</t>
+        </is>
+      </c>
+      <c r="F1001" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="G1001" s="5" t="inlineStr">
@@ -59281,12 +59277,12 @@
       <c r="L1001" s="9" t="n"/>
       <c r="M1001" s="10" t="inlineStr">
         <is>
-          <t>【閉校】2023年3月31日に閉校。閉校前の代表は0743-63-1511。架電対象外</t>
+          <t>高等部事務室</t>
         </is>
       </c>
       <c r="N1001" s="11" t="inlineStr">
         <is>
-          <t>https://rirc.or.jp/database/?rircdb=16033</t>
+          <t>https://sh.kwansei.ac.jp/</t>
         </is>
       </c>
       <c r="O1001" s="12" t="inlineStr">
@@ -59301,22 +59297,22 @@
       </c>
       <c r="B1002" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1002" s="5" t="inlineStr">
         <is>
-          <t>天理市</t>
+          <t>豊岡市</t>
         </is>
       </c>
       <c r="D1002" s="5" t="inlineStr">
         <is>
-          <t>天理高等学校</t>
+          <t>近畿大学附属豊岡高等学校</t>
         </is>
       </c>
       <c r="E1002" s="6" t="inlineStr">
         <is>
-          <t>0743-63-7691</t>
+          <t>0796-22-4305</t>
         </is>
       </c>
       <c r="F1002" s="7" t="inlineStr">
@@ -59340,12 +59336,12 @@
       <c r="L1002" s="9" t="n"/>
       <c r="M1002" s="10" t="inlineStr">
         <is>
-          <t>全日制（第一部）の番号。定時制（第二部）は0743-63-7682</t>
+          <t>中高共通番号</t>
         </is>
       </c>
       <c r="N1002" s="11" t="inlineStr">
         <is>
-          <t>https://www.tenri-h.ed.jp/1bu/</t>
+          <t>https://www.kindai-toyooka.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O1002" s="12" t="inlineStr">
@@ -59360,22 +59356,22 @@
       </c>
       <c r="B1003" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1003" s="5" t="inlineStr">
         <is>
-          <t>奈良市</t>
+          <t>神戸市須磨区</t>
         </is>
       </c>
       <c r="D1003" s="5" t="inlineStr">
         <is>
-          <t>東大寺学園高等学校</t>
+          <t>啓明学院高等学校</t>
         </is>
       </c>
       <c r="E1003" s="6" t="inlineStr">
         <is>
-          <t>0742-47-5511</t>
+          <t>078-741-1501</t>
         </is>
       </c>
       <c r="F1003" s="7" t="inlineStr">
@@ -59399,12 +59395,12 @@
       <c r="L1003" s="9" t="n"/>
       <c r="M1003" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>1サイトのみ078-741-1506と記載（誤記とみられる）</t>
         </is>
       </c>
       <c r="N1003" s="11" t="inlineStr">
         <is>
-          <t>https://www.tdj.ac.jp/access.html</t>
+          <t>https://www.keimei.ed.jp/</t>
         </is>
       </c>
       <c r="O1003" s="12" t="inlineStr">
@@ -59419,22 +59415,22 @@
       </c>
       <c r="B1004" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1004" s="5" t="inlineStr">
         <is>
-          <t>奈良市</t>
+          <t>姫路市</t>
         </is>
       </c>
       <c r="D1004" s="5" t="inlineStr">
         <is>
-          <t>奈良育英高等学校</t>
+          <t>賢明女子学院高等学校</t>
         </is>
       </c>
       <c r="E1004" s="6" t="inlineStr">
         <is>
-          <t>0742-26-2845</t>
+          <t>079-223-8456</t>
         </is>
       </c>
       <c r="F1004" s="7" t="inlineStr">
@@ -59458,12 +59454,12 @@
       <c r="L1004" s="9" t="n"/>
       <c r="M1004" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>079-223-8458はFAX</t>
         </is>
       </c>
       <c r="N1004" s="11" t="inlineStr">
         <is>
-          <t>https://www.ikuei.ed.jp/ikuei-jh/</t>
+          <t>https://www.himejikenmei.ac.jp/</t>
         </is>
       </c>
       <c r="O1004" s="12" t="inlineStr">
@@ -59478,22 +59474,22 @@
       </c>
       <c r="B1005" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1005" s="5" t="inlineStr">
         <is>
-          <t>大和郡山市</t>
+          <t>西宮市</t>
         </is>
       </c>
       <c r="D1005" s="5" t="inlineStr">
         <is>
-          <t>奈良学園高等学校</t>
+          <t>甲子園学院高等学校</t>
         </is>
       </c>
       <c r="E1005" s="6" t="inlineStr">
         <is>
-          <t>0743-54-0351</t>
+          <t>0798-65-6100</t>
         </is>
       </c>
       <c r="F1005" s="7" t="inlineStr">
@@ -59517,12 +59513,12 @@
       <c r="L1005" s="9" t="n"/>
       <c r="M1005" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>中高直通。法人本部は0798-67-2100</t>
         </is>
       </c>
       <c r="N1005" s="11" t="inlineStr">
         <is>
-          <t>https://www.naragakuen.ed.jp/info/edu_corp.html</t>
+          <t>http://www.koshiengakuin-h.ed.jp/about_us/access.html</t>
         </is>
       </c>
       <c r="O1005" s="12" t="inlineStr">
@@ -59537,22 +59533,22 @@
       </c>
       <c r="B1006" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1006" s="5" t="inlineStr">
         <is>
-          <t>奈良市</t>
+          <t>芦屋市</t>
         </is>
       </c>
       <c r="D1006" s="5" t="inlineStr">
         <is>
-          <t>奈良学園登美ヶ丘高等学校</t>
+          <t>甲南高等学校</t>
         </is>
       </c>
       <c r="E1006" s="6" t="inlineStr">
         <is>
-          <t>0742-93-5111</t>
+          <t>0797-31-0551</t>
         </is>
       </c>
       <c r="F1006" s="7" t="inlineStr">
@@ -59576,12 +59572,12 @@
       <c r="L1006" s="9" t="n"/>
       <c r="M1006" s="10" t="inlineStr">
         <is>
-          <t>代表番号。地図サイトに0742-93-5500の記載あり</t>
+          <t>中高共通番号</t>
         </is>
       </c>
       <c r="N1006" s="11" t="inlineStr">
         <is>
-          <t>https://www.naragakuen.jp/inquary/</t>
+          <t>https://www.konan.ed.jp/information/access.html</t>
         </is>
       </c>
       <c r="O1006" s="12" t="inlineStr">
@@ -59596,22 +59592,22 @@
       </c>
       <c r="B1007" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1007" s="5" t="inlineStr">
         <is>
-          <t>奈良市</t>
+          <t>神戸市東灘区</t>
         </is>
       </c>
       <c r="D1007" s="5" t="inlineStr">
         <is>
-          <t>奈良女子高等学校</t>
+          <t>甲南女子高等学校</t>
         </is>
       </c>
       <c r="E1007" s="6" t="inlineStr">
         <is>
-          <t>0742-33-3601</t>
+          <t>078-411-2531</t>
         </is>
       </c>
       <c r="F1007" s="7" t="inlineStr">
@@ -59635,12 +59631,12 @@
       <c r="L1007" s="9" t="n"/>
       <c r="M1007" s="10" t="inlineStr">
         <is>
-          <t>白藤学園。通信制課程も同じ番号</t>
+          <t>中高共通番号</t>
         </is>
       </c>
       <c r="N1007" s="11" t="inlineStr">
         <is>
-          <t>https://shirafuji.ac.jp/shirafuji_high/?page_id=43</t>
+          <t>https://gakuen.konan-wu.ac.jp/contact/</t>
         </is>
       </c>
       <c r="O1007" s="12" t="inlineStr">
@@ -59655,22 +59651,22 @@
       </c>
       <c r="B1008" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1008" s="5" t="inlineStr">
         <is>
-          <t>奈良市</t>
+          <t>神戸市灘区</t>
         </is>
       </c>
       <c r="D1008" s="5" t="inlineStr">
         <is>
-          <t>奈良大学附属高等学校</t>
+          <t>神戸海星女子学院高等学校</t>
         </is>
       </c>
       <c r="E1008" s="6" t="inlineStr">
         <is>
-          <t>0742-41-8840</t>
+          <t>078-801-5601</t>
         </is>
       </c>
       <c r="F1008" s="7" t="inlineStr">
@@ -59692,10 +59688,14 @@
       </c>
       <c r="K1008" s="8" t="n"/>
       <c r="L1008" s="9" t="n"/>
-      <c r="M1008" s="10" t="n"/>
+      <c r="M1008" s="10" t="inlineStr">
+        <is>
+          <t>代表番号</t>
+        </is>
+      </c>
       <c r="N1008" s="11" t="inlineStr">
         <is>
-          <t>https://www.nara-u-h.ed.jp/access/</t>
+          <t>https://www.kobekaisei.ed.jp/jr-high/contact/</t>
         </is>
       </c>
       <c r="O1008" s="12" t="inlineStr">
@@ -59710,22 +59710,22 @@
       </c>
       <c r="B1009" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1009" s="5" t="inlineStr">
         <is>
-          <t>大和高田市</t>
+          <t>神戸市中央区</t>
         </is>
       </c>
       <c r="D1009" s="5" t="inlineStr">
         <is>
-          <t>奈良文化高等学校</t>
+          <t>神戸学院大学附属高等学校</t>
         </is>
       </c>
       <c r="E1009" s="6" t="inlineStr">
         <is>
-          <t>0745-22-8315</t>
+          <t>078-302-2016</t>
         </is>
       </c>
       <c r="F1009" s="7" t="inlineStr">
@@ -59735,7 +59735,7 @@
       </c>
       <c r="G1009" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1009" s="8" t="n"/>
@@ -59749,12 +59749,12 @@
       <c r="L1009" s="9" t="n"/>
       <c r="M1009" s="10" t="inlineStr">
         <is>
-          <t>法人ページには0745-22-8268も掲載</t>
+          <t>2016年に中央区ポートアイランドへ移転済み（旧番号078-511-6004）</t>
         </is>
       </c>
       <c r="N1009" s="11" t="inlineStr">
         <is>
-          <t>https://www.narabunka.ed.jp/</t>
+          <t>https://www.kobegakuin-f.ed.jp/</t>
         </is>
       </c>
       <c r="O1009" s="12" t="inlineStr">
@@ -59769,22 +59769,22 @@
       </c>
       <c r="B1010" s="5" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1010" s="5" t="inlineStr">
         <is>
-          <t>河合町</t>
+          <t>神戸市北区</t>
         </is>
       </c>
       <c r="D1010" s="5" t="inlineStr">
         <is>
-          <t>西大和学園高等学校</t>
+          <t>神戸弘陵学園高等学校</t>
         </is>
       </c>
       <c r="E1010" s="6" t="inlineStr">
         <is>
-          <t>0745-73-6565</t>
+          <t>078-593-3535</t>
         </is>
       </c>
       <c r="F1010" s="7" t="inlineStr">
@@ -59806,14 +59806,10 @@
       </c>
       <c r="K1010" s="8" t="n"/>
       <c r="L1010" s="9" t="n"/>
-      <c r="M1010" s="10" t="inlineStr">
-        <is>
-          <t>中高共通番号</t>
-        </is>
-      </c>
+      <c r="M1010" s="10" t="n"/>
       <c r="N1010" s="11" t="inlineStr">
         <is>
-          <t>https://www.nishiyamato.ed.jp/contact/</t>
+          <t>https://www.kobe-koryo.com/</t>
         </is>
       </c>
       <c r="O1010" s="12" t="inlineStr">
@@ -59828,22 +59824,22 @@
       </c>
       <c r="B1011" s="5" t="inlineStr">
         <is>
-          <t>和歌山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1011" s="5" t="inlineStr">
         <is>
-          <t>和歌山市</t>
+          <t>神戸市須磨区</t>
         </is>
       </c>
       <c r="D1011" s="5" t="inlineStr">
         <is>
-          <t>開智高等学校（和歌山県）</t>
+          <t>神戸国際高等学校</t>
         </is>
       </c>
       <c r="E1011" s="6" t="inlineStr">
         <is>
-          <t>073-461-8080</t>
+          <t>078-731-4665</t>
         </is>
       </c>
       <c r="F1011" s="7" t="inlineStr">
@@ -59853,7 +59849,7 @@
       </c>
       <c r="G1011" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>専門学科</t>
         </is>
       </c>
       <c r="H1011" s="8" t="n"/>
@@ -59865,14 +59861,10 @@
       </c>
       <c r="K1011" s="8" t="n"/>
       <c r="L1011" s="9" t="n"/>
-      <c r="M1011" s="10" t="inlineStr">
-        <is>
-          <t>中学校併設</t>
-        </is>
-      </c>
+      <c r="M1011" s="10" t="n"/>
       <c r="N1011" s="11" t="inlineStr">
         <is>
-          <t>https://www.kaichi.ed.jp/about/access.html</t>
+          <t>https://kis.ed.jp/06info/</t>
         </is>
       </c>
       <c r="O1011" s="12" t="inlineStr">
@@ -59887,22 +59879,22 @@
       </c>
       <c r="B1012" s="5" t="inlineStr">
         <is>
-          <t>和歌山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1012" s="5" t="inlineStr">
         <is>
-          <t>新宮市</t>
+          <t>神戸市垂水区</t>
         </is>
       </c>
       <c r="D1012" s="5" t="inlineStr">
         <is>
-          <t>近畿大学附属新宮高等学校</t>
+          <t>神戸国際大学附属高等学校</t>
         </is>
       </c>
       <c r="E1012" s="6" t="inlineStr">
         <is>
-          <t>0735-22-2005</t>
+          <t>078-707-1001</t>
         </is>
       </c>
       <c r="F1012" s="7" t="inlineStr">
@@ -59912,7 +59904,7 @@
       </c>
       <c r="G1012" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1012" s="8" t="n"/>
@@ -59926,12 +59918,12 @@
       <c r="L1012" s="9" t="n"/>
       <c r="M1012" s="10" t="inlineStr">
         <is>
-          <t>中学校併設</t>
+          <t>代表番号</t>
         </is>
       </c>
       <c r="N1012" s="11" t="inlineStr">
         <is>
-          <t>https://www.shingu.kindai.ac.jp/current_students-graduates/</t>
+          <t>https://www.kobe-michael.ac.jp/</t>
         </is>
       </c>
       <c r="O1012" s="12" t="inlineStr">
@@ -59946,22 +59938,22 @@
       </c>
       <c r="B1013" s="5" t="inlineStr">
         <is>
-          <t>和歌山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1013" s="5" t="inlineStr">
         <is>
-          <t>和歌山市</t>
+          <t>西宮市</t>
         </is>
       </c>
       <c r="D1013" s="5" t="inlineStr">
         <is>
-          <t>近畿大学附属和歌山高等学校</t>
+          <t>神戸女学院高等学部</t>
         </is>
       </c>
       <c r="E1013" s="6" t="inlineStr">
         <is>
-          <t>073-452-1161</t>
+          <t>0798-51-8570</t>
         </is>
       </c>
       <c r="F1013" s="7" t="inlineStr">
@@ -59985,12 +59977,12 @@
       <c r="L1013" s="9" t="n"/>
       <c r="M1013" s="10" t="inlineStr">
         <is>
-          <t>中学校併設</t>
+          <t>中高共通の事務室代表（大学とは別番号）</t>
         </is>
       </c>
       <c r="N1013" s="11" t="inlineStr">
         <is>
-          <t>https://www.hwaka.kindai.ac.jp/</t>
+          <t>https://www.kobejogakuin-h.ed.jp/info/toiawase.html</t>
         </is>
       </c>
       <c r="O1013" s="12" t="inlineStr">
@@ -60005,22 +59997,22 @@
       </c>
       <c r="B1014" s="5" t="inlineStr">
         <is>
-          <t>和歌山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1014" s="5" t="inlineStr">
         <is>
-          <t>紀美野町</t>
+          <t>神戸市須磨区</t>
         </is>
       </c>
       <c r="D1014" s="5" t="inlineStr">
         <is>
-          <t>慶風高等学校</t>
+          <t>神戸星城高等学校</t>
         </is>
       </c>
       <c r="E1014" s="6" t="inlineStr">
         <is>
-          <t>073-498-0100</t>
+          <t>078-741-1860</t>
         </is>
       </c>
       <c r="F1014" s="7" t="inlineStr">
@@ -60030,7 +60022,7 @@
       </c>
       <c r="G1014" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>専門学科</t>
         </is>
       </c>
       <c r="H1014" s="8" t="n"/>
@@ -60042,14 +60034,10 @@
       </c>
       <c r="K1014" s="8" t="n"/>
       <c r="L1014" s="9" t="n"/>
-      <c r="M1014" s="10" t="inlineStr">
-        <is>
-          <t>通信制・紀美野町の本校。法人本部（和歌山市）は073-474-2828</t>
-        </is>
-      </c>
+      <c r="M1014" s="10" t="n"/>
       <c r="N1014" s="11" t="inlineStr">
         <is>
-          <t>https://keifu.ac.jp/access/</t>
+          <t>https://www.seijoh.ac.jp/06_01contact.html</t>
         </is>
       </c>
       <c r="O1014" s="12" t="inlineStr">
@@ -60064,22 +60052,22 @@
       </c>
       <c r="B1015" s="5" t="inlineStr">
         <is>
-          <t>和歌山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1015" s="5" t="inlineStr">
         <is>
-          <t>高野町</t>
+          <t>神戸市中央区</t>
         </is>
       </c>
       <c r="D1015" s="5" t="inlineStr">
         <is>
-          <t>高野山高等学校</t>
+          <t>神戸第一高等学校</t>
         </is>
       </c>
       <c r="E1015" s="6" t="inlineStr">
         <is>
-          <t>0736-56-2204</t>
+          <t>078-242-4811</t>
         </is>
       </c>
       <c r="F1015" s="7" t="inlineStr">
@@ -60104,7 +60092,7 @@
       <c r="M1015" s="10" t="n"/>
       <c r="N1015" s="11" t="inlineStr">
         <is>
-          <t>https://www.koyasan-h.ed.jp/</t>
+          <t>https://kobedai1.ed.jp/school-guide/</t>
         </is>
       </c>
       <c r="O1015" s="12" t="inlineStr">
@@ -60119,22 +60107,22 @@
       </c>
       <c r="B1016" s="5" t="inlineStr">
         <is>
-          <t>和歌山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1016" s="5" t="inlineStr">
         <is>
-          <t>和歌山市</t>
+          <t>神戸市長田区</t>
         </is>
       </c>
       <c r="D1016" s="5" t="inlineStr">
         <is>
-          <t>智辯学園和歌山高等学校</t>
+          <t>神戸常盤女子高等学校</t>
         </is>
       </c>
       <c r="E1016" s="6" t="inlineStr">
         <is>
-          <t>073-479-2811</t>
+          <t>078-691-0561</t>
         </is>
       </c>
       <c r="F1016" s="7" t="inlineStr">
@@ -60144,7 +60132,7 @@
       </c>
       <c r="G1016" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1016" s="8" t="n"/>
@@ -60156,14 +60144,10 @@
       </c>
       <c r="K1016" s="8" t="n"/>
       <c r="L1016" s="9" t="n"/>
-      <c r="M1016" s="10" t="inlineStr">
-        <is>
-          <t>中学校併設</t>
-        </is>
-      </c>
+      <c r="M1016" s="10" t="n"/>
       <c r="N1016" s="11" t="inlineStr">
         <is>
-          <t>https://www.chiben.ac.jp/wakayama/</t>
+          <t>https://www.kobe-tokiwa.ed.jp/about/</t>
         </is>
       </c>
       <c r="O1016" s="12" t="inlineStr">
@@ -60178,22 +60162,22 @@
       </c>
       <c r="B1017" s="5" t="inlineStr">
         <is>
-          <t>和歌山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1017" s="5" t="inlineStr">
         <is>
-          <t>橋本市</t>
+          <t>神戸市長田区</t>
         </is>
       </c>
       <c r="D1017" s="5" t="inlineStr">
         <is>
-          <t>初芝橋本高等学校</t>
+          <t>神戸野田高等学校</t>
         </is>
       </c>
       <c r="E1017" s="6" t="inlineStr">
         <is>
-          <t>0736-37-5600</t>
+          <t>078-731-8015</t>
         </is>
       </c>
       <c r="F1017" s="7" t="inlineStr">
@@ -60215,14 +60199,10 @@
       </c>
       <c r="K1017" s="8" t="n"/>
       <c r="L1017" s="9" t="n"/>
-      <c r="M1017" s="10" t="inlineStr">
-        <is>
-          <t>2025年4月に運営法人が利晶学園へ改称（校名は変更なし）</t>
-        </is>
-      </c>
+      <c r="M1017" s="10" t="n"/>
       <c r="N1017" s="11" t="inlineStr">
         <is>
-          <t>https://www.rishogakuen.ed.jp/hatsuhashi/guide/enkaku.html</t>
+          <t>https://kobenoda-h.ed.jp/jh-access/</t>
         </is>
       </c>
       <c r="O1017" s="12" t="inlineStr">
@@ -60237,22 +60217,22 @@
       </c>
       <c r="B1018" s="5" t="inlineStr">
         <is>
-          <t>和歌山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1018" s="5" t="inlineStr">
         <is>
-          <t>和歌山市</t>
+          <t>神戸市中央区</t>
         </is>
       </c>
       <c r="D1018" s="5" t="inlineStr">
         <is>
-          <t>和歌山信愛高等学校</t>
+          <t>神戸山手グローバル高等学校</t>
         </is>
       </c>
       <c r="E1018" s="6" t="inlineStr">
         <is>
-          <t>073-424-1141</t>
+          <t>078-341-2133</t>
         </is>
       </c>
       <c r="F1018" s="7" t="inlineStr">
@@ -60262,7 +60242,7 @@
       </c>
       <c r="G1018" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1018" s="8" t="n"/>
@@ -60276,12 +60256,12 @@
       <c r="L1018" s="9" t="n"/>
       <c r="M1018" s="10" t="inlineStr">
         <is>
-          <t>中学校併設</t>
+          <t>旧・神戸山手女子。2025年4月から共学化。中高共通番号</t>
         </is>
       </c>
       <c r="N1018" s="11" t="inlineStr">
         <is>
-          <t>https://www.shin-ai.ac.jp/</t>
+          <t>https://www.kobeyamate.ed.jp/</t>
         </is>
       </c>
       <c r="O1018" s="12" t="inlineStr">
@@ -60296,22 +60276,22 @@
       </c>
       <c r="B1019" s="5" t="inlineStr">
         <is>
-          <t>和歌山県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="C1019" s="5" t="inlineStr">
         <is>
-          <t>日高川町</t>
+          <t>神戸市中央区</t>
         </is>
       </c>
       <c r="D1019" s="5" t="inlineStr">
         <is>
-          <t>和歌山南陵高等学校</t>
+          <t>神戸龍谷高等学校</t>
         </is>
       </c>
       <c r="E1019" s="6" t="inlineStr">
         <is>
-          <t>0738-53-0316</t>
+          <t>078-241-0076</t>
         </is>
       </c>
       <c r="F1019" s="7" t="inlineStr">
@@ -60335,23 +60315,3157 @@
       <c r="L1019" s="9" t="n"/>
       <c r="M1019" s="10" t="inlineStr">
         <is>
+          <t>事務室の番号</t>
+        </is>
+      </c>
+      <c r="N1019" s="11" t="inlineStr">
+        <is>
+          <t>https://www.koberyukoku.ed.jp/graduate/certificate/</t>
+        </is>
+      </c>
+      <c r="O1019" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="4" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B1020" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1020" s="5" t="inlineStr">
+        <is>
+          <t>西宮市</t>
+        </is>
+      </c>
+      <c r="D1020" s="5" t="inlineStr">
+        <is>
+          <t>甲陽学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1020" s="6" t="inlineStr">
+        <is>
+          <t>0798-73-3011</t>
+        </is>
+      </c>
+      <c r="F1020" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1020" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1020" s="8" t="n"/>
+      <c r="I1020" s="9" t="n"/>
+      <c r="J1020" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1020" s="8" t="n"/>
+      <c r="L1020" s="9" t="n"/>
+      <c r="M1020" s="10" t="inlineStr">
+        <is>
+          <t>中学校は別キャンパス（0798-33-5012）</t>
+        </is>
+      </c>
+      <c r="N1020" s="11" t="inlineStr">
+        <is>
+          <t>https://www.koyo.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1020" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="4" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B1021" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1021" s="5" t="inlineStr">
+        <is>
+          <t>宝塚市</t>
+        </is>
+      </c>
+      <c r="D1021" s="5" t="inlineStr">
+        <is>
+          <t>小林聖心女子学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1021" s="6" t="inlineStr">
+        <is>
+          <t>0797-71-7321</t>
+        </is>
+      </c>
+      <c r="F1021" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1021" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1021" s="8" t="n"/>
+      <c r="I1021" s="9" t="n"/>
+      <c r="J1021" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1021" s="8" t="n"/>
+      <c r="L1021" s="9" t="n"/>
+      <c r="M1021" s="10" t="inlineStr">
+        <is>
+          <t>小中高の代表番号</t>
+        </is>
+      </c>
+      <c r="N1021" s="11" t="inlineStr">
+        <is>
+          <t>https://www.oby-sacred-heart.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1021" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="4" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B1022" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1022" s="5" t="inlineStr">
+        <is>
+          <t>神戸市長田区</t>
+        </is>
+      </c>
+      <c r="D1022" s="5" t="inlineStr">
+        <is>
+          <t>彩星工科高等学校</t>
+        </is>
+      </c>
+      <c r="E1022" s="6" t="inlineStr">
+        <is>
+          <t>078-575-0230</t>
+        </is>
+      </c>
+      <c r="F1022" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1022" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1022" s="8" t="n"/>
+      <c r="I1022" s="9" t="n"/>
+      <c r="J1022" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1022" s="8" t="n"/>
+      <c r="L1022" s="9" t="n"/>
+      <c r="M1022" s="10" t="n"/>
+      <c r="N1022" s="11" t="inlineStr">
+        <is>
+          <t>https://saiseikoka.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1022" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="4" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B1023" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1023" s="5" t="inlineStr">
+        <is>
+          <t>三田市</t>
+        </is>
+      </c>
+      <c r="D1023" s="5" t="inlineStr">
+        <is>
+          <t>三田学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1023" s="6" t="inlineStr">
+        <is>
+          <t>079-564-2291</t>
+        </is>
+      </c>
+      <c r="F1023" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1023" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1023" s="8" t="n"/>
+      <c r="I1023" s="9" t="n"/>
+      <c r="J1023" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1023" s="8" t="n"/>
+      <c r="L1023" s="9" t="n"/>
+      <c r="M1023" s="10" t="n"/>
+      <c r="N1023" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sandagakuen.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1023" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="4" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B1024" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1024" s="5" t="inlineStr">
+        <is>
+          <t>三田市</t>
+        </is>
+      </c>
+      <c r="D1024" s="5" t="inlineStr">
+        <is>
+          <t>三田松聖高等学校</t>
+        </is>
+      </c>
+      <c r="E1024" s="6" t="inlineStr">
+        <is>
+          <t>079-568-1001</t>
+        </is>
+      </c>
+      <c r="F1024" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1024" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1024" s="8" t="n"/>
+      <c r="I1024" s="9" t="n"/>
+      <c r="J1024" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1024" s="8" t="n"/>
+      <c r="L1024" s="9" t="n"/>
+      <c r="M1024" s="10" t="n"/>
+      <c r="N1024" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sandashosei.net/news/procedures/</t>
+        </is>
+      </c>
+      <c r="O1024" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="4" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B1025" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1025" s="5" t="inlineStr">
+        <is>
+          <t>神戸市兵庫区</t>
+        </is>
+      </c>
+      <c r="D1025" s="5" t="inlineStr">
+        <is>
+          <t>夙川高等学校</t>
+        </is>
+      </c>
+      <c r="E1025" s="6" t="inlineStr">
+        <is>
+          <t>078-578-7226</t>
+        </is>
+      </c>
+      <c r="F1025" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1025" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1025" s="8" t="n"/>
+      <c r="I1025" s="9" t="n"/>
+      <c r="J1025" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1025" s="8" t="n"/>
+      <c r="L1025" s="9" t="n"/>
+      <c r="M1025" s="10" t="inlineStr">
+        <is>
+          <t>旧・夙川学院。2019年から須磨学園が運営、神戸市兵庫区に移転（西宮の旧番号0798-74-5061とは別）</t>
+        </is>
+      </c>
+      <c r="N1025" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sumashuku.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1025" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="4" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B1026" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1026" s="5" t="inlineStr">
+        <is>
+          <t>神戸市灘区</t>
+        </is>
+      </c>
+      <c r="D1026" s="5" t="inlineStr">
+        <is>
+          <t>松蔭高等学校（兵庫県）</t>
+        </is>
+      </c>
+      <c r="E1026" s="6" t="inlineStr">
+        <is>
+          <t>078-861-1105</t>
+        </is>
+      </c>
+      <c r="F1026" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1026" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1026" s="8" t="n"/>
+      <c r="I1026" s="9" t="n"/>
+      <c r="J1026" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1026" s="8" t="n"/>
+      <c r="L1026" s="9" t="n"/>
+      <c r="M1026" s="10" t="n"/>
+      <c r="N1026" s="11" t="inlineStr">
+        <is>
+          <t>https://shoin-jhs.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1026" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="4" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B1027" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1027" s="5" t="inlineStr">
+        <is>
+          <t>神戸市中央区</t>
+        </is>
+      </c>
+      <c r="D1027" s="5" t="inlineStr">
+        <is>
+          <t>神港学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1027" s="6" t="inlineStr">
+        <is>
+          <t>078-241-3135</t>
+        </is>
+      </c>
+      <c r="F1027" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1027" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1027" s="8" t="n"/>
+      <c r="I1027" s="9" t="n"/>
+      <c r="J1027" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1027" s="8" t="n"/>
+      <c r="L1027" s="9" t="n"/>
+      <c r="M1027" s="10" t="inlineStr">
+        <is>
+          <t>「神港学園神港高等学校」表記もあり</t>
+        </is>
+      </c>
+      <c r="N1027" s="11" t="inlineStr">
+        <is>
+          <t>https://shinko.ed.jp/contacts/</t>
+        </is>
+      </c>
+      <c r="O1027" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="4" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B1028" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1028" s="5" t="inlineStr">
+        <is>
+          <t>神戸市灘区</t>
+        </is>
+      </c>
+      <c r="D1028" s="5" t="inlineStr">
+        <is>
+          <t>親和女子高等学校</t>
+        </is>
+      </c>
+      <c r="E1028" s="6" t="inlineStr">
+        <is>
+          <t>078-854-3800</t>
+        </is>
+      </c>
+      <c r="F1028" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1028" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1028" s="8" t="n"/>
+      <c r="I1028" s="9" t="n"/>
+      <c r="J1028" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1028" s="8" t="n"/>
+      <c r="L1028" s="9" t="n"/>
+      <c r="M1028" s="10" t="n"/>
+      <c r="N1028" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kobe-shinwa.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1028" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="4" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B1029" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1029" s="5" t="inlineStr">
+        <is>
+          <t>姫路市</t>
+        </is>
+      </c>
+      <c r="D1029" s="5" t="inlineStr">
+        <is>
+          <t>淳心学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1029" s="6" t="inlineStr">
+        <is>
+          <t>079-222-3581</t>
+        </is>
+      </c>
+      <c r="F1029" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1029" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1029" s="8" t="n"/>
+      <c r="I1029" s="9" t="n"/>
+      <c r="J1029" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1029" s="8" t="n"/>
+      <c r="L1029" s="9" t="n"/>
+      <c r="M1029" s="10" t="n"/>
+      <c r="N1029" s="11" t="inlineStr">
+        <is>
+          <t>https://www.junshin.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1029" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="4" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B1030" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1030" s="5" t="inlineStr">
+        <is>
+          <t>神戸市須磨区</t>
+        </is>
+      </c>
+      <c r="D1030" s="5" t="inlineStr">
+        <is>
+          <t>須磨学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1030" s="6" t="inlineStr">
+        <is>
+          <t>078-732-1968</t>
+        </is>
+      </c>
+      <c r="F1030" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1030" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1030" s="8" t="n"/>
+      <c r="I1030" s="9" t="n"/>
+      <c r="J1030" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1030" s="8" t="n"/>
+      <c r="L1030" s="9" t="n"/>
+      <c r="M1030" s="10" t="n"/>
+      <c r="N1030" s="11" t="inlineStr">
+        <is>
+          <t>https://www.suma.ac.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1030" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="4" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B1031" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1031" s="5" t="inlineStr">
+        <is>
+          <t>明石市</t>
+        </is>
+      </c>
+      <c r="D1031" s="5" t="inlineStr">
+        <is>
+          <t>青楓館高等学院</t>
+        </is>
+      </c>
+      <c r="E1031" s="6" t="inlineStr">
+        <is>
+          <t>078-915-0775</t>
+        </is>
+      </c>
+      <c r="F1031" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1031" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1031" s="8" t="n"/>
+      <c r="I1031" s="9" t="n"/>
+      <c r="J1031" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1031" s="8" t="n"/>
+      <c r="L1031" s="9" t="n"/>
+      <c r="M1031" s="10" t="inlineStr">
+        <is>
+          <t>通信制・2023年開校。明石本校の入学・広報センター番号</t>
+        </is>
+      </c>
+      <c r="N1031" s="11" t="inlineStr">
+        <is>
+          <t>https://seifukan-gakuin.com/session/</t>
+        </is>
+      </c>
+      <c r="O1031" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="4" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B1032" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1032" s="5" t="inlineStr">
+        <is>
+          <t>洲本市</t>
+        </is>
+      </c>
+      <c r="D1032" s="5" t="inlineStr">
+        <is>
+          <t>蒼開高等学校</t>
+        </is>
+      </c>
+      <c r="E1032" s="6" t="inlineStr">
+        <is>
+          <t>0799-22-2552</t>
+        </is>
+      </c>
+      <c r="F1032" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1032" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1032" s="8" t="n"/>
+      <c r="I1032" s="9" t="n"/>
+      <c r="J1032" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1032" s="8" t="n"/>
+      <c r="L1032" s="9" t="n"/>
+      <c r="M1032" s="10" t="inlineStr">
+        <is>
+          <t>中学校は0799-22-2551</t>
+        </is>
+      </c>
+      <c r="N1032" s="11" t="inlineStr">
+        <is>
+          <t>https://www.soukai-school.jp/exam/admission_hi/</t>
+        </is>
+      </c>
+      <c r="O1032" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="4" t="n">
+        <v>1029</v>
+      </c>
+      <c r="B1033" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1033" s="5" t="inlineStr">
+        <is>
+          <t>尼崎市</t>
+        </is>
+      </c>
+      <c r="D1033" s="5" t="inlineStr">
+        <is>
+          <t>園田学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1033" s="6" t="inlineStr">
+        <is>
+          <t>06-6428-2242</t>
+        </is>
+      </c>
+      <c r="F1033" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1033" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1033" s="8" t="n"/>
+      <c r="I1033" s="9" t="n"/>
+      <c r="J1033" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1033" s="8" t="n"/>
+      <c r="L1033" s="9" t="n"/>
+      <c r="M1033" s="10" t="inlineStr">
+        <is>
+          <t>尼崎市施設案内とも一致</t>
+        </is>
+      </c>
+      <c r="N1033" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sonodagakuen.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1033" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="4" t="n">
+        <v>1030</v>
+      </c>
+      <c r="B1034" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1034" s="5" t="inlineStr">
+        <is>
+          <t>神戸市須磨区</t>
+        </is>
+      </c>
+      <c r="D1034" s="5" t="inlineStr">
+        <is>
+          <t>滝川高等学校</t>
+        </is>
+      </c>
+      <c r="E1034" s="6" t="inlineStr">
+        <is>
+          <t>078-732-1625</t>
+        </is>
+      </c>
+      <c r="F1034" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1034" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1034" s="8" t="n"/>
+      <c r="I1034" s="9" t="n"/>
+      <c r="J1034" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1034" s="8" t="n"/>
+      <c r="L1034" s="9" t="n"/>
+      <c r="M1034" s="10" t="inlineStr">
+        <is>
+          <t>代表番号</t>
+        </is>
+      </c>
+      <c r="N1034" s="11" t="inlineStr">
+        <is>
+          <t>https://www.takigawa.ac.jp/enquiry.php</t>
+        </is>
+      </c>
+      <c r="O1034" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="4" t="n">
+        <v>1031</v>
+      </c>
+      <c r="B1035" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1035" s="5" t="inlineStr">
+        <is>
+          <t>神戸市西区</t>
+        </is>
+      </c>
+      <c r="D1035" s="5" t="inlineStr">
+        <is>
+          <t>滝川第二高等学校</t>
+        </is>
+      </c>
+      <c r="E1035" s="6" t="inlineStr">
+        <is>
+          <t>078-961-2381</t>
+        </is>
+      </c>
+      <c r="F1035" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1035" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1035" s="8" t="n"/>
+      <c r="I1035" s="9" t="n"/>
+      <c r="J1035" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1035" s="8" t="n"/>
+      <c r="L1035" s="9" t="n"/>
+      <c r="M1035" s="10" t="inlineStr">
+        <is>
+          <t>代表番号</t>
+        </is>
+      </c>
+      <c r="N1035" s="11" t="inlineStr">
+        <is>
+          <t>https://takigawa2.ed.jp/contact</t>
+        </is>
+      </c>
+      <c r="O1035" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="B1036" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1036" s="5" t="inlineStr">
+        <is>
+          <t>養父市</t>
+        </is>
+      </c>
+      <c r="D1036" s="5" t="inlineStr">
+        <is>
+          <t>第一学院高等学校 養父本校</t>
+        </is>
+      </c>
+      <c r="E1036" s="6" t="inlineStr">
+        <is>
+          <t>079-663-5100</t>
+        </is>
+      </c>
+      <c r="F1036" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1036" s="5" t="inlineStr">
+        <is>
+          <t>総合学科</t>
+        </is>
+      </c>
+      <c r="H1036" s="8" t="n"/>
+      <c r="I1036" s="9" t="n"/>
+      <c r="J1036" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1036" s="8" t="n"/>
+      <c r="L1036" s="9" t="n"/>
+      <c r="M1036" s="10" t="inlineStr">
+        <is>
+          <t>通信制・養父本校。フリーダイヤルは別</t>
+        </is>
+      </c>
+      <c r="N1036" s="11" t="inlineStr">
+        <is>
+          <t>https://www.daiichigakuin.ed.jp/about/outline/</t>
+        </is>
+      </c>
+      <c r="O1036" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="4" t="n">
+        <v>1033</v>
+      </c>
+      <c r="B1037" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1037" s="5" t="inlineStr">
+        <is>
+          <t>姫路市</t>
+        </is>
+      </c>
+      <c r="D1037" s="5" t="inlineStr">
+        <is>
+          <t>東洋大学附属姫路高等学校</t>
+        </is>
+      </c>
+      <c r="E1037" s="6" t="inlineStr">
+        <is>
+          <t>079-266-2626</t>
+        </is>
+      </c>
+      <c r="F1037" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1037" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1037" s="8" t="n"/>
+      <c r="I1037" s="9" t="n"/>
+      <c r="J1037" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1037" s="8" t="n"/>
+      <c r="L1037" s="9" t="n"/>
+      <c r="M1037" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1037" s="11" t="inlineStr">
+        <is>
+          <t>https://www.toyo.ac.jp/himeji/yellowpage/</t>
+        </is>
+      </c>
+      <c r="O1037" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="4" t="n">
+        <v>1034</v>
+      </c>
+      <c r="B1038" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1038" s="5" t="inlineStr">
+        <is>
+          <t>神戸市東灘区</t>
+        </is>
+      </c>
+      <c r="D1038" s="5" t="inlineStr">
+        <is>
+          <t>灘高等学校</t>
+        </is>
+      </c>
+      <c r="E1038" s="6" t="inlineStr">
+        <is>
+          <t>078-411-7234</t>
+        </is>
+      </c>
+      <c r="F1038" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1038" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1038" s="8" t="n"/>
+      <c r="I1038" s="9" t="n"/>
+      <c r="J1038" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1038" s="8" t="n"/>
+      <c r="L1038" s="9" t="n"/>
+      <c r="M1038" s="10" t="inlineStr">
+        <is>
+          <t>高校事務室の番号</t>
+        </is>
+      </c>
+      <c r="N1038" s="11" t="inlineStr">
+        <is>
+          <t>http://www.nada.ac.jp/sotugyousyoumeisyo.html</t>
+        </is>
+      </c>
+      <c r="O1038" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="4" t="n">
+        <v>1035</v>
+      </c>
+      <c r="B1039" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1039" s="5" t="inlineStr">
+        <is>
+          <t>西宮市</t>
+        </is>
+      </c>
+      <c r="D1039" s="5" t="inlineStr">
+        <is>
+          <t>仁川学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1039" s="6" t="inlineStr">
+        <is>
+          <t>0798-51-3621</t>
+        </is>
+      </c>
+      <c r="F1039" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1039" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1039" s="8" t="n"/>
+      <c r="I1039" s="9" t="n"/>
+      <c r="J1039" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1039" s="8" t="n"/>
+      <c r="L1039" s="9" t="n"/>
+      <c r="M1039" s="10" t="inlineStr">
+        <is>
+          <t>学院事務局は0798-52-0551</t>
+        </is>
+      </c>
+      <c r="N1039" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nigawa.ac.jp/inquiry/</t>
+        </is>
+      </c>
+      <c r="O1039" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="4" t="n">
+        <v>1036</v>
+      </c>
+      <c r="B1040" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1040" s="5" t="inlineStr">
+        <is>
+          <t>高砂市</t>
+        </is>
+      </c>
+      <c r="D1040" s="5" t="inlineStr">
+        <is>
+          <t>白陵高等学校</t>
+        </is>
+      </c>
+      <c r="E1040" s="6" t="inlineStr">
+        <is>
+          <t>079-447-1675</t>
+        </is>
+      </c>
+      <c r="F1040" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1040" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1040" s="8" t="n"/>
+      <c r="I1040" s="9" t="n"/>
+      <c r="J1040" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1040" s="8" t="n"/>
+      <c r="L1040" s="9" t="n"/>
+      <c r="M1040" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1040" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hakuryo.ed.jp/index4.html</t>
+        </is>
+      </c>
+      <c r="O1040" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="4" t="n">
+        <v>1037</v>
+      </c>
+      <c r="B1041" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1041" s="5" t="inlineStr">
+        <is>
+          <t>姫路市</t>
+        </is>
+      </c>
+      <c r="D1041" s="5" t="inlineStr">
+        <is>
+          <t>日ノ本学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1041" s="6" t="inlineStr">
+        <is>
+          <t>079-232-5578</t>
+        </is>
+      </c>
+      <c r="F1041" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1041" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1041" s="8" t="n"/>
+      <c r="I1041" s="9" t="n"/>
+      <c r="J1041" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1041" s="8" t="n"/>
+      <c r="L1041" s="9" t="n"/>
+      <c r="M1041" s="10" t="inlineStr">
+        <is>
+          <t>代表番号</t>
+        </is>
+      </c>
+      <c r="N1041" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hinomoto.ac.jp/school_life/access/</t>
+        </is>
+      </c>
+      <c r="O1041" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="4" t="n">
+        <v>1038</v>
+      </c>
+      <c r="B1042" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1042" s="5" t="inlineStr">
+        <is>
+          <t>宝塚市</t>
+        </is>
+      </c>
+      <c r="D1042" s="5" t="inlineStr">
+        <is>
+          <t>雲雀丘学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1042" s="6" t="inlineStr">
+        <is>
+          <t>072-759-1300</t>
+        </is>
+      </c>
+      <c r="F1042" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1042" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1042" s="8" t="n"/>
+      <c r="I1042" s="9" t="n"/>
+      <c r="J1042" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1042" s="8" t="n"/>
+      <c r="L1042" s="9" t="n"/>
+      <c r="M1042" s="10" t="inlineStr">
+        <is>
+          <t>学園事務局は072-759-3000</t>
+        </is>
+      </c>
+      <c r="N1042" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hibari-ho.ed.jp/inquiry.html</t>
+        </is>
+      </c>
+      <c r="O1042" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="4" t="n">
+        <v>1039</v>
+      </c>
+      <c r="B1043" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1043" s="5" t="inlineStr">
+        <is>
+          <t>姫路市</t>
+        </is>
+      </c>
+      <c r="D1043" s="5" t="inlineStr">
+        <is>
+          <t>姫路女学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1043" s="6" t="inlineStr">
+        <is>
+          <t>079-224-1711</t>
+        </is>
+      </c>
+      <c r="F1043" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1043" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1043" s="8" t="n"/>
+      <c r="I1043" s="9" t="n"/>
+      <c r="J1043" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1043" s="8" t="n"/>
+      <c r="L1043" s="9" t="n"/>
+      <c r="M1043" s="10" t="n"/>
+      <c r="N1043" s="11" t="inlineStr">
+        <is>
+          <t>https://www.himeji-jogakuin.ed.jp/academy_information/</t>
+        </is>
+      </c>
+      <c r="O1043" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="4" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B1044" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1044" s="5" t="inlineStr">
+        <is>
+          <t>神戸市須磨区</t>
+        </is>
+      </c>
+      <c r="D1044" s="5" t="inlineStr">
+        <is>
+          <t>兵庫大学附属須磨ノ浦高等学校</t>
+        </is>
+      </c>
+      <c r="E1044" s="6" t="inlineStr">
+        <is>
+          <t>078-735-7111</t>
+        </is>
+      </c>
+      <c r="F1044" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1044" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1044" s="8" t="n"/>
+      <c r="I1044" s="9" t="n"/>
+      <c r="J1044" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1044" s="8" t="n"/>
+      <c r="L1044" s="9" t="n"/>
+      <c r="M1044" s="10" t="n"/>
+      <c r="N1044" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sumanoura.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1044" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="4" t="n">
+        <v>1041</v>
+      </c>
+      <c r="B1045" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1045" s="5" t="inlineStr">
+        <is>
+          <t>西宮市</t>
+        </is>
+      </c>
+      <c r="D1045" s="5" t="inlineStr">
+        <is>
+          <t>報徳学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1045" s="6" t="inlineStr">
+        <is>
+          <t>0798-51-3021</t>
+        </is>
+      </c>
+      <c r="F1045" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1045" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1045" s="8" t="n"/>
+      <c r="I1045" s="9" t="n"/>
+      <c r="J1045" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1045" s="8" t="n"/>
+      <c r="L1045" s="9" t="n"/>
+      <c r="M1045" s="10" t="n"/>
+      <c r="N1045" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hotoku.ac.jp/about/access</t>
+        </is>
+      </c>
+      <c r="O1045" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="4" t="n">
+        <v>1042</v>
+      </c>
+      <c r="B1046" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1046" s="5" t="inlineStr">
+        <is>
+          <t>西宮市</t>
+        </is>
+      </c>
+      <c r="D1046" s="5" t="inlineStr">
+        <is>
+          <t>武庫川女子大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E1046" s="6" t="inlineStr">
+        <is>
+          <t>0798-47-6436</t>
+        </is>
+      </c>
+      <c r="F1046" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1046" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1046" s="8" t="n"/>
+      <c r="I1046" s="9" t="n"/>
+      <c r="J1046" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1046" s="8" t="n"/>
+      <c r="L1046" s="9" t="n"/>
+      <c r="M1046" s="10" t="inlineStr">
+        <is>
+          <t>2027年4月に「武庫川大学附属高等学校」へ校名変更予定（第三者情報）</t>
+        </is>
+      </c>
+      <c r="N1046" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mukogawa-u.ac.jp/~JHS/openschool/index.html</t>
+        </is>
+      </c>
+      <c r="O1046" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="4" t="n">
+        <v>1043</v>
+      </c>
+      <c r="B1047" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1047" s="5" t="inlineStr">
+        <is>
+          <t>尼崎市</t>
+        </is>
+      </c>
+      <c r="D1047" s="5" t="inlineStr">
+        <is>
+          <t>百合学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1047" s="6" t="inlineStr">
+        <is>
+          <t>06-6491-6298</t>
+        </is>
+      </c>
+      <c r="F1047" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G1047" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1047" s="8" t="n"/>
+      <c r="I1047" s="9" t="n"/>
+      <c r="J1047" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1047" s="8" t="n"/>
+      <c r="L1047" s="9" t="n"/>
+      <c r="M1047" s="10" t="inlineStr">
+        <is>
+          <t>公式未確認、複数サイトで一致</t>
+        </is>
+      </c>
+      <c r="N1047" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/28202/ILSP0000041583_ipclm/</t>
+        </is>
+      </c>
+      <c r="O1047" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="4" t="n">
+        <v>1044</v>
+      </c>
+      <c r="B1048" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県</t>
+        </is>
+      </c>
+      <c r="C1048" s="5" t="inlineStr">
+        <is>
+          <t>神戸市灘区</t>
+        </is>
+      </c>
+      <c r="D1048" s="5" t="inlineStr">
+        <is>
+          <t>六甲学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1048" s="6" t="inlineStr">
+        <is>
+          <t>078-871-4161</t>
+        </is>
+      </c>
+      <c r="F1048" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1048" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1048" s="8" t="n"/>
+      <c r="I1048" s="9" t="n"/>
+      <c r="J1048" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1048" s="8" t="n"/>
+      <c r="L1048" s="9" t="n"/>
+      <c r="M1048" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。中高共通</t>
+        </is>
+      </c>
+      <c r="N1048" s="11" t="inlineStr">
+        <is>
+          <t>http://rokkogakuin.ed.jp/rblog/news/</t>
+        </is>
+      </c>
+      <c r="O1048" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="4" t="n">
+        <v>1045</v>
+      </c>
+      <c r="B1049" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1049" s="5" t="inlineStr">
+        <is>
+          <t>天理市</t>
+        </is>
+      </c>
+      <c r="D1049" s="5" t="inlineStr">
+        <is>
+          <t>飛鳥未来高等学校</t>
+        </is>
+      </c>
+      <c r="E1049" s="6" t="inlineStr">
+        <is>
+          <t>0743-61-0031</t>
+        </is>
+      </c>
+      <c r="F1049" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1049" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1049" s="8" t="n"/>
+      <c r="I1049" s="9" t="n"/>
+      <c r="J1049" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1049" s="8" t="n"/>
+      <c r="L1049" s="9" t="n"/>
+      <c r="M1049" s="10" t="inlineStr">
+        <is>
+          <t>通信制・天理市の奈良本校の番号。他キャンパスは別番号</t>
+        </is>
+      </c>
+      <c r="N1049" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sanko.ac.jp/asuka/group/outline/</t>
+        </is>
+      </c>
+      <c r="O1049" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="4" t="n">
+        <v>1046</v>
+      </c>
+      <c r="B1050" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1050" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1050" s="5" t="inlineStr">
+        <is>
+          <t>育英西高等学校</t>
+        </is>
+      </c>
+      <c r="E1050" s="6" t="inlineStr">
+        <is>
+          <t>0742-47-0688</t>
+        </is>
+      </c>
+      <c r="F1050" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1050" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1050" s="8" t="n"/>
+      <c r="I1050" s="9" t="n"/>
+      <c r="J1050" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1050" s="8" t="n"/>
+      <c r="L1050" s="9" t="n"/>
+      <c r="M1050" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1050" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ikuei.ed.jp/ikunishi/about/access/</t>
+        </is>
+      </c>
+      <c r="O1050" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="4" t="n">
+        <v>1047</v>
+      </c>
+      <c r="B1051" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1051" s="5" t="inlineStr">
+        <is>
+          <t>橿原市</t>
+        </is>
+      </c>
+      <c r="D1051" s="5" t="inlineStr">
+        <is>
+          <t>橿原学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1051" s="6" t="inlineStr">
+        <is>
+          <t>0744-27-3242</t>
+        </is>
+      </c>
+      <c r="F1051" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1051" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1051" s="8" t="n"/>
+      <c r="I1051" s="9" t="n"/>
+      <c r="J1051" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1051" s="8" t="n"/>
+      <c r="L1051" s="9" t="n"/>
+      <c r="M1051" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。一部サイトに0744-27-0742の記載あり（旧番号の可能性）</t>
+        </is>
+      </c>
+      <c r="N1051" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kashigaku.ed.jp/introduction-access.html</t>
+        </is>
+      </c>
+      <c r="O1051" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="4" t="n">
+        <v>1048</v>
+      </c>
+      <c r="B1052" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1052" s="5" t="inlineStr">
+        <is>
+          <t>五條市</t>
+        </is>
+      </c>
+      <c r="D1052" s="5" t="inlineStr">
+        <is>
+          <t>智辯学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1052" s="6" t="inlineStr">
+        <is>
+          <t>0747-22-3191</t>
+        </is>
+      </c>
+      <c r="F1052" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1052" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1052" s="8" t="n"/>
+      <c r="I1052" s="9" t="n"/>
+      <c r="J1052" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1052" s="8" t="n"/>
+      <c r="L1052" s="9" t="n"/>
+      <c r="M1052" s="10" t="inlineStr">
+        <is>
+          <t>募集要項に代表として記載</t>
+        </is>
+      </c>
+      <c r="N1052" s="11" t="inlineStr">
+        <is>
+          <t>https://www.chiben.ac.jp/gojo/wp-content/uploads/sites/5/2025/07/13b1883b7cc9a504f8251f3cfd903829.pdf</t>
+        </is>
+      </c>
+      <c r="O1052" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="4" t="n">
+        <v>1049</v>
+      </c>
+      <c r="B1053" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1053" s="5" t="inlineStr">
+        <is>
+          <t>香芝市</t>
+        </is>
+      </c>
+      <c r="D1053" s="5" t="inlineStr">
+        <is>
+          <t>智辯学園奈良カレッジ高等部</t>
+        </is>
+      </c>
+      <c r="E1053" s="6" t="inlineStr">
+        <is>
+          <t>0745-79-1111</t>
+        </is>
+      </c>
+      <c r="F1053" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1053" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1053" s="8" t="n"/>
+      <c r="I1053" s="9" t="n"/>
+      <c r="J1053" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1053" s="8" t="n"/>
+      <c r="L1053" s="9" t="n"/>
+      <c r="M1053" s="10" t="inlineStr">
+        <is>
+          <t>香芝市HP（2021年）は0745-76-2001を掲載</t>
+        </is>
+      </c>
+      <c r="N1053" s="11" t="inlineStr">
+        <is>
+          <t>https://www.chiben.ac.jp/naracollege/futures/</t>
+        </is>
+      </c>
+      <c r="O1053" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="4" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B1054" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1054" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1054" s="5" t="inlineStr">
+        <is>
+          <t>帝塚山高等学校</t>
+        </is>
+      </c>
+      <c r="E1054" s="6" t="inlineStr">
+        <is>
+          <t>0742-41-4685</t>
+        </is>
+      </c>
+      <c r="F1054" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1054" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1054" s="8" t="n"/>
+      <c r="I1054" s="9" t="n"/>
+      <c r="J1054" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1054" s="8" t="n"/>
+      <c r="L1054" s="9" t="n"/>
+      <c r="M1054" s="10" t="inlineStr">
+        <is>
+          <t>中高事務室の番号。学園代表は0742-43-4433</t>
+        </is>
+      </c>
+      <c r="N1054" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tezukayama-h.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1054" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="4" t="n">
+        <v>1051</v>
+      </c>
+      <c r="B1055" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1055" s="5" t="inlineStr">
+        <is>
+          <t>天理市</t>
+        </is>
+      </c>
+      <c r="D1055" s="5" t="inlineStr">
+        <is>
+          <t>天理教校学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1055" s="14" t="n"/>
+      <c r="F1055" s="15" t="inlineStr">
+        <is>
+          <t>要調査</t>
+        </is>
+      </c>
+      <c r="G1055" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1055" s="8" t="n"/>
+      <c r="I1055" s="9" t="n"/>
+      <c r="J1055" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1055" s="8" t="n"/>
+      <c r="L1055" s="9" t="n"/>
+      <c r="M1055" s="10" t="inlineStr">
+        <is>
+          <t>【閉校】2023年3月31日に閉校。閉校前の代表は0743-63-1511。架電対象外</t>
+        </is>
+      </c>
+      <c r="N1055" s="11" t="inlineStr">
+        <is>
+          <t>https://rirc.or.jp/database/?rircdb=16033</t>
+        </is>
+      </c>
+      <c r="O1055" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="4" t="n">
+        <v>1052</v>
+      </c>
+      <c r="B1056" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1056" s="5" t="inlineStr">
+        <is>
+          <t>天理市</t>
+        </is>
+      </c>
+      <c r="D1056" s="5" t="inlineStr">
+        <is>
+          <t>天理高等学校</t>
+        </is>
+      </c>
+      <c r="E1056" s="6" t="inlineStr">
+        <is>
+          <t>0743-63-7691</t>
+        </is>
+      </c>
+      <c r="F1056" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1056" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1056" s="8" t="n"/>
+      <c r="I1056" s="9" t="n"/>
+      <c r="J1056" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1056" s="8" t="n"/>
+      <c r="L1056" s="9" t="n"/>
+      <c r="M1056" s="10" t="inlineStr">
+        <is>
+          <t>全日制（第一部）の番号。定時制（第二部）は0743-63-7682</t>
+        </is>
+      </c>
+      <c r="N1056" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tenri-h.ed.jp/1bu/</t>
+        </is>
+      </c>
+      <c r="O1056" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="4" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B1057" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1057" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1057" s="5" t="inlineStr">
+        <is>
+          <t>東大寺学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1057" s="6" t="inlineStr">
+        <is>
+          <t>0742-47-5511</t>
+        </is>
+      </c>
+      <c r="F1057" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1057" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1057" s="8" t="n"/>
+      <c r="I1057" s="9" t="n"/>
+      <c r="J1057" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1057" s="8" t="n"/>
+      <c r="L1057" s="9" t="n"/>
+      <c r="M1057" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1057" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tdj.ac.jp/access.html</t>
+        </is>
+      </c>
+      <c r="O1057" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="4" t="n">
+        <v>1054</v>
+      </c>
+      <c r="B1058" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1058" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1058" s="5" t="inlineStr">
+        <is>
+          <t>奈良育英高等学校</t>
+        </is>
+      </c>
+      <c r="E1058" s="6" t="inlineStr">
+        <is>
+          <t>0742-26-2845</t>
+        </is>
+      </c>
+      <c r="F1058" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1058" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1058" s="8" t="n"/>
+      <c r="I1058" s="9" t="n"/>
+      <c r="J1058" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1058" s="8" t="n"/>
+      <c r="L1058" s="9" t="n"/>
+      <c r="M1058" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1058" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ikuei.ed.jp/ikuei-jh/</t>
+        </is>
+      </c>
+      <c r="O1058" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="4" t="n">
+        <v>1055</v>
+      </c>
+      <c r="B1059" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1059" s="5" t="inlineStr">
+        <is>
+          <t>大和郡山市</t>
+        </is>
+      </c>
+      <c r="D1059" s="5" t="inlineStr">
+        <is>
+          <t>奈良学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1059" s="6" t="inlineStr">
+        <is>
+          <t>0743-54-0351</t>
+        </is>
+      </c>
+      <c r="F1059" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1059" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1059" s="8" t="n"/>
+      <c r="I1059" s="9" t="n"/>
+      <c r="J1059" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1059" s="8" t="n"/>
+      <c r="L1059" s="9" t="n"/>
+      <c r="M1059" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1059" s="11" t="inlineStr">
+        <is>
+          <t>https://www.naragakuen.ed.jp/info/edu_corp.html</t>
+        </is>
+      </c>
+      <c r="O1059" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="4" t="n">
+        <v>1056</v>
+      </c>
+      <c r="B1060" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1060" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1060" s="5" t="inlineStr">
+        <is>
+          <t>奈良学園登美ヶ丘高等学校</t>
+        </is>
+      </c>
+      <c r="E1060" s="6" t="inlineStr">
+        <is>
+          <t>0742-93-5111</t>
+        </is>
+      </c>
+      <c r="F1060" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1060" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1060" s="8" t="n"/>
+      <c r="I1060" s="9" t="n"/>
+      <c r="J1060" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1060" s="8" t="n"/>
+      <c r="L1060" s="9" t="n"/>
+      <c r="M1060" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。地図サイトに0742-93-5500の記載あり</t>
+        </is>
+      </c>
+      <c r="N1060" s="11" t="inlineStr">
+        <is>
+          <t>https://www.naragakuen.jp/inquary/</t>
+        </is>
+      </c>
+      <c r="O1060" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="4" t="n">
+        <v>1057</v>
+      </c>
+      <c r="B1061" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1061" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1061" s="5" t="inlineStr">
+        <is>
+          <t>奈良女子高等学校</t>
+        </is>
+      </c>
+      <c r="E1061" s="6" t="inlineStr">
+        <is>
+          <t>0742-33-3601</t>
+        </is>
+      </c>
+      <c r="F1061" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1061" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1061" s="8" t="n"/>
+      <c r="I1061" s="9" t="n"/>
+      <c r="J1061" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1061" s="8" t="n"/>
+      <c r="L1061" s="9" t="n"/>
+      <c r="M1061" s="10" t="inlineStr">
+        <is>
+          <t>白藤学園。通信制課程も同じ番号</t>
+        </is>
+      </c>
+      <c r="N1061" s="11" t="inlineStr">
+        <is>
+          <t>https://shirafuji.ac.jp/shirafuji_high/?page_id=43</t>
+        </is>
+      </c>
+      <c r="O1061" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="4" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B1062" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1062" s="5" t="inlineStr">
+        <is>
+          <t>奈良市</t>
+        </is>
+      </c>
+      <c r="D1062" s="5" t="inlineStr">
+        <is>
+          <t>奈良大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E1062" s="6" t="inlineStr">
+        <is>
+          <t>0742-41-8840</t>
+        </is>
+      </c>
+      <c r="F1062" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1062" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1062" s="8" t="n"/>
+      <c r="I1062" s="9" t="n"/>
+      <c r="J1062" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1062" s="8" t="n"/>
+      <c r="L1062" s="9" t="n"/>
+      <c r="M1062" s="10" t="n"/>
+      <c r="N1062" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nara-u-h.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1062" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="4" t="n">
+        <v>1059</v>
+      </c>
+      <c r="B1063" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1063" s="5" t="inlineStr">
+        <is>
+          <t>大和高田市</t>
+        </is>
+      </c>
+      <c r="D1063" s="5" t="inlineStr">
+        <is>
+          <t>奈良文化高等学校</t>
+        </is>
+      </c>
+      <c r="E1063" s="6" t="inlineStr">
+        <is>
+          <t>0745-22-8315</t>
+        </is>
+      </c>
+      <c r="F1063" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1063" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1063" s="8" t="n"/>
+      <c r="I1063" s="9" t="n"/>
+      <c r="J1063" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1063" s="8" t="n"/>
+      <c r="L1063" s="9" t="n"/>
+      <c r="M1063" s="10" t="inlineStr">
+        <is>
+          <t>法人ページには0745-22-8268も掲載</t>
+        </is>
+      </c>
+      <c r="N1063" s="11" t="inlineStr">
+        <is>
+          <t>https://www.narabunka.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1063" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="4" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B1064" s="5" t="inlineStr">
+        <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="C1064" s="5" t="inlineStr">
+        <is>
+          <t>河合町</t>
+        </is>
+      </c>
+      <c r="D1064" s="5" t="inlineStr">
+        <is>
+          <t>西大和学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1064" s="6" t="inlineStr">
+        <is>
+          <t>0745-73-6565</t>
+        </is>
+      </c>
+      <c r="F1064" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1064" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1064" s="8" t="n"/>
+      <c r="I1064" s="9" t="n"/>
+      <c r="J1064" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1064" s="8" t="n"/>
+      <c r="L1064" s="9" t="n"/>
+      <c r="M1064" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1064" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nishiyamato.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1064" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="4" t="n">
+        <v>1061</v>
+      </c>
+      <c r="B1065" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1065" s="5" t="inlineStr">
+        <is>
+          <t>和歌山市</t>
+        </is>
+      </c>
+      <c r="D1065" s="5" t="inlineStr">
+        <is>
+          <t>開智高等学校（和歌山県）</t>
+        </is>
+      </c>
+      <c r="E1065" s="6" t="inlineStr">
+        <is>
+          <t>073-461-8080</t>
+        </is>
+      </c>
+      <c r="F1065" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1065" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1065" s="8" t="n"/>
+      <c r="I1065" s="9" t="n"/>
+      <c r="J1065" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1065" s="8" t="n"/>
+      <c r="L1065" s="9" t="n"/>
+      <c r="M1065" s="10" t="inlineStr">
+        <is>
+          <t>中学校併設</t>
+        </is>
+      </c>
+      <c r="N1065" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kaichi.ed.jp/about/access.html</t>
+        </is>
+      </c>
+      <c r="O1065" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="4" t="n">
+        <v>1062</v>
+      </c>
+      <c r="B1066" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1066" s="5" t="inlineStr">
+        <is>
+          <t>新宮市</t>
+        </is>
+      </c>
+      <c r="D1066" s="5" t="inlineStr">
+        <is>
+          <t>近畿大学附属新宮高等学校</t>
+        </is>
+      </c>
+      <c r="E1066" s="6" t="inlineStr">
+        <is>
+          <t>0735-22-2005</t>
+        </is>
+      </c>
+      <c r="F1066" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1066" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1066" s="8" t="n"/>
+      <c r="I1066" s="9" t="n"/>
+      <c r="J1066" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1066" s="8" t="n"/>
+      <c r="L1066" s="9" t="n"/>
+      <c r="M1066" s="10" t="inlineStr">
+        <is>
+          <t>中学校併設</t>
+        </is>
+      </c>
+      <c r="N1066" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shingu.kindai.ac.jp/current_students-graduates/</t>
+        </is>
+      </c>
+      <c r="O1066" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="4" t="n">
+        <v>1063</v>
+      </c>
+      <c r="B1067" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1067" s="5" t="inlineStr">
+        <is>
+          <t>和歌山市</t>
+        </is>
+      </c>
+      <c r="D1067" s="5" t="inlineStr">
+        <is>
+          <t>近畿大学附属和歌山高等学校</t>
+        </is>
+      </c>
+      <c r="E1067" s="6" t="inlineStr">
+        <is>
+          <t>073-452-1161</t>
+        </is>
+      </c>
+      <c r="F1067" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1067" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1067" s="8" t="n"/>
+      <c r="I1067" s="9" t="n"/>
+      <c r="J1067" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1067" s="8" t="n"/>
+      <c r="L1067" s="9" t="n"/>
+      <c r="M1067" s="10" t="inlineStr">
+        <is>
+          <t>中学校併設</t>
+        </is>
+      </c>
+      <c r="N1067" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hwaka.kindai.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1067" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="4" t="n">
+        <v>1064</v>
+      </c>
+      <c r="B1068" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1068" s="5" t="inlineStr">
+        <is>
+          <t>紀美野町</t>
+        </is>
+      </c>
+      <c r="D1068" s="5" t="inlineStr">
+        <is>
+          <t>慶風高等学校</t>
+        </is>
+      </c>
+      <c r="E1068" s="6" t="inlineStr">
+        <is>
+          <t>073-498-0100</t>
+        </is>
+      </c>
+      <c r="F1068" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1068" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1068" s="8" t="n"/>
+      <c r="I1068" s="9" t="n"/>
+      <c r="J1068" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1068" s="8" t="n"/>
+      <c r="L1068" s="9" t="n"/>
+      <c r="M1068" s="10" t="inlineStr">
+        <is>
+          <t>通信制・紀美野町の本校。法人本部（和歌山市）は073-474-2828</t>
+        </is>
+      </c>
+      <c r="N1068" s="11" t="inlineStr">
+        <is>
+          <t>https://keifu.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1068" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="4" t="n">
+        <v>1065</v>
+      </c>
+      <c r="B1069" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1069" s="5" t="inlineStr">
+        <is>
+          <t>高野町</t>
+        </is>
+      </c>
+      <c r="D1069" s="5" t="inlineStr">
+        <is>
+          <t>高野山高等学校</t>
+        </is>
+      </c>
+      <c r="E1069" s="6" t="inlineStr">
+        <is>
+          <t>0736-56-2204</t>
+        </is>
+      </c>
+      <c r="F1069" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1069" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1069" s="8" t="n"/>
+      <c r="I1069" s="9" t="n"/>
+      <c r="J1069" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1069" s="8" t="n"/>
+      <c r="L1069" s="9" t="n"/>
+      <c r="M1069" s="10" t="n"/>
+      <c r="N1069" s="11" t="inlineStr">
+        <is>
+          <t>https://www.koyasan-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1069" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="4" t="n">
+        <v>1066</v>
+      </c>
+      <c r="B1070" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1070" s="5" t="inlineStr">
+        <is>
+          <t>和歌山市</t>
+        </is>
+      </c>
+      <c r="D1070" s="5" t="inlineStr">
+        <is>
+          <t>智辯学園和歌山高等学校</t>
+        </is>
+      </c>
+      <c r="E1070" s="6" t="inlineStr">
+        <is>
+          <t>073-479-2811</t>
+        </is>
+      </c>
+      <c r="F1070" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1070" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1070" s="8" t="n"/>
+      <c r="I1070" s="9" t="n"/>
+      <c r="J1070" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1070" s="8" t="n"/>
+      <c r="L1070" s="9" t="n"/>
+      <c r="M1070" s="10" t="inlineStr">
+        <is>
+          <t>中学校併設</t>
+        </is>
+      </c>
+      <c r="N1070" s="11" t="inlineStr">
+        <is>
+          <t>https://www.chiben.ac.jp/wakayama/</t>
+        </is>
+      </c>
+      <c r="O1070" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="4" t="n">
+        <v>1067</v>
+      </c>
+      <c r="B1071" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1071" s="5" t="inlineStr">
+        <is>
+          <t>橋本市</t>
+        </is>
+      </c>
+      <c r="D1071" s="5" t="inlineStr">
+        <is>
+          <t>初芝橋本高等学校</t>
+        </is>
+      </c>
+      <c r="E1071" s="6" t="inlineStr">
+        <is>
+          <t>0736-37-5600</t>
+        </is>
+      </c>
+      <c r="F1071" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1071" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1071" s="8" t="n"/>
+      <c r="I1071" s="9" t="n"/>
+      <c r="J1071" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1071" s="8" t="n"/>
+      <c r="L1071" s="9" t="n"/>
+      <c r="M1071" s="10" t="inlineStr">
+        <is>
+          <t>2025年4月に運営法人が利晶学園へ改称（校名は変更なし）</t>
+        </is>
+      </c>
+      <c r="N1071" s="11" t="inlineStr">
+        <is>
+          <t>https://www.rishogakuen.ed.jp/hatsuhashi/guide/enkaku.html</t>
+        </is>
+      </c>
+      <c r="O1071" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="4" t="n">
+        <v>1068</v>
+      </c>
+      <c r="B1072" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1072" s="5" t="inlineStr">
+        <is>
+          <t>和歌山市</t>
+        </is>
+      </c>
+      <c r="D1072" s="5" t="inlineStr">
+        <is>
+          <t>和歌山信愛高等学校</t>
+        </is>
+      </c>
+      <c r="E1072" s="6" t="inlineStr">
+        <is>
+          <t>073-424-1141</t>
+        </is>
+      </c>
+      <c r="F1072" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1072" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1072" s="8" t="n"/>
+      <c r="I1072" s="9" t="n"/>
+      <c r="J1072" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1072" s="8" t="n"/>
+      <c r="L1072" s="9" t="n"/>
+      <c r="M1072" s="10" t="inlineStr">
+        <is>
+          <t>中学校併設</t>
+        </is>
+      </c>
+      <c r="N1072" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shin-ai.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1072" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="4" t="n">
+        <v>1069</v>
+      </c>
+      <c r="B1073" s="5" t="inlineStr">
+        <is>
+          <t>和歌山県</t>
+        </is>
+      </c>
+      <c r="C1073" s="5" t="inlineStr">
+        <is>
+          <t>日高川町</t>
+        </is>
+      </c>
+      <c r="D1073" s="5" t="inlineStr">
+        <is>
+          <t>和歌山南陵高等学校</t>
+        </is>
+      </c>
+      <c r="E1073" s="6" t="inlineStr">
+        <is>
+          <t>0738-53-0316</t>
+        </is>
+      </c>
+      <c r="F1073" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1073" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1073" s="8" t="n"/>
+      <c r="I1073" s="9" t="n"/>
+      <c r="J1073" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1073" s="8" t="n"/>
+      <c r="L1073" s="9" t="n"/>
+      <c r="M1073" s="10" t="inlineStr">
+        <is>
           <t>経営難で一時募集停止命令→2024年11月解除、募集再開済み</t>
         </is>
       </c>
-      <c r="N1019" s="11" t="inlineStr">
+      <c r="N1073" s="11" t="inlineStr">
         <is>
           <t>https://w-nanryo.ed.jp/contact/</t>
         </is>
       </c>
-      <c r="O1019" s="12" t="inlineStr">
+      <c r="O1073" s="12" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O1019"/>
-  <conditionalFormatting sqref="A5:O1019">
+  <autoFilter ref="A4:O1073"/>
+  <conditionalFormatting sqref="A5:O1073">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -60360,10 +63474,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J1019" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J1073" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H1019 K5:K1019" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H1073 K5:K1073" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -61383,6 +64497,60 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1017" r:id="rId1013"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1018" r:id="rId1014"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1019" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1020" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1021" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1022" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1023" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1024" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1025" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1026" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1027" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1028" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1029" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1030" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1031" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1032" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1033" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1034" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1035" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1036" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1037" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1038" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1039" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1040" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1041" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1042" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1043" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1044" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1045" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1046" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1047" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1048" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1049" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1050" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1051" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1052" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1053" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1054" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1055" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1056" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1057" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1058" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1059" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1060" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1061" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1062" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1063" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1064" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1065" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1066" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1067" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1068" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1069" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1070" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1071" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1072" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1073" r:id="rId1069"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -61395,7 +64563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -61482,43 +64650,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A4,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A4,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1019,A4,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A4,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1073,A4,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A4,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A4,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61529,43 +64697,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A5,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A5,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1019,A5,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A5,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1073,A5,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A5,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A5,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61576,43 +64744,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A6,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A6,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1019,A6,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A6,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1073,A6,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A6,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A6,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61623,43 +64791,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A7,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A7,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1019,A7,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A7,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1073,A7,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A7,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A7,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61670,43 +64838,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A8,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A8,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1019,A8,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A8,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1073,A8,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A8,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A8,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61717,43 +64885,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A9,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A9,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1019,A9,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A9,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1073,A9,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A9,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A9,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61764,43 +64932,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A10,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A10,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1019,A10,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A10,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1073,A10,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A10,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A10,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61811,43 +64979,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A11,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A11,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1019,A11,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A11,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1073,A11,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A11,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A11,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61858,43 +65026,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A12,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A12,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1019,A12,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A12,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1073,A12,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A12,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A12,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61905,43 +65073,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A13,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A13,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1019,A13,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A13,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1073,A13,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A13,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A13,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61952,43 +65120,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A14,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A14,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1019,A14,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A14,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1073,A14,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A14,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A14,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -61999,43 +65167,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A15,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A15,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1019,A15,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A15,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1073,A15,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A15,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A15,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62046,43 +65214,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A16,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A16,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1019,A16,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A16,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1073,A16,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A16,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A16,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62093,43 +65261,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A17,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A17,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1019,A17,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A17,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1073,A17,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A17,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A17,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62140,43 +65308,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A18,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A18,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1019,A18,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A18,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1073,A18,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A18,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A18,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62187,43 +65355,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A19,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A19,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1019,A19,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A19,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1073,A19,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A19,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A19,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62234,43 +65402,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A20,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A20,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1019,A20,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A20,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1073,A20,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A20,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A20,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62281,43 +65449,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A21,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A21,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1019,A21,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A21,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1073,A21,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A21,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A21,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62328,43 +65496,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A22,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A22,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1019,A22,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A22,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1073,A22,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A22,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A22,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62375,43 +65543,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A23,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A23,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1019,A23,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A23,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1073,A23,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A23,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A23,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62422,43 +65590,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A24,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A24,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1019,A24,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A24,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1073,A24,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A24,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A24,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62469,43 +65637,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A25,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A25,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1019,A25,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A25,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1073,A25,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A25,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A25,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62516,43 +65684,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A26,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A26,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1019,A26,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A26,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1073,A26,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A26,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A26,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62563,43 +65731,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A27,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A27,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1019,A27,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A27,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1073,A27,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A27,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A27,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62610,43 +65778,43 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A28,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A28,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1019,A28,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A28,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1073,A28,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A28,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A28,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62657,43 +65825,43 @@
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A29)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A29,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A29,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1019,A29,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A29,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1073,A29,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A29,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A29,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -62704,184 +65872,231 @@
         </is>
       </c>
       <c r="B30" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A30)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A30)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A30,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A30,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1019,A30,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A30,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1073,A30,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A30,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A30,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>奈良県</t>
+          <t>兵庫県</t>
         </is>
       </c>
       <c r="B31" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A31)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A31)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A31,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A31,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1019,A31,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A31,'架電リスト'!$J$5:$J$1019,"")</f>
+        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1073,A31,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A31,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
       <c r="J31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A31,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
+          <t>奈良県</t>
+        </is>
+      </c>
+      <c r="B32" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A32)</f>
+        <v/>
+      </c>
+      <c r="C32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A32,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D32" s="16">
+        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1073,A32,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A32,'架電リスト'!$J$5:$J$1073,"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <v/>
+      </c>
+      <c r="K32" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
           <t>和歌山県</t>
         </is>
       </c>
-      <c r="B32" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1019,A32)</f>
+      <c r="B33" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A33)</f>
         <v/>
       </c>
-      <c r="C32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,A32,'架電リスト'!$E$5:$E$1019,"&lt;&gt;")</f>
+      <c r="C33" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A33,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D32" s="16">
-        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1019,A32,'架電リスト'!$J$5:$J$1019,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1019,A32,'架電リスト'!$J$5:$J$1019,"")</f>
+      <c r="D33" s="16">
+        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1073,A33,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A33,'架電リスト'!$J$5:$J$1073,"")</f>
         <v/>
       </c>
-      <c r="E32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"不在・折返し待ち")</f>
+      <c r="E33" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"担当者不在")</f>
+      <c r="F33" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"資料送付")</f>
+      <c r="G33" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
         <v/>
       </c>
-      <c r="H32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"アポ獲得")</f>
+      <c r="H33" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"検討中")</f>
+      <c r="I33" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"検討中")</f>
         <v/>
       </c>
-      <c r="J32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"NG")</f>
+      <c r="J33" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"NG")</f>
         <v/>
       </c>
-      <c r="K32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1019,$A32,'架電リスト'!$J$5:$J$1019,"番号不明")</f>
+      <c r="K33" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B33" s="17">
-        <f>SUM(B4:B32)</f>
+      <c r="B34" s="17">
+        <f>SUM(B4:B33)</f>
         <v/>
       </c>
-      <c r="C33" s="17">
-        <f>SUM(C4:C32)</f>
+      <c r="C34" s="17">
+        <f>SUM(C4:C33)</f>
         <v/>
       </c>
-      <c r="D33" s="17">
-        <f>SUM(D4:D32)</f>
+      <c r="D34" s="17">
+        <f>SUM(D4:D33)</f>
         <v/>
       </c>
-      <c r="E33" s="17">
-        <f>SUM(E4:E32)</f>
+      <c r="E34" s="17">
+        <f>SUM(E4:E33)</f>
         <v/>
       </c>
-      <c r="F33" s="17">
-        <f>SUM(F4:F32)</f>
+      <c r="F34" s="17">
+        <f>SUM(F4:F33)</f>
         <v/>
       </c>
-      <c r="G33" s="17">
-        <f>SUM(G4:G32)</f>
+      <c r="G34" s="17">
+        <f>SUM(G4:G33)</f>
         <v/>
       </c>
-      <c r="H33" s="17">
-        <f>SUM(H4:H32)</f>
+      <c r="H34" s="17">
+        <f>SUM(H4:H33)</f>
         <v/>
       </c>
-      <c r="I33" s="17">
-        <f>SUM(I4:I32)</f>
+      <c r="I34" s="17">
+        <f>SUM(I4:I33)</f>
         <v/>
       </c>
-      <c r="J33" s="17">
-        <f>SUM(J4:J32)</f>
+      <c r="J34" s="17">
+        <f>SUM(J4:J33)</f>
         <v/>
       </c>
-      <c r="K33" s="17">
-        <f>SUM(K4:K32)</f>
+      <c r="K34" s="17">
+        <f>SUM(K4:K33)</f>
         <v/>
       </c>
     </row>
@@ -62971,7 +66186,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・29都道府県、1015校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・30都道府県、1069校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1073</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1096</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O1073"/>
+  <dimension ref="A1:O1096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（30都道府県／1069校）</t>
+          <t>私立高等学校 架電リスト（31都道府県／1092校）</t>
         </is>
       </c>
     </row>
@@ -63463,9 +63463,1346 @@
         </is>
       </c>
     </row>
+    <row r="1074">
+      <c r="A1074" s="4" t="n">
+        <v>1070</v>
+      </c>
+      <c r="B1074" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1074" s="5" t="inlineStr">
+        <is>
+          <t>岡山市東区</t>
+        </is>
+      </c>
+      <c r="D1074" s="5" t="inlineStr">
+        <is>
+          <t>岡山学芸館高等学校</t>
+        </is>
+      </c>
+      <c r="E1074" s="6" t="inlineStr">
+        <is>
+          <t>086-942-3864</t>
+        </is>
+      </c>
+      <c r="F1074" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1074" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1074" s="8" t="n"/>
+      <c r="I1074" s="9" t="n"/>
+      <c r="J1074" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1074" s="8" t="n"/>
+      <c r="L1074" s="9" t="n"/>
+      <c r="M1074" s="10" t="inlineStr">
+        <is>
+          <t>通信制課程も同じ番号</t>
+        </is>
+      </c>
+      <c r="N1074" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gakugeikan.ed.jp/contact/index.html</t>
+        </is>
+      </c>
+      <c r="O1074" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="4" t="n">
+        <v>1071</v>
+      </c>
+      <c r="B1075" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1075" s="5" t="inlineStr">
+        <is>
+          <t>新見市</t>
+        </is>
+      </c>
+      <c r="D1075" s="5" t="inlineStr">
+        <is>
+          <t>岡山県共生高等学校</t>
+        </is>
+      </c>
+      <c r="E1075" s="6" t="inlineStr">
+        <is>
+          <t>0867-72-0526</t>
+        </is>
+      </c>
+      <c r="F1075" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1075" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1075" s="8" t="n"/>
+      <c r="I1075" s="9" t="n"/>
+      <c r="J1075" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1075" s="8" t="n"/>
+      <c r="L1075" s="9" t="n"/>
+      <c r="M1075" s="10" t="inlineStr">
+        <is>
+          <t>0867-72-8032はFAX</t>
+        </is>
+      </c>
+      <c r="N1075" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kyousei.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1075" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="4" t="n">
+        <v>1072</v>
+      </c>
+      <c r="B1076" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1076" s="5" t="inlineStr">
+        <is>
+          <t>倉敷市</t>
+        </is>
+      </c>
+      <c r="D1076" s="5" t="inlineStr">
+        <is>
+          <t>岡山県作陽高等学校</t>
+        </is>
+      </c>
+      <c r="E1076" s="6" t="inlineStr">
+        <is>
+          <t>086-441-1281</t>
+        </is>
+      </c>
+      <c r="F1076" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1076" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1076" s="8" t="n"/>
+      <c r="I1076" s="9" t="n"/>
+      <c r="J1076" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1076" s="8" t="n"/>
+      <c r="L1076" s="9" t="n"/>
+      <c r="M1076" s="10" t="inlineStr">
+        <is>
+          <t>2023年4月に倉敷市玉島へ移転し「作陽学園高等学校」に校名変更。津山の旧番号0868-23-2188は使用不可の可能性</t>
+        </is>
+      </c>
+      <c r="N1076" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sakuyo-h.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1076" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="4" t="n">
+        <v>1073</v>
+      </c>
+      <c r="B1077" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1077" s="5" t="inlineStr">
+        <is>
+          <t>津山市</t>
+        </is>
+      </c>
+      <c r="D1077" s="5" t="inlineStr">
+        <is>
+          <t>岡山県美作高等学校</t>
+        </is>
+      </c>
+      <c r="E1077" s="6" t="inlineStr">
+        <is>
+          <t>0868-22-4838</t>
+        </is>
+      </c>
+      <c r="F1077" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1077" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1077" s="8" t="n"/>
+      <c r="I1077" s="9" t="n"/>
+      <c r="J1077" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1077" s="8" t="n"/>
+      <c r="L1077" s="9" t="n"/>
+      <c r="M1077" s="10" t="inlineStr">
+        <is>
+          <t>全日制の番号。通信制課程は0868-23-3116</t>
+        </is>
+      </c>
+      <c r="N1077" s="11" t="inlineStr">
+        <is>
+          <t>https://mimasaka.jp/gakuen/houjin.html</t>
+        </is>
+      </c>
+      <c r="O1077" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="4" t="n">
+        <v>1074</v>
+      </c>
+      <c r="B1078" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1078" s="5" t="inlineStr">
+        <is>
+          <t>岡山市南区</t>
+        </is>
+      </c>
+      <c r="D1078" s="5" t="inlineStr">
+        <is>
+          <t>岡山高等学校</t>
+        </is>
+      </c>
+      <c r="E1078" s="6" t="inlineStr">
+        <is>
+          <t>086-282-6336</t>
+        </is>
+      </c>
+      <c r="F1078" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1078" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1078" s="8" t="n"/>
+      <c r="I1078" s="9" t="n"/>
+      <c r="J1078" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1078" s="8" t="n"/>
+      <c r="L1078" s="9" t="n"/>
+      <c r="M1078" s="10" t="inlineStr">
+        <is>
+          <t>中高一貫</t>
+        </is>
+      </c>
+      <c r="N1078" s="11" t="inlineStr">
+        <is>
+          <t>https://www.okayama-h.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1078" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="4" t="n">
+        <v>1075</v>
+      </c>
+      <c r="B1079" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1079" s="5" t="inlineStr">
+        <is>
+          <t>浅口市</t>
+        </is>
+      </c>
+      <c r="D1079" s="5" t="inlineStr">
+        <is>
+          <t>おかやま山陽高等学校</t>
+        </is>
+      </c>
+      <c r="E1079" s="6" t="inlineStr">
+        <is>
+          <t>0865-44-3100</t>
+        </is>
+      </c>
+      <c r="F1079" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1079" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1079" s="8" t="n"/>
+      <c r="I1079" s="9" t="n"/>
+      <c r="J1079" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1079" s="8" t="n"/>
+      <c r="L1079" s="9" t="n"/>
+      <c r="M1079" s="10" t="inlineStr">
+        <is>
+          <t>教員室直通は0865-44-7149</t>
+        </is>
+      </c>
+      <c r="N1079" s="11" t="inlineStr">
+        <is>
+          <t>https://www.okayama-sanyo-hs.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1079" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="4" t="n">
+        <v>1076</v>
+      </c>
+      <c r="B1080" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1080" s="5" t="inlineStr">
+        <is>
+          <t>岡山市北区</t>
+        </is>
+      </c>
+      <c r="D1080" s="5" t="inlineStr">
+        <is>
+          <t>岡山商科大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E1080" s="6" t="inlineStr">
+        <is>
+          <t>086-252-3407</t>
+        </is>
+      </c>
+      <c r="F1080" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1080" s="5" t="inlineStr">
+        <is>
+          <t>専門学科・総合学科</t>
+        </is>
+      </c>
+      <c r="H1080" s="8" t="n"/>
+      <c r="I1080" s="9" t="n"/>
+      <c r="J1080" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1080" s="8" t="n"/>
+      <c r="L1080" s="9" t="n"/>
+      <c r="M1080" s="10" t="n"/>
+      <c r="N1080" s="11" t="inlineStr">
+        <is>
+          <t>https://www.osu-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1080" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="4" t="n">
+        <v>1077</v>
+      </c>
+      <c r="B1081" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1081" s="5" t="inlineStr">
+        <is>
+          <t>赤磐市</t>
+        </is>
+      </c>
+      <c r="D1081" s="5" t="inlineStr">
+        <is>
+          <t>岡山白陵高等学校</t>
+        </is>
+      </c>
+      <c r="E1081" s="6" t="inlineStr">
+        <is>
+          <t>086-995-1255</t>
+        </is>
+      </c>
+      <c r="F1081" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1081" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1081" s="8" t="n"/>
+      <c r="I1081" s="9" t="n"/>
+      <c r="J1081" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1081" s="8" t="n"/>
+      <c r="L1081" s="9" t="n"/>
+      <c r="M1081" s="10" t="inlineStr">
+        <is>
+          <t>中学校併設</t>
+        </is>
+      </c>
+      <c r="N1081" s="11" t="inlineStr">
+        <is>
+          <t>https://www.okahaku.ed.jp/access_inquiry/</t>
+        </is>
+      </c>
+      <c r="O1081" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="4" t="n">
+        <v>1078</v>
+      </c>
+      <c r="B1082" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1082" s="5" t="inlineStr">
+        <is>
+          <t>岡山市北区</t>
+        </is>
+      </c>
+      <c r="D1082" s="5" t="inlineStr">
+        <is>
+          <t>岡山理科大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E1082" s="6" t="inlineStr">
+        <is>
+          <t>086-256-8511</t>
+        </is>
+      </c>
+      <c r="F1082" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1082" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1082" s="8" t="n"/>
+      <c r="I1082" s="9" t="n"/>
+      <c r="J1082" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1082" s="8" t="n"/>
+      <c r="L1082" s="9" t="n"/>
+      <c r="M1082" s="10" t="inlineStr">
+        <is>
+          <t>通信制課程直通は086-256-8562</t>
+        </is>
+      </c>
+      <c r="N1082" s="11" t="inlineStr">
+        <is>
+          <t>https://okayama.ridaifu.net/contact/</t>
+        </is>
+      </c>
+      <c r="O1082" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="4" t="n">
+        <v>1079</v>
+      </c>
+      <c r="B1083" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1083" s="5" t="inlineStr">
+        <is>
+          <t>笠岡市</t>
+        </is>
+      </c>
+      <c r="D1083" s="5" t="inlineStr">
+        <is>
+          <t>岡山龍谷高等学校</t>
+        </is>
+      </c>
+      <c r="E1083" s="6" t="inlineStr">
+        <is>
+          <t>0865-63-2525</t>
+        </is>
+      </c>
+      <c r="F1083" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1083" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1083" s="8" t="n"/>
+      <c r="I1083" s="9" t="n"/>
+      <c r="J1083" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1083" s="8" t="n"/>
+      <c r="L1083" s="9" t="n"/>
+      <c r="M1083" s="10" t="inlineStr">
+        <is>
+          <t>職員室は0865-63-2526</t>
+        </is>
+      </c>
+      <c r="N1083" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ok-ryukoku.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1083" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="4" t="n">
+        <v>1080</v>
+      </c>
+      <c r="B1084" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1084" s="5" t="inlineStr">
+        <is>
+          <t>倉敷市</t>
+        </is>
+      </c>
+      <c r="D1084" s="5" t="inlineStr">
+        <is>
+          <t>川崎医科大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E1084" s="6" t="inlineStr">
+        <is>
+          <t>086-462-3666</t>
+        </is>
+      </c>
+      <c r="F1084" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1084" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1084" s="8" t="n"/>
+      <c r="I1084" s="9" t="n"/>
+      <c r="J1084" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1084" s="8" t="n"/>
+      <c r="L1084" s="9" t="n"/>
+      <c r="M1084" s="10" t="n"/>
+      <c r="N1084" s="11" t="inlineStr">
+        <is>
+          <t>https://s.kawasaki-m.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1084" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="4" t="n">
+        <v>1081</v>
+      </c>
+      <c r="B1085" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1085" s="5" t="inlineStr">
+        <is>
+          <t>岡山市北区</t>
+        </is>
+      </c>
+      <c r="D1085" s="5" t="inlineStr">
+        <is>
+          <t>関西高等学校</t>
+        </is>
+      </c>
+      <c r="E1085" s="6" t="inlineStr">
+        <is>
+          <t>086-252-5121</t>
+        </is>
+      </c>
+      <c r="F1085" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1085" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1085" s="8" t="n"/>
+      <c r="I1085" s="9" t="n"/>
+      <c r="J1085" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1085" s="8" t="n"/>
+      <c r="L1085" s="9" t="n"/>
+      <c r="M1085" s="10" t="n"/>
+      <c r="N1085" s="11" t="inlineStr">
+        <is>
+          <t>https://kanzei.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1085" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="4" t="n">
+        <v>1082</v>
+      </c>
+      <c r="B1086" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1086" s="5" t="inlineStr">
+        <is>
+          <t>吉備中央町</t>
+        </is>
+      </c>
+      <c r="D1086" s="5" t="inlineStr">
+        <is>
+          <t>吉備高原学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1086" s="6" t="inlineStr">
+        <is>
+          <t>0866-56-8211</t>
+        </is>
+      </c>
+      <c r="F1086" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1086" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1086" s="8" t="n"/>
+      <c r="I1086" s="9" t="n"/>
+      <c r="J1086" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1086" s="8" t="n"/>
+      <c r="L1086" s="9" t="n"/>
+      <c r="M1086" s="10" t="inlineStr">
+        <is>
+          <t>全寮制</t>
+        </is>
+      </c>
+      <c r="N1086" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kibikogengakuen.ed.jp/inquiry/form/</t>
+        </is>
+      </c>
+      <c r="O1086" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="4" t="n">
+        <v>1083</v>
+      </c>
+      <c r="B1087" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1087" s="5" t="inlineStr">
+        <is>
+          <t>倉敷市</t>
+        </is>
+      </c>
+      <c r="D1087" s="5" t="inlineStr">
+        <is>
+          <t>倉敷高等学校</t>
+        </is>
+      </c>
+      <c r="E1087" s="6" t="inlineStr">
+        <is>
+          <t>086-462-9000</t>
+        </is>
+      </c>
+      <c r="F1087" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1087" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1087" s="8" t="n"/>
+      <c r="I1087" s="9" t="n"/>
+      <c r="J1087" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1087" s="8" t="n"/>
+      <c r="L1087" s="9" t="n"/>
+      <c r="M1087" s="10" t="inlineStr">
+        <is>
+          <t>岡山県私学協会の一覧とも一致</t>
+        </is>
+      </c>
+      <c r="N1087" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kurashiki.ac.jp/news/</t>
+        </is>
+      </c>
+      <c r="O1087" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="4" t="n">
+        <v>1084</v>
+      </c>
+      <c r="B1088" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1088" s="5" t="inlineStr">
+        <is>
+          <t>倉敷市</t>
+        </is>
+      </c>
+      <c r="D1088" s="5" t="inlineStr">
+        <is>
+          <t>倉敷翠松高等学校</t>
+        </is>
+      </c>
+      <c r="E1088" s="6" t="inlineStr">
+        <is>
+          <t>086-422-3565</t>
+        </is>
+      </c>
+      <c r="F1088" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1088" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1088" s="8" t="n"/>
+      <c r="I1088" s="9" t="n"/>
+      <c r="J1088" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1088" s="8" t="n"/>
+      <c r="L1088" s="9" t="n"/>
+      <c r="M1088" s="10" t="inlineStr">
+        <is>
+          <t>教務室086-422-3570、専攻科086-427-0941</t>
+        </is>
+      </c>
+      <c r="N1088" s="11" t="inlineStr">
+        <is>
+          <t>https://www.suisho.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1088" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="4" t="n">
+        <v>1085</v>
+      </c>
+      <c r="B1089" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1089" s="5" t="inlineStr">
+        <is>
+          <t>井原市</t>
+        </is>
+      </c>
+      <c r="D1089" s="5" t="inlineStr">
+        <is>
+          <t>興譲館高等学校</t>
+        </is>
+      </c>
+      <c r="E1089" s="6" t="inlineStr">
+        <is>
+          <t>0866-62-0124</t>
+        </is>
+      </c>
+      <c r="F1089" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1089" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1089" s="8" t="n"/>
+      <c r="I1089" s="9" t="n"/>
+      <c r="J1089" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1089" s="8" t="n"/>
+      <c r="L1089" s="9" t="n"/>
+      <c r="M1089" s="10" t="inlineStr">
+        <is>
+          <t>井原市の本校。通信制課程は0120-445033</t>
+        </is>
+      </c>
+      <c r="N1089" s="11" t="inlineStr">
+        <is>
+          <t>https://kojokan-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1089" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="4" t="n">
+        <v>1086</v>
+      </c>
+      <c r="B1090" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1090" s="5" t="inlineStr">
+        <is>
+          <t>浅口市</t>
+        </is>
+      </c>
+      <c r="D1090" s="5" t="inlineStr">
+        <is>
+          <t>金光学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1090" s="6" t="inlineStr">
+        <is>
+          <t>0865-42-3131</t>
+        </is>
+      </c>
+      <c r="F1090" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1090" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1090" s="8" t="n"/>
+      <c r="I1090" s="9" t="n"/>
+      <c r="J1090" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1090" s="8" t="n"/>
+      <c r="L1090" s="9" t="n"/>
+      <c r="M1090" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1090" s="11" t="inlineStr">
+        <is>
+          <t>https://www.konkougakuen.net/high/</t>
+        </is>
+      </c>
+      <c r="O1090" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="4" t="n">
+        <v>1087</v>
+      </c>
+      <c r="B1091" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1091" s="5" t="inlineStr">
+        <is>
+          <t>岡山市中区</t>
+        </is>
+      </c>
+      <c r="D1091" s="5" t="inlineStr">
+        <is>
+          <t>山陽学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1091" s="6" t="inlineStr">
+        <is>
+          <t>086-272-1181</t>
+        </is>
+      </c>
+      <c r="F1091" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1091" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1091" s="8" t="n"/>
+      <c r="I1091" s="9" t="n"/>
+      <c r="J1091" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1091" s="8" t="n"/>
+      <c r="L1091" s="9" t="n"/>
+      <c r="M1091" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1091" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sanyogakuen.ed.jp/school/access</t>
+        </is>
+      </c>
+      <c r="O1091" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="4" t="n">
+        <v>1088</v>
+      </c>
+      <c r="B1092" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1092" s="5" t="inlineStr">
+        <is>
+          <t>岡山市北区</t>
+        </is>
+      </c>
+      <c r="D1092" s="5" t="inlineStr">
+        <is>
+          <t>就実高等学校</t>
+        </is>
+      </c>
+      <c r="E1092" s="6" t="inlineStr">
+        <is>
+          <t>086-225-1326</t>
+        </is>
+      </c>
+      <c r="F1092" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1092" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1092" s="8" t="n"/>
+      <c r="I1092" s="9" t="n"/>
+      <c r="J1092" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1092" s="8" t="n"/>
+      <c r="L1092" s="9" t="n"/>
+      <c r="M1092" s="10" t="n"/>
+      <c r="N1092" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shujitsu-gakuen.jp/contact/index.html</t>
+        </is>
+      </c>
+      <c r="O1092" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="4" t="n">
+        <v>1089</v>
+      </c>
+      <c r="B1093" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1093" s="5" t="inlineStr">
+        <is>
+          <t>倉敷市</t>
+        </is>
+      </c>
+      <c r="D1093" s="5" t="inlineStr">
+        <is>
+          <t>清心女子高等学校（岡山県）</t>
+        </is>
+      </c>
+      <c r="E1093" s="6" t="inlineStr">
+        <is>
+          <t>086-462-1661</t>
+        </is>
+      </c>
+      <c r="F1093" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1093" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1093" s="8" t="n"/>
+      <c r="I1093" s="9" t="n"/>
+      <c r="J1093" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1093" s="8" t="n"/>
+      <c r="L1093" s="9" t="n"/>
+      <c r="M1093" s="10" t="inlineStr">
+        <is>
+          <t>ノートルダム清心学園（倉敷市）。中学校併設</t>
+        </is>
+      </c>
+      <c r="N1093" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nd-seishin.ac.jp/school/access/</t>
+        </is>
+      </c>
+      <c r="O1093" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="4" t="n">
+        <v>1090</v>
+      </c>
+      <c r="B1094" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1094" s="5" t="inlineStr">
+        <is>
+          <t>岡山市北区</t>
+        </is>
+      </c>
+      <c r="D1094" s="5" t="inlineStr">
+        <is>
+          <t>創志学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1094" s="6" t="inlineStr">
+        <is>
+          <t>086-252-2101</t>
+        </is>
+      </c>
+      <c r="F1094" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1094" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1094" s="8" t="n"/>
+      <c r="I1094" s="9" t="n"/>
+      <c r="J1094" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1094" s="8" t="n"/>
+      <c r="L1094" s="9" t="n"/>
+      <c r="M1094" s="10" t="inlineStr">
+        <is>
+          <t>入試広報室は0120-151752</t>
+        </is>
+      </c>
+      <c r="N1094" s="11" t="inlineStr">
+        <is>
+          <t>https://www.soshigakuen.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1094" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="4" t="n">
+        <v>1091</v>
+      </c>
+      <c r="B1095" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1095" s="5" t="inlineStr">
+        <is>
+          <t>高梁市</t>
+        </is>
+      </c>
+      <c r="D1095" s="5" t="inlineStr">
+        <is>
+          <t>方谷學舎高等学校</t>
+        </is>
+      </c>
+      <c r="E1095" s="6" t="inlineStr">
+        <is>
+          <t>0866-22-2205</t>
+        </is>
+      </c>
+      <c r="F1095" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1095" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1095" s="8" t="n"/>
+      <c r="I1095" s="9" t="n"/>
+      <c r="J1095" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1095" s="8" t="n"/>
+      <c r="L1095" s="9" t="n"/>
+      <c r="M1095" s="10" t="inlineStr">
+        <is>
+          <t>2023年6月に「岡山県高梁日新高等学校」から校名変更。事務室番号（教務室は0866-56-0015）</t>
+        </is>
+      </c>
+      <c r="N1095" s="11" t="inlineStr">
+        <is>
+          <t>https://www.houkoku-gakusha.ed.jp/introduction/</t>
+        </is>
+      </c>
+      <c r="O1095" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="4" t="n">
+        <v>1092</v>
+      </c>
+      <c r="B1096" s="5" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="C1096" s="5" t="inlineStr">
+        <is>
+          <t>岡山市北区</t>
+        </is>
+      </c>
+      <c r="D1096" s="5" t="inlineStr">
+        <is>
+          <t>明誠学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1096" s="6" t="inlineStr">
+        <is>
+          <t>086-252-5247</t>
+        </is>
+      </c>
+      <c r="F1096" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1096" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1096" s="8" t="n"/>
+      <c r="I1096" s="9" t="n"/>
+      <c r="J1096" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1096" s="8" t="n"/>
+      <c r="L1096" s="9" t="n"/>
+      <c r="M1096" s="10" t="n"/>
+      <c r="N1096" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meiseigakuin.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1096" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O1073"/>
-  <conditionalFormatting sqref="A5:O1073">
+  <autoFilter ref="A4:O1096"/>
+  <conditionalFormatting sqref="A5:O1096">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -63474,10 +64811,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J1073" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J1096" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H1073 K5:K1073" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H1096 K5:K1096" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -64551,6 +65888,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1071" r:id="rId1067"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1072" r:id="rId1068"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1073" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1074" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1075" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1076" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1077" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1078" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1079" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1080" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1081" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1082" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1083" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1084" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1085" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1086" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1087" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1088" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1089" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1090" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1091" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1092" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1093" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1094" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1095" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1096" r:id="rId1092"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -64563,7 +65923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -64650,43 +66010,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A4,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A4,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1073,A4,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A4,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1096,A4,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A4,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A4,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -64697,43 +66057,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A5,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A5,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1073,A5,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A5,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1096,A5,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A5,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A5,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -64744,43 +66104,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A6,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A6,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1073,A6,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A6,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1096,A6,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A6,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A6,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -64791,43 +66151,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A7,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A7,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1073,A7,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A7,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1096,A7,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A7,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A7,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -64838,43 +66198,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A8,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A8,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1073,A8,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A8,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1096,A8,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A8,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A8,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -64885,43 +66245,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A9,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A9,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1073,A9,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A9,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1096,A9,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A9,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A9,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -64932,43 +66292,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A10,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A10,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1073,A10,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A10,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1096,A10,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A10,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A10,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -64979,43 +66339,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A11,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A11,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1073,A11,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A11,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1096,A11,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A11,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A11,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65026,43 +66386,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A12,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A12,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1073,A12,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A12,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1096,A12,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A12,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A12,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65073,43 +66433,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A13,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A13,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1073,A13,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A13,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1096,A13,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A13,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A13,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65120,43 +66480,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A14,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A14,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1073,A14,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A14,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1096,A14,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A14,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A14,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65167,43 +66527,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A15,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A15,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1073,A15,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A15,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1096,A15,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A15,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A15,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65214,43 +66574,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A16,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A16,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1073,A16,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A16,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1096,A16,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A16,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A16,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65261,43 +66621,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A17,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A17,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1073,A17,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A17,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1096,A17,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A17,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A17,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65308,43 +66668,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A18,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A18,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1073,A18,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A18,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1096,A18,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A18,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A18,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65355,43 +66715,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A19,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A19,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1073,A19,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A19,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1096,A19,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A19,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A19,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65402,43 +66762,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A20,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A20,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1073,A20,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A20,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1096,A20,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A20,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A20,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65449,43 +66809,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A21,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A21,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1073,A21,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A21,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1096,A21,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A21,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A21,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65496,43 +66856,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A22,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A22,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1073,A22,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A22,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1096,A22,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A22,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A22,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65543,43 +66903,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A23,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A23,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1073,A23,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A23,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1096,A23,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A23,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A23,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65590,43 +66950,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A24,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A24,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1073,A24,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A24,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1096,A24,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A24,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A24,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65637,43 +66997,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A25,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A25,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1073,A25,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A25,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1096,A25,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A25,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A25,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65684,43 +67044,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A26,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A26,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1073,A26,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A26,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1096,A26,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A26,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A26,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65731,43 +67091,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A27,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A27,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1073,A27,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A27,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1096,A27,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A27,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A27,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65778,43 +67138,43 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A28,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A28,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1073,A28,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A28,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1096,A28,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A28,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A28,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65825,43 +67185,43 @@
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A29)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A29,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A29,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1073,A29,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A29,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1096,A29,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A29,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A29,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65872,43 +67232,43 @@
         </is>
       </c>
       <c r="B30" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A30)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A30)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A30,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A30,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1073,A30,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A30,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1096,A30,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A30,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A30,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65919,43 +67279,43 @@
         </is>
       </c>
       <c r="B31" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A31)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A31)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A31,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A31,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1073,A31,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A31,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1096,A31,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A31,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A31,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -65966,43 +67326,43 @@
         </is>
       </c>
       <c r="B32" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A32)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A32)</f>
         <v/>
       </c>
       <c r="C32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A32,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A32,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1073,A32,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A32,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1096,A32,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A32,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A32,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66013,90 +67373,137 @@
         </is>
       </c>
       <c r="B33" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1073,A33)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A33)</f>
         <v/>
       </c>
       <c r="C33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,A33,'架電リスト'!$E$5:$E$1073,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A33,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D33" s="16">
-        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1073,A33,'架電リスト'!$J$5:$J$1073,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1073,A33,'架電リスト'!$J$5:$J$1073,"")</f>
+        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1096,A33,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A33,'架電リスト'!$J$5:$J$1096,"")</f>
         <v/>
       </c>
       <c r="E33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"検討中")</f>
         <v/>
       </c>
       <c r="J33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"NG")</f>
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1073,$A33,'架電リスト'!$J$5:$J$1073,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>岡山県</t>
+        </is>
+      </c>
+      <c r="B34" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A34)</f>
+        <v/>
+      </c>
+      <c r="C34" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A34,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D34" s="16">
+        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1096,A34,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A34,'架電リスト'!$J$5:$J$1096,"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F34" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G34" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H34" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I34" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J34" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <v/>
+      </c>
+      <c r="K34" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B34" s="17">
-        <f>SUM(B4:B33)</f>
+      <c r="B35" s="17">
+        <f>SUM(B4:B34)</f>
         <v/>
       </c>
-      <c r="C34" s="17">
-        <f>SUM(C4:C33)</f>
+      <c r="C35" s="17">
+        <f>SUM(C4:C34)</f>
         <v/>
       </c>
-      <c r="D34" s="17">
-        <f>SUM(D4:D33)</f>
+      <c r="D35" s="17">
+        <f>SUM(D4:D34)</f>
         <v/>
       </c>
-      <c r="E34" s="17">
-        <f>SUM(E4:E33)</f>
+      <c r="E35" s="17">
+        <f>SUM(E4:E34)</f>
         <v/>
       </c>
-      <c r="F34" s="17">
-        <f>SUM(F4:F33)</f>
+      <c r="F35" s="17">
+        <f>SUM(F4:F34)</f>
         <v/>
       </c>
-      <c r="G34" s="17">
-        <f>SUM(G4:G33)</f>
+      <c r="G35" s="17">
+        <f>SUM(G4:G34)</f>
         <v/>
       </c>
-      <c r="H34" s="17">
-        <f>SUM(H4:H33)</f>
+      <c r="H35" s="17">
+        <f>SUM(H4:H34)</f>
         <v/>
       </c>
-      <c r="I34" s="17">
-        <f>SUM(I4:I33)</f>
+      <c r="I35" s="17">
+        <f>SUM(I4:I34)</f>
         <v/>
       </c>
-      <c r="J34" s="17">
-        <f>SUM(J4:J33)</f>
+      <c r="J35" s="17">
+        <f>SUM(J4:J34)</f>
         <v/>
       </c>
-      <c r="K34" s="17">
-        <f>SUM(K4:K33)</f>
+      <c r="K35" s="17">
+        <f>SUM(K4:K34)</f>
         <v/>
       </c>
     </row>
@@ -66186,7 +67593,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・30都道府県、1069校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・31都道府県、1092校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1096</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1133</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O1096"/>
+  <dimension ref="A1:O1133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（31都道府県／1092校）</t>
+          <t>私立高等学校 架電リスト（32都道府県／1129校）</t>
         </is>
       </c>
     </row>
@@ -64800,9 +64800,2128 @@
         </is>
       </c>
     </row>
+    <row r="1097">
+      <c r="A1097" s="4" t="n">
+        <v>1093</v>
+      </c>
+      <c r="B1097" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1097" s="5" t="inlineStr">
+        <is>
+          <t>広島市安佐南区</t>
+        </is>
+      </c>
+      <c r="D1097" s="5" t="inlineStr">
+        <is>
+          <t>AICJ高等学校</t>
+        </is>
+      </c>
+      <c r="E1097" s="6" t="inlineStr">
+        <is>
+          <t>082-832-5037</t>
+        </is>
+      </c>
+      <c r="F1097" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1097" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1097" s="8" t="n"/>
+      <c r="I1097" s="9" t="n"/>
+      <c r="J1097" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1097" s="8" t="n"/>
+      <c r="L1097" s="9" t="n"/>
+      <c r="M1097" s="10" t="inlineStr">
+        <is>
+          <t>一部サイトに旧番号らしい082-874-3081の記載あり</t>
+        </is>
+      </c>
+      <c r="N1097" s="11" t="inlineStr">
+        <is>
+          <t>https://aicj.ed.jp/access.html</t>
+        </is>
+      </c>
+      <c r="O1097" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="4" t="n">
+        <v>1094</v>
+      </c>
+      <c r="B1098" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1098" s="5" t="inlineStr">
+        <is>
+          <t>福山市</t>
+        </is>
+      </c>
+      <c r="D1098" s="5" t="inlineStr">
+        <is>
+          <t>盈進高等学校</t>
+        </is>
+      </c>
+      <c r="E1098" s="6" t="inlineStr">
+        <is>
+          <t>084-955-2333</t>
+        </is>
+      </c>
+      <c r="F1098" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1098" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1098" s="8" t="n"/>
+      <c r="I1098" s="9" t="n"/>
+      <c r="J1098" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1098" s="8" t="n"/>
+      <c r="L1098" s="9" t="n"/>
+      <c r="M1098" s="10" t="inlineStr">
+        <is>
+          <t>中高共通の代表番号</t>
+        </is>
+      </c>
+      <c r="N1098" s="11" t="inlineStr">
+        <is>
+          <t>https://www.eishin.ed.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1098" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="B1099" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1099" s="5" t="inlineStr">
+        <is>
+          <t>福山市</t>
+        </is>
+      </c>
+      <c r="D1099" s="5" t="inlineStr">
+        <is>
+          <t>英数学館高等学校</t>
+        </is>
+      </c>
+      <c r="E1099" s="6" t="inlineStr">
+        <is>
+          <t>084-941-4115</t>
+        </is>
+      </c>
+      <c r="F1099" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1099" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1099" s="8" t="n"/>
+      <c r="I1099" s="9" t="n"/>
+      <c r="J1099" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1099" s="8" t="n"/>
+      <c r="L1099" s="9" t="n"/>
+      <c r="M1099" s="10" t="inlineStr">
+        <is>
+          <t>一部サイトに084-941-4117の記載あり（旧番号か）</t>
+        </is>
+      </c>
+      <c r="N1099" s="11" t="inlineStr">
+        <is>
+          <t>https://goto.eisu-ejs.ac.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1099" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="4" t="n">
+        <v>1096</v>
+      </c>
+      <c r="B1100" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1100" s="5" t="inlineStr">
+        <is>
+          <t>尾道市</t>
+        </is>
+      </c>
+      <c r="D1100" s="5" t="inlineStr">
+        <is>
+          <t>尾道高等学校</t>
+        </is>
+      </c>
+      <c r="E1100" s="6" t="inlineStr">
+        <is>
+          <t>0848-20-6612</t>
+        </is>
+      </c>
+      <c r="F1100" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1100" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1100" s="8" t="n"/>
+      <c r="I1100" s="9" t="n"/>
+      <c r="J1100" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1100" s="8" t="n"/>
+      <c r="L1100" s="9" t="n"/>
+      <c r="M1100" s="10" t="inlineStr">
+        <is>
+          <t>2009年に向島町へ移転。旧番号0848-23-2311が残るサイトあり</t>
+        </is>
+      </c>
+      <c r="N1100" s="11" t="inlineStr">
+        <is>
+          <t>https://onomichi.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1100" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="4" t="n">
+        <v>1097</v>
+      </c>
+      <c r="B1101" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1101" s="5" t="inlineStr">
+        <is>
+          <t>東広島市</t>
+        </is>
+      </c>
+      <c r="D1101" s="5" t="inlineStr">
+        <is>
+          <t>近畿大学附属広島高等学校東広島校</t>
+        </is>
+      </c>
+      <c r="E1101" s="6" t="inlineStr">
+        <is>
+          <t>082-434-7111</t>
+        </is>
+      </c>
+      <c r="F1101" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1101" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1101" s="8" t="n"/>
+      <c r="I1101" s="9" t="n"/>
+      <c r="J1101" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1101" s="8" t="n"/>
+      <c r="L1101" s="9" t="n"/>
+      <c r="M1101" s="10" t="n"/>
+      <c r="N1101" s="11" t="inlineStr">
+        <is>
+          <t>https://hh.kindai.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1101" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="4" t="n">
+        <v>1098</v>
+      </c>
+      <c r="B1102" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1102" s="5" t="inlineStr">
+        <is>
+          <t>福山市</t>
+        </is>
+      </c>
+      <c r="D1102" s="5" t="inlineStr">
+        <is>
+          <t>近畿大学附属広島高等学校福山校</t>
+        </is>
+      </c>
+      <c r="E1102" s="6" t="inlineStr">
+        <is>
+          <t>084-951-2695</t>
+        </is>
+      </c>
+      <c r="F1102" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1102" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1102" s="8" t="n"/>
+      <c r="I1102" s="9" t="n"/>
+      <c r="J1102" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1102" s="8" t="n"/>
+      <c r="L1102" s="9" t="n"/>
+      <c r="M1102" s="10" t="inlineStr">
+        <is>
+          <t>旧称は近畿大学附属福山高等学校</t>
+        </is>
+      </c>
+      <c r="N1102" s="11" t="inlineStr">
+        <is>
+          <t>https://www.fukuyama.kindai.ac.jp/gakko/gakko-shokai.html</t>
+        </is>
+      </c>
+      <c r="O1102" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="4" t="n">
+        <v>1099</v>
+      </c>
+      <c r="B1103" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1103" s="5" t="inlineStr">
+        <is>
+          <t>福山市</t>
+        </is>
+      </c>
+      <c r="D1103" s="5" t="inlineStr">
+        <is>
+          <t>銀河学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1103" s="6" t="inlineStr">
+        <is>
+          <t>084-941-9292</t>
+        </is>
+      </c>
+      <c r="F1103" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1103" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1103" s="8" t="n"/>
+      <c r="I1103" s="9" t="n"/>
+      <c r="J1103" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1103" s="8" t="n"/>
+      <c r="L1103" s="9" t="n"/>
+      <c r="M1103" s="10" t="inlineStr">
+        <is>
+          <t>公式（法人事務室）に記載、複数サイトも一致</t>
+        </is>
+      </c>
+      <c r="N1103" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ginga.ac.jp/donationginga/</t>
+        </is>
+      </c>
+      <c r="O1103" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="4" t="n">
+        <v>1100</v>
+      </c>
+      <c r="B1104" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1104" s="5" t="inlineStr">
+        <is>
+          <t>呉市</t>
+        </is>
+      </c>
+      <c r="D1104" s="5" t="inlineStr">
+        <is>
+          <t>呉青山高等学校</t>
+        </is>
+      </c>
+      <c r="E1104" s="6" t="inlineStr">
+        <is>
+          <t>0823-32-1721</t>
+        </is>
+      </c>
+      <c r="F1104" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1104" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1104" s="8" t="n"/>
+      <c r="I1104" s="9" t="n"/>
+      <c r="J1104" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1104" s="8" t="n"/>
+      <c r="L1104" s="9" t="n"/>
+      <c r="M1104" s="10" t="inlineStr">
+        <is>
+          <t>2027年4月に「星の杜広島中学校・高等学校」へ校名変更予定</t>
+        </is>
+      </c>
+      <c r="N1104" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kureaoyama.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1104" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="4" t="n">
+        <v>1101</v>
+      </c>
+      <c r="B1105" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1105" s="5" t="inlineStr">
+        <is>
+          <t>広島市安佐南区</t>
+        </is>
+      </c>
+      <c r="D1105" s="5" t="inlineStr">
+        <is>
+          <t>広陵高等学校</t>
+        </is>
+      </c>
+      <c r="E1105" s="6" t="inlineStr">
+        <is>
+          <t>082-848-1321</t>
+        </is>
+      </c>
+      <c r="F1105" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1105" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1105" s="8" t="n"/>
+      <c r="I1105" s="9" t="n"/>
+      <c r="J1105" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1105" s="8" t="n"/>
+      <c r="L1105" s="9" t="n"/>
+      <c r="M1105" s="10" t="n"/>
+      <c r="N1105" s="11" t="inlineStr">
+        <is>
+          <t>https://www.koryo.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1105" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="4" t="n">
+        <v>1102</v>
+      </c>
+      <c r="B1106" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1106" s="5" t="inlineStr">
+        <is>
+          <t>呉市</t>
+        </is>
+      </c>
+      <c r="D1106" s="5" t="inlineStr">
+        <is>
+          <t>呉港高等学校</t>
+        </is>
+      </c>
+      <c r="E1106" s="6" t="inlineStr">
+        <is>
+          <t>0823-71-9163</t>
+        </is>
+      </c>
+      <c r="F1106" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1106" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1106" s="8" t="n"/>
+      <c r="I1106" s="9" t="n"/>
+      <c r="J1106" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1106" s="8" t="n"/>
+      <c r="L1106" s="9" t="n"/>
+      <c r="M1106" s="10" t="n"/>
+      <c r="N1106" s="11" t="inlineStr">
+        <is>
+          <t>https://www.goko.ac.jp/?page_id=96</t>
+        </is>
+      </c>
+      <c r="O1106" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="4" t="n">
+        <v>1103</v>
+      </c>
+      <c r="B1107" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1107" s="5" t="inlineStr">
+        <is>
+          <t>広島市西区</t>
+        </is>
+      </c>
+      <c r="D1107" s="5" t="inlineStr">
+        <is>
+          <t>山陽高等学校</t>
+        </is>
+      </c>
+      <c r="E1107" s="6" t="inlineStr">
+        <is>
+          <t>082-232-9156</t>
+        </is>
+      </c>
+      <c r="F1107" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1107" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1107" s="8" t="n"/>
+      <c r="I1107" s="9" t="n"/>
+      <c r="J1107" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1107" s="8" t="n"/>
+      <c r="L1107" s="9" t="n"/>
+      <c r="M1107" s="10" t="inlineStr">
+        <is>
+          <t>正式名は広島山陽学園山陽高等学校</t>
+        </is>
+      </c>
+      <c r="N1107" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sanyo.ed.jp/gakkou/access/</t>
+        </is>
+      </c>
+      <c r="O1107" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="4" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B1108" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1108" s="5" t="inlineStr">
+        <is>
+          <t>廿日市市</t>
+        </is>
+      </c>
+      <c r="D1108" s="5" t="inlineStr">
+        <is>
+          <t>山陽女学園高等部</t>
+        </is>
+      </c>
+      <c r="E1108" s="6" t="inlineStr">
+        <is>
+          <t>0829-32-2222</t>
+        </is>
+      </c>
+      <c r="F1108" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1108" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1108" s="8" t="n"/>
+      <c r="I1108" s="9" t="n"/>
+      <c r="J1108" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1108" s="8" t="n"/>
+      <c r="L1108" s="9" t="n"/>
+      <c r="M1108" s="10" t="inlineStr">
+        <is>
+          <t>通信制リアライズコースは0829-32-3330</t>
+        </is>
+      </c>
+      <c r="N1108" s="11" t="inlineStr">
+        <is>
+          <t>https://sanyo-jogakuen.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1108" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="4" t="n">
+        <v>1105</v>
+      </c>
+      <c r="B1109" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1109" s="5" t="inlineStr">
+        <is>
+          <t>呉市</t>
+        </is>
+      </c>
+      <c r="D1109" s="5" t="inlineStr">
+        <is>
+          <t>清水ヶ丘高等学校</t>
+        </is>
+      </c>
+      <c r="E1109" s="6" t="inlineStr">
+        <is>
+          <t>0823-23-1520</t>
+        </is>
+      </c>
+      <c r="F1109" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1109" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1109" s="8" t="n"/>
+      <c r="I1109" s="9" t="n"/>
+      <c r="J1109" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1109" s="8" t="n"/>
+      <c r="L1109" s="9" t="n"/>
+      <c r="M1109" s="10" t="inlineStr">
+        <is>
+          <t>法人事務局は0823-22-0012</t>
+        </is>
+      </c>
+      <c r="N1109" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shimizugaoka.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1109" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="4" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B1110" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1110" s="5" t="inlineStr">
+        <is>
+          <t>広島市中区</t>
+        </is>
+      </c>
+      <c r="D1110" s="5" t="inlineStr">
+        <is>
+          <t>修道高等学校</t>
+        </is>
+      </c>
+      <c r="E1110" s="6" t="inlineStr">
+        <is>
+          <t>082-241-8291</t>
+        </is>
+      </c>
+      <c r="F1110" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1110" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1110" s="8" t="n"/>
+      <c r="I1110" s="9" t="n"/>
+      <c r="J1110" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1110" s="8" t="n"/>
+      <c r="L1110" s="9" t="n"/>
+      <c r="M1110" s="10" t="inlineStr">
+        <is>
+          <t>中高共通の代表番号</t>
+        </is>
+      </c>
+      <c r="N1110" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shudo-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1110" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="4" t="n">
+        <v>1107</v>
+      </c>
+      <c r="B1111" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1111" s="5" t="inlineStr">
+        <is>
+          <t>広島市南区</t>
+        </is>
+      </c>
+      <c r="D1111" s="5" t="inlineStr">
+        <is>
+          <t>進徳女子高等学校</t>
+        </is>
+      </c>
+      <c r="E1111" s="6" t="inlineStr">
+        <is>
+          <t>082-251-6431</t>
+        </is>
+      </c>
+      <c r="F1111" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1111" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1111" s="8" t="n"/>
+      <c r="I1111" s="9" t="n"/>
+      <c r="J1111" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1111" s="8" t="n"/>
+      <c r="L1111" s="9" t="n"/>
+      <c r="M1111" s="10" t="n"/>
+      <c r="N1111" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shintoku.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1111" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="4" t="n">
+        <v>1108</v>
+      </c>
+      <c r="B1112" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1112" s="5" t="inlineStr">
+        <is>
+          <t>三原市</t>
+        </is>
+      </c>
+      <c r="D1112" s="5" t="inlineStr">
+        <is>
+          <t>如水館高等学校</t>
+        </is>
+      </c>
+      <c r="E1112" s="6" t="inlineStr">
+        <is>
+          <t>0848-63-2423</t>
+        </is>
+      </c>
+      <c r="F1112" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1112" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1112" s="8" t="n"/>
+      <c r="I1112" s="9" t="n"/>
+      <c r="J1112" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1112" s="8" t="n"/>
+      <c r="L1112" s="9" t="n"/>
+      <c r="M1112" s="10" t="n"/>
+      <c r="N1112" s="11" t="inlineStr">
+        <is>
+          <t>https://www.josuikan.ed.jp/about/gaiyou</t>
+        </is>
+      </c>
+      <c r="O1112" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="4" t="n">
+        <v>1109</v>
+      </c>
+      <c r="B1113" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1113" s="5" t="inlineStr">
+        <is>
+          <t>広島市西区</t>
+        </is>
+      </c>
+      <c r="D1113" s="5" t="inlineStr">
+        <is>
+          <t>崇徳高等学校</t>
+        </is>
+      </c>
+      <c r="E1113" s="6" t="inlineStr">
+        <is>
+          <t>082-237-9331</t>
+        </is>
+      </c>
+      <c r="F1113" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1113" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1113" s="8" t="n"/>
+      <c r="I1113" s="9" t="n"/>
+      <c r="J1113" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1113" s="8" t="n"/>
+      <c r="L1113" s="9" t="n"/>
+      <c r="M1113" s="10" t="n"/>
+      <c r="N1113" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sotoku.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1113" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="4" t="n">
+        <v>1110</v>
+      </c>
+      <c r="B1114" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1114" s="5" t="inlineStr">
+        <is>
+          <t>東広島市</t>
+        </is>
+      </c>
+      <c r="D1114" s="5" t="inlineStr">
+        <is>
+          <t>武田高等学校</t>
+        </is>
+      </c>
+      <c r="E1114" s="6" t="inlineStr">
+        <is>
+          <t>0823-82-2331</t>
+        </is>
+      </c>
+      <c r="F1114" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1114" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1114" s="8" t="n"/>
+      <c r="I1114" s="9" t="n"/>
+      <c r="J1114" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1114" s="8" t="n"/>
+      <c r="L1114" s="9" t="n"/>
+      <c r="M1114" s="10" t="n"/>
+      <c r="N1114" s="11" t="inlineStr">
+        <is>
+          <t>https://takeda.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1114" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="4" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B1115" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1115" s="5" t="inlineStr">
+        <is>
+          <t>福山市</t>
+        </is>
+      </c>
+      <c r="D1115" s="5" t="inlineStr">
+        <is>
+          <t>東林館高等学校</t>
+        </is>
+      </c>
+      <c r="E1115" s="6" t="inlineStr">
+        <is>
+          <t>084-923-4543</t>
+        </is>
+      </c>
+      <c r="F1115" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1115" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1115" s="8" t="n"/>
+      <c r="I1115" s="9" t="n"/>
+      <c r="J1115" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1115" s="8" t="n"/>
+      <c r="L1115" s="9" t="n"/>
+      <c r="M1115" s="10" t="inlineStr">
+        <is>
+          <t>通信制。2010年に本校を神石高原町から福山市へ移転。旧番号0847-85-2041が残るサイトあり</t>
+        </is>
+      </c>
+      <c r="N1115" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tohrinkan.com/</t>
+        </is>
+      </c>
+      <c r="O1115" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="4" t="n">
+        <v>1112</v>
+      </c>
+      <c r="B1116" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1116" s="5" t="inlineStr">
+        <is>
+          <t>広島市中区</t>
+        </is>
+      </c>
+      <c r="D1116" s="5" t="inlineStr">
+        <is>
+          <t>並木学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1116" s="6" t="inlineStr">
+        <is>
+          <t>082-241-9066</t>
+        </is>
+      </c>
+      <c r="F1116" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1116" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1116" s="8" t="n"/>
+      <c r="I1116" s="9" t="n"/>
+      <c r="J1116" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1116" s="8" t="n"/>
+      <c r="L1116" s="9" t="n"/>
+      <c r="M1116" s="10" t="inlineStr">
+        <is>
+          <t>FAXは082-241-5211</t>
+        </is>
+      </c>
+      <c r="N1116" s="11" t="inlineStr">
+        <is>
+          <t>https://namikigakuin.ac.jp/school-info/group/</t>
+        </is>
+      </c>
+      <c r="O1116" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="4" t="n">
+        <v>1113</v>
+      </c>
+      <c r="B1117" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1117" s="5" t="inlineStr">
+        <is>
+          <t>広島市西区</t>
+        </is>
+      </c>
+      <c r="D1117" s="5" t="inlineStr">
+        <is>
+          <t>ノートルダム清心高等学校</t>
+        </is>
+      </c>
+      <c r="E1117" s="6" t="inlineStr">
+        <is>
+          <t>082-271-1724</t>
+        </is>
+      </c>
+      <c r="F1117" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1117" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1117" s="8" t="n"/>
+      <c r="I1117" s="9" t="n"/>
+      <c r="J1117" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1117" s="8" t="n"/>
+      <c r="L1117" s="9" t="n"/>
+      <c r="M1117" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1117" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hiro-seishin.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1117" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="4" t="n">
+        <v>1114</v>
+      </c>
+      <c r="B1118" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1118" s="5" t="inlineStr">
+        <is>
+          <t>広島市南区</t>
+        </is>
+      </c>
+      <c r="D1118" s="5" t="inlineStr">
+        <is>
+          <t>比治山学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1118" s="6" t="inlineStr">
+        <is>
+          <t>082-251-4478</t>
+        </is>
+      </c>
+      <c r="F1118" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1118" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1118" s="8" t="n"/>
+      <c r="I1118" s="9" t="n"/>
+      <c r="J1118" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1118" s="8" t="n"/>
+      <c r="L1118" s="9" t="n"/>
+      <c r="M1118" s="10" t="inlineStr">
+        <is>
+          <t>旧・比治山女子。2026年4月に共学化・校名変更。新サイト https://www.hijiyama-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="N1118" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hijiyamajoshi-h.ed.jp/education/</t>
+        </is>
+      </c>
+      <c r="O1118" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="4" t="n">
+        <v>1115</v>
+      </c>
+      <c r="B1119" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1119" s="5" t="inlineStr">
+        <is>
+          <t>広島市西区</t>
+        </is>
+      </c>
+      <c r="D1119" s="5" t="inlineStr">
+        <is>
+          <t>広島学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1119" s="6" t="inlineStr">
+        <is>
+          <t>082-271-0241</t>
+        </is>
+      </c>
+      <c r="F1119" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1119" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1119" s="8" t="n"/>
+      <c r="I1119" s="9" t="n"/>
+      <c r="J1119" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1119" s="8" t="n"/>
+      <c r="L1119" s="9" t="n"/>
+      <c r="M1119" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1119" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hiroshimagakuin.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1119" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="4" t="n">
+        <v>1116</v>
+      </c>
+      <c r="B1120" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1120" s="5" t="inlineStr">
+        <is>
+          <t>広島市西区</t>
+        </is>
+      </c>
+      <c r="D1120" s="5" t="inlineStr">
+        <is>
+          <t>広島工業大学高等学校</t>
+        </is>
+      </c>
+      <c r="E1120" s="6" t="inlineStr">
+        <is>
+          <t>082-277-9205</t>
+        </is>
+      </c>
+      <c r="F1120" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1120" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1120" s="8" t="n"/>
+      <c r="I1120" s="9" t="n"/>
+      <c r="J1120" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1120" s="8" t="n"/>
+      <c r="L1120" s="9" t="n"/>
+      <c r="M1120" s="10" t="inlineStr">
+        <is>
+          <t>全日制（西区）。通信制（安佐南区）は082-849-6755</t>
+        </is>
+      </c>
+      <c r="N1120" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kodaikoko.ed.jp/zennichi/</t>
+        </is>
+      </c>
+      <c r="O1120" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="4" t="n">
+        <v>1117</v>
+      </c>
+      <c r="B1121" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1121" s="5" t="inlineStr">
+        <is>
+          <t>海田町</t>
+        </is>
+      </c>
+      <c r="D1121" s="5" t="inlineStr">
+        <is>
+          <t>広島国際学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1121" s="6" t="inlineStr">
+        <is>
+          <t>082-823-3401</t>
+        </is>
+      </c>
+      <c r="F1121" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1121" s="5" t="inlineStr">
+        <is>
+          <t>普通科・総合学科</t>
+        </is>
+      </c>
+      <c r="H1121" s="8" t="n"/>
+      <c r="I1121" s="9" t="n"/>
+      <c r="J1121" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1121" s="8" t="n"/>
+      <c r="L1121" s="9" t="n"/>
+      <c r="M1121" s="10" t="inlineStr">
+        <is>
+          <t>全日制（海田町）。通信制の中野キャンパスは082-820-2515</t>
+        </is>
+      </c>
+      <c r="N1121" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hi.hkg.ac.jp/access</t>
+        </is>
+      </c>
+      <c r="O1121" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="4" t="n">
+        <v>1118</v>
+      </c>
+      <c r="B1122" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1122" s="5" t="inlineStr">
+        <is>
+          <t>広島市東区</t>
+        </is>
+      </c>
+      <c r="D1122" s="5" t="inlineStr">
+        <is>
+          <t>広島桜が丘高等学校</t>
+        </is>
+      </c>
+      <c r="E1122" s="6" t="inlineStr">
+        <is>
+          <t>082-262-0128</t>
+        </is>
+      </c>
+      <c r="F1122" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G1122" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1122" s="8" t="n"/>
+      <c r="I1122" s="9" t="n"/>
+      <c r="J1122" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1122" s="8" t="n"/>
+      <c r="L1122" s="9" t="n"/>
+      <c r="M1122" s="10" t="inlineStr">
+        <is>
+          <t>公式未確認、複数サイトで一致</t>
+        </is>
+      </c>
+      <c r="N1122" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mapion.co.jp/phonebook/M11004/34102/ILSP0000041015_ipclm/</t>
+        </is>
+      </c>
+      <c r="O1122" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="4" t="n">
+        <v>1119</v>
+      </c>
+      <c r="B1123" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1123" s="5" t="inlineStr">
+        <is>
+          <t>三原市</t>
+        </is>
+      </c>
+      <c r="D1123" s="5" t="inlineStr">
+        <is>
+          <t>広島三育学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1123" s="6" t="inlineStr">
+        <is>
+          <t>0847-33-0311</t>
+        </is>
+      </c>
+      <c r="F1123" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1123" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1123" s="8" t="n"/>
+      <c r="I1123" s="9" t="n"/>
+      <c r="J1123" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1123" s="8" t="n"/>
+      <c r="L1123" s="9" t="n"/>
+      <c r="M1123" s="10" t="n"/>
+      <c r="N1123" s="11" t="inlineStr">
+        <is>
+          <t>https://www.saniku.ac.jp/hiroshima/about/profile.php</t>
+        </is>
+      </c>
+      <c r="O1123" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="4" t="n">
+        <v>1120</v>
+      </c>
+      <c r="B1124" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1124" s="5" t="inlineStr">
+        <is>
+          <t>広島市西区</t>
+        </is>
+      </c>
+      <c r="D1124" s="5" t="inlineStr">
+        <is>
+          <t>広島修道大学ひろしま協創高等学校</t>
+        </is>
+      </c>
+      <c r="E1124" s="6" t="inlineStr">
+        <is>
+          <t>082-278-1101</t>
+        </is>
+      </c>
+      <c r="F1124" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1124" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1124" s="8" t="n"/>
+      <c r="I1124" s="9" t="n"/>
+      <c r="J1124" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1124" s="8" t="n"/>
+      <c r="L1124" s="9" t="n"/>
+      <c r="M1124" s="10" t="n"/>
+      <c r="N1124" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shudo-u.ac.jp/fuzoku/</t>
+        </is>
+      </c>
+      <c r="O1124" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="4" t="n">
+        <v>1121</v>
+      </c>
+      <c r="B1125" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1125" s="5" t="inlineStr">
+        <is>
+          <t>坂町</t>
+        </is>
+      </c>
+      <c r="D1125" s="5" t="inlineStr">
+        <is>
+          <t>広島翔洋高等学校</t>
+        </is>
+      </c>
+      <c r="E1125" s="6" t="inlineStr">
+        <is>
+          <t>082-884-1616</t>
+        </is>
+      </c>
+      <c r="F1125" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1125" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1125" s="8" t="n"/>
+      <c r="I1125" s="9" t="n"/>
+      <c r="J1125" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1125" s="8" t="n"/>
+      <c r="L1125" s="9" t="n"/>
+      <c r="M1125" s="10" t="n"/>
+      <c r="N1125" s="11" t="inlineStr">
+        <is>
+          <t>https://www.h-shoyo.ed.jp/overview/details.php</t>
+        </is>
+      </c>
+      <c r="O1125" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="4" t="n">
+        <v>1122</v>
+      </c>
+      <c r="B1126" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1126" s="5" t="inlineStr">
+        <is>
+          <t>北広島町</t>
+        </is>
+      </c>
+      <c r="D1126" s="5" t="inlineStr">
+        <is>
+          <t>広島新庄高等学校</t>
+        </is>
+      </c>
+      <c r="E1126" s="6" t="inlineStr">
+        <is>
+          <t>0826-82-2323</t>
+        </is>
+      </c>
+      <c r="F1126" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1126" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1126" s="8" t="n"/>
+      <c r="I1126" s="9" t="n"/>
+      <c r="J1126" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1126" s="8" t="n"/>
+      <c r="L1126" s="9" t="n"/>
+      <c r="M1126" s="10" t="n"/>
+      <c r="N1126" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shinjou.jp/toiawase/toiawase.html</t>
+        </is>
+      </c>
+      <c r="O1126" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="4" t="n">
+        <v>1123</v>
+      </c>
+      <c r="B1127" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1127" s="5" t="inlineStr">
+        <is>
+          <t>広島市東区</t>
+        </is>
+      </c>
+      <c r="D1127" s="5" t="inlineStr">
+        <is>
+          <t>広島城北高等学校</t>
+        </is>
+      </c>
+      <c r="E1127" s="6" t="inlineStr">
+        <is>
+          <t>082-229-0111</t>
+        </is>
+      </c>
+      <c r="F1127" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1127" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1127" s="8" t="n"/>
+      <c r="I1127" s="9" t="n"/>
+      <c r="J1127" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1127" s="8" t="n"/>
+      <c r="L1127" s="9" t="n"/>
+      <c r="M1127" s="10" t="n"/>
+      <c r="N1127" s="11" t="inlineStr">
+        <is>
+          <t>https://hiroshimajohoku.ed.jp/school/about/access/</t>
+        </is>
+      </c>
+      <c r="O1127" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="4" t="n">
+        <v>1124</v>
+      </c>
+      <c r="B1128" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1128" s="5" t="inlineStr">
+        <is>
+          <t>広島市中区</t>
+        </is>
+      </c>
+      <c r="D1128" s="5" t="inlineStr">
+        <is>
+          <t>広島女学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1128" s="6" t="inlineStr">
+        <is>
+          <t>082-228-4131</t>
+        </is>
+      </c>
+      <c r="F1128" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1128" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1128" s="8" t="n"/>
+      <c r="I1128" s="9" t="n"/>
+      <c r="J1128" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1128" s="8" t="n"/>
+      <c r="L1128" s="9" t="n"/>
+      <c r="M1128" s="10" t="n"/>
+      <c r="N1128" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hjs.ed.jp/contact</t>
+        </is>
+      </c>
+      <c r="O1128" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="4" t="n">
+        <v>1125</v>
+      </c>
+      <c r="B1129" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1129" s="5" t="inlineStr">
+        <is>
+          <t>広島市東区</t>
+        </is>
+      </c>
+      <c r="D1129" s="5" t="inlineStr">
+        <is>
+          <t>広島県瀬戸内高等学校</t>
+        </is>
+      </c>
+      <c r="E1129" s="6" t="inlineStr">
+        <is>
+          <t>082-261-1296</t>
+        </is>
+      </c>
+      <c r="F1129" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1129" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1129" s="8" t="n"/>
+      <c r="I1129" s="9" t="n"/>
+      <c r="J1129" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1129" s="8" t="n"/>
+      <c r="L1129" s="9" t="n"/>
+      <c r="M1129" s="10" t="inlineStr">
+        <is>
+          <t>公式では入試広報部の番号として掲載。082-261-1298とするサイトもあり</t>
+        </is>
+      </c>
+      <c r="N1129" s="11" t="inlineStr">
+        <is>
+          <t>https://www.setouchi-h.ed.jp/extrance1.html</t>
+        </is>
+      </c>
+      <c r="O1129" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="4" t="n">
+        <v>1126</v>
+      </c>
+      <c r="B1130" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1130" s="5" t="inlineStr">
+        <is>
+          <t>広島市佐伯区</t>
+        </is>
+      </c>
+      <c r="D1130" s="5" t="inlineStr">
+        <is>
+          <t>広島なぎさ高等学校</t>
+        </is>
+      </c>
+      <c r="E1130" s="6" t="inlineStr">
+        <is>
+          <t>082-921-2137</t>
+        </is>
+      </c>
+      <c r="F1130" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1130" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1130" s="8" t="n"/>
+      <c r="I1130" s="9" t="n"/>
+      <c r="J1130" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1130" s="8" t="n"/>
+      <c r="L1130" s="9" t="n"/>
+      <c r="M1130" s="10" t="n"/>
+      <c r="N1130" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nagisa.ed.jp/high/</t>
+        </is>
+      </c>
+      <c r="O1130" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="4" t="n">
+        <v>1127</v>
+      </c>
+      <c r="B1131" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1131" s="5" t="inlineStr">
+        <is>
+          <t>広島市安佐北区</t>
+        </is>
+      </c>
+      <c r="D1131" s="5" t="inlineStr">
+        <is>
+          <t>広島文教大学附属高等学校</t>
+        </is>
+      </c>
+      <c r="E1131" s="6" t="inlineStr">
+        <is>
+          <t>082-814-3192</t>
+        </is>
+      </c>
+      <c r="F1131" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1131" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1131" s="8" t="n"/>
+      <c r="I1131" s="9" t="n"/>
+      <c r="J1131" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1131" s="8" t="n"/>
+      <c r="L1131" s="9" t="n"/>
+      <c r="M1131" s="10" t="n"/>
+      <c r="N1131" s="11" t="inlineStr">
+        <is>
+          <t>https://www.h-bunkyo.ac.jp/highschool/</t>
+        </is>
+      </c>
+      <c r="O1131" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="4" t="n">
+        <v>1128</v>
+      </c>
+      <c r="B1132" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1132" s="5" t="inlineStr">
+        <is>
+          <t>福山市</t>
+        </is>
+      </c>
+      <c r="D1132" s="5" t="inlineStr">
+        <is>
+          <t>福山暁の星女子高等学校</t>
+        </is>
+      </c>
+      <c r="E1132" s="6" t="inlineStr">
+        <is>
+          <t>084-922-1682</t>
+        </is>
+      </c>
+      <c r="F1132" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1132" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1132" s="8" t="n"/>
+      <c r="I1132" s="9" t="n"/>
+      <c r="J1132" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1132" s="8" t="n"/>
+      <c r="L1132" s="9" t="n"/>
+      <c r="M1132" s="10" t="n"/>
+      <c r="N1132" s="11" t="inlineStr">
+        <is>
+          <t>https://www.akenohoshi-cyukou.ed.jp/about/access/</t>
+        </is>
+      </c>
+      <c r="O1132" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="4" t="n">
+        <v>1129</v>
+      </c>
+      <c r="B1133" s="5" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="C1133" s="5" t="inlineStr">
+        <is>
+          <t>広島市中区</t>
+        </is>
+      </c>
+      <c r="D1133" s="5" t="inlineStr">
+        <is>
+          <t>安田女子高等学校</t>
+        </is>
+      </c>
+      <c r="E1133" s="6" t="inlineStr">
+        <is>
+          <t>082-221-3304</t>
+        </is>
+      </c>
+      <c r="F1133" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1133" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1133" s="8" t="n"/>
+      <c r="I1133" s="9" t="n"/>
+      <c r="J1133" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1133" s="8" t="n"/>
+      <c r="L1133" s="9" t="n"/>
+      <c r="M1133" s="10" t="inlineStr">
+        <is>
+          <t>高校部の番号。中学部は082-221-3362</t>
+        </is>
+      </c>
+      <c r="N1133" s="11" t="inlineStr">
+        <is>
+          <t>https://www.yasuda-u.ac.jp/jh/</t>
+        </is>
+      </c>
+      <c r="O1133" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O1096"/>
-  <conditionalFormatting sqref="A5:O1096">
+  <autoFilter ref="A4:O1133"/>
+  <conditionalFormatting sqref="A5:O1133">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -64811,10 +66930,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J1096" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J1133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H1096 K5:K1096" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H1133 K5:K1133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -65911,6 +68030,43 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1094" r:id="rId1090"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1095" r:id="rId1091"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1096" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1097" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1098" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1099" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1100" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1101" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1102" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1103" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1104" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1105" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1106" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1107" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1108" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1109" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1110" r:id="rId1106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1111" r:id="rId1107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1112" r:id="rId1108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1113" r:id="rId1109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1114" r:id="rId1110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1115" r:id="rId1111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1116" r:id="rId1112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1117" r:id="rId1113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1118" r:id="rId1114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1119" r:id="rId1115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1120" r:id="rId1116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1121" r:id="rId1117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1122" r:id="rId1118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1123" r:id="rId1119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1124" r:id="rId1120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1125" r:id="rId1121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1126" r:id="rId1122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1127" r:id="rId1123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1128" r:id="rId1124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1129" r:id="rId1125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1130" r:id="rId1126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1131" r:id="rId1127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1132" r:id="rId1128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1133" r:id="rId1129"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -65923,7 +68079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -66010,43 +68166,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A4,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A4,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1096,A4,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A4,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1133,A4,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A4,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A4,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66057,43 +68213,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A5,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A5,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1096,A5,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A5,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1133,A5,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A5,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A5,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66104,43 +68260,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A6,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A6,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1096,A6,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A6,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1133,A6,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A6,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A6,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66151,43 +68307,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A7,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A7,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1096,A7,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A7,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1133,A7,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A7,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A7,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66198,43 +68354,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A8,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A8,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1096,A8,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A8,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1133,A8,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A8,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A8,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66245,43 +68401,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A9,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A9,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1096,A9,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A9,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1133,A9,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A9,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A9,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66292,43 +68448,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A10,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A10,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1096,A10,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A10,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1133,A10,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A10,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A10,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66339,43 +68495,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A11,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A11,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1096,A11,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A11,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1133,A11,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A11,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A11,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66386,43 +68542,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A12,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A12,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1096,A12,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A12,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1133,A12,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A12,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A12,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66433,43 +68589,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A13,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A13,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1096,A13,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A13,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1133,A13,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A13,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A13,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66480,43 +68636,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A14,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A14,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1096,A14,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A14,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1133,A14,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A14,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A14,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66527,43 +68683,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A15,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A15,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1096,A15,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A15,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1133,A15,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A15,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A15,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66574,43 +68730,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A16,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A16,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1096,A16,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A16,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1133,A16,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A16,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A16,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66621,43 +68777,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A17,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A17,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1096,A17,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A17,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1133,A17,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A17,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A17,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66668,43 +68824,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A18,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A18,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1096,A18,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A18,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1133,A18,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A18,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A18,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66715,43 +68871,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A19,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A19,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1096,A19,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A19,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1133,A19,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A19,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A19,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66762,43 +68918,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A20,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A20,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1096,A20,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A20,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1133,A20,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A20,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A20,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66809,43 +68965,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A21,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A21,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1096,A21,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A21,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1133,A21,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A21,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A21,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66856,43 +69012,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A22,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A22,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1096,A22,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A22,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1133,A22,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A22,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A22,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66903,43 +69059,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A23,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A23,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1096,A23,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A23,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1133,A23,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A23,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A23,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66950,43 +69106,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A24,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A24,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1096,A24,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A24,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1133,A24,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A24,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A24,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -66997,43 +69153,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A25,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A25,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1096,A25,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A25,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1133,A25,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A25,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A25,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -67044,43 +69200,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A26,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A26,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1096,A26,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A26,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1133,A26,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A26,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A26,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -67091,43 +69247,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A27,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A27,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1096,A27,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A27,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1133,A27,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A27,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A27,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -67138,43 +69294,43 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A28,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A28,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1096,A28,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A28,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1133,A28,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A28,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A28,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -67185,43 +69341,43 @@
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A29)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A29,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A29,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1096,A29,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A29,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1133,A29,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A29,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A29,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -67232,43 +69388,43 @@
         </is>
       </c>
       <c r="B30" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A30)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A30)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A30,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A30,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1096,A30,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A30,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1133,A30,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A30,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A30,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -67279,43 +69435,43 @@
         </is>
       </c>
       <c r="B31" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A31)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A31)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A31,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A31,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1096,A31,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A31,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1133,A31,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A31,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A31,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -67326,43 +69482,43 @@
         </is>
       </c>
       <c r="B32" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A32)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A32)</f>
         <v/>
       </c>
       <c r="C32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A32,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A32,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1096,A32,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A32,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1133,A32,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A32,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A32,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -67373,43 +69529,43 @@
         </is>
       </c>
       <c r="B33" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A33)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A33)</f>
         <v/>
       </c>
       <c r="C33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A33,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A33,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D33" s="16">
-        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1096,A33,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A33,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1133,A33,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A33,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A33,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -67420,90 +69576,137 @@
         </is>
       </c>
       <c r="B34" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1096,A34)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A34)</f>
         <v/>
       </c>
       <c r="C34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,A34,'架電リスト'!$E$5:$E$1096,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A34,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1096,A34,'架電リスト'!$J$5:$J$1096,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1096,A34,'架電リスト'!$J$5:$J$1096,"")</f>
+        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1133,A34,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A34,'架電リスト'!$J$5:$J$1133,"")</f>
         <v/>
       </c>
       <c r="E34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
         <v/>
       </c>
       <c r="G34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"検討中")</f>
         <v/>
       </c>
       <c r="J34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"NG")</f>
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1096,$A34,'架電リスト'!$J$5:$J$1096,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="B35" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A35)</f>
+        <v/>
+      </c>
+      <c r="C35" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A35,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D35" s="16">
+        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1133,A35,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A35,'架電リスト'!$J$5:$J$1133,"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F35" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G35" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H35" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I35" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J35" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <v/>
+      </c>
+      <c r="K35" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B35" s="17">
-        <f>SUM(B4:B34)</f>
+      <c r="B36" s="17">
+        <f>SUM(B4:B35)</f>
         <v/>
       </c>
-      <c r="C35" s="17">
-        <f>SUM(C4:C34)</f>
+      <c r="C36" s="17">
+        <f>SUM(C4:C35)</f>
         <v/>
       </c>
-      <c r="D35" s="17">
-        <f>SUM(D4:D34)</f>
+      <c r="D36" s="17">
+        <f>SUM(D4:D35)</f>
         <v/>
       </c>
-      <c r="E35" s="17">
-        <f>SUM(E4:E34)</f>
+      <c r="E36" s="17">
+        <f>SUM(E4:E35)</f>
         <v/>
       </c>
-      <c r="F35" s="17">
-        <f>SUM(F4:F34)</f>
+      <c r="F36" s="17">
+        <f>SUM(F4:F35)</f>
         <v/>
       </c>
-      <c r="G35" s="17">
-        <f>SUM(G4:G34)</f>
+      <c r="G36" s="17">
+        <f>SUM(G4:G35)</f>
         <v/>
       </c>
-      <c r="H35" s="17">
-        <f>SUM(H4:H34)</f>
+      <c r="H36" s="17">
+        <f>SUM(H4:H35)</f>
         <v/>
       </c>
-      <c r="I35" s="17">
-        <f>SUM(I4:I34)</f>
+      <c r="I36" s="17">
+        <f>SUM(I4:I35)</f>
         <v/>
       </c>
-      <c r="J35" s="17">
-        <f>SUM(J4:J34)</f>
+      <c r="J36" s="17">
+        <f>SUM(J4:J35)</f>
         <v/>
       </c>
-      <c r="K35" s="17">
-        <f>SUM(K4:K34)</f>
+      <c r="K36" s="17">
+        <f>SUM(K4:K35)</f>
         <v/>
       </c>
     </row>
@@ -67593,7 +69796,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・31都道府県、1092校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・32都道府県、1129校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1154</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O1133"/>
+  <dimension ref="A1:O1154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（32都道府県／1129校）</t>
+          <t>私立高等学校 架電リスト（33都道府県／1150校）</t>
         </is>
       </c>
     </row>
@@ -66919,9 +66919,1212 @@
         </is>
       </c>
     </row>
+    <row r="1134">
+      <c r="A1134" s="4" t="n">
+        <v>1130</v>
+      </c>
+      <c r="B1134" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1134" s="5" t="inlineStr">
+        <is>
+          <t>宇部市</t>
+        </is>
+      </c>
+      <c r="D1134" s="5" t="inlineStr">
+        <is>
+          <t>宇部鴻城高等学校</t>
+        </is>
+      </c>
+      <c r="E1134" s="6" t="inlineStr">
+        <is>
+          <t>0836-41-8109</t>
+        </is>
+      </c>
+      <c r="F1134" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1134" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1134" s="8" t="n"/>
+      <c r="I1134" s="9" t="n"/>
+      <c r="J1134" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1134" s="8" t="n"/>
+      <c r="L1134" s="9" t="n"/>
+      <c r="M1134" s="10" t="n"/>
+      <c r="N1134" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ubekojo-h.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1134" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="4" t="n">
+        <v>1131</v>
+      </c>
+      <c r="B1135" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1135" s="5" t="inlineStr">
+        <is>
+          <t>宇部市</t>
+        </is>
+      </c>
+      <c r="D1135" s="5" t="inlineStr">
+        <is>
+          <t>宇部フロンティア大学付属香川高等学校</t>
+        </is>
+      </c>
+      <c r="E1135" s="6" t="inlineStr">
+        <is>
+          <t>0836-35-9574</t>
+        </is>
+      </c>
+      <c r="F1135" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1135" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1135" s="8" t="n"/>
+      <c r="I1135" s="9" t="n"/>
+      <c r="J1135" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1135" s="8" t="n"/>
+      <c r="L1135" s="9" t="n"/>
+      <c r="M1135" s="10" t="inlineStr">
+        <is>
+          <t>普通科職員室0836-35-9578、専門部職員室0836-35-9583</t>
+        </is>
+      </c>
+      <c r="N1135" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kagawa-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1135" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="4" t="n">
+        <v>1132</v>
+      </c>
+      <c r="B1136" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1136" s="5" t="inlineStr">
+        <is>
+          <t>宇部市</t>
+        </is>
+      </c>
+      <c r="D1136" s="5" t="inlineStr">
+        <is>
+          <t>慶進高等学校</t>
+        </is>
+      </c>
+      <c r="E1136" s="6" t="inlineStr">
+        <is>
+          <t>0836-34-1111</t>
+        </is>
+      </c>
+      <c r="F1136" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1136" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1136" s="8" t="n"/>
+      <c r="I1136" s="9" t="n"/>
+      <c r="J1136" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1136" s="8" t="n"/>
+      <c r="L1136" s="9" t="n"/>
+      <c r="M1136" s="10" t="n"/>
+      <c r="N1136" s="11" t="inlineStr">
+        <is>
+          <t>https://www.keishin-ug.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1136" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="4" t="n">
+        <v>1133</v>
+      </c>
+      <c r="B1137" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1137" s="5" t="inlineStr">
+        <is>
+          <t>山陽小野田市</t>
+        </is>
+      </c>
+      <c r="D1137" s="5" t="inlineStr">
+        <is>
+          <t>ザビエル高等学校</t>
+        </is>
+      </c>
+      <c r="E1137" s="6" t="inlineStr">
+        <is>
+          <t>0836-83-3587</t>
+        </is>
+      </c>
+      <c r="F1137" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1137" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1137" s="8" t="n"/>
+      <c r="I1137" s="9" t="n"/>
+      <c r="J1137" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1137" s="8" t="n"/>
+      <c r="L1137" s="9" t="n"/>
+      <c r="M1137" s="10" t="inlineStr">
+        <is>
+          <t>正式表記は「サビエル高等学校」</t>
+        </is>
+      </c>
+      <c r="N1137" s="11" t="inlineStr">
+        <is>
+          <t>https://xavier.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1137" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="4" t="n">
+        <v>1134</v>
+      </c>
+      <c r="B1138" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1138" s="5" t="inlineStr">
+        <is>
+          <t>下関市</t>
+        </is>
+      </c>
+      <c r="D1138" s="5" t="inlineStr">
+        <is>
+          <t>下関国際高等学校</t>
+        </is>
+      </c>
+      <c r="E1138" s="6" t="inlineStr">
+        <is>
+          <t>083-256-2321</t>
+        </is>
+      </c>
+      <c r="F1138" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1138" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1138" s="8" t="n"/>
+      <c r="I1138" s="9" t="n"/>
+      <c r="J1138" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1138" s="8" t="n"/>
+      <c r="L1138" s="9" t="n"/>
+      <c r="M1138" s="10" t="n"/>
+      <c r="N1138" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shiboyama.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1138" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="4" t="n">
+        <v>1135</v>
+      </c>
+      <c r="B1139" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1139" s="5" t="inlineStr">
+        <is>
+          <t>下関市</t>
+        </is>
+      </c>
+      <c r="D1139" s="5" t="inlineStr">
+        <is>
+          <t>下関短期大学付属高等学校</t>
+        </is>
+      </c>
+      <c r="E1139" s="6" t="inlineStr">
+        <is>
+          <t>083-232-3785</t>
+        </is>
+      </c>
+      <c r="F1139" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1139" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1139" s="8" t="n"/>
+      <c r="I1139" s="9" t="n"/>
+      <c r="J1139" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1139" s="8" t="n"/>
+      <c r="L1139" s="9" t="n"/>
+      <c r="M1139" s="10" t="inlineStr">
+        <is>
+          <t>短大の番号（083-223-0339）とは別</t>
+        </is>
+      </c>
+      <c r="N1139" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shimotan-hs.jp/pages/13/</t>
+        </is>
+      </c>
+      <c r="O1139" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="4" t="n">
+        <v>1136</v>
+      </c>
+      <c r="B1140" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1140" s="5" t="inlineStr">
+        <is>
+          <t>防府市</t>
+        </is>
+      </c>
+      <c r="D1140" s="5" t="inlineStr">
+        <is>
+          <t>誠英高等学校</t>
+        </is>
+      </c>
+      <c r="E1140" s="6" t="inlineStr">
+        <is>
+          <t>0835-38-5252</t>
+        </is>
+      </c>
+      <c r="F1140" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1140" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1140" s="8" t="n"/>
+      <c r="I1140" s="9" t="n"/>
+      <c r="J1140" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1140" s="8" t="n"/>
+      <c r="L1140" s="9" t="n"/>
+      <c r="M1140" s="10" t="inlineStr">
+        <is>
+          <t>通信制課程は0835-38-6161（第三者サイト）</t>
+        </is>
+      </c>
+      <c r="N1140" s="11" t="inlineStr">
+        <is>
+          <t>https://seiei.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1140" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="4" t="n">
+        <v>1137</v>
+      </c>
+      <c r="B1141" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1141" s="5" t="inlineStr">
+        <is>
+          <t>山口市</t>
+        </is>
+      </c>
+      <c r="D1141" s="5" t="inlineStr">
+        <is>
+          <t>精華学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1141" s="6" t="inlineStr">
+        <is>
+          <t>083-976-8833</t>
+        </is>
+      </c>
+      <c r="F1141" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1141" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1141" s="8" t="n"/>
+      <c r="I1141" s="9" t="n"/>
+      <c r="J1141" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1141" s="8" t="n"/>
+      <c r="L1141" s="9" t="n"/>
+      <c r="M1141" s="10" t="inlineStr">
+        <is>
+          <t>広域通信制・山口本校</t>
+        </is>
+      </c>
+      <c r="N1141" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seikagakuen.ac.jp/archives/691</t>
+        </is>
+      </c>
+      <c r="O1141" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="4" t="n">
+        <v>1138</v>
+      </c>
+      <c r="B1142" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1142" s="5" t="inlineStr">
+        <is>
+          <t>光市</t>
+        </is>
+      </c>
+      <c r="D1142" s="5" t="inlineStr">
+        <is>
+          <t>聖光高等学校</t>
+        </is>
+      </c>
+      <c r="E1142" s="6" t="inlineStr">
+        <is>
+          <t>0833-72-1187</t>
+        </is>
+      </c>
+      <c r="F1142" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1142" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1142" s="8" t="n"/>
+      <c r="I1142" s="9" t="n"/>
+      <c r="J1142" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1142" s="8" t="n"/>
+      <c r="L1142" s="9" t="n"/>
+      <c r="M1142" s="10" t="inlineStr">
+        <is>
+          <t>通信制は0833-72-7070（第三者サイト）</t>
+        </is>
+      </c>
+      <c r="N1142" s="11" t="inlineStr">
+        <is>
+          <t>https://www.seiko-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1142" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" s="4" t="n">
+        <v>1139</v>
+      </c>
+      <c r="B1143" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1143" s="5" t="inlineStr">
+        <is>
+          <t>美祢市</t>
+        </is>
+      </c>
+      <c r="D1143" s="5" t="inlineStr">
+        <is>
+          <t>成進高等学校</t>
+        </is>
+      </c>
+      <c r="E1143" s="6" t="inlineStr">
+        <is>
+          <t>0837-52-1350</t>
+        </is>
+      </c>
+      <c r="F1143" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1143" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1143" s="8" t="n"/>
+      <c r="I1143" s="9" t="n"/>
+      <c r="J1143" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1143" s="8" t="n"/>
+      <c r="L1143" s="9" t="n"/>
+      <c r="M1143" s="10" t="n"/>
+      <c r="N1143" s="11" t="inlineStr">
+        <is>
+          <t>https://www.mine-c.ed.jp/profile</t>
+        </is>
+      </c>
+      <c r="O1143" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="4" t="n">
+        <v>1140</v>
+      </c>
+      <c r="B1144" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1144" s="5" t="inlineStr">
+        <is>
+          <t>防府市</t>
+        </is>
+      </c>
+      <c r="D1144" s="5" t="inlineStr">
+        <is>
+          <t>高川学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1144" s="6" t="inlineStr">
+        <is>
+          <t>0835-33-0101</t>
+        </is>
+      </c>
+      <c r="F1144" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1144" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1144" s="8" t="n"/>
+      <c r="I1144" s="9" t="n"/>
+      <c r="J1144" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1144" s="8" t="n"/>
+      <c r="L1144" s="9" t="n"/>
+      <c r="M1144" s="10" t="n"/>
+      <c r="N1144" s="11" t="inlineStr">
+        <is>
+          <t>https://takagawagakuen.com/high/</t>
+        </is>
+      </c>
+      <c r="O1144" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="4" t="n">
+        <v>1141</v>
+      </c>
+      <c r="B1145" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1145" s="5" t="inlineStr">
+        <is>
+          <t>岩国市</t>
+        </is>
+      </c>
+      <c r="D1145" s="5" t="inlineStr">
+        <is>
+          <t>高水高等学校</t>
+        </is>
+      </c>
+      <c r="E1145" s="6" t="inlineStr">
+        <is>
+          <t>0827-31-7191</t>
+        </is>
+      </c>
+      <c r="F1145" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1145" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1145" s="8" t="n"/>
+      <c r="I1145" s="9" t="n"/>
+      <c r="J1145" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1145" s="8" t="n"/>
+      <c r="L1145" s="9" t="n"/>
+      <c r="M1145" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1145" s="11" t="inlineStr">
+        <is>
+          <t>https://www.takamizu.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1145" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="4" t="n">
+        <v>1142</v>
+      </c>
+      <c r="B1146" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1146" s="5" t="inlineStr">
+        <is>
+          <t>山口市</t>
+        </is>
+      </c>
+      <c r="D1146" s="5" t="inlineStr">
+        <is>
+          <t>中村女子高等学校</t>
+        </is>
+      </c>
+      <c r="E1146" s="6" t="inlineStr">
+        <is>
+          <t>083-922-0418</t>
+        </is>
+      </c>
+      <c r="F1146" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1146" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1146" s="8" t="n"/>
+      <c r="I1146" s="9" t="n"/>
+      <c r="J1146" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1146" s="8" t="n"/>
+      <c r="L1146" s="9" t="n"/>
+      <c r="M1146" s="10" t="inlineStr">
+        <is>
+          <t>現校名は山口中村学園高等学校（2025年度から共学化）。専攻科は083-928-1331</t>
+        </is>
+      </c>
+      <c r="N1146" s="11" t="inlineStr">
+        <is>
+          <t>https://www.y-nakamura.jp/</t>
+        </is>
+      </c>
+      <c r="O1146" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="4" t="n">
+        <v>1143</v>
+      </c>
+      <c r="B1147" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1147" s="5" t="inlineStr">
+        <is>
+          <t>長門市</t>
+        </is>
+      </c>
+      <c r="D1147" s="5" t="inlineStr">
+        <is>
+          <t>長門高等学校</t>
+        </is>
+      </c>
+      <c r="E1147" s="6" t="inlineStr">
+        <is>
+          <t>0837-22-2944</t>
+        </is>
+      </c>
+      <c r="F1147" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1147" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1147" s="8" t="n"/>
+      <c r="I1147" s="9" t="n"/>
+      <c r="J1147" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1147" s="8" t="n"/>
+      <c r="L1147" s="9" t="n"/>
+      <c r="M1147" s="10" t="n"/>
+      <c r="N1147" s="11" t="inlineStr">
+        <is>
+          <t>https://nagato.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1147" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="4" t="n">
+        <v>1144</v>
+      </c>
+      <c r="B1148" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1148" s="5" t="inlineStr">
+        <is>
+          <t>山口市</t>
+        </is>
+      </c>
+      <c r="D1148" s="5" t="inlineStr">
+        <is>
+          <t>野田学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1148" s="6" t="inlineStr">
+        <is>
+          <t>083-922-5000</t>
+        </is>
+      </c>
+      <c r="F1148" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1148" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1148" s="8" t="n"/>
+      <c r="I1148" s="9" t="n"/>
+      <c r="J1148" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1148" s="8" t="n"/>
+      <c r="L1148" s="9" t="n"/>
+      <c r="M1148" s="10" t="n"/>
+      <c r="N1148" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nodagakuen.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1148" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="4" t="n">
+        <v>1145</v>
+      </c>
+      <c r="B1149" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1149" s="5" t="inlineStr">
+        <is>
+          <t>萩市</t>
+        </is>
+      </c>
+      <c r="D1149" s="5" t="inlineStr">
+        <is>
+          <t>萩光塩学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1149" s="6" t="inlineStr">
+        <is>
+          <t>0838-22-0782</t>
+        </is>
+      </c>
+      <c r="F1149" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1149" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1149" s="8" t="n"/>
+      <c r="I1149" s="9" t="n"/>
+      <c r="J1149" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1149" s="8" t="n"/>
+      <c r="L1149" s="9" t="n"/>
+      <c r="M1149" s="10" t="inlineStr">
+        <is>
+          <t>小中高共通の代表番号（法人サイトでも一致）</t>
+        </is>
+      </c>
+      <c r="N1149" s="11" t="inlineStr">
+        <is>
+          <t>https://www.yamaguchi-shigaku.or.jp/tyukou/pdf/2025/20_hagikouen2025.pdf</t>
+        </is>
+      </c>
+      <c r="O1149" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="4" t="n">
+        <v>1146</v>
+      </c>
+      <c r="B1150" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1150" s="5" t="inlineStr">
+        <is>
+          <t>下関市</t>
+        </is>
+      </c>
+      <c r="D1150" s="5" t="inlineStr">
+        <is>
+          <t>早鞆高等学校</t>
+        </is>
+      </c>
+      <c r="E1150" s="6" t="inlineStr">
+        <is>
+          <t>083-231-0080</t>
+        </is>
+      </c>
+      <c r="F1150" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1150" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1150" s="8" t="n"/>
+      <c r="I1150" s="9" t="n"/>
+      <c r="J1150" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1150" s="8" t="n"/>
+      <c r="L1150" s="9" t="n"/>
+      <c r="M1150" s="10" t="n"/>
+      <c r="N1150" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hayatomo.ac.jp/course/</t>
+        </is>
+      </c>
+      <c r="O1150" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="4" t="n">
+        <v>1147</v>
+      </c>
+      <c r="B1151" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1151" s="5" t="inlineStr">
+        <is>
+          <t>下関市</t>
+        </is>
+      </c>
+      <c r="D1151" s="5" t="inlineStr">
+        <is>
+          <t>梅光学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1151" s="6" t="inlineStr">
+        <is>
+          <t>083-227-1200</t>
+        </is>
+      </c>
+      <c r="F1151" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1151" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1151" s="8" t="n"/>
+      <c r="I1151" s="9" t="n"/>
+      <c r="J1151" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1151" s="8" t="n"/>
+      <c r="L1151" s="9" t="n"/>
+      <c r="M1151" s="10" t="inlineStr">
+        <is>
+          <t>法人本部は083-227-1000</t>
+        </is>
+      </c>
+      <c r="N1151" s="11" t="inlineStr">
+        <is>
+          <t>https://www.baiko.ac.jp/highschool/</t>
+        </is>
+      </c>
+      <c r="O1151" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="4" t="n">
+        <v>1148</v>
+      </c>
+      <c r="B1152" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1152" s="5" t="inlineStr">
+        <is>
+          <t>柳井市</t>
+        </is>
+      </c>
+      <c r="D1152" s="5" t="inlineStr">
+        <is>
+          <t>柳井学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1152" s="6" t="inlineStr">
+        <is>
+          <t>0820-22-0214</t>
+        </is>
+      </c>
+      <c r="F1152" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1152" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1152" s="8" t="n"/>
+      <c r="I1152" s="9" t="n"/>
+      <c r="J1152" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1152" s="8" t="n"/>
+      <c r="L1152" s="9" t="n"/>
+      <c r="M1152" s="10" t="n"/>
+      <c r="N1152" s="11" t="inlineStr">
+        <is>
+          <t>https://yanai-g.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1152" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="4" t="n">
+        <v>1149</v>
+      </c>
+      <c r="B1153" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1153" s="5" t="inlineStr">
+        <is>
+          <t>山口市</t>
+        </is>
+      </c>
+      <c r="D1153" s="5" t="inlineStr">
+        <is>
+          <t>山口県鴻城高等学校</t>
+        </is>
+      </c>
+      <c r="E1153" s="6" t="inlineStr">
+        <is>
+          <t>083-972-0307</t>
+        </is>
+      </c>
+      <c r="F1153" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1153" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1153" s="8" t="n"/>
+      <c r="I1153" s="9" t="n"/>
+      <c r="J1153" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1153" s="8" t="n"/>
+      <c r="L1153" s="9" t="n"/>
+      <c r="M1153" s="10" t="inlineStr">
+        <is>
+          <t>衛生看護専攻科（宇部市）は別番号</t>
+        </is>
+      </c>
+      <c r="N1153" s="11" t="inlineStr">
+        <is>
+          <t>https://www.y-kojohs.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1153" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="4" t="n">
+        <v>1150</v>
+      </c>
+      <c r="B1154" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1154" s="5" t="inlineStr">
+        <is>
+          <t>周南市</t>
+        </is>
+      </c>
+      <c r="D1154" s="5" t="inlineStr">
+        <is>
+          <t>山口県桜ケ丘高等学校</t>
+        </is>
+      </c>
+      <c r="E1154" s="6" t="inlineStr">
+        <is>
+          <t>0834-21-0331</t>
+        </is>
+      </c>
+      <c r="F1154" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1154" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1154" s="8" t="n"/>
+      <c r="I1154" s="9" t="n"/>
+      <c r="J1154" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1154" s="8" t="n"/>
+      <c r="L1154" s="9" t="n"/>
+      <c r="M1154" s="10" t="inlineStr">
+        <is>
+          <t>晃英館コースは0834-33-3131</t>
+        </is>
+      </c>
+      <c r="N1154" s="11" t="inlineStr">
+        <is>
+          <t>https://www.y-sakuragaoka.ed.jp/contact.html</t>
+        </is>
+      </c>
+      <c r="O1154" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O1133"/>
-  <conditionalFormatting sqref="A5:O1133">
+  <autoFilter ref="A4:O1154"/>
+  <conditionalFormatting sqref="A5:O1154">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -66930,10 +68133,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J1133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J1154" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H1133 K5:K1133" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H1154 K5:K1154" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -68067,6 +69270,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1131" r:id="rId1127"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1132" r:id="rId1128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1133" r:id="rId1129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1134" r:id="rId1130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1135" r:id="rId1131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1136" r:id="rId1132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1137" r:id="rId1133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1138" r:id="rId1134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1139" r:id="rId1135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1140" r:id="rId1136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1141" r:id="rId1137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1142" r:id="rId1138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1143" r:id="rId1139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1144" r:id="rId1140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1145" r:id="rId1141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1146" r:id="rId1142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1147" r:id="rId1143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1148" r:id="rId1144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1149" r:id="rId1145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1150" r:id="rId1146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1151" r:id="rId1147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1152" r:id="rId1148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1153" r:id="rId1149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1154" r:id="rId1150"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -68079,7 +69303,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -68166,43 +69390,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A4,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A4,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1133,A4,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A4,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1154,A4,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A4,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A4,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68213,43 +69437,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A5,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A5,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1133,A5,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A5,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1154,A5,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A5,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A5,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68260,43 +69484,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A6,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A6,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1133,A6,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A6,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1154,A6,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A6,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A6,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68307,43 +69531,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A7,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A7,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1133,A7,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A7,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1154,A7,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A7,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A7,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68354,43 +69578,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A8,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A8,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1133,A8,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A8,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1154,A8,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A8,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A8,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68401,43 +69625,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A9,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A9,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1133,A9,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A9,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1154,A9,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A9,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A9,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68448,43 +69672,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A10,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A10,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1133,A10,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A10,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1154,A10,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A10,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A10,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68495,43 +69719,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A11,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A11,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1133,A11,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A11,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1154,A11,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A11,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A11,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68542,43 +69766,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A12,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A12,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1133,A12,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A12,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1154,A12,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A12,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A12,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68589,43 +69813,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A13,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A13,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1133,A13,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A13,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1154,A13,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A13,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A13,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68636,43 +69860,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A14,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A14,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1133,A14,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A14,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1154,A14,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A14,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A14,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68683,43 +69907,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A15,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A15,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1133,A15,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A15,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1154,A15,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A15,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A15,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68730,43 +69954,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A16,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A16,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1133,A16,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A16,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1154,A16,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A16,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A16,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68777,43 +70001,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A17,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A17,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1133,A17,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A17,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1154,A17,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A17,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A17,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68824,43 +70048,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A18,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A18,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1133,A18,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A18,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1154,A18,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A18,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A18,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68871,43 +70095,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A19,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A19,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1133,A19,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A19,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1154,A19,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A19,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A19,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68918,43 +70142,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A20,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A20,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1133,A20,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A20,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1154,A20,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A20,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A20,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -68965,43 +70189,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A21,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A21,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1133,A21,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A21,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1154,A21,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A21,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A21,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69012,43 +70236,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A22,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A22,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1133,A22,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A22,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1154,A22,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A22,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A22,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69059,43 +70283,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A23,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A23,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1133,A23,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A23,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1154,A23,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A23,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A23,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69106,43 +70330,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A24,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A24,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1133,A24,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A24,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1154,A24,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A24,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A24,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69153,43 +70377,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A25,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A25,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1133,A25,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A25,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1154,A25,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A25,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A25,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69200,43 +70424,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A26,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A26,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1133,A26,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A26,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1154,A26,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A26,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A26,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69247,43 +70471,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A27,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A27,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1133,A27,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A27,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1154,A27,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A27,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A27,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69294,43 +70518,43 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A28,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A28,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1133,A28,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A28,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1154,A28,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A28,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A28,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69341,43 +70565,43 @@
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A29)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A29,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A29,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1133,A29,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A29,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1154,A29,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A29,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A29,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69388,43 +70612,43 @@
         </is>
       </c>
       <c r="B30" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A30)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A30)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A30,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A30,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1133,A30,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A30,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1154,A30,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A30,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A30,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69435,43 +70659,43 @@
         </is>
       </c>
       <c r="B31" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A31)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A31)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A31,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A31,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1133,A31,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A31,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1154,A31,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A31,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A31,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69482,43 +70706,43 @@
         </is>
       </c>
       <c r="B32" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A32)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A32)</f>
         <v/>
       </c>
       <c r="C32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A32,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A32,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1133,A32,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A32,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1154,A32,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A32,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A32,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69529,43 +70753,43 @@
         </is>
       </c>
       <c r="B33" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A33)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A33)</f>
         <v/>
       </c>
       <c r="C33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A33,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A33,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D33" s="16">
-        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1133,A33,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A33,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1154,A33,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A33,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A33,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69576,43 +70800,43 @@
         </is>
       </c>
       <c r="B34" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A34)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A34)</f>
         <v/>
       </c>
       <c r="C34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A34,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A34,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1133,A34,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A34,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1154,A34,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A34,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A34,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69623,90 +70847,137 @@
         </is>
       </c>
       <c r="B35" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1133,A35)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A35)</f>
         <v/>
       </c>
       <c r="C35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,A35,'架電リスト'!$E$5:$E$1133,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A35,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D35" s="16">
-        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1133,A35,'架電リスト'!$J$5:$J$1133,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1133,A35,'架電リスト'!$J$5:$J$1133,"")</f>
+        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1154,A35,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A35,'架電リスト'!$J$5:$J$1154,"")</f>
         <v/>
       </c>
       <c r="E35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
         <v/>
       </c>
       <c r="G35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"検討中")</f>
         <v/>
       </c>
       <c r="J35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"NG")</f>
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1133,$A35,'架電リスト'!$J$5:$J$1133,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="B36" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A36)</f>
+        <v/>
+      </c>
+      <c r="C36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A36,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D36" s="16">
+        <f>B36-COUNTIFS('架電リスト'!$B$5:$B$1154,A36,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A36,'架電リスト'!$J$5:$J$1154,"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <v/>
+      </c>
+      <c r="K36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B36" s="17">
-        <f>SUM(B4:B35)</f>
+      <c r="B37" s="17">
+        <f>SUM(B4:B36)</f>
         <v/>
       </c>
-      <c r="C36" s="17">
-        <f>SUM(C4:C35)</f>
+      <c r="C37" s="17">
+        <f>SUM(C4:C36)</f>
         <v/>
       </c>
-      <c r="D36" s="17">
-        <f>SUM(D4:D35)</f>
+      <c r="D37" s="17">
+        <f>SUM(D4:D36)</f>
         <v/>
       </c>
-      <c r="E36" s="17">
-        <f>SUM(E4:E35)</f>
+      <c r="E37" s="17">
+        <f>SUM(E4:E36)</f>
         <v/>
       </c>
-      <c r="F36" s="17">
-        <f>SUM(F4:F35)</f>
+      <c r="F37" s="17">
+        <f>SUM(F4:F36)</f>
         <v/>
       </c>
-      <c r="G36" s="17">
-        <f>SUM(G4:G35)</f>
+      <c r="G37" s="17">
+        <f>SUM(G4:G36)</f>
         <v/>
       </c>
-      <c r="H36" s="17">
-        <f>SUM(H4:H35)</f>
+      <c r="H37" s="17">
+        <f>SUM(H4:H36)</f>
         <v/>
       </c>
-      <c r="I36" s="17">
-        <f>SUM(I4:I35)</f>
+      <c r="I37" s="17">
+        <f>SUM(I4:I36)</f>
         <v/>
       </c>
-      <c r="J36" s="17">
-        <f>SUM(J4:J35)</f>
+      <c r="J37" s="17">
+        <f>SUM(J4:J36)</f>
         <v/>
       </c>
-      <c r="K36" s="17">
-        <f>SUM(K4:K35)</f>
+      <c r="K37" s="17">
+        <f>SUM(K4:K36)</f>
         <v/>
       </c>
     </row>
@@ -69796,7 +71067,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・32都道府県、1129校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・33都道府県、1150校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1162</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O1154"/>
+  <dimension ref="A1:O1162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（33都道府県／1150校）</t>
+          <t>私立高等学校 架電リスト（34都道府県／1158校）</t>
         </is>
       </c>
     </row>
@@ -63469,22 +63469,22 @@
       </c>
       <c r="B1074" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="C1074" s="5" t="inlineStr">
         <is>
-          <t>岡山市東区</t>
+          <t>倉吉市</t>
         </is>
       </c>
       <c r="D1074" s="5" t="inlineStr">
         <is>
-          <t>岡山学芸館高等学校</t>
+          <t>倉吉北高等学校</t>
         </is>
       </c>
       <c r="E1074" s="6" t="inlineStr">
         <is>
-          <t>086-942-3864</t>
+          <t>0858-26-1351</t>
         </is>
       </c>
       <c r="F1074" s="7" t="inlineStr">
@@ -63494,7 +63494,7 @@
       </c>
       <c r="G1074" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1074" s="8" t="n"/>
@@ -63506,14 +63506,10 @@
       </c>
       <c r="K1074" s="8" t="n"/>
       <c r="L1074" s="9" t="n"/>
-      <c r="M1074" s="10" t="inlineStr">
-        <is>
-          <t>通信制課程も同じ番号</t>
-        </is>
-      </c>
+      <c r="M1074" s="10" t="n"/>
       <c r="N1074" s="11" t="inlineStr">
         <is>
-          <t>https://www.gakugeikan.ed.jp/contact/index.html</t>
+          <t>https://kurayoshikita-h.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O1074" s="12" t="inlineStr">
@@ -63528,22 +63524,22 @@
       </c>
       <c r="B1075" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="C1075" s="5" t="inlineStr">
         <is>
-          <t>新見市</t>
+          <t>鳥取市</t>
         </is>
       </c>
       <c r="D1075" s="5" t="inlineStr">
         <is>
-          <t>岡山県共生高等学校</t>
+          <t>青翔開智高等学校</t>
         </is>
       </c>
       <c r="E1075" s="6" t="inlineStr">
         <is>
-          <t>0867-72-0526</t>
+          <t>0857-30-5541</t>
         </is>
       </c>
       <c r="F1075" s="7" t="inlineStr">
@@ -63567,12 +63563,12 @@
       <c r="L1075" s="9" t="n"/>
       <c r="M1075" s="10" t="inlineStr">
         <is>
-          <t>0867-72-8032はFAX</t>
+          <t>中高一貫校の代表番号</t>
         </is>
       </c>
       <c r="N1075" s="11" t="inlineStr">
         <is>
-          <t>https://www.kyousei.ed.jp/</t>
+          <t>https://seishokaichi.jp/about/information/</t>
         </is>
       </c>
       <c r="O1075" s="12" t="inlineStr">
@@ -63587,22 +63583,22 @@
       </c>
       <c r="B1076" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="C1076" s="5" t="inlineStr">
         <is>
-          <t>倉敷市</t>
+          <t>鳥取市</t>
         </is>
       </c>
       <c r="D1076" s="5" t="inlineStr">
         <is>
-          <t>岡山県作陽高等学校</t>
+          <t>鳥取敬愛高等学校</t>
         </is>
       </c>
       <c r="E1076" s="6" t="inlineStr">
         <is>
-          <t>086-441-1281</t>
+          <t>0857-22-8397</t>
         </is>
       </c>
       <c r="F1076" s="7" t="inlineStr">
@@ -63626,12 +63622,12 @@
       <c r="L1076" s="9" t="n"/>
       <c r="M1076" s="10" t="inlineStr">
         <is>
-          <t>2023年4月に倉敷市玉島へ移転し「作陽学園高等学校」に校名変更。津山の旧番号0868-23-2188は使用不可の可能性</t>
+          <t>鳥取県資料でも一致</t>
         </is>
       </c>
       <c r="N1076" s="11" t="inlineStr">
         <is>
-          <t>https://www.sakuyo-h.ed.jp/access/</t>
+          <t>https://t-ki.jp/publics/index/2/</t>
         </is>
       </c>
       <c r="O1076" s="12" t="inlineStr">
@@ -63646,22 +63642,22 @@
       </c>
       <c r="B1077" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="C1077" s="5" t="inlineStr">
         <is>
-          <t>津山市</t>
+          <t>鳥取市</t>
         </is>
       </c>
       <c r="D1077" s="5" t="inlineStr">
         <is>
-          <t>岡山県美作高等学校</t>
+          <t>鳥取城北高等学校</t>
         </is>
       </c>
       <c r="E1077" s="6" t="inlineStr">
         <is>
-          <t>0868-22-4838</t>
+          <t>0857-23-3502</t>
         </is>
       </c>
       <c r="F1077" s="7" t="inlineStr">
@@ -63685,12 +63681,12 @@
       <c r="L1077" s="9" t="n"/>
       <c r="M1077" s="10" t="inlineStr">
         <is>
-          <t>全日制の番号。通信制課程は0868-23-3116</t>
+          <t>鳥取県資料でも一致</t>
         </is>
       </c>
       <c r="N1077" s="11" t="inlineStr">
         <is>
-          <t>https://mimasaka.jp/gakuen/houjin.html</t>
+          <t>https://www.tottori-johoku.ed.jp/contact</t>
         </is>
       </c>
       <c r="O1077" s="12" t="inlineStr">
@@ -63705,22 +63701,22 @@
       </c>
       <c r="B1078" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="C1078" s="5" t="inlineStr">
         <is>
-          <t>岡山市南区</t>
+          <t>湯梨浜町</t>
         </is>
       </c>
       <c r="D1078" s="5" t="inlineStr">
         <is>
-          <t>岡山高等学校</t>
+          <t>湯梨浜学園高等学校</t>
         </is>
       </c>
       <c r="E1078" s="6" t="inlineStr">
         <is>
-          <t>086-282-6336</t>
+          <t>0858-48-6810</t>
         </is>
       </c>
       <c r="F1078" s="7" t="inlineStr">
@@ -63744,12 +63740,12 @@
       <c r="L1078" s="9" t="n"/>
       <c r="M1078" s="10" t="inlineStr">
         <is>
-          <t>中高一貫</t>
+          <t>中高の代表番号。通信制課程の窓口は0858-32-2777</t>
         </is>
       </c>
       <c r="N1078" s="11" t="inlineStr">
         <is>
-          <t>https://www.okayama-h.ed.jp/access/</t>
+          <t>https://www.yurihamagakuen.ac.jp/about/</t>
         </is>
       </c>
       <c r="O1078" s="12" t="inlineStr">
@@ -63764,22 +63760,22 @@
       </c>
       <c r="B1079" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="C1079" s="5" t="inlineStr">
         <is>
-          <t>浅口市</t>
+          <t>米子市</t>
         </is>
       </c>
       <c r="D1079" s="5" t="inlineStr">
         <is>
-          <t>おかやま山陽高等学校</t>
+          <t>米子北高等学校</t>
         </is>
       </c>
       <c r="E1079" s="6" t="inlineStr">
         <is>
-          <t>0865-44-3100</t>
+          <t>0859-22-9371</t>
         </is>
       </c>
       <c r="F1079" s="7" t="inlineStr">
@@ -63803,12 +63799,12 @@
       <c r="L1079" s="9" t="n"/>
       <c r="M1079" s="10" t="inlineStr">
         <is>
-          <t>教員室直通は0865-44-7149</t>
+          <t>鳥取県資料でも一致</t>
         </is>
       </c>
       <c r="N1079" s="11" t="inlineStr">
         <is>
-          <t>https://www.okayama-sanyo-hs.ed.jp/</t>
+          <t>https://www.yonagokita.ed.jp/</t>
         </is>
       </c>
       <c r="O1079" s="12" t="inlineStr">
@@ -63823,22 +63819,22 @@
       </c>
       <c r="B1080" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="C1080" s="5" t="inlineStr">
         <is>
-          <t>岡山市北区</t>
+          <t>米子市</t>
         </is>
       </c>
       <c r="D1080" s="5" t="inlineStr">
         <is>
-          <t>岡山商科大学附属高等学校</t>
+          <t>米子松蔭高等学校</t>
         </is>
       </c>
       <c r="E1080" s="6" t="inlineStr">
         <is>
-          <t>086-252-3407</t>
+          <t>0859-27-0421</t>
         </is>
       </c>
       <c r="F1080" s="7" t="inlineStr">
@@ -63848,7 +63844,7 @@
       </c>
       <c r="G1080" s="5" t="inlineStr">
         <is>
-          <t>専門学科・総合学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1080" s="8" t="n"/>
@@ -63863,7 +63859,7 @@
       <c r="M1080" s="10" t="n"/>
       <c r="N1080" s="11" t="inlineStr">
         <is>
-          <t>https://www.osu-h.ed.jp/</t>
+          <t>https://www.yonagoshoin.ed.jp/</t>
         </is>
       </c>
       <c r="O1080" s="12" t="inlineStr">
@@ -63878,27 +63874,27 @@
       </c>
       <c r="B1081" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="C1081" s="5" t="inlineStr">
         <is>
-          <t>赤磐市</t>
+          <t>米子市</t>
         </is>
       </c>
       <c r="D1081" s="5" t="inlineStr">
         <is>
-          <t>岡山白陵高等学校</t>
+          <t>米子北斗高等学校</t>
         </is>
       </c>
       <c r="E1081" s="6" t="inlineStr">
         <is>
-          <t>086-995-1255</t>
-        </is>
-      </c>
-      <c r="F1081" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>0859-29-6000</t>
+        </is>
+      </c>
+      <c r="F1081" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="G1081" s="5" t="inlineStr">
@@ -63917,12 +63913,12 @@
       <c r="L1081" s="9" t="n"/>
       <c r="M1081" s="10" t="inlineStr">
         <is>
-          <t>中学校併設</t>
+          <t>公式未確認、複数サイトで一致</t>
         </is>
       </c>
       <c r="N1081" s="11" t="inlineStr">
         <is>
-          <t>https://www.okahaku.ed.jp/access_inquiry/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/31202/ILSP0000041708_ipclm/</t>
         </is>
       </c>
       <c r="O1081" s="12" t="inlineStr">
@@ -63942,17 +63938,17 @@
       </c>
       <c r="C1082" s="5" t="inlineStr">
         <is>
-          <t>岡山市北区</t>
+          <t>岡山市東区</t>
         </is>
       </c>
       <c r="D1082" s="5" t="inlineStr">
         <is>
-          <t>岡山理科大学附属高等学校</t>
+          <t>岡山学芸館高等学校</t>
         </is>
       </c>
       <c r="E1082" s="6" t="inlineStr">
         <is>
-          <t>086-256-8511</t>
+          <t>086-942-3864</t>
         </is>
       </c>
       <c r="F1082" s="7" t="inlineStr">
@@ -63962,7 +63958,7 @@
       </c>
       <c r="G1082" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1082" s="8" t="n"/>
@@ -63976,12 +63972,12 @@
       <c r="L1082" s="9" t="n"/>
       <c r="M1082" s="10" t="inlineStr">
         <is>
-          <t>通信制課程直通は086-256-8562</t>
+          <t>通信制課程も同じ番号</t>
         </is>
       </c>
       <c r="N1082" s="11" t="inlineStr">
         <is>
-          <t>https://okayama.ridaifu.net/contact/</t>
+          <t>https://www.gakugeikan.ed.jp/contact/index.html</t>
         </is>
       </c>
       <c r="O1082" s="12" t="inlineStr">
@@ -64001,17 +63997,17 @@
       </c>
       <c r="C1083" s="5" t="inlineStr">
         <is>
-          <t>笠岡市</t>
+          <t>新見市</t>
         </is>
       </c>
       <c r="D1083" s="5" t="inlineStr">
         <is>
-          <t>岡山龍谷高等学校</t>
+          <t>岡山県共生高等学校</t>
         </is>
       </c>
       <c r="E1083" s="6" t="inlineStr">
         <is>
-          <t>0865-63-2525</t>
+          <t>0867-72-0526</t>
         </is>
       </c>
       <c r="F1083" s="7" t="inlineStr">
@@ -64021,7 +64017,7 @@
       </c>
       <c r="G1083" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1083" s="8" t="n"/>
@@ -64035,12 +64031,12 @@
       <c r="L1083" s="9" t="n"/>
       <c r="M1083" s="10" t="inlineStr">
         <is>
-          <t>職員室は0865-63-2526</t>
+          <t>0867-72-8032はFAX</t>
         </is>
       </c>
       <c r="N1083" s="11" t="inlineStr">
         <is>
-          <t>https://www.ok-ryukoku.ed.jp/</t>
+          <t>https://www.kyousei.ed.jp/</t>
         </is>
       </c>
       <c r="O1083" s="12" t="inlineStr">
@@ -64065,12 +64061,12 @@
       </c>
       <c r="D1084" s="5" t="inlineStr">
         <is>
-          <t>川崎医科大学附属高等学校</t>
+          <t>岡山県作陽高等学校</t>
         </is>
       </c>
       <c r="E1084" s="6" t="inlineStr">
         <is>
-          <t>086-462-3666</t>
+          <t>086-441-1281</t>
         </is>
       </c>
       <c r="F1084" s="7" t="inlineStr">
@@ -64092,10 +64088,14 @@
       </c>
       <c r="K1084" s="8" t="n"/>
       <c r="L1084" s="9" t="n"/>
-      <c r="M1084" s="10" t="n"/>
+      <c r="M1084" s="10" t="inlineStr">
+        <is>
+          <t>2023年4月に倉敷市玉島へ移転し「作陽学園高等学校」に校名変更。津山の旧番号0868-23-2188は使用不可の可能性</t>
+        </is>
+      </c>
       <c r="N1084" s="11" t="inlineStr">
         <is>
-          <t>https://s.kawasaki-m.ac.jp/</t>
+          <t>https://www.sakuyo-h.ed.jp/access/</t>
         </is>
       </c>
       <c r="O1084" s="12" t="inlineStr">
@@ -64115,17 +64115,17 @@
       </c>
       <c r="C1085" s="5" t="inlineStr">
         <is>
-          <t>岡山市北区</t>
+          <t>津山市</t>
         </is>
       </c>
       <c r="D1085" s="5" t="inlineStr">
         <is>
-          <t>関西高等学校</t>
+          <t>岡山県美作高等学校</t>
         </is>
       </c>
       <c r="E1085" s="6" t="inlineStr">
         <is>
-          <t>086-252-5121</t>
+          <t>0868-22-4838</t>
         </is>
       </c>
       <c r="F1085" s="7" t="inlineStr">
@@ -64135,7 +64135,7 @@
       </c>
       <c r="G1085" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1085" s="8" t="n"/>
@@ -64147,10 +64147,14 @@
       </c>
       <c r="K1085" s="8" t="n"/>
       <c r="L1085" s="9" t="n"/>
-      <c r="M1085" s="10" t="n"/>
+      <c r="M1085" s="10" t="inlineStr">
+        <is>
+          <t>全日制の番号。通信制課程は0868-23-3116</t>
+        </is>
+      </c>
       <c r="N1085" s="11" t="inlineStr">
         <is>
-          <t>https://kanzei.ac.jp/</t>
+          <t>https://mimasaka.jp/gakuen/houjin.html</t>
         </is>
       </c>
       <c r="O1085" s="12" t="inlineStr">
@@ -64170,17 +64174,17 @@
       </c>
       <c r="C1086" s="5" t="inlineStr">
         <is>
-          <t>吉備中央町</t>
+          <t>岡山市南区</t>
         </is>
       </c>
       <c r="D1086" s="5" t="inlineStr">
         <is>
-          <t>吉備高原学園高等学校</t>
+          <t>岡山高等学校</t>
         </is>
       </c>
       <c r="E1086" s="6" t="inlineStr">
         <is>
-          <t>0866-56-8211</t>
+          <t>086-282-6336</t>
         </is>
       </c>
       <c r="F1086" s="7" t="inlineStr">
@@ -64204,12 +64208,12 @@
       <c r="L1086" s="9" t="n"/>
       <c r="M1086" s="10" t="inlineStr">
         <is>
-          <t>全寮制</t>
+          <t>中高一貫</t>
         </is>
       </c>
       <c r="N1086" s="11" t="inlineStr">
         <is>
-          <t>https://www.kibikogengakuen.ed.jp/inquiry/form/</t>
+          <t>https://www.okayama-h.ed.jp/access/</t>
         </is>
       </c>
       <c r="O1086" s="12" t="inlineStr">
@@ -64229,17 +64233,17 @@
       </c>
       <c r="C1087" s="5" t="inlineStr">
         <is>
-          <t>倉敷市</t>
+          <t>浅口市</t>
         </is>
       </c>
       <c r="D1087" s="5" t="inlineStr">
         <is>
-          <t>倉敷高等学校</t>
+          <t>おかやま山陽高等学校</t>
         </is>
       </c>
       <c r="E1087" s="6" t="inlineStr">
         <is>
-          <t>086-462-9000</t>
+          <t>0865-44-3100</t>
         </is>
       </c>
       <c r="F1087" s="7" t="inlineStr">
@@ -64263,12 +64267,12 @@
       <c r="L1087" s="9" t="n"/>
       <c r="M1087" s="10" t="inlineStr">
         <is>
-          <t>岡山県私学協会の一覧とも一致</t>
+          <t>教員室直通は0865-44-7149</t>
         </is>
       </c>
       <c r="N1087" s="11" t="inlineStr">
         <is>
-          <t>https://www.kurashiki.ac.jp/news/</t>
+          <t>https://www.okayama-sanyo-hs.ed.jp/</t>
         </is>
       </c>
       <c r="O1087" s="12" t="inlineStr">
@@ -64288,17 +64292,17 @@
       </c>
       <c r="C1088" s="5" t="inlineStr">
         <is>
-          <t>倉敷市</t>
+          <t>岡山市北区</t>
         </is>
       </c>
       <c r="D1088" s="5" t="inlineStr">
         <is>
-          <t>倉敷翠松高等学校</t>
+          <t>岡山商科大学附属高等学校</t>
         </is>
       </c>
       <c r="E1088" s="6" t="inlineStr">
         <is>
-          <t>086-422-3565</t>
+          <t>086-252-3407</t>
         </is>
       </c>
       <c r="F1088" s="7" t="inlineStr">
@@ -64308,7 +64312,7 @@
       </c>
       <c r="G1088" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>専門学科・総合学科</t>
         </is>
       </c>
       <c r="H1088" s="8" t="n"/>
@@ -64320,14 +64324,10 @@
       </c>
       <c r="K1088" s="8" t="n"/>
       <c r="L1088" s="9" t="n"/>
-      <c r="M1088" s="10" t="inlineStr">
-        <is>
-          <t>教務室086-422-3570、専攻科086-427-0941</t>
-        </is>
-      </c>
+      <c r="M1088" s="10" t="n"/>
       <c r="N1088" s="11" t="inlineStr">
         <is>
-          <t>https://www.suisho.ed.jp/</t>
+          <t>https://www.osu-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1088" s="12" t="inlineStr">
@@ -64347,17 +64347,17 @@
       </c>
       <c r="C1089" s="5" t="inlineStr">
         <is>
-          <t>井原市</t>
+          <t>赤磐市</t>
         </is>
       </c>
       <c r="D1089" s="5" t="inlineStr">
         <is>
-          <t>興譲館高等学校</t>
+          <t>岡山白陵高等学校</t>
         </is>
       </c>
       <c r="E1089" s="6" t="inlineStr">
         <is>
-          <t>0866-62-0124</t>
+          <t>086-995-1255</t>
         </is>
       </c>
       <c r="F1089" s="7" t="inlineStr">
@@ -64381,12 +64381,12 @@
       <c r="L1089" s="9" t="n"/>
       <c r="M1089" s="10" t="inlineStr">
         <is>
-          <t>井原市の本校。通信制課程は0120-445033</t>
+          <t>中学校併設</t>
         </is>
       </c>
       <c r="N1089" s="11" t="inlineStr">
         <is>
-          <t>https://kojokan-h.ed.jp/</t>
+          <t>https://www.okahaku.ed.jp/access_inquiry/</t>
         </is>
       </c>
       <c r="O1089" s="12" t="inlineStr">
@@ -64406,17 +64406,17 @@
       </c>
       <c r="C1090" s="5" t="inlineStr">
         <is>
-          <t>浅口市</t>
+          <t>岡山市北区</t>
         </is>
       </c>
       <c r="D1090" s="5" t="inlineStr">
         <is>
-          <t>金光学園高等学校</t>
+          <t>岡山理科大学附属高等学校</t>
         </is>
       </c>
       <c r="E1090" s="6" t="inlineStr">
         <is>
-          <t>0865-42-3131</t>
+          <t>086-256-8511</t>
         </is>
       </c>
       <c r="F1090" s="7" t="inlineStr">
@@ -64440,12 +64440,12 @@
       <c r="L1090" s="9" t="n"/>
       <c r="M1090" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>通信制課程直通は086-256-8562</t>
         </is>
       </c>
       <c r="N1090" s="11" t="inlineStr">
         <is>
-          <t>https://www.konkougakuen.net/high/</t>
+          <t>https://okayama.ridaifu.net/contact/</t>
         </is>
       </c>
       <c r="O1090" s="12" t="inlineStr">
@@ -64465,17 +64465,17 @@
       </c>
       <c r="C1091" s="5" t="inlineStr">
         <is>
-          <t>岡山市中区</t>
+          <t>笠岡市</t>
         </is>
       </c>
       <c r="D1091" s="5" t="inlineStr">
         <is>
-          <t>山陽学園高等学校</t>
+          <t>岡山龍谷高等学校</t>
         </is>
       </c>
       <c r="E1091" s="6" t="inlineStr">
         <is>
-          <t>086-272-1181</t>
+          <t>0865-63-2525</t>
         </is>
       </c>
       <c r="F1091" s="7" t="inlineStr">
@@ -64485,7 +64485,7 @@
       </c>
       <c r="G1091" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1091" s="8" t="n"/>
@@ -64499,12 +64499,12 @@
       <c r="L1091" s="9" t="n"/>
       <c r="M1091" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>職員室は0865-63-2526</t>
         </is>
       </c>
       <c r="N1091" s="11" t="inlineStr">
         <is>
-          <t>https://www.sanyogakuen.ed.jp/school/access</t>
+          <t>https://www.ok-ryukoku.ed.jp/</t>
         </is>
       </c>
       <c r="O1091" s="12" t="inlineStr">
@@ -64524,17 +64524,17 @@
       </c>
       <c r="C1092" s="5" t="inlineStr">
         <is>
-          <t>岡山市北区</t>
+          <t>倉敷市</t>
         </is>
       </c>
       <c r="D1092" s="5" t="inlineStr">
         <is>
-          <t>就実高等学校</t>
+          <t>川崎医科大学附属高等学校</t>
         </is>
       </c>
       <c r="E1092" s="6" t="inlineStr">
         <is>
-          <t>086-225-1326</t>
+          <t>086-462-3666</t>
         </is>
       </c>
       <c r="F1092" s="7" t="inlineStr">
@@ -64559,7 +64559,7 @@
       <c r="M1092" s="10" t="n"/>
       <c r="N1092" s="11" t="inlineStr">
         <is>
-          <t>https://www.shujitsu-gakuen.jp/contact/index.html</t>
+          <t>https://s.kawasaki-m.ac.jp/</t>
         </is>
       </c>
       <c r="O1092" s="12" t="inlineStr">
@@ -64579,17 +64579,17 @@
       </c>
       <c r="C1093" s="5" t="inlineStr">
         <is>
-          <t>倉敷市</t>
+          <t>岡山市北区</t>
         </is>
       </c>
       <c r="D1093" s="5" t="inlineStr">
         <is>
-          <t>清心女子高等学校（岡山県）</t>
+          <t>関西高等学校</t>
         </is>
       </c>
       <c r="E1093" s="6" t="inlineStr">
         <is>
-          <t>086-462-1661</t>
+          <t>086-252-5121</t>
         </is>
       </c>
       <c r="F1093" s="7" t="inlineStr">
@@ -64599,7 +64599,7 @@
       </c>
       <c r="G1093" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1093" s="8" t="n"/>
@@ -64611,14 +64611,10 @@
       </c>
       <c r="K1093" s="8" t="n"/>
       <c r="L1093" s="9" t="n"/>
-      <c r="M1093" s="10" t="inlineStr">
-        <is>
-          <t>ノートルダム清心学園（倉敷市）。中学校併設</t>
-        </is>
-      </c>
+      <c r="M1093" s="10" t="n"/>
       <c r="N1093" s="11" t="inlineStr">
         <is>
-          <t>https://www.nd-seishin.ac.jp/school/access/</t>
+          <t>https://kanzei.ac.jp/</t>
         </is>
       </c>
       <c r="O1093" s="12" t="inlineStr">
@@ -64638,17 +64634,17 @@
       </c>
       <c r="C1094" s="5" t="inlineStr">
         <is>
-          <t>岡山市北区</t>
+          <t>吉備中央町</t>
         </is>
       </c>
       <c r="D1094" s="5" t="inlineStr">
         <is>
-          <t>創志学園高等学校</t>
+          <t>吉備高原学園高等学校</t>
         </is>
       </c>
       <c r="E1094" s="6" t="inlineStr">
         <is>
-          <t>086-252-2101</t>
+          <t>0866-56-8211</t>
         </is>
       </c>
       <c r="F1094" s="7" t="inlineStr">
@@ -64658,7 +64654,7 @@
       </c>
       <c r="G1094" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1094" s="8" t="n"/>
@@ -64672,12 +64668,12 @@
       <c r="L1094" s="9" t="n"/>
       <c r="M1094" s="10" t="inlineStr">
         <is>
-          <t>入試広報室は0120-151752</t>
+          <t>全寮制</t>
         </is>
       </c>
       <c r="N1094" s="11" t="inlineStr">
         <is>
-          <t>https://www.soshigakuen.ed.jp/access/</t>
+          <t>https://www.kibikogengakuen.ed.jp/inquiry/form/</t>
         </is>
       </c>
       <c r="O1094" s="12" t="inlineStr">
@@ -64697,17 +64693,17 @@
       </c>
       <c r="C1095" s="5" t="inlineStr">
         <is>
-          <t>高梁市</t>
+          <t>倉敷市</t>
         </is>
       </c>
       <c r="D1095" s="5" t="inlineStr">
         <is>
-          <t>方谷學舎高等学校</t>
+          <t>倉敷高等学校</t>
         </is>
       </c>
       <c r="E1095" s="6" t="inlineStr">
         <is>
-          <t>0866-22-2205</t>
+          <t>086-462-9000</t>
         </is>
       </c>
       <c r="F1095" s="7" t="inlineStr">
@@ -64717,7 +64713,7 @@
       </c>
       <c r="G1095" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1095" s="8" t="n"/>
@@ -64731,12 +64727,12 @@
       <c r="L1095" s="9" t="n"/>
       <c r="M1095" s="10" t="inlineStr">
         <is>
-          <t>2023年6月に「岡山県高梁日新高等学校」から校名変更。事務室番号（教務室は0866-56-0015）</t>
+          <t>岡山県私学協会の一覧とも一致</t>
         </is>
       </c>
       <c r="N1095" s="11" t="inlineStr">
         <is>
-          <t>https://www.houkoku-gakusha.ed.jp/introduction/</t>
+          <t>https://www.kurashiki.ac.jp/news/</t>
         </is>
       </c>
       <c r="O1095" s="12" t="inlineStr">
@@ -64756,17 +64752,17 @@
       </c>
       <c r="C1096" s="5" t="inlineStr">
         <is>
-          <t>岡山市北区</t>
+          <t>倉敷市</t>
         </is>
       </c>
       <c r="D1096" s="5" t="inlineStr">
         <is>
-          <t>明誠学院高等学校</t>
+          <t>倉敷翠松高等学校</t>
         </is>
       </c>
       <c r="E1096" s="6" t="inlineStr">
         <is>
-          <t>086-252-5247</t>
+          <t>086-422-3565</t>
         </is>
       </c>
       <c r="F1096" s="7" t="inlineStr">
@@ -64776,7 +64772,7 @@
       </c>
       <c r="G1096" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1096" s="8" t="n"/>
@@ -64788,10 +64784,14 @@
       </c>
       <c r="K1096" s="8" t="n"/>
       <c r="L1096" s="9" t="n"/>
-      <c r="M1096" s="10" t="n"/>
+      <c r="M1096" s="10" t="inlineStr">
+        <is>
+          <t>教務室086-422-3570、専攻科086-427-0941</t>
+        </is>
+      </c>
       <c r="N1096" s="11" t="inlineStr">
         <is>
-          <t>https://www.meiseigakuin.ac.jp/</t>
+          <t>https://www.suisho.ed.jp/</t>
         </is>
       </c>
       <c r="O1096" s="12" t="inlineStr">
@@ -64806,22 +64806,22 @@
       </c>
       <c r="B1097" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1097" s="5" t="inlineStr">
         <is>
-          <t>広島市安佐南区</t>
+          <t>井原市</t>
         </is>
       </c>
       <c r="D1097" s="5" t="inlineStr">
         <is>
-          <t>AICJ高等学校</t>
+          <t>興譲館高等学校</t>
         </is>
       </c>
       <c r="E1097" s="6" t="inlineStr">
         <is>
-          <t>082-832-5037</t>
+          <t>0866-62-0124</t>
         </is>
       </c>
       <c r="F1097" s="7" t="inlineStr">
@@ -64845,12 +64845,12 @@
       <c r="L1097" s="9" t="n"/>
       <c r="M1097" s="10" t="inlineStr">
         <is>
-          <t>一部サイトに旧番号らしい082-874-3081の記載あり</t>
+          <t>井原市の本校。通信制課程は0120-445033</t>
         </is>
       </c>
       <c r="N1097" s="11" t="inlineStr">
         <is>
-          <t>https://aicj.ed.jp/access.html</t>
+          <t>https://kojokan-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1097" s="12" t="inlineStr">
@@ -64865,22 +64865,22 @@
       </c>
       <c r="B1098" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1098" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>浅口市</t>
         </is>
       </c>
       <c r="D1098" s="5" t="inlineStr">
         <is>
-          <t>盈進高等学校</t>
+          <t>金光学園高等学校</t>
         </is>
       </c>
       <c r="E1098" s="6" t="inlineStr">
         <is>
-          <t>084-955-2333</t>
+          <t>0865-42-3131</t>
         </is>
       </c>
       <c r="F1098" s="7" t="inlineStr">
@@ -64904,12 +64904,12 @@
       <c r="L1098" s="9" t="n"/>
       <c r="M1098" s="10" t="inlineStr">
         <is>
-          <t>中高共通の代表番号</t>
+          <t>中高共通番号</t>
         </is>
       </c>
       <c r="N1098" s="11" t="inlineStr">
         <is>
-          <t>https://www.eishin.ed.jp/access/</t>
+          <t>https://www.konkougakuen.net/high/</t>
         </is>
       </c>
       <c r="O1098" s="12" t="inlineStr">
@@ -64924,22 +64924,22 @@
       </c>
       <c r="B1099" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1099" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>岡山市中区</t>
         </is>
       </c>
       <c r="D1099" s="5" t="inlineStr">
         <is>
-          <t>英数学館高等学校</t>
+          <t>山陽学園高等学校</t>
         </is>
       </c>
       <c r="E1099" s="6" t="inlineStr">
         <is>
-          <t>084-941-4115</t>
+          <t>086-272-1181</t>
         </is>
       </c>
       <c r="F1099" s="7" t="inlineStr">
@@ -64963,12 +64963,12 @@
       <c r="L1099" s="9" t="n"/>
       <c r="M1099" s="10" t="inlineStr">
         <is>
-          <t>一部サイトに084-941-4117の記載あり（旧番号か）</t>
+          <t>中高共通番号</t>
         </is>
       </c>
       <c r="N1099" s="11" t="inlineStr">
         <is>
-          <t>https://goto.eisu-ejs.ac.jp/access/</t>
+          <t>https://www.sanyogakuen.ed.jp/school/access</t>
         </is>
       </c>
       <c r="O1099" s="12" t="inlineStr">
@@ -64983,22 +64983,22 @@
       </c>
       <c r="B1100" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1100" s="5" t="inlineStr">
         <is>
-          <t>尾道市</t>
+          <t>岡山市北区</t>
         </is>
       </c>
       <c r="D1100" s="5" t="inlineStr">
         <is>
-          <t>尾道高等学校</t>
+          <t>就実高等学校</t>
         </is>
       </c>
       <c r="E1100" s="6" t="inlineStr">
         <is>
-          <t>0848-20-6612</t>
+          <t>086-225-1326</t>
         </is>
       </c>
       <c r="F1100" s="7" t="inlineStr">
@@ -65008,7 +65008,7 @@
       </c>
       <c r="G1100" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1100" s="8" t="n"/>
@@ -65020,14 +65020,10 @@
       </c>
       <c r="K1100" s="8" t="n"/>
       <c r="L1100" s="9" t="n"/>
-      <c r="M1100" s="10" t="inlineStr">
-        <is>
-          <t>2009年に向島町へ移転。旧番号0848-23-2311が残るサイトあり</t>
-        </is>
-      </c>
+      <c r="M1100" s="10" t="n"/>
       <c r="N1100" s="11" t="inlineStr">
         <is>
-          <t>https://onomichi.ac.jp/</t>
+          <t>https://www.shujitsu-gakuen.jp/contact/index.html</t>
         </is>
       </c>
       <c r="O1100" s="12" t="inlineStr">
@@ -65042,22 +65038,22 @@
       </c>
       <c r="B1101" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1101" s="5" t="inlineStr">
         <is>
-          <t>東広島市</t>
+          <t>倉敷市</t>
         </is>
       </c>
       <c r="D1101" s="5" t="inlineStr">
         <is>
-          <t>近畿大学附属広島高等学校東広島校</t>
+          <t>清心女子高等学校（岡山県）</t>
         </is>
       </c>
       <c r="E1101" s="6" t="inlineStr">
         <is>
-          <t>082-434-7111</t>
+          <t>086-462-1661</t>
         </is>
       </c>
       <c r="F1101" s="7" t="inlineStr">
@@ -65079,10 +65075,14 @@
       </c>
       <c r="K1101" s="8" t="n"/>
       <c r="L1101" s="9" t="n"/>
-      <c r="M1101" s="10" t="n"/>
+      <c r="M1101" s="10" t="inlineStr">
+        <is>
+          <t>ノートルダム清心学園（倉敷市）。中学校併設</t>
+        </is>
+      </c>
       <c r="N1101" s="11" t="inlineStr">
         <is>
-          <t>https://hh.kindai.ac.jp/</t>
+          <t>https://www.nd-seishin.ac.jp/school/access/</t>
         </is>
       </c>
       <c r="O1101" s="12" t="inlineStr">
@@ -65097,22 +65097,22 @@
       </c>
       <c r="B1102" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1102" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>岡山市北区</t>
         </is>
       </c>
       <c r="D1102" s="5" t="inlineStr">
         <is>
-          <t>近畿大学附属広島高等学校福山校</t>
+          <t>創志学園高等学校</t>
         </is>
       </c>
       <c r="E1102" s="6" t="inlineStr">
         <is>
-          <t>084-951-2695</t>
+          <t>086-252-2101</t>
         </is>
       </c>
       <c r="F1102" s="7" t="inlineStr">
@@ -65122,7 +65122,7 @@
       </c>
       <c r="G1102" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1102" s="8" t="n"/>
@@ -65136,12 +65136,12 @@
       <c r="L1102" s="9" t="n"/>
       <c r="M1102" s="10" t="inlineStr">
         <is>
-          <t>旧称は近畿大学附属福山高等学校</t>
+          <t>入試広報室は0120-151752</t>
         </is>
       </c>
       <c r="N1102" s="11" t="inlineStr">
         <is>
-          <t>https://www.fukuyama.kindai.ac.jp/gakko/gakko-shokai.html</t>
+          <t>https://www.soshigakuen.ed.jp/access/</t>
         </is>
       </c>
       <c r="O1102" s="12" t="inlineStr">
@@ -65156,22 +65156,22 @@
       </c>
       <c r="B1103" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1103" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>高梁市</t>
         </is>
       </c>
       <c r="D1103" s="5" t="inlineStr">
         <is>
-          <t>銀河学院高等学校</t>
+          <t>方谷學舎高等学校</t>
         </is>
       </c>
       <c r="E1103" s="6" t="inlineStr">
         <is>
-          <t>084-941-9292</t>
+          <t>0866-22-2205</t>
         </is>
       </c>
       <c r="F1103" s="7" t="inlineStr">
@@ -65195,12 +65195,12 @@
       <c r="L1103" s="9" t="n"/>
       <c r="M1103" s="10" t="inlineStr">
         <is>
-          <t>公式（法人事務室）に記載、複数サイトも一致</t>
+          <t>2023年6月に「岡山県高梁日新高等学校」から校名変更。事務室番号（教務室は0866-56-0015）</t>
         </is>
       </c>
       <c r="N1103" s="11" t="inlineStr">
         <is>
-          <t>https://www.ginga.ac.jp/donationginga/</t>
+          <t>https://www.houkoku-gakusha.ed.jp/introduction/</t>
         </is>
       </c>
       <c r="O1103" s="12" t="inlineStr">
@@ -65215,22 +65215,22 @@
       </c>
       <c r="B1104" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1104" s="5" t="inlineStr">
         <is>
-          <t>呉市</t>
+          <t>岡山市北区</t>
         </is>
       </c>
       <c r="D1104" s="5" t="inlineStr">
         <is>
-          <t>呉青山高等学校</t>
+          <t>明誠学院高等学校</t>
         </is>
       </c>
       <c r="E1104" s="6" t="inlineStr">
         <is>
-          <t>0823-32-1721</t>
+          <t>086-252-5247</t>
         </is>
       </c>
       <c r="F1104" s="7" t="inlineStr">
@@ -65252,14 +65252,10 @@
       </c>
       <c r="K1104" s="8" t="n"/>
       <c r="L1104" s="9" t="n"/>
-      <c r="M1104" s="10" t="inlineStr">
-        <is>
-          <t>2027年4月に「星の杜広島中学校・高等学校」へ校名変更予定</t>
-        </is>
-      </c>
+      <c r="M1104" s="10" t="n"/>
       <c r="N1104" s="11" t="inlineStr">
         <is>
-          <t>https://www.kureaoyama.ed.jp/</t>
+          <t>https://www.meiseigakuin.ac.jp/</t>
         </is>
       </c>
       <c r="O1104" s="12" t="inlineStr">
@@ -65284,12 +65280,12 @@
       </c>
       <c r="D1105" s="5" t="inlineStr">
         <is>
-          <t>広陵高等学校</t>
+          <t>AICJ高等学校</t>
         </is>
       </c>
       <c r="E1105" s="6" t="inlineStr">
         <is>
-          <t>082-848-1321</t>
+          <t>082-832-5037</t>
         </is>
       </c>
       <c r="F1105" s="7" t="inlineStr">
@@ -65311,10 +65307,14 @@
       </c>
       <c r="K1105" s="8" t="n"/>
       <c r="L1105" s="9" t="n"/>
-      <c r="M1105" s="10" t="n"/>
+      <c r="M1105" s="10" t="inlineStr">
+        <is>
+          <t>一部サイトに旧番号らしい082-874-3081の記載あり</t>
+        </is>
+      </c>
       <c r="N1105" s="11" t="inlineStr">
         <is>
-          <t>https://www.koryo.ac.jp/</t>
+          <t>https://aicj.ed.jp/access.html</t>
         </is>
       </c>
       <c r="O1105" s="12" t="inlineStr">
@@ -65334,17 +65334,17 @@
       </c>
       <c r="C1106" s="5" t="inlineStr">
         <is>
-          <t>呉市</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1106" s="5" t="inlineStr">
         <is>
-          <t>呉港高等学校</t>
+          <t>盈進高等学校</t>
         </is>
       </c>
       <c r="E1106" s="6" t="inlineStr">
         <is>
-          <t>0823-71-9163</t>
+          <t>084-955-2333</t>
         </is>
       </c>
       <c r="F1106" s="7" t="inlineStr">
@@ -65354,7 +65354,7 @@
       </c>
       <c r="G1106" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1106" s="8" t="n"/>
@@ -65366,10 +65366,14 @@
       </c>
       <c r="K1106" s="8" t="n"/>
       <c r="L1106" s="9" t="n"/>
-      <c r="M1106" s="10" t="n"/>
+      <c r="M1106" s="10" t="inlineStr">
+        <is>
+          <t>中高共通の代表番号</t>
+        </is>
+      </c>
       <c r="N1106" s="11" t="inlineStr">
         <is>
-          <t>https://www.goko.ac.jp/?page_id=96</t>
+          <t>https://www.eishin.ed.jp/access/</t>
         </is>
       </c>
       <c r="O1106" s="12" t="inlineStr">
@@ -65389,17 +65393,17 @@
       </c>
       <c r="C1107" s="5" t="inlineStr">
         <is>
-          <t>広島市西区</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1107" s="5" t="inlineStr">
         <is>
-          <t>山陽高等学校</t>
+          <t>英数学館高等学校</t>
         </is>
       </c>
       <c r="E1107" s="6" t="inlineStr">
         <is>
-          <t>082-232-9156</t>
+          <t>084-941-4115</t>
         </is>
       </c>
       <c r="F1107" s="7" t="inlineStr">
@@ -65409,7 +65413,7 @@
       </c>
       <c r="G1107" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1107" s="8" t="n"/>
@@ -65423,12 +65427,12 @@
       <c r="L1107" s="9" t="n"/>
       <c r="M1107" s="10" t="inlineStr">
         <is>
-          <t>正式名は広島山陽学園山陽高等学校</t>
+          <t>一部サイトに084-941-4117の記載あり（旧番号か）</t>
         </is>
       </c>
       <c r="N1107" s="11" t="inlineStr">
         <is>
-          <t>https://www.sanyo.ed.jp/gakkou/access/</t>
+          <t>https://goto.eisu-ejs.ac.jp/access/</t>
         </is>
       </c>
       <c r="O1107" s="12" t="inlineStr">
@@ -65448,17 +65452,17 @@
       </c>
       <c r="C1108" s="5" t="inlineStr">
         <is>
-          <t>廿日市市</t>
+          <t>尾道市</t>
         </is>
       </c>
       <c r="D1108" s="5" t="inlineStr">
         <is>
-          <t>山陽女学園高等部</t>
+          <t>尾道高等学校</t>
         </is>
       </c>
       <c r="E1108" s="6" t="inlineStr">
         <is>
-          <t>0829-32-2222</t>
+          <t>0848-20-6612</t>
         </is>
       </c>
       <c r="F1108" s="7" t="inlineStr">
@@ -65482,12 +65486,12 @@
       <c r="L1108" s="9" t="n"/>
       <c r="M1108" s="10" t="inlineStr">
         <is>
-          <t>通信制リアライズコースは0829-32-3330</t>
+          <t>2009年に向島町へ移転。旧番号0848-23-2311が残るサイトあり</t>
         </is>
       </c>
       <c r="N1108" s="11" t="inlineStr">
         <is>
-          <t>https://sanyo-jogakuen.ed.jp/</t>
+          <t>https://onomichi.ac.jp/</t>
         </is>
       </c>
       <c r="O1108" s="12" t="inlineStr">
@@ -65507,17 +65511,17 @@
       </c>
       <c r="C1109" s="5" t="inlineStr">
         <is>
-          <t>呉市</t>
+          <t>東広島市</t>
         </is>
       </c>
       <c r="D1109" s="5" t="inlineStr">
         <is>
-          <t>清水ヶ丘高等学校</t>
+          <t>近畿大学附属広島高等学校東広島校</t>
         </is>
       </c>
       <c r="E1109" s="6" t="inlineStr">
         <is>
-          <t>0823-23-1520</t>
+          <t>082-434-7111</t>
         </is>
       </c>
       <c r="F1109" s="7" t="inlineStr">
@@ -65527,7 +65531,7 @@
       </c>
       <c r="G1109" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1109" s="8" t="n"/>
@@ -65539,14 +65543,10 @@
       </c>
       <c r="K1109" s="8" t="n"/>
       <c r="L1109" s="9" t="n"/>
-      <c r="M1109" s="10" t="inlineStr">
-        <is>
-          <t>法人事務局は0823-22-0012</t>
-        </is>
-      </c>
+      <c r="M1109" s="10" t="n"/>
       <c r="N1109" s="11" t="inlineStr">
         <is>
-          <t>https://www.shimizugaoka.ed.jp/</t>
+          <t>https://hh.kindai.ac.jp/</t>
         </is>
       </c>
       <c r="O1109" s="12" t="inlineStr">
@@ -65566,17 +65566,17 @@
       </c>
       <c r="C1110" s="5" t="inlineStr">
         <is>
-          <t>広島市中区</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1110" s="5" t="inlineStr">
         <is>
-          <t>修道高等学校</t>
+          <t>近畿大学附属広島高等学校福山校</t>
         </is>
       </c>
       <c r="E1110" s="6" t="inlineStr">
         <is>
-          <t>082-241-8291</t>
+          <t>084-951-2695</t>
         </is>
       </c>
       <c r="F1110" s="7" t="inlineStr">
@@ -65600,12 +65600,12 @@
       <c r="L1110" s="9" t="n"/>
       <c r="M1110" s="10" t="inlineStr">
         <is>
-          <t>中高共通の代表番号</t>
+          <t>旧称は近畿大学附属福山高等学校</t>
         </is>
       </c>
       <c r="N1110" s="11" t="inlineStr">
         <is>
-          <t>https://www.shudo-h.ed.jp/</t>
+          <t>https://www.fukuyama.kindai.ac.jp/gakko/gakko-shokai.html</t>
         </is>
       </c>
       <c r="O1110" s="12" t="inlineStr">
@@ -65625,17 +65625,17 @@
       </c>
       <c r="C1111" s="5" t="inlineStr">
         <is>
-          <t>広島市南区</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1111" s="5" t="inlineStr">
         <is>
-          <t>進徳女子高等学校</t>
+          <t>銀河学院高等学校</t>
         </is>
       </c>
       <c r="E1111" s="6" t="inlineStr">
         <is>
-          <t>082-251-6431</t>
+          <t>084-941-9292</t>
         </is>
       </c>
       <c r="F1111" s="7" t="inlineStr">
@@ -65645,7 +65645,7 @@
       </c>
       <c r="G1111" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1111" s="8" t="n"/>
@@ -65657,10 +65657,14 @@
       </c>
       <c r="K1111" s="8" t="n"/>
       <c r="L1111" s="9" t="n"/>
-      <c r="M1111" s="10" t="n"/>
+      <c r="M1111" s="10" t="inlineStr">
+        <is>
+          <t>公式（法人事務室）に記載、複数サイトも一致</t>
+        </is>
+      </c>
       <c r="N1111" s="11" t="inlineStr">
         <is>
-          <t>https://www.shintoku.ed.jp/</t>
+          <t>https://www.ginga.ac.jp/donationginga/</t>
         </is>
       </c>
       <c r="O1111" s="12" t="inlineStr">
@@ -65680,17 +65684,17 @@
       </c>
       <c r="C1112" s="5" t="inlineStr">
         <is>
-          <t>三原市</t>
+          <t>呉市</t>
         </is>
       </c>
       <c r="D1112" s="5" t="inlineStr">
         <is>
-          <t>如水館高等学校</t>
+          <t>呉青山高等学校</t>
         </is>
       </c>
       <c r="E1112" s="6" t="inlineStr">
         <is>
-          <t>0848-63-2423</t>
+          <t>0823-32-1721</t>
         </is>
       </c>
       <c r="F1112" s="7" t="inlineStr">
@@ -65712,10 +65716,14 @@
       </c>
       <c r="K1112" s="8" t="n"/>
       <c r="L1112" s="9" t="n"/>
-      <c r="M1112" s="10" t="n"/>
+      <c r="M1112" s="10" t="inlineStr">
+        <is>
+          <t>2027年4月に「星の杜広島中学校・高等学校」へ校名変更予定</t>
+        </is>
+      </c>
       <c r="N1112" s="11" t="inlineStr">
         <is>
-          <t>https://www.josuikan.ed.jp/about/gaiyou</t>
+          <t>https://www.kureaoyama.ed.jp/</t>
         </is>
       </c>
       <c r="O1112" s="12" t="inlineStr">
@@ -65735,17 +65743,17 @@
       </c>
       <c r="C1113" s="5" t="inlineStr">
         <is>
-          <t>広島市西区</t>
+          <t>広島市安佐南区</t>
         </is>
       </c>
       <c r="D1113" s="5" t="inlineStr">
         <is>
-          <t>崇徳高等学校</t>
+          <t>広陵高等学校</t>
         </is>
       </c>
       <c r="E1113" s="6" t="inlineStr">
         <is>
-          <t>082-237-9331</t>
+          <t>082-848-1321</t>
         </is>
       </c>
       <c r="F1113" s="7" t="inlineStr">
@@ -65770,7 +65778,7 @@
       <c r="M1113" s="10" t="n"/>
       <c r="N1113" s="11" t="inlineStr">
         <is>
-          <t>https://www.sotoku.ed.jp/</t>
+          <t>https://www.koryo.ac.jp/</t>
         </is>
       </c>
       <c r="O1113" s="12" t="inlineStr">
@@ -65790,17 +65798,17 @@
       </c>
       <c r="C1114" s="5" t="inlineStr">
         <is>
-          <t>東広島市</t>
+          <t>呉市</t>
         </is>
       </c>
       <c r="D1114" s="5" t="inlineStr">
         <is>
-          <t>武田高等学校</t>
+          <t>呉港高等学校</t>
         </is>
       </c>
       <c r="E1114" s="6" t="inlineStr">
         <is>
-          <t>0823-82-2331</t>
+          <t>0823-71-9163</t>
         </is>
       </c>
       <c r="F1114" s="7" t="inlineStr">
@@ -65810,7 +65818,7 @@
       </c>
       <c r="G1114" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1114" s="8" t="n"/>
@@ -65825,7 +65833,7 @@
       <c r="M1114" s="10" t="n"/>
       <c r="N1114" s="11" t="inlineStr">
         <is>
-          <t>https://takeda.ed.jp/</t>
+          <t>https://www.goko.ac.jp/?page_id=96</t>
         </is>
       </c>
       <c r="O1114" s="12" t="inlineStr">
@@ -65845,17 +65853,17 @@
       </c>
       <c r="C1115" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>広島市西区</t>
         </is>
       </c>
       <c r="D1115" s="5" t="inlineStr">
         <is>
-          <t>東林館高等学校</t>
+          <t>山陽高等学校</t>
         </is>
       </c>
       <c r="E1115" s="6" t="inlineStr">
         <is>
-          <t>084-923-4543</t>
+          <t>082-232-9156</t>
         </is>
       </c>
       <c r="F1115" s="7" t="inlineStr">
@@ -65865,7 +65873,7 @@
       </c>
       <c r="G1115" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1115" s="8" t="n"/>
@@ -65879,12 +65887,12 @@
       <c r="L1115" s="9" t="n"/>
       <c r="M1115" s="10" t="inlineStr">
         <is>
-          <t>通信制。2010年に本校を神石高原町から福山市へ移転。旧番号0847-85-2041が残るサイトあり</t>
+          <t>正式名は広島山陽学園山陽高等学校</t>
         </is>
       </c>
       <c r="N1115" s="11" t="inlineStr">
         <is>
-          <t>https://www.tohrinkan.com/</t>
+          <t>https://www.sanyo.ed.jp/gakkou/access/</t>
         </is>
       </c>
       <c r="O1115" s="12" t="inlineStr">
@@ -65904,17 +65912,17 @@
       </c>
       <c r="C1116" s="5" t="inlineStr">
         <is>
-          <t>広島市中区</t>
+          <t>廿日市市</t>
         </is>
       </c>
       <c r="D1116" s="5" t="inlineStr">
         <is>
-          <t>並木学院高等学校</t>
+          <t>山陽女学園高等部</t>
         </is>
       </c>
       <c r="E1116" s="6" t="inlineStr">
         <is>
-          <t>082-241-9066</t>
+          <t>0829-32-2222</t>
         </is>
       </c>
       <c r="F1116" s="7" t="inlineStr">
@@ -65924,7 +65932,7 @@
       </c>
       <c r="G1116" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1116" s="8" t="n"/>
@@ -65938,12 +65946,12 @@
       <c r="L1116" s="9" t="n"/>
       <c r="M1116" s="10" t="inlineStr">
         <is>
-          <t>FAXは082-241-5211</t>
+          <t>通信制リアライズコースは0829-32-3330</t>
         </is>
       </c>
       <c r="N1116" s="11" t="inlineStr">
         <is>
-          <t>https://namikigakuin.ac.jp/school-info/group/</t>
+          <t>https://sanyo-jogakuen.ed.jp/</t>
         </is>
       </c>
       <c r="O1116" s="12" t="inlineStr">
@@ -65963,17 +65971,17 @@
       </c>
       <c r="C1117" s="5" t="inlineStr">
         <is>
-          <t>広島市西区</t>
+          <t>呉市</t>
         </is>
       </c>
       <c r="D1117" s="5" t="inlineStr">
         <is>
-          <t>ノートルダム清心高等学校</t>
+          <t>清水ヶ丘高等学校</t>
         </is>
       </c>
       <c r="E1117" s="6" t="inlineStr">
         <is>
-          <t>082-271-1724</t>
+          <t>0823-23-1520</t>
         </is>
       </c>
       <c r="F1117" s="7" t="inlineStr">
@@ -65983,7 +65991,7 @@
       </c>
       <c r="G1117" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1117" s="8" t="n"/>
@@ -65997,12 +66005,12 @@
       <c r="L1117" s="9" t="n"/>
       <c r="M1117" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>法人事務局は0823-22-0012</t>
         </is>
       </c>
       <c r="N1117" s="11" t="inlineStr">
         <is>
-          <t>https://www.hiro-seishin.ed.jp/contact/</t>
+          <t>https://www.shimizugaoka.ed.jp/</t>
         </is>
       </c>
       <c r="O1117" s="12" t="inlineStr">
@@ -66022,17 +66030,17 @@
       </c>
       <c r="C1118" s="5" t="inlineStr">
         <is>
-          <t>広島市南区</t>
+          <t>広島市中区</t>
         </is>
       </c>
       <c r="D1118" s="5" t="inlineStr">
         <is>
-          <t>比治山学園高等学校</t>
+          <t>修道高等学校</t>
         </is>
       </c>
       <c r="E1118" s="6" t="inlineStr">
         <is>
-          <t>082-251-4478</t>
+          <t>082-241-8291</t>
         </is>
       </c>
       <c r="F1118" s="7" t="inlineStr">
@@ -66056,12 +66064,12 @@
       <c r="L1118" s="9" t="n"/>
       <c r="M1118" s="10" t="inlineStr">
         <is>
-          <t>旧・比治山女子。2026年4月に共学化・校名変更。新サイト https://www.hijiyama-h.ed.jp/</t>
+          <t>中高共通の代表番号</t>
         </is>
       </c>
       <c r="N1118" s="11" t="inlineStr">
         <is>
-          <t>https://www.hijiyamajoshi-h.ed.jp/education/</t>
+          <t>https://www.shudo-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1118" s="12" t="inlineStr">
@@ -66081,17 +66089,17 @@
       </c>
       <c r="C1119" s="5" t="inlineStr">
         <is>
-          <t>広島市西区</t>
+          <t>広島市南区</t>
         </is>
       </c>
       <c r="D1119" s="5" t="inlineStr">
         <is>
-          <t>広島学院高等学校</t>
+          <t>進徳女子高等学校</t>
         </is>
       </c>
       <c r="E1119" s="6" t="inlineStr">
         <is>
-          <t>082-271-0241</t>
+          <t>082-251-6431</t>
         </is>
       </c>
       <c r="F1119" s="7" t="inlineStr">
@@ -66101,7 +66109,7 @@
       </c>
       <c r="G1119" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1119" s="8" t="n"/>
@@ -66113,14 +66121,10 @@
       </c>
       <c r="K1119" s="8" t="n"/>
       <c r="L1119" s="9" t="n"/>
-      <c r="M1119" s="10" t="inlineStr">
-        <is>
-          <t>中高共通番号</t>
-        </is>
-      </c>
+      <c r="M1119" s="10" t="n"/>
       <c r="N1119" s="11" t="inlineStr">
         <is>
-          <t>https://www.hiroshimagakuin.ed.jp/contact/</t>
+          <t>https://www.shintoku.ed.jp/</t>
         </is>
       </c>
       <c r="O1119" s="12" t="inlineStr">
@@ -66140,17 +66144,17 @@
       </c>
       <c r="C1120" s="5" t="inlineStr">
         <is>
-          <t>広島市西区</t>
+          <t>三原市</t>
         </is>
       </c>
       <c r="D1120" s="5" t="inlineStr">
         <is>
-          <t>広島工業大学高等学校</t>
+          <t>如水館高等学校</t>
         </is>
       </c>
       <c r="E1120" s="6" t="inlineStr">
         <is>
-          <t>082-277-9205</t>
+          <t>0848-63-2423</t>
         </is>
       </c>
       <c r="F1120" s="7" t="inlineStr">
@@ -66172,14 +66176,10 @@
       </c>
       <c r="K1120" s="8" t="n"/>
       <c r="L1120" s="9" t="n"/>
-      <c r="M1120" s="10" t="inlineStr">
-        <is>
-          <t>全日制（西区）。通信制（安佐南区）は082-849-6755</t>
-        </is>
-      </c>
+      <c r="M1120" s="10" t="n"/>
       <c r="N1120" s="11" t="inlineStr">
         <is>
-          <t>https://www.kodaikoko.ed.jp/zennichi/</t>
+          <t>https://www.josuikan.ed.jp/about/gaiyou</t>
         </is>
       </c>
       <c r="O1120" s="12" t="inlineStr">
@@ -66199,17 +66199,17 @@
       </c>
       <c r="C1121" s="5" t="inlineStr">
         <is>
-          <t>海田町</t>
+          <t>広島市西区</t>
         </is>
       </c>
       <c r="D1121" s="5" t="inlineStr">
         <is>
-          <t>広島国際学院高等学校</t>
+          <t>崇徳高等学校</t>
         </is>
       </c>
       <c r="E1121" s="6" t="inlineStr">
         <is>
-          <t>082-823-3401</t>
+          <t>082-237-9331</t>
         </is>
       </c>
       <c r="F1121" s="7" t="inlineStr">
@@ -66219,7 +66219,7 @@
       </c>
       <c r="G1121" s="5" t="inlineStr">
         <is>
-          <t>普通科・総合学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1121" s="8" t="n"/>
@@ -66231,14 +66231,10 @@
       </c>
       <c r="K1121" s="8" t="n"/>
       <c r="L1121" s="9" t="n"/>
-      <c r="M1121" s="10" t="inlineStr">
-        <is>
-          <t>全日制（海田町）。通信制の中野キャンパスは082-820-2515</t>
-        </is>
-      </c>
+      <c r="M1121" s="10" t="n"/>
       <c r="N1121" s="11" t="inlineStr">
         <is>
-          <t>https://www.hi.hkg.ac.jp/access</t>
+          <t>https://www.sotoku.ed.jp/</t>
         </is>
       </c>
       <c r="O1121" s="12" t="inlineStr">
@@ -66258,22 +66254,22 @@
       </c>
       <c r="C1122" s="5" t="inlineStr">
         <is>
-          <t>広島市東区</t>
+          <t>東広島市</t>
         </is>
       </c>
       <c r="D1122" s="5" t="inlineStr">
         <is>
-          <t>広島桜が丘高等学校</t>
+          <t>武田高等学校</t>
         </is>
       </c>
       <c r="E1122" s="6" t="inlineStr">
         <is>
-          <t>082-262-0128</t>
-        </is>
-      </c>
-      <c r="F1122" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>0823-82-2331</t>
+        </is>
+      </c>
+      <c r="F1122" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="G1122" s="5" t="inlineStr">
@@ -66290,14 +66286,10 @@
       </c>
       <c r="K1122" s="8" t="n"/>
       <c r="L1122" s="9" t="n"/>
-      <c r="M1122" s="10" t="inlineStr">
-        <is>
-          <t>公式未確認、複数サイトで一致</t>
-        </is>
-      </c>
+      <c r="M1122" s="10" t="n"/>
       <c r="N1122" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/34102/ILSP0000041015_ipclm/</t>
+          <t>https://takeda.ed.jp/</t>
         </is>
       </c>
       <c r="O1122" s="12" t="inlineStr">
@@ -66317,17 +66309,17 @@
       </c>
       <c r="C1123" s="5" t="inlineStr">
         <is>
-          <t>三原市</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1123" s="5" t="inlineStr">
         <is>
-          <t>広島三育学院高等学校</t>
+          <t>東林館高等学校</t>
         </is>
       </c>
       <c r="E1123" s="6" t="inlineStr">
         <is>
-          <t>0847-33-0311</t>
+          <t>084-923-4543</t>
         </is>
       </c>
       <c r="F1123" s="7" t="inlineStr">
@@ -66349,10 +66341,14 @@
       </c>
       <c r="K1123" s="8" t="n"/>
       <c r="L1123" s="9" t="n"/>
-      <c r="M1123" s="10" t="n"/>
+      <c r="M1123" s="10" t="inlineStr">
+        <is>
+          <t>通信制。2010年に本校を神石高原町から福山市へ移転。旧番号0847-85-2041が残るサイトあり</t>
+        </is>
+      </c>
       <c r="N1123" s="11" t="inlineStr">
         <is>
-          <t>https://www.saniku.ac.jp/hiroshima/about/profile.php</t>
+          <t>https://www.tohrinkan.com/</t>
         </is>
       </c>
       <c r="O1123" s="12" t="inlineStr">
@@ -66372,17 +66368,17 @@
       </c>
       <c r="C1124" s="5" t="inlineStr">
         <is>
-          <t>広島市西区</t>
+          <t>広島市中区</t>
         </is>
       </c>
       <c r="D1124" s="5" t="inlineStr">
         <is>
-          <t>広島修道大学ひろしま協創高等学校</t>
+          <t>並木学院高等学校</t>
         </is>
       </c>
       <c r="E1124" s="6" t="inlineStr">
         <is>
-          <t>082-278-1101</t>
+          <t>082-241-9066</t>
         </is>
       </c>
       <c r="F1124" s="7" t="inlineStr">
@@ -66404,10 +66400,14 @@
       </c>
       <c r="K1124" s="8" t="n"/>
       <c r="L1124" s="9" t="n"/>
-      <c r="M1124" s="10" t="n"/>
+      <c r="M1124" s="10" t="inlineStr">
+        <is>
+          <t>FAXは082-241-5211</t>
+        </is>
+      </c>
       <c r="N1124" s="11" t="inlineStr">
         <is>
-          <t>https://www.shudo-u.ac.jp/fuzoku/</t>
+          <t>https://namikigakuin.ac.jp/school-info/group/</t>
         </is>
       </c>
       <c r="O1124" s="12" t="inlineStr">
@@ -66427,17 +66427,17 @@
       </c>
       <c r="C1125" s="5" t="inlineStr">
         <is>
-          <t>坂町</t>
+          <t>広島市西区</t>
         </is>
       </c>
       <c r="D1125" s="5" t="inlineStr">
         <is>
-          <t>広島翔洋高等学校</t>
+          <t>ノートルダム清心高等学校</t>
         </is>
       </c>
       <c r="E1125" s="6" t="inlineStr">
         <is>
-          <t>082-884-1616</t>
+          <t>082-271-1724</t>
         </is>
       </c>
       <c r="F1125" s="7" t="inlineStr">
@@ -66447,7 +66447,7 @@
       </c>
       <c r="G1125" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1125" s="8" t="n"/>
@@ -66459,10 +66459,14 @@
       </c>
       <c r="K1125" s="8" t="n"/>
       <c r="L1125" s="9" t="n"/>
-      <c r="M1125" s="10" t="n"/>
+      <c r="M1125" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
       <c r="N1125" s="11" t="inlineStr">
         <is>
-          <t>https://www.h-shoyo.ed.jp/overview/details.php</t>
+          <t>https://www.hiro-seishin.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O1125" s="12" t="inlineStr">
@@ -66482,17 +66486,17 @@
       </c>
       <c r="C1126" s="5" t="inlineStr">
         <is>
-          <t>北広島町</t>
+          <t>広島市南区</t>
         </is>
       </c>
       <c r="D1126" s="5" t="inlineStr">
         <is>
-          <t>広島新庄高等学校</t>
+          <t>比治山学園高等学校</t>
         </is>
       </c>
       <c r="E1126" s="6" t="inlineStr">
         <is>
-          <t>0826-82-2323</t>
+          <t>082-251-4478</t>
         </is>
       </c>
       <c r="F1126" s="7" t="inlineStr">
@@ -66514,10 +66518,14 @@
       </c>
       <c r="K1126" s="8" t="n"/>
       <c r="L1126" s="9" t="n"/>
-      <c r="M1126" s="10" t="n"/>
+      <c r="M1126" s="10" t="inlineStr">
+        <is>
+          <t>旧・比治山女子。2026年4月に共学化・校名変更。新サイト https://www.hijiyama-h.ed.jp/</t>
+        </is>
+      </c>
       <c r="N1126" s="11" t="inlineStr">
         <is>
-          <t>https://www.shinjou.jp/toiawase/toiawase.html</t>
+          <t>https://www.hijiyamajoshi-h.ed.jp/education/</t>
         </is>
       </c>
       <c r="O1126" s="12" t="inlineStr">
@@ -66537,17 +66545,17 @@
       </c>
       <c r="C1127" s="5" t="inlineStr">
         <is>
-          <t>広島市東区</t>
+          <t>広島市西区</t>
         </is>
       </c>
       <c r="D1127" s="5" t="inlineStr">
         <is>
-          <t>広島城北高等学校</t>
+          <t>広島学院高等学校</t>
         </is>
       </c>
       <c r="E1127" s="6" t="inlineStr">
         <is>
-          <t>082-229-0111</t>
+          <t>082-271-0241</t>
         </is>
       </c>
       <c r="F1127" s="7" t="inlineStr">
@@ -66569,10 +66577,14 @@
       </c>
       <c r="K1127" s="8" t="n"/>
       <c r="L1127" s="9" t="n"/>
-      <c r="M1127" s="10" t="n"/>
+      <c r="M1127" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
       <c r="N1127" s="11" t="inlineStr">
         <is>
-          <t>https://hiroshimajohoku.ed.jp/school/about/access/</t>
+          <t>https://www.hiroshimagakuin.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O1127" s="12" t="inlineStr">
@@ -66592,17 +66604,17 @@
       </c>
       <c r="C1128" s="5" t="inlineStr">
         <is>
-          <t>広島市中区</t>
+          <t>広島市西区</t>
         </is>
       </c>
       <c r="D1128" s="5" t="inlineStr">
         <is>
-          <t>広島女学院高等学校</t>
+          <t>広島工業大学高等学校</t>
         </is>
       </c>
       <c r="E1128" s="6" t="inlineStr">
         <is>
-          <t>082-228-4131</t>
+          <t>082-277-9205</t>
         </is>
       </c>
       <c r="F1128" s="7" t="inlineStr">
@@ -66624,10 +66636,14 @@
       </c>
       <c r="K1128" s="8" t="n"/>
       <c r="L1128" s="9" t="n"/>
-      <c r="M1128" s="10" t="n"/>
+      <c r="M1128" s="10" t="inlineStr">
+        <is>
+          <t>全日制（西区）。通信制（安佐南区）は082-849-6755</t>
+        </is>
+      </c>
       <c r="N1128" s="11" t="inlineStr">
         <is>
-          <t>https://www.hjs.ed.jp/contact</t>
+          <t>https://www.kodaikoko.ed.jp/zennichi/</t>
         </is>
       </c>
       <c r="O1128" s="12" t="inlineStr">
@@ -66647,17 +66663,17 @@
       </c>
       <c r="C1129" s="5" t="inlineStr">
         <is>
-          <t>広島市東区</t>
+          <t>海田町</t>
         </is>
       </c>
       <c r="D1129" s="5" t="inlineStr">
         <is>
-          <t>広島県瀬戸内高等学校</t>
+          <t>広島国際学院高等学校</t>
         </is>
       </c>
       <c r="E1129" s="6" t="inlineStr">
         <is>
-          <t>082-261-1296</t>
+          <t>082-823-3401</t>
         </is>
       </c>
       <c r="F1129" s="7" t="inlineStr">
@@ -66667,7 +66683,7 @@
       </c>
       <c r="G1129" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・総合学科</t>
         </is>
       </c>
       <c r="H1129" s="8" t="n"/>
@@ -66681,12 +66697,12 @@
       <c r="L1129" s="9" t="n"/>
       <c r="M1129" s="10" t="inlineStr">
         <is>
-          <t>公式では入試広報部の番号として掲載。082-261-1298とするサイトもあり</t>
+          <t>全日制（海田町）。通信制の中野キャンパスは082-820-2515</t>
         </is>
       </c>
       <c r="N1129" s="11" t="inlineStr">
         <is>
-          <t>https://www.setouchi-h.ed.jp/extrance1.html</t>
+          <t>https://www.hi.hkg.ac.jp/access</t>
         </is>
       </c>
       <c r="O1129" s="12" t="inlineStr">
@@ -66706,22 +66722,22 @@
       </c>
       <c r="C1130" s="5" t="inlineStr">
         <is>
-          <t>広島市佐伯区</t>
+          <t>広島市東区</t>
         </is>
       </c>
       <c r="D1130" s="5" t="inlineStr">
         <is>
-          <t>広島なぎさ高等学校</t>
+          <t>広島桜が丘高等学校</t>
         </is>
       </c>
       <c r="E1130" s="6" t="inlineStr">
         <is>
-          <t>082-921-2137</t>
-        </is>
-      </c>
-      <c r="F1130" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>082-262-0128</t>
+        </is>
+      </c>
+      <c r="F1130" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="G1130" s="5" t="inlineStr">
@@ -66738,10 +66754,14 @@
       </c>
       <c r="K1130" s="8" t="n"/>
       <c r="L1130" s="9" t="n"/>
-      <c r="M1130" s="10" t="n"/>
+      <c r="M1130" s="10" t="inlineStr">
+        <is>
+          <t>公式未確認、複数サイトで一致</t>
+        </is>
+      </c>
       <c r="N1130" s="11" t="inlineStr">
         <is>
-          <t>https://www.nagisa.ed.jp/high/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/34102/ILSP0000041015_ipclm/</t>
         </is>
       </c>
       <c r="O1130" s="12" t="inlineStr">
@@ -66761,17 +66781,17 @@
       </c>
       <c r="C1131" s="5" t="inlineStr">
         <is>
-          <t>広島市安佐北区</t>
+          <t>三原市</t>
         </is>
       </c>
       <c r="D1131" s="5" t="inlineStr">
         <is>
-          <t>広島文教大学附属高等学校</t>
+          <t>広島三育学院高等学校</t>
         </is>
       </c>
       <c r="E1131" s="6" t="inlineStr">
         <is>
-          <t>082-814-3192</t>
+          <t>0847-33-0311</t>
         </is>
       </c>
       <c r="F1131" s="7" t="inlineStr">
@@ -66796,7 +66816,7 @@
       <c r="M1131" s="10" t="n"/>
       <c r="N1131" s="11" t="inlineStr">
         <is>
-          <t>https://www.h-bunkyo.ac.jp/highschool/</t>
+          <t>https://www.saniku.ac.jp/hiroshima/about/profile.php</t>
         </is>
       </c>
       <c r="O1131" s="12" t="inlineStr">
@@ -66816,17 +66836,17 @@
       </c>
       <c r="C1132" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>広島市西区</t>
         </is>
       </c>
       <c r="D1132" s="5" t="inlineStr">
         <is>
-          <t>福山暁の星女子高等学校</t>
+          <t>広島修道大学ひろしま協創高等学校</t>
         </is>
       </c>
       <c r="E1132" s="6" t="inlineStr">
         <is>
-          <t>084-922-1682</t>
+          <t>082-278-1101</t>
         </is>
       </c>
       <c r="F1132" s="7" t="inlineStr">
@@ -66851,7 +66871,7 @@
       <c r="M1132" s="10" t="n"/>
       <c r="N1132" s="11" t="inlineStr">
         <is>
-          <t>https://www.akenohoshi-cyukou.ed.jp/about/access/</t>
+          <t>https://www.shudo-u.ac.jp/fuzoku/</t>
         </is>
       </c>
       <c r="O1132" s="12" t="inlineStr">
@@ -66871,17 +66891,17 @@
       </c>
       <c r="C1133" s="5" t="inlineStr">
         <is>
-          <t>広島市中区</t>
+          <t>坂町</t>
         </is>
       </c>
       <c r="D1133" s="5" t="inlineStr">
         <is>
-          <t>安田女子高等学校</t>
+          <t>広島翔洋高等学校</t>
         </is>
       </c>
       <c r="E1133" s="6" t="inlineStr">
         <is>
-          <t>082-221-3304</t>
+          <t>082-884-1616</t>
         </is>
       </c>
       <c r="F1133" s="7" t="inlineStr">
@@ -66891,7 +66911,7 @@
       </c>
       <c r="G1133" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1133" s="8" t="n"/>
@@ -66903,14 +66923,10 @@
       </c>
       <c r="K1133" s="8" t="n"/>
       <c r="L1133" s="9" t="n"/>
-      <c r="M1133" s="10" t="inlineStr">
-        <is>
-          <t>高校部の番号。中学部は082-221-3362</t>
-        </is>
-      </c>
+      <c r="M1133" s="10" t="n"/>
       <c r="N1133" s="11" t="inlineStr">
         <is>
-          <t>https://www.yasuda-u.ac.jp/jh/</t>
+          <t>https://www.h-shoyo.ed.jp/overview/details.php</t>
         </is>
       </c>
       <c r="O1133" s="12" t="inlineStr">
@@ -66925,22 +66941,22 @@
       </c>
       <c r="B1134" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1134" s="5" t="inlineStr">
         <is>
-          <t>宇部市</t>
+          <t>北広島町</t>
         </is>
       </c>
       <c r="D1134" s="5" t="inlineStr">
         <is>
-          <t>宇部鴻城高等学校</t>
+          <t>広島新庄高等学校</t>
         </is>
       </c>
       <c r="E1134" s="6" t="inlineStr">
         <is>
-          <t>0836-41-8109</t>
+          <t>0826-82-2323</t>
         </is>
       </c>
       <c r="F1134" s="7" t="inlineStr">
@@ -66950,7 +66966,7 @@
       </c>
       <c r="G1134" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1134" s="8" t="n"/>
@@ -66965,7 +66981,7 @@
       <c r="M1134" s="10" t="n"/>
       <c r="N1134" s="11" t="inlineStr">
         <is>
-          <t>https://www.ubekojo-h.ed.jp/contact/</t>
+          <t>https://www.shinjou.jp/toiawase/toiawase.html</t>
         </is>
       </c>
       <c r="O1134" s="12" t="inlineStr">
@@ -66980,22 +66996,22 @@
       </c>
       <c r="B1135" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1135" s="5" t="inlineStr">
         <is>
-          <t>宇部市</t>
+          <t>広島市東区</t>
         </is>
       </c>
       <c r="D1135" s="5" t="inlineStr">
         <is>
-          <t>宇部フロンティア大学付属香川高等学校</t>
+          <t>広島城北高等学校</t>
         </is>
       </c>
       <c r="E1135" s="6" t="inlineStr">
         <is>
-          <t>0836-35-9574</t>
+          <t>082-229-0111</t>
         </is>
       </c>
       <c r="F1135" s="7" t="inlineStr">
@@ -67005,7 +67021,7 @@
       </c>
       <c r="G1135" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1135" s="8" t="n"/>
@@ -67017,14 +67033,10 @@
       </c>
       <c r="K1135" s="8" t="n"/>
       <c r="L1135" s="9" t="n"/>
-      <c r="M1135" s="10" t="inlineStr">
-        <is>
-          <t>普通科職員室0836-35-9578、専門部職員室0836-35-9583</t>
-        </is>
-      </c>
+      <c r="M1135" s="10" t="n"/>
       <c r="N1135" s="11" t="inlineStr">
         <is>
-          <t>https://www.kagawa-h.ed.jp/</t>
+          <t>https://hiroshimajohoku.ed.jp/school/about/access/</t>
         </is>
       </c>
       <c r="O1135" s="12" t="inlineStr">
@@ -67039,22 +67051,22 @@
       </c>
       <c r="B1136" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1136" s="5" t="inlineStr">
         <is>
-          <t>宇部市</t>
+          <t>広島市中区</t>
         </is>
       </c>
       <c r="D1136" s="5" t="inlineStr">
         <is>
-          <t>慶進高等学校</t>
+          <t>広島女学院高等学校</t>
         </is>
       </c>
       <c r="E1136" s="6" t="inlineStr">
         <is>
-          <t>0836-34-1111</t>
+          <t>082-228-4131</t>
         </is>
       </c>
       <c r="F1136" s="7" t="inlineStr">
@@ -67079,7 +67091,7 @@
       <c r="M1136" s="10" t="n"/>
       <c r="N1136" s="11" t="inlineStr">
         <is>
-          <t>https://www.keishin-ug.ed.jp/</t>
+          <t>https://www.hjs.ed.jp/contact</t>
         </is>
       </c>
       <c r="O1136" s="12" t="inlineStr">
@@ -67094,22 +67106,22 @@
       </c>
       <c r="B1137" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1137" s="5" t="inlineStr">
         <is>
-          <t>山陽小野田市</t>
+          <t>広島市東区</t>
         </is>
       </c>
       <c r="D1137" s="5" t="inlineStr">
         <is>
-          <t>ザビエル高等学校</t>
+          <t>広島県瀬戸内高等学校</t>
         </is>
       </c>
       <c r="E1137" s="6" t="inlineStr">
         <is>
-          <t>0836-83-3587</t>
+          <t>082-261-1296</t>
         </is>
       </c>
       <c r="F1137" s="7" t="inlineStr">
@@ -67133,12 +67145,12 @@
       <c r="L1137" s="9" t="n"/>
       <c r="M1137" s="10" t="inlineStr">
         <is>
-          <t>正式表記は「サビエル高等学校」</t>
+          <t>公式では入試広報部の番号として掲載。082-261-1298とするサイトもあり</t>
         </is>
       </c>
       <c r="N1137" s="11" t="inlineStr">
         <is>
-          <t>https://xavier.ed.jp/</t>
+          <t>https://www.setouchi-h.ed.jp/extrance1.html</t>
         </is>
       </c>
       <c r="O1137" s="12" t="inlineStr">
@@ -67153,22 +67165,22 @@
       </c>
       <c r="B1138" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1138" s="5" t="inlineStr">
         <is>
-          <t>下関市</t>
+          <t>広島市佐伯区</t>
         </is>
       </c>
       <c r="D1138" s="5" t="inlineStr">
         <is>
-          <t>下関国際高等学校</t>
+          <t>広島なぎさ高等学校</t>
         </is>
       </c>
       <c r="E1138" s="6" t="inlineStr">
         <is>
-          <t>083-256-2321</t>
+          <t>082-921-2137</t>
         </is>
       </c>
       <c r="F1138" s="7" t="inlineStr">
@@ -67178,7 +67190,7 @@
       </c>
       <c r="G1138" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1138" s="8" t="n"/>
@@ -67193,7 +67205,7 @@
       <c r="M1138" s="10" t="n"/>
       <c r="N1138" s="11" t="inlineStr">
         <is>
-          <t>https://www.shiboyama.ac.jp/</t>
+          <t>https://www.nagisa.ed.jp/high/</t>
         </is>
       </c>
       <c r="O1138" s="12" t="inlineStr">
@@ -67208,22 +67220,22 @@
       </c>
       <c r="B1139" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1139" s="5" t="inlineStr">
         <is>
-          <t>下関市</t>
+          <t>広島市安佐北区</t>
         </is>
       </c>
       <c r="D1139" s="5" t="inlineStr">
         <is>
-          <t>下関短期大学付属高等学校</t>
+          <t>広島文教大学附属高等学校</t>
         </is>
       </c>
       <c r="E1139" s="6" t="inlineStr">
         <is>
-          <t>083-232-3785</t>
+          <t>082-814-3192</t>
         </is>
       </c>
       <c r="F1139" s="7" t="inlineStr">
@@ -67233,7 +67245,7 @@
       </c>
       <c r="G1139" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1139" s="8" t="n"/>
@@ -67245,14 +67257,10 @@
       </c>
       <c r="K1139" s="8" t="n"/>
       <c r="L1139" s="9" t="n"/>
-      <c r="M1139" s="10" t="inlineStr">
-        <is>
-          <t>短大の番号（083-223-0339）とは別</t>
-        </is>
-      </c>
+      <c r="M1139" s="10" t="n"/>
       <c r="N1139" s="11" t="inlineStr">
         <is>
-          <t>https://www.shimotan-hs.jp/pages/13/</t>
+          <t>https://www.h-bunkyo.ac.jp/highschool/</t>
         </is>
       </c>
       <c r="O1139" s="12" t="inlineStr">
@@ -67267,22 +67275,22 @@
       </c>
       <c r="B1140" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1140" s="5" t="inlineStr">
         <is>
-          <t>防府市</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1140" s="5" t="inlineStr">
         <is>
-          <t>誠英高等学校</t>
+          <t>福山暁の星女子高等学校</t>
         </is>
       </c>
       <c r="E1140" s="6" t="inlineStr">
         <is>
-          <t>0835-38-5252</t>
+          <t>084-922-1682</t>
         </is>
       </c>
       <c r="F1140" s="7" t="inlineStr">
@@ -67292,7 +67300,7 @@
       </c>
       <c r="G1140" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1140" s="8" t="n"/>
@@ -67304,14 +67312,10 @@
       </c>
       <c r="K1140" s="8" t="n"/>
       <c r="L1140" s="9" t="n"/>
-      <c r="M1140" s="10" t="inlineStr">
-        <is>
-          <t>通信制課程は0835-38-6161（第三者サイト）</t>
-        </is>
-      </c>
+      <c r="M1140" s="10" t="n"/>
       <c r="N1140" s="11" t="inlineStr">
         <is>
-          <t>https://seiei.ac.jp/</t>
+          <t>https://www.akenohoshi-cyukou.ed.jp/about/access/</t>
         </is>
       </c>
       <c r="O1140" s="12" t="inlineStr">
@@ -67326,22 +67330,22 @@
       </c>
       <c r="B1141" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1141" s="5" t="inlineStr">
         <is>
-          <t>山口市</t>
+          <t>広島市中区</t>
         </is>
       </c>
       <c r="D1141" s="5" t="inlineStr">
         <is>
-          <t>精華学園高等学校</t>
+          <t>安田女子高等学校</t>
         </is>
       </c>
       <c r="E1141" s="6" t="inlineStr">
         <is>
-          <t>083-976-8833</t>
+          <t>082-221-3304</t>
         </is>
       </c>
       <c r="F1141" s="7" t="inlineStr">
@@ -67365,12 +67369,12 @@
       <c r="L1141" s="9" t="n"/>
       <c r="M1141" s="10" t="inlineStr">
         <is>
-          <t>広域通信制・山口本校</t>
+          <t>高校部の番号。中学部は082-221-3362</t>
         </is>
       </c>
       <c r="N1141" s="11" t="inlineStr">
         <is>
-          <t>https://www.seikagakuen.ac.jp/archives/691</t>
+          <t>https://www.yasuda-u.ac.jp/jh/</t>
         </is>
       </c>
       <c r="O1141" s="12" t="inlineStr">
@@ -67390,17 +67394,17 @@
       </c>
       <c r="C1142" s="5" t="inlineStr">
         <is>
-          <t>光市</t>
+          <t>宇部市</t>
         </is>
       </c>
       <c r="D1142" s="5" t="inlineStr">
         <is>
-          <t>聖光高等学校</t>
+          <t>宇部鴻城高等学校</t>
         </is>
       </c>
       <c r="E1142" s="6" t="inlineStr">
         <is>
-          <t>0833-72-1187</t>
+          <t>0836-41-8109</t>
         </is>
       </c>
       <c r="F1142" s="7" t="inlineStr">
@@ -67422,14 +67426,10 @@
       </c>
       <c r="K1142" s="8" t="n"/>
       <c r="L1142" s="9" t="n"/>
-      <c r="M1142" s="10" t="inlineStr">
-        <is>
-          <t>通信制は0833-72-7070（第三者サイト）</t>
-        </is>
-      </c>
+      <c r="M1142" s="10" t="n"/>
       <c r="N1142" s="11" t="inlineStr">
         <is>
-          <t>https://www.seiko-h.ed.jp/</t>
+          <t>https://www.ubekojo-h.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O1142" s="12" t="inlineStr">
@@ -67449,17 +67449,17 @@
       </c>
       <c r="C1143" s="5" t="inlineStr">
         <is>
-          <t>美祢市</t>
+          <t>宇部市</t>
         </is>
       </c>
       <c r="D1143" s="5" t="inlineStr">
         <is>
-          <t>成進高等学校</t>
+          <t>宇部フロンティア大学付属香川高等学校</t>
         </is>
       </c>
       <c r="E1143" s="6" t="inlineStr">
         <is>
-          <t>0837-52-1350</t>
+          <t>0836-35-9574</t>
         </is>
       </c>
       <c r="F1143" s="7" t="inlineStr">
@@ -67481,10 +67481,14 @@
       </c>
       <c r="K1143" s="8" t="n"/>
       <c r="L1143" s="9" t="n"/>
-      <c r="M1143" s="10" t="n"/>
+      <c r="M1143" s="10" t="inlineStr">
+        <is>
+          <t>普通科職員室0836-35-9578、専門部職員室0836-35-9583</t>
+        </is>
+      </c>
       <c r="N1143" s="11" t="inlineStr">
         <is>
-          <t>https://www.mine-c.ed.jp/profile</t>
+          <t>https://www.kagawa-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1143" s="12" t="inlineStr">
@@ -67504,17 +67508,17 @@
       </c>
       <c r="C1144" s="5" t="inlineStr">
         <is>
-          <t>防府市</t>
+          <t>宇部市</t>
         </is>
       </c>
       <c r="D1144" s="5" t="inlineStr">
         <is>
-          <t>高川学園高等学校</t>
+          <t>慶進高等学校</t>
         </is>
       </c>
       <c r="E1144" s="6" t="inlineStr">
         <is>
-          <t>0835-33-0101</t>
+          <t>0836-34-1111</t>
         </is>
       </c>
       <c r="F1144" s="7" t="inlineStr">
@@ -67539,7 +67543,7 @@
       <c r="M1144" s="10" t="n"/>
       <c r="N1144" s="11" t="inlineStr">
         <is>
-          <t>https://takagawagakuen.com/high/</t>
+          <t>https://www.keishin-ug.ed.jp/</t>
         </is>
       </c>
       <c r="O1144" s="12" t="inlineStr">
@@ -67559,17 +67563,17 @@
       </c>
       <c r="C1145" s="5" t="inlineStr">
         <is>
-          <t>岩国市</t>
+          <t>山陽小野田市</t>
         </is>
       </c>
       <c r="D1145" s="5" t="inlineStr">
         <is>
-          <t>高水高等学校</t>
+          <t>ザビエル高等学校</t>
         </is>
       </c>
       <c r="E1145" s="6" t="inlineStr">
         <is>
-          <t>0827-31-7191</t>
+          <t>0836-83-3587</t>
         </is>
       </c>
       <c r="F1145" s="7" t="inlineStr">
@@ -67593,12 +67597,12 @@
       <c r="L1145" s="9" t="n"/>
       <c r="M1145" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>正式表記は「サビエル高等学校」</t>
         </is>
       </c>
       <c r="N1145" s="11" t="inlineStr">
         <is>
-          <t>https://www.takamizu.ed.jp/</t>
+          <t>https://xavier.ed.jp/</t>
         </is>
       </c>
       <c r="O1145" s="12" t="inlineStr">
@@ -67618,17 +67622,17 @@
       </c>
       <c r="C1146" s="5" t="inlineStr">
         <is>
-          <t>山口市</t>
+          <t>下関市</t>
         </is>
       </c>
       <c r="D1146" s="5" t="inlineStr">
         <is>
-          <t>中村女子高等学校</t>
+          <t>下関国際高等学校</t>
         </is>
       </c>
       <c r="E1146" s="6" t="inlineStr">
         <is>
-          <t>083-922-0418</t>
+          <t>083-256-2321</t>
         </is>
       </c>
       <c r="F1146" s="7" t="inlineStr">
@@ -67650,14 +67654,10 @@
       </c>
       <c r="K1146" s="8" t="n"/>
       <c r="L1146" s="9" t="n"/>
-      <c r="M1146" s="10" t="inlineStr">
-        <is>
-          <t>現校名は山口中村学園高等学校（2025年度から共学化）。専攻科は083-928-1331</t>
-        </is>
-      </c>
+      <c r="M1146" s="10" t="n"/>
       <c r="N1146" s="11" t="inlineStr">
         <is>
-          <t>https://www.y-nakamura.jp/</t>
+          <t>https://www.shiboyama.ac.jp/</t>
         </is>
       </c>
       <c r="O1146" s="12" t="inlineStr">
@@ -67677,17 +67677,17 @@
       </c>
       <c r="C1147" s="5" t="inlineStr">
         <is>
-          <t>長門市</t>
+          <t>下関市</t>
         </is>
       </c>
       <c r="D1147" s="5" t="inlineStr">
         <is>
-          <t>長門高等学校</t>
+          <t>下関短期大学付属高等学校</t>
         </is>
       </c>
       <c r="E1147" s="6" t="inlineStr">
         <is>
-          <t>0837-22-2944</t>
+          <t>083-232-3785</t>
         </is>
       </c>
       <c r="F1147" s="7" t="inlineStr">
@@ -67709,10 +67709,14 @@
       </c>
       <c r="K1147" s="8" t="n"/>
       <c r="L1147" s="9" t="n"/>
-      <c r="M1147" s="10" t="n"/>
+      <c r="M1147" s="10" t="inlineStr">
+        <is>
+          <t>短大の番号（083-223-0339）とは別</t>
+        </is>
+      </c>
       <c r="N1147" s="11" t="inlineStr">
         <is>
-          <t>https://nagato.ac.jp/</t>
+          <t>https://www.shimotan-hs.jp/pages/13/</t>
         </is>
       </c>
       <c r="O1147" s="12" t="inlineStr">
@@ -67732,17 +67736,17 @@
       </c>
       <c r="C1148" s="5" t="inlineStr">
         <is>
-          <t>山口市</t>
+          <t>防府市</t>
         </is>
       </c>
       <c r="D1148" s="5" t="inlineStr">
         <is>
-          <t>野田学園高等学校</t>
+          <t>誠英高等学校</t>
         </is>
       </c>
       <c r="E1148" s="6" t="inlineStr">
         <is>
-          <t>083-922-5000</t>
+          <t>0835-38-5252</t>
         </is>
       </c>
       <c r="F1148" s="7" t="inlineStr">
@@ -67752,7 +67756,7 @@
       </c>
       <c r="G1148" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1148" s="8" t="n"/>
@@ -67764,10 +67768,14 @@
       </c>
       <c r="K1148" s="8" t="n"/>
       <c r="L1148" s="9" t="n"/>
-      <c r="M1148" s="10" t="n"/>
+      <c r="M1148" s="10" t="inlineStr">
+        <is>
+          <t>通信制課程は0835-38-6161（第三者サイト）</t>
+        </is>
+      </c>
       <c r="N1148" s="11" t="inlineStr">
         <is>
-          <t>https://www.nodagakuen.ed.jp/</t>
+          <t>https://seiei.ac.jp/</t>
         </is>
       </c>
       <c r="O1148" s="12" t="inlineStr">
@@ -67787,17 +67795,17 @@
       </c>
       <c r="C1149" s="5" t="inlineStr">
         <is>
-          <t>萩市</t>
+          <t>山口市</t>
         </is>
       </c>
       <c r="D1149" s="5" t="inlineStr">
         <is>
-          <t>萩光塩学院高等学校</t>
+          <t>精華学園高等学校</t>
         </is>
       </c>
       <c r="E1149" s="6" t="inlineStr">
         <is>
-          <t>0838-22-0782</t>
+          <t>083-976-8833</t>
         </is>
       </c>
       <c r="F1149" s="7" t="inlineStr">
@@ -67821,12 +67829,12 @@
       <c r="L1149" s="9" t="n"/>
       <c r="M1149" s="10" t="inlineStr">
         <is>
-          <t>小中高共通の代表番号（法人サイトでも一致）</t>
+          <t>広域通信制・山口本校</t>
         </is>
       </c>
       <c r="N1149" s="11" t="inlineStr">
         <is>
-          <t>https://www.yamaguchi-shigaku.or.jp/tyukou/pdf/2025/20_hagikouen2025.pdf</t>
+          <t>https://www.seikagakuen.ac.jp/archives/691</t>
         </is>
       </c>
       <c r="O1149" s="12" t="inlineStr">
@@ -67846,17 +67854,17 @@
       </c>
       <c r="C1150" s="5" t="inlineStr">
         <is>
-          <t>下関市</t>
+          <t>光市</t>
         </is>
       </c>
       <c r="D1150" s="5" t="inlineStr">
         <is>
-          <t>早鞆高等学校</t>
+          <t>聖光高等学校</t>
         </is>
       </c>
       <c r="E1150" s="6" t="inlineStr">
         <is>
-          <t>083-231-0080</t>
+          <t>0833-72-1187</t>
         </is>
       </c>
       <c r="F1150" s="7" t="inlineStr">
@@ -67878,10 +67886,14 @@
       </c>
       <c r="K1150" s="8" t="n"/>
       <c r="L1150" s="9" t="n"/>
-      <c r="M1150" s="10" t="n"/>
+      <c r="M1150" s="10" t="inlineStr">
+        <is>
+          <t>通信制は0833-72-7070（第三者サイト）</t>
+        </is>
+      </c>
       <c r="N1150" s="11" t="inlineStr">
         <is>
-          <t>https://www.hayatomo.ac.jp/course/</t>
+          <t>https://www.seiko-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1150" s="12" t="inlineStr">
@@ -67901,17 +67913,17 @@
       </c>
       <c r="C1151" s="5" t="inlineStr">
         <is>
-          <t>下関市</t>
+          <t>美祢市</t>
         </is>
       </c>
       <c r="D1151" s="5" t="inlineStr">
         <is>
-          <t>梅光学院高等学校</t>
+          <t>成進高等学校</t>
         </is>
       </c>
       <c r="E1151" s="6" t="inlineStr">
         <is>
-          <t>083-227-1200</t>
+          <t>0837-52-1350</t>
         </is>
       </c>
       <c r="F1151" s="7" t="inlineStr">
@@ -67933,14 +67945,10 @@
       </c>
       <c r="K1151" s="8" t="n"/>
       <c r="L1151" s="9" t="n"/>
-      <c r="M1151" s="10" t="inlineStr">
-        <is>
-          <t>法人本部は083-227-1000</t>
-        </is>
-      </c>
+      <c r="M1151" s="10" t="n"/>
       <c r="N1151" s="11" t="inlineStr">
         <is>
-          <t>https://www.baiko.ac.jp/highschool/</t>
+          <t>https://www.mine-c.ed.jp/profile</t>
         </is>
       </c>
       <c r="O1151" s="12" t="inlineStr">
@@ -67960,17 +67968,17 @@
       </c>
       <c r="C1152" s="5" t="inlineStr">
         <is>
-          <t>柳井市</t>
+          <t>防府市</t>
         </is>
       </c>
       <c r="D1152" s="5" t="inlineStr">
         <is>
-          <t>柳井学園高等学校</t>
+          <t>高川学園高等学校</t>
         </is>
       </c>
       <c r="E1152" s="6" t="inlineStr">
         <is>
-          <t>0820-22-0214</t>
+          <t>0835-33-0101</t>
         </is>
       </c>
       <c r="F1152" s="7" t="inlineStr">
@@ -67980,7 +67988,7 @@
       </c>
       <c r="G1152" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1152" s="8" t="n"/>
@@ -67995,7 +68003,7 @@
       <c r="M1152" s="10" t="n"/>
       <c r="N1152" s="11" t="inlineStr">
         <is>
-          <t>https://yanai-g.ed.jp/contact/</t>
+          <t>https://takagawagakuen.com/high/</t>
         </is>
       </c>
       <c r="O1152" s="12" t="inlineStr">
@@ -68015,17 +68023,17 @@
       </c>
       <c r="C1153" s="5" t="inlineStr">
         <is>
-          <t>山口市</t>
+          <t>岩国市</t>
         </is>
       </c>
       <c r="D1153" s="5" t="inlineStr">
         <is>
-          <t>山口県鴻城高等学校</t>
+          <t>高水高等学校</t>
         </is>
       </c>
       <c r="E1153" s="6" t="inlineStr">
         <is>
-          <t>083-972-0307</t>
+          <t>0827-31-7191</t>
         </is>
       </c>
       <c r="F1153" s="7" t="inlineStr">
@@ -68035,7 +68043,7 @@
       </c>
       <c r="G1153" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1153" s="8" t="n"/>
@@ -68049,12 +68057,12 @@
       <c r="L1153" s="9" t="n"/>
       <c r="M1153" s="10" t="inlineStr">
         <is>
-          <t>衛生看護専攻科（宇部市）は別番号</t>
+          <t>中高共通番号</t>
         </is>
       </c>
       <c r="N1153" s="11" t="inlineStr">
         <is>
-          <t>https://www.y-kojohs.jp/access/</t>
+          <t>https://www.takamizu.ed.jp/</t>
         </is>
       </c>
       <c r="O1153" s="12" t="inlineStr">
@@ -68074,17 +68082,17 @@
       </c>
       <c r="C1154" s="5" t="inlineStr">
         <is>
-          <t>周南市</t>
+          <t>山口市</t>
         </is>
       </c>
       <c r="D1154" s="5" t="inlineStr">
         <is>
-          <t>山口県桜ケ丘高等学校</t>
+          <t>中村女子高等学校</t>
         </is>
       </c>
       <c r="E1154" s="6" t="inlineStr">
         <is>
-          <t>0834-21-0331</t>
+          <t>083-922-0418</t>
         </is>
       </c>
       <c r="F1154" s="7" t="inlineStr">
@@ -68108,23 +68116,479 @@
       <c r="L1154" s="9" t="n"/>
       <c r="M1154" s="10" t="inlineStr">
         <is>
+          <t>現校名は山口中村学園高等学校（2025年度から共学化）。専攻科は083-928-1331</t>
+        </is>
+      </c>
+      <c r="N1154" s="11" t="inlineStr">
+        <is>
+          <t>https://www.y-nakamura.jp/</t>
+        </is>
+      </c>
+      <c r="O1154" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="4" t="n">
+        <v>1151</v>
+      </c>
+      <c r="B1155" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1155" s="5" t="inlineStr">
+        <is>
+          <t>長門市</t>
+        </is>
+      </c>
+      <c r="D1155" s="5" t="inlineStr">
+        <is>
+          <t>長門高等学校</t>
+        </is>
+      </c>
+      <c r="E1155" s="6" t="inlineStr">
+        <is>
+          <t>0837-22-2944</t>
+        </is>
+      </c>
+      <c r="F1155" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1155" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1155" s="8" t="n"/>
+      <c r="I1155" s="9" t="n"/>
+      <c r="J1155" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1155" s="8" t="n"/>
+      <c r="L1155" s="9" t="n"/>
+      <c r="M1155" s="10" t="n"/>
+      <c r="N1155" s="11" t="inlineStr">
+        <is>
+          <t>https://nagato.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1155" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="4" t="n">
+        <v>1152</v>
+      </c>
+      <c r="B1156" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1156" s="5" t="inlineStr">
+        <is>
+          <t>山口市</t>
+        </is>
+      </c>
+      <c r="D1156" s="5" t="inlineStr">
+        <is>
+          <t>野田学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1156" s="6" t="inlineStr">
+        <is>
+          <t>083-922-5000</t>
+        </is>
+      </c>
+      <c r="F1156" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1156" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1156" s="8" t="n"/>
+      <c r="I1156" s="9" t="n"/>
+      <c r="J1156" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1156" s="8" t="n"/>
+      <c r="L1156" s="9" t="n"/>
+      <c r="M1156" s="10" t="n"/>
+      <c r="N1156" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nodagakuen.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1156" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="4" t="n">
+        <v>1153</v>
+      </c>
+      <c r="B1157" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1157" s="5" t="inlineStr">
+        <is>
+          <t>萩市</t>
+        </is>
+      </c>
+      <c r="D1157" s="5" t="inlineStr">
+        <is>
+          <t>萩光塩学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1157" s="6" t="inlineStr">
+        <is>
+          <t>0838-22-0782</t>
+        </is>
+      </c>
+      <c r="F1157" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1157" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1157" s="8" t="n"/>
+      <c r="I1157" s="9" t="n"/>
+      <c r="J1157" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1157" s="8" t="n"/>
+      <c r="L1157" s="9" t="n"/>
+      <c r="M1157" s="10" t="inlineStr">
+        <is>
+          <t>小中高共通の代表番号（法人サイトでも一致）</t>
+        </is>
+      </c>
+      <c r="N1157" s="11" t="inlineStr">
+        <is>
+          <t>https://www.yamaguchi-shigaku.or.jp/tyukou/pdf/2025/20_hagikouen2025.pdf</t>
+        </is>
+      </c>
+      <c r="O1157" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="4" t="n">
+        <v>1154</v>
+      </c>
+      <c r="B1158" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1158" s="5" t="inlineStr">
+        <is>
+          <t>下関市</t>
+        </is>
+      </c>
+      <c r="D1158" s="5" t="inlineStr">
+        <is>
+          <t>早鞆高等学校</t>
+        </is>
+      </c>
+      <c r="E1158" s="6" t="inlineStr">
+        <is>
+          <t>083-231-0080</t>
+        </is>
+      </c>
+      <c r="F1158" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1158" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1158" s="8" t="n"/>
+      <c r="I1158" s="9" t="n"/>
+      <c r="J1158" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1158" s="8" t="n"/>
+      <c r="L1158" s="9" t="n"/>
+      <c r="M1158" s="10" t="n"/>
+      <c r="N1158" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hayatomo.ac.jp/course/</t>
+        </is>
+      </c>
+      <c r="O1158" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="4" t="n">
+        <v>1155</v>
+      </c>
+      <c r="B1159" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1159" s="5" t="inlineStr">
+        <is>
+          <t>下関市</t>
+        </is>
+      </c>
+      <c r="D1159" s="5" t="inlineStr">
+        <is>
+          <t>梅光学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1159" s="6" t="inlineStr">
+        <is>
+          <t>083-227-1200</t>
+        </is>
+      </c>
+      <c r="F1159" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1159" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1159" s="8" t="n"/>
+      <c r="I1159" s="9" t="n"/>
+      <c r="J1159" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1159" s="8" t="n"/>
+      <c r="L1159" s="9" t="n"/>
+      <c r="M1159" s="10" t="inlineStr">
+        <is>
+          <t>法人本部は083-227-1000</t>
+        </is>
+      </c>
+      <c r="N1159" s="11" t="inlineStr">
+        <is>
+          <t>https://www.baiko.ac.jp/highschool/</t>
+        </is>
+      </c>
+      <c r="O1159" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="4" t="n">
+        <v>1156</v>
+      </c>
+      <c r="B1160" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1160" s="5" t="inlineStr">
+        <is>
+          <t>柳井市</t>
+        </is>
+      </c>
+      <c r="D1160" s="5" t="inlineStr">
+        <is>
+          <t>柳井学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1160" s="6" t="inlineStr">
+        <is>
+          <t>0820-22-0214</t>
+        </is>
+      </c>
+      <c r="F1160" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1160" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1160" s="8" t="n"/>
+      <c r="I1160" s="9" t="n"/>
+      <c r="J1160" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1160" s="8" t="n"/>
+      <c r="L1160" s="9" t="n"/>
+      <c r="M1160" s="10" t="n"/>
+      <c r="N1160" s="11" t="inlineStr">
+        <is>
+          <t>https://yanai-g.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1160" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="4" t="n">
+        <v>1157</v>
+      </c>
+      <c r="B1161" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1161" s="5" t="inlineStr">
+        <is>
+          <t>山口市</t>
+        </is>
+      </c>
+      <c r="D1161" s="5" t="inlineStr">
+        <is>
+          <t>山口県鴻城高等学校</t>
+        </is>
+      </c>
+      <c r="E1161" s="6" t="inlineStr">
+        <is>
+          <t>083-972-0307</t>
+        </is>
+      </c>
+      <c r="F1161" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1161" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1161" s="8" t="n"/>
+      <c r="I1161" s="9" t="n"/>
+      <c r="J1161" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1161" s="8" t="n"/>
+      <c r="L1161" s="9" t="n"/>
+      <c r="M1161" s="10" t="inlineStr">
+        <is>
+          <t>衛生看護専攻科（宇部市）は別番号</t>
+        </is>
+      </c>
+      <c r="N1161" s="11" t="inlineStr">
+        <is>
+          <t>https://www.y-kojohs.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1161" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="4" t="n">
+        <v>1158</v>
+      </c>
+      <c r="B1162" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1162" s="5" t="inlineStr">
+        <is>
+          <t>周南市</t>
+        </is>
+      </c>
+      <c r="D1162" s="5" t="inlineStr">
+        <is>
+          <t>山口県桜ケ丘高等学校</t>
+        </is>
+      </c>
+      <c r="E1162" s="6" t="inlineStr">
+        <is>
+          <t>0834-21-0331</t>
+        </is>
+      </c>
+      <c r="F1162" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1162" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1162" s="8" t="n"/>
+      <c r="I1162" s="9" t="n"/>
+      <c r="J1162" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1162" s="8" t="n"/>
+      <c r="L1162" s="9" t="n"/>
+      <c r="M1162" s="10" t="inlineStr">
+        <is>
           <t>晃英館コースは0834-33-3131</t>
         </is>
       </c>
-      <c r="N1154" s="11" t="inlineStr">
+      <c r="N1162" s="11" t="inlineStr">
         <is>
           <t>https://www.y-sakuragaoka.ed.jp/contact.html</t>
         </is>
       </c>
-      <c r="O1154" s="12" t="inlineStr">
+      <c r="O1162" s="12" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O1154"/>
-  <conditionalFormatting sqref="A5:O1154">
+  <autoFilter ref="A4:O1162"/>
+  <conditionalFormatting sqref="A5:O1162">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -68133,10 +68597,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J1154" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J1162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H1154 K5:K1154" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H1162 K5:K1162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -69291,6 +69755,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1152" r:id="rId1148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1153" r:id="rId1149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1154" r:id="rId1150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1155" r:id="rId1151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1156" r:id="rId1152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1157" r:id="rId1153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1158" r:id="rId1154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1159" r:id="rId1155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1160" r:id="rId1156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1161" r:id="rId1157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1162" r:id="rId1158"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -69303,7 +69775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -69390,43 +69862,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A4,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A4,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1154,A4,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A4,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1162,A4,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A4,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A4,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69437,43 +69909,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A5,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A5,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1154,A5,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A5,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1162,A5,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A5,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A5,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69484,43 +69956,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A6,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A6,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1154,A6,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A6,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1162,A6,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A6,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A6,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69531,43 +70003,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A7,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A7,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1154,A7,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A7,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1162,A7,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A7,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A7,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69578,43 +70050,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A8,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A8,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1154,A8,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A8,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1162,A8,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A8,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A8,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69625,43 +70097,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A9,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A9,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1154,A9,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A9,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1162,A9,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A9,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A9,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69672,43 +70144,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A10,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A10,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1154,A10,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A10,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1162,A10,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A10,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A10,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69719,43 +70191,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A11,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A11,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1154,A11,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A11,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1162,A11,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A11,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A11,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69766,43 +70238,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A12,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A12,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1154,A12,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A12,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1162,A12,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A12,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A12,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69813,43 +70285,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A13,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A13,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1154,A13,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A13,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1162,A13,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A13,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A13,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69860,43 +70332,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A14,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A14,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1154,A14,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A14,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1162,A14,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A14,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A14,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69907,43 +70379,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A15,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A15,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1154,A15,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A15,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1162,A15,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A15,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A15,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69954,43 +70426,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A16,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A16,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1154,A16,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A16,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1162,A16,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A16,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A16,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70001,43 +70473,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A17,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A17,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1154,A17,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A17,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1162,A17,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A17,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A17,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70048,43 +70520,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A18,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A18,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1154,A18,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A18,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1162,A18,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A18,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A18,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70095,43 +70567,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A19,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A19,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1154,A19,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A19,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1162,A19,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A19,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A19,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70142,43 +70614,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A20,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A20,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1154,A20,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A20,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1162,A20,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A20,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A20,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70189,43 +70661,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A21,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A21,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1154,A21,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A21,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1162,A21,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A21,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A21,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70236,43 +70708,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A22,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A22,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1154,A22,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A22,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1162,A22,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A22,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A22,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70283,43 +70755,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A23,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A23,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1154,A23,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A23,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1162,A23,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A23,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A23,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70330,43 +70802,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A24,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A24,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1154,A24,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A24,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1162,A24,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A24,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A24,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70377,43 +70849,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A25,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A25,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1154,A25,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A25,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1162,A25,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A25,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A25,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70424,43 +70896,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A26,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A26,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1154,A26,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A26,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1162,A26,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A26,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A26,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70471,43 +70943,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A27,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A27,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1154,A27,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A27,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1162,A27,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A27,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A27,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70518,43 +70990,43 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A28,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A28,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1154,A28,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A28,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1162,A28,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A28,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A28,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70565,43 +71037,43 @@
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A29)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A29,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A29,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1154,A29,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A29,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1162,A29,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A29,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A29,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70612,43 +71084,43 @@
         </is>
       </c>
       <c r="B30" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A30)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A30)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A30,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A30,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1154,A30,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A30,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1162,A30,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A30,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A30,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70659,43 +71131,43 @@
         </is>
       </c>
       <c r="B31" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A31)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A31)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A31,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A31,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1154,A31,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A31,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1162,A31,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A31,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A31,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70706,43 +71178,43 @@
         </is>
       </c>
       <c r="B32" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A32)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A32)</f>
         <v/>
       </c>
       <c r="C32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A32,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A32,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1154,A32,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A32,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1162,A32,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A32,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A32,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70753,231 +71225,278 @@
         </is>
       </c>
       <c r="B33" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A33)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A33)</f>
         <v/>
       </c>
       <c r="C33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A33,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A33,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D33" s="16">
-        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1154,A33,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A33,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1162,A33,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A33,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A33,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>鳥取県</t>
         </is>
       </c>
       <c r="B34" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A34)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A34)</f>
         <v/>
       </c>
       <c r="C34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A34,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A34,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1154,A34,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A34,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1162,A34,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A34,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A34,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B35" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A35)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A35)</f>
         <v/>
       </c>
       <c r="C35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A35,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A35,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D35" s="16">
-        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1154,A35,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A35,'架電リスト'!$J$5:$J$1154,"")</f>
+        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1162,A35,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A35,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
       <c r="E35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
       <c r="G35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
       <c r="J35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A35,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="B36" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A36)</f>
+        <v/>
+      </c>
+      <c r="C36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A36,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D36" s="16">
+        <f>B36-COUNTIFS('架電リスト'!$B$5:$B$1162,A36,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A36,'架電リスト'!$J$5:$J$1162,"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <v/>
+      </c>
+      <c r="K36" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
           <t>山口県</t>
         </is>
       </c>
-      <c r="B36" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1154,A36)</f>
+      <c r="B37" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A37)</f>
         <v/>
       </c>
-      <c r="C36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,A36,'架電リスト'!$E$5:$E$1154,"&lt;&gt;")</f>
+      <c r="C37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A37,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D36" s="16">
-        <f>B36-COUNTIFS('架電リスト'!$B$5:$B$1154,A36,'架電リスト'!$J$5:$J$1154,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1154,A36,'架電リスト'!$J$5:$J$1154,"")</f>
+      <c r="D37" s="16">
+        <f>B37-COUNTIFS('架電リスト'!$B$5:$B$1162,A37,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A37,'架電リスト'!$J$5:$J$1162,"")</f>
         <v/>
       </c>
-      <c r="E36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"不在・折返し待ち")</f>
+      <c r="E37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"担当者不在")</f>
+      <c r="F37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"資料送付")</f>
+      <c r="G37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
         <v/>
       </c>
-      <c r="H36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"アポ獲得")</f>
+      <c r="H37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"検討中")</f>
+      <c r="I37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"検討中")</f>
         <v/>
       </c>
-      <c r="J36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"NG")</f>
+      <c r="J37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"NG")</f>
         <v/>
       </c>
-      <c r="K36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1154,$A36,'架電リスト'!$J$5:$J$1154,"番号不明")</f>
+      <c r="K37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B37" s="17">
-        <f>SUM(B4:B36)</f>
+      <c r="B38" s="17">
+        <f>SUM(B4:B37)</f>
         <v/>
       </c>
-      <c r="C37" s="17">
-        <f>SUM(C4:C36)</f>
+      <c r="C38" s="17">
+        <f>SUM(C4:C37)</f>
         <v/>
       </c>
-      <c r="D37" s="17">
-        <f>SUM(D4:D36)</f>
+      <c r="D38" s="17">
+        <f>SUM(D4:D37)</f>
         <v/>
       </c>
-      <c r="E37" s="17">
-        <f>SUM(E4:E36)</f>
+      <c r="E38" s="17">
+        <f>SUM(E4:E37)</f>
         <v/>
       </c>
-      <c r="F37" s="17">
-        <f>SUM(F4:F36)</f>
+      <c r="F38" s="17">
+        <f>SUM(F4:F37)</f>
         <v/>
       </c>
-      <c r="G37" s="17">
-        <f>SUM(G4:G36)</f>
+      <c r="G38" s="17">
+        <f>SUM(G4:G37)</f>
         <v/>
       </c>
-      <c r="H37" s="17">
-        <f>SUM(H4:H36)</f>
+      <c r="H38" s="17">
+        <f>SUM(H4:H37)</f>
         <v/>
       </c>
-      <c r="I37" s="17">
-        <f>SUM(I4:I36)</f>
+      <c r="I38" s="17">
+        <f>SUM(I4:I37)</f>
         <v/>
       </c>
-      <c r="J37" s="17">
-        <f>SUM(J4:J36)</f>
+      <c r="J38" s="17">
+        <f>SUM(J4:J37)</f>
         <v/>
       </c>
-      <c r="K37" s="17">
-        <f>SUM(K4:K36)</f>
+      <c r="K38" s="17">
+        <f>SUM(K4:K37)</f>
         <v/>
       </c>
     </row>
@@ -71067,7 +71586,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・33都道府県、1150校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・34都道府県、1158校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1172</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O1162"/>
+  <dimension ref="A1:O1172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（34都道府県／1158校）</t>
+          <t>私立高等学校 架電リスト（35都道府県／1168校）</t>
         </is>
       </c>
     </row>
@@ -63933,22 +63933,22 @@
       </c>
       <c r="B1082" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="C1082" s="5" t="inlineStr">
         <is>
-          <t>岡山市東区</t>
+          <t>出雲市</t>
         </is>
       </c>
       <c r="D1082" s="5" t="inlineStr">
         <is>
-          <t>岡山学芸館高等学校</t>
+          <t>出雲西高等学校</t>
         </is>
       </c>
       <c r="E1082" s="6" t="inlineStr">
         <is>
-          <t>086-942-3864</t>
+          <t>0853-21-1183</t>
         </is>
       </c>
       <c r="F1082" s="7" t="inlineStr">
@@ -63958,7 +63958,7 @@
       </c>
       <c r="G1082" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1082" s="8" t="n"/>
@@ -63970,14 +63970,10 @@
       </c>
       <c r="K1082" s="8" t="n"/>
       <c r="L1082" s="9" t="n"/>
-      <c r="M1082" s="10" t="inlineStr">
-        <is>
-          <t>通信制課程も同じ番号</t>
-        </is>
-      </c>
+      <c r="M1082" s="10" t="n"/>
       <c r="N1082" s="11" t="inlineStr">
         <is>
-          <t>https://www.gakugeikan.ed.jp/contact/index.html</t>
+          <t>https://www.izumonishikou.jp/contact/</t>
         </is>
       </c>
       <c r="O1082" s="12" t="inlineStr">
@@ -63992,22 +63988,22 @@
       </c>
       <c r="B1083" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="C1083" s="5" t="inlineStr">
         <is>
-          <t>新見市</t>
+          <t>出雲市</t>
         </is>
       </c>
       <c r="D1083" s="5" t="inlineStr">
         <is>
-          <t>岡山県共生高等学校</t>
+          <t>出雲北陵高等学校</t>
         </is>
       </c>
       <c r="E1083" s="6" t="inlineStr">
         <is>
-          <t>0867-72-0526</t>
+          <t>0853-21-1871</t>
         </is>
       </c>
       <c r="F1083" s="7" t="inlineStr">
@@ -64031,12 +64027,12 @@
       <c r="L1083" s="9" t="n"/>
       <c r="M1083" s="10" t="inlineStr">
         <is>
-          <t>0867-72-8032はFAX</t>
+          <t>事務室（代表）。高校職員室は0853-21-1887</t>
         </is>
       </c>
       <c r="N1083" s="11" t="inlineStr">
         <is>
-          <t>https://www.kyousei.ed.jp/</t>
+          <t>https://izumohokuryo-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1083" s="12" t="inlineStr">
@@ -64051,22 +64047,22 @@
       </c>
       <c r="B1084" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="C1084" s="5" t="inlineStr">
         <is>
-          <t>倉敷市</t>
+          <t>江津市</t>
         </is>
       </c>
       <c r="D1084" s="5" t="inlineStr">
         <is>
-          <t>岡山県作陽高等学校</t>
+          <t>石見智翠館高等学校</t>
         </is>
       </c>
       <c r="E1084" s="6" t="inlineStr">
         <is>
-          <t>086-441-1281</t>
+          <t>0855-52-2457</t>
         </is>
       </c>
       <c r="F1084" s="7" t="inlineStr">
@@ -64090,12 +64086,12 @@
       <c r="L1084" s="9" t="n"/>
       <c r="M1084" s="10" t="inlineStr">
         <is>
-          <t>2023年4月に倉敷市玉島へ移転し「作陽学園高等学校」に校名変更。津山の旧番号0868-23-2188は使用不可の可能性</t>
+          <t>通信制の直通は0855-52-4955</t>
         </is>
       </c>
       <c r="N1084" s="11" t="inlineStr">
         <is>
-          <t>https://www.sakuyo-h.ed.jp/access/</t>
+          <t>https://www.iwamichisuikan.ed.jp/guardian/contact</t>
         </is>
       </c>
       <c r="O1084" s="12" t="inlineStr">
@@ -64110,22 +64106,22 @@
       </c>
       <c r="B1085" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="C1085" s="5" t="inlineStr">
         <is>
-          <t>津山市</t>
+          <t>松江市</t>
         </is>
       </c>
       <c r="D1085" s="5" t="inlineStr">
         <is>
-          <t>岡山県美作高等学校</t>
+          <t>開星高等学校</t>
         </is>
       </c>
       <c r="E1085" s="6" t="inlineStr">
         <is>
-          <t>0868-22-4838</t>
+          <t>0852-21-4915</t>
         </is>
       </c>
       <c r="F1085" s="7" t="inlineStr">
@@ -64147,14 +64143,10 @@
       </c>
       <c r="K1085" s="8" t="n"/>
       <c r="L1085" s="9" t="n"/>
-      <c r="M1085" s="10" t="inlineStr">
-        <is>
-          <t>全日制の番号。通信制課程は0868-23-3116</t>
-        </is>
-      </c>
+      <c r="M1085" s="10" t="n"/>
       <c r="N1085" s="11" t="inlineStr">
         <is>
-          <t>https://mimasaka.jp/gakuen/houjin.html</t>
+          <t>https://shimane-kaisei.ed.jp/news/nyuushi/12016</t>
         </is>
       </c>
       <c r="O1085" s="12" t="inlineStr">
@@ -64169,22 +64161,22 @@
       </c>
       <c r="B1086" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="C1086" s="5" t="inlineStr">
         <is>
-          <t>岡山市南区</t>
+          <t>江津市</t>
         </is>
       </c>
       <c r="D1086" s="5" t="inlineStr">
         <is>
-          <t>岡山高等学校</t>
+          <t>キリスト教愛真高等学校</t>
         </is>
       </c>
       <c r="E1086" s="6" t="inlineStr">
         <is>
-          <t>086-282-6336</t>
+          <t>0855-52-5795</t>
         </is>
       </c>
       <c r="F1086" s="7" t="inlineStr">
@@ -64206,14 +64198,10 @@
       </c>
       <c r="K1086" s="8" t="n"/>
       <c r="L1086" s="9" t="n"/>
-      <c r="M1086" s="10" t="inlineStr">
-        <is>
-          <t>中高一貫</t>
-        </is>
-      </c>
+      <c r="M1086" s="10" t="n"/>
       <c r="N1086" s="11" t="inlineStr">
         <is>
-          <t>https://www.okayama-h.ed.jp/access/</t>
+          <t>https://aishinhigh.ed.jp/</t>
         </is>
       </c>
       <c r="O1086" s="12" t="inlineStr">
@@ -64228,22 +64216,22 @@
       </c>
       <c r="B1087" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="C1087" s="5" t="inlineStr">
         <is>
-          <t>浅口市</t>
+          <t>松江市</t>
         </is>
       </c>
       <c r="D1087" s="5" t="inlineStr">
         <is>
-          <t>おかやま山陽高等学校</t>
+          <t>松徳学院高等学校</t>
         </is>
       </c>
       <c r="E1087" s="6" t="inlineStr">
         <is>
-          <t>0865-44-3100</t>
+          <t>0852-21-5478</t>
         </is>
       </c>
       <c r="F1087" s="7" t="inlineStr">
@@ -64253,7 +64241,7 @@
       </c>
       <c r="G1087" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1087" s="8" t="n"/>
@@ -64267,12 +64255,12 @@
       <c r="L1087" s="9" t="n"/>
       <c r="M1087" s="10" t="inlineStr">
         <is>
-          <t>教員室直通は0865-44-7149</t>
+          <t>島根県資料では0852-21-5578も併記</t>
         </is>
       </c>
       <c r="N1087" s="11" t="inlineStr">
         <is>
-          <t>https://www.okayama-sanyo-hs.ed.jp/</t>
+          <t>https://shotoku-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1087" s="12" t="inlineStr">
@@ -64287,22 +64275,22 @@
       </c>
       <c r="B1088" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="C1088" s="5" t="inlineStr">
         <is>
-          <t>岡山市北区</t>
+          <t>益田市</t>
         </is>
       </c>
       <c r="D1088" s="5" t="inlineStr">
         <is>
-          <t>岡山商科大学附属高等学校</t>
+          <t>益田東高等学校</t>
         </is>
       </c>
       <c r="E1088" s="6" t="inlineStr">
         <is>
-          <t>086-252-3407</t>
+          <t>0856-23-3435</t>
         </is>
       </c>
       <c r="F1088" s="7" t="inlineStr">
@@ -64312,7 +64300,7 @@
       </c>
       <c r="G1088" s="5" t="inlineStr">
         <is>
-          <t>専門学科・総合学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1088" s="8" t="n"/>
@@ -64327,7 +64315,7 @@
       <c r="M1088" s="10" t="n"/>
       <c r="N1088" s="11" t="inlineStr">
         <is>
-          <t>https://www.osu-h.ed.jp/</t>
+          <t>https://masuda-higashi.com/contact/</t>
         </is>
       </c>
       <c r="O1088" s="12" t="inlineStr">
@@ -64342,22 +64330,22 @@
       </c>
       <c r="B1089" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="C1089" s="5" t="inlineStr">
         <is>
-          <t>赤磐市</t>
+          <t>松江市</t>
         </is>
       </c>
       <c r="D1089" s="5" t="inlineStr">
         <is>
-          <t>岡山白陵高等学校</t>
+          <t>松江西高等学校</t>
         </is>
       </c>
       <c r="E1089" s="6" t="inlineStr">
         <is>
-          <t>086-995-1255</t>
+          <t>0852-21-2925</t>
         </is>
       </c>
       <c r="F1089" s="7" t="inlineStr">
@@ -64367,7 +64355,7 @@
       </c>
       <c r="G1089" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1089" s="8" t="n"/>
@@ -64379,14 +64367,10 @@
       </c>
       <c r="K1089" s="8" t="n"/>
       <c r="L1089" s="9" t="n"/>
-      <c r="M1089" s="10" t="inlineStr">
-        <is>
-          <t>中学校併設</t>
-        </is>
-      </c>
+      <c r="M1089" s="10" t="n"/>
       <c r="N1089" s="11" t="inlineStr">
         <is>
-          <t>https://www.okahaku.ed.jp/access_inquiry/</t>
+          <t>https://www.matsuenishi-h.ed.jp/inquiry</t>
         </is>
       </c>
       <c r="O1089" s="12" t="inlineStr">
@@ -64401,22 +64385,22 @@
       </c>
       <c r="B1090" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="C1090" s="5" t="inlineStr">
         <is>
-          <t>岡山市北区</t>
+          <t>益田市</t>
         </is>
       </c>
       <c r="D1090" s="5" t="inlineStr">
         <is>
-          <t>岡山理科大学附属高等学校</t>
+          <t>明誠高等学校</t>
         </is>
       </c>
       <c r="E1090" s="6" t="inlineStr">
         <is>
-          <t>086-256-8511</t>
+          <t>0856-22-1052</t>
         </is>
       </c>
       <c r="F1090" s="7" t="inlineStr">
@@ -64426,7 +64410,7 @@
       </c>
       <c r="G1090" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1090" s="8" t="n"/>
@@ -64440,12 +64424,12 @@
       <c r="L1090" s="9" t="n"/>
       <c r="M1090" s="10" t="inlineStr">
         <is>
-          <t>通信制課程直通は086-256-8562</t>
+          <t>全日制の番号。通信制課程は0856-23-6877</t>
         </is>
       </c>
       <c r="N1090" s="11" t="inlineStr">
         <is>
-          <t>https://okayama.ridaifu.net/contact/</t>
+          <t>https://www.meisei-masuda.ed.jp/</t>
         </is>
       </c>
       <c r="O1090" s="12" t="inlineStr">
@@ -64460,22 +64444,22 @@
       </c>
       <c r="B1091" s="5" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="C1091" s="5" t="inlineStr">
         <is>
-          <t>笠岡市</t>
+          <t>松江市</t>
         </is>
       </c>
       <c r="D1091" s="5" t="inlineStr">
         <is>
-          <t>岡山龍谷高等学校</t>
+          <t>立正大学淞南高等学校</t>
         </is>
       </c>
       <c r="E1091" s="6" t="inlineStr">
         <is>
-          <t>0865-63-2525</t>
+          <t>0852-21-9634</t>
         </is>
       </c>
       <c r="F1091" s="7" t="inlineStr">
@@ -64485,7 +64469,7 @@
       </c>
       <c r="G1091" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1091" s="8" t="n"/>
@@ -64497,14 +64481,10 @@
       </c>
       <c r="K1091" s="8" t="n"/>
       <c r="L1091" s="9" t="n"/>
-      <c r="M1091" s="10" t="inlineStr">
-        <is>
-          <t>職員室は0865-63-2526</t>
-        </is>
-      </c>
+      <c r="M1091" s="10" t="n"/>
       <c r="N1091" s="11" t="inlineStr">
         <is>
-          <t>https://www.ok-ryukoku.ed.jp/</t>
+          <t>https://www.shonangakuen-h.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O1091" s="12" t="inlineStr">
@@ -64524,17 +64504,17 @@
       </c>
       <c r="C1092" s="5" t="inlineStr">
         <is>
-          <t>倉敷市</t>
+          <t>岡山市東区</t>
         </is>
       </c>
       <c r="D1092" s="5" t="inlineStr">
         <is>
-          <t>川崎医科大学附属高等学校</t>
+          <t>岡山学芸館高等学校</t>
         </is>
       </c>
       <c r="E1092" s="6" t="inlineStr">
         <is>
-          <t>086-462-3666</t>
+          <t>086-942-3864</t>
         </is>
       </c>
       <c r="F1092" s="7" t="inlineStr">
@@ -64544,7 +64524,7 @@
       </c>
       <c r="G1092" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1092" s="8" t="n"/>
@@ -64556,10 +64536,14 @@
       </c>
       <c r="K1092" s="8" t="n"/>
       <c r="L1092" s="9" t="n"/>
-      <c r="M1092" s="10" t="n"/>
+      <c r="M1092" s="10" t="inlineStr">
+        <is>
+          <t>通信制課程も同じ番号</t>
+        </is>
+      </c>
       <c r="N1092" s="11" t="inlineStr">
         <is>
-          <t>https://s.kawasaki-m.ac.jp/</t>
+          <t>https://www.gakugeikan.ed.jp/contact/index.html</t>
         </is>
       </c>
       <c r="O1092" s="12" t="inlineStr">
@@ -64579,17 +64563,17 @@
       </c>
       <c r="C1093" s="5" t="inlineStr">
         <is>
-          <t>岡山市北区</t>
+          <t>新見市</t>
         </is>
       </c>
       <c r="D1093" s="5" t="inlineStr">
         <is>
-          <t>関西高等学校</t>
+          <t>岡山県共生高等学校</t>
         </is>
       </c>
       <c r="E1093" s="6" t="inlineStr">
         <is>
-          <t>086-252-5121</t>
+          <t>0867-72-0526</t>
         </is>
       </c>
       <c r="F1093" s="7" t="inlineStr">
@@ -64599,7 +64583,7 @@
       </c>
       <c r="G1093" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1093" s="8" t="n"/>
@@ -64611,10 +64595,14 @@
       </c>
       <c r="K1093" s="8" t="n"/>
       <c r="L1093" s="9" t="n"/>
-      <c r="M1093" s="10" t="n"/>
+      <c r="M1093" s="10" t="inlineStr">
+        <is>
+          <t>0867-72-8032はFAX</t>
+        </is>
+      </c>
       <c r="N1093" s="11" t="inlineStr">
         <is>
-          <t>https://kanzei.ac.jp/</t>
+          <t>https://www.kyousei.ed.jp/</t>
         </is>
       </c>
       <c r="O1093" s="12" t="inlineStr">
@@ -64634,17 +64622,17 @@
       </c>
       <c r="C1094" s="5" t="inlineStr">
         <is>
-          <t>吉備中央町</t>
+          <t>倉敷市</t>
         </is>
       </c>
       <c r="D1094" s="5" t="inlineStr">
         <is>
-          <t>吉備高原学園高等学校</t>
+          <t>岡山県作陽高等学校</t>
         </is>
       </c>
       <c r="E1094" s="6" t="inlineStr">
         <is>
-          <t>0866-56-8211</t>
+          <t>086-441-1281</t>
         </is>
       </c>
       <c r="F1094" s="7" t="inlineStr">
@@ -64668,12 +64656,12 @@
       <c r="L1094" s="9" t="n"/>
       <c r="M1094" s="10" t="inlineStr">
         <is>
-          <t>全寮制</t>
+          <t>2023年4月に倉敷市玉島へ移転し「作陽学園高等学校」に校名変更。津山の旧番号0868-23-2188は使用不可の可能性</t>
         </is>
       </c>
       <c r="N1094" s="11" t="inlineStr">
         <is>
-          <t>https://www.kibikogengakuen.ed.jp/inquiry/form/</t>
+          <t>https://www.sakuyo-h.ed.jp/access/</t>
         </is>
       </c>
       <c r="O1094" s="12" t="inlineStr">
@@ -64693,17 +64681,17 @@
       </c>
       <c r="C1095" s="5" t="inlineStr">
         <is>
-          <t>倉敷市</t>
+          <t>津山市</t>
         </is>
       </c>
       <c r="D1095" s="5" t="inlineStr">
         <is>
-          <t>倉敷高等学校</t>
+          <t>岡山県美作高等学校</t>
         </is>
       </c>
       <c r="E1095" s="6" t="inlineStr">
         <is>
-          <t>086-462-9000</t>
+          <t>0868-22-4838</t>
         </is>
       </c>
       <c r="F1095" s="7" t="inlineStr">
@@ -64713,7 +64701,7 @@
       </c>
       <c r="G1095" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1095" s="8" t="n"/>
@@ -64727,12 +64715,12 @@
       <c r="L1095" s="9" t="n"/>
       <c r="M1095" s="10" t="inlineStr">
         <is>
-          <t>岡山県私学協会の一覧とも一致</t>
+          <t>全日制の番号。通信制課程は0868-23-3116</t>
         </is>
       </c>
       <c r="N1095" s="11" t="inlineStr">
         <is>
-          <t>https://www.kurashiki.ac.jp/news/</t>
+          <t>https://mimasaka.jp/gakuen/houjin.html</t>
         </is>
       </c>
       <c r="O1095" s="12" t="inlineStr">
@@ -64752,17 +64740,17 @@
       </c>
       <c r="C1096" s="5" t="inlineStr">
         <is>
-          <t>倉敷市</t>
+          <t>岡山市南区</t>
         </is>
       </c>
       <c r="D1096" s="5" t="inlineStr">
         <is>
-          <t>倉敷翠松高等学校</t>
+          <t>岡山高等学校</t>
         </is>
       </c>
       <c r="E1096" s="6" t="inlineStr">
         <is>
-          <t>086-422-3565</t>
+          <t>086-282-6336</t>
         </is>
       </c>
       <c r="F1096" s="7" t="inlineStr">
@@ -64772,7 +64760,7 @@
       </c>
       <c r="G1096" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1096" s="8" t="n"/>
@@ -64786,12 +64774,12 @@
       <c r="L1096" s="9" t="n"/>
       <c r="M1096" s="10" t="inlineStr">
         <is>
-          <t>教務室086-422-3570、専攻科086-427-0941</t>
+          <t>中高一貫</t>
         </is>
       </c>
       <c r="N1096" s="11" t="inlineStr">
         <is>
-          <t>https://www.suisho.ed.jp/</t>
+          <t>https://www.okayama-h.ed.jp/access/</t>
         </is>
       </c>
       <c r="O1096" s="12" t="inlineStr">
@@ -64811,17 +64799,17 @@
       </c>
       <c r="C1097" s="5" t="inlineStr">
         <is>
-          <t>井原市</t>
+          <t>浅口市</t>
         </is>
       </c>
       <c r="D1097" s="5" t="inlineStr">
         <is>
-          <t>興譲館高等学校</t>
+          <t>おかやま山陽高等学校</t>
         </is>
       </c>
       <c r="E1097" s="6" t="inlineStr">
         <is>
-          <t>0866-62-0124</t>
+          <t>0865-44-3100</t>
         </is>
       </c>
       <c r="F1097" s="7" t="inlineStr">
@@ -64831,7 +64819,7 @@
       </c>
       <c r="G1097" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1097" s="8" t="n"/>
@@ -64845,12 +64833,12 @@
       <c r="L1097" s="9" t="n"/>
       <c r="M1097" s="10" t="inlineStr">
         <is>
-          <t>井原市の本校。通信制課程は0120-445033</t>
+          <t>教員室直通は0865-44-7149</t>
         </is>
       </c>
       <c r="N1097" s="11" t="inlineStr">
         <is>
-          <t>https://kojokan-h.ed.jp/</t>
+          <t>https://www.okayama-sanyo-hs.ed.jp/</t>
         </is>
       </c>
       <c r="O1097" s="12" t="inlineStr">
@@ -64870,17 +64858,17 @@
       </c>
       <c r="C1098" s="5" t="inlineStr">
         <is>
-          <t>浅口市</t>
+          <t>岡山市北区</t>
         </is>
       </c>
       <c r="D1098" s="5" t="inlineStr">
         <is>
-          <t>金光学園高等学校</t>
+          <t>岡山商科大学附属高等学校</t>
         </is>
       </c>
       <c r="E1098" s="6" t="inlineStr">
         <is>
-          <t>0865-42-3131</t>
+          <t>086-252-3407</t>
         </is>
       </c>
       <c r="F1098" s="7" t="inlineStr">
@@ -64890,7 +64878,7 @@
       </c>
       <c r="G1098" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>専門学科・総合学科</t>
         </is>
       </c>
       <c r="H1098" s="8" t="n"/>
@@ -64902,14 +64890,10 @@
       </c>
       <c r="K1098" s="8" t="n"/>
       <c r="L1098" s="9" t="n"/>
-      <c r="M1098" s="10" t="inlineStr">
-        <is>
-          <t>中高共通番号</t>
-        </is>
-      </c>
+      <c r="M1098" s="10" t="n"/>
       <c r="N1098" s="11" t="inlineStr">
         <is>
-          <t>https://www.konkougakuen.net/high/</t>
+          <t>https://www.osu-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1098" s="12" t="inlineStr">
@@ -64929,17 +64913,17 @@
       </c>
       <c r="C1099" s="5" t="inlineStr">
         <is>
-          <t>岡山市中区</t>
+          <t>赤磐市</t>
         </is>
       </c>
       <c r="D1099" s="5" t="inlineStr">
         <is>
-          <t>山陽学園高等学校</t>
+          <t>岡山白陵高等学校</t>
         </is>
       </c>
       <c r="E1099" s="6" t="inlineStr">
         <is>
-          <t>086-272-1181</t>
+          <t>086-995-1255</t>
         </is>
       </c>
       <c r="F1099" s="7" t="inlineStr">
@@ -64963,12 +64947,12 @@
       <c r="L1099" s="9" t="n"/>
       <c r="M1099" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>中学校併設</t>
         </is>
       </c>
       <c r="N1099" s="11" t="inlineStr">
         <is>
-          <t>https://www.sanyogakuen.ed.jp/school/access</t>
+          <t>https://www.okahaku.ed.jp/access_inquiry/</t>
         </is>
       </c>
       <c r="O1099" s="12" t="inlineStr">
@@ -64993,12 +64977,12 @@
       </c>
       <c r="D1100" s="5" t="inlineStr">
         <is>
-          <t>就実高等学校</t>
+          <t>岡山理科大学附属高等学校</t>
         </is>
       </c>
       <c r="E1100" s="6" t="inlineStr">
         <is>
-          <t>086-225-1326</t>
+          <t>086-256-8511</t>
         </is>
       </c>
       <c r="F1100" s="7" t="inlineStr">
@@ -65020,10 +65004,14 @@
       </c>
       <c r="K1100" s="8" t="n"/>
       <c r="L1100" s="9" t="n"/>
-      <c r="M1100" s="10" t="n"/>
+      <c r="M1100" s="10" t="inlineStr">
+        <is>
+          <t>通信制課程直通は086-256-8562</t>
+        </is>
+      </c>
       <c r="N1100" s="11" t="inlineStr">
         <is>
-          <t>https://www.shujitsu-gakuen.jp/contact/index.html</t>
+          <t>https://okayama.ridaifu.net/contact/</t>
         </is>
       </c>
       <c r="O1100" s="12" t="inlineStr">
@@ -65043,17 +65031,17 @@
       </c>
       <c r="C1101" s="5" t="inlineStr">
         <is>
-          <t>倉敷市</t>
+          <t>笠岡市</t>
         </is>
       </c>
       <c r="D1101" s="5" t="inlineStr">
         <is>
-          <t>清心女子高等学校（岡山県）</t>
+          <t>岡山龍谷高等学校</t>
         </is>
       </c>
       <c r="E1101" s="6" t="inlineStr">
         <is>
-          <t>086-462-1661</t>
+          <t>0865-63-2525</t>
         </is>
       </c>
       <c r="F1101" s="7" t="inlineStr">
@@ -65063,7 +65051,7 @@
       </c>
       <c r="G1101" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1101" s="8" t="n"/>
@@ -65077,12 +65065,12 @@
       <c r="L1101" s="9" t="n"/>
       <c r="M1101" s="10" t="inlineStr">
         <is>
-          <t>ノートルダム清心学園（倉敷市）。中学校併設</t>
+          <t>職員室は0865-63-2526</t>
         </is>
       </c>
       <c r="N1101" s="11" t="inlineStr">
         <is>
-          <t>https://www.nd-seishin.ac.jp/school/access/</t>
+          <t>https://www.ok-ryukoku.ed.jp/</t>
         </is>
       </c>
       <c r="O1101" s="12" t="inlineStr">
@@ -65102,17 +65090,17 @@
       </c>
       <c r="C1102" s="5" t="inlineStr">
         <is>
-          <t>岡山市北区</t>
+          <t>倉敷市</t>
         </is>
       </c>
       <c r="D1102" s="5" t="inlineStr">
         <is>
-          <t>創志学園高等学校</t>
+          <t>川崎医科大学附属高等学校</t>
         </is>
       </c>
       <c r="E1102" s="6" t="inlineStr">
         <is>
-          <t>086-252-2101</t>
+          <t>086-462-3666</t>
         </is>
       </c>
       <c r="F1102" s="7" t="inlineStr">
@@ -65122,7 +65110,7 @@
       </c>
       <c r="G1102" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1102" s="8" t="n"/>
@@ -65134,14 +65122,10 @@
       </c>
       <c r="K1102" s="8" t="n"/>
       <c r="L1102" s="9" t="n"/>
-      <c r="M1102" s="10" t="inlineStr">
-        <is>
-          <t>入試広報室は0120-151752</t>
-        </is>
-      </c>
+      <c r="M1102" s="10" t="n"/>
       <c r="N1102" s="11" t="inlineStr">
         <is>
-          <t>https://www.soshigakuen.ed.jp/access/</t>
+          <t>https://s.kawasaki-m.ac.jp/</t>
         </is>
       </c>
       <c r="O1102" s="12" t="inlineStr">
@@ -65161,17 +65145,17 @@
       </c>
       <c r="C1103" s="5" t="inlineStr">
         <is>
-          <t>高梁市</t>
+          <t>岡山市北区</t>
         </is>
       </c>
       <c r="D1103" s="5" t="inlineStr">
         <is>
-          <t>方谷學舎高等学校</t>
+          <t>関西高等学校</t>
         </is>
       </c>
       <c r="E1103" s="6" t="inlineStr">
         <is>
-          <t>0866-22-2205</t>
+          <t>086-252-5121</t>
         </is>
       </c>
       <c r="F1103" s="7" t="inlineStr">
@@ -65181,7 +65165,7 @@
       </c>
       <c r="G1103" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1103" s="8" t="n"/>
@@ -65193,14 +65177,10 @@
       </c>
       <c r="K1103" s="8" t="n"/>
       <c r="L1103" s="9" t="n"/>
-      <c r="M1103" s="10" t="inlineStr">
-        <is>
-          <t>2023年6月に「岡山県高梁日新高等学校」から校名変更。事務室番号（教務室は0866-56-0015）</t>
-        </is>
-      </c>
+      <c r="M1103" s="10" t="n"/>
       <c r="N1103" s="11" t="inlineStr">
         <is>
-          <t>https://www.houkoku-gakusha.ed.jp/introduction/</t>
+          <t>https://kanzei.ac.jp/</t>
         </is>
       </c>
       <c r="O1103" s="12" t="inlineStr">
@@ -65220,17 +65200,17 @@
       </c>
       <c r="C1104" s="5" t="inlineStr">
         <is>
-          <t>岡山市北区</t>
+          <t>吉備中央町</t>
         </is>
       </c>
       <c r="D1104" s="5" t="inlineStr">
         <is>
-          <t>明誠学院高等学校</t>
+          <t>吉備高原学園高等学校</t>
         </is>
       </c>
       <c r="E1104" s="6" t="inlineStr">
         <is>
-          <t>086-252-5247</t>
+          <t>0866-56-8211</t>
         </is>
       </c>
       <c r="F1104" s="7" t="inlineStr">
@@ -65252,10 +65232,14 @@
       </c>
       <c r="K1104" s="8" t="n"/>
       <c r="L1104" s="9" t="n"/>
-      <c r="M1104" s="10" t="n"/>
+      <c r="M1104" s="10" t="inlineStr">
+        <is>
+          <t>全寮制</t>
+        </is>
+      </c>
       <c r="N1104" s="11" t="inlineStr">
         <is>
-          <t>https://www.meiseigakuin.ac.jp/</t>
+          <t>https://www.kibikogengakuen.ed.jp/inquiry/form/</t>
         </is>
       </c>
       <c r="O1104" s="12" t="inlineStr">
@@ -65270,22 +65254,22 @@
       </c>
       <c r="B1105" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1105" s="5" t="inlineStr">
         <is>
-          <t>広島市安佐南区</t>
+          <t>倉敷市</t>
         </is>
       </c>
       <c r="D1105" s="5" t="inlineStr">
         <is>
-          <t>AICJ高等学校</t>
+          <t>倉敷高等学校</t>
         </is>
       </c>
       <c r="E1105" s="6" t="inlineStr">
         <is>
-          <t>082-832-5037</t>
+          <t>086-462-9000</t>
         </is>
       </c>
       <c r="F1105" s="7" t="inlineStr">
@@ -65295,7 +65279,7 @@
       </c>
       <c r="G1105" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1105" s="8" t="n"/>
@@ -65309,12 +65293,12 @@
       <c r="L1105" s="9" t="n"/>
       <c r="M1105" s="10" t="inlineStr">
         <is>
-          <t>一部サイトに旧番号らしい082-874-3081の記載あり</t>
+          <t>岡山県私学協会の一覧とも一致</t>
         </is>
       </c>
       <c r="N1105" s="11" t="inlineStr">
         <is>
-          <t>https://aicj.ed.jp/access.html</t>
+          <t>https://www.kurashiki.ac.jp/news/</t>
         </is>
       </c>
       <c r="O1105" s="12" t="inlineStr">
@@ -65329,22 +65313,22 @@
       </c>
       <c r="B1106" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1106" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>倉敷市</t>
         </is>
       </c>
       <c r="D1106" s="5" t="inlineStr">
         <is>
-          <t>盈進高等学校</t>
+          <t>倉敷翠松高等学校</t>
         </is>
       </c>
       <c r="E1106" s="6" t="inlineStr">
         <is>
-          <t>084-955-2333</t>
+          <t>086-422-3565</t>
         </is>
       </c>
       <c r="F1106" s="7" t="inlineStr">
@@ -65354,7 +65338,7 @@
       </c>
       <c r="G1106" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1106" s="8" t="n"/>
@@ -65368,12 +65352,12 @@
       <c r="L1106" s="9" t="n"/>
       <c r="M1106" s="10" t="inlineStr">
         <is>
-          <t>中高共通の代表番号</t>
+          <t>教務室086-422-3570、専攻科086-427-0941</t>
         </is>
       </c>
       <c r="N1106" s="11" t="inlineStr">
         <is>
-          <t>https://www.eishin.ed.jp/access/</t>
+          <t>https://www.suisho.ed.jp/</t>
         </is>
       </c>
       <c r="O1106" s="12" t="inlineStr">
@@ -65388,22 +65372,22 @@
       </c>
       <c r="B1107" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1107" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>井原市</t>
         </is>
       </c>
       <c r="D1107" s="5" t="inlineStr">
         <is>
-          <t>英数学館高等学校</t>
+          <t>興譲館高等学校</t>
         </is>
       </c>
       <c r="E1107" s="6" t="inlineStr">
         <is>
-          <t>084-941-4115</t>
+          <t>0866-62-0124</t>
         </is>
       </c>
       <c r="F1107" s="7" t="inlineStr">
@@ -65427,12 +65411,12 @@
       <c r="L1107" s="9" t="n"/>
       <c r="M1107" s="10" t="inlineStr">
         <is>
-          <t>一部サイトに084-941-4117の記載あり（旧番号か）</t>
+          <t>井原市の本校。通信制課程は0120-445033</t>
         </is>
       </c>
       <c r="N1107" s="11" t="inlineStr">
         <is>
-          <t>https://goto.eisu-ejs.ac.jp/access/</t>
+          <t>https://kojokan-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1107" s="12" t="inlineStr">
@@ -65447,22 +65431,22 @@
       </c>
       <c r="B1108" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1108" s="5" t="inlineStr">
         <is>
-          <t>尾道市</t>
+          <t>浅口市</t>
         </is>
       </c>
       <c r="D1108" s="5" t="inlineStr">
         <is>
-          <t>尾道高等学校</t>
+          <t>金光学園高等学校</t>
         </is>
       </c>
       <c r="E1108" s="6" t="inlineStr">
         <is>
-          <t>0848-20-6612</t>
+          <t>0865-42-3131</t>
         </is>
       </c>
       <c r="F1108" s="7" t="inlineStr">
@@ -65472,7 +65456,7 @@
       </c>
       <c r="G1108" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1108" s="8" t="n"/>
@@ -65486,12 +65470,12 @@
       <c r="L1108" s="9" t="n"/>
       <c r="M1108" s="10" t="inlineStr">
         <is>
-          <t>2009年に向島町へ移転。旧番号0848-23-2311が残るサイトあり</t>
+          <t>中高共通番号</t>
         </is>
       </c>
       <c r="N1108" s="11" t="inlineStr">
         <is>
-          <t>https://onomichi.ac.jp/</t>
+          <t>https://www.konkougakuen.net/high/</t>
         </is>
       </c>
       <c r="O1108" s="12" t="inlineStr">
@@ -65506,22 +65490,22 @@
       </c>
       <c r="B1109" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1109" s="5" t="inlineStr">
         <is>
-          <t>東広島市</t>
+          <t>岡山市中区</t>
         </is>
       </c>
       <c r="D1109" s="5" t="inlineStr">
         <is>
-          <t>近畿大学附属広島高等学校東広島校</t>
+          <t>山陽学園高等学校</t>
         </is>
       </c>
       <c r="E1109" s="6" t="inlineStr">
         <is>
-          <t>082-434-7111</t>
+          <t>086-272-1181</t>
         </is>
       </c>
       <c r="F1109" s="7" t="inlineStr">
@@ -65543,10 +65527,14 @@
       </c>
       <c r="K1109" s="8" t="n"/>
       <c r="L1109" s="9" t="n"/>
-      <c r="M1109" s="10" t="n"/>
+      <c r="M1109" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
       <c r="N1109" s="11" t="inlineStr">
         <is>
-          <t>https://hh.kindai.ac.jp/</t>
+          <t>https://www.sanyogakuen.ed.jp/school/access</t>
         </is>
       </c>
       <c r="O1109" s="12" t="inlineStr">
@@ -65561,22 +65549,22 @@
       </c>
       <c r="B1110" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1110" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>岡山市北区</t>
         </is>
       </c>
       <c r="D1110" s="5" t="inlineStr">
         <is>
-          <t>近畿大学附属広島高等学校福山校</t>
+          <t>就実高等学校</t>
         </is>
       </c>
       <c r="E1110" s="6" t="inlineStr">
         <is>
-          <t>084-951-2695</t>
+          <t>086-225-1326</t>
         </is>
       </c>
       <c r="F1110" s="7" t="inlineStr">
@@ -65598,14 +65586,10 @@
       </c>
       <c r="K1110" s="8" t="n"/>
       <c r="L1110" s="9" t="n"/>
-      <c r="M1110" s="10" t="inlineStr">
-        <is>
-          <t>旧称は近畿大学附属福山高等学校</t>
-        </is>
-      </c>
+      <c r="M1110" s="10" t="n"/>
       <c r="N1110" s="11" t="inlineStr">
         <is>
-          <t>https://www.fukuyama.kindai.ac.jp/gakko/gakko-shokai.html</t>
+          <t>https://www.shujitsu-gakuen.jp/contact/index.html</t>
         </is>
       </c>
       <c r="O1110" s="12" t="inlineStr">
@@ -65620,22 +65604,22 @@
       </c>
       <c r="B1111" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1111" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>倉敷市</t>
         </is>
       </c>
       <c r="D1111" s="5" t="inlineStr">
         <is>
-          <t>銀河学院高等学校</t>
+          <t>清心女子高等学校（岡山県）</t>
         </is>
       </c>
       <c r="E1111" s="6" t="inlineStr">
         <is>
-          <t>084-941-9292</t>
+          <t>086-462-1661</t>
         </is>
       </c>
       <c r="F1111" s="7" t="inlineStr">
@@ -65659,12 +65643,12 @@
       <c r="L1111" s="9" t="n"/>
       <c r="M1111" s="10" t="inlineStr">
         <is>
-          <t>公式（法人事務室）に記載、複数サイトも一致</t>
+          <t>ノートルダム清心学園（倉敷市）。中学校併設</t>
         </is>
       </c>
       <c r="N1111" s="11" t="inlineStr">
         <is>
-          <t>https://www.ginga.ac.jp/donationginga/</t>
+          <t>https://www.nd-seishin.ac.jp/school/access/</t>
         </is>
       </c>
       <c r="O1111" s="12" t="inlineStr">
@@ -65679,22 +65663,22 @@
       </c>
       <c r="B1112" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1112" s="5" t="inlineStr">
         <is>
-          <t>呉市</t>
+          <t>岡山市北区</t>
         </is>
       </c>
       <c r="D1112" s="5" t="inlineStr">
         <is>
-          <t>呉青山高等学校</t>
+          <t>創志学園高等学校</t>
         </is>
       </c>
       <c r="E1112" s="6" t="inlineStr">
         <is>
-          <t>0823-32-1721</t>
+          <t>086-252-2101</t>
         </is>
       </c>
       <c r="F1112" s="7" t="inlineStr">
@@ -65704,7 +65688,7 @@
       </c>
       <c r="G1112" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1112" s="8" t="n"/>
@@ -65718,12 +65702,12 @@
       <c r="L1112" s="9" t="n"/>
       <c r="M1112" s="10" t="inlineStr">
         <is>
-          <t>2027年4月に「星の杜広島中学校・高等学校」へ校名変更予定</t>
+          <t>入試広報室は0120-151752</t>
         </is>
       </c>
       <c r="N1112" s="11" t="inlineStr">
         <is>
-          <t>https://www.kureaoyama.ed.jp/</t>
+          <t>https://www.soshigakuen.ed.jp/access/</t>
         </is>
       </c>
       <c r="O1112" s="12" t="inlineStr">
@@ -65738,22 +65722,22 @@
       </c>
       <c r="B1113" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1113" s="5" t="inlineStr">
         <is>
-          <t>広島市安佐南区</t>
+          <t>高梁市</t>
         </is>
       </c>
       <c r="D1113" s="5" t="inlineStr">
         <is>
-          <t>広陵高等学校</t>
+          <t>方谷學舎高等学校</t>
         </is>
       </c>
       <c r="E1113" s="6" t="inlineStr">
         <is>
-          <t>082-848-1321</t>
+          <t>0866-22-2205</t>
         </is>
       </c>
       <c r="F1113" s="7" t="inlineStr">
@@ -65775,10 +65759,14 @@
       </c>
       <c r="K1113" s="8" t="n"/>
       <c r="L1113" s="9" t="n"/>
-      <c r="M1113" s="10" t="n"/>
+      <c r="M1113" s="10" t="inlineStr">
+        <is>
+          <t>2023年6月に「岡山県高梁日新高等学校」から校名変更。事務室番号（教務室は0866-56-0015）</t>
+        </is>
+      </c>
       <c r="N1113" s="11" t="inlineStr">
         <is>
-          <t>https://www.koryo.ac.jp/</t>
+          <t>https://www.houkoku-gakusha.ed.jp/introduction/</t>
         </is>
       </c>
       <c r="O1113" s="12" t="inlineStr">
@@ -65793,22 +65781,22 @@
       </c>
       <c r="B1114" s="5" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="C1114" s="5" t="inlineStr">
         <is>
-          <t>呉市</t>
+          <t>岡山市北区</t>
         </is>
       </c>
       <c r="D1114" s="5" t="inlineStr">
         <is>
-          <t>呉港高等学校</t>
+          <t>明誠学院高等学校</t>
         </is>
       </c>
       <c r="E1114" s="6" t="inlineStr">
         <is>
-          <t>0823-71-9163</t>
+          <t>086-252-5247</t>
         </is>
       </c>
       <c r="F1114" s="7" t="inlineStr">
@@ -65818,7 +65806,7 @@
       </c>
       <c r="G1114" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1114" s="8" t="n"/>
@@ -65833,7 +65821,7 @@
       <c r="M1114" s="10" t="n"/>
       <c r="N1114" s="11" t="inlineStr">
         <is>
-          <t>https://www.goko.ac.jp/?page_id=96</t>
+          <t>https://www.meiseigakuin.ac.jp/</t>
         </is>
       </c>
       <c r="O1114" s="12" t="inlineStr">
@@ -65853,17 +65841,17 @@
       </c>
       <c r="C1115" s="5" t="inlineStr">
         <is>
-          <t>広島市西区</t>
+          <t>広島市安佐南区</t>
         </is>
       </c>
       <c r="D1115" s="5" t="inlineStr">
         <is>
-          <t>山陽高等学校</t>
+          <t>AICJ高等学校</t>
         </is>
       </c>
       <c r="E1115" s="6" t="inlineStr">
         <is>
-          <t>082-232-9156</t>
+          <t>082-832-5037</t>
         </is>
       </c>
       <c r="F1115" s="7" t="inlineStr">
@@ -65873,7 +65861,7 @@
       </c>
       <c r="G1115" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1115" s="8" t="n"/>
@@ -65887,12 +65875,12 @@
       <c r="L1115" s="9" t="n"/>
       <c r="M1115" s="10" t="inlineStr">
         <is>
-          <t>正式名は広島山陽学園山陽高等学校</t>
+          <t>一部サイトに旧番号らしい082-874-3081の記載あり</t>
         </is>
       </c>
       <c r="N1115" s="11" t="inlineStr">
         <is>
-          <t>https://www.sanyo.ed.jp/gakkou/access/</t>
+          <t>https://aicj.ed.jp/access.html</t>
         </is>
       </c>
       <c r="O1115" s="12" t="inlineStr">
@@ -65912,17 +65900,17 @@
       </c>
       <c r="C1116" s="5" t="inlineStr">
         <is>
-          <t>廿日市市</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1116" s="5" t="inlineStr">
         <is>
-          <t>山陽女学園高等部</t>
+          <t>盈進高等学校</t>
         </is>
       </c>
       <c r="E1116" s="6" t="inlineStr">
         <is>
-          <t>0829-32-2222</t>
+          <t>084-955-2333</t>
         </is>
       </c>
       <c r="F1116" s="7" t="inlineStr">
@@ -65932,7 +65920,7 @@
       </c>
       <c r="G1116" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1116" s="8" t="n"/>
@@ -65946,12 +65934,12 @@
       <c r="L1116" s="9" t="n"/>
       <c r="M1116" s="10" t="inlineStr">
         <is>
-          <t>通信制リアライズコースは0829-32-3330</t>
+          <t>中高共通の代表番号</t>
         </is>
       </c>
       <c r="N1116" s="11" t="inlineStr">
         <is>
-          <t>https://sanyo-jogakuen.ed.jp/</t>
+          <t>https://www.eishin.ed.jp/access/</t>
         </is>
       </c>
       <c r="O1116" s="12" t="inlineStr">
@@ -65971,17 +65959,17 @@
       </c>
       <c r="C1117" s="5" t="inlineStr">
         <is>
-          <t>呉市</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1117" s="5" t="inlineStr">
         <is>
-          <t>清水ヶ丘高等学校</t>
+          <t>英数学館高等学校</t>
         </is>
       </c>
       <c r="E1117" s="6" t="inlineStr">
         <is>
-          <t>0823-23-1520</t>
+          <t>084-941-4115</t>
         </is>
       </c>
       <c r="F1117" s="7" t="inlineStr">
@@ -65991,7 +65979,7 @@
       </c>
       <c r="G1117" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1117" s="8" t="n"/>
@@ -66005,12 +65993,12 @@
       <c r="L1117" s="9" t="n"/>
       <c r="M1117" s="10" t="inlineStr">
         <is>
-          <t>法人事務局は0823-22-0012</t>
+          <t>一部サイトに084-941-4117の記載あり（旧番号か）</t>
         </is>
       </c>
       <c r="N1117" s="11" t="inlineStr">
         <is>
-          <t>https://www.shimizugaoka.ed.jp/</t>
+          <t>https://goto.eisu-ejs.ac.jp/access/</t>
         </is>
       </c>
       <c r="O1117" s="12" t="inlineStr">
@@ -66030,17 +66018,17 @@
       </c>
       <c r="C1118" s="5" t="inlineStr">
         <is>
-          <t>広島市中区</t>
+          <t>尾道市</t>
         </is>
       </c>
       <c r="D1118" s="5" t="inlineStr">
         <is>
-          <t>修道高等学校</t>
+          <t>尾道高等学校</t>
         </is>
       </c>
       <c r="E1118" s="6" t="inlineStr">
         <is>
-          <t>082-241-8291</t>
+          <t>0848-20-6612</t>
         </is>
       </c>
       <c r="F1118" s="7" t="inlineStr">
@@ -66050,7 +66038,7 @@
       </c>
       <c r="G1118" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1118" s="8" t="n"/>
@@ -66064,12 +66052,12 @@
       <c r="L1118" s="9" t="n"/>
       <c r="M1118" s="10" t="inlineStr">
         <is>
-          <t>中高共通の代表番号</t>
+          <t>2009年に向島町へ移転。旧番号0848-23-2311が残るサイトあり</t>
         </is>
       </c>
       <c r="N1118" s="11" t="inlineStr">
         <is>
-          <t>https://www.shudo-h.ed.jp/</t>
+          <t>https://onomichi.ac.jp/</t>
         </is>
       </c>
       <c r="O1118" s="12" t="inlineStr">
@@ -66089,17 +66077,17 @@
       </c>
       <c r="C1119" s="5" t="inlineStr">
         <is>
-          <t>広島市南区</t>
+          <t>東広島市</t>
         </is>
       </c>
       <c r="D1119" s="5" t="inlineStr">
         <is>
-          <t>進徳女子高等学校</t>
+          <t>近畿大学附属広島高等学校東広島校</t>
         </is>
       </c>
       <c r="E1119" s="6" t="inlineStr">
         <is>
-          <t>082-251-6431</t>
+          <t>082-434-7111</t>
         </is>
       </c>
       <c r="F1119" s="7" t="inlineStr">
@@ -66109,7 +66097,7 @@
       </c>
       <c r="G1119" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1119" s="8" t="n"/>
@@ -66124,7 +66112,7 @@
       <c r="M1119" s="10" t="n"/>
       <c r="N1119" s="11" t="inlineStr">
         <is>
-          <t>https://www.shintoku.ed.jp/</t>
+          <t>https://hh.kindai.ac.jp/</t>
         </is>
       </c>
       <c r="O1119" s="12" t="inlineStr">
@@ -66144,17 +66132,17 @@
       </c>
       <c r="C1120" s="5" t="inlineStr">
         <is>
-          <t>三原市</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1120" s="5" t="inlineStr">
         <is>
-          <t>如水館高等学校</t>
+          <t>近畿大学附属広島高等学校福山校</t>
         </is>
       </c>
       <c r="E1120" s="6" t="inlineStr">
         <is>
-          <t>0848-63-2423</t>
+          <t>084-951-2695</t>
         </is>
       </c>
       <c r="F1120" s="7" t="inlineStr">
@@ -66176,10 +66164,14 @@
       </c>
       <c r="K1120" s="8" t="n"/>
       <c r="L1120" s="9" t="n"/>
-      <c r="M1120" s="10" t="n"/>
+      <c r="M1120" s="10" t="inlineStr">
+        <is>
+          <t>旧称は近畿大学附属福山高等学校</t>
+        </is>
+      </c>
       <c r="N1120" s="11" t="inlineStr">
         <is>
-          <t>https://www.josuikan.ed.jp/about/gaiyou</t>
+          <t>https://www.fukuyama.kindai.ac.jp/gakko/gakko-shokai.html</t>
         </is>
       </c>
       <c r="O1120" s="12" t="inlineStr">
@@ -66199,17 +66191,17 @@
       </c>
       <c r="C1121" s="5" t="inlineStr">
         <is>
-          <t>広島市西区</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1121" s="5" t="inlineStr">
         <is>
-          <t>崇徳高等学校</t>
+          <t>銀河学院高等学校</t>
         </is>
       </c>
       <c r="E1121" s="6" t="inlineStr">
         <is>
-          <t>082-237-9331</t>
+          <t>084-941-9292</t>
         </is>
       </c>
       <c r="F1121" s="7" t="inlineStr">
@@ -66231,10 +66223,14 @@
       </c>
       <c r="K1121" s="8" t="n"/>
       <c r="L1121" s="9" t="n"/>
-      <c r="M1121" s="10" t="n"/>
+      <c r="M1121" s="10" t="inlineStr">
+        <is>
+          <t>公式（法人事務室）に記載、複数サイトも一致</t>
+        </is>
+      </c>
       <c r="N1121" s="11" t="inlineStr">
         <is>
-          <t>https://www.sotoku.ed.jp/</t>
+          <t>https://www.ginga.ac.jp/donationginga/</t>
         </is>
       </c>
       <c r="O1121" s="12" t="inlineStr">
@@ -66254,17 +66250,17 @@
       </c>
       <c r="C1122" s="5" t="inlineStr">
         <is>
-          <t>東広島市</t>
+          <t>呉市</t>
         </is>
       </c>
       <c r="D1122" s="5" t="inlineStr">
         <is>
-          <t>武田高等学校</t>
+          <t>呉青山高等学校</t>
         </is>
       </c>
       <c r="E1122" s="6" t="inlineStr">
         <is>
-          <t>0823-82-2331</t>
+          <t>0823-32-1721</t>
         </is>
       </c>
       <c r="F1122" s="7" t="inlineStr">
@@ -66286,10 +66282,14 @@
       </c>
       <c r="K1122" s="8" t="n"/>
       <c r="L1122" s="9" t="n"/>
-      <c r="M1122" s="10" t="n"/>
+      <c r="M1122" s="10" t="inlineStr">
+        <is>
+          <t>2027年4月に「星の杜広島中学校・高等学校」へ校名変更予定</t>
+        </is>
+      </c>
       <c r="N1122" s="11" t="inlineStr">
         <is>
-          <t>https://takeda.ed.jp/</t>
+          <t>https://www.kureaoyama.ed.jp/</t>
         </is>
       </c>
       <c r="O1122" s="12" t="inlineStr">
@@ -66309,17 +66309,17 @@
       </c>
       <c r="C1123" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>広島市安佐南区</t>
         </is>
       </c>
       <c r="D1123" s="5" t="inlineStr">
         <is>
-          <t>東林館高等学校</t>
+          <t>広陵高等学校</t>
         </is>
       </c>
       <c r="E1123" s="6" t="inlineStr">
         <is>
-          <t>084-923-4543</t>
+          <t>082-848-1321</t>
         </is>
       </c>
       <c r="F1123" s="7" t="inlineStr">
@@ -66341,14 +66341,10 @@
       </c>
       <c r="K1123" s="8" t="n"/>
       <c r="L1123" s="9" t="n"/>
-      <c r="M1123" s="10" t="inlineStr">
-        <is>
-          <t>通信制。2010年に本校を神石高原町から福山市へ移転。旧番号0847-85-2041が残るサイトあり</t>
-        </is>
-      </c>
+      <c r="M1123" s="10" t="n"/>
       <c r="N1123" s="11" t="inlineStr">
         <is>
-          <t>https://www.tohrinkan.com/</t>
+          <t>https://www.koryo.ac.jp/</t>
         </is>
       </c>
       <c r="O1123" s="12" t="inlineStr">
@@ -66368,17 +66364,17 @@
       </c>
       <c r="C1124" s="5" t="inlineStr">
         <is>
-          <t>広島市中区</t>
+          <t>呉市</t>
         </is>
       </c>
       <c r="D1124" s="5" t="inlineStr">
         <is>
-          <t>並木学院高等学校</t>
+          <t>呉港高等学校</t>
         </is>
       </c>
       <c r="E1124" s="6" t="inlineStr">
         <is>
-          <t>082-241-9066</t>
+          <t>0823-71-9163</t>
         </is>
       </c>
       <c r="F1124" s="7" t="inlineStr">
@@ -66388,7 +66384,7 @@
       </c>
       <c r="G1124" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1124" s="8" t="n"/>
@@ -66400,14 +66396,10 @@
       </c>
       <c r="K1124" s="8" t="n"/>
       <c r="L1124" s="9" t="n"/>
-      <c r="M1124" s="10" t="inlineStr">
-        <is>
-          <t>FAXは082-241-5211</t>
-        </is>
-      </c>
+      <c r="M1124" s="10" t="n"/>
       <c r="N1124" s="11" t="inlineStr">
         <is>
-          <t>https://namikigakuin.ac.jp/school-info/group/</t>
+          <t>https://www.goko.ac.jp/?page_id=96</t>
         </is>
       </c>
       <c r="O1124" s="12" t="inlineStr">
@@ -66432,12 +66424,12 @@
       </c>
       <c r="D1125" s="5" t="inlineStr">
         <is>
-          <t>ノートルダム清心高等学校</t>
+          <t>山陽高等学校</t>
         </is>
       </c>
       <c r="E1125" s="6" t="inlineStr">
         <is>
-          <t>082-271-1724</t>
+          <t>082-232-9156</t>
         </is>
       </c>
       <c r="F1125" s="7" t="inlineStr">
@@ -66447,7 +66439,7 @@
       </c>
       <c r="G1125" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1125" s="8" t="n"/>
@@ -66461,12 +66453,12 @@
       <c r="L1125" s="9" t="n"/>
       <c r="M1125" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>正式名は広島山陽学園山陽高等学校</t>
         </is>
       </c>
       <c r="N1125" s="11" t="inlineStr">
         <is>
-          <t>https://www.hiro-seishin.ed.jp/contact/</t>
+          <t>https://www.sanyo.ed.jp/gakkou/access/</t>
         </is>
       </c>
       <c r="O1125" s="12" t="inlineStr">
@@ -66486,17 +66478,17 @@
       </c>
       <c r="C1126" s="5" t="inlineStr">
         <is>
-          <t>広島市南区</t>
+          <t>廿日市市</t>
         </is>
       </c>
       <c r="D1126" s="5" t="inlineStr">
         <is>
-          <t>比治山学園高等学校</t>
+          <t>山陽女学園高等部</t>
         </is>
       </c>
       <c r="E1126" s="6" t="inlineStr">
         <is>
-          <t>082-251-4478</t>
+          <t>0829-32-2222</t>
         </is>
       </c>
       <c r="F1126" s="7" t="inlineStr">
@@ -66506,7 +66498,7 @@
       </c>
       <c r="G1126" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1126" s="8" t="n"/>
@@ -66520,12 +66512,12 @@
       <c r="L1126" s="9" t="n"/>
       <c r="M1126" s="10" t="inlineStr">
         <is>
-          <t>旧・比治山女子。2026年4月に共学化・校名変更。新サイト https://www.hijiyama-h.ed.jp/</t>
+          <t>通信制リアライズコースは0829-32-3330</t>
         </is>
       </c>
       <c r="N1126" s="11" t="inlineStr">
         <is>
-          <t>https://www.hijiyamajoshi-h.ed.jp/education/</t>
+          <t>https://sanyo-jogakuen.ed.jp/</t>
         </is>
       </c>
       <c r="O1126" s="12" t="inlineStr">
@@ -66545,17 +66537,17 @@
       </c>
       <c r="C1127" s="5" t="inlineStr">
         <is>
-          <t>広島市西区</t>
+          <t>呉市</t>
         </is>
       </c>
       <c r="D1127" s="5" t="inlineStr">
         <is>
-          <t>広島学院高等学校</t>
+          <t>清水ヶ丘高等学校</t>
         </is>
       </c>
       <c r="E1127" s="6" t="inlineStr">
         <is>
-          <t>082-271-0241</t>
+          <t>0823-23-1520</t>
         </is>
       </c>
       <c r="F1127" s="7" t="inlineStr">
@@ -66565,7 +66557,7 @@
       </c>
       <c r="G1127" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1127" s="8" t="n"/>
@@ -66579,12 +66571,12 @@
       <c r="L1127" s="9" t="n"/>
       <c r="M1127" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>法人事務局は0823-22-0012</t>
         </is>
       </c>
       <c r="N1127" s="11" t="inlineStr">
         <is>
-          <t>https://www.hiroshimagakuin.ed.jp/contact/</t>
+          <t>https://www.shimizugaoka.ed.jp/</t>
         </is>
       </c>
       <c r="O1127" s="12" t="inlineStr">
@@ -66604,17 +66596,17 @@
       </c>
       <c r="C1128" s="5" t="inlineStr">
         <is>
-          <t>広島市西区</t>
+          <t>広島市中区</t>
         </is>
       </c>
       <c r="D1128" s="5" t="inlineStr">
         <is>
-          <t>広島工業大学高等学校</t>
+          <t>修道高等学校</t>
         </is>
       </c>
       <c r="E1128" s="6" t="inlineStr">
         <is>
-          <t>082-277-9205</t>
+          <t>082-241-8291</t>
         </is>
       </c>
       <c r="F1128" s="7" t="inlineStr">
@@ -66638,12 +66630,12 @@
       <c r="L1128" s="9" t="n"/>
       <c r="M1128" s="10" t="inlineStr">
         <is>
-          <t>全日制（西区）。通信制（安佐南区）は082-849-6755</t>
+          <t>中高共通の代表番号</t>
         </is>
       </c>
       <c r="N1128" s="11" t="inlineStr">
         <is>
-          <t>https://www.kodaikoko.ed.jp/zennichi/</t>
+          <t>https://www.shudo-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1128" s="12" t="inlineStr">
@@ -66663,17 +66655,17 @@
       </c>
       <c r="C1129" s="5" t="inlineStr">
         <is>
-          <t>海田町</t>
+          <t>広島市南区</t>
         </is>
       </c>
       <c r="D1129" s="5" t="inlineStr">
         <is>
-          <t>広島国際学院高等学校</t>
+          <t>進徳女子高等学校</t>
         </is>
       </c>
       <c r="E1129" s="6" t="inlineStr">
         <is>
-          <t>082-823-3401</t>
+          <t>082-251-6431</t>
         </is>
       </c>
       <c r="F1129" s="7" t="inlineStr">
@@ -66683,7 +66675,7 @@
       </c>
       <c r="G1129" s="5" t="inlineStr">
         <is>
-          <t>普通科・総合学科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1129" s="8" t="n"/>
@@ -66695,14 +66687,10 @@
       </c>
       <c r="K1129" s="8" t="n"/>
       <c r="L1129" s="9" t="n"/>
-      <c r="M1129" s="10" t="inlineStr">
-        <is>
-          <t>全日制（海田町）。通信制の中野キャンパスは082-820-2515</t>
-        </is>
-      </c>
+      <c r="M1129" s="10" t="n"/>
       <c r="N1129" s="11" t="inlineStr">
         <is>
-          <t>https://www.hi.hkg.ac.jp/access</t>
+          <t>https://www.shintoku.ed.jp/</t>
         </is>
       </c>
       <c r="O1129" s="12" t="inlineStr">
@@ -66722,22 +66710,22 @@
       </c>
       <c r="C1130" s="5" t="inlineStr">
         <is>
-          <t>広島市東区</t>
+          <t>三原市</t>
         </is>
       </c>
       <c r="D1130" s="5" t="inlineStr">
         <is>
-          <t>広島桜が丘高等学校</t>
+          <t>如水館高等学校</t>
         </is>
       </c>
       <c r="E1130" s="6" t="inlineStr">
         <is>
-          <t>082-262-0128</t>
-        </is>
-      </c>
-      <c r="F1130" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>0848-63-2423</t>
+        </is>
+      </c>
+      <c r="F1130" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="G1130" s="5" t="inlineStr">
@@ -66754,14 +66742,10 @@
       </c>
       <c r="K1130" s="8" t="n"/>
       <c r="L1130" s="9" t="n"/>
-      <c r="M1130" s="10" t="inlineStr">
-        <is>
-          <t>公式未確認、複数サイトで一致</t>
-        </is>
-      </c>
+      <c r="M1130" s="10" t="n"/>
       <c r="N1130" s="11" t="inlineStr">
         <is>
-          <t>https://www.mapion.co.jp/phonebook/M11004/34102/ILSP0000041015_ipclm/</t>
+          <t>https://www.josuikan.ed.jp/about/gaiyou</t>
         </is>
       </c>
       <c r="O1130" s="12" t="inlineStr">
@@ -66781,17 +66765,17 @@
       </c>
       <c r="C1131" s="5" t="inlineStr">
         <is>
-          <t>三原市</t>
+          <t>広島市西区</t>
         </is>
       </c>
       <c r="D1131" s="5" t="inlineStr">
         <is>
-          <t>広島三育学院高等学校</t>
+          <t>崇徳高等学校</t>
         </is>
       </c>
       <c r="E1131" s="6" t="inlineStr">
         <is>
-          <t>0847-33-0311</t>
+          <t>082-237-9331</t>
         </is>
       </c>
       <c r="F1131" s="7" t="inlineStr">
@@ -66816,7 +66800,7 @@
       <c r="M1131" s="10" t="n"/>
       <c r="N1131" s="11" t="inlineStr">
         <is>
-          <t>https://www.saniku.ac.jp/hiroshima/about/profile.php</t>
+          <t>https://www.sotoku.ed.jp/</t>
         </is>
       </c>
       <c r="O1131" s="12" t="inlineStr">
@@ -66836,17 +66820,17 @@
       </c>
       <c r="C1132" s="5" t="inlineStr">
         <is>
-          <t>広島市西区</t>
+          <t>東広島市</t>
         </is>
       </c>
       <c r="D1132" s="5" t="inlineStr">
         <is>
-          <t>広島修道大学ひろしま協創高等学校</t>
+          <t>武田高等学校</t>
         </is>
       </c>
       <c r="E1132" s="6" t="inlineStr">
         <is>
-          <t>082-278-1101</t>
+          <t>0823-82-2331</t>
         </is>
       </c>
       <c r="F1132" s="7" t="inlineStr">
@@ -66871,7 +66855,7 @@
       <c r="M1132" s="10" t="n"/>
       <c r="N1132" s="11" t="inlineStr">
         <is>
-          <t>https://www.shudo-u.ac.jp/fuzoku/</t>
+          <t>https://takeda.ed.jp/</t>
         </is>
       </c>
       <c r="O1132" s="12" t="inlineStr">
@@ -66891,17 +66875,17 @@
       </c>
       <c r="C1133" s="5" t="inlineStr">
         <is>
-          <t>坂町</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1133" s="5" t="inlineStr">
         <is>
-          <t>広島翔洋高等学校</t>
+          <t>東林館高等学校</t>
         </is>
       </c>
       <c r="E1133" s="6" t="inlineStr">
         <is>
-          <t>082-884-1616</t>
+          <t>084-923-4543</t>
         </is>
       </c>
       <c r="F1133" s="7" t="inlineStr">
@@ -66911,7 +66895,7 @@
       </c>
       <c r="G1133" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1133" s="8" t="n"/>
@@ -66923,10 +66907,14 @@
       </c>
       <c r="K1133" s="8" t="n"/>
       <c r="L1133" s="9" t="n"/>
-      <c r="M1133" s="10" t="n"/>
+      <c r="M1133" s="10" t="inlineStr">
+        <is>
+          <t>通信制。2010年に本校を神石高原町から福山市へ移転。旧番号0847-85-2041が残るサイトあり</t>
+        </is>
+      </c>
       <c r="N1133" s="11" t="inlineStr">
         <is>
-          <t>https://www.h-shoyo.ed.jp/overview/details.php</t>
+          <t>https://www.tohrinkan.com/</t>
         </is>
       </c>
       <c r="O1133" s="12" t="inlineStr">
@@ -66946,17 +66934,17 @@
       </c>
       <c r="C1134" s="5" t="inlineStr">
         <is>
-          <t>北広島町</t>
+          <t>広島市中区</t>
         </is>
       </c>
       <c r="D1134" s="5" t="inlineStr">
         <is>
-          <t>広島新庄高等学校</t>
+          <t>並木学院高等学校</t>
         </is>
       </c>
       <c r="E1134" s="6" t="inlineStr">
         <is>
-          <t>0826-82-2323</t>
+          <t>082-241-9066</t>
         </is>
       </c>
       <c r="F1134" s="7" t="inlineStr">
@@ -66978,10 +66966,14 @@
       </c>
       <c r="K1134" s="8" t="n"/>
       <c r="L1134" s="9" t="n"/>
-      <c r="M1134" s="10" t="n"/>
+      <c r="M1134" s="10" t="inlineStr">
+        <is>
+          <t>FAXは082-241-5211</t>
+        </is>
+      </c>
       <c r="N1134" s="11" t="inlineStr">
         <is>
-          <t>https://www.shinjou.jp/toiawase/toiawase.html</t>
+          <t>https://namikigakuin.ac.jp/school-info/group/</t>
         </is>
       </c>
       <c r="O1134" s="12" t="inlineStr">
@@ -67001,17 +66993,17 @@
       </c>
       <c r="C1135" s="5" t="inlineStr">
         <is>
-          <t>広島市東区</t>
+          <t>広島市西区</t>
         </is>
       </c>
       <c r="D1135" s="5" t="inlineStr">
         <is>
-          <t>広島城北高等学校</t>
+          <t>ノートルダム清心高等学校</t>
         </is>
       </c>
       <c r="E1135" s="6" t="inlineStr">
         <is>
-          <t>082-229-0111</t>
+          <t>082-271-1724</t>
         </is>
       </c>
       <c r="F1135" s="7" t="inlineStr">
@@ -67033,10 +67025,14 @@
       </c>
       <c r="K1135" s="8" t="n"/>
       <c r="L1135" s="9" t="n"/>
-      <c r="M1135" s="10" t="n"/>
+      <c r="M1135" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
       <c r="N1135" s="11" t="inlineStr">
         <is>
-          <t>https://hiroshimajohoku.ed.jp/school/about/access/</t>
+          <t>https://www.hiro-seishin.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O1135" s="12" t="inlineStr">
@@ -67056,17 +67052,17 @@
       </c>
       <c r="C1136" s="5" t="inlineStr">
         <is>
-          <t>広島市中区</t>
+          <t>広島市南区</t>
         </is>
       </c>
       <c r="D1136" s="5" t="inlineStr">
         <is>
-          <t>広島女学院高等学校</t>
+          <t>比治山学園高等学校</t>
         </is>
       </c>
       <c r="E1136" s="6" t="inlineStr">
         <is>
-          <t>082-228-4131</t>
+          <t>082-251-4478</t>
         </is>
       </c>
       <c r="F1136" s="7" t="inlineStr">
@@ -67088,10 +67084,14 @@
       </c>
       <c r="K1136" s="8" t="n"/>
       <c r="L1136" s="9" t="n"/>
-      <c r="M1136" s="10" t="n"/>
+      <c r="M1136" s="10" t="inlineStr">
+        <is>
+          <t>旧・比治山女子。2026年4月に共学化・校名変更。新サイト https://www.hijiyama-h.ed.jp/</t>
+        </is>
+      </c>
       <c r="N1136" s="11" t="inlineStr">
         <is>
-          <t>https://www.hjs.ed.jp/contact</t>
+          <t>https://www.hijiyamajoshi-h.ed.jp/education/</t>
         </is>
       </c>
       <c r="O1136" s="12" t="inlineStr">
@@ -67111,17 +67111,17 @@
       </c>
       <c r="C1137" s="5" t="inlineStr">
         <is>
-          <t>広島市東区</t>
+          <t>広島市西区</t>
         </is>
       </c>
       <c r="D1137" s="5" t="inlineStr">
         <is>
-          <t>広島県瀬戸内高等学校</t>
+          <t>広島学院高等学校</t>
         </is>
       </c>
       <c r="E1137" s="6" t="inlineStr">
         <is>
-          <t>082-261-1296</t>
+          <t>082-271-0241</t>
         </is>
       </c>
       <c r="F1137" s="7" t="inlineStr">
@@ -67145,12 +67145,12 @@
       <c r="L1137" s="9" t="n"/>
       <c r="M1137" s="10" t="inlineStr">
         <is>
-          <t>公式では入試広報部の番号として掲載。082-261-1298とするサイトもあり</t>
+          <t>中高共通番号</t>
         </is>
       </c>
       <c r="N1137" s="11" t="inlineStr">
         <is>
-          <t>https://www.setouchi-h.ed.jp/extrance1.html</t>
+          <t>https://www.hiroshimagakuin.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O1137" s="12" t="inlineStr">
@@ -67170,17 +67170,17 @@
       </c>
       <c r="C1138" s="5" t="inlineStr">
         <is>
-          <t>広島市佐伯区</t>
+          <t>広島市西区</t>
         </is>
       </c>
       <c r="D1138" s="5" t="inlineStr">
         <is>
-          <t>広島なぎさ高等学校</t>
+          <t>広島工業大学高等学校</t>
         </is>
       </c>
       <c r="E1138" s="6" t="inlineStr">
         <is>
-          <t>082-921-2137</t>
+          <t>082-277-9205</t>
         </is>
       </c>
       <c r="F1138" s="7" t="inlineStr">
@@ -67202,10 +67202,14 @@
       </c>
       <c r="K1138" s="8" t="n"/>
       <c r="L1138" s="9" t="n"/>
-      <c r="M1138" s="10" t="n"/>
+      <c r="M1138" s="10" t="inlineStr">
+        <is>
+          <t>全日制（西区）。通信制（安佐南区）は082-849-6755</t>
+        </is>
+      </c>
       <c r="N1138" s="11" t="inlineStr">
         <is>
-          <t>https://www.nagisa.ed.jp/high/</t>
+          <t>https://www.kodaikoko.ed.jp/zennichi/</t>
         </is>
       </c>
       <c r="O1138" s="12" t="inlineStr">
@@ -67225,17 +67229,17 @@
       </c>
       <c r="C1139" s="5" t="inlineStr">
         <is>
-          <t>広島市安佐北区</t>
+          <t>海田町</t>
         </is>
       </c>
       <c r="D1139" s="5" t="inlineStr">
         <is>
-          <t>広島文教大学附属高等学校</t>
+          <t>広島国際学院高等学校</t>
         </is>
       </c>
       <c r="E1139" s="6" t="inlineStr">
         <is>
-          <t>082-814-3192</t>
+          <t>082-823-3401</t>
         </is>
       </c>
       <c r="F1139" s="7" t="inlineStr">
@@ -67245,7 +67249,7 @@
       </c>
       <c r="G1139" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・総合学科</t>
         </is>
       </c>
       <c r="H1139" s="8" t="n"/>
@@ -67257,10 +67261,14 @@
       </c>
       <c r="K1139" s="8" t="n"/>
       <c r="L1139" s="9" t="n"/>
-      <c r="M1139" s="10" t="n"/>
+      <c r="M1139" s="10" t="inlineStr">
+        <is>
+          <t>全日制（海田町）。通信制の中野キャンパスは082-820-2515</t>
+        </is>
+      </c>
       <c r="N1139" s="11" t="inlineStr">
         <is>
-          <t>https://www.h-bunkyo.ac.jp/highschool/</t>
+          <t>https://www.hi.hkg.ac.jp/access</t>
         </is>
       </c>
       <c r="O1139" s="12" t="inlineStr">
@@ -67280,22 +67288,22 @@
       </c>
       <c r="C1140" s="5" t="inlineStr">
         <is>
-          <t>福山市</t>
+          <t>広島市東区</t>
         </is>
       </c>
       <c r="D1140" s="5" t="inlineStr">
         <is>
-          <t>福山暁の星女子高等学校</t>
+          <t>広島桜が丘高等学校</t>
         </is>
       </c>
       <c r="E1140" s="6" t="inlineStr">
         <is>
-          <t>084-922-1682</t>
-        </is>
-      </c>
-      <c r="F1140" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>082-262-0128</t>
+        </is>
+      </c>
+      <c r="F1140" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="G1140" s="5" t="inlineStr">
@@ -67312,10 +67320,14 @@
       </c>
       <c r="K1140" s="8" t="n"/>
       <c r="L1140" s="9" t="n"/>
-      <c r="M1140" s="10" t="n"/>
+      <c r="M1140" s="10" t="inlineStr">
+        <is>
+          <t>公式未確認、複数サイトで一致</t>
+        </is>
+      </c>
       <c r="N1140" s="11" t="inlineStr">
         <is>
-          <t>https://www.akenohoshi-cyukou.ed.jp/about/access/</t>
+          <t>https://www.mapion.co.jp/phonebook/M11004/34102/ILSP0000041015_ipclm/</t>
         </is>
       </c>
       <c r="O1140" s="12" t="inlineStr">
@@ -67335,17 +67347,17 @@
       </c>
       <c r="C1141" s="5" t="inlineStr">
         <is>
-          <t>広島市中区</t>
+          <t>三原市</t>
         </is>
       </c>
       <c r="D1141" s="5" t="inlineStr">
         <is>
-          <t>安田女子高等学校</t>
+          <t>広島三育学院高等学校</t>
         </is>
       </c>
       <c r="E1141" s="6" t="inlineStr">
         <is>
-          <t>082-221-3304</t>
+          <t>0847-33-0311</t>
         </is>
       </c>
       <c r="F1141" s="7" t="inlineStr">
@@ -67367,14 +67379,10 @@
       </c>
       <c r="K1141" s="8" t="n"/>
       <c r="L1141" s="9" t="n"/>
-      <c r="M1141" s="10" t="inlineStr">
-        <is>
-          <t>高校部の番号。中学部は082-221-3362</t>
-        </is>
-      </c>
+      <c r="M1141" s="10" t="n"/>
       <c r="N1141" s="11" t="inlineStr">
         <is>
-          <t>https://www.yasuda-u.ac.jp/jh/</t>
+          <t>https://www.saniku.ac.jp/hiroshima/about/profile.php</t>
         </is>
       </c>
       <c r="O1141" s="12" t="inlineStr">
@@ -67389,22 +67397,22 @@
       </c>
       <c r="B1142" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1142" s="5" t="inlineStr">
         <is>
-          <t>宇部市</t>
+          <t>広島市西区</t>
         </is>
       </c>
       <c r="D1142" s="5" t="inlineStr">
         <is>
-          <t>宇部鴻城高等学校</t>
+          <t>広島修道大学ひろしま協創高等学校</t>
         </is>
       </c>
       <c r="E1142" s="6" t="inlineStr">
         <is>
-          <t>0836-41-8109</t>
+          <t>082-278-1101</t>
         </is>
       </c>
       <c r="F1142" s="7" t="inlineStr">
@@ -67414,7 +67422,7 @@
       </c>
       <c r="G1142" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1142" s="8" t="n"/>
@@ -67429,7 +67437,7 @@
       <c r="M1142" s="10" t="n"/>
       <c r="N1142" s="11" t="inlineStr">
         <is>
-          <t>https://www.ubekojo-h.ed.jp/contact/</t>
+          <t>https://www.shudo-u.ac.jp/fuzoku/</t>
         </is>
       </c>
       <c r="O1142" s="12" t="inlineStr">
@@ -67444,22 +67452,22 @@
       </c>
       <c r="B1143" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1143" s="5" t="inlineStr">
         <is>
-          <t>宇部市</t>
+          <t>坂町</t>
         </is>
       </c>
       <c r="D1143" s="5" t="inlineStr">
         <is>
-          <t>宇部フロンティア大学付属香川高等学校</t>
+          <t>広島翔洋高等学校</t>
         </is>
       </c>
       <c r="E1143" s="6" t="inlineStr">
         <is>
-          <t>0836-35-9574</t>
+          <t>082-884-1616</t>
         </is>
       </c>
       <c r="F1143" s="7" t="inlineStr">
@@ -67481,14 +67489,10 @@
       </c>
       <c r="K1143" s="8" t="n"/>
       <c r="L1143" s="9" t="n"/>
-      <c r="M1143" s="10" t="inlineStr">
-        <is>
-          <t>普通科職員室0836-35-9578、専門部職員室0836-35-9583</t>
-        </is>
-      </c>
+      <c r="M1143" s="10" t="n"/>
       <c r="N1143" s="11" t="inlineStr">
         <is>
-          <t>https://www.kagawa-h.ed.jp/</t>
+          <t>https://www.h-shoyo.ed.jp/overview/details.php</t>
         </is>
       </c>
       <c r="O1143" s="12" t="inlineStr">
@@ -67503,22 +67507,22 @@
       </c>
       <c r="B1144" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1144" s="5" t="inlineStr">
         <is>
-          <t>宇部市</t>
+          <t>北広島町</t>
         </is>
       </c>
       <c r="D1144" s="5" t="inlineStr">
         <is>
-          <t>慶進高等学校</t>
+          <t>広島新庄高等学校</t>
         </is>
       </c>
       <c r="E1144" s="6" t="inlineStr">
         <is>
-          <t>0836-34-1111</t>
+          <t>0826-82-2323</t>
         </is>
       </c>
       <c r="F1144" s="7" t="inlineStr">
@@ -67543,7 +67547,7 @@
       <c r="M1144" s="10" t="n"/>
       <c r="N1144" s="11" t="inlineStr">
         <is>
-          <t>https://www.keishin-ug.ed.jp/</t>
+          <t>https://www.shinjou.jp/toiawase/toiawase.html</t>
         </is>
       </c>
       <c r="O1144" s="12" t="inlineStr">
@@ -67558,22 +67562,22 @@
       </c>
       <c r="B1145" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1145" s="5" t="inlineStr">
         <is>
-          <t>山陽小野田市</t>
+          <t>広島市東区</t>
         </is>
       </c>
       <c r="D1145" s="5" t="inlineStr">
         <is>
-          <t>ザビエル高等学校</t>
+          <t>広島城北高等学校</t>
         </is>
       </c>
       <c r="E1145" s="6" t="inlineStr">
         <is>
-          <t>0836-83-3587</t>
+          <t>082-229-0111</t>
         </is>
       </c>
       <c r="F1145" s="7" t="inlineStr">
@@ -67595,14 +67599,10 @@
       </c>
       <c r="K1145" s="8" t="n"/>
       <c r="L1145" s="9" t="n"/>
-      <c r="M1145" s="10" t="inlineStr">
-        <is>
-          <t>正式表記は「サビエル高等学校」</t>
-        </is>
-      </c>
+      <c r="M1145" s="10" t="n"/>
       <c r="N1145" s="11" t="inlineStr">
         <is>
-          <t>https://xavier.ed.jp/</t>
+          <t>https://hiroshimajohoku.ed.jp/school/about/access/</t>
         </is>
       </c>
       <c r="O1145" s="12" t="inlineStr">
@@ -67617,22 +67617,22 @@
       </c>
       <c r="B1146" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1146" s="5" t="inlineStr">
         <is>
-          <t>下関市</t>
+          <t>広島市中区</t>
         </is>
       </c>
       <c r="D1146" s="5" t="inlineStr">
         <is>
-          <t>下関国際高等学校</t>
+          <t>広島女学院高等学校</t>
         </is>
       </c>
       <c r="E1146" s="6" t="inlineStr">
         <is>
-          <t>083-256-2321</t>
+          <t>082-228-4131</t>
         </is>
       </c>
       <c r="F1146" s="7" t="inlineStr">
@@ -67642,7 +67642,7 @@
       </c>
       <c r="G1146" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1146" s="8" t="n"/>
@@ -67657,7 +67657,7 @@
       <c r="M1146" s="10" t="n"/>
       <c r="N1146" s="11" t="inlineStr">
         <is>
-          <t>https://www.shiboyama.ac.jp/</t>
+          <t>https://www.hjs.ed.jp/contact</t>
         </is>
       </c>
       <c r="O1146" s="12" t="inlineStr">
@@ -67672,22 +67672,22 @@
       </c>
       <c r="B1147" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1147" s="5" t="inlineStr">
         <is>
-          <t>下関市</t>
+          <t>広島市東区</t>
         </is>
       </c>
       <c r="D1147" s="5" t="inlineStr">
         <is>
-          <t>下関短期大学付属高等学校</t>
+          <t>広島県瀬戸内高等学校</t>
         </is>
       </c>
       <c r="E1147" s="6" t="inlineStr">
         <is>
-          <t>083-232-3785</t>
+          <t>082-261-1296</t>
         </is>
       </c>
       <c r="F1147" s="7" t="inlineStr">
@@ -67697,7 +67697,7 @@
       </c>
       <c r="G1147" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1147" s="8" t="n"/>
@@ -67711,12 +67711,12 @@
       <c r="L1147" s="9" t="n"/>
       <c r="M1147" s="10" t="inlineStr">
         <is>
-          <t>短大の番号（083-223-0339）とは別</t>
+          <t>公式では入試広報部の番号として掲載。082-261-1298とするサイトもあり</t>
         </is>
       </c>
       <c r="N1147" s="11" t="inlineStr">
         <is>
-          <t>https://www.shimotan-hs.jp/pages/13/</t>
+          <t>https://www.setouchi-h.ed.jp/extrance1.html</t>
         </is>
       </c>
       <c r="O1147" s="12" t="inlineStr">
@@ -67731,22 +67731,22 @@
       </c>
       <c r="B1148" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1148" s="5" t="inlineStr">
         <is>
-          <t>防府市</t>
+          <t>広島市佐伯区</t>
         </is>
       </c>
       <c r="D1148" s="5" t="inlineStr">
         <is>
-          <t>誠英高等学校</t>
+          <t>広島なぎさ高等学校</t>
         </is>
       </c>
       <c r="E1148" s="6" t="inlineStr">
         <is>
-          <t>0835-38-5252</t>
+          <t>082-921-2137</t>
         </is>
       </c>
       <c r="F1148" s="7" t="inlineStr">
@@ -67756,7 +67756,7 @@
       </c>
       <c r="G1148" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1148" s="8" t="n"/>
@@ -67768,14 +67768,10 @@
       </c>
       <c r="K1148" s="8" t="n"/>
       <c r="L1148" s="9" t="n"/>
-      <c r="M1148" s="10" t="inlineStr">
-        <is>
-          <t>通信制課程は0835-38-6161（第三者サイト）</t>
-        </is>
-      </c>
+      <c r="M1148" s="10" t="n"/>
       <c r="N1148" s="11" t="inlineStr">
         <is>
-          <t>https://seiei.ac.jp/</t>
+          <t>https://www.nagisa.ed.jp/high/</t>
         </is>
       </c>
       <c r="O1148" s="12" t="inlineStr">
@@ -67790,22 +67786,22 @@
       </c>
       <c r="B1149" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1149" s="5" t="inlineStr">
         <is>
-          <t>山口市</t>
+          <t>広島市安佐北区</t>
         </is>
       </c>
       <c r="D1149" s="5" t="inlineStr">
         <is>
-          <t>精華学園高等学校</t>
+          <t>広島文教大学附属高等学校</t>
         </is>
       </c>
       <c r="E1149" s="6" t="inlineStr">
         <is>
-          <t>083-976-8833</t>
+          <t>082-814-3192</t>
         </is>
       </c>
       <c r="F1149" s="7" t="inlineStr">
@@ -67827,14 +67823,10 @@
       </c>
       <c r="K1149" s="8" t="n"/>
       <c r="L1149" s="9" t="n"/>
-      <c r="M1149" s="10" t="inlineStr">
-        <is>
-          <t>広域通信制・山口本校</t>
-        </is>
-      </c>
+      <c r="M1149" s="10" t="n"/>
       <c r="N1149" s="11" t="inlineStr">
         <is>
-          <t>https://www.seikagakuen.ac.jp/archives/691</t>
+          <t>https://www.h-bunkyo.ac.jp/highschool/</t>
         </is>
       </c>
       <c r="O1149" s="12" t="inlineStr">
@@ -67849,22 +67841,22 @@
       </c>
       <c r="B1150" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1150" s="5" t="inlineStr">
         <is>
-          <t>光市</t>
+          <t>福山市</t>
         </is>
       </c>
       <c r="D1150" s="5" t="inlineStr">
         <is>
-          <t>聖光高等学校</t>
+          <t>福山暁の星女子高等学校</t>
         </is>
       </c>
       <c r="E1150" s="6" t="inlineStr">
         <is>
-          <t>0833-72-1187</t>
+          <t>084-922-1682</t>
         </is>
       </c>
       <c r="F1150" s="7" t="inlineStr">
@@ -67874,7 +67866,7 @@
       </c>
       <c r="G1150" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1150" s="8" t="n"/>
@@ -67886,14 +67878,10 @@
       </c>
       <c r="K1150" s="8" t="n"/>
       <c r="L1150" s="9" t="n"/>
-      <c r="M1150" s="10" t="inlineStr">
-        <is>
-          <t>通信制は0833-72-7070（第三者サイト）</t>
-        </is>
-      </c>
+      <c r="M1150" s="10" t="n"/>
       <c r="N1150" s="11" t="inlineStr">
         <is>
-          <t>https://www.seiko-h.ed.jp/</t>
+          <t>https://www.akenohoshi-cyukou.ed.jp/about/access/</t>
         </is>
       </c>
       <c r="O1150" s="12" t="inlineStr">
@@ -67908,22 +67896,22 @@
       </c>
       <c r="B1151" s="5" t="inlineStr">
         <is>
-          <t>山口県</t>
+          <t>広島県</t>
         </is>
       </c>
       <c r="C1151" s="5" t="inlineStr">
         <is>
-          <t>美祢市</t>
+          <t>広島市中区</t>
         </is>
       </c>
       <c r="D1151" s="5" t="inlineStr">
         <is>
-          <t>成進高等学校</t>
+          <t>安田女子高等学校</t>
         </is>
       </c>
       <c r="E1151" s="6" t="inlineStr">
         <is>
-          <t>0837-52-1350</t>
+          <t>082-221-3304</t>
         </is>
       </c>
       <c r="F1151" s="7" t="inlineStr">
@@ -67933,7 +67921,7 @@
       </c>
       <c r="G1151" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1151" s="8" t="n"/>
@@ -67945,10 +67933,14 @@
       </c>
       <c r="K1151" s="8" t="n"/>
       <c r="L1151" s="9" t="n"/>
-      <c r="M1151" s="10" t="n"/>
+      <c r="M1151" s="10" t="inlineStr">
+        <is>
+          <t>高校部の番号。中学部は082-221-3362</t>
+        </is>
+      </c>
       <c r="N1151" s="11" t="inlineStr">
         <is>
-          <t>https://www.mine-c.ed.jp/profile</t>
+          <t>https://www.yasuda-u.ac.jp/jh/</t>
         </is>
       </c>
       <c r="O1151" s="12" t="inlineStr">
@@ -67968,17 +67960,17 @@
       </c>
       <c r="C1152" s="5" t="inlineStr">
         <is>
-          <t>防府市</t>
+          <t>宇部市</t>
         </is>
       </c>
       <c r="D1152" s="5" t="inlineStr">
         <is>
-          <t>高川学園高等学校</t>
+          <t>宇部鴻城高等学校</t>
         </is>
       </c>
       <c r="E1152" s="6" t="inlineStr">
         <is>
-          <t>0835-33-0101</t>
+          <t>0836-41-8109</t>
         </is>
       </c>
       <c r="F1152" s="7" t="inlineStr">
@@ -67988,7 +67980,7 @@
       </c>
       <c r="G1152" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1152" s="8" t="n"/>
@@ -68003,7 +67995,7 @@
       <c r="M1152" s="10" t="n"/>
       <c r="N1152" s="11" t="inlineStr">
         <is>
-          <t>https://takagawagakuen.com/high/</t>
+          <t>https://www.ubekojo-h.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O1152" s="12" t="inlineStr">
@@ -68023,17 +68015,17 @@
       </c>
       <c r="C1153" s="5" t="inlineStr">
         <is>
-          <t>岩国市</t>
+          <t>宇部市</t>
         </is>
       </c>
       <c r="D1153" s="5" t="inlineStr">
         <is>
-          <t>高水高等学校</t>
+          <t>宇部フロンティア大学付属香川高等学校</t>
         </is>
       </c>
       <c r="E1153" s="6" t="inlineStr">
         <is>
-          <t>0827-31-7191</t>
+          <t>0836-35-9574</t>
         </is>
       </c>
       <c r="F1153" s="7" t="inlineStr">
@@ -68043,7 +68035,7 @@
       </c>
       <c r="G1153" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1153" s="8" t="n"/>
@@ -68057,12 +68049,12 @@
       <c r="L1153" s="9" t="n"/>
       <c r="M1153" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>普通科職員室0836-35-9578、専門部職員室0836-35-9583</t>
         </is>
       </c>
       <c r="N1153" s="11" t="inlineStr">
         <is>
-          <t>https://www.takamizu.ed.jp/</t>
+          <t>https://www.kagawa-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1153" s="12" t="inlineStr">
@@ -68082,17 +68074,17 @@
       </c>
       <c r="C1154" s="5" t="inlineStr">
         <is>
-          <t>山口市</t>
+          <t>宇部市</t>
         </is>
       </c>
       <c r="D1154" s="5" t="inlineStr">
         <is>
-          <t>中村女子高等学校</t>
+          <t>慶進高等学校</t>
         </is>
       </c>
       <c r="E1154" s="6" t="inlineStr">
         <is>
-          <t>083-922-0418</t>
+          <t>0836-34-1111</t>
         </is>
       </c>
       <c r="F1154" s="7" t="inlineStr">
@@ -68102,7 +68094,7 @@
       </c>
       <c r="G1154" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1154" s="8" t="n"/>
@@ -68114,14 +68106,10 @@
       </c>
       <c r="K1154" s="8" t="n"/>
       <c r="L1154" s="9" t="n"/>
-      <c r="M1154" s="10" t="inlineStr">
-        <is>
-          <t>現校名は山口中村学園高等学校（2025年度から共学化）。専攻科は083-928-1331</t>
-        </is>
-      </c>
+      <c r="M1154" s="10" t="n"/>
       <c r="N1154" s="11" t="inlineStr">
         <is>
-          <t>https://www.y-nakamura.jp/</t>
+          <t>https://www.keishin-ug.ed.jp/</t>
         </is>
       </c>
       <c r="O1154" s="12" t="inlineStr">
@@ -68141,17 +68129,17 @@
       </c>
       <c r="C1155" s="5" t="inlineStr">
         <is>
-          <t>長門市</t>
+          <t>山陽小野田市</t>
         </is>
       </c>
       <c r="D1155" s="5" t="inlineStr">
         <is>
-          <t>長門高等学校</t>
+          <t>ザビエル高等学校</t>
         </is>
       </c>
       <c r="E1155" s="6" t="inlineStr">
         <is>
-          <t>0837-22-2944</t>
+          <t>0836-83-3587</t>
         </is>
       </c>
       <c r="F1155" s="7" t="inlineStr">
@@ -68161,7 +68149,7 @@
       </c>
       <c r="G1155" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1155" s="8" t="n"/>
@@ -68173,10 +68161,14 @@
       </c>
       <c r="K1155" s="8" t="n"/>
       <c r="L1155" s="9" t="n"/>
-      <c r="M1155" s="10" t="n"/>
+      <c r="M1155" s="10" t="inlineStr">
+        <is>
+          <t>正式表記は「サビエル高等学校」</t>
+        </is>
+      </c>
       <c r="N1155" s="11" t="inlineStr">
         <is>
-          <t>https://nagato.ac.jp/</t>
+          <t>https://xavier.ed.jp/</t>
         </is>
       </c>
       <c r="O1155" s="12" t="inlineStr">
@@ -68196,17 +68188,17 @@
       </c>
       <c r="C1156" s="5" t="inlineStr">
         <is>
-          <t>山口市</t>
+          <t>下関市</t>
         </is>
       </c>
       <c r="D1156" s="5" t="inlineStr">
         <is>
-          <t>野田学園高等学校</t>
+          <t>下関国際高等学校</t>
         </is>
       </c>
       <c r="E1156" s="6" t="inlineStr">
         <is>
-          <t>083-922-5000</t>
+          <t>083-256-2321</t>
         </is>
       </c>
       <c r="F1156" s="7" t="inlineStr">
@@ -68216,7 +68208,7 @@
       </c>
       <c r="G1156" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1156" s="8" t="n"/>
@@ -68231,7 +68223,7 @@
       <c r="M1156" s="10" t="n"/>
       <c r="N1156" s="11" t="inlineStr">
         <is>
-          <t>https://www.nodagakuen.ed.jp/</t>
+          <t>https://www.shiboyama.ac.jp/</t>
         </is>
       </c>
       <c r="O1156" s="12" t="inlineStr">
@@ -68251,17 +68243,17 @@
       </c>
       <c r="C1157" s="5" t="inlineStr">
         <is>
-          <t>萩市</t>
+          <t>下関市</t>
         </is>
       </c>
       <c r="D1157" s="5" t="inlineStr">
         <is>
-          <t>萩光塩学院高等学校</t>
+          <t>下関短期大学付属高等学校</t>
         </is>
       </c>
       <c r="E1157" s="6" t="inlineStr">
         <is>
-          <t>0838-22-0782</t>
+          <t>083-232-3785</t>
         </is>
       </c>
       <c r="F1157" s="7" t="inlineStr">
@@ -68271,7 +68263,7 @@
       </c>
       <c r="G1157" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1157" s="8" t="n"/>
@@ -68285,12 +68277,12 @@
       <c r="L1157" s="9" t="n"/>
       <c r="M1157" s="10" t="inlineStr">
         <is>
-          <t>小中高共通の代表番号（法人サイトでも一致）</t>
+          <t>短大の番号（083-223-0339）とは別</t>
         </is>
       </c>
       <c r="N1157" s="11" t="inlineStr">
         <is>
-          <t>https://www.yamaguchi-shigaku.or.jp/tyukou/pdf/2025/20_hagikouen2025.pdf</t>
+          <t>https://www.shimotan-hs.jp/pages/13/</t>
         </is>
       </c>
       <c r="O1157" s="12" t="inlineStr">
@@ -68310,17 +68302,17 @@
       </c>
       <c r="C1158" s="5" t="inlineStr">
         <is>
-          <t>下関市</t>
+          <t>防府市</t>
         </is>
       </c>
       <c r="D1158" s="5" t="inlineStr">
         <is>
-          <t>早鞆高等学校</t>
+          <t>誠英高等学校</t>
         </is>
       </c>
       <c r="E1158" s="6" t="inlineStr">
         <is>
-          <t>083-231-0080</t>
+          <t>0835-38-5252</t>
         </is>
       </c>
       <c r="F1158" s="7" t="inlineStr">
@@ -68342,10 +68334,14 @@
       </c>
       <c r="K1158" s="8" t="n"/>
       <c r="L1158" s="9" t="n"/>
-      <c r="M1158" s="10" t="n"/>
+      <c r="M1158" s="10" t="inlineStr">
+        <is>
+          <t>通信制課程は0835-38-6161（第三者サイト）</t>
+        </is>
+      </c>
       <c r="N1158" s="11" t="inlineStr">
         <is>
-          <t>https://www.hayatomo.ac.jp/course/</t>
+          <t>https://seiei.ac.jp/</t>
         </is>
       </c>
       <c r="O1158" s="12" t="inlineStr">
@@ -68365,17 +68361,17 @@
       </c>
       <c r="C1159" s="5" t="inlineStr">
         <is>
-          <t>下関市</t>
+          <t>山口市</t>
         </is>
       </c>
       <c r="D1159" s="5" t="inlineStr">
         <is>
-          <t>梅光学院高等学校</t>
+          <t>精華学園高等学校</t>
         </is>
       </c>
       <c r="E1159" s="6" t="inlineStr">
         <is>
-          <t>083-227-1200</t>
+          <t>083-976-8833</t>
         </is>
       </c>
       <c r="F1159" s="7" t="inlineStr">
@@ -68385,7 +68381,7 @@
       </c>
       <c r="G1159" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1159" s="8" t="n"/>
@@ -68399,12 +68395,12 @@
       <c r="L1159" s="9" t="n"/>
       <c r="M1159" s="10" t="inlineStr">
         <is>
-          <t>法人本部は083-227-1000</t>
+          <t>広域通信制・山口本校</t>
         </is>
       </c>
       <c r="N1159" s="11" t="inlineStr">
         <is>
-          <t>https://www.baiko.ac.jp/highschool/</t>
+          <t>https://www.seikagakuen.ac.jp/archives/691</t>
         </is>
       </c>
       <c r="O1159" s="12" t="inlineStr">
@@ -68424,17 +68420,17 @@
       </c>
       <c r="C1160" s="5" t="inlineStr">
         <is>
-          <t>柳井市</t>
+          <t>光市</t>
         </is>
       </c>
       <c r="D1160" s="5" t="inlineStr">
         <is>
-          <t>柳井学園高等学校</t>
+          <t>聖光高等学校</t>
         </is>
       </c>
       <c r="E1160" s="6" t="inlineStr">
         <is>
-          <t>0820-22-0214</t>
+          <t>0833-72-1187</t>
         </is>
       </c>
       <c r="F1160" s="7" t="inlineStr">
@@ -68456,10 +68452,14 @@
       </c>
       <c r="K1160" s="8" t="n"/>
       <c r="L1160" s="9" t="n"/>
-      <c r="M1160" s="10" t="n"/>
+      <c r="M1160" s="10" t="inlineStr">
+        <is>
+          <t>通信制は0833-72-7070（第三者サイト）</t>
+        </is>
+      </c>
       <c r="N1160" s="11" t="inlineStr">
         <is>
-          <t>https://yanai-g.ed.jp/contact/</t>
+          <t>https://www.seiko-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1160" s="12" t="inlineStr">
@@ -68479,17 +68479,17 @@
       </c>
       <c r="C1161" s="5" t="inlineStr">
         <is>
-          <t>山口市</t>
+          <t>美祢市</t>
         </is>
       </c>
       <c r="D1161" s="5" t="inlineStr">
         <is>
-          <t>山口県鴻城高等学校</t>
+          <t>成進高等学校</t>
         </is>
       </c>
       <c r="E1161" s="6" t="inlineStr">
         <is>
-          <t>083-972-0307</t>
+          <t>0837-52-1350</t>
         </is>
       </c>
       <c r="F1161" s="7" t="inlineStr">
@@ -68511,14 +68511,10 @@
       </c>
       <c r="K1161" s="8" t="n"/>
       <c r="L1161" s="9" t="n"/>
-      <c r="M1161" s="10" t="inlineStr">
-        <is>
-          <t>衛生看護専攻科（宇部市）は別番号</t>
-        </is>
-      </c>
+      <c r="M1161" s="10" t="n"/>
       <c r="N1161" s="11" t="inlineStr">
         <is>
-          <t>https://www.y-kojohs.jp/access/</t>
+          <t>https://www.mine-c.ed.jp/profile</t>
         </is>
       </c>
       <c r="O1161" s="12" t="inlineStr">
@@ -68538,17 +68534,17 @@
       </c>
       <c r="C1162" s="5" t="inlineStr">
         <is>
-          <t>周南市</t>
+          <t>防府市</t>
         </is>
       </c>
       <c r="D1162" s="5" t="inlineStr">
         <is>
-          <t>山口県桜ケ丘高等学校</t>
+          <t>高川学園高等学校</t>
         </is>
       </c>
       <c r="E1162" s="6" t="inlineStr">
         <is>
-          <t>0834-21-0331</t>
+          <t>0835-33-0101</t>
         </is>
       </c>
       <c r="F1162" s="7" t="inlineStr">
@@ -68558,7 +68554,7 @@
       </c>
       <c r="G1162" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1162" s="8" t="n"/>
@@ -68570,25 +68566,595 @@
       </c>
       <c r="K1162" s="8" t="n"/>
       <c r="L1162" s="9" t="n"/>
-      <c r="M1162" s="10" t="inlineStr">
+      <c r="M1162" s="10" t="n"/>
+      <c r="N1162" s="11" t="inlineStr">
+        <is>
+          <t>https://takagawagakuen.com/high/</t>
+        </is>
+      </c>
+      <c r="O1162" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="4" t="n">
+        <v>1159</v>
+      </c>
+      <c r="B1163" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1163" s="5" t="inlineStr">
+        <is>
+          <t>岩国市</t>
+        </is>
+      </c>
+      <c r="D1163" s="5" t="inlineStr">
+        <is>
+          <t>高水高等学校</t>
+        </is>
+      </c>
+      <c r="E1163" s="6" t="inlineStr">
+        <is>
+          <t>0827-31-7191</t>
+        </is>
+      </c>
+      <c r="F1163" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1163" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1163" s="8" t="n"/>
+      <c r="I1163" s="9" t="n"/>
+      <c r="J1163" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1163" s="8" t="n"/>
+      <c r="L1163" s="9" t="n"/>
+      <c r="M1163" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1163" s="11" t="inlineStr">
+        <is>
+          <t>https://www.takamizu.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1163" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="B1164" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1164" s="5" t="inlineStr">
+        <is>
+          <t>山口市</t>
+        </is>
+      </c>
+      <c r="D1164" s="5" t="inlineStr">
+        <is>
+          <t>中村女子高等学校</t>
+        </is>
+      </c>
+      <c r="E1164" s="6" t="inlineStr">
+        <is>
+          <t>083-922-0418</t>
+        </is>
+      </c>
+      <c r="F1164" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1164" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1164" s="8" t="n"/>
+      <c r="I1164" s="9" t="n"/>
+      <c r="J1164" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1164" s="8" t="n"/>
+      <c r="L1164" s="9" t="n"/>
+      <c r="M1164" s="10" t="inlineStr">
+        <is>
+          <t>現校名は山口中村学園高等学校（2025年度から共学化）。専攻科は083-928-1331</t>
+        </is>
+      </c>
+      <c r="N1164" s="11" t="inlineStr">
+        <is>
+          <t>https://www.y-nakamura.jp/</t>
+        </is>
+      </c>
+      <c r="O1164" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="4" t="n">
+        <v>1161</v>
+      </c>
+      <c r="B1165" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1165" s="5" t="inlineStr">
+        <is>
+          <t>長門市</t>
+        </is>
+      </c>
+      <c r="D1165" s="5" t="inlineStr">
+        <is>
+          <t>長門高等学校</t>
+        </is>
+      </c>
+      <c r="E1165" s="6" t="inlineStr">
+        <is>
+          <t>0837-22-2944</t>
+        </is>
+      </c>
+      <c r="F1165" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1165" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1165" s="8" t="n"/>
+      <c r="I1165" s="9" t="n"/>
+      <c r="J1165" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1165" s="8" t="n"/>
+      <c r="L1165" s="9" t="n"/>
+      <c r="M1165" s="10" t="n"/>
+      <c r="N1165" s="11" t="inlineStr">
+        <is>
+          <t>https://nagato.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1165" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="4" t="n">
+        <v>1162</v>
+      </c>
+      <c r="B1166" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1166" s="5" t="inlineStr">
+        <is>
+          <t>山口市</t>
+        </is>
+      </c>
+      <c r="D1166" s="5" t="inlineStr">
+        <is>
+          <t>野田学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1166" s="6" t="inlineStr">
+        <is>
+          <t>083-922-5000</t>
+        </is>
+      </c>
+      <c r="F1166" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1166" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1166" s="8" t="n"/>
+      <c r="I1166" s="9" t="n"/>
+      <c r="J1166" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1166" s="8" t="n"/>
+      <c r="L1166" s="9" t="n"/>
+      <c r="M1166" s="10" t="n"/>
+      <c r="N1166" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nodagakuen.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1166" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="4" t="n">
+        <v>1163</v>
+      </c>
+      <c r="B1167" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1167" s="5" t="inlineStr">
+        <is>
+          <t>萩市</t>
+        </is>
+      </c>
+      <c r="D1167" s="5" t="inlineStr">
+        <is>
+          <t>萩光塩学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1167" s="6" t="inlineStr">
+        <is>
+          <t>0838-22-0782</t>
+        </is>
+      </c>
+      <c r="F1167" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1167" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1167" s="8" t="n"/>
+      <c r="I1167" s="9" t="n"/>
+      <c r="J1167" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1167" s="8" t="n"/>
+      <c r="L1167" s="9" t="n"/>
+      <c r="M1167" s="10" t="inlineStr">
+        <is>
+          <t>小中高共通の代表番号（法人サイトでも一致）</t>
+        </is>
+      </c>
+      <c r="N1167" s="11" t="inlineStr">
+        <is>
+          <t>https://www.yamaguchi-shigaku.or.jp/tyukou/pdf/2025/20_hagikouen2025.pdf</t>
+        </is>
+      </c>
+      <c r="O1167" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="4" t="n">
+        <v>1164</v>
+      </c>
+      <c r="B1168" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1168" s="5" t="inlineStr">
+        <is>
+          <t>下関市</t>
+        </is>
+      </c>
+      <c r="D1168" s="5" t="inlineStr">
+        <is>
+          <t>早鞆高等学校</t>
+        </is>
+      </c>
+      <c r="E1168" s="6" t="inlineStr">
+        <is>
+          <t>083-231-0080</t>
+        </is>
+      </c>
+      <c r="F1168" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1168" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1168" s="8" t="n"/>
+      <c r="I1168" s="9" t="n"/>
+      <c r="J1168" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1168" s="8" t="n"/>
+      <c r="L1168" s="9" t="n"/>
+      <c r="M1168" s="10" t="n"/>
+      <c r="N1168" s="11" t="inlineStr">
+        <is>
+          <t>https://www.hayatomo.ac.jp/course/</t>
+        </is>
+      </c>
+      <c r="O1168" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="4" t="n">
+        <v>1165</v>
+      </c>
+      <c r="B1169" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1169" s="5" t="inlineStr">
+        <is>
+          <t>下関市</t>
+        </is>
+      </c>
+      <c r="D1169" s="5" t="inlineStr">
+        <is>
+          <t>梅光学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1169" s="6" t="inlineStr">
+        <is>
+          <t>083-227-1200</t>
+        </is>
+      </c>
+      <c r="F1169" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1169" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1169" s="8" t="n"/>
+      <c r="I1169" s="9" t="n"/>
+      <c r="J1169" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1169" s="8" t="n"/>
+      <c r="L1169" s="9" t="n"/>
+      <c r="M1169" s="10" t="inlineStr">
+        <is>
+          <t>法人本部は083-227-1000</t>
+        </is>
+      </c>
+      <c r="N1169" s="11" t="inlineStr">
+        <is>
+          <t>https://www.baiko.ac.jp/highschool/</t>
+        </is>
+      </c>
+      <c r="O1169" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="4" t="n">
+        <v>1166</v>
+      </c>
+      <c r="B1170" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1170" s="5" t="inlineStr">
+        <is>
+          <t>柳井市</t>
+        </is>
+      </c>
+      <c r="D1170" s="5" t="inlineStr">
+        <is>
+          <t>柳井学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1170" s="6" t="inlineStr">
+        <is>
+          <t>0820-22-0214</t>
+        </is>
+      </c>
+      <c r="F1170" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1170" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1170" s="8" t="n"/>
+      <c r="I1170" s="9" t="n"/>
+      <c r="J1170" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1170" s="8" t="n"/>
+      <c r="L1170" s="9" t="n"/>
+      <c r="M1170" s="10" t="n"/>
+      <c r="N1170" s="11" t="inlineStr">
+        <is>
+          <t>https://yanai-g.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1170" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="4" t="n">
+        <v>1167</v>
+      </c>
+      <c r="B1171" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1171" s="5" t="inlineStr">
+        <is>
+          <t>山口市</t>
+        </is>
+      </c>
+      <c r="D1171" s="5" t="inlineStr">
+        <is>
+          <t>山口県鴻城高等学校</t>
+        </is>
+      </c>
+      <c r="E1171" s="6" t="inlineStr">
+        <is>
+          <t>083-972-0307</t>
+        </is>
+      </c>
+      <c r="F1171" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1171" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1171" s="8" t="n"/>
+      <c r="I1171" s="9" t="n"/>
+      <c r="J1171" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1171" s="8" t="n"/>
+      <c r="L1171" s="9" t="n"/>
+      <c r="M1171" s="10" t="inlineStr">
+        <is>
+          <t>衛生看護専攻科（宇部市）は別番号</t>
+        </is>
+      </c>
+      <c r="N1171" s="11" t="inlineStr">
+        <is>
+          <t>https://www.y-kojohs.jp/access/</t>
+        </is>
+      </c>
+      <c r="O1171" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="4" t="n">
+        <v>1168</v>
+      </c>
+      <c r="B1172" s="5" t="inlineStr">
+        <is>
+          <t>山口県</t>
+        </is>
+      </c>
+      <c r="C1172" s="5" t="inlineStr">
+        <is>
+          <t>周南市</t>
+        </is>
+      </c>
+      <c r="D1172" s="5" t="inlineStr">
+        <is>
+          <t>山口県桜ケ丘高等学校</t>
+        </is>
+      </c>
+      <c r="E1172" s="6" t="inlineStr">
+        <is>
+          <t>0834-21-0331</t>
+        </is>
+      </c>
+      <c r="F1172" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1172" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1172" s="8" t="n"/>
+      <c r="I1172" s="9" t="n"/>
+      <c r="J1172" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1172" s="8" t="n"/>
+      <c r="L1172" s="9" t="n"/>
+      <c r="M1172" s="10" t="inlineStr">
         <is>
           <t>晃英館コースは0834-33-3131</t>
         </is>
       </c>
-      <c r="N1162" s="11" t="inlineStr">
+      <c r="N1172" s="11" t="inlineStr">
         <is>
           <t>https://www.y-sakuragaoka.ed.jp/contact.html</t>
         </is>
       </c>
-      <c r="O1162" s="12" t="inlineStr">
+      <c r="O1172" s="12" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O1162"/>
-  <conditionalFormatting sqref="A5:O1162">
+  <autoFilter ref="A4:O1172"/>
+  <conditionalFormatting sqref="A5:O1172">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -68597,10 +69163,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J1162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J1172" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H1162 K5:K1162" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H1172 K5:K1172" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -69763,6 +70329,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1160" r:id="rId1156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1161" r:id="rId1157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1162" r:id="rId1158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1163" r:id="rId1159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1164" r:id="rId1160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1165" r:id="rId1161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1166" r:id="rId1162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1167" r:id="rId1163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1168" r:id="rId1164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1169" r:id="rId1165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1170" r:id="rId1166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1171" r:id="rId1167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1172" r:id="rId1168"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -69775,7 +70351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -69862,43 +70438,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A4,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A4,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1162,A4,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A4,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1172,A4,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A4,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A4,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69909,43 +70485,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A5,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A5,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1162,A5,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A5,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1172,A5,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A5,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A5,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -69956,43 +70532,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A6,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A6,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1162,A6,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A6,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1172,A6,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A6,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A6,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70003,43 +70579,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A7,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A7,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1162,A7,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A7,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1172,A7,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A7,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A7,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70050,43 +70626,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A8,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A8,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1162,A8,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A8,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1172,A8,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A8,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A8,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70097,43 +70673,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A9,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A9,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1162,A9,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A9,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1172,A9,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A9,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A9,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70144,43 +70720,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A10,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A10,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1162,A10,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A10,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1172,A10,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A10,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A10,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70191,43 +70767,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A11,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A11,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1162,A11,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A11,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1172,A11,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A11,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A11,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70238,43 +70814,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A12,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A12,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1162,A12,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A12,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1172,A12,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A12,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A12,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70285,43 +70861,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A13,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A13,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1162,A13,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A13,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1172,A13,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A13,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A13,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70332,43 +70908,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A14,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A14,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1162,A14,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A14,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1172,A14,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A14,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A14,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70379,43 +70955,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A15,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A15,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1162,A15,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A15,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1172,A15,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A15,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A15,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70426,43 +71002,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A16,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A16,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1162,A16,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A16,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1172,A16,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A16,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A16,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70473,43 +71049,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A17,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A17,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1162,A17,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A17,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1172,A17,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A17,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A17,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70520,43 +71096,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A18,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A18,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1162,A18,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A18,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1172,A18,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A18,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A18,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70567,43 +71143,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A19,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A19,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1162,A19,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A19,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1172,A19,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A19,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A19,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70614,43 +71190,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A20,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A20,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1162,A20,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A20,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1172,A20,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A20,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A20,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70661,43 +71237,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A21,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A21,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1162,A21,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A21,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1172,A21,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A21,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A21,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70708,43 +71284,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A22,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A22,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1162,A22,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A22,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1172,A22,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A22,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A22,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70755,43 +71331,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A23,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A23,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1162,A23,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A23,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1172,A23,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A23,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A23,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70802,43 +71378,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A24,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A24,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1162,A24,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A24,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1172,A24,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A24,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A24,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70849,43 +71425,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A25,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A25,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1162,A25,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A25,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1172,A25,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A25,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A25,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70896,43 +71472,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A26,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A26,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1162,A26,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A26,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1172,A26,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A26,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A26,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70943,43 +71519,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A27,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A27,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1162,A27,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A27,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1172,A27,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A27,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A27,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70990,43 +71566,43 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A28,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A28,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1162,A28,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A28,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1172,A28,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A28,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A28,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71037,43 +71613,43 @@
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A29)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A29,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A29,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1162,A29,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A29,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1172,A29,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A29,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A29,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71084,43 +71660,43 @@
         </is>
       </c>
       <c r="B30" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A30)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A30)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A30,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A30,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1162,A30,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A30,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1172,A30,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A30,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A30,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71131,43 +71707,43 @@
         </is>
       </c>
       <c r="B31" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A31)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A31)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A31,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A31,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1162,A31,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A31,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1172,A31,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A31,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A31,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71178,43 +71754,43 @@
         </is>
       </c>
       <c r="B32" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A32)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A32)</f>
         <v/>
       </c>
       <c r="C32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A32,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A32,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1162,A32,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A32,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1172,A32,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A32,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A32,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71225,43 +71801,43 @@
         </is>
       </c>
       <c r="B33" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A33)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A33)</f>
         <v/>
       </c>
       <c r="C33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A33,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A33,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D33" s="16">
-        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1162,A33,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A33,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1172,A33,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A33,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A33,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71272,231 +71848,278 @@
         </is>
       </c>
       <c r="B34" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A34)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A34)</f>
         <v/>
       </c>
       <c r="C34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A34,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A34,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1162,A34,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A34,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1172,A34,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A34,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A34,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>岡山県</t>
+          <t>島根県</t>
         </is>
       </c>
       <c r="B35" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A35)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A35)</f>
         <v/>
       </c>
       <c r="C35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A35,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A35,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D35" s="16">
-        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1162,A35,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A35,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1172,A35,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A35,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A35,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>広島県</t>
+          <t>岡山県</t>
         </is>
       </c>
       <c r="B36" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A36)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A36)</f>
         <v/>
       </c>
       <c r="C36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A36,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A36,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D36" s="16">
-        <f>B36-COUNTIFS('架電リスト'!$B$5:$B$1162,A36,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A36,'架電リスト'!$J$5:$J$1162,"")</f>
+        <f>B36-COUNTIFS('架電リスト'!$B$5:$B$1172,A36,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A36,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
       <c r="E36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
       <c r="G36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
       <c r="J36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A36,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
+          <t>広島県</t>
+        </is>
+      </c>
+      <c r="B37" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A37)</f>
+        <v/>
+      </c>
+      <c r="C37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A37,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D37" s="16">
+        <f>B37-COUNTIFS('架電リスト'!$B$5:$B$1172,A37,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A37,'架電リスト'!$J$5:$J$1172,"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <v/>
+      </c>
+      <c r="K37" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
           <t>山口県</t>
         </is>
       </c>
-      <c r="B37" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1162,A37)</f>
+      <c r="B38" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A38)</f>
         <v/>
       </c>
-      <c r="C37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,A37,'架電リスト'!$E$5:$E$1162,"&lt;&gt;")</f>
+      <c r="C38" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A38,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="D37" s="16">
-        <f>B37-COUNTIFS('架電リスト'!$B$5:$B$1162,A37,'架電リスト'!$J$5:$J$1162,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1162,A37,'架電リスト'!$J$5:$J$1162,"")</f>
+      <c r="D38" s="16">
+        <f>B38-COUNTIFS('架電リスト'!$B$5:$B$1172,A38,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A38,'架電リスト'!$J$5:$J$1172,"")</f>
         <v/>
       </c>
-      <c r="E37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"不在・折返し待ち")</f>
+      <c r="E38" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"担当者不在")</f>
+      <c r="F38" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"資料送付")</f>
+      <c r="G38" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
         <v/>
       </c>
-      <c r="H37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"アポ獲得")</f>
+      <c r="H38" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
         <v/>
       </c>
-      <c r="I37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"検討中")</f>
+      <c r="I38" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"検討中")</f>
         <v/>
       </c>
-      <c r="J37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"NG")</f>
+      <c r="J38" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"NG")</f>
         <v/>
       </c>
-      <c r="K37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1162,$A37,'架電リスト'!$J$5:$J$1162,"番号不明")</f>
+      <c r="K38" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B38" s="17">
-        <f>SUM(B4:B37)</f>
+      <c r="B39" s="17">
+        <f>SUM(B4:B38)</f>
         <v/>
       </c>
-      <c r="C38" s="17">
-        <f>SUM(C4:C37)</f>
+      <c r="C39" s="17">
+        <f>SUM(C4:C38)</f>
         <v/>
       </c>
-      <c r="D38" s="17">
-        <f>SUM(D4:D37)</f>
+      <c r="D39" s="17">
+        <f>SUM(D4:D38)</f>
         <v/>
       </c>
-      <c r="E38" s="17">
-        <f>SUM(E4:E37)</f>
+      <c r="E39" s="17">
+        <f>SUM(E4:E38)</f>
         <v/>
       </c>
-      <c r="F38" s="17">
-        <f>SUM(F4:F37)</f>
+      <c r="F39" s="17">
+        <f>SUM(F4:F38)</f>
         <v/>
       </c>
-      <c r="G38" s="17">
-        <f>SUM(G4:G37)</f>
+      <c r="G39" s="17">
+        <f>SUM(G4:G38)</f>
         <v/>
       </c>
-      <c r="H38" s="17">
-        <f>SUM(H4:H37)</f>
+      <c r="H39" s="17">
+        <f>SUM(H4:H38)</f>
         <v/>
       </c>
-      <c r="I38" s="17">
-        <f>SUM(I4:I37)</f>
+      <c r="I39" s="17">
+        <f>SUM(I4:I38)</f>
         <v/>
       </c>
-      <c r="J38" s="17">
-        <f>SUM(J4:J37)</f>
+      <c r="J39" s="17">
+        <f>SUM(J4:J38)</f>
         <v/>
       </c>
-      <c r="K38" s="17">
-        <f>SUM(K4:K37)</f>
+      <c r="K39" s="17">
+        <f>SUM(K4:K38)</f>
         <v/>
       </c>
     </row>
@@ -71586,7 +72209,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・34都道府県、1158校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・35都道府県、1168校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1182</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O1172"/>
+  <dimension ref="A1:O1182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（35都道府県／1168校）</t>
+          <t>私立高等学校 架電リスト（36都道府県／1178校）</t>
         </is>
       </c>
     </row>
@@ -69152,9 +69152,587 @@
         </is>
       </c>
     </row>
+    <row r="1173">
+      <c r="A1173" s="4" t="n">
+        <v>1169</v>
+      </c>
+      <c r="B1173" s="5" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="C1173" s="5" t="inlineStr">
+        <is>
+          <t>高松市</t>
+        </is>
+      </c>
+      <c r="D1173" s="5" t="inlineStr">
+        <is>
+          <t>英明高等学校</t>
+        </is>
+      </c>
+      <c r="E1173" s="6" t="inlineStr">
+        <is>
+          <t>087-833-3737</t>
+        </is>
+      </c>
+      <c r="F1173" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G1173" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1173" s="8" t="n"/>
+      <c r="I1173" s="9" t="n"/>
+      <c r="J1173" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1173" s="8" t="n"/>
+      <c r="L1173" s="9" t="n"/>
+      <c r="M1173" s="10" t="inlineStr">
+        <is>
+          <t>公式未確認。香川県私立中高連合会・複数サイトで一致。通信制課程も同じ番号</t>
+        </is>
+      </c>
+      <c r="N1173" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kagawa-shigaku.jp/eimei</t>
+        </is>
+      </c>
+      <c r="O1173" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="4" t="n">
+        <v>1170</v>
+      </c>
+      <c r="B1174" s="5" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="C1174" s="5" t="inlineStr">
+        <is>
+          <t>高松市</t>
+        </is>
+      </c>
+      <c r="D1174" s="5" t="inlineStr">
+        <is>
+          <t>大手前高松高等学校</t>
+        </is>
+      </c>
+      <c r="E1174" s="6" t="inlineStr">
+        <is>
+          <t>087-867-5970</t>
+        </is>
+      </c>
+      <c r="F1174" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1174" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1174" s="8" t="n"/>
+      <c r="I1174" s="9" t="n"/>
+      <c r="J1174" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1174" s="8" t="n"/>
+      <c r="L1174" s="9" t="n"/>
+      <c r="M1174" s="10" t="n"/>
+      <c r="N1174" s="11" t="inlineStr">
+        <is>
+          <t>https://www.otemae.net/contact/</t>
+        </is>
+      </c>
+      <c r="O1174" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="4" t="n">
+        <v>1171</v>
+      </c>
+      <c r="B1175" s="5" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="C1175" s="5" t="inlineStr">
+        <is>
+          <t>丸亀市</t>
+        </is>
+      </c>
+      <c r="D1175" s="5" t="inlineStr">
+        <is>
+          <t>大手前丸亀高等学校</t>
+        </is>
+      </c>
+      <c r="E1175" s="6" t="inlineStr">
+        <is>
+          <t>0877-23-3161</t>
+        </is>
+      </c>
+      <c r="F1175" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1175" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1175" s="8" t="n"/>
+      <c r="I1175" s="9" t="n"/>
+      <c r="J1175" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1175" s="8" t="n"/>
+      <c r="L1175" s="9" t="n"/>
+      <c r="M1175" s="10" t="n"/>
+      <c r="N1175" s="11" t="inlineStr">
+        <is>
+          <t>https://www.otemae.ed.jp/contact_form/otoiawase.html</t>
+        </is>
+      </c>
+      <c r="O1175" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="4" t="n">
+        <v>1172</v>
+      </c>
+      <c r="B1176" s="5" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="C1176" s="5" t="inlineStr">
+        <is>
+          <t>丸亀市</t>
+        </is>
+      </c>
+      <c r="D1176" s="5" t="inlineStr">
+        <is>
+          <t>香川県藤井高等学校</t>
+        </is>
+      </c>
+      <c r="E1176" s="6" t="inlineStr">
+        <is>
+          <t>0877-22-2328</t>
+        </is>
+      </c>
+      <c r="F1176" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1176" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1176" s="8" t="n"/>
+      <c r="I1176" s="9" t="n"/>
+      <c r="J1176" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1176" s="8" t="n"/>
+      <c r="L1176" s="9" t="n"/>
+      <c r="M1176" s="10" t="inlineStr">
+        <is>
+          <t>2026年度から「蓬莱高等学校」に校名変更（法人も蓬莱学園に改称）</t>
+        </is>
+      </c>
+      <c r="N1176" s="11" t="inlineStr">
+        <is>
+          <t>https://www.fujii.ed.jp/fujii/</t>
+        </is>
+      </c>
+      <c r="O1176" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="4" t="n">
+        <v>1173</v>
+      </c>
+      <c r="B1177" s="5" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="C1177" s="5" t="inlineStr">
+        <is>
+          <t>高松市</t>
+        </is>
+      </c>
+      <c r="D1177" s="5" t="inlineStr">
+        <is>
+          <t>香川誠陵高等学校</t>
+        </is>
+      </c>
+      <c r="E1177" s="6" t="inlineStr">
+        <is>
+          <t>087-881-7800</t>
+        </is>
+      </c>
+      <c r="F1177" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1177" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1177" s="8" t="n"/>
+      <c r="I1177" s="9" t="n"/>
+      <c r="J1177" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1177" s="8" t="n"/>
+      <c r="L1177" s="9" t="n"/>
+      <c r="M1177" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1177" s="11" t="inlineStr">
+        <is>
+          <t>https://k-seiryo.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1177" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="4" t="n">
+        <v>1174</v>
+      </c>
+      <c r="B1178" s="5" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="C1178" s="5" t="inlineStr">
+        <is>
+          <t>坂出市</t>
+        </is>
+      </c>
+      <c r="D1178" s="5" t="inlineStr">
+        <is>
+          <t>坂出第一高等学校</t>
+        </is>
+      </c>
+      <c r="E1178" s="6" t="inlineStr">
+        <is>
+          <t>0877-46-2157</t>
+        </is>
+      </c>
+      <c r="F1178" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1178" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1178" s="8" t="n"/>
+      <c r="I1178" s="9" t="n"/>
+      <c r="J1178" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1178" s="8" t="n"/>
+      <c r="L1178" s="9" t="n"/>
+      <c r="M1178" s="10" t="n"/>
+      <c r="N1178" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sakaide1-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1178" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="4" t="n">
+        <v>1175</v>
+      </c>
+      <c r="B1179" s="5" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="C1179" s="5" t="inlineStr">
+        <is>
+          <t>三豊市</t>
+        </is>
+      </c>
+      <c r="D1179" s="5" t="inlineStr">
+        <is>
+          <t>四国学院大学香川西高等学校</t>
+        </is>
+      </c>
+      <c r="E1179" s="6" t="inlineStr">
+        <is>
+          <t>0875-72-5193</t>
+        </is>
+      </c>
+      <c r="F1179" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1179" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1179" s="8" t="n"/>
+      <c r="I1179" s="9" t="n"/>
+      <c r="J1179" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1179" s="8" t="n"/>
+      <c r="L1179" s="9" t="n"/>
+      <c r="M1179" s="10" t="inlineStr">
+        <is>
+          <t>三豊市HPとも一致</t>
+        </is>
+      </c>
+      <c r="N1179" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kagawanishikou.com/contact</t>
+        </is>
+      </c>
+      <c r="O1179" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="4" t="n">
+        <v>1176</v>
+      </c>
+      <c r="B1180" s="5" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="C1180" s="5" t="inlineStr">
+        <is>
+          <t>善通寺市</t>
+        </is>
+      </c>
+      <c r="D1180" s="5" t="inlineStr">
+        <is>
+          <t>尽誠学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1180" s="6" t="inlineStr">
+        <is>
+          <t>0877-62-1515</t>
+        </is>
+      </c>
+      <c r="F1180" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1180" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1180" s="8" t="n"/>
+      <c r="I1180" s="9" t="n"/>
+      <c r="J1180" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1180" s="8" t="n"/>
+      <c r="L1180" s="9" t="n"/>
+      <c r="M1180" s="10" t="inlineStr">
+        <is>
+          <t>県私立中高連合会とも一致。法人本部は0877-63-1717</t>
+        </is>
+      </c>
+      <c r="N1180" s="11" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/jinsei.ac.jp/jinseiopenschool2020</t>
+        </is>
+      </c>
+      <c r="O1180" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="4" t="n">
+        <v>1177</v>
+      </c>
+      <c r="B1181" s="5" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="C1181" s="5" t="inlineStr">
+        <is>
+          <t>高松市</t>
+        </is>
+      </c>
+      <c r="D1181" s="5" t="inlineStr">
+        <is>
+          <t>高松中央高等学校</t>
+        </is>
+      </c>
+      <c r="E1181" s="6" t="inlineStr">
+        <is>
+          <t>087-831-1291</t>
+        </is>
+      </c>
+      <c r="F1181" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1181" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1181" s="8" t="n"/>
+      <c r="I1181" s="9" t="n"/>
+      <c r="J1181" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1181" s="8" t="n"/>
+      <c r="L1181" s="9" t="n"/>
+      <c r="M1181" s="10" t="inlineStr">
+        <is>
+          <t>全日制の番号。通信制課程は087-812-5285</t>
+        </is>
+      </c>
+      <c r="N1181" s="11" t="inlineStr">
+        <is>
+          <t>https://www.ta-chuo.ed.jp/contact/</t>
+        </is>
+      </c>
+      <c r="O1181" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="4" t="n">
+        <v>1178</v>
+      </c>
+      <c r="B1182" s="5" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="C1182" s="5" t="inlineStr">
+        <is>
+          <t>さぬき市</t>
+        </is>
+      </c>
+      <c r="D1182" s="5" t="inlineStr">
+        <is>
+          <t>藤井学園寒川高等学校</t>
+        </is>
+      </c>
+      <c r="E1182" s="6" t="inlineStr">
+        <is>
+          <t>0879-43-2571</t>
+        </is>
+      </c>
+      <c r="F1182" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1182" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1182" s="8" t="n"/>
+      <c r="I1182" s="9" t="n"/>
+      <c r="J1182" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1182" s="8" t="n"/>
+      <c r="L1182" s="9" t="n"/>
+      <c r="M1182" s="10" t="inlineStr">
+        <is>
+          <t>法人名は2026年に蓬莱学園へ改称</t>
+        </is>
+      </c>
+      <c r="N1182" s="11" t="inlineStr">
+        <is>
+          <t>https://www.sangawa.ed.jp/wp/contact/</t>
+        </is>
+      </c>
+      <c r="O1182" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O1172"/>
-  <conditionalFormatting sqref="A5:O1172">
+  <autoFilter ref="A4:O1182"/>
+  <conditionalFormatting sqref="A5:O1182">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -69163,10 +69741,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J1172" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J1182" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H1172 K5:K1172" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H1182 K5:K1182" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -70339,6 +70917,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1170" r:id="rId1166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1171" r:id="rId1167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1172" r:id="rId1168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1173" r:id="rId1169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1174" r:id="rId1170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1175" r:id="rId1171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1176" r:id="rId1172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1177" r:id="rId1173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1178" r:id="rId1174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1179" r:id="rId1175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1180" r:id="rId1176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1181" r:id="rId1177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1182" r:id="rId1178"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -70351,7 +70939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -70438,43 +71026,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A4,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A4,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1172,A4,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A4,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1182,A4,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A4,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A4,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70485,43 +71073,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A5,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A5,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1172,A5,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A5,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1182,A5,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A5,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A5,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70532,43 +71120,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A6,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A6,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1172,A6,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A6,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1182,A6,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A6,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A6,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70579,43 +71167,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A7,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A7,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1172,A7,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A7,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1182,A7,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A7,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A7,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70626,43 +71214,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A8,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A8,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1172,A8,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A8,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1182,A8,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A8,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A8,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70673,43 +71261,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A9,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A9,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1172,A9,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A9,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1182,A9,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A9,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A9,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70720,43 +71308,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A10,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A10,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1172,A10,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A10,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1182,A10,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A10,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A10,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70767,43 +71355,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A11,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A11,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1172,A11,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A11,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1182,A11,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A11,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A11,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70814,43 +71402,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A12,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A12,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1172,A12,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A12,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1182,A12,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A12,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A12,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70861,43 +71449,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A13,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A13,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1172,A13,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A13,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1182,A13,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A13,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A13,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70908,43 +71496,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A14,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A14,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1172,A14,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A14,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1182,A14,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A14,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A14,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -70955,43 +71543,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A15,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A15,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1172,A15,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A15,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1182,A15,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A15,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A15,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71002,43 +71590,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A16,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A16,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1172,A16,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A16,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1182,A16,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A16,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A16,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71049,43 +71637,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A17,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A17,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1172,A17,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A17,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1182,A17,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A17,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A17,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71096,43 +71684,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A18,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A18,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1172,A18,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A18,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1182,A18,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A18,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A18,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71143,43 +71731,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A19,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A19,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1172,A19,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A19,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1182,A19,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A19,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A19,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71190,43 +71778,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A20,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A20,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1172,A20,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A20,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1182,A20,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A20,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A20,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71237,43 +71825,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A21,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A21,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1172,A21,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A21,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1182,A21,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A21,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A21,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71284,43 +71872,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A22,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A22,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1172,A22,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A22,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1182,A22,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A22,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A22,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71331,43 +71919,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A23,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A23,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1172,A23,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A23,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1182,A23,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A23,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A23,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71378,43 +71966,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A24,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A24,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1172,A24,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A24,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1182,A24,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A24,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A24,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71425,43 +72013,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A25,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A25,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1172,A25,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A25,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1182,A25,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A25,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A25,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71472,43 +72060,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A26,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A26,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1172,A26,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A26,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1182,A26,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A26,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A26,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71519,43 +72107,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A27,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A27,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1172,A27,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A27,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1182,A27,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A27,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A27,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71566,43 +72154,43 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A28,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A28,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1172,A28,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A28,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1182,A28,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A28,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A28,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71613,43 +72201,43 @@
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A29)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A29,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A29,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1172,A29,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A29,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1182,A29,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A29,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A29,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71660,43 +72248,43 @@
         </is>
       </c>
       <c r="B30" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A30)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A30)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A30,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A30,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1172,A30,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A30,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1182,A30,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A30,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A30,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71707,43 +72295,43 @@
         </is>
       </c>
       <c r="B31" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A31)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A31)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A31,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A31,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1172,A31,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A31,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1182,A31,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A31,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A31,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71754,43 +72342,43 @@
         </is>
       </c>
       <c r="B32" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A32)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A32)</f>
         <v/>
       </c>
       <c r="C32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A32,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A32,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1172,A32,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A32,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1182,A32,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A32,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A32,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71801,43 +72389,43 @@
         </is>
       </c>
       <c r="B33" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A33)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A33)</f>
         <v/>
       </c>
       <c r="C33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A33,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A33,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D33" s="16">
-        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1172,A33,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A33,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1182,A33,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A33,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A33,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71848,43 +72436,43 @@
         </is>
       </c>
       <c r="B34" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A34)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A34)</f>
         <v/>
       </c>
       <c r="C34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A34,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A34,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1172,A34,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A34,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1182,A34,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A34,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A34,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71895,43 +72483,43 @@
         </is>
       </c>
       <c r="B35" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A35)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A35)</f>
         <v/>
       </c>
       <c r="C35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A35,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A35,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D35" s="16">
-        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1172,A35,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A35,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1182,A35,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A35,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A35,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71942,43 +72530,43 @@
         </is>
       </c>
       <c r="B36" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A36)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A36)</f>
         <v/>
       </c>
       <c r="C36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A36,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A36,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D36" s="16">
-        <f>B36-COUNTIFS('架電リスト'!$B$5:$B$1172,A36,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A36,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B36-COUNTIFS('架電リスト'!$B$5:$B$1182,A36,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A36,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A36,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71989,43 +72577,43 @@
         </is>
       </c>
       <c r="B37" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A37)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A37)</f>
         <v/>
       </c>
       <c r="C37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A37,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A37,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D37" s="16">
-        <f>B37-COUNTIFS('架電リスト'!$B$5:$B$1172,A37,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A37,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B37-COUNTIFS('架電リスト'!$B$5:$B$1182,A37,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A37,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A37,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72036,90 +72624,137 @@
         </is>
       </c>
       <c r="B38" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1172,A38)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A38)</f>
         <v/>
       </c>
       <c r="C38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,A38,'架電リスト'!$E$5:$E$1172,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A38,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D38" s="16">
-        <f>B38-COUNTIFS('架電リスト'!$B$5:$B$1172,A38,'架電リスト'!$J$5:$J$1172,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1172,A38,'架電リスト'!$J$5:$J$1172,"")</f>
+        <f>B38-COUNTIFS('架電リスト'!$B$5:$B$1182,A38,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A38,'架電リスト'!$J$5:$J$1182,"")</f>
         <v/>
       </c>
       <c r="E38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
         <v/>
       </c>
       <c r="G38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"検討中")</f>
         <v/>
       </c>
       <c r="J38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"NG")</f>
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1172,$A38,'架電リスト'!$J$5:$J$1172,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>香川県</t>
+        </is>
+      </c>
+      <c r="B39" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A39)</f>
+        <v/>
+      </c>
+      <c r="C39" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A39,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D39" s="16">
+        <f>B39-COUNTIFS('架電リスト'!$B$5:$B$1182,A39,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A39,'架電リスト'!$J$5:$J$1182,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F39" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G39" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H39" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I39" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J39" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <v/>
+      </c>
+      <c r="K39" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B39" s="17">
-        <f>SUM(B4:B38)</f>
+      <c r="B40" s="17">
+        <f>SUM(B4:B39)</f>
         <v/>
       </c>
-      <c r="C39" s="17">
-        <f>SUM(C4:C38)</f>
+      <c r="C40" s="17">
+        <f>SUM(C4:C39)</f>
         <v/>
       </c>
-      <c r="D39" s="17">
-        <f>SUM(D4:D38)</f>
+      <c r="D40" s="17">
+        <f>SUM(D4:D39)</f>
         <v/>
       </c>
-      <c r="E39" s="17">
-        <f>SUM(E4:E38)</f>
+      <c r="E40" s="17">
+        <f>SUM(E4:E39)</f>
         <v/>
       </c>
-      <c r="F39" s="17">
-        <f>SUM(F4:F38)</f>
+      <c r="F40" s="17">
+        <f>SUM(F4:F39)</f>
         <v/>
       </c>
-      <c r="G39" s="17">
-        <f>SUM(G4:G38)</f>
+      <c r="G40" s="17">
+        <f>SUM(G4:G39)</f>
         <v/>
       </c>
-      <c r="H39" s="17">
-        <f>SUM(H4:H38)</f>
+      <c r="H40" s="17">
+        <f>SUM(H4:H39)</f>
         <v/>
       </c>
-      <c r="I39" s="17">
-        <f>SUM(I4:I38)</f>
+      <c r="I40" s="17">
+        <f>SUM(I4:I39)</f>
         <v/>
       </c>
-      <c r="J39" s="17">
-        <f>SUM(J4:J38)</f>
+      <c r="J40" s="17">
+        <f>SUM(J4:J39)</f>
         <v/>
       </c>
-      <c r="K39" s="17">
-        <f>SUM(K4:K38)</f>
+      <c r="K40" s="17">
+        <f>SUM(K4:K39)</f>
         <v/>
       </c>
     </row>
@@ -72209,7 +72844,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・35都道府県、1168校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・36都道府県、1178校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1196</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O1182"/>
+  <dimension ref="A1:O1196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（36都道府県／1178校）</t>
+          <t>私立高等学校 架電リスト（37都道府県／1192校）</t>
         </is>
       </c>
     </row>
@@ -69730,9 +69730,819 @@
         </is>
       </c>
     </row>
+    <row r="1183">
+      <c r="A1183" s="4" t="n">
+        <v>1179</v>
+      </c>
+      <c r="B1183" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1183" s="5" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D1183" s="5" t="inlineStr">
+        <is>
+          <t>愛光高等学校</t>
+        </is>
+      </c>
+      <c r="E1183" s="6" t="inlineStr">
+        <is>
+          <t>089-922-8980</t>
+        </is>
+      </c>
+      <c r="F1183" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1183" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1183" s="8" t="n"/>
+      <c r="I1183" s="9" t="n"/>
+      <c r="J1183" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1183" s="8" t="n"/>
+      <c r="L1183" s="9" t="n"/>
+      <c r="M1183" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1183" s="11" t="inlineStr">
+        <is>
+          <t>https://www.aiko.ed.jp/outline/shisetu.html</t>
+        </is>
+      </c>
+      <c r="O1183" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="4" t="n">
+        <v>1180</v>
+      </c>
+      <c r="B1184" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1184" s="5" t="inlineStr">
+        <is>
+          <t>今治市</t>
+        </is>
+      </c>
+      <c r="D1184" s="5" t="inlineStr">
+        <is>
+          <t>今治精華高等学校</t>
+        </is>
+      </c>
+      <c r="E1184" s="6" t="inlineStr">
+        <is>
+          <t>0898-32-7100</t>
+        </is>
+      </c>
+      <c r="F1184" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1184" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1184" s="8" t="n"/>
+      <c r="I1184" s="9" t="n"/>
+      <c r="J1184" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1184" s="8" t="n"/>
+      <c r="L1184" s="9" t="n"/>
+      <c r="M1184" s="10" t="inlineStr">
+        <is>
+          <t>一部サイトに0898-32-7260の記載あり（旧情報の可能性）</t>
+        </is>
+      </c>
+      <c r="N1184" s="11" t="inlineStr">
+        <is>
+          <t>https://highschool.imabariseika.ac.jp/summary/about/</t>
+        </is>
+      </c>
+      <c r="O1184" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="4" t="n">
+        <v>1181</v>
+      </c>
+      <c r="B1185" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1185" s="5" t="inlineStr">
+        <is>
+          <t>今治市</t>
+        </is>
+      </c>
+      <c r="D1185" s="5" t="inlineStr">
+        <is>
+          <t>FC今治高等学校 里山校</t>
+        </is>
+      </c>
+      <c r="E1185" s="6" t="inlineStr">
+        <is>
+          <t>0898-22-1230</t>
+        </is>
+      </c>
+      <c r="F1185" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G1185" s="5" t="inlineStr"/>
+      <c r="H1185" s="8" t="n"/>
+      <c r="I1185" s="9" t="n"/>
+      <c r="J1185" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1185" s="8" t="n"/>
+      <c r="L1185" s="9" t="n"/>
+      <c r="M1185" s="10" t="inlineStr">
+        <is>
+          <t>公式未確認。複数サイト・公式Facebookで一致。2024年に今治明徳高校矢田分校から改称</t>
+        </is>
+      </c>
+      <c r="N1185" s="11" t="inlineStr">
+        <is>
+          <t>https://www.gakkou.net/kou/view/index_306788.html</t>
+        </is>
+      </c>
+      <c r="O1185" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="4" t="n">
+        <v>1182</v>
+      </c>
+      <c r="B1186" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1186" s="5" t="inlineStr">
+        <is>
+          <t>今治市</t>
+        </is>
+      </c>
+      <c r="D1186" s="5" t="inlineStr">
+        <is>
+          <t>FC今治高等学校 明徳校</t>
+        </is>
+      </c>
+      <c r="E1186" s="6" t="inlineStr">
+        <is>
+          <t>0898-22-6767</t>
+        </is>
+      </c>
+      <c r="F1186" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1186" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1186" s="8" t="n"/>
+      <c r="I1186" s="9" t="n"/>
+      <c r="J1186" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1186" s="8" t="n"/>
+      <c r="L1186" s="9" t="n"/>
+      <c r="M1186" s="10" t="inlineStr">
+        <is>
+          <t>旧・今治明徳高校本校（2024年改称）</t>
+        </is>
+      </c>
+      <c r="N1186" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meitokuhonko.com/</t>
+        </is>
+      </c>
+      <c r="O1186" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="4" t="n">
+        <v>1183</v>
+      </c>
+      <c r="B1187" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1187" s="5" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D1187" s="5" t="inlineStr">
+        <is>
+          <t>済美高等学校（愛媛県）</t>
+        </is>
+      </c>
+      <c r="E1187" s="6" t="inlineStr">
+        <is>
+          <t>089-943-4185</t>
+        </is>
+      </c>
+      <c r="F1187" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1187" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1187" s="8" t="n"/>
+      <c r="I1187" s="9" t="n"/>
+      <c r="J1187" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1187" s="8" t="n"/>
+      <c r="L1187" s="9" t="n"/>
+      <c r="M1187" s="10" t="inlineStr">
+        <is>
+          <t>電話受付は平日7:30-16:55、土曜7:30-13:00</t>
+        </is>
+      </c>
+      <c r="N1187" s="11" t="inlineStr">
+        <is>
+          <t>https://www.saibi.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1187" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="4" t="n">
+        <v>1184</v>
+      </c>
+      <c r="B1188" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1188" s="5" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D1188" s="5" t="inlineStr">
+        <is>
+          <t>聖カタリナ学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1188" s="6" t="inlineStr">
+        <is>
+          <t>089-933-3291</t>
+        </is>
+      </c>
+      <c r="F1188" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1188" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科・総合学科</t>
+        </is>
+      </c>
+      <c r="H1188" s="8" t="n"/>
+      <c r="I1188" s="9" t="n"/>
+      <c r="J1188" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1188" s="8" t="n"/>
+      <c r="L1188" s="9" t="n"/>
+      <c r="M1188" s="10" t="n"/>
+      <c r="N1188" s="11" t="inlineStr">
+        <is>
+          <t>https://catalina.ed.jp/about/outline/</t>
+        </is>
+      </c>
+      <c r="O1188" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="4" t="n">
+        <v>1185</v>
+      </c>
+      <c r="B1189" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1189" s="5" t="inlineStr">
+        <is>
+          <t>大洲市</t>
+        </is>
+      </c>
+      <c r="D1189" s="5" t="inlineStr">
+        <is>
+          <t>帝京第五高等学校</t>
+        </is>
+      </c>
+      <c r="E1189" s="6" t="inlineStr">
+        <is>
+          <t>0893-25-0511</t>
+        </is>
+      </c>
+      <c r="F1189" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1189" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科・総合学科</t>
+        </is>
+      </c>
+      <c r="H1189" s="8" t="n"/>
+      <c r="I1189" s="9" t="n"/>
+      <c r="J1189" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1189" s="8" t="n"/>
+      <c r="L1189" s="9" t="n"/>
+      <c r="M1189" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。職員室0893-25-0566、通信制0893-57-6850</t>
+        </is>
+      </c>
+      <c r="N1189" s="11" t="inlineStr">
+        <is>
+          <t>https://teikyo5-h.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1189" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="4" t="n">
+        <v>1186</v>
+      </c>
+      <c r="B1190" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1190" s="5" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D1190" s="5" t="inlineStr">
+        <is>
+          <t>新田高等学校</t>
+        </is>
+      </c>
+      <c r="E1190" s="6" t="inlineStr">
+        <is>
+          <t>089-951-0188</t>
+        </is>
+      </c>
+      <c r="F1190" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1190" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1190" s="8" t="n"/>
+      <c r="I1190" s="9" t="n"/>
+      <c r="J1190" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1190" s="8" t="n"/>
+      <c r="L1190" s="9" t="n"/>
+      <c r="M1190" s="10" t="n"/>
+      <c r="N1190" s="11" t="inlineStr">
+        <is>
+          <t>https://www.nitta.ac.jp/information/about/</t>
+        </is>
+      </c>
+      <c r="O1190" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="4" t="n">
+        <v>1187</v>
+      </c>
+      <c r="B1191" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1191" s="5" t="inlineStr">
+        <is>
+          <t>今治市</t>
+        </is>
+      </c>
+      <c r="D1191" s="5" t="inlineStr">
+        <is>
+          <t>日本ウェルネス高等学校</t>
+        </is>
+      </c>
+      <c r="E1191" s="6" t="inlineStr">
+        <is>
+          <t>0897-74-1356</t>
+        </is>
+      </c>
+      <c r="F1191" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1191" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1191" s="8" t="n"/>
+      <c r="I1191" s="9" t="n"/>
+      <c r="J1191" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1191" s="8" t="n"/>
+      <c r="L1191" s="9" t="n"/>
+      <c r="M1191" s="10" t="inlineStr">
+        <is>
+          <t>通信制・今治本校（大三島町）。総合案内は東京03-3938-7500</t>
+        </is>
+      </c>
+      <c r="N1191" s="11" t="inlineStr">
+        <is>
+          <t>https://www.taiken.ac.jp/gakuin/school/index.html</t>
+        </is>
+      </c>
+      <c r="O1191" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="4" t="n">
+        <v>1188</v>
+      </c>
+      <c r="B1192" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1192" s="5" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D1192" s="5" t="inlineStr">
+        <is>
+          <t>松山学院高等学校</t>
+        </is>
+      </c>
+      <c r="E1192" s="6" t="inlineStr">
+        <is>
+          <t>089-976-4343</t>
+        </is>
+      </c>
+      <c r="F1192" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1192" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1192" s="8" t="n"/>
+      <c r="I1192" s="9" t="n"/>
+      <c r="J1192" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1192" s="8" t="n"/>
+      <c r="L1192" s="9" t="n"/>
+      <c r="M1192" s="10" t="n"/>
+      <c r="N1192" s="11" t="inlineStr">
+        <is>
+          <t>https://mg-h.ed.jp/form/contact/</t>
+        </is>
+      </c>
+      <c r="O1192" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="4" t="n">
+        <v>1189</v>
+      </c>
+      <c r="B1193" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1193" s="5" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D1193" s="5" t="inlineStr">
+        <is>
+          <t>松山東雲高等学校</t>
+        </is>
+      </c>
+      <c r="E1193" s="6" t="inlineStr">
+        <is>
+          <t>089-941-4136</t>
+        </is>
+      </c>
+      <c r="F1193" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1193" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1193" s="8" t="n"/>
+      <c r="I1193" s="9" t="n"/>
+      <c r="J1193" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1193" s="8" t="n"/>
+      <c r="L1193" s="9" t="n"/>
+      <c r="M1193" s="10" t="inlineStr">
+        <is>
+          <t>中高の番号。学園代表は089-931-6211</t>
+        </is>
+      </c>
+      <c r="N1193" s="11" t="inlineStr">
+        <is>
+          <t>https://www.shinonome.ac.jp/overview/contact/</t>
+        </is>
+      </c>
+      <c r="O1193" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="4" t="n">
+        <v>1190</v>
+      </c>
+      <c r="B1194" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1194" s="5" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D1194" s="5" t="inlineStr">
+        <is>
+          <t>松山聖陵高等学校</t>
+        </is>
+      </c>
+      <c r="E1194" s="6" t="inlineStr">
+        <is>
+          <t>089-924-8783</t>
+        </is>
+      </c>
+      <c r="F1194" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1194" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1194" s="8" t="n"/>
+      <c r="I1194" s="9" t="n"/>
+      <c r="J1194" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1194" s="8" t="n"/>
+      <c r="L1194" s="9" t="n"/>
+      <c r="M1194" s="10" t="inlineStr">
+        <is>
+          <t>事務室の電話対応は8:00-16:30</t>
+        </is>
+      </c>
+      <c r="N1194" s="11" t="inlineStr">
+        <is>
+          <t>https://matsuyamaseiryo-h.ed.jp/guidance/about/</t>
+        </is>
+      </c>
+      <c r="O1194" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="4" t="n">
+        <v>1191</v>
+      </c>
+      <c r="B1195" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1195" s="5" t="inlineStr">
+        <is>
+          <t>松山市</t>
+        </is>
+      </c>
+      <c r="D1195" s="5" t="inlineStr">
+        <is>
+          <t>未来高等学校</t>
+        </is>
+      </c>
+      <c r="E1195" s="6" t="inlineStr">
+        <is>
+          <t>089-947-4447</t>
+        </is>
+      </c>
+      <c r="F1195" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1195" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1195" s="8" t="n"/>
+      <c r="I1195" s="9" t="n"/>
+      <c r="J1195" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1195" s="8" t="n"/>
+      <c r="L1195" s="9" t="n"/>
+      <c r="M1195" s="10" t="inlineStr">
+        <is>
+          <t>通信制・松山本校。フリーダイヤル0120-89-4447</t>
+        </is>
+      </c>
+      <c r="N1195" s="11" t="inlineStr">
+        <is>
+          <t>https://mirai-hs.kawahara.ac.jp/</t>
+        </is>
+      </c>
+      <c r="O1195" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="4" t="n">
+        <v>1192</v>
+      </c>
+      <c r="B1196" s="5" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="C1196" s="5" t="inlineStr">
+        <is>
+          <t>新居浜市</t>
+        </is>
+      </c>
+      <c r="D1196" s="5" t="inlineStr">
+        <is>
+          <t>未来高等学校 新居浜分校</t>
+        </is>
+      </c>
+      <c r="E1196" s="6" t="inlineStr">
+        <is>
+          <t>0897-34-9555</t>
+        </is>
+      </c>
+      <c r="F1196" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1196" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1196" s="8" t="n"/>
+      <c r="I1196" s="9" t="n"/>
+      <c r="J1196" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1196" s="8" t="n"/>
+      <c r="L1196" s="9" t="n"/>
+      <c r="M1196" s="10" t="inlineStr">
+        <is>
+          <t>通信制・新居浜校</t>
+        </is>
+      </c>
+      <c r="N1196" s="11" t="inlineStr">
+        <is>
+          <t>https://mirai-hs.kawahara.ac.jp/center/</t>
+        </is>
+      </c>
+      <c r="O1196" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O1182"/>
-  <conditionalFormatting sqref="A5:O1182">
+  <autoFilter ref="A4:O1196"/>
+  <conditionalFormatting sqref="A5:O1196">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -69741,10 +70551,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J1182" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J1196" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H1182 K5:K1182" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H1196 K5:K1196" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -70927,6 +71737,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1180" r:id="rId1176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1181" r:id="rId1177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1182" r:id="rId1178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1183" r:id="rId1179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1184" r:id="rId1180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1185" r:id="rId1181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1186" r:id="rId1182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1187" r:id="rId1183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1188" r:id="rId1184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1189" r:id="rId1185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1190" r:id="rId1186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1191" r:id="rId1187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1192" r:id="rId1188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1193" r:id="rId1189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1194" r:id="rId1190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1195" r:id="rId1191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1196" r:id="rId1192"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -70939,7 +71763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -71026,43 +71850,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A4,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A4,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1182,A4,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A4,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1196,A4,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A4,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A4,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71073,43 +71897,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A5,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A5,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1182,A5,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A5,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1196,A5,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A5,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A5,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71120,43 +71944,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A6,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A6,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1182,A6,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A6,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1196,A6,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A6,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A6,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71167,43 +71991,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A7,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A7,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1182,A7,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A7,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1196,A7,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A7,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A7,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71214,43 +72038,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A8,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A8,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1182,A8,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A8,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1196,A8,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A8,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A8,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71261,43 +72085,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A9,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A9,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1182,A9,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A9,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1196,A9,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A9,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A9,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71308,43 +72132,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A10,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A10,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1182,A10,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A10,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1196,A10,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A10,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A10,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71355,43 +72179,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A11,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A11,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1182,A11,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A11,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1196,A11,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A11,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A11,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71402,43 +72226,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A12,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A12,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1182,A12,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A12,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1196,A12,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A12,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A12,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71449,43 +72273,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A13,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A13,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1182,A13,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A13,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1196,A13,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A13,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A13,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71496,43 +72320,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A14,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A14,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1182,A14,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A14,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1196,A14,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A14,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A14,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71543,43 +72367,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A15,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A15,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1182,A15,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A15,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1196,A15,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A15,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A15,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71590,43 +72414,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A16,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A16,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1182,A16,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A16,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1196,A16,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A16,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A16,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71637,43 +72461,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A17,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A17,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1182,A17,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A17,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1196,A17,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A17,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A17,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71684,43 +72508,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A18,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A18,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1182,A18,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A18,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1196,A18,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A18,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A18,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71731,43 +72555,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A19,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A19,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1182,A19,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A19,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1196,A19,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A19,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A19,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71778,43 +72602,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A20,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A20,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1182,A20,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A20,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1196,A20,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A20,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A20,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71825,43 +72649,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A21,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A21,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1182,A21,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A21,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1196,A21,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A21,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A21,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71872,43 +72696,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A22,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A22,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1182,A22,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A22,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1196,A22,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A22,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A22,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71919,43 +72743,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A23,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A23,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1182,A23,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A23,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1196,A23,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A23,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A23,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71966,43 +72790,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A24,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A24,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1182,A24,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A24,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1196,A24,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A24,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A24,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72013,43 +72837,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A25,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A25,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1182,A25,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A25,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1196,A25,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A25,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A25,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72060,43 +72884,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A26,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A26,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1182,A26,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A26,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1196,A26,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A26,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A26,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72107,43 +72931,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A27,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A27,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1182,A27,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A27,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1196,A27,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A27,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A27,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72154,43 +72978,43 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A28,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A28,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1182,A28,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A28,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1196,A28,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A28,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A28,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72201,43 +73025,43 @@
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A29)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A29,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A29,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1182,A29,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A29,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1196,A29,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A29,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A29,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72248,43 +73072,43 @@
         </is>
       </c>
       <c r="B30" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A30)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A30)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A30,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A30,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1182,A30,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A30,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1196,A30,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A30,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A30,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72295,43 +73119,43 @@
         </is>
       </c>
       <c r="B31" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A31)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A31)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A31,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A31,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1182,A31,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A31,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1196,A31,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A31,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A31,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72342,43 +73166,43 @@
         </is>
       </c>
       <c r="B32" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A32)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A32)</f>
         <v/>
       </c>
       <c r="C32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A32,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A32,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1182,A32,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A32,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1196,A32,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A32,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A32,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72389,43 +73213,43 @@
         </is>
       </c>
       <c r="B33" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A33)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A33)</f>
         <v/>
       </c>
       <c r="C33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A33,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A33,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D33" s="16">
-        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1182,A33,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A33,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1196,A33,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A33,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A33,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72436,43 +73260,43 @@
         </is>
       </c>
       <c r="B34" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A34)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A34)</f>
         <v/>
       </c>
       <c r="C34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A34,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A34,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1182,A34,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A34,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1196,A34,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A34,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A34,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72483,43 +73307,43 @@
         </is>
       </c>
       <c r="B35" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A35)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A35)</f>
         <v/>
       </c>
       <c r="C35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A35,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A35,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D35" s="16">
-        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1182,A35,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A35,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1196,A35,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A35,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A35,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72530,43 +73354,43 @@
         </is>
       </c>
       <c r="B36" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A36)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A36)</f>
         <v/>
       </c>
       <c r="C36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A36,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A36,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D36" s="16">
-        <f>B36-COUNTIFS('架電リスト'!$B$5:$B$1182,A36,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A36,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B36-COUNTIFS('架電リスト'!$B$5:$B$1196,A36,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A36,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A36,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72577,43 +73401,43 @@
         </is>
       </c>
       <c r="B37" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A37)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A37)</f>
         <v/>
       </c>
       <c r="C37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A37,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A37,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D37" s="16">
-        <f>B37-COUNTIFS('架電リスト'!$B$5:$B$1182,A37,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A37,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B37-COUNTIFS('架電リスト'!$B$5:$B$1196,A37,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A37,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A37,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72624,43 +73448,43 @@
         </is>
       </c>
       <c r="B38" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A38)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A38)</f>
         <v/>
       </c>
       <c r="C38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A38,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A38,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D38" s="16">
-        <f>B38-COUNTIFS('架電リスト'!$B$5:$B$1182,A38,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A38,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B38-COUNTIFS('架電リスト'!$B$5:$B$1196,A38,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A38,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A38,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72671,90 +73495,137 @@
         </is>
       </c>
       <c r="B39" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1182,A39)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A39)</f>
         <v/>
       </c>
       <c r="C39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,A39,'架電リスト'!$E$5:$E$1182,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A39,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D39" s="16">
-        <f>B39-COUNTIFS('架電リスト'!$B$5:$B$1182,A39,'架電リスト'!$J$5:$J$1182,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1182,A39,'架電リスト'!$J$5:$J$1182,"")</f>
+        <f>B39-COUNTIFS('架電リスト'!$B$5:$B$1196,A39,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A39,'架電リスト'!$J$5:$J$1196,"")</f>
         <v/>
       </c>
       <c r="E39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
         <v/>
       </c>
       <c r="G39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
         <v/>
       </c>
       <c r="H39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"検討中")</f>
         <v/>
       </c>
       <c r="J39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"NG")</f>
         <v/>
       </c>
       <c r="K39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1182,$A39,'架電リスト'!$J$5:$J$1182,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>愛媛県</t>
+        </is>
+      </c>
+      <c r="B40" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A40)</f>
+        <v/>
+      </c>
+      <c r="C40" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A40,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D40" s="16">
+        <f>B40-COUNTIFS('架電リスト'!$B$5:$B$1196,A40,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A40,'架電リスト'!$J$5:$J$1196,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F40" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G40" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H40" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I40" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J40" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <v/>
+      </c>
+      <c r="K40" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B40" s="17">
-        <f>SUM(B4:B39)</f>
+      <c r="B41" s="17">
+        <f>SUM(B4:B40)</f>
         <v/>
       </c>
-      <c r="C40" s="17">
-        <f>SUM(C4:C39)</f>
+      <c r="C41" s="17">
+        <f>SUM(C4:C40)</f>
         <v/>
       </c>
-      <c r="D40" s="17">
-        <f>SUM(D4:D39)</f>
+      <c r="D41" s="17">
+        <f>SUM(D4:D40)</f>
         <v/>
       </c>
-      <c r="E40" s="17">
-        <f>SUM(E4:E39)</f>
+      <c r="E41" s="17">
+        <f>SUM(E4:E40)</f>
         <v/>
       </c>
-      <c r="F40" s="17">
-        <f>SUM(F4:F39)</f>
+      <c r="F41" s="17">
+        <f>SUM(F4:F40)</f>
         <v/>
       </c>
-      <c r="G40" s="17">
-        <f>SUM(G4:G39)</f>
+      <c r="G41" s="17">
+        <f>SUM(G4:G40)</f>
         <v/>
       </c>
-      <c r="H40" s="17">
-        <f>SUM(H4:H39)</f>
+      <c r="H41" s="17">
+        <f>SUM(H4:H40)</f>
         <v/>
       </c>
-      <c r="I40" s="17">
-        <f>SUM(I4:I39)</f>
+      <c r="I41" s="17">
+        <f>SUM(I4:I40)</f>
         <v/>
       </c>
-      <c r="J40" s="17">
-        <f>SUM(J4:J39)</f>
+      <c r="J41" s="17">
+        <f>SUM(J4:J40)</f>
         <v/>
       </c>
-      <c r="K40" s="17">
-        <f>SUM(K4:K39)</f>
+      <c r="K41" s="17">
+        <f>SUM(K4:K40)</f>
         <v/>
       </c>
     </row>
@@ -72844,7 +73715,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・36都道府県、1178校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・37都道府県、1192校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1196</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1205</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O1196"/>
+  <dimension ref="A1:O1205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（37都道府県／1192校）</t>
+          <t>私立高等学校 架電リスト（38都道府県／1201校）</t>
         </is>
       </c>
     </row>
@@ -70540,9 +70540,536 @@
         </is>
       </c>
     </row>
+    <row r="1197">
+      <c r="A1197" s="4" t="n">
+        <v>1193</v>
+      </c>
+      <c r="B1197" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1197" s="5" t="inlineStr">
+        <is>
+          <t>高知市</t>
+        </is>
+      </c>
+      <c r="D1197" s="5" t="inlineStr">
+        <is>
+          <t>高知学芸高等学校</t>
+        </is>
+      </c>
+      <c r="E1197" s="6" t="inlineStr">
+        <is>
+          <t>088-844-1831</t>
+        </is>
+      </c>
+      <c r="F1197" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1197" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1197" s="8" t="n"/>
+      <c r="I1197" s="9" t="n"/>
+      <c r="J1197" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1197" s="8" t="n"/>
+      <c r="L1197" s="9" t="n"/>
+      <c r="M1197" s="10" t="inlineStr">
+        <is>
+          <t>中高一体。公式の入試案内ページ（渉外部）に掲載、私学連合会とも一致</t>
+        </is>
+      </c>
+      <c r="N1197" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kochi-gakugei.ed.jp/page.html?id=45</t>
+        </is>
+      </c>
+      <c r="O1197" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="4" t="n">
+        <v>1194</v>
+      </c>
+      <c r="B1198" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1198" s="5" t="inlineStr">
+        <is>
+          <t>高知市</t>
+        </is>
+      </c>
+      <c r="D1198" s="5" t="inlineStr">
+        <is>
+          <t>高知高等学校</t>
+        </is>
+      </c>
+      <c r="E1198" s="6" t="inlineStr">
+        <is>
+          <t>088-840-1111</t>
+        </is>
+      </c>
+      <c r="F1198" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1198" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1198" s="8" t="n"/>
+      <c r="I1198" s="9" t="n"/>
+      <c r="J1198" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1198" s="8" t="n"/>
+      <c r="L1198" s="9" t="n"/>
+      <c r="M1198" s="10" t="inlineStr">
+        <is>
+          <t>高知中学高等学校（高知学園）</t>
+        </is>
+      </c>
+      <c r="N1198" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kochigakuen.jp/access.html</t>
+        </is>
+      </c>
+      <c r="O1198" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="4" t="n">
+        <v>1195</v>
+      </c>
+      <c r="B1199" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1199" s="5" t="inlineStr">
+        <is>
+          <t>高知市</t>
+        </is>
+      </c>
+      <c r="D1199" s="5" t="inlineStr">
+        <is>
+          <t>高知中央高等学校</t>
+        </is>
+      </c>
+      <c r="E1199" s="6" t="inlineStr">
+        <is>
+          <t>088-866-3166</t>
+        </is>
+      </c>
+      <c r="F1199" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1199" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
+      <c r="H1199" s="8" t="n"/>
+      <c r="I1199" s="9" t="n"/>
+      <c r="J1199" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1199" s="8" t="n"/>
+      <c r="L1199" s="9" t="n"/>
+      <c r="M1199" s="10" t="n"/>
+      <c r="N1199" s="11" t="inlineStr">
+        <is>
+          <t>https://www.kochi-chuo.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1199" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="4" t="n">
+        <v>1196</v>
+      </c>
+      <c r="B1200" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1200" s="5" t="inlineStr">
+        <is>
+          <t>南国市</t>
+        </is>
+      </c>
+      <c r="D1200" s="5" t="inlineStr">
+        <is>
+          <t>清和女子高等学校</t>
+        </is>
+      </c>
+      <c r="E1200" s="6" t="inlineStr">
+        <is>
+          <t>088-863-1200</t>
+        </is>
+      </c>
+      <c r="F1200" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1200" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1200" s="8" t="n"/>
+      <c r="I1200" s="9" t="n"/>
+      <c r="J1200" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1200" s="8" t="n"/>
+      <c r="L1200" s="9" t="n"/>
+      <c r="M1200" s="10" t="inlineStr">
+        <is>
+          <t>清和女子中高等学校</t>
+        </is>
+      </c>
+      <c r="N1200" s="11" t="inlineStr">
+        <is>
+          <t>https://seiwa-girl.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1200" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="4" t="n">
+        <v>1197</v>
+      </c>
+      <c r="B1201" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1201" s="5" t="inlineStr">
+        <is>
+          <t>高知市</t>
+        </is>
+      </c>
+      <c r="D1201" s="5" t="inlineStr">
+        <is>
+          <t>太平洋学園高等学校</t>
+        </is>
+      </c>
+      <c r="E1201" s="6" t="inlineStr">
+        <is>
+          <t>088-822-3584</t>
+        </is>
+      </c>
+      <c r="F1201" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1201" s="5" t="inlineStr">
+        <is>
+          <t>総合学科</t>
+        </is>
+      </c>
+      <c r="H1201" s="8" t="n"/>
+      <c r="I1201" s="9" t="n"/>
+      <c r="J1201" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1201" s="8" t="n"/>
+      <c r="L1201" s="9" t="n"/>
+      <c r="M1201" s="10" t="inlineStr">
+        <is>
+          <t>通信制・定時制あり。088-822-3585も掲載（FAX兼用の可能性）</t>
+        </is>
+      </c>
+      <c r="N1201" s="11" t="inlineStr">
+        <is>
+          <t>https://www.taiheiyo.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1201" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="4" t="n">
+        <v>1198</v>
+      </c>
+      <c r="B1202" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1202" s="5" t="inlineStr">
+        <is>
+          <t>高知市</t>
+        </is>
+      </c>
+      <c r="D1202" s="5" t="inlineStr">
+        <is>
+          <t>土佐高等学校</t>
+        </is>
+      </c>
+      <c r="E1202" s="6" t="inlineStr">
+        <is>
+          <t>088-833-4394</t>
+        </is>
+      </c>
+      <c r="F1202" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1202" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1202" s="8" t="n"/>
+      <c r="I1202" s="9" t="n"/>
+      <c r="J1202" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1202" s="8" t="n"/>
+      <c r="L1202" s="9" t="n"/>
+      <c r="M1202" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1202" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tosa.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1202" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="4" t="n">
+        <v>1199</v>
+      </c>
+      <c r="B1203" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1203" s="5" t="inlineStr">
+        <is>
+          <t>高知市</t>
+        </is>
+      </c>
+      <c r="D1203" s="5" t="inlineStr">
+        <is>
+          <t>土佐塾高等学校</t>
+        </is>
+      </c>
+      <c r="E1203" s="6" t="inlineStr">
+        <is>
+          <t>088-831-1717</t>
+        </is>
+      </c>
+      <c r="F1203" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1203" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1203" s="8" t="n"/>
+      <c r="I1203" s="9" t="n"/>
+      <c r="J1203" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1203" s="8" t="n"/>
+      <c r="L1203" s="9" t="n"/>
+      <c r="M1203" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1203" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tosajuku.ed.jp/contact.html</t>
+        </is>
+      </c>
+      <c r="O1203" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="4" t="n">
+        <v>1200</v>
+      </c>
+      <c r="B1204" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1204" s="5" t="inlineStr">
+        <is>
+          <t>高知市</t>
+        </is>
+      </c>
+      <c r="D1204" s="5" t="inlineStr">
+        <is>
+          <t>土佐女子高等学校</t>
+        </is>
+      </c>
+      <c r="E1204" s="6" t="inlineStr">
+        <is>
+          <t>088-875-3111</t>
+        </is>
+      </c>
+      <c r="F1204" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1204" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1204" s="8" t="n"/>
+      <c r="I1204" s="9" t="n"/>
+      <c r="J1204" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1204" s="8" t="n"/>
+      <c r="L1204" s="9" t="n"/>
+      <c r="M1204" s="10" t="inlineStr">
+        <is>
+          <t>088-873-1670は寄宿舎の番号</t>
+        </is>
+      </c>
+      <c r="N1204" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tosajoshi-jh.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1204" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="4" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B1205" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1205" s="5" t="inlineStr">
+        <is>
+          <t>須崎市</t>
+        </is>
+      </c>
+      <c r="D1205" s="5" t="inlineStr">
+        <is>
+          <t>明徳義塾高等学校</t>
+        </is>
+      </c>
+      <c r="E1205" s="6" t="inlineStr">
+        <is>
+          <t>088-856-1211</t>
+        </is>
+      </c>
+      <c r="F1205" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1205" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1205" s="8" t="n"/>
+      <c r="I1205" s="9" t="n"/>
+      <c r="J1205" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1205" s="8" t="n"/>
+      <c r="L1205" s="9" t="n"/>
+      <c r="M1205" s="10" t="inlineStr">
+        <is>
+          <t>本校（堂ノ浦キャンパス）。須崎市公式ページとも一致</t>
+        </is>
+      </c>
+      <c r="N1205" s="11" t="inlineStr">
+        <is>
+          <t>https://www.meitoku-gijuku.ed.jp/senior_c2.php</t>
+        </is>
+      </c>
+      <c r="O1205" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O1196"/>
-  <conditionalFormatting sqref="A5:O1196">
+  <autoFilter ref="A4:O1205"/>
+  <conditionalFormatting sqref="A5:O1205">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -70551,10 +71078,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J1196" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J1205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H1196 K5:K1196" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H1205 K5:K1205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -71751,6 +72278,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1194" r:id="rId1190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1195" r:id="rId1191"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1196" r:id="rId1192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1197" r:id="rId1193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1198" r:id="rId1194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1199" r:id="rId1195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1200" r:id="rId1196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1201" r:id="rId1197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1202" r:id="rId1198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1203" r:id="rId1199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1204" r:id="rId1200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1205" r:id="rId1201"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -71763,7 +72299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -71850,43 +72386,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A4,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A4,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1196,A4,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A4,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1205,A4,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A4,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A4,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71897,43 +72433,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A5,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A5,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1196,A5,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A5,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1205,A5,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A5,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A5,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71944,43 +72480,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A6,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A6,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1196,A6,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A6,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1205,A6,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A6,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A6,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -71991,43 +72527,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A7,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A7,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1196,A7,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A7,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1205,A7,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A7,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A7,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72038,43 +72574,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A8,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A8,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1196,A8,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A8,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1205,A8,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A8,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A8,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72085,43 +72621,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A9,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A9,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1196,A9,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A9,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1205,A9,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A9,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A9,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72132,43 +72668,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A10,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A10,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1196,A10,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A10,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1205,A10,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A10,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A10,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72179,43 +72715,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A11,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A11,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1196,A11,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A11,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1205,A11,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A11,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A11,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72226,43 +72762,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A12,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A12,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1196,A12,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A12,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1205,A12,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A12,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A12,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72273,43 +72809,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A13,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A13,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1196,A13,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A13,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1205,A13,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A13,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A13,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72320,43 +72856,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A14,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A14,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1196,A14,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A14,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1205,A14,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A14,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A14,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72367,43 +72903,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A15,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A15,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1196,A15,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A15,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1205,A15,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A15,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A15,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72414,43 +72950,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A16,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A16,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1196,A16,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A16,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1205,A16,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A16,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A16,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72461,43 +72997,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A17,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A17,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1196,A17,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A17,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1205,A17,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A17,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A17,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72508,43 +73044,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A18,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A18,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1196,A18,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A18,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1205,A18,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A18,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A18,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72555,43 +73091,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A19,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A19,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1196,A19,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A19,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1205,A19,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A19,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A19,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A19,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A19,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A19,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A19,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A19,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A19,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A19,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72602,43 +73138,43 @@
         </is>
       </c>
       <c r="B20" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A20)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A20)</f>
         <v/>
       </c>
       <c r="C20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A20,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A20,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1196,A20,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A20,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B20-COUNTIFS('架電リスト'!$B$5:$B$1205,A20,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A20,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A20,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A20,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A20,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A20,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A20,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A20,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A20,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A20,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72649,43 +73185,43 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A21)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A21)</f>
         <v/>
       </c>
       <c r="C21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A21,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A21,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1196,A21,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A21,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B21-COUNTIFS('架電リスト'!$B$5:$B$1205,A21,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A21,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A21,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A21,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A21,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A21,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A21,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A21,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A21,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A21,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72696,43 +73232,43 @@
         </is>
       </c>
       <c r="B22" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A22)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A22)</f>
         <v/>
       </c>
       <c r="C22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A22,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A22,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D22" s="16">
-        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1196,A22,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A22,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B22-COUNTIFS('架電リスト'!$B$5:$B$1205,A22,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A22,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A22,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A22,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A22,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A22,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A22,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A22,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A22,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A22,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72743,43 +73279,43 @@
         </is>
       </c>
       <c r="B23" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A23)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A23)</f>
         <v/>
       </c>
       <c r="C23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A23,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A23,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1196,A23,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A23,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B23-COUNTIFS('架電リスト'!$B$5:$B$1205,A23,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A23,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A23,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A23,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A23,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A23,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A23,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A23,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A23,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A23,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72790,43 +73326,43 @@
         </is>
       </c>
       <c r="B24" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A24)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A24)</f>
         <v/>
       </c>
       <c r="C24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A24,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A24,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1196,A24,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A24,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B24-COUNTIFS('架電リスト'!$B$5:$B$1205,A24,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A24,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A24,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A24,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A24,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A24,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A24,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A24,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A24,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A24,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72837,43 +73373,43 @@
         </is>
       </c>
       <c r="B25" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A25)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A25)</f>
         <v/>
       </c>
       <c r="C25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A25,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A25,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D25" s="16">
-        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1196,A25,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A25,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B25-COUNTIFS('架電リスト'!$B$5:$B$1205,A25,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A25,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A25,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A25,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A25,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A25,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A25,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A25,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A25,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A25,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72884,43 +73420,43 @@
         </is>
       </c>
       <c r="B26" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A26)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A26)</f>
         <v/>
       </c>
       <c r="C26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A26,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A26,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D26" s="16">
-        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1196,A26,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A26,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B26-COUNTIFS('架電リスト'!$B$5:$B$1205,A26,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A26,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A26,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A26,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A26,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A26,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A26,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A26,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A26,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A26,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72931,43 +73467,43 @@
         </is>
       </c>
       <c r="B27" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A27)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A27)</f>
         <v/>
       </c>
       <c r="C27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A27,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A27,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1196,A27,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A27,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B27-COUNTIFS('架電リスト'!$B$5:$B$1205,A27,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A27,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A27,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A27,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A27,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A27,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A27,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A27,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A27,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A27,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72978,43 +73514,43 @@
         </is>
       </c>
       <c r="B28" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A28)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A28)</f>
         <v/>
       </c>
       <c r="C28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A28,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A28,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D28" s="16">
-        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1196,A28,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A28,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B28-COUNTIFS('架電リスト'!$B$5:$B$1205,A28,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A28,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A28,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A28,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A28,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A28,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A28,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A28,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A28,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A28,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73025,43 +73561,43 @@
         </is>
       </c>
       <c r="B29" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A29)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A29)</f>
         <v/>
       </c>
       <c r="C29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A29,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A29,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D29" s="16">
-        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1196,A29,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A29,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B29-COUNTIFS('架電リスト'!$B$5:$B$1205,A29,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A29,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A29,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A29,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A29,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A29,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A29,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A29,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A29,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A29,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73072,43 +73608,43 @@
         </is>
       </c>
       <c r="B30" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A30)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A30)</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A30,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A30,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1196,A30,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A30,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B30-COUNTIFS('架電リスト'!$B$5:$B$1205,A30,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A30,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A30,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A30,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A30,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A30,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A30,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A30,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A30,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A30,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73119,43 +73655,43 @@
         </is>
       </c>
       <c r="B31" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A31)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A31)</f>
         <v/>
       </c>
       <c r="C31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A31,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A31,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1196,A31,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A31,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B31-COUNTIFS('架電リスト'!$B$5:$B$1205,A31,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A31,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A31,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A31,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A31,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A31,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A31,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A31,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A31,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A31,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73166,43 +73702,43 @@
         </is>
       </c>
       <c r="B32" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A32)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A32)</f>
         <v/>
       </c>
       <c r="C32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A32,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A32,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D32" s="16">
-        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1196,A32,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A32,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B32-COUNTIFS('架電リスト'!$B$5:$B$1205,A32,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A32,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A32,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A32,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A32,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A32,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A32,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A32,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A32,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A32,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73213,43 +73749,43 @@
         </is>
       </c>
       <c r="B33" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A33)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A33)</f>
         <v/>
       </c>
       <c r="C33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A33,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A33,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D33" s="16">
-        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1196,A33,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A33,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B33-COUNTIFS('架電リスト'!$B$5:$B$1205,A33,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A33,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A33,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A33,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A33,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A33,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A33,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A33,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A33,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A33,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73260,43 +73796,43 @@
         </is>
       </c>
       <c r="B34" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A34)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A34)</f>
         <v/>
       </c>
       <c r="C34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A34,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A34,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1196,A34,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A34,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B34-COUNTIFS('架電リスト'!$B$5:$B$1205,A34,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A34,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A34,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A34,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A34,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A34,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A34,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A34,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A34,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A34,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73307,43 +73843,43 @@
         </is>
       </c>
       <c r="B35" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A35)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A35)</f>
         <v/>
       </c>
       <c r="C35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A35,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A35,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D35" s="16">
-        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1196,A35,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A35,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B35-COUNTIFS('架電リスト'!$B$5:$B$1205,A35,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A35,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A35,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A35,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A35,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A35,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A35,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A35,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A35,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A35,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73354,43 +73890,43 @@
         </is>
       </c>
       <c r="B36" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A36)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A36)</f>
         <v/>
       </c>
       <c r="C36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A36,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A36,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D36" s="16">
-        <f>B36-COUNTIFS('架電リスト'!$B$5:$B$1196,A36,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A36,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B36-COUNTIFS('架電リスト'!$B$5:$B$1205,A36,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A36,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A36,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A36,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A36,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A36,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A36,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A36,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A36,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A36,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73401,43 +73937,43 @@
         </is>
       </c>
       <c r="B37" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A37)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A37)</f>
         <v/>
       </c>
       <c r="C37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A37,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A37,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D37" s="16">
-        <f>B37-COUNTIFS('架電リスト'!$B$5:$B$1196,A37,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A37,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B37-COUNTIFS('架電リスト'!$B$5:$B$1205,A37,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A37,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A37,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A37,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A37,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A37,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A37,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A37,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K37" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A37,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A37,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73448,43 +73984,43 @@
         </is>
       </c>
       <c r="B38" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A38)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A38)</f>
         <v/>
       </c>
       <c r="C38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A38,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A38,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D38" s="16">
-        <f>B38-COUNTIFS('架電リスト'!$B$5:$B$1196,A38,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A38,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B38-COUNTIFS('架電リスト'!$B$5:$B$1205,A38,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A38,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A38,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A38,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A38,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A38,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A38,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A38,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A38,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A38,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73495,43 +74031,43 @@
         </is>
       </c>
       <c r="B39" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A39)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A39)</f>
         <v/>
       </c>
       <c r="C39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A39,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A39,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D39" s="16">
-        <f>B39-COUNTIFS('架電リスト'!$B$5:$B$1196,A39,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A39,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B39-COUNTIFS('架電リスト'!$B$5:$B$1205,A39,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A39,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A39,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A39,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A39,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A39,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A39,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A39,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K39" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A39,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A39,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73542,90 +74078,137 @@
         </is>
       </c>
       <c r="B40" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1196,A40)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A40)</f>
         <v/>
       </c>
       <c r="C40" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,A40,'架電リスト'!$E$5:$E$1196,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A40,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D40" s="16">
-        <f>B40-COUNTIFS('架電リスト'!$B$5:$B$1196,A40,'架電リスト'!$J$5:$J$1196,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1196,A40,'架電リスト'!$J$5:$J$1196,"")</f>
+        <f>B40-COUNTIFS('架電リスト'!$B$5:$B$1205,A40,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A40,'架電リスト'!$J$5:$J$1205,"")</f>
         <v/>
       </c>
       <c r="E40" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A40,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F40" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A40,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
         <v/>
       </c>
       <c r="G40" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A40,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
         <v/>
       </c>
       <c r="H40" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A40,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I40" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A40,'架電リスト'!$J$5:$J$1205,"検討中")</f>
         <v/>
       </c>
       <c r="J40" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A40,'架電リスト'!$J$5:$J$1205,"NG")</f>
         <v/>
       </c>
       <c r="K40" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1196,$A40,'架電リスト'!$J$5:$J$1196,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A40,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="B41" s="16">
+        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A41)</f>
+        <v/>
+      </c>
+      <c r="C41" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A41,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="D41" s="16">
+        <f>B41-COUNTIFS('架電リスト'!$B$5:$B$1205,A41,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A41,'架電リスト'!$J$5:$J$1205,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A41,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <v/>
+      </c>
+      <c r="F41" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A41,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <v/>
+      </c>
+      <c r="G41" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A41,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <v/>
+      </c>
+      <c r="H41" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A41,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <v/>
+      </c>
+      <c r="I41" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A41,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <v/>
+      </c>
+      <c r="J41" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A41,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <v/>
+      </c>
+      <c r="K41" s="16">
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A41,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B41" s="17">
-        <f>SUM(B4:B40)</f>
+      <c r="B42" s="17">
+        <f>SUM(B4:B41)</f>
         <v/>
       </c>
-      <c r="C41" s="17">
-        <f>SUM(C4:C40)</f>
+      <c r="C42" s="17">
+        <f>SUM(C4:C41)</f>
         <v/>
       </c>
-      <c r="D41" s="17">
-        <f>SUM(D4:D40)</f>
+      <c r="D42" s="17">
+        <f>SUM(D4:D41)</f>
         <v/>
       </c>
-      <c r="E41" s="17">
-        <f>SUM(E4:E40)</f>
+      <c r="E42" s="17">
+        <f>SUM(E4:E41)</f>
         <v/>
       </c>
-      <c r="F41" s="17">
-        <f>SUM(F4:F40)</f>
+      <c r="F42" s="17">
+        <f>SUM(F4:F41)</f>
         <v/>
       </c>
-      <c r="G41" s="17">
-        <f>SUM(G4:G40)</f>
+      <c r="G42" s="17">
+        <f>SUM(G4:G41)</f>
         <v/>
       </c>
-      <c r="H41" s="17">
-        <f>SUM(H4:H40)</f>
+      <c r="H42" s="17">
+        <f>SUM(H4:H41)</f>
         <v/>
       </c>
-      <c r="I41" s="17">
-        <f>SUM(I4:I40)</f>
+      <c r="I42" s="17">
+        <f>SUM(I4:I41)</f>
         <v/>
       </c>
-      <c r="J41" s="17">
-        <f>SUM(J4:J40)</f>
+      <c r="J42" s="17">
+        <f>SUM(J4:J41)</f>
         <v/>
       </c>
-      <c r="K41" s="17">
-        <f>SUM(K4:K40)</f>
+      <c r="K42" s="17">
+        <f>SUM(K4:K41)</f>
         <v/>
       </c>
     </row>
@@ -73715,7 +74298,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・37都道府県、1192校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
+          <t>・出典：ご提供いただいた学校ネットの検索結果（私立高校・38都道府県、1201校）の貼り付けデータ。並び順は都道府県ごとに元データの掲載順です。</t>
         </is>
       </c>
     </row>

--- a/call-list/私立高校_架電リスト_全体.xlsx
+++ b/call-list/私立高校_架電リスト_全体.xlsx
@@ -12,7 +12,7 @@
     <sheet name="使い方・注意事項" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'架電リスト'!$A$4:$O$1208</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'架電リスト'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O1205"/>
+  <dimension ref="A1:O1208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>私立高等学校 架電リスト（38都道府県／1201校）</t>
+          <t>私立高等学校 架電リスト（39都道府県／1204校）</t>
         </is>
       </c>
     </row>
@@ -69158,27 +69158,27 @@
       </c>
       <c r="B1173" s="5" t="inlineStr">
         <is>
-          <t>香川県</t>
+          <t>徳島県</t>
         </is>
       </c>
       <c r="C1173" s="5" t="inlineStr">
         <is>
-          <t>高松市</t>
+          <t>徳島市</t>
         </is>
       </c>
       <c r="D1173" s="5" t="inlineStr">
         <is>
-          <t>英明高等学校</t>
+          <t>香蘭高等学校</t>
         </is>
       </c>
       <c r="E1173" s="6" t="inlineStr">
         <is>
-          <t>087-833-3737</t>
-        </is>
-      </c>
-      <c r="F1173" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>088-652-5044</t>
+        </is>
+      </c>
+      <c r="F1173" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="G1173" s="5" t="inlineStr">
@@ -69197,12 +69197,12 @@
       <c r="L1173" s="9" t="n"/>
       <c r="M1173" s="10" t="inlineStr">
         <is>
-          <t>公式未確認。香川県私立中高連合会・複数サイトで一致。通信制課程も同じ番号</t>
+          <t>徳島県私立学校一覧でも一致</t>
         </is>
       </c>
       <c r="N1173" s="11" t="inlineStr">
         <is>
-          <t>https://www.kagawa-shigaku.jp/eimei</t>
+          <t>https://kouran-kou.jp/nyusi.html</t>
         </is>
       </c>
       <c r="O1173" s="12" t="inlineStr">
@@ -69217,22 +69217,22 @@
       </c>
       <c r="B1174" s="5" t="inlineStr">
         <is>
-          <t>香川県</t>
+          <t>徳島県</t>
         </is>
       </c>
       <c r="C1174" s="5" t="inlineStr">
         <is>
-          <t>高松市</t>
+          <t>徳島市</t>
         </is>
       </c>
       <c r="D1174" s="5" t="inlineStr">
         <is>
-          <t>大手前高松高等学校</t>
+          <t>生光学園高等学校</t>
         </is>
       </c>
       <c r="E1174" s="6" t="inlineStr">
         <is>
-          <t>087-867-5970</t>
+          <t>088-641-1032</t>
         </is>
       </c>
       <c r="F1174" s="7" t="inlineStr">
@@ -69254,10 +69254,14 @@
       </c>
       <c r="K1174" s="8" t="n"/>
       <c r="L1174" s="9" t="n"/>
-      <c r="M1174" s="10" t="n"/>
+      <c r="M1174" s="10" t="inlineStr">
+        <is>
+          <t>代表番号</t>
+        </is>
+      </c>
       <c r="N1174" s="11" t="inlineStr">
         <is>
-          <t>https://www.otemae.net/contact/</t>
+          <t>http://www.seikogakuen.ac.jp/guide.html</t>
         </is>
       </c>
       <c r="O1174" s="12" t="inlineStr">
@@ -69272,22 +69276,22 @@
       </c>
       <c r="B1175" s="5" t="inlineStr">
         <is>
-          <t>香川県</t>
+          <t>徳島県</t>
         </is>
       </c>
       <c r="C1175" s="5" t="inlineStr">
         <is>
-          <t>丸亀市</t>
+          <t>徳島市</t>
         </is>
       </c>
       <c r="D1175" s="5" t="inlineStr">
         <is>
-          <t>大手前丸亀高等学校</t>
+          <t>徳島文理高等学校</t>
         </is>
       </c>
       <c r="E1175" s="6" t="inlineStr">
         <is>
-          <t>0877-23-3161</t>
+          <t>088-626-1225</t>
         </is>
       </c>
       <c r="F1175" s="7" t="inlineStr">
@@ -69309,10 +69313,14 @@
       </c>
       <c r="K1175" s="8" t="n"/>
       <c r="L1175" s="9" t="n"/>
-      <c r="M1175" s="10" t="n"/>
+      <c r="M1175" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
       <c r="N1175" s="11" t="inlineStr">
         <is>
-          <t>https://www.otemae.ed.jp/contact_form/otoiawase.html</t>
+          <t>https://www.bunri.ed.jp/access/</t>
         </is>
       </c>
       <c r="O1175" s="12" t="inlineStr">
@@ -69332,27 +69340,27 @@
       </c>
       <c r="C1176" s="5" t="inlineStr">
         <is>
-          <t>丸亀市</t>
+          <t>高松市</t>
         </is>
       </c>
       <c r="D1176" s="5" t="inlineStr">
         <is>
-          <t>香川県藤井高等学校</t>
+          <t>英明高等学校</t>
         </is>
       </c>
       <c r="E1176" s="6" t="inlineStr">
         <is>
-          <t>0877-22-2328</t>
-        </is>
-      </c>
-      <c r="F1176" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>087-833-3737</t>
+        </is>
+      </c>
+      <c r="F1176" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="G1176" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1176" s="8" t="n"/>
@@ -69366,12 +69374,12 @@
       <c r="L1176" s="9" t="n"/>
       <c r="M1176" s="10" t="inlineStr">
         <is>
-          <t>2026年度から「蓬莱高等学校」に校名変更（法人も蓬莱学園に改称）</t>
+          <t>公式未確認。香川県私立中高連合会・複数サイトで一致。通信制課程も同じ番号</t>
         </is>
       </c>
       <c r="N1176" s="11" t="inlineStr">
         <is>
-          <t>https://www.fujii.ed.jp/fujii/</t>
+          <t>https://www.kagawa-shigaku.jp/eimei</t>
         </is>
       </c>
       <c r="O1176" s="12" t="inlineStr">
@@ -69396,12 +69404,12 @@
       </c>
       <c r="D1177" s="5" t="inlineStr">
         <is>
-          <t>香川誠陵高等学校</t>
+          <t>大手前高松高等学校</t>
         </is>
       </c>
       <c r="E1177" s="6" t="inlineStr">
         <is>
-          <t>087-881-7800</t>
+          <t>087-867-5970</t>
         </is>
       </c>
       <c r="F1177" s="7" t="inlineStr">
@@ -69423,14 +69431,10 @@
       </c>
       <c r="K1177" s="8" t="n"/>
       <c r="L1177" s="9" t="n"/>
-      <c r="M1177" s="10" t="inlineStr">
-        <is>
-          <t>中高共通番号</t>
-        </is>
-      </c>
+      <c r="M1177" s="10" t="n"/>
       <c r="N1177" s="11" t="inlineStr">
         <is>
-          <t>https://k-seiryo.ed.jp/</t>
+          <t>https://www.otemae.net/contact/</t>
         </is>
       </c>
       <c r="O1177" s="12" t="inlineStr">
@@ -69450,17 +69454,17 @@
       </c>
       <c r="C1178" s="5" t="inlineStr">
         <is>
-          <t>坂出市</t>
+          <t>丸亀市</t>
         </is>
       </c>
       <c r="D1178" s="5" t="inlineStr">
         <is>
-          <t>坂出第一高等学校</t>
+          <t>大手前丸亀高等学校</t>
         </is>
       </c>
       <c r="E1178" s="6" t="inlineStr">
         <is>
-          <t>0877-46-2157</t>
+          <t>0877-23-3161</t>
         </is>
       </c>
       <c r="F1178" s="7" t="inlineStr">
@@ -69470,7 +69474,7 @@
       </c>
       <c r="G1178" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1178" s="8" t="n"/>
@@ -69485,7 +69489,7 @@
       <c r="M1178" s="10" t="n"/>
       <c r="N1178" s="11" t="inlineStr">
         <is>
-          <t>https://www.sakaide1-h.ed.jp/</t>
+          <t>https://www.otemae.ed.jp/contact_form/otoiawase.html</t>
         </is>
       </c>
       <c r="O1178" s="12" t="inlineStr">
@@ -69505,17 +69509,17 @@
       </c>
       <c r="C1179" s="5" t="inlineStr">
         <is>
-          <t>三豊市</t>
+          <t>丸亀市</t>
         </is>
       </c>
       <c r="D1179" s="5" t="inlineStr">
         <is>
-          <t>四国学院大学香川西高等学校</t>
+          <t>香川県藤井高等学校</t>
         </is>
       </c>
       <c r="E1179" s="6" t="inlineStr">
         <is>
-          <t>0875-72-5193</t>
+          <t>0877-22-2328</t>
         </is>
       </c>
       <c r="F1179" s="7" t="inlineStr">
@@ -69539,12 +69543,12 @@
       <c r="L1179" s="9" t="n"/>
       <c r="M1179" s="10" t="inlineStr">
         <is>
-          <t>三豊市HPとも一致</t>
+          <t>2026年度から「蓬莱高等学校」に校名変更（法人も蓬莱学園に改称）</t>
         </is>
       </c>
       <c r="N1179" s="11" t="inlineStr">
         <is>
-          <t>https://www.kagawanishikou.com/contact</t>
+          <t>https://www.fujii.ed.jp/fujii/</t>
         </is>
       </c>
       <c r="O1179" s="12" t="inlineStr">
@@ -69564,17 +69568,17 @@
       </c>
       <c r="C1180" s="5" t="inlineStr">
         <is>
-          <t>善通寺市</t>
+          <t>高松市</t>
         </is>
       </c>
       <c r="D1180" s="5" t="inlineStr">
         <is>
-          <t>尽誠学園高等学校</t>
+          <t>香川誠陵高等学校</t>
         </is>
       </c>
       <c r="E1180" s="6" t="inlineStr">
         <is>
-          <t>0877-62-1515</t>
+          <t>087-881-7800</t>
         </is>
       </c>
       <c r="F1180" s="7" t="inlineStr">
@@ -69584,7 +69588,7 @@
       </c>
       <c r="G1180" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1180" s="8" t="n"/>
@@ -69598,12 +69602,12 @@
       <c r="L1180" s="9" t="n"/>
       <c r="M1180" s="10" t="inlineStr">
         <is>
-          <t>県私立中高連合会とも一致。法人本部は0877-63-1717</t>
+          <t>中高共通番号</t>
         </is>
       </c>
       <c r="N1180" s="11" t="inlineStr">
         <is>
-          <t>https://sites.google.com/jinsei.ac.jp/jinseiopenschool2020</t>
+          <t>https://k-seiryo.ed.jp/</t>
         </is>
       </c>
       <c r="O1180" s="12" t="inlineStr">
@@ -69623,17 +69627,17 @@
       </c>
       <c r="C1181" s="5" t="inlineStr">
         <is>
-          <t>高松市</t>
+          <t>坂出市</t>
         </is>
       </c>
       <c r="D1181" s="5" t="inlineStr">
         <is>
-          <t>高松中央高等学校</t>
+          <t>坂出第一高等学校</t>
         </is>
       </c>
       <c r="E1181" s="6" t="inlineStr">
         <is>
-          <t>087-831-1291</t>
+          <t>0877-46-2157</t>
         </is>
       </c>
       <c r="F1181" s="7" t="inlineStr">
@@ -69655,14 +69659,10 @@
       </c>
       <c r="K1181" s="8" t="n"/>
       <c r="L1181" s="9" t="n"/>
-      <c r="M1181" s="10" t="inlineStr">
-        <is>
-          <t>全日制の番号。通信制課程は087-812-5285</t>
-        </is>
-      </c>
+      <c r="M1181" s="10" t="n"/>
       <c r="N1181" s="11" t="inlineStr">
         <is>
-          <t>https://www.ta-chuo.ed.jp/contact/</t>
+          <t>https://www.sakaide1-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1181" s="12" t="inlineStr">
@@ -69682,17 +69682,17 @@
       </c>
       <c r="C1182" s="5" t="inlineStr">
         <is>
-          <t>さぬき市</t>
+          <t>三豊市</t>
         </is>
       </c>
       <c r="D1182" s="5" t="inlineStr">
         <is>
-          <t>藤井学園寒川高等学校</t>
+          <t>四国学院大学香川西高等学校</t>
         </is>
       </c>
       <c r="E1182" s="6" t="inlineStr">
         <is>
-          <t>0879-43-2571</t>
+          <t>0875-72-5193</t>
         </is>
       </c>
       <c r="F1182" s="7" t="inlineStr">
@@ -69716,12 +69716,12 @@
       <c r="L1182" s="9" t="n"/>
       <c r="M1182" s="10" t="inlineStr">
         <is>
-          <t>法人名は2026年に蓬莱学園へ改称</t>
+          <t>三豊市HPとも一致</t>
         </is>
       </c>
       <c r="N1182" s="11" t="inlineStr">
         <is>
-          <t>https://www.sangawa.ed.jp/wp/contact/</t>
+          <t>https://www.kagawanishikou.com/contact</t>
         </is>
       </c>
       <c r="O1182" s="12" t="inlineStr">
@@ -69736,22 +69736,22 @@
       </c>
       <c r="B1183" s="5" t="inlineStr">
         <is>
-          <t>愛媛県</t>
+          <t>香川県</t>
         </is>
       </c>
       <c r="C1183" s="5" t="inlineStr">
         <is>
-          <t>松山市</t>
+          <t>善通寺市</t>
         </is>
       </c>
       <c r="D1183" s="5" t="inlineStr">
         <is>
-          <t>愛光高等学校</t>
+          <t>尽誠学園高等学校</t>
         </is>
       </c>
       <c r="E1183" s="6" t="inlineStr">
         <is>
-          <t>089-922-8980</t>
+          <t>0877-62-1515</t>
         </is>
       </c>
       <c r="F1183" s="7" t="inlineStr">
@@ -69761,7 +69761,7 @@
       </c>
       <c r="G1183" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1183" s="8" t="n"/>
@@ -69775,12 +69775,12 @@
       <c r="L1183" s="9" t="n"/>
       <c r="M1183" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>県私立中高連合会とも一致。法人本部は0877-63-1717</t>
         </is>
       </c>
       <c r="N1183" s="11" t="inlineStr">
         <is>
-          <t>https://www.aiko.ed.jp/outline/shisetu.html</t>
+          <t>https://sites.google.com/jinsei.ac.jp/jinseiopenschool2020</t>
         </is>
       </c>
       <c r="O1183" s="12" t="inlineStr">
@@ -69795,22 +69795,22 @@
       </c>
       <c r="B1184" s="5" t="inlineStr">
         <is>
-          <t>愛媛県</t>
+          <t>香川県</t>
         </is>
       </c>
       <c r="C1184" s="5" t="inlineStr">
         <is>
-          <t>今治市</t>
+          <t>高松市</t>
         </is>
       </c>
       <c r="D1184" s="5" t="inlineStr">
         <is>
-          <t>今治精華高等学校</t>
+          <t>高松中央高等学校</t>
         </is>
       </c>
       <c r="E1184" s="6" t="inlineStr">
         <is>
-          <t>0898-32-7100</t>
+          <t>087-831-1291</t>
         </is>
       </c>
       <c r="F1184" s="7" t="inlineStr">
@@ -69834,12 +69834,12 @@
       <c r="L1184" s="9" t="n"/>
       <c r="M1184" s="10" t="inlineStr">
         <is>
-          <t>一部サイトに0898-32-7260の記載あり（旧情報の可能性）</t>
+          <t>全日制の番号。通信制課程は087-812-5285</t>
         </is>
       </c>
       <c r="N1184" s="11" t="inlineStr">
         <is>
-          <t>https://highschool.imabariseika.ac.jp/summary/about/</t>
+          <t>https://www.ta-chuo.ed.jp/contact/</t>
         </is>
       </c>
       <c r="O1184" s="12" t="inlineStr">
@@ -69854,30 +69854,34 @@
       </c>
       <c r="B1185" s="5" t="inlineStr">
         <is>
-          <t>愛媛県</t>
+          <t>香川県</t>
         </is>
       </c>
       <c r="C1185" s="5" t="inlineStr">
         <is>
-          <t>今治市</t>
+          <t>さぬき市</t>
         </is>
       </c>
       <c r="D1185" s="5" t="inlineStr">
         <is>
-          <t>FC今治高等学校 里山校</t>
+          <t>藤井学園寒川高等学校</t>
         </is>
       </c>
       <c r="E1185" s="6" t="inlineStr">
         <is>
-          <t>0898-22-1230</t>
-        </is>
-      </c>
-      <c r="F1185" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="G1185" s="5" t="inlineStr"/>
+          <t>0879-43-2571</t>
+        </is>
+      </c>
+      <c r="F1185" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1185" s="5" t="inlineStr">
+        <is>
+          <t>普通科・専門学科</t>
+        </is>
+      </c>
       <c r="H1185" s="8" t="n"/>
       <c r="I1185" s="9" t="n"/>
       <c r="J1185" s="9" t="inlineStr">
@@ -69889,12 +69893,12 @@
       <c r="L1185" s="9" t="n"/>
       <c r="M1185" s="10" t="inlineStr">
         <is>
-          <t>公式未確認。複数サイト・公式Facebookで一致。2024年に今治明徳高校矢田分校から改称</t>
+          <t>法人名は2026年に蓬莱学園へ改称</t>
         </is>
       </c>
       <c r="N1185" s="11" t="inlineStr">
         <is>
-          <t>https://www.gakkou.net/kou/view/index_306788.html</t>
+          <t>https://www.sangawa.ed.jp/wp/contact/</t>
         </is>
       </c>
       <c r="O1185" s="12" t="inlineStr">
@@ -69914,17 +69918,17 @@
       </c>
       <c r="C1186" s="5" t="inlineStr">
         <is>
-          <t>今治市</t>
+          <t>松山市</t>
         </is>
       </c>
       <c r="D1186" s="5" t="inlineStr">
         <is>
-          <t>FC今治高等学校 明徳校</t>
+          <t>愛光高等学校</t>
         </is>
       </c>
       <c r="E1186" s="6" t="inlineStr">
         <is>
-          <t>0898-22-6767</t>
+          <t>089-922-8980</t>
         </is>
       </c>
       <c r="F1186" s="7" t="inlineStr">
@@ -69948,12 +69952,12 @@
       <c r="L1186" s="9" t="n"/>
       <c r="M1186" s="10" t="inlineStr">
         <is>
-          <t>旧・今治明徳高校本校（2024年改称）</t>
+          <t>中高共通番号</t>
         </is>
       </c>
       <c r="N1186" s="11" t="inlineStr">
         <is>
-          <t>https://www.meitokuhonko.com/</t>
+          <t>https://www.aiko.ed.jp/outline/shisetu.html</t>
         </is>
       </c>
       <c r="O1186" s="12" t="inlineStr">
@@ -69973,17 +69977,17 @@
       </c>
       <c r="C1187" s="5" t="inlineStr">
         <is>
-          <t>松山市</t>
+          <t>今治市</t>
         </is>
       </c>
       <c r="D1187" s="5" t="inlineStr">
         <is>
-          <t>済美高等学校（愛媛県）</t>
+          <t>今治精華高等学校</t>
         </is>
       </c>
       <c r="E1187" s="6" t="inlineStr">
         <is>
-          <t>089-943-4185</t>
+          <t>0898-32-7100</t>
         </is>
       </c>
       <c r="F1187" s="7" t="inlineStr">
@@ -70007,12 +70011,12 @@
       <c r="L1187" s="9" t="n"/>
       <c r="M1187" s="10" t="inlineStr">
         <is>
-          <t>電話受付は平日7:30-16:55、土曜7:30-13:00</t>
+          <t>一部サイトに0898-32-7260の記載あり（旧情報の可能性）</t>
         </is>
       </c>
       <c r="N1187" s="11" t="inlineStr">
         <is>
-          <t>https://www.saibi.ac.jp/</t>
+          <t>https://highschool.imabariseika.ac.jp/summary/about/</t>
         </is>
       </c>
       <c r="O1187" s="12" t="inlineStr">
@@ -70032,29 +70036,25 @@
       </c>
       <c r="C1188" s="5" t="inlineStr">
         <is>
-          <t>松山市</t>
+          <t>今治市</t>
         </is>
       </c>
       <c r="D1188" s="5" t="inlineStr">
         <is>
-          <t>聖カタリナ学園高等学校</t>
+          <t>FC今治高等学校 里山校</t>
         </is>
       </c>
       <c r="E1188" s="6" t="inlineStr">
         <is>
-          <t>089-933-3291</t>
-        </is>
-      </c>
-      <c r="F1188" s="7" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="G1188" s="5" t="inlineStr">
-        <is>
-          <t>普通科・専門学科・総合学科</t>
-        </is>
-      </c>
+          <t>0898-22-1230</t>
+        </is>
+      </c>
+      <c r="F1188" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="G1188" s="5" t="inlineStr"/>
       <c r="H1188" s="8" t="n"/>
       <c r="I1188" s="9" t="n"/>
       <c r="J1188" s="9" t="inlineStr">
@@ -70064,10 +70064,14 @@
       </c>
       <c r="K1188" s="8" t="n"/>
       <c r="L1188" s="9" t="n"/>
-      <c r="M1188" s="10" t="n"/>
+      <c r="M1188" s="10" t="inlineStr">
+        <is>
+          <t>公式未確認。複数サイト・公式Facebookで一致。2024年に今治明徳高校矢田分校から改称</t>
+        </is>
+      </c>
       <c r="N1188" s="11" t="inlineStr">
         <is>
-          <t>https://catalina.ed.jp/about/outline/</t>
+          <t>https://www.gakkou.net/kou/view/index_306788.html</t>
         </is>
       </c>
       <c r="O1188" s="12" t="inlineStr">
@@ -70087,17 +70091,17 @@
       </c>
       <c r="C1189" s="5" t="inlineStr">
         <is>
-          <t>大洲市</t>
+          <t>今治市</t>
         </is>
       </c>
       <c r="D1189" s="5" t="inlineStr">
         <is>
-          <t>帝京第五高等学校</t>
+          <t>FC今治高等学校 明徳校</t>
         </is>
       </c>
       <c r="E1189" s="6" t="inlineStr">
         <is>
-          <t>0893-25-0511</t>
+          <t>0898-22-6767</t>
         </is>
       </c>
       <c r="F1189" s="7" t="inlineStr">
@@ -70107,7 +70111,7 @@
       </c>
       <c r="G1189" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科・総合学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1189" s="8" t="n"/>
@@ -70121,12 +70125,12 @@
       <c r="L1189" s="9" t="n"/>
       <c r="M1189" s="10" t="inlineStr">
         <is>
-          <t>代表番号。職員室0893-25-0566、通信制0893-57-6850</t>
+          <t>旧・今治明徳高校本校（2024年改称）</t>
         </is>
       </c>
       <c r="N1189" s="11" t="inlineStr">
         <is>
-          <t>https://teikyo5-h.ed.jp/</t>
+          <t>https://www.meitokuhonko.com/</t>
         </is>
       </c>
       <c r="O1189" s="12" t="inlineStr">
@@ -70151,12 +70155,12 @@
       </c>
       <c r="D1190" s="5" t="inlineStr">
         <is>
-          <t>新田高等学校</t>
+          <t>済美高等学校（愛媛県）</t>
         </is>
       </c>
       <c r="E1190" s="6" t="inlineStr">
         <is>
-          <t>089-951-0188</t>
+          <t>089-943-4185</t>
         </is>
       </c>
       <c r="F1190" s="7" t="inlineStr">
@@ -70178,10 +70182,14 @@
       </c>
       <c r="K1190" s="8" t="n"/>
       <c r="L1190" s="9" t="n"/>
-      <c r="M1190" s="10" t="n"/>
+      <c r="M1190" s="10" t="inlineStr">
+        <is>
+          <t>電話受付は平日7:30-16:55、土曜7:30-13:00</t>
+        </is>
+      </c>
       <c r="N1190" s="11" t="inlineStr">
         <is>
-          <t>https://www.nitta.ac.jp/information/about/</t>
+          <t>https://www.saibi.ac.jp/</t>
         </is>
       </c>
       <c r="O1190" s="12" t="inlineStr">
@@ -70201,17 +70209,17 @@
       </c>
       <c r="C1191" s="5" t="inlineStr">
         <is>
-          <t>今治市</t>
+          <t>松山市</t>
         </is>
       </c>
       <c r="D1191" s="5" t="inlineStr">
         <is>
-          <t>日本ウェルネス高等学校</t>
+          <t>聖カタリナ学園高等学校</t>
         </is>
       </c>
       <c r="E1191" s="6" t="inlineStr">
         <is>
-          <t>0897-74-1356</t>
+          <t>089-933-3291</t>
         </is>
       </c>
       <c r="F1191" s="7" t="inlineStr">
@@ -70221,7 +70229,7 @@
       </c>
       <c r="G1191" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科・総合学科</t>
         </is>
       </c>
       <c r="H1191" s="8" t="n"/>
@@ -70233,14 +70241,10 @@
       </c>
       <c r="K1191" s="8" t="n"/>
       <c r="L1191" s="9" t="n"/>
-      <c r="M1191" s="10" t="inlineStr">
-        <is>
-          <t>通信制・今治本校（大三島町）。総合案内は東京03-3938-7500</t>
-        </is>
-      </c>
+      <c r="M1191" s="10" t="n"/>
       <c r="N1191" s="11" t="inlineStr">
         <is>
-          <t>https://www.taiken.ac.jp/gakuin/school/index.html</t>
+          <t>https://catalina.ed.jp/about/outline/</t>
         </is>
       </c>
       <c r="O1191" s="12" t="inlineStr">
@@ -70260,17 +70264,17 @@
       </c>
       <c r="C1192" s="5" t="inlineStr">
         <is>
-          <t>松山市</t>
+          <t>大洲市</t>
         </is>
       </c>
       <c r="D1192" s="5" t="inlineStr">
         <is>
-          <t>松山学院高等学校</t>
+          <t>帝京第五高等学校</t>
         </is>
       </c>
       <c r="E1192" s="6" t="inlineStr">
         <is>
-          <t>089-976-4343</t>
+          <t>0893-25-0511</t>
         </is>
       </c>
       <c r="F1192" s="7" t="inlineStr">
@@ -70280,7 +70284,7 @@
       </c>
       <c r="G1192" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科・専門学科・総合学科</t>
         </is>
       </c>
       <c r="H1192" s="8" t="n"/>
@@ -70292,10 +70296,14 @@
       </c>
       <c r="K1192" s="8" t="n"/>
       <c r="L1192" s="9" t="n"/>
-      <c r="M1192" s="10" t="n"/>
+      <c r="M1192" s="10" t="inlineStr">
+        <is>
+          <t>代表番号。職員室0893-25-0566、通信制0893-57-6850</t>
+        </is>
+      </c>
       <c r="N1192" s="11" t="inlineStr">
         <is>
-          <t>https://mg-h.ed.jp/form/contact/</t>
+          <t>https://teikyo5-h.ed.jp/</t>
         </is>
       </c>
       <c r="O1192" s="12" t="inlineStr">
@@ -70320,12 +70328,12 @@
       </c>
       <c r="D1193" s="5" t="inlineStr">
         <is>
-          <t>松山東雲高等学校</t>
+          <t>新田高等学校</t>
         </is>
       </c>
       <c r="E1193" s="6" t="inlineStr">
         <is>
-          <t>089-941-4136</t>
+          <t>089-951-0188</t>
         </is>
       </c>
       <c r="F1193" s="7" t="inlineStr">
@@ -70335,7 +70343,7 @@
       </c>
       <c r="G1193" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1193" s="8" t="n"/>
@@ -70347,14 +70355,10 @@
       </c>
       <c r="K1193" s="8" t="n"/>
       <c r="L1193" s="9" t="n"/>
-      <c r="M1193" s="10" t="inlineStr">
-        <is>
-          <t>中高の番号。学園代表は089-931-6211</t>
-        </is>
-      </c>
+      <c r="M1193" s="10" t="n"/>
       <c r="N1193" s="11" t="inlineStr">
         <is>
-          <t>https://www.shinonome.ac.jp/overview/contact/</t>
+          <t>https://www.nitta.ac.jp/information/about/</t>
         </is>
       </c>
       <c r="O1193" s="12" t="inlineStr">
@@ -70374,17 +70378,17 @@
       </c>
       <c r="C1194" s="5" t="inlineStr">
         <is>
-          <t>松山市</t>
+          <t>今治市</t>
         </is>
       </c>
       <c r="D1194" s="5" t="inlineStr">
         <is>
-          <t>松山聖陵高等学校</t>
+          <t>日本ウェルネス高等学校</t>
         </is>
       </c>
       <c r="E1194" s="6" t="inlineStr">
         <is>
-          <t>089-924-8783</t>
+          <t>0897-74-1356</t>
         </is>
       </c>
       <c r="F1194" s="7" t="inlineStr">
@@ -70394,7 +70398,7 @@
       </c>
       <c r="G1194" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1194" s="8" t="n"/>
@@ -70408,12 +70412,12 @@
       <c r="L1194" s="9" t="n"/>
       <c r="M1194" s="10" t="inlineStr">
         <is>
-          <t>事務室の電話対応は8:00-16:30</t>
+          <t>通信制・今治本校（大三島町）。総合案内は東京03-3938-7500</t>
         </is>
       </c>
       <c r="N1194" s="11" t="inlineStr">
         <is>
-          <t>https://matsuyamaseiryo-h.ed.jp/guidance/about/</t>
+          <t>https://www.taiken.ac.jp/gakuin/school/index.html</t>
         </is>
       </c>
       <c r="O1194" s="12" t="inlineStr">
@@ -70438,12 +70442,12 @@
       </c>
       <c r="D1195" s="5" t="inlineStr">
         <is>
-          <t>未来高等学校</t>
+          <t>松山学院高等学校</t>
         </is>
       </c>
       <c r="E1195" s="6" t="inlineStr">
         <is>
-          <t>089-947-4447</t>
+          <t>089-976-4343</t>
         </is>
       </c>
       <c r="F1195" s="7" t="inlineStr">
@@ -70453,7 +70457,7 @@
       </c>
       <c r="G1195" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1195" s="8" t="n"/>
@@ -70465,14 +70469,10 @@
       </c>
       <c r="K1195" s="8" t="n"/>
       <c r="L1195" s="9" t="n"/>
-      <c r="M1195" s="10" t="inlineStr">
-        <is>
-          <t>通信制・松山本校。フリーダイヤル0120-89-4447</t>
-        </is>
-      </c>
+      <c r="M1195" s="10" t="n"/>
       <c r="N1195" s="11" t="inlineStr">
         <is>
-          <t>https://mirai-hs.kawahara.ac.jp/</t>
+          <t>https://mg-h.ed.jp/form/contact/</t>
         </is>
       </c>
       <c r="O1195" s="12" t="inlineStr">
@@ -70492,17 +70492,17 @@
       </c>
       <c r="C1196" s="5" t="inlineStr">
         <is>
-          <t>新居浜市</t>
+          <t>松山市</t>
         </is>
       </c>
       <c r="D1196" s="5" t="inlineStr">
         <is>
-          <t>未来高等学校 新居浜分校</t>
+          <t>松山東雲高等学校</t>
         </is>
       </c>
       <c r="E1196" s="6" t="inlineStr">
         <is>
-          <t>0897-34-9555</t>
+          <t>089-941-4136</t>
         </is>
       </c>
       <c r="F1196" s="7" t="inlineStr">
@@ -70526,12 +70526,12 @@
       <c r="L1196" s="9" t="n"/>
       <c r="M1196" s="10" t="inlineStr">
         <is>
-          <t>通信制・新居浜校</t>
+          <t>中高の番号。学園代表は089-931-6211</t>
         </is>
       </c>
       <c r="N1196" s="11" t="inlineStr">
         <is>
-          <t>https://mirai-hs.kawahara.ac.jp/center/</t>
+          <t>https://www.shinonome.ac.jp/overview/contact/</t>
         </is>
       </c>
       <c r="O1196" s="12" t="inlineStr">
@@ -70546,22 +70546,22 @@
       </c>
       <c r="B1197" s="5" t="inlineStr">
         <is>
-          <t>高知県</t>
+          <t>愛媛県</t>
         </is>
       </c>
       <c r="C1197" s="5" t="inlineStr">
         <is>
-          <t>高知市</t>
+          <t>松山市</t>
         </is>
       </c>
       <c r="D1197" s="5" t="inlineStr">
         <is>
-          <t>高知学芸高等学校</t>
+          <t>松山聖陵高等学校</t>
         </is>
       </c>
       <c r="E1197" s="6" t="inlineStr">
         <is>
-          <t>088-844-1831</t>
+          <t>089-924-8783</t>
         </is>
       </c>
       <c r="F1197" s="7" t="inlineStr">
@@ -70571,7 +70571,7 @@
       </c>
       <c r="G1197" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1197" s="8" t="n"/>
@@ -70585,12 +70585,12 @@
       <c r="L1197" s="9" t="n"/>
       <c r="M1197" s="10" t="inlineStr">
         <is>
-          <t>中高一体。公式の入試案内ページ（渉外部）に掲載、私学連合会とも一致</t>
+          <t>事務室の電話対応は8:00-16:30</t>
         </is>
       </c>
       <c r="N1197" s="11" t="inlineStr">
         <is>
-          <t>https://www.kochi-gakugei.ed.jp/page.html?id=45</t>
+          <t>https://matsuyamaseiryo-h.ed.jp/guidance/about/</t>
         </is>
       </c>
       <c r="O1197" s="12" t="inlineStr">
@@ -70605,22 +70605,22 @@
       </c>
       <c r="B1198" s="5" t="inlineStr">
         <is>
-          <t>高知県</t>
+          <t>愛媛県</t>
         </is>
       </c>
       <c r="C1198" s="5" t="inlineStr">
         <is>
-          <t>高知市</t>
+          <t>松山市</t>
         </is>
       </c>
       <c r="D1198" s="5" t="inlineStr">
         <is>
-          <t>高知高等学校</t>
+          <t>未来高等学校</t>
         </is>
       </c>
       <c r="E1198" s="6" t="inlineStr">
         <is>
-          <t>088-840-1111</t>
+          <t>089-947-4447</t>
         </is>
       </c>
       <c r="F1198" s="7" t="inlineStr">
@@ -70644,12 +70644,12 @@
       <c r="L1198" s="9" t="n"/>
       <c r="M1198" s="10" t="inlineStr">
         <is>
-          <t>高知中学高等学校（高知学園）</t>
+          <t>通信制・松山本校。フリーダイヤル0120-89-4447</t>
         </is>
       </c>
       <c r="N1198" s="11" t="inlineStr">
         <is>
-          <t>https://www.kochigakuen.jp/access.html</t>
+          <t>https://mirai-hs.kawahara.ac.jp/</t>
         </is>
       </c>
       <c r="O1198" s="12" t="inlineStr">
@@ -70664,22 +70664,22 @@
       </c>
       <c r="B1199" s="5" t="inlineStr">
         <is>
-          <t>高知県</t>
+          <t>愛媛県</t>
         </is>
       </c>
       <c r="C1199" s="5" t="inlineStr">
         <is>
-          <t>高知市</t>
+          <t>新居浜市</t>
         </is>
       </c>
       <c r="D1199" s="5" t="inlineStr">
         <is>
-          <t>高知中央高等学校</t>
+          <t>未来高等学校 新居浜分校</t>
         </is>
       </c>
       <c r="E1199" s="6" t="inlineStr">
         <is>
-          <t>088-866-3166</t>
+          <t>0897-34-9555</t>
         </is>
       </c>
       <c r="F1199" s="7" t="inlineStr">
@@ -70689,7 +70689,7 @@
       </c>
       <c r="G1199" s="5" t="inlineStr">
         <is>
-          <t>普通科・専門学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1199" s="8" t="n"/>
@@ -70701,10 +70701,14 @@
       </c>
       <c r="K1199" s="8" t="n"/>
       <c r="L1199" s="9" t="n"/>
-      <c r="M1199" s="10" t="n"/>
+      <c r="M1199" s="10" t="inlineStr">
+        <is>
+          <t>通信制・新居浜校</t>
+        </is>
+      </c>
       <c r="N1199" s="11" t="inlineStr">
         <is>
-          <t>https://www.kochi-chuo.ed.jp/</t>
+          <t>https://mirai-hs.kawahara.ac.jp/center/</t>
         </is>
       </c>
       <c r="O1199" s="12" t="inlineStr">
@@ -70724,17 +70728,17 @@
       </c>
       <c r="C1200" s="5" t="inlineStr">
         <is>
-          <t>南国市</t>
+          <t>高知市</t>
         </is>
       </c>
       <c r="D1200" s="5" t="inlineStr">
         <is>
-          <t>清和女子高等学校</t>
+          <t>高知学芸高等学校</t>
         </is>
       </c>
       <c r="E1200" s="6" t="inlineStr">
         <is>
-          <t>088-863-1200</t>
+          <t>088-844-1831</t>
         </is>
       </c>
       <c r="F1200" s="7" t="inlineStr">
@@ -70758,12 +70762,12 @@
       <c r="L1200" s="9" t="n"/>
       <c r="M1200" s="10" t="inlineStr">
         <is>
-          <t>清和女子中高等学校</t>
+          <t>中高一体。公式の入試案内ページ（渉外部）に掲載、私学連合会とも一致</t>
         </is>
       </c>
       <c r="N1200" s="11" t="inlineStr">
         <is>
-          <t>https://seiwa-girl.ed.jp/</t>
+          <t>https://www.kochi-gakugei.ed.jp/page.html?id=45</t>
         </is>
       </c>
       <c r="O1200" s="12" t="inlineStr">
@@ -70788,12 +70792,12 @@
       </c>
       <c r="D1201" s="5" t="inlineStr">
         <is>
-          <t>太平洋学園高等学校</t>
+          <t>高知高等学校</t>
         </is>
       </c>
       <c r="E1201" s="6" t="inlineStr">
         <is>
-          <t>088-822-3584</t>
+          <t>088-840-1111</t>
         </is>
       </c>
       <c r="F1201" s="7" t="inlineStr">
@@ -70803,7 +70807,7 @@
       </c>
       <c r="G1201" s="5" t="inlineStr">
         <is>
-          <t>総合学科</t>
+          <t>普通科</t>
         </is>
       </c>
       <c r="H1201" s="8" t="n"/>
@@ -70817,12 +70821,12 @@
       <c r="L1201" s="9" t="n"/>
       <c r="M1201" s="10" t="inlineStr">
         <is>
-          <t>通信制・定時制あり。088-822-3585も掲載（FAX兼用の可能性）</t>
+          <t>高知中学高等学校（高知学園）</t>
         </is>
       </c>
       <c r="N1201" s="11" t="inlineStr">
         <is>
-          <t>https://www.taiheiyo.ed.jp/</t>
+          <t>https://www.kochigakuen.jp/access.html</t>
         </is>
       </c>
       <c r="O1201" s="12" t="inlineStr">
@@ -70847,12 +70851,12 @@
       </c>
       <c r="D1202" s="5" t="inlineStr">
         <is>
-          <t>土佐高等学校</t>
+          <t>高知中央高等学校</t>
         </is>
       </c>
       <c r="E1202" s="6" t="inlineStr">
         <is>
-          <t>088-833-4394</t>
+          <t>088-866-3166</t>
         </is>
       </c>
       <c r="F1202" s="7" t="inlineStr">
@@ -70862,7 +70866,7 @@
       </c>
       <c r="G1202" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>普通科・専門学科</t>
         </is>
       </c>
       <c r="H1202" s="8" t="n"/>
@@ -70874,14 +70878,10 @@
       </c>
       <c r="K1202" s="8" t="n"/>
       <c r="L1202" s="9" t="n"/>
-      <c r="M1202" s="10" t="inlineStr">
-        <is>
-          <t>中高共通番号</t>
-        </is>
-      </c>
+      <c r="M1202" s="10" t="n"/>
       <c r="N1202" s="11" t="inlineStr">
         <is>
-          <t>https://www.tosa.ed.jp/</t>
+          <t>https://www.kochi-chuo.ed.jp/</t>
         </is>
       </c>
       <c r="O1202" s="12" t="inlineStr">
@@ -70901,17 +70901,17 @@
       </c>
       <c r="C1203" s="5" t="inlineStr">
         <is>
-          <t>高知市</t>
+          <t>南国市</t>
         </is>
       </c>
       <c r="D1203" s="5" t="inlineStr">
         <is>
-          <t>土佐塾高等学校</t>
+          <t>清和女子高等学校</t>
         </is>
       </c>
       <c r="E1203" s="6" t="inlineStr">
         <is>
-          <t>088-831-1717</t>
+          <t>088-863-1200</t>
         </is>
       </c>
       <c r="F1203" s="7" t="inlineStr">
@@ -70935,12 +70935,12 @@
       <c r="L1203" s="9" t="n"/>
       <c r="M1203" s="10" t="inlineStr">
         <is>
-          <t>中高共通番号</t>
+          <t>清和女子中高等学校</t>
         </is>
       </c>
       <c r="N1203" s="11" t="inlineStr">
         <is>
-          <t>https://www.tosajuku.ed.jp/contact.html</t>
+          <t>https://seiwa-girl.ed.jp/</t>
         </is>
       </c>
       <c r="O1203" s="12" t="inlineStr">
@@ -70965,12 +70965,12 @@
       </c>
       <c r="D1204" s="5" t="inlineStr">
         <is>
-          <t>土佐女子高等学校</t>
+          <t>太平洋学園高等学校</t>
         </is>
       </c>
       <c r="E1204" s="6" t="inlineStr">
         <is>
-          <t>088-875-3111</t>
+          <t>088-822-3584</t>
         </is>
       </c>
       <c r="F1204" s="7" t="inlineStr">
@@ -70980,7 +70980,7 @@
       </c>
       <c r="G1204" s="5" t="inlineStr">
         <is>
-          <t>普通科</t>
+          <t>総合学科</t>
         </is>
       </c>
       <c r="H1204" s="8" t="n"/>
@@ -70994,12 +70994,12 @@
       <c r="L1204" s="9" t="n"/>
       <c r="M1204" s="10" t="inlineStr">
         <is>
-          <t>088-873-1670は寄宿舎の番号</t>
+          <t>通信制・定時制あり。088-822-3585も掲載（FAX兼用の可能性）</t>
         </is>
       </c>
       <c r="N1204" s="11" t="inlineStr">
         <is>
-          <t>https://www.tosajoshi-jh.ed.jp/</t>
+          <t>https://www.taiheiyo.ed.jp/</t>
         </is>
       </c>
       <c r="O1204" s="12" t="inlineStr">
@@ -71019,17 +71019,17 @@
       </c>
       <c r="C1205" s="5" t="inlineStr">
         <is>
-          <t>須崎市</t>
+          <t>高知市</t>
         </is>
       </c>
       <c r="D1205" s="5" t="inlineStr">
         <is>
-          <t>明徳義塾高等学校</t>
+          <t>土佐高等学校</t>
         </is>
       </c>
       <c r="E1205" s="6" t="inlineStr">
         <is>
-          <t>088-856-1211</t>
+          <t>088-833-4394</t>
         </is>
       </c>
       <c r="F1205" s="7" t="inlineStr">
@@ -71053,23 +71053,200 @@
       <c r="L1205" s="9" t="n"/>
       <c r="M1205" s="10" t="inlineStr">
         <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1205" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tosa.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1205" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B1206" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1206" s="5" t="inlineStr">
+        <is>
+          <t>高知市</t>
+        </is>
+      </c>
+      <c r="D1206" s="5" t="inlineStr">
+        <is>
+          <t>土佐塾高等学校</t>
+        </is>
+      </c>
+      <c r="E1206" s="6" t="inlineStr">
+        <is>
+          <t>088-831-1717</t>
+        </is>
+      </c>
+      <c r="F1206" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1206" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1206" s="8" t="n"/>
+      <c r="I1206" s="9" t="n"/>
+      <c r="J1206" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1206" s="8" t="n"/>
+      <c r="L1206" s="9" t="n"/>
+      <c r="M1206" s="10" t="inlineStr">
+        <is>
+          <t>中高共通番号</t>
+        </is>
+      </c>
+      <c r="N1206" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tosajuku.ed.jp/contact.html</t>
+        </is>
+      </c>
+      <c r="O1206" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="4" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B1207" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1207" s="5" t="inlineStr">
+        <is>
+          <t>高知市</t>
+        </is>
+      </c>
+      <c r="D1207" s="5" t="inlineStr">
+        <is>
+          <t>土佐女子高等学校</t>
+        </is>
+      </c>
+      <c r="E1207" s="6" t="inlineStr">
+        <is>
+          <t>088-875-3111</t>
+        </is>
+      </c>
+      <c r="F1207" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1207" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1207" s="8" t="n"/>
+      <c r="I1207" s="9" t="n"/>
+      <c r="J1207" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1207" s="8" t="n"/>
+      <c r="L1207" s="9" t="n"/>
+      <c r="M1207" s="10" t="inlineStr">
+        <is>
+          <t>088-873-1670は寄宿舎の番号</t>
+        </is>
+      </c>
+      <c r="N1207" s="11" t="inlineStr">
+        <is>
+          <t>https://www.tosajoshi-jh.ed.jp/</t>
+        </is>
+      </c>
+      <c r="O1207" s="12" t="inlineStr">
+        <is>
+          <t>開く</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="4" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B1208" s="5" t="inlineStr">
+        <is>
+          <t>高知県</t>
+        </is>
+      </c>
+      <c r="C1208" s="5" t="inlineStr">
+        <is>
+          <t>須崎市</t>
+        </is>
+      </c>
+      <c r="D1208" s="5" t="inlineStr">
+        <is>
+          <t>明徳義塾高等学校</t>
+        </is>
+      </c>
+      <c r="E1208" s="6" t="inlineStr">
+        <is>
+          <t>088-856-1211</t>
+        </is>
+      </c>
+      <c r="F1208" s="7" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="G1208" s="5" t="inlineStr">
+        <is>
+          <t>普通科</t>
+        </is>
+      </c>
+      <c r="H1208" s="8" t="n"/>
+      <c r="I1208" s="9" t="n"/>
+      <c r="J1208" s="9" t="inlineStr">
+        <is>
+          <t>未架電</t>
+        </is>
+      </c>
+      <c r="K1208" s="8" t="n"/>
+      <c r="L1208" s="9" t="n"/>
+      <c r="M1208" s="10" t="inlineStr">
+        <is>
           <t>本校（堂ノ浦キャンパス）。須崎市公式ページとも一致</t>
         </is>
       </c>
-      <c r="N1205" s="11" t="inlineStr">
+      <c r="N1208" s="11" t="inlineStr">
         <is>
           <t>https://www.meitoku-gijuku.ed.jp/senior_c2.php</t>
         </is>
       </c>
-      <c r="O1205" s="12" t="inlineStr">
+      <c r="O1208" s="12" t="inlineStr">
         <is>
           <t>開く</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O1205"/>
-  <conditionalFormatting sqref="A5:O1205">
+  <autoFilter ref="A4:O1208"/>
+  <conditionalFormatting sqref="A5:O1208">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$J5="アポ獲得"</formula>
     </cfRule>
@@ -71078,10 +71255,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="J5:J1205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J5:J1208" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"未架電,不在・折返し待ち,担当者不在,資料送付,アポ獲得,検討中,NG,番号不明"</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H1205 K5:K1205" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
+    <dataValidation sqref="H5:H1208 K5:K1208" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="日付" error="日付で入力してください（例：2026/10/9）" type="date" operator="greaterThan">
       <formula1>36526</formula1>
     </dataValidation>
   </dataValidations>
@@ -72287,6 +72464,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1203" r:id="rId1199"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1204" r:id="rId1200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1205" r:id="rId1201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1206" r:id="rId1202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1207" r:id="rId1203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O1208" r:id="rId1204"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -72299,7 +72479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -72386,43 +72566,43 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A4)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A4)</f>
         <v/>
       </c>
       <c r="C4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A4,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A4,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D4" s="16">
-        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1205,A4,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A4,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B4-COUNTIFS('架電リスト'!$B$5:$B$1208,A4,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A4,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A4,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A4,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A4,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A4,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A4,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A4,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K4" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A4,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A4,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72433,43 +72613,43 @@
         </is>
       </c>
       <c r="B5" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A5)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A5)</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A5,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A5,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1205,A5,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A5,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B5-COUNTIFS('架電リスト'!$B$5:$B$1208,A5,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A5,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A5,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A5,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A5,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A5,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A5,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A5,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A5,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A5,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72480,43 +72660,43 @@
         </is>
       </c>
       <c r="B6" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A6)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A6)</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A6,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A6,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1205,A6,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A6,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B6-COUNTIFS('架電リスト'!$B$5:$B$1208,A6,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A6,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A6,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A6,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A6,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A6,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A6,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A6,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A6,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A6,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72527,43 +72707,43 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A7)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A7)</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A7,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A7,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1205,A7,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A7,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B7-COUNTIFS('架電リスト'!$B$5:$B$1208,A7,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A7,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A7,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A7,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A7,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A7,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A7,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A7,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A7,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A7,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72574,43 +72754,43 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A8)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A8)</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A8,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A8,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1205,A8,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A8,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B8-COUNTIFS('架電リスト'!$B$5:$B$1208,A8,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A8,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A8,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A8,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A8,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A8,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A8,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A8,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A8,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A8,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72621,43 +72801,43 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A9)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A9)</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A9,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A9,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1205,A9,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A9,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B9-COUNTIFS('架電リスト'!$B$5:$B$1208,A9,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A9,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A9,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A9,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A9,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A9,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A9,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A9,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A9,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A9,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72668,43 +72848,43 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A10)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A10)</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A10,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A10,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1205,A10,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A10,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B10-COUNTIFS('架電リスト'!$B$5:$B$1208,A10,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A10,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A10,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A10,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A10,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A10,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A10,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A10,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A10,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A10,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72715,43 +72895,43 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A11)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A11)</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A11,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A11,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1205,A11,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A11,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B11-COUNTIFS('架電リスト'!$B$5:$B$1208,A11,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A11,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A11,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A11,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A11,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A11,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A11,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A11,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A11,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A11,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72762,43 +72942,43 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A12)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A12)</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A12,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A12,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1205,A12,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A12,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B12-COUNTIFS('架電リスト'!$B$5:$B$1208,A12,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A12,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A12,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A12,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A12,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A12,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A12,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A12,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A12,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A12,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72809,43 +72989,43 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A13)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A13)</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A13,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A13,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1205,A13,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A13,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B13-COUNTIFS('架電リスト'!$B$5:$B$1208,A13,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A13,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A13,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A13,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A13,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A13,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A13,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A13,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A13,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A13,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72856,43 +73036,43 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A14)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A14)</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A14,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A14,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1205,A14,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A14,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B14-COUNTIFS('架電リスト'!$B$5:$B$1208,A14,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A14,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A14,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A14,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A14,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A14,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A14,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A14,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A14,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A14,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72903,43 +73083,43 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A15)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A15)</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A15,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A15,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1205,A15,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A15,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B15-COUNTIFS('架電リスト'!$B$5:$B$1208,A15,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A15,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A15,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A15,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A15,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A15,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A15,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A15,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A15,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A15,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72950,43 +73130,43 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A16)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A16)</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A16,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A16,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1205,A16,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A16,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B16-COUNTIFS('架電リスト'!$B$5:$B$1208,A16,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A16,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A16,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A16,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A16,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A16,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A16,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A16,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A16,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A16,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -72997,43 +73177,43 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A17)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A17)</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A17,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A17,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1205,A17,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A17,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B17-COUNTIFS('架電リスト'!$B$5:$B$1208,A17,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A17,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A17,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A17,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A17,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A17,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A17,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A17,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A17,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A17,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73044,43 +73224,43 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A18)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A18)</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A18,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A18,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1205,A18,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A18,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B18-COUNTIFS('架電リスト'!$B$5:$B$1208,A18,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1208,A18,'架電リスト'!$J$5:$J$1208,"")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"不在・折返し待ち")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A18,'架電リスト'!$J$5:$J$1208,"不在・折返し待ち")</f>
         <v/>
       </c>
       <c r="F18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"担当者不在")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A18,'架電リスト'!$J$5:$J$1208,"担当者不在")</f>
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"資料送付")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A18,'架電リスト'!$J$5:$J$1208,"資料送付")</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"アポ獲得")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A18,'架電リスト'!$J$5:$J$1208,"アポ獲得")</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"検討中")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A18,'架電リスト'!$J$5:$J$1208,"検討中")</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"NG")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A18,'架電リスト'!$J$5:$J$1208,"NG")</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,$A18,'架電リスト'!$J$5:$J$1205,"番号不明")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,$A18,'架電リスト'!$J$5:$J$1208,"番号不明")</f>
         <v/>
       </c>
     </row>
@@ -73091,43 +73271,43 @@
         </is>
       </c>
       <c r="B19" s="16">
-        <f>COUNTIF('架電リスト'!$B$5:$B$1205,A19)</f>
+        <f>COUNTIF('架電リスト'!$B$5:$B$1208,A19)</f>
         <v/>
       </c>
       <c r="C19" s="16">
-        <f>COUNTIFS('架電リスト'!$B$5:$B$1205,A19,'架電リスト'!$E$5:$E$1205,"&lt;&gt;")</f>
+        <f>COUNTIFS('架電リスト'!$B$5:$B$1208,A19,'架電リスト'!$E$5:$E$1208,"&lt;&gt;")</f>
         <v/>
       </c>
       <c r="D19" s="16">
-        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1205,A19,'架電リスト'!$J$5:$J$1205,"未架電")-COUNTIFS('架電リスト'!$B$5:$B$1205,A19,'架電リスト'!$J$5:$J$1205,"")</f>
+        <f>B19-COUNTIFS('架電リスト'!$B$5:$B$1208,A19,'架電リスト'!$J$5:$J$1208,"未架電")-COUNTI